--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -608,7 +608,7 @@
         <v>-2.23</v>
       </c>
       <c r="I2" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J2" t="n">
         <v>1.96</v>
@@ -687,7 +687,7 @@
         <v>0.91</v>
       </c>
       <c r="I3" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J3" t="n">
         <v>1.98</v>
@@ -762,7 +762,7 @@
         <v>-7.24</v>
       </c>
       <c r="I4" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J4" t="n">
         <v>1.99</v>
@@ -841,7 +841,7 @@
         <v>-0.98</v>
       </c>
       <c r="I5" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J5" t="n">
         <v>2</v>
@@ -916,7 +916,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J6" t="n">
         <v>2.01</v>
@@ -991,7 +991,7 @@
         <v>4.43</v>
       </c>
       <c r="I7" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J7" t="n">
         <v>2.03</v>
@@ -1066,7 +1066,7 @@
         <v>-6.6</v>
       </c>
       <c r="I8" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J8" t="n">
         <v>2.04</v>
@@ -1145,7 +1145,7 @@
         <v>-3.54</v>
       </c>
       <c r="I9" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J9" t="n">
         <v>2.05</v>
@@ -1220,7 +1220,7 @@
         <v>5.24</v>
       </c>
       <c r="I10" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J10" t="n">
         <v>2.06</v>
@@ -1295,7 +1295,7 @@
         <v>3.98</v>
       </c>
       <c r="I11" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J11" t="n">
         <v>2.06</v>
@@ -1370,7 +1370,7 @@
         <v>0.48</v>
       </c>
       <c r="I12" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J12" t="n">
         <v>2.07</v>
@@ -1445,7 +1445,7 @@
         <v>-5.71</v>
       </c>
       <c r="I13" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J13" t="n">
         <v>2.06</v>
@@ -1524,7 +1524,7 @@
         <v>5.56</v>
       </c>
       <c r="I14" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J14" t="n">
         <v>2.07</v>
@@ -1599,7 +1599,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J15" t="n">
         <v>2.08</v>
@@ -1674,7 +1674,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J16" t="n">
         <v>2.08</v>
@@ -1749,7 +1749,7 @@
         <v>6.7</v>
       </c>
       <c r="I17" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J17" t="n">
         <v>2.09</v>
@@ -1824,7 +1824,7 @@
         <v>1.79</v>
       </c>
       <c r="I18" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J18" t="n">
         <v>2.1</v>
@@ -1899,13 +1899,13 @@
         <v>3.96</v>
       </c>
       <c r="I19" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J19" t="n">
         <v>2.11</v>
       </c>
       <c r="K19" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="L19" t="n">
         <v>2.59</v>
@@ -1974,7 +1974,7 @@
         <v>3.81</v>
       </c>
       <c r="I20" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J20" t="n">
         <v>2.13</v>
@@ -2049,7 +2049,7 @@
         <v>1.22</v>
       </c>
       <c r="I21" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J21" t="n">
         <v>2.14</v>
@@ -2124,7 +2124,7 @@
         <v>-4.84</v>
       </c>
       <c r="I22" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J22" t="n">
         <v>2.15</v>
@@ -2199,7 +2199,7 @@
         <v>-0.42</v>
       </c>
       <c r="I23" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J23" t="n">
         <v>2.15</v>
@@ -2274,13 +2274,13 @@
         <v>0.43</v>
       </c>
       <c r="I24" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J24" t="n">
         <v>2.17</v>
       </c>
       <c r="K24" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="L24" t="n">
         <v>2.53</v>
@@ -2349,7 +2349,7 @@
         <v>1.69</v>
       </c>
       <c r="I25" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J25" t="n">
         <v>2.19</v>
@@ -2424,7 +2424,7 @@
         <v>-10</v>
       </c>
       <c r="I26" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J26" t="n">
         <v>2.19</v>
@@ -2503,7 +2503,7 @@
         <v>-6.94</v>
       </c>
       <c r="I27" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J27" t="n">
         <v>2.19</v>
@@ -2582,7 +2582,7 @@
         <v>-1.49</v>
       </c>
       <c r="I28" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J28" t="n">
         <v>2.19</v>
@@ -2657,7 +2657,7 @@
         <v>1.01</v>
       </c>
       <c r="I29" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J29" t="n">
         <v>2.19</v>
@@ -2732,7 +2732,7 @@
         <v>8</v>
       </c>
       <c r="I30" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J30" t="n">
         <v>2.2</v>
@@ -2807,7 +2807,7 @@
         <v>-5.56</v>
       </c>
       <c r="I31" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J31" t="n">
         <v>2.2</v>
@@ -2886,7 +2886,7 @@
         <v>3.43</v>
       </c>
       <c r="I32" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J32" t="n">
         <v>2.2</v>
@@ -2961,7 +2961,7 @@
         <v>-8.529999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J33" t="n">
         <v>2.2</v>
@@ -3044,7 +3044,7 @@
         <v>3.11</v>
       </c>
       <c r="I34" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J34" t="n">
         <v>2.19</v>
@@ -3123,7 +3123,7 @@
         <v>7.04</v>
       </c>
       <c r="I35" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J35" t="n">
         <v>2.19</v>
@@ -3198,7 +3198,7 @@
         <v>-3.76</v>
       </c>
       <c r="I36" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J36" t="n">
         <v>2.19</v>
@@ -3277,7 +3277,7 @@
         <v>4.88</v>
       </c>
       <c r="I37" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J37" t="n">
         <v>2.19</v>
@@ -3352,7 +3352,7 @@
         <v>8.84</v>
       </c>
       <c r="I38" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J38" t="n">
         <v>2.19</v>
@@ -3427,7 +3427,7 @@
         <v>-4.7</v>
       </c>
       <c r="I39" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J39" t="n">
         <v>2.18</v>
@@ -3502,7 +3502,7 @@
         <v>1.35</v>
       </c>
       <c r="I40" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J40" t="n">
         <v>2.17</v>
@@ -3577,7 +3577,7 @@
         <v>-2.65</v>
       </c>
       <c r="I41" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J41" t="n">
         <v>2.16</v>
@@ -3652,7 +3652,7 @@
         <v>0.91</v>
       </c>
       <c r="I42" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J42" t="n">
         <v>2.15</v>
@@ -3727,7 +3727,7 @@
         <v>2.25</v>
       </c>
       <c r="I43" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J43" t="n">
         <v>2.15</v>
@@ -3802,7 +3802,7 @@
         <v>-1.32</v>
       </c>
       <c r="I44" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J44" t="n">
         <v>2.14</v>
@@ -3877,7 +3877,7 @@
         <v>-1.34</v>
       </c>
       <c r="I45" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J45" t="n">
         <v>2.13</v>
@@ -3952,7 +3952,7 @@
         <v>-1.81</v>
       </c>
       <c r="I46" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J46" t="n">
         <v>2.13</v>
@@ -4027,7 +4027,7 @@
         <v>-9.220000000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J47" t="n">
         <v>2.13</v>
@@ -4106,7 +4106,7 @@
         <v>-4.06</v>
       </c>
       <c r="I48" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J48" t="n">
         <v>2.13</v>
@@ -4181,7 +4181,7 @@
         <v>4.76</v>
       </c>
       <c r="I49" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J49" t="n">
         <v>2.13</v>
@@ -4256,7 +4256,7 @@
         <v>-1.01</v>
       </c>
       <c r="I50" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J50" t="n">
         <v>2.12</v>
@@ -4331,7 +4331,7 @@
         <v>-8.67</v>
       </c>
       <c r="I51" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J51" t="n">
         <v>2.1</v>
@@ -4410,7 +4410,7 @@
         <v>-10.61</v>
       </c>
       <c r="I52" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J52" t="n">
         <v>2.08</v>
@@ -4493,7 +4493,7 @@
         <v>-3.12</v>
       </c>
       <c r="I53" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J53" t="n">
         <v>2.06</v>
@@ -4576,7 +4576,7 @@
         <v>-10.32</v>
       </c>
       <c r="I54" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J54" t="n">
         <v>2.03</v>
@@ -4659,7 +4659,7 @@
         <v>24.46</v>
       </c>
       <c r="I55" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J55" t="n">
         <v>2.01</v>
@@ -4738,7 +4738,7 @@
         <v>-6.94</v>
       </c>
       <c r="I56" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J56" t="n">
         <v>1.99</v>
@@ -4817,7 +4817,7 @@
         <v>14.29</v>
       </c>
       <c r="I57" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J57" t="n">
         <v>1.97</v>
@@ -4896,7 +4896,7 @@
         <v>-0.54</v>
       </c>
       <c r="I58" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J58" t="n">
         <v>1.95</v>
@@ -4971,7 +4971,7 @@
         <v>0.55</v>
       </c>
       <c r="I59" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J59" t="n">
         <v>1.93</v>
@@ -5046,7 +5046,7 @@
         <v>-2.17</v>
       </c>
       <c r="I60" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J60" t="n">
         <v>1.9</v>
@@ -5125,7 +5125,7 @@
         <v>1.67</v>
       </c>
       <c r="I61" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J61" t="n">
         <v>1.89</v>
@@ -5204,7 +5204,7 @@
         <v>0.55</v>
       </c>
       <c r="I62" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J62" t="n">
         <v>1.87</v>
@@ -5279,7 +5279,7 @@
         <v>2.17</v>
       </c>
       <c r="I63" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J63" t="n">
         <v>1.85</v>
@@ -5354,7 +5354,7 @@
         <v>3.72</v>
       </c>
       <c r="I64" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J64" t="n">
         <v>1.83</v>
@@ -5433,7 +5433,7 @@
         <v>2.05</v>
       </c>
       <c r="I65" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J65" t="n">
         <v>1.82</v>
@@ -5508,7 +5508,7 @@
         <v>-0.5</v>
       </c>
       <c r="I66" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J66" t="n">
         <v>1.81</v>
@@ -5583,7 +5583,7 @@
         <v>-1.01</v>
       </c>
       <c r="I67" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J67" t="n">
         <v>1.81</v>
@@ -5658,7 +5658,7 @@
         <v>2.55</v>
       </c>
       <c r="I68" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J68" t="n">
         <v>1.82</v>
@@ -5733,7 +5733,7 @@
         <v>0.5</v>
       </c>
       <c r="I69" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J69" t="n">
         <v>1.82</v>
@@ -5808,7 +5808,7 @@
         <v>-2.97</v>
       </c>
       <c r="I70" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J70" t="n">
         <v>1.82</v>
@@ -5883,7 +5883,7 @@
         <v>10.71</v>
       </c>
       <c r="I71" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J71" t="n">
         <v>1.84</v>
@@ -5958,7 +5958,7 @@
         <v>4.15</v>
       </c>
       <c r="I72" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J72" t="n">
         <v>1.87</v>
@@ -6033,7 +6033,7 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J73" t="n">
         <v>1.91</v>
@@ -6108,7 +6108,7 @@
         <v>-3.54</v>
       </c>
       <c r="I74" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J74" t="n">
         <v>1.95</v>
@@ -6183,7 +6183,7 @@
         <v>-3.21</v>
       </c>
       <c r="I75" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J75" t="n">
         <v>1.97</v>
@@ -6258,7 +6258,7 @@
         <v>2.84</v>
       </c>
       <c r="I76" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J76" t="n">
         <v>1.99</v>
@@ -6333,7 +6333,7 @@
         <v>1.38</v>
       </c>
       <c r="I77" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J77" t="n">
         <v>2.01</v>
@@ -6408,7 +6408,7 @@
         <v>0.45</v>
       </c>
       <c r="I78" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J78" t="n">
         <v>2.03</v>
@@ -6483,7 +6483,7 @@
         <v>2.71</v>
       </c>
       <c r="I79" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J79" t="n">
         <v>2.05</v>
@@ -6558,7 +6558,7 @@
         <v>0.88</v>
       </c>
       <c r="I80" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J80" t="n">
         <v>2.08</v>
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J81" t="n">
         <v>2.1</v>
@@ -6708,7 +6708,7 @@
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J82" t="n">
         <v>2.12</v>
@@ -6783,7 +6783,7 @@
         <v>-2.18</v>
       </c>
       <c r="I83" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J83" t="n">
         <v>2.14</v>
@@ -6858,7 +6858,7 @@
         <v>3.57</v>
       </c>
       <c r="I84" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J84" t="n">
         <v>2.16</v>
@@ -6933,7 +6933,7 @@
         <v>-3.88</v>
       </c>
       <c r="I85" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J85" t="n">
         <v>2.17</v>
@@ -7008,7 +7008,7 @@
         <v>3.14</v>
       </c>
       <c r="I86" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J86" t="n">
         <v>2.19</v>
@@ -7083,7 +7083,7 @@
         <v>4.78</v>
       </c>
       <c r="I87" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J87" t="n">
         <v>2.21</v>
@@ -7158,7 +7158,7 @@
         <v>3.73</v>
       </c>
       <c r="I88" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J88" t="n">
         <v>2.23</v>
@@ -7233,7 +7233,7 @@
         <v>5.2</v>
       </c>
       <c r="I89" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J89" t="n">
         <v>2.26</v>
@@ -7308,7 +7308,7 @@
         <v>-5.7</v>
       </c>
       <c r="I90" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J90" t="n">
         <v>2.29</v>
@@ -7383,7 +7383,7 @@
         <v>5.65</v>
       </c>
       <c r="I91" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J91" t="n">
         <v>2.31</v>
@@ -7458,7 +7458,7 @@
         <v>1.15</v>
       </c>
       <c r="I92" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J92" t="n">
         <v>2.33</v>
@@ -7533,7 +7533,7 @@
         <v>9.43</v>
       </c>
       <c r="I93" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J93" t="n">
         <v>2.36</v>
@@ -7608,7 +7608,7 @@
         <v>6.55</v>
       </c>
       <c r="I94" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J94" t="n">
         <v>2.41</v>
@@ -7683,7 +7683,7 @@
         <v>0.65</v>
       </c>
       <c r="I95" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J95" t="n">
         <v>2.46</v>
@@ -7758,7 +7758,7 @@
         <v>4.5</v>
       </c>
       <c r="I96" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J96" t="n">
         <v>2.51</v>
@@ -7833,7 +7833,7 @@
         <v>-1.54</v>
       </c>
       <c r="I97" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J97" t="n">
         <v>2.56</v>
@@ -7908,7 +7908,7 @@
         <v>3.75</v>
       </c>
       <c r="I98" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J98" t="n">
         <v>2.62</v>
@@ -7983,7 +7983,7 @@
         <v>3.31</v>
       </c>
       <c r="I99" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J99" t="n">
         <v>2.68</v>
@@ -8058,7 +8058,7 @@
         <v>-5.83</v>
       </c>
       <c r="I100" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J100" t="n">
         <v>2.72</v>
@@ -8133,7 +8133,7 @@
         <v>8.050000000000001</v>
       </c>
       <c r="I101" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J101" t="n">
         <v>2.78</v>
@@ -8208,7 +8208,7 @@
         <v>-6.88</v>
       </c>
       <c r="I102" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J102" t="n">
         <v>2.83</v>
@@ -8283,7 +8283,7 @@
         <v>5.23</v>
       </c>
       <c r="I103" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J103" t="n">
         <v>2.89</v>
@@ -8358,7 +8358,7 @@
         <v>2.92</v>
       </c>
       <c r="I104" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J104" t="n">
         <v>2.95</v>
@@ -8433,7 +8433,7 @@
         <v>3.69</v>
       </c>
       <c r="I105" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J105" t="n">
         <v>3.02</v>
@@ -8508,7 +8508,7 @@
         <v>14.25</v>
       </c>
       <c r="I106" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J106" t="n">
         <v>3.12</v>
@@ -8583,7 +8583,7 @@
         <v>-1.2</v>
       </c>
       <c r="I107" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J107" t="n">
         <v>3.2</v>
@@ -8658,7 +8658,7 @@
         <v>-1.94</v>
       </c>
       <c r="I108" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J108" t="n">
         <v>3.28</v>
@@ -8733,7 +8733,7 @@
         <v>-4.95</v>
       </c>
       <c r="I109" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J109" t="n">
         <v>3.34</v>
@@ -8808,7 +8808,7 @@
         <v>4.17</v>
       </c>
       <c r="I110" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J110" t="n">
         <v>3.42</v>
@@ -8883,13 +8883,13 @@
         <v>-0.5</v>
       </c>
       <c r="I111" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J111" t="n">
         <v>3.48</v>
       </c>
       <c r="K111" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="L111" t="n">
         <v>2.33</v>
@@ -8958,7 +8958,7 @@
         <v>1.26</v>
       </c>
       <c r="I112" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J112" t="n">
         <v>3.55</v>
@@ -9033,7 +9033,7 @@
         <v>2.73</v>
       </c>
       <c r="I113" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J113" t="n">
         <v>3.61</v>
@@ -9108,7 +9108,7 @@
         <v>-10.39</v>
       </c>
       <c r="I114" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J114" t="n">
         <v>3.65</v>
@@ -9183,7 +9183,7 @@
         <v>8.09</v>
       </c>
       <c r="I115" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J115" t="n">
         <v>3.69</v>
@@ -9258,7 +9258,7 @@
         <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J116" t="n">
         <v>3.73</v>
@@ -9333,7 +9333,7 @@
         <v>4.49</v>
       </c>
       <c r="I117" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J117" t="n">
         <v>3.78</v>
@@ -9408,7 +9408,7 @@
         <v>-2.39</v>
       </c>
       <c r="I118" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J118" t="n">
         <v>3.82</v>
@@ -9483,7 +9483,7 @@
         <v>2.44</v>
       </c>
       <c r="I119" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J119" t="n">
         <v>3.85</v>
@@ -9558,7 +9558,7 @@
         <v>-0.48</v>
       </c>
       <c r="I120" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J120" t="n">
         <v>3.9</v>
@@ -9633,7 +9633,7 @@
         <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J121" t="n">
         <v>3.94</v>
@@ -9708,7 +9708,7 @@
         <v>-0.24</v>
       </c>
       <c r="I122" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J122" t="n">
         <v>3.98</v>
@@ -9783,7 +9783,7 @@
         <v>-2.64</v>
       </c>
       <c r="I123" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J123" t="n">
         <v>4.01</v>
@@ -9858,7 +9858,7 @@
         <v>5.93</v>
       </c>
       <c r="I124" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J124" t="n">
         <v>4.05</v>
@@ -9933,7 +9933,7 @@
         <v>-3.73</v>
       </c>
       <c r="I125" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J125" t="n">
         <v>4.07</v>
@@ -10008,7 +10008,7 @@
         <v>3.63</v>
       </c>
       <c r="I126" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J126" t="n">
         <v>4.08</v>
@@ -10083,7 +10083,7 @@
         <v>-2.1</v>
       </c>
       <c r="I127" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J127" t="n">
         <v>4.08</v>
@@ -10158,7 +10158,7 @@
         <v>-0.48</v>
       </c>
       <c r="I128" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J128" t="n">
         <v>4.09</v>
@@ -10233,7 +10233,7 @@
         <v>-2.16</v>
       </c>
       <c r="I129" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J129" t="n">
         <v>4.1</v>
@@ -10312,7 +10312,7 @@
         <v>3.19</v>
       </c>
       <c r="I130" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J130" t="n">
         <v>4.11</v>
@@ -10387,7 +10387,7 @@
         <v>0.95</v>
       </c>
       <c r="I131" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J131" t="n">
         <v>4.13</v>
@@ -10462,7 +10462,7 @@
         <v>-3.76</v>
       </c>
       <c r="I132" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J132" t="n">
         <v>4.13</v>
@@ -10541,7 +10541,7 @@
         <v>-9.050000000000001</v>
       </c>
       <c r="I133" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J133" t="n">
         <v>4.11</v>
@@ -10616,7 +10616,7 @@
         <v>7.26</v>
       </c>
       <c r="I134" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J134" t="n">
         <v>4.12</v>
@@ -10691,7 +10691,7 @@
         <v>2.26</v>
       </c>
       <c r="I135" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J135" t="n">
         <v>4.13</v>
@@ -10766,7 +10766,7 @@
         <v>0.98</v>
       </c>
       <c r="I136" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J136" t="n">
         <v>4.13</v>
@@ -10841,7 +10841,7 @@
         <v>0.97</v>
       </c>
       <c r="I137" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J137" t="n">
         <v>4.13</v>
@@ -10916,7 +10916,7 @@
         <v>0.24</v>
       </c>
       <c r="I138" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J138" t="n">
         <v>4.13</v>
@@ -10991,7 +10991,7 @@
         <v>-1.92</v>
       </c>
       <c r="I139" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J139" t="n">
         <v>4.13</v>
@@ -11070,7 +11070,7 @@
         <v>4.16</v>
       </c>
       <c r="I140" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J140" t="n">
         <v>4.13</v>
@@ -11145,7 +11145,7 @@
         <v>2.58</v>
       </c>
       <c r="I141" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J141" t="n">
         <v>4.14</v>
@@ -11220,7 +11220,7 @@
         <v>-4.12</v>
       </c>
       <c r="I142" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J142" t="n">
         <v>4.14</v>
@@ -11295,7 +11295,7 @@
         <v>-1.19</v>
       </c>
       <c r="I143" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J143" t="n">
         <v>4.15</v>
@@ -11374,7 +11374,7 @@
         <v>-2.42</v>
       </c>
       <c r="I144" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J144" t="n">
         <v>4.14</v>
@@ -11449,7 +11449,7 @@
         <v>-5.45</v>
       </c>
       <c r="I145" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J145" t="n">
         <v>4.12</v>
@@ -11524,7 +11524,7 @@
         <v>-0.52</v>
       </c>
       <c r="I146" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J146" t="n">
         <v>4.1</v>
@@ -11599,7 +11599,7 @@
         <v>-0.79</v>
       </c>
       <c r="I147" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J147" t="n">
         <v>4.08</v>
@@ -11678,7 +11678,7 @@
         <v>9.81</v>
       </c>
       <c r="I148" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J148" t="n">
         <v>4.07</v>
@@ -11753,7 +11753,7 @@
         <v>-3.38</v>
       </c>
       <c r="I149" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J149" t="n">
         <v>4.07</v>
@@ -11832,7 +11832,7 @@
         <v>-1.5</v>
       </c>
       <c r="I150" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J150" t="n">
         <v>4.06</v>
@@ -11907,7 +11907,7 @@
         <v>0.51</v>
       </c>
       <c r="I151" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J151" t="n">
         <v>4.04</v>
@@ -11982,7 +11982,7 @@
         <v>4.55</v>
       </c>
       <c r="I152" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J152" t="n">
         <v>4.04</v>
@@ -12057,7 +12057,7 @@
         <v>-5.56</v>
       </c>
       <c r="I153" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J153" t="n">
         <v>4.05</v>
@@ -12136,7 +12136,7 @@
         <v>-1.53</v>
       </c>
       <c r="I154" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J154" t="n">
         <v>4.05</v>
@@ -12211,7 +12211,7 @@
         <v>3.9</v>
       </c>
       <c r="I155" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J155" t="n">
         <v>4.04</v>
@@ -12286,7 +12286,7 @@
         <v>0.75</v>
       </c>
       <c r="I156" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J156" t="n">
         <v>4.04</v>
@@ -12361,7 +12361,7 @@
         <v>2.23</v>
       </c>
       <c r="I157" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J157" t="n">
         <v>4.04</v>
@@ -12436,7 +12436,7 @@
         <v>1.94</v>
       </c>
       <c r="I158" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J158" t="n">
         <v>4.04</v>
@@ -12511,7 +12511,7 @@
         <v>3.1</v>
       </c>
       <c r="I159" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J159" t="n">
         <v>4.05</v>
@@ -12586,7 +12586,7 @@
         <v>6.93</v>
       </c>
       <c r="I160" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J160" t="n">
         <v>4.07</v>
@@ -12661,7 +12661,7 @@
         <v>4.75</v>
       </c>
       <c r="I161" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J161" t="n">
         <v>4.09</v>
@@ -12736,7 +12736,7 @@
         <v>3.09</v>
       </c>
       <c r="I162" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J162" t="n">
         <v>4.13</v>
@@ -12811,7 +12811,7 @@
         <v>2</v>
       </c>
       <c r="I163" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J163" t="n">
         <v>4.18</v>
@@ -12886,7 +12886,7 @@
         <v>5.69</v>
       </c>
       <c r="I164" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J164" t="n">
         <v>4.25</v>
@@ -12961,7 +12961,7 @@
         <v>-3.34</v>
       </c>
       <c r="I165" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J165" t="n">
         <v>4.32</v>
@@ -13036,7 +13036,7 @@
         <v>3.65</v>
       </c>
       <c r="I166" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J166" t="n">
         <v>4.4</v>
@@ -13111,7 +13111,7 @@
         <v>-2.96</v>
       </c>
       <c r="I167" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J167" t="n">
         <v>4.47</v>
@@ -13186,7 +13186,7 @@
         <v>5.92</v>
       </c>
       <c r="I168" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J168" t="n">
         <v>4.54</v>
@@ -13261,7 +13261,7 @@
         <v>-0.54</v>
       </c>
       <c r="I169" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J169" t="n">
         <v>4.62</v>
@@ -13336,7 +13336,7 @@
         <v>-5.25</v>
       </c>
       <c r="I170" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J170" t="n">
         <v>4.68</v>
@@ -13411,7 +13411,7 @@
         <v>-0.57</v>
       </c>
       <c r="I171" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J171" t="n">
         <v>4.74</v>
@@ -13486,7 +13486,7 @@
         <v>-3.85</v>
       </c>
       <c r="I172" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J172" t="n">
         <v>4.79</v>
@@ -13561,10 +13561,10 @@
         <v>5</v>
       </c>
       <c r="I173" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J173" t="n">
-        <v>4.85</v>
+        <v>4.86</v>
       </c>
       <c r="K173" t="n">
         <v>4.34</v>
@@ -13636,7 +13636,7 @@
         <v>-0.38</v>
       </c>
       <c r="I174" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J174" t="n">
         <v>4.92</v>
@@ -13711,7 +13711,7 @@
         <v>6.5</v>
       </c>
       <c r="I175" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J175" t="n">
         <v>5</v>
@@ -13786,7 +13786,7 @@
         <v>6.1</v>
       </c>
       <c r="I176" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J176" t="n">
         <v>5.1</v>
@@ -13861,7 +13861,7 @@
         <v>1.18</v>
       </c>
       <c r="I177" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J177" t="n">
         <v>5.19</v>
@@ -13936,7 +13936,7 @@
         <v>3.18</v>
       </c>
       <c r="I178" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J178" t="n">
         <v>5.29</v>
@@ -14011,7 +14011,7 @@
         <v>-4.86</v>
       </c>
       <c r="I179" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J179" t="n">
         <v>5.36</v>
@@ -14086,7 +14086,7 @@
         <v>2.73</v>
       </c>
       <c r="I180" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J180" t="n">
         <v>5.44</v>
@@ -14161,7 +14161,7 @@
         <v>-2.65</v>
       </c>
       <c r="I181" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J181" t="n">
         <v>5.49</v>
@@ -14236,7 +14236,7 @@
         <v>-9.710000000000001</v>
       </c>
       <c r="I182" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J182" t="n">
         <v>5.5</v>
@@ -14315,7 +14315,7 @@
         <v>10.38</v>
       </c>
       <c r="I183" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J183" t="n">
         <v>5.54</v>
@@ -14390,7 +14390,7 @@
         <v>-3.25</v>
       </c>
       <c r="I184" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J184" t="n">
         <v>5.55</v>
@@ -14465,7 +14465,7 @@
         <v>8.83</v>
       </c>
       <c r="I185" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J185" t="n">
         <v>5.6</v>
@@ -14540,7 +14540,7 @@
         <v>9.58</v>
       </c>
       <c r="I186" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J186" t="n">
         <v>5.67</v>
@@ -14615,7 +14615,7 @@
         <v>2.07</v>
       </c>
       <c r="I187" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J187" t="n">
         <v>5.75</v>
@@ -14690,7 +14690,7 @@
         <v>6.68</v>
       </c>
       <c r="I188" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J188" t="n">
         <v>5.84</v>
@@ -14765,7 +14765,7 @@
         <v>-6.12</v>
       </c>
       <c r="I189" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J189" t="n">
         <v>5.91</v>
@@ -14840,7 +14840,7 @@
         <v>2.75</v>
       </c>
       <c r="I190" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J190" t="n">
         <v>6</v>
@@ -14915,7 +14915,7 @@
         <v>1.97</v>
       </c>
       <c r="I191" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J191" t="n">
         <v>6.1</v>
@@ -14990,7 +14990,7 @@
         <v>6.64</v>
       </c>
       <c r="I192" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J192" t="n">
         <v>6.24</v>
@@ -15065,7 +15065,7 @@
         <v>7.39</v>
       </c>
       <c r="I193" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J193" t="n">
         <v>6.39</v>
@@ -15140,7 +15140,7 @@
         <v>0.36</v>
       </c>
       <c r="I194" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J194" t="n">
         <v>6.54</v>
@@ -15215,7 +15215,7 @@
         <v>7.82</v>
       </c>
       <c r="I195" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J195" t="n">
         <v>6.71</v>
@@ -15290,7 +15290,7 @@
         <v>-5.02</v>
       </c>
       <c r="I196" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J196" t="n">
         <v>6.84</v>
@@ -15365,7 +15365,7 @@
         <v>5.17</v>
       </c>
       <c r="I197" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J197" t="n">
         <v>6.99</v>
@@ -15440,7 +15440,7 @@
         <v>11.62</v>
       </c>
       <c r="I198" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J198" t="n">
         <v>7.18</v>
@@ -15515,7 +15515,7 @@
         <v>-14.81</v>
       </c>
       <c r="I199" s="4" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J199" s="4" t="n">
         <v>7.32</v>
@@ -15590,7 +15590,7 @@
         <v>2.47</v>
       </c>
       <c r="I200" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J200" t="n">
         <v>7.45</v>
@@ -15665,7 +15665,7 @@
         <v>-9.52</v>
       </c>
       <c r="I201" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J201" t="n">
         <v>7.55</v>
@@ -15740,7 +15740,7 @@
         <v>-5.7</v>
       </c>
       <c r="I202" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J202" t="n">
         <v>7.66</v>
@@ -15819,7 +15819,7 @@
         <v>12.5</v>
       </c>
       <c r="I203" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J203" t="n">
         <v>7.78</v>
@@ -15894,7 +15894,7 @@
         <v>-1.19</v>
       </c>
       <c r="I204" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J204" t="n">
         <v>7.91</v>
@@ -15969,7 +15969,7 @@
         <v>2.06</v>
       </c>
       <c r="I205" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J205" t="n">
         <v>8.029999999999999</v>
@@ -16044,7 +16044,7 @@
         <v>-5.92</v>
       </c>
       <c r="I206" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J206" t="n">
         <v>8.09</v>
@@ -16123,7 +16123,7 @@
         <v>0.38</v>
       </c>
       <c r="I207" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J207" t="n">
         <v>8.140000000000001</v>
@@ -16198,7 +16198,7 @@
         <v>-3.76</v>
       </c>
       <c r="I208" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J208" t="n">
         <v>8.16</v>
@@ -16273,7 +16273,7 @@
         <v>-4.69</v>
       </c>
       <c r="I209" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J209" t="n">
         <v>8.18</v>
@@ -16348,7 +16348,7 @@
         <v>-3.28</v>
       </c>
       <c r="I210" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J210" t="n">
         <v>8.18</v>
@@ -16423,7 +16423,7 @@
         <v>-6.79</v>
       </c>
       <c r="I211" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J211" t="n">
         <v>8.140000000000001</v>
@@ -16502,7 +16502,7 @@
         <v>2.28</v>
       </c>
       <c r="I212" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J212" t="n">
         <v>8.1</v>
@@ -16577,7 +16577,7 @@
         <v>3.71</v>
       </c>
       <c r="I213" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J213" t="n">
         <v>8.029999999999999</v>
@@ -16652,7 +16652,7 @@
         <v>-2</v>
       </c>
       <c r="I214" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J214" t="n">
         <v>7.96</v>
@@ -16727,7 +16727,7 @@
         <v>5.99</v>
       </c>
       <c r="I215" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J215" t="n">
         <v>7.87</v>
@@ -16802,7 +16802,7 @@
         <v>-2.2</v>
       </c>
       <c r="I216" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J216" t="n">
         <v>7.8</v>
@@ -16877,7 +16877,7 @@
         <v>-0.99</v>
       </c>
       <c r="I217" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J217" t="n">
         <v>7.71</v>
@@ -16952,7 +16952,7 @@
         <v>4.69</v>
       </c>
       <c r="I218" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J218" t="n">
         <v>7.58</v>
@@ -17027,7 +17027,7 @@
         <v>2.99</v>
       </c>
       <c r="I219" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J219" t="n">
         <v>7.53</v>
@@ -17102,7 +17102,7 @@
         <v>-3.56</v>
       </c>
       <c r="I220" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J220" t="n">
         <v>7.46</v>
@@ -17181,7 +17181,7 @@
         <v>7.66</v>
       </c>
       <c r="I221" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J221" t="n">
         <v>7.46</v>
@@ -17256,7 +17256,7 @@
         <v>2.41</v>
       </c>
       <c r="I222" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J222" t="n">
         <v>7.49</v>
@@ -17331,7 +17331,7 @@
         <v>1.49</v>
       </c>
       <c r="I223" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J223" t="n">
         <v>7.48</v>
@@ -17406,7 +17406,7 @@
         <v>3.67</v>
       </c>
       <c r="I224" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J224" t="n">
         <v>7.49</v>
@@ -17481,7 +17481,7 @@
         <v>-5.31</v>
       </c>
       <c r="I225" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J225" t="n">
         <v>7.47</v>
@@ -17556,7 +17556,7 @@
         <v>-7.35</v>
       </c>
       <c r="I226" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J226" t="n">
         <v>7.44</v>
@@ -17631,7 +17631,7 @@
         <v>0</v>
       </c>
       <c r="I227" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J227" t="n">
         <v>7.42</v>
@@ -17706,7 +17706,7 @@
         <v>-4.03</v>
       </c>
       <c r="I228" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J228" t="n">
         <v>7.39</v>
@@ -17785,7 +17785,7 @@
         <v>-2.94</v>
       </c>
       <c r="I229" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J229" t="n">
         <v>7.37</v>
@@ -17864,7 +17864,7 @@
         <v>4.91</v>
       </c>
       <c r="I230" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J230" t="n">
         <v>7.38</v>
@@ -17939,7 +17939,7 @@
         <v>4.13</v>
       </c>
       <c r="I231" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J231" t="n">
         <v>7.43</v>
@@ -18014,7 +18014,7 @@
         <v>1.45</v>
       </c>
       <c r="I232" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J232" t="n">
         <v>7.48</v>
@@ -18089,7 +18089,7 @@
         <v>3.26</v>
       </c>
       <c r="I233" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J233" t="n">
         <v>7.53</v>
@@ -18164,7 +18164,7 @@
         <v>5.8</v>
       </c>
       <c r="I234" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J234" t="n">
         <v>7.6</v>
@@ -18239,7 +18239,7 @@
         <v>3.93</v>
       </c>
       <c r="I235" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J235" t="n">
         <v>7.68</v>
@@ -18314,7 +18314,7 @@
         <v>9.06</v>
       </c>
       <c r="I236" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J236" t="n">
         <v>7.8</v>
@@ -18389,7 +18389,7 @@
         <v>-0.53</v>
       </c>
       <c r="I237" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J237" t="n">
         <v>7.92</v>
@@ -18464,7 +18464,7 @@
         <v>-4.02</v>
       </c>
       <c r="I238" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J238" t="n">
         <v>8</v>
@@ -18539,7 +18539,7 @@
         <v>14.76</v>
       </c>
       <c r="I239" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J239" t="n">
         <v>8.15</v>
@@ -18614,7 +18614,7 @@
         <v>7.87</v>
       </c>
       <c r="I240" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J240" t="n">
         <v>8.34</v>
@@ -18689,7 +18689,7 @@
         <v>8.19</v>
       </c>
       <c r="I241" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J241" t="n">
         <v>8.56</v>
@@ -18764,7 +18764,7 @@
         <v>-1.73</v>
       </c>
       <c r="I242" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J242" t="n">
         <v>8.75</v>
@@ -18839,7 +18839,7 @@
         <v>-1.17</v>
       </c>
       <c r="I243" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J243" t="n">
         <v>8.93</v>
@@ -18914,7 +18914,7 @@
         <v>6.01</v>
       </c>
       <c r="I244" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J244" t="n">
         <v>9.130000000000001</v>
@@ -18989,7 +18989,7 @@
         <v>0.48</v>
       </c>
       <c r="I245" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J245" t="n">
         <v>9.359999999999999</v>
@@ -19064,7 +19064,7 @@
         <v>-4.05</v>
       </c>
       <c r="I246" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J246" t="n">
         <v>9.59</v>
@@ -19139,7 +19139,7 @@
         <v>5.72</v>
       </c>
       <c r="I247" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J247" t="n">
         <v>9.859999999999999</v>
@@ -19214,7 +19214,7 @@
         <v>4</v>
       </c>
       <c r="I248" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J248" t="n">
         <v>10.17</v>
@@ -19289,7 +19289,7 @@
         <v>3.17</v>
       </c>
       <c r="I249" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J249" t="n">
         <v>10.5</v>
@@ -19364,7 +19364,7 @@
         <v>-3.51</v>
       </c>
       <c r="I250" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J250" t="n">
         <v>10.8</v>
@@ -19439,7 +19439,7 @@
         <v>12.57</v>
       </c>
       <c r="I251" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J251" t="n">
         <v>11.17</v>
@@ -19514,7 +19514,7 @@
         <v>1.01</v>
       </c>
       <c r="I252" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J252" t="n">
         <v>11.53</v>
@@ -19589,7 +19589,7 @@
         <v>4.99</v>
       </c>
       <c r="I253" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J253" t="n">
         <v>11.92</v>
@@ -19664,7 +19664,7 @@
         <v>-1.46</v>
       </c>
       <c r="I254" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J254" t="n">
         <v>12.28</v>
@@ -19739,7 +19739,7 @@
         <v>13.38</v>
       </c>
       <c r="I255" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J255" t="n">
         <v>12.73</v>
@@ -19814,7 +19814,7 @@
         <v>7.21</v>
       </c>
       <c r="I256" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J256" t="n">
         <v>13.2</v>
@@ -19889,7 +19889,7 @@
         <v>-2.7</v>
       </c>
       <c r="I257" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J257" t="n">
         <v>13.64</v>
@@ -19964,7 +19964,7 @@
         <v>-5.39</v>
       </c>
       <c r="I258" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J258" t="n">
         <v>14.06</v>
@@ -20039,7 +20039,7 @@
         <v>-3.16</v>
       </c>
       <c r="I259" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J259" t="n">
         <v>14.38</v>
@@ -20114,7 +20114,7 @@
         <v>7.78</v>
       </c>
       <c r="I260" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J260" t="n">
         <v>14.72</v>
@@ -20189,7 +20189,7 @@
         <v>-9.199999999999999</v>
       </c>
       <c r="I261" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J261" t="n">
         <v>14.94</v>
@@ -20264,7 +20264,7 @@
         <v>-0.61</v>
       </c>
       <c r="I262" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J262" t="n">
         <v>15.16</v>
@@ -20339,7 +20339,7 @@
         <v>10.87</v>
       </c>
       <c r="I263" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J263" t="n">
         <v>15.48</v>
@@ -20414,7 +20414,7 @@
         <v>3.36</v>
       </c>
       <c r="I264" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J264" t="n">
         <v>15.79</v>
@@ -20489,7 +20489,7 @@
         <v>-3.57</v>
       </c>
       <c r="I265" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J265" t="n">
         <v>16.07</v>
@@ -20564,7 +20564,7 @@
         <v>14.14</v>
       </c>
       <c r="I266" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J266" t="n">
         <v>16.5</v>
@@ -20639,7 +20639,7 @@
         <v>1.06</v>
       </c>
       <c r="I267" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J267" t="n">
         <v>16.9</v>
@@ -20714,7 +20714,7 @@
         <v>7.14</v>
       </c>
       <c r="I268" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J268" t="n">
         <v>17.36</v>
@@ -20789,7 +20789,7 @@
         <v>-6.79</v>
       </c>
       <c r="I269" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J269" t="n">
         <v>17.72</v>
@@ -20864,7 +20864,7 @@
         <v>4.46</v>
       </c>
       <c r="I270" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J270" t="n">
         <v>18.15</v>
@@ -20939,7 +20939,7 @@
         <v>5</v>
       </c>
       <c r="I271" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J271" t="n">
         <v>18.55</v>
@@ -21014,7 +21014,7 @@
         <v>14.65</v>
       </c>
       <c r="I272" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J272" t="n">
         <v>19.1</v>
@@ -21089,7 +21089,7 @@
         <v>-5.03</v>
       </c>
       <c r="I273" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J273" t="n">
         <v>19.56</v>
@@ -21164,7 +21164,7 @@
         <v>10.96</v>
       </c>
       <c r="I274" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J274" t="n">
         <v>20.17</v>
@@ -21239,7 +21239,7 @@
         <v>9.08</v>
       </c>
       <c r="I275" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J275" t="n">
         <v>20.79</v>
@@ -21314,7 +21314,7 @@
         <v>2.79</v>
       </c>
       <c r="I276" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J276" t="n">
         <v>21.4</v>
@@ -21389,7 +21389,7 @@
         <v>1.65</v>
       </c>
       <c r="I277" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J277" t="n">
         <v>22.05</v>
@@ -21464,7 +21464,7 @@
         <v>-7.15</v>
       </c>
       <c r="I278" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J278" t="n">
         <v>22.64</v>
@@ -21539,7 +21539,7 @@
         <v>-31.09</v>
       </c>
       <c r="I279" s="4" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J279" s="4" t="n">
         <v>22.81</v>
@@ -21618,7 +21618,7 @@
         <v>4.37</v>
       </c>
       <c r="I280" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J280" t="n">
         <v>22.95</v>
@@ -21693,7 +21693,7 @@
         <v>-18.45</v>
       </c>
       <c r="I281" s="4" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J281" s="4" t="n">
         <v>22.99</v>
@@ -21768,7 +21768,7 @@
         <v>1.52</v>
       </c>
       <c r="I282" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J282" t="n">
         <v>23.04</v>
@@ -21847,7 +21847,7 @@
         <v>15.68</v>
       </c>
       <c r="I283" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J283" t="n">
         <v>23.14</v>
@@ -21922,7 +21922,7 @@
         <v>-7.25</v>
       </c>
       <c r="I284" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J284" t="n">
         <v>23.13</v>
@@ -21997,7 +21997,7 @@
         <v>5.46</v>
       </c>
       <c r="I285" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J285" t="n">
         <v>23.21</v>
@@ -22072,7 +22072,7 @@
         <v>-20.25</v>
       </c>
       <c r="I286" s="4" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J286" s="4" t="n">
         <v>22.97</v>
@@ -22145,7 +22145,7 @@
         <v>0.64</v>
       </c>
       <c r="I287" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J287" t="n">
         <v>22.71</v>
@@ -22224,7 +22224,7 @@
         <v>21</v>
       </c>
       <c r="I288" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J288" t="n">
         <v>22.55</v>
@@ -22299,7 +22299,7 @@
         <v>3.4</v>
       </c>
       <c r="I289" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J289" t="n">
         <v>22.5</v>
@@ -22374,7 +22374,7 @@
         <v>-5.01</v>
       </c>
       <c r="I290" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J290" t="n">
         <v>22.35</v>
@@ -22449,7 +22449,7 @@
         <v>5.8</v>
       </c>
       <c r="I291" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J291" t="n">
         <v>22.2</v>
@@ -22524,7 +22524,7 @@
         <v>-19.32</v>
       </c>
       <c r="I292" s="4" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J292" s="4" t="n">
         <v>21.69</v>
@@ -22607,7 +22607,7 @@
         <v>17.71</v>
       </c>
       <c r="I293" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J293" t="n">
         <v>21.39</v>
@@ -22682,7 +22682,7 @@
         <v>-11.12</v>
       </c>
       <c r="I294" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J294" t="n">
         <v>20.85</v>
@@ -22761,7 +22761,7 @@
         <v>-2.38</v>
       </c>
       <c r="I295" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J295" t="n">
         <v>20.16</v>
@@ -22836,7 +22836,7 @@
         <v>-17.58</v>
       </c>
       <c r="I296" s="4" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J296" s="4" t="n">
         <v>19.28</v>
@@ -22911,7 +22911,7 @@
         <v>1.48</v>
       </c>
       <c r="I297" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J297" t="n">
         <v>18.39</v>
@@ -22990,7 +22990,7 @@
         <v>-11.24</v>
       </c>
       <c r="I298" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J298" t="n">
         <v>17.54</v>
@@ -23069,7 +23069,7 @@
         <v>16.86</v>
       </c>
       <c r="I299" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J299" t="n">
         <v>17.24</v>
@@ -23144,7 +23144,7 @@
         <v>7.67</v>
       </c>
       <c r="I300" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J300" t="n">
         <v>16.96</v>
@@ -23219,7 +23219,7 @@
         <v>-7.78</v>
       </c>
       <c r="I301" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J301" t="n">
         <v>16.8</v>
@@ -23294,7 +23294,7 @@
         <v>7.02</v>
       </c>
       <c r="I302" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J302" t="n">
         <v>16.69</v>
@@ -23369,7 +23369,7 @@
         <v>2.98</v>
       </c>
       <c r="I303" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J303" t="n">
         <v>16.46</v>
@@ -23448,7 +23448,7 @@
         <v>30.23</v>
       </c>
       <c r="I304" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J304" t="n">
         <v>16.54</v>
@@ -23523,7 +23523,7 @@
         <v>-1.38</v>
       </c>
       <c r="I305" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J305" t="n">
         <v>16.55</v>
@@ -23598,7 +23598,7 @@
         <v>-1.35</v>
       </c>
       <c r="I306" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J306" t="n">
         <v>16.75</v>
@@ -23673,7 +23673,7 @@
         <v>5.08</v>
       </c>
       <c r="I307" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J307" t="n">
         <v>17</v>
@@ -23748,7 +23748,7 @@
         <v>11.98</v>
       </c>
       <c r="I308" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J308" t="n">
         <v>17.2</v>
@@ -23823,7 +23823,7 @@
         <v>-3.84</v>
       </c>
       <c r="I309" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J309" t="n">
         <v>17.32</v>
@@ -23898,7 +23898,7 @@
         <v>5.2</v>
       </c>
       <c r="I310" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J310" t="n">
         <v>17.56</v>
@@ -23973,7 +23973,7 @@
         <v>9.98</v>
       </c>
       <c r="I311" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J311" t="n">
         <v>17.85</v>
@@ -24048,7 +24048,7 @@
         <v>-4.23</v>
       </c>
       <c r="I312" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J312" t="n">
         <v>18.28</v>
@@ -24123,7 +24123,7 @@
         <v>-6.52</v>
       </c>
       <c r="I313" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J313" t="n">
         <v>18.5</v>
@@ -24198,7 +24198,7 @@
         <v>17.54</v>
       </c>
       <c r="I314" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J314" t="n">
         <v>19.01</v>
@@ -24273,7 +24273,7 @@
         <v>-9.65</v>
       </c>
       <c r="I315" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J315" t="n">
         <v>19.42</v>
@@ -24348,7 +24348,7 @@
         <v>7.34</v>
       </c>
       <c r="I316" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J316" t="n">
         <v>20.06</v>
@@ -24423,7 +24423,7 @@
         <v>4.67</v>
       </c>
       <c r="I317" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J317" t="n">
         <v>20.75</v>
@@ -24498,7 +24498,7 @@
         <v>-4.57</v>
       </c>
       <c r="I318" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J318" t="n">
         <v>21.46</v>
@@ -24573,7 +24573,7 @@
         <v>-0.8</v>
       </c>
       <c r="I319" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J319" t="n">
         <v>22.05</v>
@@ -24648,7 +24648,7 @@
         <v>12.69</v>
       </c>
       <c r="I320" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J320" t="n">
         <v>22.76</v>
@@ -24723,7 +24723,7 @@
         <v>2.52</v>
       </c>
       <c r="I321" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J321" t="n">
         <v>23.56</v>
@@ -24798,7 +24798,7 @@
         <v>3.19</v>
       </c>
       <c r="I322" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J322" t="n">
         <v>24.36</v>
@@ -24873,7 +24873,7 @@
         <v>17.69</v>
       </c>
       <c r="I323" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J323" t="n">
         <v>25.41</v>
@@ -24948,7 +24948,7 @@
         <v>14.65</v>
       </c>
       <c r="I324" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J324" t="n">
         <v>26.5</v>
@@ -25023,7 +25023,7 @@
         <v>-8.41</v>
       </c>
       <c r="I325" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J325" t="n">
         <v>27.42</v>
@@ -25098,7 +25098,7 @@
         <v>22.62</v>
       </c>
       <c r="I326" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J326" t="n">
         <v>28.79</v>
@@ -25173,7 +25173,7 @@
         <v>4.33</v>
       </c>
       <c r="I327" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J327" t="n">
         <v>30.21</v>
@@ -25248,7 +25248,7 @@
         <v>-22.56</v>
       </c>
       <c r="I328" s="4" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J328" s="4" t="n">
         <v>30.96</v>
@@ -25323,7 +25323,7 @@
         <v>17.42</v>
       </c>
       <c r="I329" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J329" t="n">
         <v>32.08</v>
@@ -25398,7 +25398,7 @@
         <v>2.91</v>
       </c>
       <c r="I330" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J330" t="n">
         <v>33.2</v>
@@ -25473,7 +25473,7 @@
         <v>-18.31</v>
       </c>
       <c r="I331" s="4" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J331" s="4" t="n">
         <v>33.79</v>
@@ -25548,7 +25548,7 @@
         <v>-5</v>
       </c>
       <c r="I332" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J332" t="n">
         <v>34.34</v>
@@ -25623,7 +25623,7 @@
         <v>-3.36</v>
       </c>
       <c r="I333" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J333" t="n">
         <v>34.91</v>
@@ -25702,7 +25702,7 @@
         <v>10.26</v>
       </c>
       <c r="I334" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J334" t="n">
         <v>35.46</v>
@@ -25777,7 +25777,7 @@
         <v>10.31</v>
       </c>
       <c r="I335" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J335" t="n">
         <v>36.33</v>
@@ -25852,7 +25852,7 @@
         <v>-6.98</v>
       </c>
       <c r="I336" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J336" t="n">
         <v>36.96</v>
@@ -25927,7 +25927,7 @@
         <v>30.06</v>
       </c>
       <c r="I337" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J337" t="n">
         <v>38.12</v>
@@ -26002,7 +26002,7 @@
         <v>-3.57</v>
       </c>
       <c r="I338" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J338" t="n">
         <v>39.25</v>
@@ -26077,7 +26077,7 @@
         <v>12.4</v>
       </c>
       <c r="I339" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J339" t="n">
         <v>40.7</v>
@@ -26152,7 +26152,7 @@
         <v>-0.93</v>
       </c>
       <c r="I340" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J340" t="n">
         <v>41.96</v>
@@ -26227,7 +26227,7 @@
         <v>16.04</v>
       </c>
       <c r="I341" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J341" t="n">
         <v>43.61</v>
@@ -26302,7 +26302,7 @@
         <v>-3.16</v>
       </c>
       <c r="I342" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J342" t="n">
         <v>45.12</v>
@@ -26377,7 +26377,7 @@
         <v>-2.29</v>
       </c>
       <c r="I343" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J343" t="n">
         <v>46.28</v>
@@ -26452,7 +26452,7 @@
         <v>-12.28</v>
       </c>
       <c r="I344" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J344" t="n">
         <v>46.81</v>
@@ -26527,7 +26527,7 @@
         <v>-41.89</v>
       </c>
       <c r="I345" s="4" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J345" s="4" t="n">
         <v>46.41</v>
@@ -26606,7 +26606,7 @@
         <v>16.3</v>
       </c>
       <c r="I346" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J346" t="n">
         <v>45.83</v>
@@ -26681,7 +26681,7 @@
         <v>-2.45</v>
       </c>
       <c r="I347" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J347" t="n">
         <v>45.1</v>
@@ -26756,7 +26756,7 @@
         <v>-9.050000000000001</v>
       </c>
       <c r="I348" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J348" t="n">
         <v>44.77</v>
@@ -26831,7 +26831,7 @@
         <v>33.78</v>
       </c>
       <c r="I349" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J349" t="n">
         <v>44.64</v>
@@ -26906,7 +26906,7 @@
         <v>-2.04</v>
       </c>
       <c r="I350" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J350" t="n">
         <v>44.41</v>
@@ -26981,7 +26981,7 @@
         <v>21.14</v>
       </c>
       <c r="I351" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J351" t="n">
         <v>45.03</v>
@@ -27056,7 +27056,7 @@
         <v>-8.029999999999999</v>
       </c>
       <c r="I352" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J352" t="n">
         <v>45.54</v>
@@ -27131,7 +27131,7 @@
         <v>-0.5</v>
       </c>
       <c r="I353" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J353" t="n">
         <v>46.1</v>
@@ -27210,7 +27210,7 @@
         <v>19.29</v>
       </c>
       <c r="I354" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J354" t="n">
         <v>46.93</v>
@@ -27285,7 +27285,7 @@
         <v>-0.2</v>
       </c>
       <c r="I355" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J355" t="n">
         <v>47.55</v>
@@ -27360,7 +27360,7 @@
         <v>-35.7</v>
       </c>
       <c r="I356" s="4" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J356" s="4" t="n">
         <v>47.35</v>
@@ -27439,7 +27439,7 @@
         <v>5.89</v>
       </c>
       <c r="I357" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J357" t="n">
         <v>46.66</v>
@@ -27514,7 +27514,7 @@
         <v>11.85</v>
       </c>
       <c r="I358" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J358" t="n">
         <v>46.29</v>
@@ -27589,7 +27589,7 @@
         <v>-10.9</v>
       </c>
       <c r="I359" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J359" t="n">
         <v>45.39</v>
@@ -27664,7 +27664,7 @@
         <v>-0.03</v>
       </c>
       <c r="I360" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J360" t="n">
         <v>44.51</v>
@@ -27739,7 +27739,7 @@
         <v>5.82</v>
       </c>
       <c r="I361" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J361" t="n">
         <v>43.3</v>
@@ -27814,7 +27814,7 @@
         <v>-23.21</v>
       </c>
       <c r="I362" s="4" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J362" s="4" t="n">
         <v>41.74</v>
@@ -27893,7 +27893,7 @@
         <v>-9.77</v>
       </c>
       <c r="I363" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J363" t="n">
         <v>40.1</v>
@@ -27972,7 +27972,7 @@
         <v>15.37</v>
       </c>
       <c r="I364" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J364" t="n">
         <v>39.04</v>
@@ -28047,7 +28047,7 @@
         <v>-12.78</v>
       </c>
       <c r="I365" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J365" t="n">
         <v>38.87</v>
@@ -28126,7 +28126,7 @@
         <v>1.58</v>
       </c>
       <c r="I366" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J366" t="n">
         <v>38.48</v>
@@ -28201,7 +28201,7 @@
         <v>3</v>
       </c>
       <c r="I367" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J367" t="n">
         <v>38.18</v>
@@ -28276,7 +28276,7 @@
         <v>-2.28</v>
       </c>
       <c r="I368" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J368" t="n">
         <v>38</v>
@@ -28355,7 +28355,7 @@
         <v>-24.74</v>
       </c>
       <c r="I369" s="4" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J369" s="4" t="n">
         <v>36.94</v>
@@ -28430,7 +28430,7 @@
         <v>14.84</v>
       </c>
       <c r="I370" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J370" t="n">
         <v>36.08</v>
@@ -28505,7 +28505,7 @@
         <v>-9.140000000000001</v>
       </c>
       <c r="I371" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J371" t="n">
         <v>34.68</v>
@@ -28580,7 +28580,7 @@
         <v>-14.72</v>
       </c>
       <c r="I372" s="4" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J372" s="4" t="n">
         <v>33.31</v>
@@ -28659,7 +28659,7 @@
         <v>-2.09</v>
       </c>
       <c r="I373" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J373" t="n">
         <v>31.94</v>
@@ -28738,7 +28738,7 @@
         <v>0.82</v>
       </c>
       <c r="I374" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J374" t="n">
         <v>30.13</v>
@@ -28815,7 +28815,7 @@
         <v>18.03</v>
       </c>
       <c r="I375" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J375" t="n">
         <v>28.5</v>
@@ -28888,7 +28888,7 @@
         <v>-4.46</v>
       </c>
       <c r="I376" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J376" t="n">
         <v>27.79</v>
@@ -28961,7 +28961,7 @@
         <v>6.02</v>
       </c>
       <c r="I377" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J377" t="n">
         <v>27.03</v>
@@ -29034,7 +29034,7 @@
         <v>-18.9</v>
       </c>
       <c r="I378" s="4" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J378" s="4" t="n">
         <v>25.85</v>
@@ -29111,7 +29111,7 @@
         <v>-3.59</v>
       </c>
       <c r="I379" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J379" t="n">
         <v>24.87</v>
@@ -29184,7 +29184,7 @@
         <v>-17.78</v>
       </c>
       <c r="I380" s="4" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J380" s="4" t="n">
         <v>23.73</v>
@@ -29261,7 +29261,7 @@
         <v>-14.63</v>
       </c>
       <c r="I381" s="4" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J381" s="4" t="n">
         <v>22.38</v>
@@ -29338,7 +29338,7 @@
         <v>34.77</v>
       </c>
       <c r="I382" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J382" t="n">
         <v>21.69</v>
@@ -29411,7 +29411,7 @@
         <v>-7.92</v>
       </c>
       <c r="I383" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J383" t="n">
         <v>21.09</v>
@@ -29484,7 +29484,7 @@
         <v>5.87</v>
       </c>
       <c r="I384" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J384" t="n">
         <v>20.32</v>
@@ -29557,7 +29557,7 @@
         <v>20.48</v>
       </c>
       <c r="I385" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J385" t="n">
         <v>19.91</v>
@@ -29630,7 +29630,7 @@
         <v>-3.56</v>
       </c>
       <c r="I386" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J386" t="n">
         <v>19.45</v>
@@ -29703,7 +29703,7 @@
         <v>-8.84</v>
       </c>
       <c r="I387" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J387" t="n">
         <v>18.87</v>
@@ -29776,7 +29776,7 @@
         <v>3.27</v>
       </c>
       <c r="I388" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J388" t="n">
         <v>18.34</v>
@@ -29849,7 +29849,7 @@
         <v>-5.47</v>
       </c>
       <c r="I389" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J389" t="n">
         <v>18.12</v>
@@ -29922,7 +29922,7 @@
         <v>7.5</v>
       </c>
       <c r="I390" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J390" t="n">
         <v>17.8</v>
@@ -29995,7 +29995,7 @@
         <v>15.19</v>
       </c>
       <c r="I391" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J391" t="n">
         <v>17.72</v>
@@ -30068,7 +30068,7 @@
         <v>4.68</v>
       </c>
       <c r="I392" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J392" t="n">
         <v>17.85</v>
@@ -30141,7 +30141,7 @@
         <v>1.55</v>
       </c>
       <c r="I393" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J393" t="n">
         <v>18.02</v>
@@ -30214,7 +30214,7 @@
         <v>8.98</v>
       </c>
       <c r="I394" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J394" t="n">
         <v>18.27</v>
@@ -30287,7 +30287,7 @@
         <v>-24.21</v>
       </c>
       <c r="I395" s="4" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J395" s="4" t="n">
         <v>18.08</v>
@@ -30364,7 +30364,7 @@
         <v>7.12</v>
       </c>
       <c r="I396" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J396" t="n">
         <v>18</v>
@@ -30437,7 +30437,7 @@
         <v>6.38</v>
       </c>
       <c r="I397" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J397" t="n">
         <v>17.91</v>
@@ -30510,7 +30510,7 @@
         <v>0.15</v>
       </c>
       <c r="I398" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J398" t="n">
         <v>18.04</v>
@@ -30583,7 +30583,7 @@
         <v>-7.86</v>
       </c>
       <c r="I399" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J399" t="n">
         <v>18.11</v>
@@ -30656,7 +30656,7 @@
         <v>11.03</v>
       </c>
       <c r="I400" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J400" t="n">
         <v>18.45</v>
@@ -30729,7 +30729,7 @@
         <v>-1.63</v>
       </c>
       <c r="I401" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J401" t="n">
         <v>18.87</v>
@@ -30802,7 +30802,7 @@
         <v>4.49</v>
       </c>
       <c r="I402" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J402" t="n">
         <v>19.12</v>
@@ -30875,7 +30875,7 @@
         <v>-2.99</v>
       </c>
       <c r="I403" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J403" t="n">
         <v>19.41</v>
@@ -30948,7 +30948,7 @@
         <v>0.91</v>
       </c>
       <c r="I404" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J404" t="n">
         <v>19.67</v>
@@ -31021,7 +31021,7 @@
         <v>-8.49</v>
       </c>
       <c r="I405" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J405" t="n">
         <v>19.67</v>
@@ -31098,7 +31098,7 @@
         <v>5.06</v>
       </c>
       <c r="I406" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J406" t="n">
         <v>19.76</v>
@@ -31171,7 +31171,7 @@
         <v>2.68</v>
       </c>
       <c r="I407" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J407" t="n">
         <v>19.95</v>
@@ -31244,7 +31244,7 @@
         <v>13.44</v>
       </c>
       <c r="I408" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J408" t="n">
         <v>20.26</v>
@@ -31317,7 +31317,7 @@
         <v>1.58</v>
       </c>
       <c r="I409" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J409" t="n">
         <v>20.63</v>
@@ -31390,7 +31390,7 @@
         <v>1.51</v>
       </c>
       <c r="I410" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J410" t="n">
         <v>20.96</v>
@@ -31463,7 +31463,7 @@
         <v>-12.52</v>
       </c>
       <c r="I411" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J411" t="n">
         <v>21</v>
@@ -31536,7 +31536,7 @@
         <v>8.970000000000001</v>
       </c>
       <c r="I412" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J412" t="n">
         <v>21.09</v>
@@ -31579,6 +31579,83 @@
         <v>154.5</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" s="4" t="inlineStr">
+        <is>
+          <t>KORU</t>
+        </is>
+      </c>
+      <c r="B413" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C413" s="4" t="n">
+        <v>19.38</v>
+      </c>
+      <c r="D413" s="4" t="n">
+        <v>19.76</v>
+      </c>
+      <c r="E413" s="4" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="F413" s="4" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="G413" s="4" t="n">
+        <v>33962635</v>
+      </c>
+      <c r="H413" s="5" t="n">
+        <v>-15.43</v>
+      </c>
+      <c r="I413" s="4" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="J413" s="4" t="n">
+        <v>20.98</v>
+      </c>
+      <c r="K413" s="4" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="L413" s="4" t="n">
+        <v>28.41</v>
+      </c>
+      <c r="M413" s="4" t="n">
+        <v>23.08</v>
+      </c>
+      <c r="N413" s="6" t="n">
+        <v>51.93</v>
+      </c>
+      <c r="O413" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="P413" s="4" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" s="4" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" s="4" t="inlineStr">
+        <is>
+          <t>1st: MA20, 10% cash</t>
+        </is>
+      </c>
+      <c r="S413" s="4" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T413" s="6" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="U413" s="6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="V413" s="4" t="inlineStr"/>
+      <c r="W413" s="6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -611,7 +611,7 @@
         <v>13.4</v>
       </c>
       <c r="J2" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="K2" t="n">
         <v>2.22</v>
@@ -1905,7 +1905,7 @@
         <v>2.11</v>
       </c>
       <c r="K19" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="L19" t="n">
         <v>2.59</v>
@@ -2280,7 +2280,7 @@
         <v>2.17</v>
       </c>
       <c r="K24" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="L24" t="n">
         <v>2.53</v>
@@ -8889,7 +8889,7 @@
         <v>3.48</v>
       </c>
       <c r="K111" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="L111" t="n">
         <v>2.33</v>
@@ -13564,7 +13564,7 @@
         <v>13.4</v>
       </c>
       <c r="J173" t="n">
-        <v>4.86</v>
+        <v>4.85</v>
       </c>
       <c r="K173" t="n">
         <v>4.34</v>
@@ -31600,31 +31600,31 @@
         <v>18.35</v>
       </c>
       <c r="F413" s="4" t="n">
-        <v>19.51</v>
+        <v>18.57</v>
       </c>
       <c r="G413" s="4" t="n">
-        <v>33962635</v>
+        <v>38025096</v>
       </c>
       <c r="H413" s="5" t="n">
-        <v>-15.43</v>
+        <v>-19.51</v>
       </c>
       <c r="I413" s="4" t="n">
         <v>13.4</v>
       </c>
       <c r="J413" s="4" t="n">
-        <v>20.98</v>
+        <v>20.94</v>
       </c>
       <c r="K413" s="4" t="n">
-        <v>23.65</v>
+        <v>23.63</v>
       </c>
       <c r="L413" s="4" t="n">
-        <v>28.41</v>
+        <v>28.4</v>
       </c>
       <c r="M413" s="4" t="n">
         <v>23.08</v>
       </c>
       <c r="N413" s="6" t="n">
-        <v>51.93</v>
+        <v>49.53</v>
       </c>
       <c r="O413" s="4" t="n">
         <v>31</v>
@@ -31645,16 +31645,18 @@
         </is>
       </c>
       <c r="S413" s="4" t="n">
-        <v>4.95</v>
+        <v>4.96</v>
       </c>
       <c r="T413" s="6" t="n">
-        <v>16.7</v>
+        <v>17.1</v>
       </c>
       <c r="U413" s="6" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="V413" s="4" t="inlineStr"/>
-      <c r="W413" s="6" t="inlineStr"/>
+      <c r="W413" s="6" t="n">
+        <v>152.1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -608,7 +608,7 @@
         <v>0.91</v>
       </c>
       <c r="I2" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J2" t="n">
         <v>1.98</v>
@@ -683,7 +683,7 @@
         <v>-7.24</v>
       </c>
       <c r="I3" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J3" t="n">
         <v>1.99</v>
@@ -762,7 +762,7 @@
         <v>-0.98</v>
       </c>
       <c r="I4" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J4" t="n">
         <v>2</v>
@@ -837,7 +837,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J5" t="n">
         <v>2.01</v>
@@ -912,7 +912,7 @@
         <v>4.43</v>
       </c>
       <c r="I6" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J6" t="n">
         <v>2.03</v>
@@ -987,7 +987,7 @@
         <v>-6.6</v>
       </c>
       <c r="I7" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J7" t="n">
         <v>2.04</v>
@@ -1066,7 +1066,7 @@
         <v>-3.54</v>
       </c>
       <c r="I8" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J8" t="n">
         <v>2.05</v>
@@ -1141,7 +1141,7 @@
         <v>5.24</v>
       </c>
       <c r="I9" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J9" t="n">
         <v>2.06</v>
@@ -1216,7 +1216,7 @@
         <v>3.98</v>
       </c>
       <c r="I10" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J10" t="n">
         <v>2.06</v>
@@ -1291,7 +1291,7 @@
         <v>0.48</v>
       </c>
       <c r="I11" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J11" t="n">
         <v>2.07</v>
@@ -1366,7 +1366,7 @@
         <v>-5.71</v>
       </c>
       <c r="I12" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J12" t="n">
         <v>2.06</v>
@@ -1445,7 +1445,7 @@
         <v>5.56</v>
       </c>
       <c r="I13" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J13" t="n">
         <v>2.07</v>
@@ -1520,7 +1520,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J14" t="n">
         <v>2.08</v>
@@ -1595,7 +1595,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J15" t="n">
         <v>2.08</v>
@@ -1670,7 +1670,7 @@
         <v>6.7</v>
       </c>
       <c r="I16" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J16" t="n">
         <v>2.09</v>
@@ -1745,7 +1745,7 @@
         <v>1.79</v>
       </c>
       <c r="I17" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J17" t="n">
         <v>2.1</v>
@@ -1820,7 +1820,7 @@
         <v>3.96</v>
       </c>
       <c r="I18" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J18" t="n">
         <v>2.11</v>
@@ -1895,7 +1895,7 @@
         <v>3.81</v>
       </c>
       <c r="I19" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J19" t="n">
         <v>2.13</v>
@@ -1970,7 +1970,7 @@
         <v>1.22</v>
       </c>
       <c r="I20" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J20" t="n">
         <v>2.14</v>
@@ -2045,7 +2045,7 @@
         <v>-4.84</v>
       </c>
       <c r="I21" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J21" t="n">
         <v>2.15</v>
@@ -2120,7 +2120,7 @@
         <v>-0.42</v>
       </c>
       <c r="I22" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J22" t="n">
         <v>2.15</v>
@@ -2195,7 +2195,7 @@
         <v>0.43</v>
       </c>
       <c r="I23" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J23" t="n">
         <v>2.17</v>
@@ -2270,7 +2270,7 @@
         <v>1.69</v>
       </c>
       <c r="I24" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J24" t="n">
         <v>2.19</v>
@@ -2345,7 +2345,7 @@
         <v>-10</v>
       </c>
       <c r="I25" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J25" t="n">
         <v>2.19</v>
@@ -2424,7 +2424,7 @@
         <v>-6.94</v>
       </c>
       <c r="I26" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J26" t="n">
         <v>2.19</v>
@@ -2503,7 +2503,7 @@
         <v>-1.49</v>
       </c>
       <c r="I27" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J27" t="n">
         <v>2.19</v>
@@ -2578,7 +2578,7 @@
         <v>1.01</v>
       </c>
       <c r="I28" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J28" t="n">
         <v>2.19</v>
@@ -2653,7 +2653,7 @@
         <v>8</v>
       </c>
       <c r="I29" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J29" t="n">
         <v>2.2</v>
@@ -2728,7 +2728,7 @@
         <v>-5.56</v>
       </c>
       <c r="I30" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J30" t="n">
         <v>2.2</v>
@@ -2807,7 +2807,7 @@
         <v>3.43</v>
       </c>
       <c r="I31" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J31" t="n">
         <v>2.2</v>
@@ -2882,7 +2882,7 @@
         <v>-8.529999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J32" t="n">
         <v>2.2</v>
@@ -2965,7 +2965,7 @@
         <v>3.11</v>
       </c>
       <c r="I33" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J33" t="n">
         <v>2.19</v>
@@ -3044,7 +3044,7 @@
         <v>7.04</v>
       </c>
       <c r="I34" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J34" t="n">
         <v>2.19</v>
@@ -3119,7 +3119,7 @@
         <v>-3.76</v>
       </c>
       <c r="I35" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J35" t="n">
         <v>2.19</v>
@@ -3198,7 +3198,7 @@
         <v>4.88</v>
       </c>
       <c r="I36" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J36" t="n">
         <v>2.19</v>
@@ -3273,7 +3273,7 @@
         <v>8.84</v>
       </c>
       <c r="I37" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J37" t="n">
         <v>2.19</v>
@@ -3348,7 +3348,7 @@
         <v>-4.7</v>
       </c>
       <c r="I38" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J38" t="n">
         <v>2.18</v>
@@ -3423,7 +3423,7 @@
         <v>1.35</v>
       </c>
       <c r="I39" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J39" t="n">
         <v>2.17</v>
@@ -3498,7 +3498,7 @@
         <v>-2.65</v>
       </c>
       <c r="I40" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J40" t="n">
         <v>2.16</v>
@@ -3573,7 +3573,7 @@
         <v>0.91</v>
       </c>
       <c r="I41" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J41" t="n">
         <v>2.15</v>
@@ -3648,7 +3648,7 @@
         <v>2.25</v>
       </c>
       <c r="I42" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J42" t="n">
         <v>2.15</v>
@@ -3723,7 +3723,7 @@
         <v>-1.32</v>
       </c>
       <c r="I43" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J43" t="n">
         <v>2.14</v>
@@ -3798,7 +3798,7 @@
         <v>-1.34</v>
       </c>
       <c r="I44" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J44" t="n">
         <v>2.13</v>
@@ -3873,7 +3873,7 @@
         <v>-1.81</v>
       </c>
       <c r="I45" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J45" t="n">
         <v>2.13</v>
@@ -3948,7 +3948,7 @@
         <v>-9.220000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J46" t="n">
         <v>2.13</v>
@@ -4027,7 +4027,7 @@
         <v>-4.06</v>
       </c>
       <c r="I47" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J47" t="n">
         <v>2.13</v>
@@ -4102,7 +4102,7 @@
         <v>4.76</v>
       </c>
       <c r="I48" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J48" t="n">
         <v>2.13</v>
@@ -4177,7 +4177,7 @@
         <v>-1.01</v>
       </c>
       <c r="I49" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J49" t="n">
         <v>2.12</v>
@@ -4252,7 +4252,7 @@
         <v>-8.67</v>
       </c>
       <c r="I50" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J50" t="n">
         <v>2.1</v>
@@ -4331,7 +4331,7 @@
         <v>-10.61</v>
       </c>
       <c r="I51" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J51" t="n">
         <v>2.08</v>
@@ -4414,7 +4414,7 @@
         <v>-3.12</v>
       </c>
       <c r="I52" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J52" t="n">
         <v>2.06</v>
@@ -4497,7 +4497,7 @@
         <v>-10.32</v>
       </c>
       <c r="I53" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J53" t="n">
         <v>2.03</v>
@@ -4580,7 +4580,7 @@
         <v>24.46</v>
       </c>
       <c r="I54" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J54" t="n">
         <v>2.01</v>
@@ -4659,7 +4659,7 @@
         <v>-6.94</v>
       </c>
       <c r="I55" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J55" t="n">
         <v>1.99</v>
@@ -4738,7 +4738,7 @@
         <v>14.29</v>
       </c>
       <c r="I56" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J56" t="n">
         <v>1.97</v>
@@ -4817,7 +4817,7 @@
         <v>-0.54</v>
       </c>
       <c r="I57" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J57" t="n">
         <v>1.95</v>
@@ -4892,7 +4892,7 @@
         <v>0.55</v>
       </c>
       <c r="I58" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J58" t="n">
         <v>1.93</v>
@@ -4967,7 +4967,7 @@
         <v>-2.17</v>
       </c>
       <c r="I59" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J59" t="n">
         <v>1.9</v>
@@ -5046,7 +5046,7 @@
         <v>1.67</v>
       </c>
       <c r="I60" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J60" t="n">
         <v>1.89</v>
@@ -5125,7 +5125,7 @@
         <v>0.55</v>
       </c>
       <c r="I61" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J61" t="n">
         <v>1.87</v>
@@ -5200,7 +5200,7 @@
         <v>2.17</v>
       </c>
       <c r="I62" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J62" t="n">
         <v>1.85</v>
@@ -5275,7 +5275,7 @@
         <v>3.72</v>
       </c>
       <c r="I63" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J63" t="n">
         <v>1.83</v>
@@ -5354,7 +5354,7 @@
         <v>2.05</v>
       </c>
       <c r="I64" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J64" t="n">
         <v>1.82</v>
@@ -5429,7 +5429,7 @@
         <v>-0.5</v>
       </c>
       <c r="I65" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J65" t="n">
         <v>1.81</v>
@@ -5504,7 +5504,7 @@
         <v>-1.01</v>
       </c>
       <c r="I66" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J66" t="n">
         <v>1.81</v>
@@ -5579,7 +5579,7 @@
         <v>2.55</v>
       </c>
       <c r="I67" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J67" t="n">
         <v>1.82</v>
@@ -5654,7 +5654,7 @@
         <v>0.5</v>
       </c>
       <c r="I68" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J68" t="n">
         <v>1.82</v>
@@ -5729,7 +5729,7 @@
         <v>-2.97</v>
       </c>
       <c r="I69" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J69" t="n">
         <v>1.82</v>
@@ -5804,7 +5804,7 @@
         <v>10.71</v>
       </c>
       <c r="I70" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J70" t="n">
         <v>1.84</v>
@@ -5879,7 +5879,7 @@
         <v>4.15</v>
       </c>
       <c r="I71" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J71" t="n">
         <v>1.87</v>
@@ -5954,7 +5954,7 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J72" t="n">
         <v>1.91</v>
@@ -6029,7 +6029,7 @@
         <v>-3.54</v>
       </c>
       <c r="I73" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J73" t="n">
         <v>1.95</v>
@@ -6104,7 +6104,7 @@
         <v>-3.21</v>
       </c>
       <c r="I74" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J74" t="n">
         <v>1.97</v>
@@ -6179,7 +6179,7 @@
         <v>2.84</v>
       </c>
       <c r="I75" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J75" t="n">
         <v>1.99</v>
@@ -6254,7 +6254,7 @@
         <v>1.38</v>
       </c>
       <c r="I76" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J76" t="n">
         <v>2.01</v>
@@ -6329,7 +6329,7 @@
         <v>0.45</v>
       </c>
       <c r="I77" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J77" t="n">
         <v>2.03</v>
@@ -6404,7 +6404,7 @@
         <v>2.71</v>
       </c>
       <c r="I78" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J78" t="n">
         <v>2.05</v>
@@ -6479,7 +6479,7 @@
         <v>0.88</v>
       </c>
       <c r="I79" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J79" t="n">
         <v>2.08</v>
@@ -6554,7 +6554,7 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J80" t="n">
         <v>2.1</v>
@@ -6629,7 +6629,7 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J81" t="n">
         <v>2.12</v>
@@ -6704,7 +6704,7 @@
         <v>-2.18</v>
       </c>
       <c r="I82" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J82" t="n">
         <v>2.14</v>
@@ -6779,7 +6779,7 @@
         <v>3.57</v>
       </c>
       <c r="I83" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J83" t="n">
         <v>2.16</v>
@@ -6854,7 +6854,7 @@
         <v>-3.88</v>
       </c>
       <c r="I84" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J84" t="n">
         <v>2.17</v>
@@ -6929,7 +6929,7 @@
         <v>3.14</v>
       </c>
       <c r="I85" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J85" t="n">
         <v>2.19</v>
@@ -7004,7 +7004,7 @@
         <v>4.78</v>
       </c>
       <c r="I86" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J86" t="n">
         <v>2.21</v>
@@ -7079,7 +7079,7 @@
         <v>3.73</v>
       </c>
       <c r="I87" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J87" t="n">
         <v>2.23</v>
@@ -7154,7 +7154,7 @@
         <v>5.2</v>
       </c>
       <c r="I88" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J88" t="n">
         <v>2.26</v>
@@ -7229,7 +7229,7 @@
         <v>-5.7</v>
       </c>
       <c r="I89" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J89" t="n">
         <v>2.29</v>
@@ -7304,7 +7304,7 @@
         <v>5.65</v>
       </c>
       <c r="I90" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J90" t="n">
         <v>2.31</v>
@@ -7379,7 +7379,7 @@
         <v>1.15</v>
       </c>
       <c r="I91" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J91" t="n">
         <v>2.33</v>
@@ -7454,7 +7454,7 @@
         <v>9.43</v>
       </c>
       <c r="I92" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J92" t="n">
         <v>2.36</v>
@@ -7529,7 +7529,7 @@
         <v>6.55</v>
       </c>
       <c r="I93" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J93" t="n">
         <v>2.41</v>
@@ -7604,7 +7604,7 @@
         <v>0.65</v>
       </c>
       <c r="I94" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J94" t="n">
         <v>2.46</v>
@@ -7679,7 +7679,7 @@
         <v>4.5</v>
       </c>
       <c r="I95" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J95" t="n">
         <v>2.51</v>
@@ -7754,7 +7754,7 @@
         <v>-1.54</v>
       </c>
       <c r="I96" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J96" t="n">
         <v>2.56</v>
@@ -7829,7 +7829,7 @@
         <v>3.75</v>
       </c>
       <c r="I97" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J97" t="n">
         <v>2.62</v>
@@ -7904,7 +7904,7 @@
         <v>3.31</v>
       </c>
       <c r="I98" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J98" t="n">
         <v>2.68</v>
@@ -7979,7 +7979,7 @@
         <v>-5.83</v>
       </c>
       <c r="I99" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J99" t="n">
         <v>2.72</v>
@@ -8054,7 +8054,7 @@
         <v>8.050000000000001</v>
       </c>
       <c r="I100" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J100" t="n">
         <v>2.78</v>
@@ -8129,7 +8129,7 @@
         <v>-6.88</v>
       </c>
       <c r="I101" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J101" t="n">
         <v>2.83</v>
@@ -8204,7 +8204,7 @@
         <v>5.23</v>
       </c>
       <c r="I102" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J102" t="n">
         <v>2.89</v>
@@ -8279,7 +8279,7 @@
         <v>2.92</v>
       </c>
       <c r="I103" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J103" t="n">
         <v>2.95</v>
@@ -8354,7 +8354,7 @@
         <v>3.69</v>
       </c>
       <c r="I104" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J104" t="n">
         <v>3.02</v>
@@ -8429,7 +8429,7 @@
         <v>14.25</v>
       </c>
       <c r="I105" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J105" t="n">
         <v>3.12</v>
@@ -8504,7 +8504,7 @@
         <v>-1.2</v>
       </c>
       <c r="I106" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J106" t="n">
         <v>3.2</v>
@@ -8579,7 +8579,7 @@
         <v>-1.94</v>
       </c>
       <c r="I107" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J107" t="n">
         <v>3.28</v>
@@ -8654,7 +8654,7 @@
         <v>-4.95</v>
       </c>
       <c r="I108" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J108" t="n">
         <v>3.34</v>
@@ -8729,7 +8729,7 @@
         <v>4.17</v>
       </c>
       <c r="I109" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J109" t="n">
         <v>3.42</v>
@@ -8804,7 +8804,7 @@
         <v>-0.5</v>
       </c>
       <c r="I110" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J110" t="n">
         <v>3.48</v>
@@ -8879,7 +8879,7 @@
         <v>1.26</v>
       </c>
       <c r="I111" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J111" t="n">
         <v>3.55</v>
@@ -8954,7 +8954,7 @@
         <v>2.73</v>
       </c>
       <c r="I112" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J112" t="n">
         <v>3.61</v>
@@ -9029,7 +9029,7 @@
         <v>-10.39</v>
       </c>
       <c r="I113" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J113" t="n">
         <v>3.65</v>
@@ -9104,7 +9104,7 @@
         <v>8.09</v>
       </c>
       <c r="I114" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J114" t="n">
         <v>3.69</v>
@@ -9179,7 +9179,7 @@
         <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J115" t="n">
         <v>3.73</v>
@@ -9254,7 +9254,7 @@
         <v>4.49</v>
       </c>
       <c r="I116" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J116" t="n">
         <v>3.78</v>
@@ -9329,7 +9329,7 @@
         <v>-2.39</v>
       </c>
       <c r="I117" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J117" t="n">
         <v>3.82</v>
@@ -9404,7 +9404,7 @@
         <v>2.44</v>
       </c>
       <c r="I118" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J118" t="n">
         <v>3.85</v>
@@ -9479,7 +9479,7 @@
         <v>-0.48</v>
       </c>
       <c r="I119" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J119" t="n">
         <v>3.9</v>
@@ -9554,7 +9554,7 @@
         <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J120" t="n">
         <v>3.94</v>
@@ -9629,7 +9629,7 @@
         <v>-0.24</v>
       </c>
       <c r="I121" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J121" t="n">
         <v>3.98</v>
@@ -9704,7 +9704,7 @@
         <v>-2.64</v>
       </c>
       <c r="I122" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J122" t="n">
         <v>4.01</v>
@@ -9779,7 +9779,7 @@
         <v>5.93</v>
       </c>
       <c r="I123" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J123" t="n">
         <v>4.05</v>
@@ -9854,7 +9854,7 @@
         <v>-3.73</v>
       </c>
       <c r="I124" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J124" t="n">
         <v>4.07</v>
@@ -9929,7 +9929,7 @@
         <v>3.63</v>
       </c>
       <c r="I125" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J125" t="n">
         <v>4.08</v>
@@ -10004,7 +10004,7 @@
         <v>-2.1</v>
       </c>
       <c r="I126" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J126" t="n">
         <v>4.08</v>
@@ -10079,7 +10079,7 @@
         <v>-0.48</v>
       </c>
       <c r="I127" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J127" t="n">
         <v>4.09</v>
@@ -10154,7 +10154,7 @@
         <v>-2.16</v>
       </c>
       <c r="I128" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J128" t="n">
         <v>4.1</v>
@@ -10233,7 +10233,7 @@
         <v>3.19</v>
       </c>
       <c r="I129" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J129" t="n">
         <v>4.11</v>
@@ -10308,7 +10308,7 @@
         <v>0.95</v>
       </c>
       <c r="I130" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J130" t="n">
         <v>4.13</v>
@@ -10383,7 +10383,7 @@
         <v>-3.76</v>
       </c>
       <c r="I131" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J131" t="n">
         <v>4.13</v>
@@ -10462,7 +10462,7 @@
         <v>-9.050000000000001</v>
       </c>
       <c r="I132" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J132" t="n">
         <v>4.11</v>
@@ -10537,7 +10537,7 @@
         <v>7.26</v>
       </c>
       <c r="I133" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J133" t="n">
         <v>4.12</v>
@@ -10612,7 +10612,7 @@
         <v>2.26</v>
       </c>
       <c r="I134" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J134" t="n">
         <v>4.13</v>
@@ -10687,7 +10687,7 @@
         <v>0.98</v>
       </c>
       <c r="I135" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J135" t="n">
         <v>4.13</v>
@@ -10762,7 +10762,7 @@
         <v>0.97</v>
       </c>
       <c r="I136" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J136" t="n">
         <v>4.13</v>
@@ -10837,7 +10837,7 @@
         <v>0.24</v>
       </c>
       <c r="I137" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J137" t="n">
         <v>4.13</v>
@@ -10912,7 +10912,7 @@
         <v>-1.92</v>
       </c>
       <c r="I138" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J138" t="n">
         <v>4.13</v>
@@ -10991,7 +10991,7 @@
         <v>4.16</v>
       </c>
       <c r="I139" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J139" t="n">
         <v>4.13</v>
@@ -11066,7 +11066,7 @@
         <v>2.58</v>
       </c>
       <c r="I140" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J140" t="n">
         <v>4.14</v>
@@ -11141,7 +11141,7 @@
         <v>-4.12</v>
       </c>
       <c r="I141" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J141" t="n">
         <v>4.14</v>
@@ -11216,7 +11216,7 @@
         <v>-1.19</v>
       </c>
       <c r="I142" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J142" t="n">
         <v>4.15</v>
@@ -11295,7 +11295,7 @@
         <v>-2.42</v>
       </c>
       <c r="I143" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J143" t="n">
         <v>4.14</v>
@@ -11370,7 +11370,7 @@
         <v>-5.45</v>
       </c>
       <c r="I144" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J144" t="n">
         <v>4.12</v>
@@ -11445,7 +11445,7 @@
         <v>-0.52</v>
       </c>
       <c r="I145" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J145" t="n">
         <v>4.1</v>
@@ -11520,7 +11520,7 @@
         <v>-0.79</v>
       </c>
       <c r="I146" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J146" t="n">
         <v>4.08</v>
@@ -11599,7 +11599,7 @@
         <v>9.81</v>
       </c>
       <c r="I147" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J147" t="n">
         <v>4.07</v>
@@ -11674,7 +11674,7 @@
         <v>-3.38</v>
       </c>
       <c r="I148" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J148" t="n">
         <v>4.07</v>
@@ -11753,7 +11753,7 @@
         <v>-1.5</v>
       </c>
       <c r="I149" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J149" t="n">
         <v>4.06</v>
@@ -11828,7 +11828,7 @@
         <v>0.51</v>
       </c>
       <c r="I150" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J150" t="n">
         <v>4.04</v>
@@ -11903,7 +11903,7 @@
         <v>4.55</v>
       </c>
       <c r="I151" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J151" t="n">
         <v>4.04</v>
@@ -11978,7 +11978,7 @@
         <v>-5.56</v>
       </c>
       <c r="I152" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J152" t="n">
         <v>4.05</v>
@@ -12057,7 +12057,7 @@
         <v>-1.53</v>
       </c>
       <c r="I153" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J153" t="n">
         <v>4.05</v>
@@ -12132,7 +12132,7 @@
         <v>3.9</v>
       </c>
       <c r="I154" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J154" t="n">
         <v>4.04</v>
@@ -12207,7 +12207,7 @@
         <v>0.75</v>
       </c>
       <c r="I155" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J155" t="n">
         <v>4.04</v>
@@ -12282,7 +12282,7 @@
         <v>2.23</v>
       </c>
       <c r="I156" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J156" t="n">
         <v>4.04</v>
@@ -12357,7 +12357,7 @@
         <v>1.94</v>
       </c>
       <c r="I157" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J157" t="n">
         <v>4.04</v>
@@ -12432,7 +12432,7 @@
         <v>3.1</v>
       </c>
       <c r="I158" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J158" t="n">
         <v>4.05</v>
@@ -12507,7 +12507,7 @@
         <v>6.93</v>
       </c>
       <c r="I159" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J159" t="n">
         <v>4.07</v>
@@ -12582,7 +12582,7 @@
         <v>4.75</v>
       </c>
       <c r="I160" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J160" t="n">
         <v>4.09</v>
@@ -12657,7 +12657,7 @@
         <v>3.09</v>
       </c>
       <c r="I161" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J161" t="n">
         <v>4.13</v>
@@ -12732,7 +12732,7 @@
         <v>2</v>
       </c>
       <c r="I162" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J162" t="n">
         <v>4.18</v>
@@ -12807,7 +12807,7 @@
         <v>5.69</v>
       </c>
       <c r="I163" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J163" t="n">
         <v>4.25</v>
@@ -12882,7 +12882,7 @@
         <v>-3.34</v>
       </c>
       <c r="I164" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J164" t="n">
         <v>4.32</v>
@@ -12957,7 +12957,7 @@
         <v>3.65</v>
       </c>
       <c r="I165" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J165" t="n">
         <v>4.4</v>
@@ -13032,7 +13032,7 @@
         <v>-2.96</v>
       </c>
       <c r="I166" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J166" t="n">
         <v>4.47</v>
@@ -13107,7 +13107,7 @@
         <v>5.92</v>
       </c>
       <c r="I167" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J167" t="n">
         <v>4.54</v>
@@ -13182,7 +13182,7 @@
         <v>-0.54</v>
       </c>
       <c r="I168" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J168" t="n">
         <v>4.62</v>
@@ -13257,7 +13257,7 @@
         <v>-5.25</v>
       </c>
       <c r="I169" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J169" t="n">
         <v>4.68</v>
@@ -13332,7 +13332,7 @@
         <v>-0.57</v>
       </c>
       <c r="I170" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J170" t="n">
         <v>4.74</v>
@@ -13407,7 +13407,7 @@
         <v>-3.85</v>
       </c>
       <c r="I171" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J171" t="n">
         <v>4.79</v>
@@ -13482,7 +13482,7 @@
         <v>5</v>
       </c>
       <c r="I172" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J172" t="n">
         <v>4.85</v>
@@ -13557,7 +13557,7 @@
         <v>-0.38</v>
       </c>
       <c r="I173" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J173" t="n">
         <v>4.92</v>
@@ -13632,7 +13632,7 @@
         <v>6.5</v>
       </c>
       <c r="I174" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J174" t="n">
         <v>5</v>
@@ -13707,7 +13707,7 @@
         <v>6.1</v>
       </c>
       <c r="I175" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J175" t="n">
         <v>5.1</v>
@@ -13782,7 +13782,7 @@
         <v>1.18</v>
       </c>
       <c r="I176" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J176" t="n">
         <v>5.19</v>
@@ -13857,7 +13857,7 @@
         <v>3.18</v>
       </c>
       <c r="I177" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J177" t="n">
         <v>5.29</v>
@@ -13932,7 +13932,7 @@
         <v>-4.86</v>
       </c>
       <c r="I178" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J178" t="n">
         <v>5.36</v>
@@ -14007,7 +14007,7 @@
         <v>2.73</v>
       </c>
       <c r="I179" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J179" t="n">
         <v>5.44</v>
@@ -14082,7 +14082,7 @@
         <v>-2.65</v>
       </c>
       <c r="I180" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J180" t="n">
         <v>5.49</v>
@@ -14157,7 +14157,7 @@
         <v>-9.710000000000001</v>
       </c>
       <c r="I181" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J181" t="n">
         <v>5.5</v>
@@ -14236,7 +14236,7 @@
         <v>10.38</v>
       </c>
       <c r="I182" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J182" t="n">
         <v>5.54</v>
@@ -14311,7 +14311,7 @@
         <v>-3.25</v>
       </c>
       <c r="I183" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J183" t="n">
         <v>5.55</v>
@@ -14386,7 +14386,7 @@
         <v>8.83</v>
       </c>
       <c r="I184" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J184" t="n">
         <v>5.6</v>
@@ -14461,7 +14461,7 @@
         <v>9.58</v>
       </c>
       <c r="I185" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J185" t="n">
         <v>5.67</v>
@@ -14536,7 +14536,7 @@
         <v>2.07</v>
       </c>
       <c r="I186" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J186" t="n">
         <v>5.75</v>
@@ -14611,7 +14611,7 @@
         <v>6.68</v>
       </c>
       <c r="I187" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J187" t="n">
         <v>5.84</v>
@@ -14686,7 +14686,7 @@
         <v>-6.12</v>
       </c>
       <c r="I188" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J188" t="n">
         <v>5.91</v>
@@ -14761,7 +14761,7 @@
         <v>2.75</v>
       </c>
       <c r="I189" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J189" t="n">
         <v>6</v>
@@ -14836,7 +14836,7 @@
         <v>1.97</v>
       </c>
       <c r="I190" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J190" t="n">
         <v>6.1</v>
@@ -14911,7 +14911,7 @@
         <v>6.64</v>
       </c>
       <c r="I191" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J191" t="n">
         <v>6.24</v>
@@ -14986,7 +14986,7 @@
         <v>7.39</v>
       </c>
       <c r="I192" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J192" t="n">
         <v>6.39</v>
@@ -15061,7 +15061,7 @@
         <v>0.36</v>
       </c>
       <c r="I193" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J193" t="n">
         <v>6.54</v>
@@ -15136,7 +15136,7 @@
         <v>7.82</v>
       </c>
       <c r="I194" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J194" t="n">
         <v>6.71</v>
@@ -15211,7 +15211,7 @@
         <v>-5.02</v>
       </c>
       <c r="I195" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J195" t="n">
         <v>6.84</v>
@@ -15286,7 +15286,7 @@
         <v>5.17</v>
       </c>
       <c r="I196" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J196" t="n">
         <v>6.99</v>
@@ -15361,7 +15361,7 @@
         <v>11.62</v>
       </c>
       <c r="I197" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J197" t="n">
         <v>7.18</v>
@@ -15436,7 +15436,7 @@
         <v>-14.81</v>
       </c>
       <c r="I198" s="4" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J198" s="4" t="n">
         <v>7.32</v>
@@ -15511,7 +15511,7 @@
         <v>2.47</v>
       </c>
       <c r="I199" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J199" t="n">
         <v>7.45</v>
@@ -15586,7 +15586,7 @@
         <v>-9.52</v>
       </c>
       <c r="I200" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J200" t="n">
         <v>7.55</v>
@@ -15661,7 +15661,7 @@
         <v>-5.7</v>
       </c>
       <c r="I201" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J201" t="n">
         <v>7.66</v>
@@ -15740,7 +15740,7 @@
         <v>12.5</v>
       </c>
       <c r="I202" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J202" t="n">
         <v>7.78</v>
@@ -15815,7 +15815,7 @@
         <v>-1.19</v>
       </c>
       <c r="I203" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J203" t="n">
         <v>7.91</v>
@@ -15890,7 +15890,7 @@
         <v>2.06</v>
       </c>
       <c r="I204" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J204" t="n">
         <v>8.029999999999999</v>
@@ -15965,7 +15965,7 @@
         <v>-5.92</v>
       </c>
       <c r="I205" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J205" t="n">
         <v>8.09</v>
@@ -16044,7 +16044,7 @@
         <v>0.38</v>
       </c>
       <c r="I206" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J206" t="n">
         <v>8.140000000000001</v>
@@ -16119,7 +16119,7 @@
         <v>-3.76</v>
       </c>
       <c r="I207" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J207" t="n">
         <v>8.16</v>
@@ -16194,7 +16194,7 @@
         <v>-4.69</v>
       </c>
       <c r="I208" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J208" t="n">
         <v>8.18</v>
@@ -16269,7 +16269,7 @@
         <v>-3.28</v>
       </c>
       <c r="I209" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J209" t="n">
         <v>8.18</v>
@@ -16344,7 +16344,7 @@
         <v>-6.79</v>
       </c>
       <c r="I210" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J210" t="n">
         <v>8.140000000000001</v>
@@ -16423,7 +16423,7 @@
         <v>2.28</v>
       </c>
       <c r="I211" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J211" t="n">
         <v>8.1</v>
@@ -16498,7 +16498,7 @@
         <v>3.71</v>
       </c>
       <c r="I212" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J212" t="n">
         <v>8.029999999999999</v>
@@ -16573,7 +16573,7 @@
         <v>-2</v>
       </c>
       <c r="I213" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J213" t="n">
         <v>7.96</v>
@@ -16648,7 +16648,7 @@
         <v>5.99</v>
       </c>
       <c r="I214" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J214" t="n">
         <v>7.87</v>
@@ -16723,7 +16723,7 @@
         <v>-2.2</v>
       </c>
       <c r="I215" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J215" t="n">
         <v>7.8</v>
@@ -16798,7 +16798,7 @@
         <v>-0.99</v>
       </c>
       <c r="I216" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J216" t="n">
         <v>7.71</v>
@@ -16873,7 +16873,7 @@
         <v>4.69</v>
       </c>
       <c r="I217" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J217" t="n">
         <v>7.58</v>
@@ -16948,7 +16948,7 @@
         <v>2.99</v>
       </c>
       <c r="I218" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J218" t="n">
         <v>7.53</v>
@@ -17023,7 +17023,7 @@
         <v>-3.56</v>
       </c>
       <c r="I219" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J219" t="n">
         <v>7.46</v>
@@ -17102,7 +17102,7 @@
         <v>7.66</v>
       </c>
       <c r="I220" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J220" t="n">
         <v>7.46</v>
@@ -17177,7 +17177,7 @@
         <v>2.41</v>
       </c>
       <c r="I221" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J221" t="n">
         <v>7.49</v>
@@ -17252,7 +17252,7 @@
         <v>1.49</v>
       </c>
       <c r="I222" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J222" t="n">
         <v>7.48</v>
@@ -17327,7 +17327,7 @@
         <v>3.67</v>
       </c>
       <c r="I223" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J223" t="n">
         <v>7.49</v>
@@ -17402,7 +17402,7 @@
         <v>-5.31</v>
       </c>
       <c r="I224" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J224" t="n">
         <v>7.47</v>
@@ -17477,7 +17477,7 @@
         <v>-7.35</v>
       </c>
       <c r="I225" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J225" t="n">
         <v>7.44</v>
@@ -17552,7 +17552,7 @@
         <v>0</v>
       </c>
       <c r="I226" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J226" t="n">
         <v>7.42</v>
@@ -17627,7 +17627,7 @@
         <v>-4.03</v>
       </c>
       <c r="I227" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J227" t="n">
         <v>7.39</v>
@@ -17706,7 +17706,7 @@
         <v>-2.94</v>
       </c>
       <c r="I228" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J228" t="n">
         <v>7.37</v>
@@ -17785,7 +17785,7 @@
         <v>4.91</v>
       </c>
       <c r="I229" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J229" t="n">
         <v>7.38</v>
@@ -17860,7 +17860,7 @@
         <v>4.13</v>
       </c>
       <c r="I230" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J230" t="n">
         <v>7.43</v>
@@ -17935,7 +17935,7 @@
         <v>1.45</v>
       </c>
       <c r="I231" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J231" t="n">
         <v>7.48</v>
@@ -18010,7 +18010,7 @@
         <v>3.26</v>
       </c>
       <c r="I232" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J232" t="n">
         <v>7.53</v>
@@ -18085,7 +18085,7 @@
         <v>5.8</v>
       </c>
       <c r="I233" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J233" t="n">
         <v>7.6</v>
@@ -18160,7 +18160,7 @@
         <v>3.93</v>
       </c>
       <c r="I234" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J234" t="n">
         <v>7.68</v>
@@ -18235,7 +18235,7 @@
         <v>9.06</v>
       </c>
       <c r="I235" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J235" t="n">
         <v>7.8</v>
@@ -18310,7 +18310,7 @@
         <v>-0.53</v>
       </c>
       <c r="I236" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J236" t="n">
         <v>7.92</v>
@@ -18385,7 +18385,7 @@
         <v>-4.02</v>
       </c>
       <c r="I237" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J237" t="n">
         <v>8</v>
@@ -18460,7 +18460,7 @@
         <v>14.76</v>
       </c>
       <c r="I238" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J238" t="n">
         <v>8.15</v>
@@ -18535,7 +18535,7 @@
         <v>7.87</v>
       </c>
       <c r="I239" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J239" t="n">
         <v>8.34</v>
@@ -18610,7 +18610,7 @@
         <v>8.19</v>
       </c>
       <c r="I240" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J240" t="n">
         <v>8.56</v>
@@ -18685,7 +18685,7 @@
         <v>-1.73</v>
       </c>
       <c r="I241" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J241" t="n">
         <v>8.75</v>
@@ -18760,7 +18760,7 @@
         <v>-1.17</v>
       </c>
       <c r="I242" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J242" t="n">
         <v>8.93</v>
@@ -18835,7 +18835,7 @@
         <v>6.01</v>
       </c>
       <c r="I243" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J243" t="n">
         <v>9.130000000000001</v>
@@ -18910,7 +18910,7 @@
         <v>0.48</v>
       </c>
       <c r="I244" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J244" t="n">
         <v>9.359999999999999</v>
@@ -18985,7 +18985,7 @@
         <v>-4.05</v>
       </c>
       <c r="I245" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J245" t="n">
         <v>9.59</v>
@@ -19060,7 +19060,7 @@
         <v>5.72</v>
       </c>
       <c r="I246" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J246" t="n">
         <v>9.859999999999999</v>
@@ -19135,7 +19135,7 @@
         <v>4</v>
       </c>
       <c r="I247" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J247" t="n">
         <v>10.17</v>
@@ -19210,7 +19210,7 @@
         <v>3.17</v>
       </c>
       <c r="I248" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J248" t="n">
         <v>10.5</v>
@@ -19285,7 +19285,7 @@
         <v>-3.51</v>
       </c>
       <c r="I249" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J249" t="n">
         <v>10.8</v>
@@ -19360,7 +19360,7 @@
         <v>12.57</v>
       </c>
       <c r="I250" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J250" t="n">
         <v>11.17</v>
@@ -19435,7 +19435,7 @@
         <v>1.01</v>
       </c>
       <c r="I251" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J251" t="n">
         <v>11.53</v>
@@ -19510,7 +19510,7 @@
         <v>4.99</v>
       </c>
       <c r="I252" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J252" t="n">
         <v>11.92</v>
@@ -19585,7 +19585,7 @@
         <v>-1.46</v>
       </c>
       <c r="I253" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J253" t="n">
         <v>12.28</v>
@@ -19660,7 +19660,7 @@
         <v>13.38</v>
       </c>
       <c r="I254" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J254" t="n">
         <v>12.73</v>
@@ -19735,7 +19735,7 @@
         <v>7.21</v>
       </c>
       <c r="I255" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J255" t="n">
         <v>13.2</v>
@@ -19810,7 +19810,7 @@
         <v>-2.7</v>
       </c>
       <c r="I256" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J256" t="n">
         <v>13.64</v>
@@ -19885,7 +19885,7 @@
         <v>-5.39</v>
       </c>
       <c r="I257" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J257" t="n">
         <v>14.06</v>
@@ -19960,7 +19960,7 @@
         <v>-3.16</v>
       </c>
       <c r="I258" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J258" t="n">
         <v>14.38</v>
@@ -20035,7 +20035,7 @@
         <v>7.78</v>
       </c>
       <c r="I259" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J259" t="n">
         <v>14.72</v>
@@ -20110,7 +20110,7 @@
         <v>-9.199999999999999</v>
       </c>
       <c r="I260" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J260" t="n">
         <v>14.94</v>
@@ -20185,7 +20185,7 @@
         <v>-0.61</v>
       </c>
       <c r="I261" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J261" t="n">
         <v>15.16</v>
@@ -20260,7 +20260,7 @@
         <v>10.87</v>
       </c>
       <c r="I262" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J262" t="n">
         <v>15.48</v>
@@ -20335,7 +20335,7 @@
         <v>3.36</v>
       </c>
       <c r="I263" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J263" t="n">
         <v>15.79</v>
@@ -20410,7 +20410,7 @@
         <v>-3.57</v>
       </c>
       <c r="I264" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J264" t="n">
         <v>16.07</v>
@@ -20485,7 +20485,7 @@
         <v>14.14</v>
       </c>
       <c r="I265" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J265" t="n">
         <v>16.5</v>
@@ -20560,7 +20560,7 @@
         <v>1.06</v>
       </c>
       <c r="I266" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J266" t="n">
         <v>16.9</v>
@@ -20635,7 +20635,7 @@
         <v>7.14</v>
       </c>
       <c r="I267" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J267" t="n">
         <v>17.36</v>
@@ -20710,7 +20710,7 @@
         <v>-6.79</v>
       </c>
       <c r="I268" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J268" t="n">
         <v>17.72</v>
@@ -20785,7 +20785,7 @@
         <v>4.46</v>
       </c>
       <c r="I269" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J269" t="n">
         <v>18.15</v>
@@ -20860,7 +20860,7 @@
         <v>5</v>
       </c>
       <c r="I270" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J270" t="n">
         <v>18.55</v>
@@ -20935,7 +20935,7 @@
         <v>14.65</v>
       </c>
       <c r="I271" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J271" t="n">
         <v>19.1</v>
@@ -21010,7 +21010,7 @@
         <v>-5.03</v>
       </c>
       <c r="I272" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J272" t="n">
         <v>19.56</v>
@@ -21085,7 +21085,7 @@
         <v>10.96</v>
       </c>
       <c r="I273" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J273" t="n">
         <v>20.17</v>
@@ -21160,7 +21160,7 @@
         <v>9.08</v>
       </c>
       <c r="I274" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J274" t="n">
         <v>20.79</v>
@@ -21235,7 +21235,7 @@
         <v>2.79</v>
       </c>
       <c r="I275" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J275" t="n">
         <v>21.4</v>
@@ -21310,7 +21310,7 @@
         <v>1.65</v>
       </c>
       <c r="I276" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J276" t="n">
         <v>22.05</v>
@@ -21385,7 +21385,7 @@
         <v>-7.15</v>
       </c>
       <c r="I277" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J277" t="n">
         <v>22.64</v>
@@ -21460,7 +21460,7 @@
         <v>-31.09</v>
       </c>
       <c r="I278" s="4" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J278" s="4" t="n">
         <v>22.81</v>
@@ -21539,7 +21539,7 @@
         <v>4.37</v>
       </c>
       <c r="I279" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J279" t="n">
         <v>22.95</v>
@@ -21614,7 +21614,7 @@
         <v>-18.45</v>
       </c>
       <c r="I280" s="4" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J280" s="4" t="n">
         <v>22.99</v>
@@ -21689,7 +21689,7 @@
         <v>1.52</v>
       </c>
       <c r="I281" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J281" t="n">
         <v>23.04</v>
@@ -21768,7 +21768,7 @@
         <v>15.68</v>
       </c>
       <c r="I282" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J282" t="n">
         <v>23.14</v>
@@ -21843,7 +21843,7 @@
         <v>-7.25</v>
       </c>
       <c r="I283" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J283" t="n">
         <v>23.13</v>
@@ -21918,7 +21918,7 @@
         <v>5.46</v>
       </c>
       <c r="I284" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J284" t="n">
         <v>23.21</v>
@@ -21993,7 +21993,7 @@
         <v>-20.25</v>
       </c>
       <c r="I285" s="4" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J285" s="4" t="n">
         <v>22.97</v>
@@ -22066,7 +22066,7 @@
         <v>0.64</v>
       </c>
       <c r="I286" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J286" t="n">
         <v>22.71</v>
@@ -22145,7 +22145,7 @@
         <v>21</v>
       </c>
       <c r="I287" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J287" t="n">
         <v>22.55</v>
@@ -22220,7 +22220,7 @@
         <v>3.4</v>
       </c>
       <c r="I288" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J288" t="n">
         <v>22.5</v>
@@ -22295,7 +22295,7 @@
         <v>-5.01</v>
       </c>
       <c r="I289" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J289" t="n">
         <v>22.35</v>
@@ -22370,7 +22370,7 @@
         <v>5.8</v>
       </c>
       <c r="I290" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J290" t="n">
         <v>22.2</v>
@@ -22445,7 +22445,7 @@
         <v>-19.32</v>
       </c>
       <c r="I291" s="4" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J291" s="4" t="n">
         <v>21.69</v>
@@ -22528,7 +22528,7 @@
         <v>17.71</v>
       </c>
       <c r="I292" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J292" t="n">
         <v>21.39</v>
@@ -22603,7 +22603,7 @@
         <v>-11.12</v>
       </c>
       <c r="I293" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J293" t="n">
         <v>20.85</v>
@@ -22682,7 +22682,7 @@
         <v>-2.38</v>
       </c>
       <c r="I294" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J294" t="n">
         <v>20.16</v>
@@ -22757,7 +22757,7 @@
         <v>-17.58</v>
       </c>
       <c r="I295" s="4" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J295" s="4" t="n">
         <v>19.28</v>
@@ -22832,7 +22832,7 @@
         <v>1.48</v>
       </c>
       <c r="I296" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J296" t="n">
         <v>18.39</v>
@@ -22911,7 +22911,7 @@
         <v>-11.24</v>
       </c>
       <c r="I297" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J297" t="n">
         <v>17.54</v>
@@ -22990,7 +22990,7 @@
         <v>16.86</v>
       </c>
       <c r="I298" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J298" t="n">
         <v>17.24</v>
@@ -23065,7 +23065,7 @@
         <v>7.67</v>
       </c>
       <c r="I299" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J299" t="n">
         <v>16.96</v>
@@ -23140,7 +23140,7 @@
         <v>-7.78</v>
       </c>
       <c r="I300" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J300" t="n">
         <v>16.8</v>
@@ -23215,7 +23215,7 @@
         <v>7.02</v>
       </c>
       <c r="I301" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J301" t="n">
         <v>16.69</v>
@@ -23290,7 +23290,7 @@
         <v>2.98</v>
       </c>
       <c r="I302" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J302" t="n">
         <v>16.46</v>
@@ -23369,7 +23369,7 @@
         <v>30.23</v>
       </c>
       <c r="I303" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J303" t="n">
         <v>16.54</v>
@@ -23444,7 +23444,7 @@
         <v>-1.38</v>
       </c>
       <c r="I304" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J304" t="n">
         <v>16.55</v>
@@ -23519,7 +23519,7 @@
         <v>-1.35</v>
       </c>
       <c r="I305" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J305" t="n">
         <v>16.75</v>
@@ -23594,7 +23594,7 @@
         <v>5.08</v>
       </c>
       <c r="I306" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J306" t="n">
         <v>17</v>
@@ -23669,7 +23669,7 @@
         <v>11.98</v>
       </c>
       <c r="I307" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J307" t="n">
         <v>17.2</v>
@@ -23744,7 +23744,7 @@
         <v>-3.84</v>
       </c>
       <c r="I308" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J308" t="n">
         <v>17.32</v>
@@ -23819,7 +23819,7 @@
         <v>5.2</v>
       </c>
       <c r="I309" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J309" t="n">
         <v>17.56</v>
@@ -23894,7 +23894,7 @@
         <v>9.98</v>
       </c>
       <c r="I310" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J310" t="n">
         <v>17.85</v>
@@ -23969,7 +23969,7 @@
         <v>-4.23</v>
       </c>
       <c r="I311" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J311" t="n">
         <v>18.28</v>
@@ -24044,7 +24044,7 @@
         <v>-6.52</v>
       </c>
       <c r="I312" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J312" t="n">
         <v>18.5</v>
@@ -24119,7 +24119,7 @@
         <v>17.54</v>
       </c>
       <c r="I313" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J313" t="n">
         <v>19.01</v>
@@ -24194,7 +24194,7 @@
         <v>-9.65</v>
       </c>
       <c r="I314" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J314" t="n">
         <v>19.42</v>
@@ -24269,7 +24269,7 @@
         <v>7.34</v>
       </c>
       <c r="I315" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J315" t="n">
         <v>20.06</v>
@@ -24344,7 +24344,7 @@
         <v>4.67</v>
       </c>
       <c r="I316" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J316" t="n">
         <v>20.75</v>
@@ -24419,7 +24419,7 @@
         <v>-4.57</v>
       </c>
       <c r="I317" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J317" t="n">
         <v>21.46</v>
@@ -24494,7 +24494,7 @@
         <v>-0.8</v>
       </c>
       <c r="I318" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J318" t="n">
         <v>22.05</v>
@@ -24569,7 +24569,7 @@
         <v>12.69</v>
       </c>
       <c r="I319" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J319" t="n">
         <v>22.76</v>
@@ -24644,7 +24644,7 @@
         <v>2.52</v>
       </c>
       <c r="I320" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J320" t="n">
         <v>23.56</v>
@@ -24719,7 +24719,7 @@
         <v>3.19</v>
       </c>
       <c r="I321" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J321" t="n">
         <v>24.36</v>
@@ -24794,7 +24794,7 @@
         <v>17.69</v>
       </c>
       <c r="I322" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J322" t="n">
         <v>25.41</v>
@@ -24869,7 +24869,7 @@
         <v>14.65</v>
       </c>
       <c r="I323" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J323" t="n">
         <v>26.5</v>
@@ -24944,7 +24944,7 @@
         <v>-8.41</v>
       </c>
       <c r="I324" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J324" t="n">
         <v>27.42</v>
@@ -25019,7 +25019,7 @@
         <v>22.62</v>
       </c>
       <c r="I325" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J325" t="n">
         <v>28.79</v>
@@ -25094,7 +25094,7 @@
         <v>4.33</v>
       </c>
       <c r="I326" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J326" t="n">
         <v>30.21</v>
@@ -25169,7 +25169,7 @@
         <v>-22.56</v>
       </c>
       <c r="I327" s="4" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J327" s="4" t="n">
         <v>30.96</v>
@@ -25244,7 +25244,7 @@
         <v>17.42</v>
       </c>
       <c r="I328" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J328" t="n">
         <v>32.08</v>
@@ -25319,7 +25319,7 @@
         <v>2.91</v>
       </c>
       <c r="I329" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J329" t="n">
         <v>33.2</v>
@@ -25394,7 +25394,7 @@
         <v>-18.31</v>
       </c>
       <c r="I330" s="4" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J330" s="4" t="n">
         <v>33.79</v>
@@ -25469,7 +25469,7 @@
         <v>-5</v>
       </c>
       <c r="I331" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J331" t="n">
         <v>34.34</v>
@@ -25544,7 +25544,7 @@
         <v>-3.36</v>
       </c>
       <c r="I332" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J332" t="n">
         <v>34.91</v>
@@ -25623,7 +25623,7 @@
         <v>10.26</v>
       </c>
       <c r="I333" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J333" t="n">
         <v>35.46</v>
@@ -25698,7 +25698,7 @@
         <v>10.31</v>
       </c>
       <c r="I334" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J334" t="n">
         <v>36.33</v>
@@ -25773,7 +25773,7 @@
         <v>-6.98</v>
       </c>
       <c r="I335" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J335" t="n">
         <v>36.96</v>
@@ -25848,7 +25848,7 @@
         <v>30.06</v>
       </c>
       <c r="I336" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J336" t="n">
         <v>38.12</v>
@@ -25923,7 +25923,7 @@
         <v>-3.57</v>
       </c>
       <c r="I337" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J337" t="n">
         <v>39.25</v>
@@ -25998,7 +25998,7 @@
         <v>12.4</v>
       </c>
       <c r="I338" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J338" t="n">
         <v>40.7</v>
@@ -26073,7 +26073,7 @@
         <v>-0.93</v>
       </c>
       <c r="I339" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J339" t="n">
         <v>41.96</v>
@@ -26148,7 +26148,7 @@
         <v>16.04</v>
       </c>
       <c r="I340" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J340" t="n">
         <v>43.61</v>
@@ -26223,7 +26223,7 @@
         <v>-3.16</v>
       </c>
       <c r="I341" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J341" t="n">
         <v>45.12</v>
@@ -26298,7 +26298,7 @@
         <v>-2.29</v>
       </c>
       <c r="I342" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J342" t="n">
         <v>46.28</v>
@@ -26373,7 +26373,7 @@
         <v>-12.28</v>
       </c>
       <c r="I343" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J343" t="n">
         <v>46.81</v>
@@ -26448,7 +26448,7 @@
         <v>-41.89</v>
       </c>
       <c r="I344" s="4" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J344" s="4" t="n">
         <v>46.41</v>
@@ -26527,7 +26527,7 @@
         <v>16.3</v>
       </c>
       <c r="I345" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J345" t="n">
         <v>45.83</v>
@@ -26602,7 +26602,7 @@
         <v>-2.45</v>
       </c>
       <c r="I346" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J346" t="n">
         <v>45.1</v>
@@ -26677,7 +26677,7 @@
         <v>-9.050000000000001</v>
       </c>
       <c r="I347" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J347" t="n">
         <v>44.77</v>
@@ -26752,7 +26752,7 @@
         <v>33.78</v>
       </c>
       <c r="I348" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J348" t="n">
         <v>44.64</v>
@@ -26827,7 +26827,7 @@
         <v>-2.04</v>
       </c>
       <c r="I349" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J349" t="n">
         <v>44.41</v>
@@ -26902,7 +26902,7 @@
         <v>21.14</v>
       </c>
       <c r="I350" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J350" t="n">
         <v>45.03</v>
@@ -26977,7 +26977,7 @@
         <v>-8.029999999999999</v>
       </c>
       <c r="I351" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J351" t="n">
         <v>45.54</v>
@@ -27052,7 +27052,7 @@
         <v>-0.5</v>
       </c>
       <c r="I352" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J352" t="n">
         <v>46.1</v>
@@ -27131,7 +27131,7 @@
         <v>19.29</v>
       </c>
       <c r="I353" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J353" t="n">
         <v>46.93</v>
@@ -27206,7 +27206,7 @@
         <v>-0.2</v>
       </c>
       <c r="I354" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J354" t="n">
         <v>47.55</v>
@@ -27281,7 +27281,7 @@
         <v>-35.7</v>
       </c>
       <c r="I355" s="4" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J355" s="4" t="n">
         <v>47.35</v>
@@ -27360,7 +27360,7 @@
         <v>5.89</v>
       </c>
       <c r="I356" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J356" t="n">
         <v>46.66</v>
@@ -27435,7 +27435,7 @@
         <v>11.85</v>
       </c>
       <c r="I357" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J357" t="n">
         <v>46.29</v>
@@ -27510,7 +27510,7 @@
         <v>-10.9</v>
       </c>
       <c r="I358" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J358" t="n">
         <v>45.39</v>
@@ -27585,7 +27585,7 @@
         <v>-0.03</v>
       </c>
       <c r="I359" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J359" t="n">
         <v>44.51</v>
@@ -27660,7 +27660,7 @@
         <v>5.82</v>
       </c>
       <c r="I360" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J360" t="n">
         <v>43.3</v>
@@ -27735,7 +27735,7 @@
         <v>-23.21</v>
       </c>
       <c r="I361" s="4" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J361" s="4" t="n">
         <v>41.74</v>
@@ -27814,7 +27814,7 @@
         <v>-9.77</v>
       </c>
       <c r="I362" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J362" t="n">
         <v>40.1</v>
@@ -27893,7 +27893,7 @@
         <v>15.37</v>
       </c>
       <c r="I363" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J363" t="n">
         <v>39.04</v>
@@ -27968,7 +27968,7 @@
         <v>-12.78</v>
       </c>
       <c r="I364" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J364" t="n">
         <v>38.87</v>
@@ -28047,7 +28047,7 @@
         <v>1.58</v>
       </c>
       <c r="I365" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J365" t="n">
         <v>38.48</v>
@@ -28122,7 +28122,7 @@
         <v>3</v>
       </c>
       <c r="I366" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J366" t="n">
         <v>38.18</v>
@@ -28197,7 +28197,7 @@
         <v>-2.28</v>
       </c>
       <c r="I367" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J367" t="n">
         <v>38</v>
@@ -28276,7 +28276,7 @@
         <v>-24.74</v>
       </c>
       <c r="I368" s="4" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J368" s="4" t="n">
         <v>36.94</v>
@@ -28351,7 +28351,7 @@
         <v>14.84</v>
       </c>
       <c r="I369" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J369" t="n">
         <v>36.08</v>
@@ -28426,7 +28426,7 @@
         <v>-9.140000000000001</v>
       </c>
       <c r="I370" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J370" t="n">
         <v>34.68</v>
@@ -28501,7 +28501,7 @@
         <v>-14.72</v>
       </c>
       <c r="I371" s="4" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J371" s="4" t="n">
         <v>33.31</v>
@@ -28580,7 +28580,7 @@
         <v>-2.09</v>
       </c>
       <c r="I372" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J372" t="n">
         <v>31.94</v>
@@ -28659,7 +28659,7 @@
         <v>0.82</v>
       </c>
       <c r="I373" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J373" t="n">
         <v>30.13</v>
@@ -28736,7 +28736,7 @@
         <v>18.03</v>
       </c>
       <c r="I374" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J374" t="n">
         <v>28.5</v>
@@ -28809,7 +28809,7 @@
         <v>-4.46</v>
       </c>
       <c r="I375" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J375" t="n">
         <v>27.79</v>
@@ -28882,7 +28882,7 @@
         <v>6.02</v>
       </c>
       <c r="I376" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J376" t="n">
         <v>27.03</v>
@@ -28955,7 +28955,7 @@
         <v>-18.9</v>
       </c>
       <c r="I377" s="4" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J377" s="4" t="n">
         <v>25.85</v>
@@ -29032,7 +29032,7 @@
         <v>-3.59</v>
       </c>
       <c r="I378" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J378" t="n">
         <v>24.87</v>
@@ -29105,7 +29105,7 @@
         <v>-17.78</v>
       </c>
       <c r="I379" s="4" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J379" s="4" t="n">
         <v>23.73</v>
@@ -29182,7 +29182,7 @@
         <v>-14.63</v>
       </c>
       <c r="I380" s="4" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J380" s="4" t="n">
         <v>22.38</v>
@@ -29259,7 +29259,7 @@
         <v>34.77</v>
       </c>
       <c r="I381" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J381" t="n">
         <v>21.69</v>
@@ -29332,7 +29332,7 @@
         <v>-7.92</v>
       </c>
       <c r="I382" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J382" t="n">
         <v>21.09</v>
@@ -29405,7 +29405,7 @@
         <v>5.87</v>
       </c>
       <c r="I383" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J383" t="n">
         <v>20.32</v>
@@ -29478,7 +29478,7 @@
         <v>20.48</v>
       </c>
       <c r="I384" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J384" t="n">
         <v>19.91</v>
@@ -29551,7 +29551,7 @@
         <v>-3.56</v>
       </c>
       <c r="I385" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J385" t="n">
         <v>19.45</v>
@@ -29624,7 +29624,7 @@
         <v>-8.84</v>
       </c>
       <c r="I386" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J386" t="n">
         <v>18.87</v>
@@ -29697,7 +29697,7 @@
         <v>3.27</v>
       </c>
       <c r="I387" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J387" t="n">
         <v>18.34</v>
@@ -29770,7 +29770,7 @@
         <v>-5.47</v>
       </c>
       <c r="I388" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J388" t="n">
         <v>18.12</v>
@@ -29843,7 +29843,7 @@
         <v>7.5</v>
       </c>
       <c r="I389" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J389" t="n">
         <v>17.8</v>
@@ -29916,7 +29916,7 @@
         <v>15.19</v>
       </c>
       <c r="I390" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J390" t="n">
         <v>17.72</v>
@@ -29989,7 +29989,7 @@
         <v>4.68</v>
       </c>
       <c r="I391" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J391" t="n">
         <v>17.85</v>
@@ -30062,7 +30062,7 @@
         <v>1.55</v>
       </c>
       <c r="I392" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J392" t="n">
         <v>18.02</v>
@@ -30135,7 +30135,7 @@
         <v>8.98</v>
       </c>
       <c r="I393" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J393" t="n">
         <v>18.27</v>
@@ -30208,7 +30208,7 @@
         <v>-24.21</v>
       </c>
       <c r="I394" s="4" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J394" s="4" t="n">
         <v>18.08</v>
@@ -30285,7 +30285,7 @@
         <v>7.12</v>
       </c>
       <c r="I395" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J395" t="n">
         <v>18</v>
@@ -30358,7 +30358,7 @@
         <v>6.38</v>
       </c>
       <c r="I396" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J396" t="n">
         <v>17.91</v>
@@ -30431,7 +30431,7 @@
         <v>0.15</v>
       </c>
       <c r="I397" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J397" t="n">
         <v>18.04</v>
@@ -30504,7 +30504,7 @@
         <v>-7.86</v>
       </c>
       <c r="I398" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J398" t="n">
         <v>18.11</v>
@@ -30577,7 +30577,7 @@
         <v>11.03</v>
       </c>
       <c r="I399" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J399" t="n">
         <v>18.45</v>
@@ -30650,7 +30650,7 @@
         <v>-1.63</v>
       </c>
       <c r="I400" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J400" t="n">
         <v>18.87</v>
@@ -30723,7 +30723,7 @@
         <v>4.49</v>
       </c>
       <c r="I401" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J401" t="n">
         <v>19.12</v>
@@ -30796,7 +30796,7 @@
         <v>-2.99</v>
       </c>
       <c r="I402" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J402" t="n">
         <v>19.41</v>
@@ -30869,7 +30869,7 @@
         <v>0.91</v>
       </c>
       <c r="I403" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J403" t="n">
         <v>19.67</v>
@@ -30942,7 +30942,7 @@
         <v>-8.49</v>
       </c>
       <c r="I404" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J404" t="n">
         <v>19.67</v>
@@ -31019,7 +31019,7 @@
         <v>5.06</v>
       </c>
       <c r="I405" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J405" t="n">
         <v>19.76</v>
@@ -31092,7 +31092,7 @@
         <v>2.68</v>
       </c>
       <c r="I406" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J406" t="n">
         <v>19.95</v>
@@ -31165,7 +31165,7 @@
         <v>13.44</v>
       </c>
       <c r="I407" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J407" t="n">
         <v>20.26</v>
@@ -31238,7 +31238,7 @@
         <v>1.58</v>
       </c>
       <c r="I408" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J408" t="n">
         <v>20.63</v>
@@ -31311,7 +31311,7 @@
         <v>1.51</v>
       </c>
       <c r="I409" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J409" t="n">
         <v>20.96</v>
@@ -31384,7 +31384,7 @@
         <v>-12.52</v>
       </c>
       <c r="I410" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J410" t="n">
         <v>21</v>
@@ -31451,13 +31451,13 @@
         <v>23.07</v>
       </c>
       <c r="G411" t="n">
-        <v>16025600</v>
+        <v>16124500</v>
       </c>
       <c r="H411" s="1" t="n">
         <v>8.970000000000001</v>
       </c>
       <c r="I411" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="J411" t="n">
         <v>21.09</v>
@@ -31501,61 +31501,79 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" t="inlineStr">
-        <is>
-          <t>KORU</t>
-        </is>
-      </c>
-      <c r="B412" t="inlineStr">
+      <c r="A412" s="4" t="inlineStr">
+        <is>
+          <t>KORU</t>
+        </is>
+      </c>
+      <c r="B412" s="4" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
-      <c r="G412" t="n">
-        <v>38025096</v>
-      </c>
-      <c r="H412" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I412" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr"/>
-      <c r="L412" t="inlineStr"/>
-      <c r="M412" t="inlineStr"/>
-      <c r="N412" s="3" t="n">
-        <v>63.56</v>
-      </c>
-      <c r="O412" t="n">
-        <v>31</v>
-      </c>
-      <c r="P412" t="inlineStr">
+      <c r="C412" s="4" t="n">
+        <v>19.38</v>
+      </c>
+      <c r="D412" s="4" t="n">
+        <v>19.77</v>
+      </c>
+      <c r="E412" s="4" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="F412" s="4" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="G412" s="4" t="n">
+        <v>38357200</v>
+      </c>
+      <c r="H412" s="5" t="n">
+        <v>-19.51</v>
+      </c>
+      <c r="I412" s="4" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="J412" s="4" t="n">
+        <v>20.94</v>
+      </c>
+      <c r="K412" s="4" t="n">
+        <v>23.63</v>
+      </c>
+      <c r="L412" s="4" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M412" s="4" t="n">
+        <v>23.08</v>
+      </c>
+      <c r="N412" s="6" t="n">
+        <v>49.53</v>
+      </c>
+      <c r="O412" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="P412" s="4" t="inlineStr">
         <is>
           <t>fear</t>
         </is>
       </c>
-      <c r="Q412" t="inlineStr">
-        <is>
-          <t>BUY STOP</t>
-        </is>
-      </c>
-      <c r="R412" t="inlineStr"/>
-      <c r="S412" t="n">
+      <c r="Q412" s="4" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R412" s="4" t="inlineStr">
+        <is>
+          <t>1st: MA20, 10% cash</t>
+        </is>
+      </c>
+      <c r="S412" s="4" t="n">
         <v>4.96</v>
       </c>
-      <c r="T412" s="3" t="n">
+      <c r="T412" s="6" t="n">
         <v>17.1</v>
       </c>
-      <c r="U412" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="V412" t="inlineStr"/>
-      <c r="W412" s="3" t="n">
+      <c r="U412" s="6" t="inlineStr"/>
+      <c r="V412" s="4" t="inlineStr"/>
+      <c r="W412" s="6" t="n">
         <v>152.1</v>
       </c>
     </row>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31548,7 +31548,7 @@
         <v>49.53</v>
       </c>
       <c r="O412" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P412" s="4" t="inlineStr">
         <is>
@@ -31577,6 +31577,79 @@
         <v>152.1</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>KORU</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>19.34</v>
+      </c>
+      <c r="D413" t="n">
+        <v>19.38</v>
+      </c>
+      <c r="E413" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="F413" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="G413" t="n">
+        <v>14223761</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I413" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="J413" t="n">
+        <v>20.69</v>
+      </c>
+      <c r="K413" t="n">
+        <v>23.03</v>
+      </c>
+      <c r="L413" t="n">
+        <v>28.41</v>
+      </c>
+      <c r="M413" t="n">
+        <v>23.14</v>
+      </c>
+      <c r="N413" s="3" t="n">
+        <v>43.83</v>
+      </c>
+      <c r="O413" t="n">
+        <v>29</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="T413" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="U413" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -645,9 +645,7 @@
       <c r="T2" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="U2" s="3" t="n">
-        <v>9</v>
-      </c>
+      <c r="U2" s="3" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" s="2" t="n">
         <v>173.2</v>
@@ -724,9 +722,7 @@
       <c r="T3" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="U3" s="3" t="n">
-        <v>14.7</v>
-      </c>
+      <c r="U3" s="3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" s="2" t="n">
         <v>168.6</v>
@@ -799,9 +795,7 @@
       <c r="T4" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="U4" s="3" t="n">
-        <v>13.5</v>
-      </c>
+      <c r="U4" s="3" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" s="2" t="n">
         <v>163.6</v>
@@ -874,9 +868,7 @@
       <c r="T5" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="U5" s="3" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U5" s="3" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" s="2" t="n">
         <v>157.4</v>
@@ -949,9 +941,7 @@
       <c r="T6" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="U6" s="3" t="n">
-        <v>14.7</v>
-      </c>
+      <c r="U6" s="3" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" s="2" t="n">
         <v>156.7</v>
@@ -1028,9 +1018,7 @@
       <c r="T7" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="U7" s="3" t="n">
-        <v>16.5</v>
-      </c>
+      <c r="U7" s="3" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" s="2" t="n">
         <v>158.5</v>
@@ -1103,9 +1091,7 @@
       <c r="T8" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="U8" s="3" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="U8" s="3" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
       <c r="W8" s="2" t="n">
         <v>155.4</v>
@@ -1178,9 +1164,7 @@
       <c r="T9" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="U9" s="3" t="n">
-        <v>15</v>
-      </c>
+      <c r="U9" s="3" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
       <c r="W9" s="2" t="n">
         <v>159.4</v>
@@ -1253,9 +1237,7 @@
       <c r="T10" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="U10" s="3" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U10" s="3" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10" s="2" t="n">
         <v>162.6</v>
@@ -1328,9 +1310,7 @@
       <c r="T11" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="U11" s="3" t="n">
-        <v>15.8</v>
-      </c>
+      <c r="U11" s="3" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
       <c r="W11" s="2" t="n">
         <v>163.6</v>
@@ -1407,9 +1387,7 @@
       <c r="T12" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="U12" s="3" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U12" s="3" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12" s="2" t="n">
         <v>166.5</v>
@@ -1482,9 +1460,7 @@
       <c r="T13" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="U13" s="3" t="n">
-        <v>11.3</v>
-      </c>
+      <c r="U13" s="3" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
       <c r="W13" s="2" t="n">
         <v>166.9</v>
@@ -1557,9 +1533,7 @@
       <c r="T14" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="U14" s="3" t="n">
-        <v>14.1</v>
-      </c>
+      <c r="U14" s="3" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" s="2" t="n">
         <v>168.8</v>
@@ -1632,9 +1606,7 @@
       <c r="T15" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="U15" s="3" t="n">
-        <v>12.8</v>
-      </c>
+      <c r="U15" s="3" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15" s="2" t="n">
         <v>166.1</v>
@@ -1707,9 +1679,7 @@
       <c r="T16" s="3" t="n">
         <v>15.1</v>
       </c>
-      <c r="U16" s="3" t="n">
-        <v>11</v>
-      </c>
+      <c r="U16" s="3" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" s="2" t="n">
         <v>163.4</v>
@@ -1782,9 +1752,7 @@
       <c r="T17" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="U17" s="3" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U17" s="3" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
       <c r="W17" s="2" t="n">
         <v>168</v>
@@ -1826,7 +1794,7 @@
         <v>2.11</v>
       </c>
       <c r="K18" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="L18" t="n">
         <v>2.59</v>
@@ -1857,9 +1825,7 @@
       <c r="T18" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="U18" s="3" t="n">
-        <v>9.300000000000001</v>
-      </c>
+      <c r="U18" s="3" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
       <c r="W18" s="2" t="n">
         <v>183.1</v>
@@ -1932,9 +1898,7 @@
       <c r="T19" s="3" t="n">
         <v>15.3</v>
       </c>
-      <c r="U19" s="3" t="n">
-        <v>9.300000000000001</v>
-      </c>
+      <c r="U19" s="3" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
       <c r="W19" s="2" t="n">
         <v>175.8</v>
@@ -2007,9 +1971,7 @@
       <c r="T20" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="U20" s="3" t="n">
-        <v>11.2</v>
-      </c>
+      <c r="U20" s="3" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
       <c r="W20" s="2" t="n">
         <v>178.6</v>
@@ -2082,9 +2044,7 @@
       <c r="T21" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="U21" s="3" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="U21" s="3" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
       <c r="W21" s="2" t="n">
         <v>165</v>
@@ -2157,9 +2117,7 @@
       <c r="T22" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="U22" s="3" t="n">
-        <v>15.1</v>
-      </c>
+      <c r="U22" s="3" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
       <c r="W22" s="2" t="n">
         <v>156.9</v>
@@ -2201,7 +2159,7 @@
         <v>2.17</v>
       </c>
       <c r="K23" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="L23" t="n">
         <v>2.53</v>
@@ -2232,9 +2190,7 @@
       <c r="T23" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="U23" s="3" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U23" s="3" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
       <c r="W23" s="2" t="n">
         <v>157.6</v>
@@ -2307,9 +2263,7 @@
       <c r="T24" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="U24" s="3" t="n">
-        <v>20.5</v>
-      </c>
+      <c r="U24" s="3" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
       <c r="W24" s="3" t="n">
         <v>153.4</v>
@@ -2386,9 +2340,7 @@
       <c r="T25" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="U25" s="3" t="n">
-        <v>19.5</v>
-      </c>
+      <c r="U25" s="3" t="inlineStr"/>
       <c r="V25" t="inlineStr"/>
       <c r="W25" s="3" t="n">
         <v>149.3</v>
@@ -2465,9 +2417,7 @@
       <c r="T26" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="U26" s="3" t="n">
-        <v>18.7</v>
-      </c>
+      <c r="U26" s="3" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
       <c r="W26" s="2" t="n">
         <v>157.9</v>
@@ -2540,9 +2490,7 @@
       <c r="T27" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="U27" s="3" t="n">
-        <v>21.8</v>
-      </c>
+      <c r="U27" s="3" t="inlineStr"/>
       <c r="V27" t="inlineStr"/>
       <c r="W27" s="3" t="n">
         <v>154.3</v>
@@ -2615,9 +2563,7 @@
       <c r="T28" s="3" t="n">
         <v>23.5</v>
       </c>
-      <c r="U28" s="3" t="n">
-        <v>24.6</v>
-      </c>
+      <c r="U28" s="3" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
       <c r="W28" s="3" t="n">
         <v>151.4</v>
@@ -2690,9 +2636,7 @@
       <c r="T29" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="U29" s="3" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U29" s="3" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
       <c r="W29" s="3" t="n">
         <v>138.9</v>
@@ -2769,9 +2713,7 @@
       <c r="T30" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="U30" s="1" t="n">
-        <v>31.1</v>
-      </c>
+      <c r="U30" s="3" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
       <c r="W30" s="3" t="n">
         <v>137.6</v>
@@ -2844,9 +2786,7 @@
       <c r="T31" s="3" t="n">
         <v>23.4</v>
       </c>
-      <c r="U31" s="3" t="n">
-        <v>24.7</v>
-      </c>
+      <c r="U31" s="3" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
       <c r="W31" s="3" t="n">
         <v>139.9</v>
@@ -2923,14 +2863,8 @@
       <c r="T32" s="1" t="n">
         <v>27.9</v>
       </c>
-      <c r="U32" s="1" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="V32" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U32" s="3" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
       <c r="W32" s="3" t="n">
         <v>146</v>
       </c>
@@ -3002,14 +2936,8 @@
       <c r="T33" s="1" t="n">
         <v>26.9</v>
       </c>
-      <c r="U33" s="1" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="V33" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U33" s="3" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
       <c r="W33" s="3" t="n">
         <v>132.8</v>
       </c>
@@ -3081,9 +3009,7 @@
       <c r="T34" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="U34" s="3" t="n">
-        <v>23.2</v>
-      </c>
+      <c r="U34" s="3" t="inlineStr"/>
       <c r="V34" t="inlineStr"/>
       <c r="W34" s="3" t="n">
         <v>128.7</v>
@@ -3160,9 +3086,7 @@
       <c r="T35" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="U35" s="3" t="n">
-        <v>23.4</v>
-      </c>
+      <c r="U35" s="3" t="inlineStr"/>
       <c r="V35" t="inlineStr"/>
       <c r="W35" s="3" t="n">
         <v>128.9</v>
@@ -3235,9 +3159,7 @@
       <c r="T36" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="U36" s="3" t="n">
-        <v>21.4</v>
-      </c>
+      <c r="U36" s="3" t="inlineStr"/>
       <c r="V36" t="inlineStr"/>
       <c r="W36" s="3" t="n">
         <v>130.3</v>
@@ -3310,9 +3232,7 @@
       <c r="T37" s="3" t="n">
         <v>20.5</v>
       </c>
-      <c r="U37" s="3" t="n">
-        <v>16.4</v>
-      </c>
+      <c r="U37" s="3" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
       <c r="W37" s="3" t="n">
         <v>133.9</v>
@@ -3385,9 +3305,7 @@
       <c r="T38" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="U38" s="3" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U38" s="3" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
       <c r="W38" s="3" t="n">
         <v>136.8</v>
@@ -3460,9 +3378,7 @@
       <c r="T39" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="U39" s="3" t="n">
-        <v>18.5</v>
-      </c>
+      <c r="U39" s="3" t="inlineStr"/>
       <c r="V39" t="inlineStr"/>
       <c r="W39" s="3" t="n">
         <v>136.4</v>
@@ -3535,9 +3451,7 @@
       <c r="T40" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="U40" s="3" t="n">
-        <v>18.6</v>
-      </c>
+      <c r="U40" s="3" t="inlineStr"/>
       <c r="V40" t="inlineStr"/>
       <c r="W40" s="3" t="n">
         <v>140.8</v>
@@ -3610,9 +3524,7 @@
       <c r="T41" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="U41" s="3" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U41" s="3" t="inlineStr"/>
       <c r="V41" t="inlineStr"/>
       <c r="W41" s="3" t="n">
         <v>141.7</v>
@@ -3685,9 +3597,7 @@
       <c r="T42" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="U42" s="3" t="n">
-        <v>13</v>
-      </c>
+      <c r="U42" s="3" t="inlineStr"/>
       <c r="V42" t="inlineStr"/>
       <c r="W42" s="3" t="n">
         <v>144</v>
@@ -3760,9 +3670,7 @@
       <c r="T43" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="U43" s="3" t="n">
-        <v>12.2</v>
-      </c>
+      <c r="U43" s="3" t="inlineStr"/>
       <c r="V43" t="inlineStr"/>
       <c r="W43" s="3" t="n">
         <v>148.7</v>
@@ -3835,9 +3743,7 @@
       <c r="T44" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="U44" s="3" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U44" s="3" t="inlineStr"/>
       <c r="V44" t="inlineStr"/>
       <c r="W44" s="3" t="n">
         <v>144.8</v>
@@ -3910,9 +3816,7 @@
       <c r="T45" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="U45" s="3" t="n">
-        <v>17.1</v>
-      </c>
+      <c r="U45" s="3" t="inlineStr"/>
       <c r="V45" t="inlineStr"/>
       <c r="W45" s="3" t="n">
         <v>140.9</v>
@@ -3989,9 +3893,7 @@
       <c r="T46" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="U46" s="1" t="n">
-        <v>25.4</v>
-      </c>
+      <c r="U46" s="3" t="inlineStr"/>
       <c r="V46" t="inlineStr"/>
       <c r="W46" s="3" t="n">
         <v>139</v>
@@ -4064,9 +3966,7 @@
       <c r="T47" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="U47" s="3" t="n">
-        <v>21.8</v>
-      </c>
+      <c r="U47" s="3" t="inlineStr"/>
       <c r="V47" t="inlineStr"/>
       <c r="W47" s="3" t="n">
         <v>148.6</v>
@@ -4139,9 +4039,7 @@
       <c r="T48" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="U48" s="3" t="n">
-        <v>20.1</v>
-      </c>
+      <c r="U48" s="3" t="inlineStr"/>
       <c r="V48" t="inlineStr"/>
       <c r="W48" s="3" t="n">
         <v>143</v>
@@ -4214,9 +4112,7 @@
       <c r="T49" s="3" t="n">
         <v>21.5</v>
       </c>
-      <c r="U49" s="1" t="n">
-        <v>26.7</v>
-      </c>
+      <c r="U49" s="3" t="inlineStr"/>
       <c r="V49" t="inlineStr"/>
       <c r="W49" s="3" t="n">
         <v>144.3</v>
@@ -4289,14 +4185,8 @@
       <c r="T50" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="U50" s="1" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="V50" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U50" s="3" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
       <c r="W50" s="3" t="n">
         <v>139.2</v>
       </c>
@@ -4372,14 +4262,8 @@
       <c r="T51" s="1" t="n">
         <v>45.3</v>
       </c>
-      <c r="U51" s="1" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="V51" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U51" s="3" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
       <c r="W51" s="3" t="n">
         <v>136.5</v>
       </c>
@@ -4455,14 +4339,8 @@
       <c r="T52" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="U52" s="1" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="V52" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U52" s="3" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
       <c r="W52" s="3" t="n">
         <v>133.8</v>
       </c>
@@ -4538,14 +4416,8 @@
       <c r="T53" s="1" t="n">
         <v>52.3</v>
       </c>
-      <c r="U53" s="1" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="V53" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U53" s="3" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
       <c r="W53" s="3" t="n">
         <v>135.7</v>
       </c>
@@ -4617,14 +4489,8 @@
       <c r="T54" s="1" t="n">
         <v>33.6</v>
       </c>
-      <c r="U54" s="1" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="V54" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U54" s="3" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
       <c r="W54" s="3" t="n">
         <v>142.2</v>
       </c>
@@ -4696,14 +4562,8 @@
       <c r="T55" s="1" t="n">
         <v>40.7</v>
       </c>
-      <c r="U55" s="1" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="V55" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U55" s="3" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
       <c r="W55" s="3" t="n">
         <v>127.5</v>
       </c>
@@ -4775,14 +4635,8 @@
       <c r="T56" s="1" t="n">
         <v>37.6</v>
       </c>
-      <c r="U56" s="1" t="n">
-        <v>54.2</v>
-      </c>
-      <c r="V56" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U56" s="3" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
       <c r="W56" s="3" t="n">
         <v>128.6</v>
       </c>
@@ -4854,9 +4708,7 @@
       <c r="T57" s="1" t="n">
         <v>30.9</v>
       </c>
-      <c r="U57" s="1" t="n">
-        <v>28.5</v>
-      </c>
+      <c r="U57" s="3" t="inlineStr"/>
       <c r="V57" t="inlineStr"/>
       <c r="W57" s="3" t="n">
         <v>135.7</v>
@@ -4929,9 +4781,7 @@
       <c r="T58" s="1" t="n">
         <v>30.1</v>
       </c>
-      <c r="U58" s="1" t="n">
-        <v>26</v>
-      </c>
+      <c r="U58" s="3" t="inlineStr"/>
       <c r="V58" t="inlineStr"/>
       <c r="W58" s="3" t="n">
         <v>135.8</v>
@@ -5004,14 +4854,8 @@
       <c r="T59" s="1" t="n">
         <v>32.6</v>
       </c>
-      <c r="U59" s="1" t="n">
-        <v>35</v>
-      </c>
-      <c r="V59" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U59" s="3" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
       <c r="W59" s="3" t="n">
         <v>131.3</v>
       </c>
@@ -5083,14 +4927,8 @@
       <c r="T60" s="1" t="n">
         <v>29.6</v>
       </c>
-      <c r="U60" s="1" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="V60" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U60" s="3" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
       <c r="W60" s="3" t="n">
         <v>130</v>
       </c>
@@ -5162,9 +5000,7 @@
       <c r="T61" s="1" t="n">
         <v>33.8</v>
       </c>
-      <c r="U61" s="1" t="n">
-        <v>30.6</v>
-      </c>
+      <c r="U61" s="3" t="inlineStr"/>
       <c r="V61" t="inlineStr"/>
       <c r="W61" s="1" t="n">
         <v>125.8</v>
@@ -5237,9 +5073,7 @@
       <c r="T62" s="1" t="n">
         <v>30.6</v>
       </c>
-      <c r="U62" s="1" t="n">
-        <v>29.1</v>
-      </c>
+      <c r="U62" s="3" t="inlineStr"/>
       <c r="V62" t="inlineStr"/>
       <c r="W62" s="1" t="n">
         <v>125.9</v>
@@ -5312,14 +5146,8 @@
       <c r="T63" s="1" t="n">
         <v>28.5</v>
       </c>
-      <c r="U63" s="1" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="V63" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U63" s="3" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
       <c r="W63" s="1" t="n">
         <v>126.7</v>
       </c>
@@ -5391,9 +5219,7 @@
       <c r="T64" s="1" t="n">
         <v>26.5</v>
       </c>
-      <c r="U64" s="1" t="n">
-        <v>25.7</v>
-      </c>
+      <c r="U64" s="3" t="inlineStr"/>
       <c r="V64" t="inlineStr"/>
       <c r="W64" s="3" t="n">
         <v>129</v>
@@ -5466,9 +5292,7 @@
       <c r="T65" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="U65" s="3" t="n">
-        <v>23.6</v>
-      </c>
+      <c r="U65" s="3" t="inlineStr"/>
       <c r="V65" t="inlineStr"/>
       <c r="W65" s="3" t="n">
         <v>132.4</v>
@@ -5541,9 +5365,7 @@
       <c r="T66" s="1" t="n">
         <v>25.1</v>
       </c>
-      <c r="U66" s="3" t="n">
-        <v>21.4</v>
-      </c>
+      <c r="U66" s="3" t="inlineStr"/>
       <c r="V66" t="inlineStr"/>
       <c r="W66" s="3" t="n">
         <v>131.3</v>
@@ -5616,9 +5438,7 @@
       <c r="T67" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="U67" s="3" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U67" s="3" t="inlineStr"/>
       <c r="V67" t="inlineStr"/>
       <c r="W67" s="3" t="n">
         <v>134.3</v>
@@ -5691,9 +5511,7 @@
       <c r="T68" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="U68" s="3" t="n">
-        <v>22.9</v>
-      </c>
+      <c r="U68" s="3" t="inlineStr"/>
       <c r="V68" t="inlineStr"/>
       <c r="W68" s="3" t="n">
         <v>132.7</v>
@@ -5766,9 +5584,7 @@
       <c r="T69" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="U69" s="1" t="n">
-        <v>27.5</v>
-      </c>
+      <c r="U69" s="3" t="inlineStr"/>
       <c r="V69" t="inlineStr"/>
       <c r="W69" s="3" t="n">
         <v>134.1</v>
@@ -5841,9 +5657,7 @@
       <c r="T70" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="U70" s="3" t="n">
-        <v>20</v>
-      </c>
+      <c r="U70" s="3" t="inlineStr"/>
       <c r="V70" t="inlineStr"/>
       <c r="W70" s="3" t="n">
         <v>134.8</v>
@@ -5916,9 +5730,7 @@
       <c r="T71" s="3" t="n">
         <v>23.6</v>
       </c>
-      <c r="U71" s="3" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U71" s="3" t="inlineStr"/>
       <c r="V71" t="inlineStr"/>
       <c r="W71" s="3" t="n">
         <v>134.1</v>
@@ -5991,9 +5803,7 @@
       <c r="T72" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="U72" s="3" t="n">
-        <v>22.2</v>
-      </c>
+      <c r="U72" s="3" t="inlineStr"/>
       <c r="V72" t="inlineStr"/>
       <c r="W72" s="3" t="n">
         <v>133.2</v>
@@ -6066,9 +5876,7 @@
       <c r="T73" s="3" t="n">
         <v>23.5</v>
       </c>
-      <c r="U73" s="3" t="n">
-        <v>19.8</v>
-      </c>
+      <c r="U73" s="3" t="inlineStr"/>
       <c r="V73" t="inlineStr"/>
       <c r="W73" s="3" t="n">
         <v>132.2</v>
@@ -6141,9 +5949,7 @@
       <c r="T74" s="3" t="n">
         <v>22.5</v>
       </c>
-      <c r="U74" s="3" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="U74" s="3" t="inlineStr"/>
       <c r="V74" t="inlineStr"/>
       <c r="W74" s="3" t="n">
         <v>131.5</v>
@@ -6216,9 +6022,7 @@
       <c r="T75" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="U75" s="1" t="n">
-        <v>26.9</v>
-      </c>
+      <c r="U75" s="3" t="inlineStr"/>
       <c r="V75" t="inlineStr"/>
       <c r="W75" s="3" t="n">
         <v>128.4</v>
@@ -6291,9 +6095,7 @@
       <c r="T76" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="U76" s="3" t="n">
-        <v>18.7</v>
-      </c>
+      <c r="U76" s="3" t="inlineStr"/>
       <c r="V76" t="inlineStr"/>
       <c r="W76" s="3" t="n">
         <v>137.7</v>
@@ -6366,9 +6168,7 @@
       <c r="T77" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="U77" s="3" t="n">
-        <v>15.4</v>
-      </c>
+      <c r="U77" s="3" t="inlineStr"/>
       <c r="V77" t="inlineStr"/>
       <c r="W77" s="3" t="n">
         <v>140.5</v>
@@ -6441,9 +6241,7 @@
       <c r="T78" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="U78" s="3" t="n">
-        <v>15.2</v>
-      </c>
+      <c r="U78" s="3" t="inlineStr"/>
       <c r="V78" t="inlineStr"/>
       <c r="W78" s="3" t="n">
         <v>138.9</v>
@@ -6516,9 +6314,7 @@
       <c r="T79" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="U79" s="3" t="n">
-        <v>15.1</v>
-      </c>
+      <c r="U79" s="3" t="inlineStr"/>
       <c r="V79" t="inlineStr"/>
       <c r="W79" s="3" t="n">
         <v>140.9</v>
@@ -6591,9 +6387,7 @@
       <c r="T80" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="U80" s="3" t="n">
-        <v>13.4</v>
-      </c>
+      <c r="U80" s="3" t="inlineStr"/>
       <c r="V80" t="inlineStr"/>
       <c r="W80" s="3" t="n">
         <v>136</v>
@@ -6666,9 +6460,7 @@
       <c r="T81" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="U81" s="3" t="n">
-        <v>13.5</v>
-      </c>
+      <c r="U81" s="3" t="inlineStr"/>
       <c r="V81" t="inlineStr"/>
       <c r="W81" s="3" t="n">
         <v>135.9</v>
@@ -6741,9 +6533,7 @@
       <c r="T82" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="U82" s="3" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U82" s="3" t="inlineStr"/>
       <c r="V82" t="inlineStr"/>
       <c r="W82" s="3" t="n">
         <v>137.3</v>
@@ -6816,9 +6606,7 @@
       <c r="T83" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="U83" s="3" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="U83" s="3" t="inlineStr"/>
       <c r="V83" t="inlineStr"/>
       <c r="W83" s="3" t="n">
         <v>137.3</v>
@@ -6891,9 +6679,7 @@
       <c r="T84" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="U84" s="3" t="n">
-        <v>16.5</v>
-      </c>
+      <c r="U84" s="3" t="inlineStr"/>
       <c r="V84" t="inlineStr"/>
       <c r="W84" s="3" t="n">
         <v>139</v>
@@ -6966,9 +6752,7 @@
       <c r="T85" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="U85" s="3" t="n">
-        <v>21.7</v>
-      </c>
+      <c r="U85" s="3" t="inlineStr"/>
       <c r="V85" t="inlineStr"/>
       <c r="W85" s="3" t="n">
         <v>139.3</v>
@@ -7041,9 +6825,7 @@
       <c r="T86" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="U86" s="3" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U86" s="3" t="inlineStr"/>
       <c r="V86" t="inlineStr"/>
       <c r="W86" s="3" t="n">
         <v>140.9</v>
@@ -7116,9 +6898,7 @@
       <c r="T87" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="U87" s="3" t="n">
-        <v>19.5</v>
-      </c>
+      <c r="U87" s="3" t="inlineStr"/>
       <c r="V87" t="inlineStr"/>
       <c r="W87" s="3" t="n">
         <v>137.6</v>
@@ -7191,9 +6971,7 @@
       <c r="T88" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="U88" s="3" t="n">
-        <v>17.4</v>
-      </c>
+      <c r="U88" s="3" t="inlineStr"/>
       <c r="V88" t="inlineStr"/>
       <c r="W88" s="3" t="n">
         <v>137.3</v>
@@ -7266,9 +7044,7 @@
       <c r="T89" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="U89" s="3" t="n">
-        <v>17</v>
-      </c>
+      <c r="U89" s="3" t="inlineStr"/>
       <c r="V89" t="inlineStr"/>
       <c r="W89" s="3" t="n">
         <v>138.2</v>
@@ -7341,9 +7117,7 @@
       <c r="T90" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="U90" s="3" t="n">
-        <v>13.3</v>
-      </c>
+      <c r="U90" s="3" t="inlineStr"/>
       <c r="V90" t="inlineStr"/>
       <c r="W90" s="3" t="n">
         <v>141</v>
@@ -7416,9 +7190,7 @@
       <c r="T91" s="3" t="n">
         <v>17.7</v>
       </c>
-      <c r="U91" s="3" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U91" s="3" t="inlineStr"/>
       <c r="V91" t="inlineStr"/>
       <c r="W91" s="3" t="n">
         <v>141.6</v>
@@ -7491,9 +7263,7 @@
       <c r="T92" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="U92" s="3" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U92" s="3" t="inlineStr"/>
       <c r="V92" t="inlineStr"/>
       <c r="W92" s="3" t="n">
         <v>137.5</v>
@@ -7566,9 +7336,7 @@
       <c r="T93" s="3" t="n">
         <v>18.5</v>
       </c>
-      <c r="U93" s="3" t="n">
-        <v>19</v>
-      </c>
+      <c r="U93" s="3" t="inlineStr"/>
       <c r="V93" t="inlineStr"/>
       <c r="W93" s="3" t="n">
         <v>140.1</v>
@@ -7641,9 +7409,7 @@
       <c r="T94" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="U94" s="3" t="n">
-        <v>14.3</v>
-      </c>
+      <c r="U94" s="3" t="inlineStr"/>
       <c r="V94" t="inlineStr"/>
       <c r="W94" s="3" t="n">
         <v>138.9</v>
@@ -7716,9 +7482,7 @@
       <c r="T95" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="U95" s="3" t="n">
-        <v>12.3</v>
-      </c>
+      <c r="U95" s="3" t="inlineStr"/>
       <c r="V95" t="inlineStr"/>
       <c r="W95" s="3" t="n">
         <v>139.2</v>
@@ -7791,9 +7555,7 @@
       <c r="T96" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="U96" s="3" t="n">
-        <v>15.9</v>
-      </c>
+      <c r="U96" s="3" t="inlineStr"/>
       <c r="V96" t="inlineStr"/>
       <c r="W96" s="3" t="n">
         <v>141.2</v>
@@ -7866,9 +7628,7 @@
       <c r="T97" s="3" t="n">
         <v>17.3</v>
       </c>
-      <c r="U97" s="3" t="n">
-        <v>13.9</v>
-      </c>
+      <c r="U97" s="3" t="inlineStr"/>
       <c r="V97" t="inlineStr"/>
       <c r="W97" s="3" t="n">
         <v>141.4</v>
@@ -7941,9 +7701,7 @@
       <c r="T98" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="U98" s="3" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U98" s="3" t="inlineStr"/>
       <c r="V98" t="inlineStr"/>
       <c r="W98" s="3" t="n">
         <v>145.6</v>
@@ -8016,9 +7774,7 @@
       <c r="T99" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="U99" s="3" t="n">
-        <v>21.7</v>
-      </c>
+      <c r="U99" s="3" t="inlineStr"/>
       <c r="V99" t="inlineStr"/>
       <c r="W99" s="3" t="n">
         <v>149.6</v>
@@ -8091,9 +7847,7 @@
       <c r="T100" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="U100" s="3" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U100" s="3" t="inlineStr"/>
       <c r="V100" t="inlineStr"/>
       <c r="W100" s="2" t="n">
         <v>156.6</v>
@@ -8166,9 +7920,7 @@
       <c r="T101" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="U101" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="U101" s="3" t="inlineStr"/>
       <c r="V101" t="inlineStr"/>
       <c r="W101" s="3" t="n">
         <v>154.4</v>
@@ -8241,9 +7993,7 @@
       <c r="T102" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="U102" s="3" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U102" s="3" t="inlineStr"/>
       <c r="V102" t="inlineStr"/>
       <c r="W102" s="3" t="n">
         <v>148.4</v>
@@ -8316,9 +8066,7 @@
       <c r="T103" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="U103" s="3" t="n">
-        <v>18.4</v>
-      </c>
+      <c r="U103" s="3" t="inlineStr"/>
       <c r="V103" t="inlineStr"/>
       <c r="W103" s="3" t="n">
         <v>149.2</v>
@@ -8391,9 +8139,7 @@
       <c r="T104" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="U104" s="3" t="n">
-        <v>13.4</v>
-      </c>
+      <c r="U104" s="3" t="inlineStr"/>
       <c r="V104" t="inlineStr"/>
       <c r="W104" s="3" t="n">
         <v>154.8</v>
@@ -8466,9 +8212,7 @@
       <c r="T105" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="U105" s="3" t="n">
-        <v>11.2</v>
-      </c>
+      <c r="U105" s="3" t="inlineStr"/>
       <c r="V105" t="inlineStr"/>
       <c r="W105" s="2" t="n">
         <v>155</v>
@@ -8541,9 +8285,7 @@
       <c r="T106" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="U106" s="3" t="n">
-        <v>10.4</v>
-      </c>
+      <c r="U106" s="3" t="inlineStr"/>
       <c r="V106" t="inlineStr"/>
       <c r="W106" s="3" t="n">
         <v>152.2</v>
@@ -8616,9 +8358,7 @@
       <c r="T107" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="U107" s="3" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U107" s="3" t="inlineStr"/>
       <c r="V107" t="inlineStr"/>
       <c r="W107" s="3" t="n">
         <v>147.5</v>
@@ -8691,9 +8431,7 @@
       <c r="T108" s="3" t="n">
         <v>16.3</v>
       </c>
-      <c r="U108" s="3" t="n">
-        <v>12.2</v>
-      </c>
+      <c r="U108" s="3" t="inlineStr"/>
       <c r="V108" t="inlineStr"/>
       <c r="W108" s="3" t="n">
         <v>143.4</v>
@@ -8766,9 +8504,7 @@
       <c r="T109" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="U109" s="3" t="n">
-        <v>10.2</v>
-      </c>
+      <c r="U109" s="3" t="inlineStr"/>
       <c r="V109" t="inlineStr"/>
       <c r="W109" s="3" t="n">
         <v>139.6</v>
@@ -8810,7 +8546,7 @@
         <v>3.48</v>
       </c>
       <c r="K110" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="L110" t="n">
         <v>2.33</v>
@@ -8841,9 +8577,7 @@
       <c r="T110" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="U110" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
+      <c r="U110" s="3" t="inlineStr"/>
       <c r="V110" t="inlineStr"/>
       <c r="W110" s="3" t="n">
         <v>140.1</v>
@@ -8916,9 +8650,7 @@
       <c r="T111" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="U111" s="3" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U111" s="3" t="inlineStr"/>
       <c r="V111" t="inlineStr"/>
       <c r="W111" s="3" t="n">
         <v>139.3</v>
@@ -8991,9 +8723,7 @@
       <c r="T112" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="U112" s="3" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U112" s="3" t="inlineStr"/>
       <c r="V112" t="inlineStr"/>
       <c r="W112" s="3" t="n">
         <v>141.4</v>
@@ -9066,9 +8796,7 @@
       <c r="T113" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="U113" s="3" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U113" s="3" t="inlineStr"/>
       <c r="V113" t="inlineStr"/>
       <c r="W113" s="3" t="n">
         <v>138</v>
@@ -9141,9 +8869,7 @@
       <c r="T114" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="U114" s="3" t="n">
-        <v>10.5</v>
-      </c>
+      <c r="U114" s="3" t="inlineStr"/>
       <c r="V114" t="inlineStr"/>
       <c r="W114" s="3" t="n">
         <v>140.8</v>
@@ -9216,9 +8942,7 @@
       <c r="T115" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="U115" s="3" t="n">
-        <v>9.6</v>
-      </c>
+      <c r="U115" s="3" t="inlineStr"/>
       <c r="V115" t="inlineStr"/>
       <c r="W115" s="3" t="n">
         <v>141.8</v>
@@ -9291,9 +9015,7 @@
       <c r="T116" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="U116" s="3" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U116" s="3" t="inlineStr"/>
       <c r="V116" t="inlineStr"/>
       <c r="W116" s="3" t="n">
         <v>143.3</v>
@@ -9366,9 +9088,7 @@
       <c r="T117" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="U117" s="3" t="n">
-        <v>12.5</v>
-      </c>
+      <c r="U117" s="3" t="inlineStr"/>
       <c r="V117" t="inlineStr"/>
       <c r="W117" s="3" t="n">
         <v>145</v>
@@ -9441,9 +9161,7 @@
       <c r="T118" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="U118" s="3" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U118" s="3" t="inlineStr"/>
       <c r="V118" t="inlineStr"/>
       <c r="W118" s="3" t="n">
         <v>147</v>
@@ -9516,9 +9234,7 @@
       <c r="T119" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="U119" s="3" t="n">
-        <v>12.2</v>
-      </c>
+      <c r="U119" s="3" t="inlineStr"/>
       <c r="V119" t="inlineStr"/>
       <c r="W119" s="3" t="n">
         <v>143.7</v>
@@ -9591,9 +9307,7 @@
       <c r="T120" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="U120" s="3" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U120" s="3" t="inlineStr"/>
       <c r="V120" t="inlineStr"/>
       <c r="W120" s="3" t="n">
         <v>146.7</v>
@@ -9666,9 +9380,7 @@
       <c r="T121" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="U121" s="3" t="n">
-        <v>10.8</v>
-      </c>
+      <c r="U121" s="3" t="inlineStr"/>
       <c r="V121" t="inlineStr"/>
       <c r="W121" s="3" t="n">
         <v>151.1</v>
@@ -9741,9 +9453,7 @@
       <c r="T122" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="U122" s="3" t="n">
-        <v>9.9</v>
-      </c>
+      <c r="U122" s="3" t="inlineStr"/>
       <c r="V122" t="inlineStr"/>
       <c r="W122" s="3" t="n">
         <v>150.4</v>
@@ -9816,9 +9526,7 @@
       <c r="T123" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="U123" s="3" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U123" s="3" t="inlineStr"/>
       <c r="V123" t="inlineStr"/>
       <c r="W123" s="3" t="n">
         <v>154.8</v>
@@ -9891,9 +9599,7 @@
       <c r="T124" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="U124" s="3" t="n">
-        <v>8.4</v>
-      </c>
+      <c r="U124" s="3" t="inlineStr"/>
       <c r="V124" t="inlineStr"/>
       <c r="W124" s="3" t="n">
         <v>153.4</v>
@@ -9966,9 +9672,7 @@
       <c r="T125" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="U125" s="3" t="n">
-        <v>10</v>
-      </c>
+      <c r="U125" s="3" t="inlineStr"/>
       <c r="V125" t="inlineStr"/>
       <c r="W125" s="2" t="n">
         <v>159.3</v>
@@ -10041,9 +9745,7 @@
       <c r="T126" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="U126" s="3" t="n">
-        <v>10</v>
-      </c>
+      <c r="U126" s="3" t="inlineStr"/>
       <c r="V126" t="inlineStr"/>
       <c r="W126" s="2" t="n">
         <v>159.4</v>
@@ -10116,9 +9818,7 @@
       <c r="T127" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="U127" s="3" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U127" s="3" t="inlineStr"/>
       <c r="V127" t="inlineStr"/>
       <c r="W127" s="3" t="n">
         <v>145.6</v>
@@ -10195,9 +9895,7 @@
       <c r="T128" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="U128" s="3" t="n">
-        <v>7.9</v>
-      </c>
+      <c r="U128" s="3" t="inlineStr"/>
       <c r="V128" t="inlineStr"/>
       <c r="W128" s="3" t="n">
         <v>147.6</v>
@@ -10270,9 +9968,7 @@
       <c r="T129" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="U129" s="3" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U129" s="3" t="inlineStr"/>
       <c r="V129" t="inlineStr"/>
       <c r="W129" s="3" t="n">
         <v>149.1</v>
@@ -10345,9 +10041,7 @@
       <c r="T130" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="U130" s="3" t="n">
-        <v>13.8</v>
-      </c>
+      <c r="U130" s="3" t="inlineStr"/>
       <c r="V130" t="inlineStr"/>
       <c r="W130" s="3" t="n">
         <v>154.1</v>
@@ -10424,9 +10118,7 @@
       <c r="T131" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="U131" s="3" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="U131" s="3" t="inlineStr"/>
       <c r="V131" t="inlineStr"/>
       <c r="W131" s="3" t="n">
         <v>152.3</v>
@@ -10499,9 +10191,7 @@
       <c r="T132" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="U132" s="3" t="n">
-        <v>20</v>
-      </c>
+      <c r="U132" s="3" t="inlineStr"/>
       <c r="V132" t="inlineStr"/>
       <c r="W132" s="2" t="n">
         <v>155.5</v>
@@ -10574,9 +10264,7 @@
       <c r="T133" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="U133" s="3" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U133" s="3" t="inlineStr"/>
       <c r="V133" t="inlineStr"/>
       <c r="W133" s="2" t="n">
         <v>159.3</v>
@@ -10649,9 +10337,7 @@
       <c r="T134" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="U134" s="3" t="n">
-        <v>12.3</v>
-      </c>
+      <c r="U134" s="3" t="inlineStr"/>
       <c r="V134" t="inlineStr"/>
       <c r="W134" s="3" t="n">
         <v>149.9</v>
@@ -10724,9 +10410,7 @@
       <c r="T135" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="U135" s="3" t="n">
-        <v>11.4</v>
-      </c>
+      <c r="U135" s="3" t="inlineStr"/>
       <c r="V135" t="inlineStr"/>
       <c r="W135" s="3" t="n">
         <v>149.7</v>
@@ -10799,9 +10483,7 @@
       <c r="T136" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="U136" s="3" t="n">
-        <v>12.5</v>
-      </c>
+      <c r="U136" s="3" t="inlineStr"/>
       <c r="V136" t="inlineStr"/>
       <c r="W136" s="3" t="n">
         <v>147</v>
@@ -10874,9 +10556,7 @@
       <c r="T137" s="3" t="n">
         <v>15.1</v>
       </c>
-      <c r="U137" s="3" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U137" s="3" t="inlineStr"/>
       <c r="V137" t="inlineStr"/>
       <c r="W137" s="3" t="n">
         <v>147.5</v>
@@ -10953,9 +10633,7 @@
       <c r="T138" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="U138" s="3" t="n">
-        <v>15.9</v>
-      </c>
+      <c r="U138" s="3" t="inlineStr"/>
       <c r="V138" t="inlineStr"/>
       <c r="W138" s="3" t="n">
         <v>148.6</v>
@@ -11028,9 +10706,7 @@
       <c r="T139" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="U139" s="3" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U139" s="3" t="inlineStr"/>
       <c r="V139" t="inlineStr"/>
       <c r="W139" s="3" t="n">
         <v>151.4</v>
@@ -11103,9 +10779,7 @@
       <c r="T140" s="3" t="n">
         <v>14.5</v>
       </c>
-      <c r="U140" s="3" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U140" s="3" t="inlineStr"/>
       <c r="V140" t="inlineStr"/>
       <c r="W140" s="3" t="n">
         <v>153.1</v>
@@ -11178,9 +10852,7 @@
       <c r="T141" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="U141" s="3" t="n">
-        <v>11.9</v>
-      </c>
+      <c r="U141" s="3" t="inlineStr"/>
       <c r="V141" t="inlineStr"/>
       <c r="W141" s="3" t="n">
         <v>150.6</v>
@@ -11257,9 +10929,7 @@
       <c r="T142" s="3" t="n">
         <v>15.1</v>
       </c>
-      <c r="U142" s="3" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U142" s="3" t="inlineStr"/>
       <c r="V142" t="inlineStr"/>
       <c r="W142" s="3" t="n">
         <v>153.8</v>
@@ -11332,9 +11002,7 @@
       <c r="T143" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="U143" s="3" t="n">
-        <v>7.8</v>
-      </c>
+      <c r="U143" s="3" t="inlineStr"/>
       <c r="V143" t="inlineStr"/>
       <c r="W143" s="3" t="n">
         <v>153.9</v>
@@ -11407,9 +11075,7 @@
       <c r="T144" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="U144" s="3" t="n">
-        <v>10.2</v>
-      </c>
+      <c r="U144" s="3" t="inlineStr"/>
       <c r="V144" t="inlineStr"/>
       <c r="W144" s="3" t="n">
         <v>153.2</v>
@@ -11482,9 +11148,7 @@
       <c r="T145" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="U145" s="3" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U145" s="3" t="inlineStr"/>
       <c r="V145" t="inlineStr"/>
       <c r="W145" s="3" t="n">
         <v>144.6</v>
@@ -11561,9 +11225,7 @@
       <c r="T146" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="U146" s="3" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="U146" s="3" t="inlineStr"/>
       <c r="V146" t="inlineStr"/>
       <c r="W146" s="3" t="n">
         <v>144.3</v>
@@ -11636,9 +11298,7 @@
       <c r="T147" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="U147" s="3" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U147" s="3" t="inlineStr"/>
       <c r="V147" t="inlineStr"/>
       <c r="W147" s="3" t="n">
         <v>146.4</v>
@@ -11715,9 +11375,7 @@
       <c r="T148" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="U148" s="3" t="n">
-        <v>8.1</v>
-      </c>
+      <c r="U148" s="3" t="inlineStr"/>
       <c r="V148" t="inlineStr"/>
       <c r="W148" s="3" t="n">
         <v>150</v>
@@ -11790,9 +11448,7 @@
       <c r="T149" s="3" t="n">
         <v>14.6</v>
       </c>
-      <c r="U149" s="3" t="n">
-        <v>7.8</v>
-      </c>
+      <c r="U149" s="3" t="inlineStr"/>
       <c r="V149" t="inlineStr"/>
       <c r="W149" s="2" t="n">
         <v>156.5</v>
@@ -11865,9 +11521,7 @@
       <c r="T150" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="U150" s="3" t="n">
-        <v>15.1</v>
-      </c>
+      <c r="U150" s="3" t="inlineStr"/>
       <c r="V150" t="inlineStr"/>
       <c r="W150" s="3" t="n">
         <v>150.9</v>
@@ -11940,9 +11594,7 @@
       <c r="T151" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="U151" s="3" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U151" s="3" t="inlineStr"/>
       <c r="V151" t="inlineStr"/>
       <c r="W151" s="3" t="n">
         <v>152.5</v>
@@ -12019,9 +11671,7 @@
       <c r="T152" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="U152" s="3" t="n">
-        <v>11.6</v>
-      </c>
+      <c r="U152" s="3" t="inlineStr"/>
       <c r="V152" t="inlineStr"/>
       <c r="W152" s="3" t="n">
         <v>152.1</v>
@@ -12094,9 +11744,7 @@
       <c r="T153" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="U153" s="3" t="n">
-        <v>11.4</v>
-      </c>
+      <c r="U153" s="3" t="inlineStr"/>
       <c r="V153" t="inlineStr"/>
       <c r="W153" s="3" t="n">
         <v>151.5</v>
@@ -12169,9 +11817,7 @@
       <c r="T154" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="U154" s="3" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U154" s="3" t="inlineStr"/>
       <c r="V154" t="inlineStr"/>
       <c r="W154" s="3" t="n">
         <v>150.2</v>
@@ -12244,9 +11890,7 @@
       <c r="T155" s="3" t="n">
         <v>15.3</v>
       </c>
-      <c r="U155" s="3" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U155" s="3" t="inlineStr"/>
       <c r="V155" t="inlineStr"/>
       <c r="W155" s="3" t="n">
         <v>154</v>
@@ -12319,9 +11963,7 @@
       <c r="T156" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="U156" s="3" t="n">
-        <v>10</v>
-      </c>
+      <c r="U156" s="3" t="inlineStr"/>
       <c r="V156" t="inlineStr"/>
       <c r="W156" s="3" t="n">
         <v>148.2</v>
@@ -12394,9 +12036,7 @@
       <c r="T157" s="3" t="n">
         <v>15.1</v>
       </c>
-      <c r="U157" s="3" t="n">
-        <v>8.300000000000001</v>
-      </c>
+      <c r="U157" s="3" t="inlineStr"/>
       <c r="V157" t="inlineStr"/>
       <c r="W157" s="3" t="n">
         <v>148.8</v>
@@ -12469,9 +12109,7 @@
       <c r="T158" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="U158" s="3" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U158" s="3" t="inlineStr"/>
       <c r="V158" t="inlineStr"/>
       <c r="W158" s="3" t="n">
         <v>150.9</v>
@@ -12544,9 +12182,7 @@
       <c r="T159" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="U159" s="3" t="n">
-        <v>13.4</v>
-      </c>
+      <c r="U159" s="3" t="inlineStr"/>
       <c r="V159" t="inlineStr"/>
       <c r="W159" s="3" t="n">
         <v>151.9</v>
@@ -12619,9 +12255,7 @@
       <c r="T160" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="U160" s="3" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U160" s="3" t="inlineStr"/>
       <c r="V160" t="inlineStr"/>
       <c r="W160" s="3" t="n">
         <v>147.6</v>
@@ -12694,9 +12328,7 @@
       <c r="T161" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="U161" s="3" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="U161" s="3" t="inlineStr"/>
       <c r="V161" t="inlineStr"/>
       <c r="W161" s="3" t="n">
         <v>149.5</v>
@@ -12769,9 +12401,7 @@
       <c r="T162" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="U162" s="3" t="n">
-        <v>9</v>
-      </c>
+      <c r="U162" s="3" t="inlineStr"/>
       <c r="V162" t="inlineStr"/>
       <c r="W162" s="3" t="n">
         <v>152.1</v>
@@ -12844,9 +12474,7 @@
       <c r="T163" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="U163" s="3" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="U163" s="3" t="inlineStr"/>
       <c r="V163" t="inlineStr"/>
       <c r="W163" s="3" t="n">
         <v>148.2</v>
@@ -12919,9 +12547,7 @@
       <c r="T164" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="U164" s="3" t="n">
-        <v>14.8</v>
-      </c>
+      <c r="U164" s="3" t="inlineStr"/>
       <c r="V164" t="inlineStr"/>
       <c r="W164" s="3" t="n">
         <v>146.4</v>
@@ -12994,9 +12620,7 @@
       <c r="T165" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="U165" s="3" t="n">
-        <v>14.4</v>
-      </c>
+      <c r="U165" s="3" t="inlineStr"/>
       <c r="V165" t="inlineStr"/>
       <c r="W165" s="3" t="n">
         <v>148.2</v>
@@ -13069,9 +12693,7 @@
       <c r="T166" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="U166" s="3" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U166" s="3" t="inlineStr"/>
       <c r="V166" t="inlineStr"/>
       <c r="W166" s="3" t="n">
         <v>147</v>
@@ -13144,9 +12766,7 @@
       <c r="T167" s="3" t="n">
         <v>16.1</v>
       </c>
-      <c r="U167" s="3" t="n">
-        <v>9.1</v>
-      </c>
+      <c r="U167" s="3" t="inlineStr"/>
       <c r="V167" t="inlineStr"/>
       <c r="W167" s="3" t="n">
         <v>145.5</v>
@@ -13219,9 +12839,7 @@
       <c r="T168" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="U168" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
+      <c r="U168" s="3" t="inlineStr"/>
       <c r="V168" t="inlineStr"/>
       <c r="W168" s="3" t="n">
         <v>146.5</v>
@@ -13294,9 +12912,7 @@
       <c r="T169" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="U169" s="3" t="n">
-        <v>9.4</v>
-      </c>
+      <c r="U169" s="3" t="inlineStr"/>
       <c r="V169" t="inlineStr"/>
       <c r="W169" s="3" t="n">
         <v>145.9</v>
@@ -13369,9 +12985,7 @@
       <c r="T170" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="U170" s="3" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U170" s="3" t="inlineStr"/>
       <c r="V170" t="inlineStr"/>
       <c r="W170" s="3" t="n">
         <v>145.9</v>
@@ -13444,9 +13058,7 @@
       <c r="T171" s="3" t="n">
         <v>15.3</v>
       </c>
-      <c r="U171" s="3" t="n">
-        <v>10.3</v>
-      </c>
+      <c r="U171" s="3" t="inlineStr"/>
       <c r="V171" t="inlineStr"/>
       <c r="W171" s="3" t="n">
         <v>141.5</v>
@@ -13485,7 +13097,7 @@
         <v>13.4</v>
       </c>
       <c r="J172" t="n">
-        <v>4.85</v>
+        <v>4.86</v>
       </c>
       <c r="K172" t="n">
         <v>4.34</v>
@@ -13519,9 +13131,7 @@
       <c r="T172" s="3" t="n">
         <v>16.1</v>
       </c>
-      <c r="U172" s="3" t="n">
-        <v>10.2</v>
-      </c>
+      <c r="U172" s="3" t="inlineStr"/>
       <c r="V172" t="inlineStr"/>
       <c r="W172" s="3" t="n">
         <v>143</v>
@@ -13594,9 +13204,7 @@
       <c r="T173" s="3" t="n">
         <v>16.3</v>
       </c>
-      <c r="U173" s="3" t="n">
-        <v>12</v>
-      </c>
+      <c r="U173" s="3" t="inlineStr"/>
       <c r="V173" t="inlineStr"/>
       <c r="W173" s="3" t="n">
         <v>143.4</v>
@@ -13669,9 +13277,7 @@
       <c r="T174" s="3" t="n">
         <v>16.3</v>
       </c>
-      <c r="U174" s="3" t="n">
-        <v>10.3</v>
-      </c>
+      <c r="U174" s="3" t="inlineStr"/>
       <c r="V174" t="inlineStr"/>
       <c r="W174" s="3" t="n">
         <v>143.7</v>
@@ -13744,9 +13350,7 @@
       <c r="T175" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="U175" s="3" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U175" s="3" t="inlineStr"/>
       <c r="V175" t="inlineStr"/>
       <c r="W175" s="3" t="n">
         <v>145.9</v>
@@ -13819,9 +13423,7 @@
       <c r="T176" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="U176" s="3" t="n">
-        <v>11.9</v>
-      </c>
+      <c r="U176" s="3" t="inlineStr"/>
       <c r="V176" t="inlineStr"/>
       <c r="W176" s="3" t="n">
         <v>144.6</v>
@@ -13894,9 +13496,7 @@
       <c r="T177" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="U177" s="3" t="n">
-        <v>8.4</v>
-      </c>
+      <c r="U177" s="3" t="inlineStr"/>
       <c r="V177" t="inlineStr"/>
       <c r="W177" s="3" t="n">
         <v>142.5</v>
@@ -13969,9 +13569,7 @@
       <c r="T178" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="U178" s="3" t="n">
-        <v>11.3</v>
-      </c>
+      <c r="U178" s="3" t="inlineStr"/>
       <c r="V178" t="inlineStr"/>
       <c r="W178" s="3" t="n">
         <v>145.2</v>
@@ -14044,9 +13642,7 @@
       <c r="T179" s="3" t="n">
         <v>16.3</v>
       </c>
-      <c r="U179" s="3" t="n">
-        <v>10</v>
-      </c>
+      <c r="U179" s="3" t="inlineStr"/>
       <c r="V179" t="inlineStr"/>
       <c r="W179" s="3" t="n">
         <v>145.8</v>
@@ -14119,9 +13715,7 @@
       <c r="T180" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="U180" s="3" t="n">
-        <v>11.3</v>
-      </c>
+      <c r="U180" s="3" t="inlineStr"/>
       <c r="V180" t="inlineStr"/>
       <c r="W180" s="3" t="n">
         <v>145.3</v>
@@ -14198,9 +13792,7 @@
       <c r="T181" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="U181" s="1" t="n">
-        <v>25.7</v>
-      </c>
+      <c r="U181" s="3" t="inlineStr"/>
       <c r="V181" t="inlineStr"/>
       <c r="W181" s="3" t="n">
         <v>138.9</v>
@@ -14273,9 +13865,7 @@
       <c r="T182" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="U182" s="3" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U182" s="3" t="inlineStr"/>
       <c r="V182" t="inlineStr"/>
       <c r="W182" s="3" t="n">
         <v>142.8</v>
@@ -14348,9 +13938,7 @@
       <c r="T183" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="U183" s="3" t="n">
-        <v>17.7</v>
-      </c>
+      <c r="U183" s="3" t="inlineStr"/>
       <c r="V183" t="inlineStr"/>
       <c r="W183" s="3" t="n">
         <v>146.5</v>
@@ -14423,9 +14011,7 @@
       <c r="T184" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="U184" s="3" t="n">
-        <v>17.1</v>
-      </c>
+      <c r="U184" s="3" t="inlineStr"/>
       <c r="V184" t="inlineStr"/>
       <c r="W184" s="3" t="n">
         <v>145</v>
@@ -14498,9 +14084,7 @@
       <c r="T185" s="1" t="n">
         <v>25.3</v>
       </c>
-      <c r="U185" s="3" t="n">
-        <v>23.8</v>
-      </c>
+      <c r="U185" s="3" t="inlineStr"/>
       <c r="V185" t="inlineStr"/>
       <c r="W185" s="3" t="n">
         <v>147.1</v>
@@ -14573,9 +14157,7 @@
       <c r="T186" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="U186" s="3" t="n">
-        <v>17.9</v>
-      </c>
+      <c r="U186" s="3" t="inlineStr"/>
       <c r="V186" t="inlineStr"/>
       <c r="W186" s="3" t="n">
         <v>147.6</v>
@@ -14648,9 +14230,7 @@
       <c r="T187" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="U187" s="3" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U187" s="3" t="inlineStr"/>
       <c r="V187" t="inlineStr"/>
       <c r="W187" s="3" t="n">
         <v>151.3</v>
@@ -14723,9 +14303,7 @@
       <c r="T188" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="U188" s="3" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U188" s="3" t="inlineStr"/>
       <c r="V188" t="inlineStr"/>
       <c r="W188" s="3" t="n">
         <v>149.9</v>
@@ -14798,9 +14376,7 @@
       <c r="T189" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="U189" s="3" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U189" s="3" t="inlineStr"/>
       <c r="V189" t="inlineStr"/>
       <c r="W189" s="3" t="n">
         <v>152.9</v>
@@ -14873,9 +14449,7 @@
       <c r="T190" s="3" t="n">
         <v>17.3</v>
       </c>
-      <c r="U190" s="3" t="n">
-        <v>13.8</v>
-      </c>
+      <c r="U190" s="3" t="inlineStr"/>
       <c r="V190" t="inlineStr"/>
       <c r="W190" s="3" t="n">
         <v>154.3</v>
@@ -14948,9 +14522,7 @@
       <c r="T191" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="U191" s="3" t="n">
-        <v>14.5</v>
-      </c>
+      <c r="U191" s="3" t="inlineStr"/>
       <c r="V191" t="inlineStr"/>
       <c r="W191" s="3" t="n">
         <v>153.5</v>
@@ -15023,9 +14595,7 @@
       <c r="T192" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="U192" s="3" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U192" s="3" t="inlineStr"/>
       <c r="V192" t="inlineStr"/>
       <c r="W192" s="3" t="n">
         <v>148.5</v>
@@ -15098,9 +14668,7 @@
       <c r="T193" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="U193" s="3" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U193" s="3" t="inlineStr"/>
       <c r="V193" t="inlineStr"/>
       <c r="W193" s="3" t="n">
         <v>140.4</v>
@@ -15173,9 +14741,7 @@
       <c r="T194" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="U194" s="3" t="n">
-        <v>15.2</v>
-      </c>
+      <c r="U194" s="3" t="inlineStr"/>
       <c r="V194" t="inlineStr"/>
       <c r="W194" s="3" t="n">
         <v>139.4</v>
@@ -15248,9 +14814,7 @@
       <c r="T195" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="U195" s="3" t="n">
-        <v>14.2</v>
-      </c>
+      <c r="U195" s="3" t="inlineStr"/>
       <c r="V195" t="inlineStr"/>
       <c r="W195" s="3" t="n">
         <v>141.1</v>
@@ -15323,9 +14887,7 @@
       <c r="T196" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="U196" s="3" t="n">
-        <v>13.8</v>
-      </c>
+      <c r="U196" s="3" t="inlineStr"/>
       <c r="V196" t="inlineStr"/>
       <c r="W196" s="3" t="n">
         <v>142.8</v>
@@ -15398,9 +14960,7 @@
       <c r="T197" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="U197" s="3" t="n">
-        <v>10</v>
-      </c>
+      <c r="U197" s="3" t="inlineStr"/>
       <c r="V197" t="inlineStr"/>
       <c r="W197" s="3" t="n">
         <v>142</v>
@@ -15473,9 +15033,7 @@
       <c r="T198" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="U198" s="6" t="n">
-        <v>15.2</v>
-      </c>
+      <c r="U198" s="6" t="inlineStr"/>
       <c r="V198" s="4" t="inlineStr"/>
       <c r="W198" s="6" t="n">
         <v>144</v>
@@ -15548,9 +15106,7 @@
       <c r="T199" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="U199" s="3" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U199" s="3" t="inlineStr"/>
       <c r="V199" t="inlineStr"/>
       <c r="W199" s="3" t="n">
         <v>143.6</v>
@@ -15623,9 +15179,7 @@
       <c r="T200" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="U200" s="3" t="n">
-        <v>15.9</v>
-      </c>
+      <c r="U200" s="3" t="inlineStr"/>
       <c r="V200" t="inlineStr"/>
       <c r="W200" s="3" t="n">
         <v>143.5</v>
@@ -15702,9 +15256,7 @@
       <c r="T201" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="U201" s="3" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="U201" s="3" t="inlineStr"/>
       <c r="V201" t="inlineStr"/>
       <c r="W201" s="3" t="n">
         <v>141.3</v>
@@ -15777,9 +15329,7 @@
       <c r="T202" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="U202" s="3" t="n">
-        <v>11.2</v>
-      </c>
+      <c r="U202" s="3" t="inlineStr"/>
       <c r="V202" t="inlineStr"/>
       <c r="W202" s="3" t="n">
         <v>142.9</v>
@@ -15852,9 +15402,7 @@
       <c r="T203" s="3" t="n">
         <v>17.3</v>
       </c>
-      <c r="U203" s="3" t="n">
-        <v>10.8</v>
-      </c>
+      <c r="U203" s="3" t="inlineStr"/>
       <c r="V203" t="inlineStr"/>
       <c r="W203" s="3" t="n">
         <v>143.4</v>
@@ -15927,9 +15475,7 @@
       <c r="T204" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="U204" s="3" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U204" s="3" t="inlineStr"/>
       <c r="V204" t="inlineStr"/>
       <c r="W204" s="3" t="n">
         <v>138.6</v>
@@ -16006,9 +15552,7 @@
       <c r="T205" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="U205" s="3" t="n">
-        <v>17</v>
-      </c>
+      <c r="U205" s="3" t="inlineStr"/>
       <c r="V205" t="inlineStr"/>
       <c r="W205" s="3" t="n">
         <v>142.5</v>
@@ -16081,9 +15625,7 @@
       <c r="T206" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="U206" s="3" t="n">
-        <v>18.5</v>
-      </c>
+      <c r="U206" s="3" t="inlineStr"/>
       <c r="V206" t="inlineStr"/>
       <c r="W206" s="3" t="n">
         <v>137.9</v>
@@ -16156,9 +15698,7 @@
       <c r="T207" s="3" t="n">
         <v>22.4</v>
       </c>
-      <c r="U207" s="3" t="n">
-        <v>19.4</v>
-      </c>
+      <c r="U207" s="3" t="inlineStr"/>
       <c r="V207" t="inlineStr"/>
       <c r="W207" s="3" t="n">
         <v>140.9</v>
@@ -16231,9 +15771,7 @@
       <c r="T208" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="U208" s="3" t="n">
-        <v>20.9</v>
-      </c>
+      <c r="U208" s="3" t="inlineStr"/>
       <c r="V208" t="inlineStr"/>
       <c r="W208" s="3" t="n">
         <v>143</v>
@@ -16306,9 +15844,7 @@
       <c r="T209" s="3" t="n">
         <v>23.7</v>
       </c>
-      <c r="U209" s="1" t="n">
-        <v>26.9</v>
-      </c>
+      <c r="U209" s="3" t="inlineStr"/>
       <c r="V209" t="inlineStr"/>
       <c r="W209" s="3" t="n">
         <v>143.1</v>
@@ -16381,14 +15917,8 @@
       <c r="T210" s="1" t="n">
         <v>26.4</v>
       </c>
-      <c r="U210" s="1" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="V210" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U210" s="3" t="inlineStr"/>
+      <c r="V210" t="inlineStr"/>
       <c r="W210" s="3" t="n">
         <v>145</v>
       </c>
@@ -16460,9 +15990,7 @@
       <c r="T211" s="3" t="n">
         <v>23.4</v>
       </c>
-      <c r="U211" s="3" t="n">
-        <v>23.3</v>
-      </c>
+      <c r="U211" s="3" t="inlineStr"/>
       <c r="V211" t="inlineStr"/>
       <c r="W211" s="3" t="n">
         <v>148.3</v>
@@ -16535,9 +16063,7 @@
       <c r="T212" s="3" t="n">
         <v>20.5</v>
       </c>
-      <c r="U212" s="3" t="n">
-        <v>14.3</v>
-      </c>
+      <c r="U212" s="3" t="inlineStr"/>
       <c r="V212" t="inlineStr"/>
       <c r="W212" s="3" t="n">
         <v>148.6</v>
@@ -16610,9 +16136,7 @@
       <c r="T213" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="U213" s="3" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U213" s="3" t="inlineStr"/>
       <c r="V213" t="inlineStr"/>
       <c r="W213" s="3" t="n">
         <v>151.7</v>
@@ -16685,9 +16209,7 @@
       <c r="T214" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="U214" s="3" t="n">
-        <v>14.7</v>
-      </c>
+      <c r="U214" s="3" t="inlineStr"/>
       <c r="V214" t="inlineStr"/>
       <c r="W214" s="3" t="n">
         <v>145</v>
@@ -16760,9 +16282,7 @@
       <c r="T215" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="U215" s="3" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U215" s="3" t="inlineStr"/>
       <c r="V215" t="inlineStr"/>
       <c r="W215" s="3" t="n">
         <v>143</v>
@@ -16835,9 +16355,7 @@
       <c r="T216" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="U216" s="3" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U216" s="3" t="inlineStr"/>
       <c r="V216" t="inlineStr"/>
       <c r="W216" s="3" t="n">
         <v>144.9</v>
@@ -16910,9 +16428,7 @@
       <c r="T217" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="U217" s="3" t="n">
-        <v>10.5</v>
-      </c>
+      <c r="U217" s="3" t="inlineStr"/>
       <c r="V217" t="inlineStr"/>
       <c r="W217" s="3" t="n">
         <v>144.9</v>
@@ -16985,9 +16501,7 @@
       <c r="T218" s="3" t="n">
         <v>16.1</v>
       </c>
-      <c r="U218" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
+      <c r="U218" s="3" t="inlineStr"/>
       <c r="V218" t="inlineStr"/>
       <c r="W218" s="3" t="n">
         <v>149.2</v>
@@ -17064,9 +16578,7 @@
       <c r="T219" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="U219" s="3" t="n">
-        <v>10.3</v>
-      </c>
+      <c r="U219" s="3" t="inlineStr"/>
       <c r="V219" t="inlineStr"/>
       <c r="W219" s="3" t="n">
         <v>148.9</v>
@@ -17139,9 +16651,7 @@
       <c r="T220" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="U220" s="3" t="n">
-        <v>9.9</v>
-      </c>
+      <c r="U220" s="3" t="inlineStr"/>
       <c r="V220" t="inlineStr"/>
       <c r="W220" s="3" t="n">
         <v>148.8</v>
@@ -17214,9 +16724,7 @@
       <c r="T221" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="U221" s="3" t="n">
-        <v>9.4</v>
-      </c>
+      <c r="U221" s="3" t="inlineStr"/>
       <c r="V221" t="inlineStr"/>
       <c r="W221" s="3" t="n">
         <v>150.6</v>
@@ -17289,9 +16797,7 @@
       <c r="T222" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="U222" s="3" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U222" s="3" t="inlineStr"/>
       <c r="V222" t="inlineStr"/>
       <c r="W222" s="3" t="n">
         <v>150.3</v>
@@ -17364,9 +16870,7 @@
       <c r="T223" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="U223" s="3" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U223" s="3" t="inlineStr"/>
       <c r="V223" t="inlineStr"/>
       <c r="W223" s="3" t="n">
         <v>147.6</v>
@@ -17439,9 +16943,7 @@
       <c r="T224" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="U224" s="3" t="n">
-        <v>10.7</v>
-      </c>
+      <c r="U224" s="3" t="inlineStr"/>
       <c r="V224" t="inlineStr"/>
       <c r="W224" s="3" t="n">
         <v>148.3</v>
@@ -17514,9 +17016,7 @@
       <c r="T225" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="U225" s="3" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U225" s="3" t="inlineStr"/>
       <c r="V225" t="inlineStr"/>
       <c r="W225" s="3" t="n">
         <v>153.6</v>
@@ -17589,9 +17089,7 @@
       <c r="T226" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="U226" s="3" t="n">
-        <v>12.9</v>
-      </c>
+      <c r="U226" s="3" t="inlineStr"/>
       <c r="V226" t="inlineStr"/>
       <c r="W226" s="2" t="n">
         <v>161.9</v>
@@ -17668,9 +17166,7 @@
       <c r="T227" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="U227" s="3" t="n">
-        <v>11.9</v>
-      </c>
+      <c r="U227" s="3" t="inlineStr"/>
       <c r="V227" t="inlineStr"/>
       <c r="W227" s="2" t="n">
         <v>157</v>
@@ -17747,9 +17243,7 @@
       <c r="T228" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="U228" s="3" t="n">
-        <v>16.9</v>
-      </c>
+      <c r="U228" s="3" t="inlineStr"/>
       <c r="V228" t="inlineStr"/>
       <c r="W228" s="3" t="n">
         <v>153.5</v>
@@ -17822,9 +17316,7 @@
       <c r="T229" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="U229" s="3" t="n">
-        <v>15.8</v>
-      </c>
+      <c r="U229" s="3" t="inlineStr"/>
       <c r="V229" t="inlineStr"/>
       <c r="W229" s="2" t="n">
         <v>155.4</v>
@@ -17897,9 +17389,7 @@
       <c r="T230" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="U230" s="3" t="n">
-        <v>10.4</v>
-      </c>
+      <c r="U230" s="3" t="inlineStr"/>
       <c r="V230" t="inlineStr"/>
       <c r="W230" s="2" t="n">
         <v>155.9</v>
@@ -17972,9 +17462,7 @@
       <c r="T231" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="U231" s="3" t="n">
-        <v>7.7</v>
-      </c>
+      <c r="U231" s="3" t="inlineStr"/>
       <c r="V231" t="inlineStr"/>
       <c r="W231" s="2" t="n">
         <v>159.9</v>
@@ -18047,9 +17535,7 @@
       <c r="T232" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="U232" s="3" t="n">
-        <v>7.6</v>
-      </c>
+      <c r="U232" s="3" t="inlineStr"/>
       <c r="V232" t="inlineStr"/>
       <c r="W232" s="2" t="n">
         <v>160.5</v>
@@ -18122,9 +17608,7 @@
       <c r="T233" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="U233" s="3" t="n">
-        <v>7.4</v>
-      </c>
+      <c r="U233" s="3" t="inlineStr"/>
       <c r="V233" t="inlineStr"/>
       <c r="W233" s="2" t="n">
         <v>160.5</v>
@@ -18197,9 +17681,7 @@
       <c r="T234" s="3" t="n">
         <v>13.6</v>
       </c>
-      <c r="U234" s="3" t="n">
-        <v>7.7</v>
-      </c>
+      <c r="U234" s="3" t="inlineStr"/>
       <c r="V234" t="inlineStr"/>
       <c r="W234" s="3" t="n">
         <v>151.4</v>
@@ -18272,9 +17754,7 @@
       <c r="T235" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="U235" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
+      <c r="U235" s="3" t="inlineStr"/>
       <c r="V235" t="inlineStr"/>
       <c r="W235" s="3" t="n">
         <v>150.5</v>
@@ -18347,9 +17827,7 @@
       <c r="T236" s="3" t="n">
         <v>14.3</v>
       </c>
-      <c r="U236" s="3" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U236" s="3" t="inlineStr"/>
       <c r="V236" t="inlineStr"/>
       <c r="W236" s="3" t="n">
         <v>148.3</v>
@@ -18422,9 +17900,7 @@
       <c r="T237" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="U237" s="3" t="n">
-        <v>10.7</v>
-      </c>
+      <c r="U237" s="3" t="inlineStr"/>
       <c r="V237" t="inlineStr"/>
       <c r="W237" s="3" t="n">
         <v>148.7</v>
@@ -18497,9 +17973,7 @@
       <c r="T238" s="3" t="n">
         <v>14.5</v>
       </c>
-      <c r="U238" s="3" t="n">
-        <v>9.9</v>
-      </c>
+      <c r="U238" s="3" t="inlineStr"/>
       <c r="V238" t="inlineStr"/>
       <c r="W238" s="3" t="n">
         <v>141.9</v>
@@ -18572,9 +18046,7 @@
       <c r="T239" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="U239" s="3" t="n">
-        <v>8.300000000000001</v>
-      </c>
+      <c r="U239" s="3" t="inlineStr"/>
       <c r="V239" t="inlineStr"/>
       <c r="W239" s="3" t="n">
         <v>142.4</v>
@@ -18647,9 +18119,7 @@
       <c r="T240" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="U240" s="3" t="n">
-        <v>8</v>
-      </c>
+      <c r="U240" s="3" t="inlineStr"/>
       <c r="V240" t="inlineStr"/>
       <c r="W240" s="3" t="n">
         <v>146.2</v>
@@ -18722,9 +18192,7 @@
       <c r="T241" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="U241" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
+      <c r="U241" s="3" t="inlineStr"/>
       <c r="V241" t="inlineStr"/>
       <c r="W241" s="3" t="n">
         <v>143.6</v>
@@ -18797,9 +18265,7 @@
       <c r="T242" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="U242" s="3" t="n">
-        <v>13.6</v>
-      </c>
+      <c r="U242" s="3" t="inlineStr"/>
       <c r="V242" t="inlineStr"/>
       <c r="W242" s="3" t="n">
         <v>147.1</v>
@@ -18872,9 +18338,7 @@
       <c r="T243" s="3" t="n">
         <v>14.5</v>
       </c>
-      <c r="U243" s="3" t="n">
-        <v>8.5</v>
-      </c>
+      <c r="U243" s="3" t="inlineStr"/>
       <c r="V243" t="inlineStr"/>
       <c r="W243" s="3" t="n">
         <v>146</v>
@@ -18947,9 +18411,7 @@
       <c r="T244" s="3" t="n">
         <v>15.1</v>
       </c>
-      <c r="U244" s="3" t="n">
-        <v>9.6</v>
-      </c>
+      <c r="U244" s="3" t="inlineStr"/>
       <c r="V244" t="inlineStr"/>
       <c r="W244" s="3" t="n">
         <v>149.8</v>
@@ -19022,9 +18484,7 @@
       <c r="T245" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="U245" s="3" t="n">
-        <v>10.8</v>
-      </c>
+      <c r="U245" s="3" t="inlineStr"/>
       <c r="V245" t="inlineStr"/>
       <c r="W245" s="3" t="n">
         <v>151.6</v>
@@ -19097,9 +18557,7 @@
       <c r="T246" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="U246" s="3" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U246" s="3" t="inlineStr"/>
       <c r="V246" t="inlineStr"/>
       <c r="W246" s="3" t="n">
         <v>152.5</v>
@@ -19172,9 +18630,7 @@
       <c r="T247" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="U247" s="3" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U247" s="3" t="inlineStr"/>
       <c r="V247" t="inlineStr"/>
       <c r="W247" s="3" t="n">
         <v>151.6</v>
@@ -19247,9 +18703,7 @@
       <c r="T248" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="U248" s="3" t="n">
-        <v>12.3</v>
-      </c>
+      <c r="U248" s="3" t="inlineStr"/>
       <c r="V248" t="inlineStr"/>
       <c r="W248" s="3" t="n">
         <v>153.6</v>
@@ -19322,9 +18776,7 @@
       <c r="T249" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="U249" s="3" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="U249" s="3" t="inlineStr"/>
       <c r="V249" t="inlineStr"/>
       <c r="W249" s="2" t="n">
         <v>155</v>
@@ -19397,9 +18849,7 @@
       <c r="T250" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="U250" s="3" t="n">
-        <v>12.2</v>
-      </c>
+      <c r="U250" s="3" t="inlineStr"/>
       <c r="V250" t="inlineStr"/>
       <c r="W250" s="3" t="n">
         <v>144.4</v>
@@ -19472,9 +18922,7 @@
       <c r="T251" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="U251" s="3" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U251" s="3" t="inlineStr"/>
       <c r="V251" t="inlineStr"/>
       <c r="W251" s="3" t="n">
         <v>141.3</v>
@@ -19547,9 +18995,7 @@
       <c r="T252" s="3" t="n">
         <v>16.1</v>
       </c>
-      <c r="U252" s="3" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U252" s="3" t="inlineStr"/>
       <c r="V252" t="inlineStr"/>
       <c r="W252" s="3" t="n">
         <v>144</v>
@@ -19622,9 +19068,7 @@
       <c r="T253" s="3" t="n">
         <v>16.1</v>
       </c>
-      <c r="U253" s="3" t="n">
-        <v>9</v>
-      </c>
+      <c r="U253" s="3" t="inlineStr"/>
       <c r="V253" t="inlineStr"/>
       <c r="W253" s="3" t="n">
         <v>148.1</v>
@@ -19697,9 +19141,7 @@
       <c r="T254" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="U254" s="3" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U254" s="3" t="inlineStr"/>
       <c r="V254" t="inlineStr"/>
       <c r="W254" s="3" t="n">
         <v>147.2</v>
@@ -19772,9 +19214,7 @@
       <c r="T255" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="U255" s="3" t="n">
-        <v>13.2</v>
-      </c>
+      <c r="U255" s="3" t="inlineStr"/>
       <c r="V255" t="inlineStr"/>
       <c r="W255" s="3" t="n">
         <v>145</v>
@@ -19847,9 +19287,7 @@
       <c r="T256" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="U256" s="3" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U256" s="3" t="inlineStr"/>
       <c r="V256" t="inlineStr"/>
       <c r="W256" s="3" t="n">
         <v>143.7</v>
@@ -19922,9 +19360,7 @@
       <c r="T257" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="U257" s="3" t="n">
-        <v>16.4</v>
-      </c>
+      <c r="U257" s="3" t="inlineStr"/>
       <c r="V257" t="inlineStr"/>
       <c r="W257" s="3" t="n">
         <v>143.6</v>
@@ -19997,9 +19433,7 @@
       <c r="T258" s="3" t="n">
         <v>16.3</v>
       </c>
-      <c r="U258" s="3" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U258" s="3" t="inlineStr"/>
       <c r="V258" t="inlineStr"/>
       <c r="W258" s="3" t="n">
         <v>146.6</v>
@@ -20072,9 +19506,7 @@
       <c r="T259" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="U259" s="3" t="n">
-        <v>14.5</v>
-      </c>
+      <c r="U259" s="3" t="inlineStr"/>
       <c r="V259" t="inlineStr"/>
       <c r="W259" s="3" t="n">
         <v>143.9</v>
@@ -20147,9 +19579,7 @@
       <c r="T260" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="U260" s="3" t="n">
-        <v>17.5</v>
-      </c>
+      <c r="U260" s="3" t="inlineStr"/>
       <c r="V260" t="inlineStr"/>
       <c r="W260" s="3" t="n">
         <v>143.2</v>
@@ -20222,9 +19652,7 @@
       <c r="T261" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="U261" s="3" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U261" s="3" t="inlineStr"/>
       <c r="V261" t="inlineStr"/>
       <c r="W261" s="3" t="n">
         <v>137.2</v>
@@ -20297,9 +19725,7 @@
       <c r="T262" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="U262" s="3" t="n">
-        <v>15</v>
-      </c>
+      <c r="U262" s="3" t="inlineStr"/>
       <c r="V262" t="inlineStr"/>
       <c r="W262" s="3" t="n">
         <v>140.3</v>
@@ -20372,9 +19798,7 @@
       <c r="T263" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="U263" s="3" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U263" s="3" t="inlineStr"/>
       <c r="V263" t="inlineStr"/>
       <c r="W263" s="3" t="n">
         <v>145.2</v>
@@ -20447,9 +19871,7 @@
       <c r="T264" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="U264" s="3" t="n">
-        <v>13.6</v>
-      </c>
+      <c r="U264" s="3" t="inlineStr"/>
       <c r="V264" t="inlineStr"/>
       <c r="W264" s="3" t="n">
         <v>145.7</v>
@@ -20522,9 +19944,7 @@
       <c r="T265" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="U265" s="3" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U265" s="3" t="inlineStr"/>
       <c r="V265" t="inlineStr"/>
       <c r="W265" s="3" t="n">
         <v>143.8</v>
@@ -20597,9 +20017,7 @@
       <c r="T266" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="U266" s="3" t="n">
-        <v>21.5</v>
-      </c>
+      <c r="U266" s="3" t="inlineStr"/>
       <c r="V266" t="inlineStr"/>
       <c r="W266" s="3" t="n">
         <v>142.5</v>
@@ -20672,9 +20090,7 @@
       <c r="T267" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="U267" s="3" t="n">
-        <v>22.4</v>
-      </c>
+      <c r="U267" s="3" t="inlineStr"/>
       <c r="V267" t="inlineStr"/>
       <c r="W267" s="3" t="n">
         <v>139.4</v>
@@ -20747,9 +20163,7 @@
       <c r="T268" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="U268" s="3" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="U268" s="3" t="inlineStr"/>
       <c r="V268" t="inlineStr"/>
       <c r="W268" s="3" t="n">
         <v>140.3</v>
@@ -20822,9 +20236,7 @@
       <c r="T269" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="U269" s="3" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U269" s="3" t="inlineStr"/>
       <c r="V269" t="inlineStr"/>
       <c r="W269" s="3" t="n">
         <v>139.2</v>
@@ -20897,9 +20309,7 @@
       <c r="T270" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="U270" s="3" t="n">
-        <v>16.6</v>
-      </c>
+      <c r="U270" s="3" t="inlineStr"/>
       <c r="V270" t="inlineStr"/>
       <c r="W270" s="3" t="n">
         <v>141.2</v>
@@ -20972,9 +20382,7 @@
       <c r="T271" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="U271" s="3" t="n">
-        <v>17.8</v>
-      </c>
+      <c r="U271" s="3" t="inlineStr"/>
       <c r="V271" t="inlineStr"/>
       <c r="W271" s="3" t="n">
         <v>145.5</v>
@@ -21047,9 +20455,7 @@
       <c r="T272" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="U272" s="3" t="n">
-        <v>15.1</v>
-      </c>
+      <c r="U272" s="3" t="inlineStr"/>
       <c r="V272" t="inlineStr"/>
       <c r="W272" s="3" t="n">
         <v>141.4</v>
@@ -21122,9 +20528,7 @@
       <c r="T273" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="U273" s="3" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U273" s="3" t="inlineStr"/>
       <c r="V273" t="inlineStr"/>
       <c r="W273" s="3" t="n">
         <v>141.9</v>
@@ -21197,9 +20601,7 @@
       <c r="T274" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="U274" s="3" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U274" s="3" t="inlineStr"/>
       <c r="V274" t="inlineStr"/>
       <c r="W274" s="3" t="n">
         <v>146.1</v>
@@ -21272,9 +20674,7 @@
       <c r="T275" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="U275" s="3" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U275" s="3" t="inlineStr"/>
       <c r="V275" t="inlineStr"/>
       <c r="W275" s="3" t="n">
         <v>146.6</v>
@@ -21347,9 +20747,7 @@
       <c r="T276" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="U276" s="3" t="n">
-        <v>19</v>
-      </c>
+      <c r="U276" s="3" t="inlineStr"/>
       <c r="V276" t="inlineStr"/>
       <c r="W276" s="3" t="n">
         <v>146.7</v>
@@ -21422,9 +20820,7 @@
       <c r="T277" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="U277" s="3" t="n">
-        <v>16.3</v>
-      </c>
+      <c r="U277" s="3" t="inlineStr"/>
       <c r="V277" t="inlineStr"/>
       <c r="W277" s="3" t="n">
         <v>151.8</v>
@@ -21501,9 +20897,7 @@
       <c r="T278" s="6" t="n">
         <v>23.6</v>
       </c>
-      <c r="U278" s="6" t="n">
-        <v>20.3</v>
-      </c>
+      <c r="U278" s="6" t="inlineStr"/>
       <c r="V278" s="4" t="inlineStr"/>
       <c r="W278" s="6" t="n">
         <v>152.8</v>
@@ -21576,9 +20970,7 @@
       <c r="T279" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="U279" s="3" t="n">
-        <v>17.8</v>
-      </c>
+      <c r="U279" s="3" t="inlineStr"/>
       <c r="V279" t="inlineStr"/>
       <c r="W279" s="3" t="n">
         <v>152.9</v>
@@ -21651,9 +21043,7 @@
       <c r="T280" s="6" t="n">
         <v>23.8</v>
       </c>
-      <c r="U280" s="6" t="n">
-        <v>21.9</v>
-      </c>
+      <c r="U280" s="6" t="inlineStr"/>
       <c r="V280" s="4" t="inlineStr"/>
       <c r="W280" s="6" t="n">
         <v>153.9</v>
@@ -21726,14 +21116,8 @@
       <c r="T281" s="1" t="n">
         <v>29.5</v>
       </c>
-      <c r="U281" s="1" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="V281" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U281" s="3" t="inlineStr"/>
+      <c r="V281" t="inlineStr"/>
       <c r="W281" s="3" t="n">
         <v>151.8</v>
       </c>
@@ -21805,9 +21189,7 @@
       <c r="T282" s="1" t="n">
         <v>25.5</v>
       </c>
-      <c r="U282" s="3" t="n">
-        <v>22.7</v>
-      </c>
+      <c r="U282" s="3" t="inlineStr"/>
       <c r="V282" t="inlineStr"/>
       <c r="W282" s="2" t="n">
         <v>158</v>
@@ -21880,9 +21262,7 @@
       <c r="T283" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="U283" s="3" t="n">
-        <v>21.3</v>
-      </c>
+      <c r="U283" s="3" t="inlineStr"/>
       <c r="V283" t="inlineStr"/>
       <c r="W283" s="3" t="n">
         <v>154.5</v>
@@ -21955,9 +21335,7 @@
       <c r="T284" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="U284" s="3" t="n">
-        <v>19</v>
-      </c>
+      <c r="U284" s="3" t="inlineStr"/>
       <c r="V284" t="inlineStr"/>
       <c r="W284" s="3" t="n">
         <v>152.4</v>
@@ -22028,9 +21406,7 @@
       <c r="T285" s="7" t="n">
         <v>27.3</v>
       </c>
-      <c r="U285" s="6" t="n">
-        <v>24.2</v>
-      </c>
+      <c r="U285" s="6" t="inlineStr"/>
       <c r="V285" s="4" t="inlineStr"/>
       <c r="W285" s="6" t="n">
         <v>139.9</v>
@@ -22103,14 +21479,8 @@
       <c r="T286" s="1" t="n">
         <v>27.2</v>
       </c>
-      <c r="U286" s="1" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="V286" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U286" s="3" t="inlineStr"/>
+      <c r="V286" t="inlineStr"/>
       <c r="W286" s="3" t="n">
         <v>137.8</v>
       </c>
@@ -22182,9 +21552,7 @@
       <c r="T287" s="3" t="n">
         <v>23.5</v>
       </c>
-      <c r="U287" s="3" t="n">
-        <v>17.4</v>
-      </c>
+      <c r="U287" s="3" t="inlineStr"/>
       <c r="V287" t="inlineStr"/>
       <c r="W287" s="3" t="n">
         <v>141.5</v>
@@ -22257,9 +21625,7 @@
       <c r="T288" s="3" t="n">
         <v>22.4</v>
       </c>
-      <c r="U288" s="3" t="n">
-        <v>17.5</v>
-      </c>
+      <c r="U288" s="3" t="inlineStr"/>
       <c r="V288" t="inlineStr"/>
       <c r="W288" s="3" t="n">
         <v>145</v>
@@ -22332,9 +21698,7 @@
       <c r="T289" s="1" t="n">
         <v>25.1</v>
       </c>
-      <c r="U289" s="3" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="U289" s="3" t="inlineStr"/>
       <c r="V289" t="inlineStr"/>
       <c r="W289" s="3" t="n">
         <v>136.5</v>
@@ -22407,9 +21771,7 @@
       <c r="T290" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="U290" s="3" t="n">
-        <v>20.7</v>
-      </c>
+      <c r="U290" s="3" t="inlineStr"/>
       <c r="V290" t="inlineStr"/>
       <c r="W290" s="3" t="n">
         <v>138.3</v>
@@ -22486,14 +21848,8 @@
       <c r="T291" s="7" t="n">
         <v>26.8</v>
       </c>
-      <c r="U291" s="7" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="V291" s="7" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U291" s="6" t="inlineStr"/>
+      <c r="V291" s="4" t="inlineStr"/>
       <c r="W291" s="6" t="n">
         <v>139.1</v>
       </c>
@@ -22565,9 +21921,7 @@
       <c r="T292" s="1" t="n">
         <v>26.1</v>
       </c>
-      <c r="U292" s="3" t="n">
-        <v>23.2</v>
-      </c>
+      <c r="U292" s="3" t="inlineStr"/>
       <c r="V292" t="inlineStr"/>
       <c r="W292" s="3" t="n">
         <v>142</v>
@@ -22644,9 +21998,7 @@
       <c r="T293" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="U293" s="3" t="n">
-        <v>20.7</v>
-      </c>
+      <c r="U293" s="3" t="inlineStr"/>
       <c r="V293" t="inlineStr"/>
       <c r="W293" s="3" t="n">
         <v>142.6</v>
@@ -22719,9 +22071,7 @@
       <c r="T294" s="1" t="n">
         <v>25.3</v>
       </c>
-      <c r="U294" s="3" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="U294" s="3" t="inlineStr"/>
       <c r="V294" t="inlineStr"/>
       <c r="W294" s="3" t="n">
         <v>140.9</v>
@@ -22794,9 +22144,7 @@
       <c r="T295" s="7" t="n">
         <v>27.4</v>
       </c>
-      <c r="U295" s="6" t="n">
-        <v>23.9</v>
-      </c>
+      <c r="U295" s="6" t="inlineStr"/>
       <c r="V295" s="4" t="inlineStr"/>
       <c r="W295" s="6" t="n">
         <v>144</v>
@@ -22869,14 +22217,8 @@
       <c r="T296" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="U296" s="1" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="V296" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U296" s="3" t="inlineStr"/>
+      <c r="V296" t="inlineStr"/>
       <c r="W296" s="3" t="n">
         <v>139</v>
       </c>
@@ -22952,9 +22294,7 @@
       <c r="T297" s="1" t="n">
         <v>30.6</v>
       </c>
-      <c r="U297" s="3" t="n">
-        <v>23</v>
-      </c>
+      <c r="U297" s="3" t="inlineStr"/>
       <c r="V297" t="inlineStr"/>
       <c r="W297" s="3" t="n">
         <v>142.2</v>
@@ -23027,9 +22367,7 @@
       <c r="T298" s="1" t="n">
         <v>25.2</v>
       </c>
-      <c r="U298" s="3" t="n">
-        <v>19</v>
-      </c>
+      <c r="U298" s="3" t="inlineStr"/>
       <c r="V298" t="inlineStr"/>
       <c r="W298" s="3" t="n">
         <v>145.4</v>
@@ -23102,9 +22440,7 @@
       <c r="T299" s="3" t="n">
         <v>24.5</v>
       </c>
-      <c r="U299" s="3" t="n">
-        <v>23</v>
-      </c>
+      <c r="U299" s="3" t="inlineStr"/>
       <c r="V299" t="inlineStr"/>
       <c r="W299" s="3" t="n">
         <v>143.8</v>
@@ -23177,9 +22513,7 @@
       <c r="T300" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="U300" s="1" t="n">
-        <v>27.6</v>
-      </c>
+      <c r="U300" s="3" t="inlineStr"/>
       <c r="V300" t="inlineStr"/>
       <c r="W300" s="3" t="n">
         <v>146.9</v>
@@ -23252,9 +22586,7 @@
       <c r="T301" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="U301" s="3" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="U301" s="3" t="inlineStr"/>
       <c r="V301" t="inlineStr"/>
       <c r="W301" s="3" t="n">
         <v>147.6</v>
@@ -23327,14 +22659,8 @@
       <c r="T302" s="1" t="n">
         <v>25.8</v>
       </c>
-      <c r="U302" s="1" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="V302" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
+      <c r="U302" s="3" t="inlineStr"/>
+      <c r="V302" t="inlineStr"/>
       <c r="W302" s="3" t="n">
         <v>148.4</v>
       </c>
@@ -23406,9 +22732,7 @@
       <c r="T303" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="U303" s="3" t="n">
-        <v>16.5</v>
-      </c>
+      <c r="U303" s="3" t="inlineStr"/>
       <c r="V303" t="inlineStr"/>
       <c r="W303" s="3" t="n">
         <v>150.4</v>
@@ -23481,9 +22805,7 @@
       <c r="T304" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="U304" s="3" t="n">
-        <v>14.1</v>
-      </c>
+      <c r="U304" s="3" t="inlineStr"/>
       <c r="V304" t="inlineStr"/>
       <c r="W304" s="3" t="n">
         <v>143.3</v>
@@ -23556,9 +22878,7 @@
       <c r="T305" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="U305" s="3" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="U305" s="3" t="inlineStr"/>
       <c r="V305" t="inlineStr"/>
       <c r="W305" s="3" t="n">
         <v>144.2</v>
@@ -23631,9 +22951,7 @@
       <c r="T306" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="U306" s="3" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U306" s="3" t="inlineStr"/>
       <c r="V306" t="inlineStr"/>
       <c r="W306" s="2" t="n">
         <v>156.9</v>
@@ -23706,9 +23024,7 @@
       <c r="T307" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="U307" s="3" t="n">
-        <v>12.5</v>
-      </c>
+      <c r="U307" s="3" t="inlineStr"/>
       <c r="V307" t="inlineStr"/>
       <c r="W307" s="3" t="n">
         <v>149.9</v>
@@ -23781,9 +23097,7 @@
       <c r="T308" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="U308" s="3" t="n">
-        <v>12.6</v>
-      </c>
+      <c r="U308" s="3" t="inlineStr"/>
       <c r="V308" t="inlineStr"/>
       <c r="W308" s="3" t="n">
         <v>139.2</v>
@@ -23856,9 +23170,7 @@
       <c r="T309" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="U309" s="3" t="n">
-        <v>12</v>
-      </c>
+      <c r="U309" s="3" t="inlineStr"/>
       <c r="V309" t="inlineStr"/>
       <c r="W309" s="3" t="n">
         <v>140.7</v>
@@ -23931,9 +23243,7 @@
       <c r="T310" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="U310" s="3" t="n">
-        <v>14.2</v>
-      </c>
+      <c r="U310" s="3" t="inlineStr"/>
       <c r="V310" t="inlineStr"/>
       <c r="W310" s="3" t="n">
         <v>141.8</v>
@@ -24006,9 +23316,7 @@
       <c r="T311" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="U311" s="3" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="U311" s="3" t="inlineStr"/>
       <c r="V311" t="inlineStr"/>
       <c r="W311" s="3" t="n">
         <v>141.9</v>
@@ -24081,9 +23389,7 @@
       <c r="T312" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="U312" s="3" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="U312" s="3" t="inlineStr"/>
       <c r="V312" t="inlineStr"/>
       <c r="W312" s="3" t="n">
         <v>140.9</v>
@@ -24156,9 +23462,7 @@
       <c r="T313" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="U313" s="3" t="n">
-        <v>12.3</v>
-      </c>
+      <c r="U313" s="3" t="inlineStr"/>
       <c r="V313" t="inlineStr"/>
       <c r="W313" s="3" t="n">
         <v>140.8</v>
@@ -24231,9 +23535,7 @@
       <c r="T314" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="U314" s="3" t="n">
-        <v>14.8</v>
-      </c>
+      <c r="U314" s="3" t="inlineStr"/>
       <c r="V314" t="inlineStr"/>
       <c r="W314" s="3" t="n">
         <v>139.6</v>
@@ -24306,9 +23608,7 @@
       <c r="T315" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="U315" s="3" t="n">
-        <v>16.6</v>
-      </c>
+      <c r="U315" s="3" t="inlineStr"/>
       <c r="V315" t="inlineStr"/>
       <c r="W315" s="3" t="n">
         <v>139.1</v>
@@ -24381,9 +23681,7 @@
       <c r="T316" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="U316" s="3" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U316" s="3" t="inlineStr"/>
       <c r="V316" t="inlineStr"/>
       <c r="W316" s="3" t="n">
         <v>139.6</v>
@@ -24456,9 +23754,7 @@
       <c r="T317" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="U317" s="3" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U317" s="3" t="inlineStr"/>
       <c r="V317" t="inlineStr"/>
       <c r="W317" s="3" t="n">
         <v>138.2</v>
@@ -24531,9 +23827,7 @@
       <c r="T318" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="U318" s="3" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="U318" s="3" t="inlineStr"/>
       <c r="V318" t="inlineStr"/>
       <c r="W318" s="3" t="n">
         <v>141.9</v>
@@ -24606,9 +23900,7 @@
       <c r="T319" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="U319" s="3" t="n">
-        <v>11.6</v>
-      </c>
+      <c r="U319" s="3" t="inlineStr"/>
       <c r="V319" t="inlineStr"/>
       <c r="W319" s="3" t="n">
         <v>143.3</v>
@@ -24681,9 +23973,7 @@
       <c r="T320" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="U320" s="3" t="n">
-        <v>13.7</v>
-      </c>
+      <c r="U320" s="3" t="inlineStr"/>
       <c r="V320" t="inlineStr"/>
       <c r="W320" s="3" t="n">
         <v>141.4</v>
@@ -24756,9 +24046,7 @@
       <c r="T321" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="U321" s="3" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U321" s="3" t="inlineStr"/>
       <c r="V321" t="inlineStr"/>
       <c r="W321" s="3" t="n">
         <v>141.7</v>
@@ -24831,9 +24119,7 @@
       <c r="T322" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="U322" s="3" t="n">
-        <v>10.8</v>
-      </c>
+      <c r="U322" s="3" t="inlineStr"/>
       <c r="V322" t="inlineStr"/>
       <c r="W322" s="3" t="n">
         <v>138.7</v>
@@ -24906,9 +24192,7 @@
       <c r="T323" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="U323" s="3" t="n">
-        <v>11.7</v>
-      </c>
+      <c r="U323" s="3" t="inlineStr"/>
       <c r="V323" t="inlineStr"/>
       <c r="W323" s="3" t="n">
         <v>135.4</v>
@@ -24981,9 +24265,7 @@
       <c r="T324" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="U324" s="3" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U324" s="3" t="inlineStr"/>
       <c r="V324" t="inlineStr"/>
       <c r="W324" s="3" t="n">
         <v>136.1</v>
@@ -25056,9 +24338,7 @@
       <c r="T325" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="U325" s="3" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U325" s="3" t="inlineStr"/>
       <c r="V325" t="inlineStr"/>
       <c r="W325" s="3" t="n">
         <v>138.2</v>
@@ -25131,9 +24411,7 @@
       <c r="T326" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="U326" s="3" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="U326" s="3" t="inlineStr"/>
       <c r="V326" t="inlineStr"/>
       <c r="W326" s="3" t="n">
         <v>140.2</v>
@@ -25206,9 +24484,7 @@
       <c r="T327" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="U327" s="6" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U327" s="6" t="inlineStr"/>
       <c r="V327" s="4" t="inlineStr"/>
       <c r="W327" s="6" t="n">
         <v>139.4</v>
@@ -25281,9 +24557,7 @@
       <c r="T328" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="U328" s="3" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="U328" s="3" t="inlineStr"/>
       <c r="V328" t="inlineStr"/>
       <c r="W328" s="3" t="n">
         <v>141.5</v>
@@ -25356,9 +24630,7 @@
       <c r="T329" s="3" t="n">
         <v>17.3</v>
       </c>
-      <c r="U329" s="3" t="n">
-        <v>11.8</v>
-      </c>
+      <c r="U329" s="3" t="inlineStr"/>
       <c r="V329" t="inlineStr"/>
       <c r="W329" s="3" t="n">
         <v>139.3</v>
@@ -25431,9 +24703,7 @@
       <c r="T330" s="6" t="n">
         <v>18.4</v>
       </c>
-      <c r="U330" s="6" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="U330" s="6" t="inlineStr"/>
       <c r="V330" s="4" t="inlineStr"/>
       <c r="W330" s="6" t="n">
         <v>145.8</v>
@@ -25506,9 +24776,7 @@
       <c r="T331" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="U331" s="3" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U331" s="3" t="inlineStr"/>
       <c r="V331" t="inlineStr"/>
       <c r="W331" s="3" t="n">
         <v>138.4</v>
@@ -25585,9 +24853,7 @@
       <c r="T332" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="U332" s="3" t="n">
-        <v>13.3</v>
-      </c>
+      <c r="U332" s="3" t="inlineStr"/>
       <c r="V332" t="inlineStr"/>
       <c r="W332" s="3" t="n">
         <v>135.5</v>
@@ -25660,9 +24926,7 @@
       <c r="T333" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="U333" s="3" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="U333" s="3" t="inlineStr"/>
       <c r="V333" t="inlineStr"/>
       <c r="W333" s="3" t="n">
         <v>132.3</v>
@@ -25735,9 +24999,7 @@
       <c r="T334" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="U334" s="3" t="n">
-        <v>14</v>
-      </c>
+      <c r="U334" s="3" t="inlineStr"/>
       <c r="V334" t="inlineStr"/>
       <c r="W334" s="3" t="n">
         <v>137</v>
@@ -25810,9 +25072,7 @@
       <c r="T335" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="U335" s="3" t="n">
-        <v>17.4</v>
-      </c>
+      <c r="U335" s="3" t="inlineStr"/>
       <c r="V335" t="inlineStr"/>
       <c r="W335" s="3" t="n">
         <v>137.4</v>
@@ -25885,9 +25145,7 @@
       <c r="T336" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="U336" s="3" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="U336" s="3" t="inlineStr"/>
       <c r="V336" t="inlineStr"/>
       <c r="W336" s="3" t="n">
         <v>139</v>
@@ -25960,9 +25218,7 @@
       <c r="T337" s="3" t="n">
         <v>16.3</v>
       </c>
-      <c r="U337" s="3" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U337" s="3" t="inlineStr"/>
       <c r="V337" t="inlineStr"/>
       <c r="W337" s="3" t="n">
         <v>138.6</v>
@@ -26035,9 +25291,7 @@
       <c r="T338" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="U338" s="3" t="n">
-        <v>10.9</v>
-      </c>
+      <c r="U338" s="3" t="inlineStr"/>
       <c r="V338" t="inlineStr"/>
       <c r="W338" s="3" t="n">
         <v>139.5</v>
@@ -26110,9 +25364,7 @@
       <c r="T339" s="3" t="n">
         <v>15.3</v>
       </c>
-      <c r="U339" s="3" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U339" s="3" t="inlineStr"/>
       <c r="V339" t="inlineStr"/>
       <c r="W339" s="3" t="n">
         <v>144.2</v>
@@ -26185,9 +25437,7 @@
       <c r="T340" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="U340" s="3" t="n">
-        <v>9.6</v>
-      </c>
+      <c r="U340" s="3" t="inlineStr"/>
       <c r="V340" t="inlineStr"/>
       <c r="W340" s="3" t="n">
         <v>142.5</v>
@@ -26260,9 +25510,7 @@
       <c r="T341" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="U341" s="3" t="n">
-        <v>8.9</v>
-      </c>
+      <c r="U341" s="3" t="inlineStr"/>
       <c r="V341" t="inlineStr"/>
       <c r="W341" s="3" t="n">
         <v>143.2</v>
@@ -26335,9 +25583,7 @@
       <c r="T342" s="3" t="n">
         <v>16.1</v>
       </c>
-      <c r="U342" s="3" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="U342" s="3" t="inlineStr"/>
       <c r="V342" t="inlineStr"/>
       <c r="W342" s="3" t="n">
         <v>136.9</v>
@@ -26410,9 +25656,7 @@
       <c r="T343" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="U343" s="3" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U343" s="3" t="inlineStr"/>
       <c r="V343" t="inlineStr"/>
       <c r="W343" s="3" t="n">
         <v>142.1</v>
@@ -26489,9 +25733,7 @@
       <c r="T344" s="6" t="n">
         <v>21.5</v>
       </c>
-      <c r="U344" s="7" t="n">
-        <v>28.7</v>
-      </c>
+      <c r="U344" s="6" t="inlineStr"/>
       <c r="V344" s="4" t="inlineStr"/>
       <c r="W344" s="6" t="n">
         <v>152.2</v>
@@ -26564,9 +25806,7 @@
       <c r="T345" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="U345" s="3" t="n">
-        <v>16</v>
-      </c>
+      <c r="U345" s="3" t="inlineStr"/>
       <c r="V345" t="inlineStr"/>
       <c r="W345" s="3" t="n">
         <v>145</v>
@@ -26639,9 +25879,7 @@
       <c r="T346" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="U346" s="3" t="n">
-        <v>20.6</v>
-      </c>
+      <c r="U346" s="3" t="inlineStr"/>
       <c r="V346" t="inlineStr"/>
       <c r="W346" s="3" t="n">
         <v>142</v>
@@ -26714,9 +25952,7 @@
       <c r="T347" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="U347" s="3" t="n">
-        <v>23.9</v>
-      </c>
+      <c r="U347" s="3" t="inlineStr"/>
       <c r="V347" t="inlineStr"/>
       <c r="W347" s="3" t="n">
         <v>143.1</v>
@@ -26789,9 +26025,7 @@
       <c r="T348" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="U348" s="3" t="n">
-        <v>21.1</v>
-      </c>
+      <c r="U348" s="3" t="inlineStr"/>
       <c r="V348" t="inlineStr"/>
       <c r="W348" s="3" t="n">
         <v>143</v>
@@ -26864,9 +26098,7 @@
       <c r="T349" s="3" t="n">
         <v>17.7</v>
       </c>
-      <c r="U349" s="3" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="U349" s="3" t="inlineStr"/>
       <c r="V349" t="inlineStr"/>
       <c r="W349" s="3" t="n">
         <v>142.6</v>
@@ -26939,9 +26171,7 @@
       <c r="T350" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="U350" s="3" t="n">
-        <v>12.9</v>
-      </c>
+      <c r="U350" s="3" t="inlineStr"/>
       <c r="V350" t="inlineStr"/>
       <c r="W350" s="3" t="n">
         <v>144.3</v>
@@ -27014,9 +26244,7 @@
       <c r="T351" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="U351" s="3" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="U351" s="3" t="inlineStr"/>
       <c r="V351" t="inlineStr"/>
       <c r="W351" s="3" t="n">
         <v>142.7</v>
@@ -27093,9 +26321,7 @@
       <c r="T352" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="U352" s="3" t="n">
-        <v>20.7</v>
-      </c>
+      <c r="U352" s="3" t="inlineStr"/>
       <c r="V352" t="inlineStr"/>
       <c r="W352" s="3" t="n">
         <v>142.6</v>
@@ -27168,9 +26394,7 @@
       <c r="T353" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="U353" s="3" t="n">
-        <v>15.7</v>
-      </c>
+      <c r="U353" s="3" t="inlineStr"/>
       <c r="V353" t="inlineStr"/>
       <c r="W353" s="3" t="n">
         <v>146.7</v>
@@ -27243,9 +26467,7 @@
       <c r="T354" s="3" t="n">
         <v>17.3</v>
       </c>
-      <c r="U354" s="3" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="U354" s="3" t="inlineStr"/>
       <c r="V354" t="inlineStr"/>
       <c r="W354" s="3" t="n">
         <v>141.9</v>
@@ -27322,9 +26544,7 @@
       <c r="T355" s="6" t="n">
         <v>19.5</v>
       </c>
-      <c r="U355" s="6" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U355" s="6" t="inlineStr"/>
       <c r="V355" s="4" t="inlineStr"/>
       <c r="W355" s="6" t="n">
         <v>143.1</v>
@@ -27397,9 +26617,7 @@
       <c r="T356" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="U356" s="3" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U356" s="3" t="inlineStr"/>
       <c r="V356" t="inlineStr"/>
       <c r="W356" s="3" t="n">
         <v>145.3</v>
@@ -27472,9 +26690,7 @@
       <c r="T357" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="U357" s="3" t="n">
-        <v>16</v>
-      </c>
+      <c r="U357" s="3" t="inlineStr"/>
       <c r="V357" t="inlineStr"/>
       <c r="W357" s="3" t="n">
         <v>139.9</v>
@@ -27547,9 +26763,7 @@
       <c r="T358" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="U358" s="3" t="n">
-        <v>17.6</v>
-      </c>
+      <c r="U358" s="3" t="inlineStr"/>
       <c r="V358" t="inlineStr"/>
       <c r="W358" s="3" t="n">
         <v>139.4</v>
@@ -27622,9 +26836,7 @@
       <c r="T359" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="U359" s="3" t="n">
-        <v>13.6</v>
-      </c>
+      <c r="U359" s="3" t="inlineStr"/>
       <c r="V359" t="inlineStr"/>
       <c r="W359" s="3" t="n">
         <v>144.5</v>
@@ -27697,9 +26909,7 @@
       <c r="T360" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="U360" s="3" t="n">
-        <v>11.6</v>
-      </c>
+      <c r="U360" s="3" t="inlineStr"/>
       <c r="V360" t="inlineStr"/>
       <c r="W360" s="3" t="n">
         <v>149.6</v>
@@ -27776,9 +26986,7 @@
       <c r="T361" s="6" t="n">
         <v>16.6</v>
       </c>
-      <c r="U361" s="6" t="n">
-        <v>13</v>
-      </c>
+      <c r="U361" s="6" t="inlineStr"/>
       <c r="V361" s="4" t="inlineStr"/>
       <c r="W361" s="6" t="n">
         <v>154.8</v>
@@ -27855,9 +27063,7 @@
       <c r="T362" s="3" t="n">
         <v>16.1</v>
       </c>
-      <c r="U362" s="3" t="n">
-        <v>13.2</v>
-      </c>
+      <c r="U362" s="3" t="inlineStr"/>
       <c r="V362" t="inlineStr"/>
       <c r="W362" s="3" t="n">
         <v>150</v>
@@ -27930,9 +27136,7 @@
       <c r="T363" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="U363" s="3" t="n">
-        <v>8.699999999999999</v>
-      </c>
+      <c r="U363" s="3" t="inlineStr"/>
       <c r="V363" t="inlineStr"/>
       <c r="W363" s="3" t="n">
         <v>145.4</v>
@@ -28009,9 +27213,7 @@
       <c r="T364" s="3" t="n">
         <v>16.1</v>
       </c>
-      <c r="U364" s="3" t="n">
-        <v>10.7</v>
-      </c>
+      <c r="U364" s="3" t="inlineStr"/>
       <c r="V364" t="inlineStr"/>
       <c r="W364" s="3" t="n">
         <v>145.7</v>
@@ -28084,9 +27286,7 @@
       <c r="T365" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="U365" s="3" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U365" s="3" t="inlineStr"/>
       <c r="V365" t="inlineStr"/>
       <c r="W365" s="3" t="n">
         <v>149.8</v>
@@ -28159,9 +27359,7 @@
       <c r="T366" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="U366" s="3" t="n">
-        <v>10.1</v>
-      </c>
+      <c r="U366" s="3" t="inlineStr"/>
       <c r="V366" t="inlineStr"/>
       <c r="W366" s="3" t="n">
         <v>144.7</v>
@@ -28238,9 +27436,7 @@
       <c r="T367" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="U367" s="3" t="n">
-        <v>9.9</v>
-      </c>
+      <c r="U367" s="3" t="inlineStr"/>
       <c r="V367" t="inlineStr"/>
       <c r="W367" s="3" t="n">
         <v>144.3</v>
@@ -28313,9 +27509,7 @@
       <c r="T368" s="6" t="n">
         <v>17.2</v>
       </c>
-      <c r="U368" s="6" t="n">
-        <v>14.6</v>
-      </c>
+      <c r="U368" s="6" t="inlineStr"/>
       <c r="V368" s="4" t="inlineStr"/>
       <c r="W368" s="6" t="n">
         <v>145.7</v>
@@ -28388,9 +27582,7 @@
       <c r="T369" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="U369" s="3" t="n">
-        <v>10.6</v>
-      </c>
+      <c r="U369" s="3" t="inlineStr"/>
       <c r="V369" t="inlineStr"/>
       <c r="W369" s="3" t="n">
         <v>145.1</v>
@@ -28463,9 +27655,7 @@
       <c r="T370" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="U370" s="3" t="n">
-        <v>9.5</v>
-      </c>
+      <c r="U370" s="3" t="inlineStr"/>
       <c r="V370" t="inlineStr"/>
       <c r="W370" s="3" t="n">
         <v>148.5</v>
@@ -28542,9 +27732,7 @@
       <c r="T371" s="6" t="n">
         <v>16.7</v>
       </c>
-      <c r="U371" s="6" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="U371" s="6" t="inlineStr"/>
       <c r="V371" s="4" t="inlineStr"/>
       <c r="W371" s="6" t="n">
         <v>145.7</v>
@@ -28621,9 +27809,7 @@
       <c r="T372" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="U372" s="3" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="U372" s="3" t="inlineStr"/>
       <c r="V372" t="inlineStr"/>
       <c r="W372" s="3" t="n">
         <v>147.3</v>
@@ -31524,7 +30710,7 @@
         <v>18.57</v>
       </c>
       <c r="G412" s="4" t="n">
-        <v>38357200</v>
+        <v>39223800</v>
       </c>
       <c r="H412" s="5" t="n">
         <v>-19.51</v>
@@ -31598,13 +30784,13 @@
         <v>18.25</v>
       </c>
       <c r="F413" t="n">
-        <v>18.57</v>
+        <v>18.6</v>
       </c>
       <c r="G413" t="n">
-        <v>14223761</v>
-      </c>
-      <c r="H413" s="3" t="n">
-        <v>0</v>
+        <v>15959834</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>0.16</v>
       </c>
       <c r="I413" t="n">
         <v>13.4</v>
@@ -31622,7 +30808,7 @@
         <v>23.14</v>
       </c>
       <c r="N413" s="3" t="n">
-        <v>43.83</v>
+        <v>43.92</v>
       </c>
       <c r="O413" t="n">
         <v>29</v>
@@ -31639,16 +30825,18 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>5.01</v>
+        <v>5</v>
       </c>
       <c r="T413" s="3" t="n">
-        <v>17.6</v>
+        <v>17.2</v>
       </c>
       <c r="U413" s="3" t="n">
-        <v>14.8</v>
+        <v>17.1</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="3" t="inlineStr"/>
+      <c r="W413" s="3" t="n">
+        <v>146.6</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -30701,28 +30701,44 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
+      <c r="C412" t="n">
+        <v>19.34</v>
+      </c>
+      <c r="D412" t="n">
+        <v>19.38</v>
+      </c>
+      <c r="E412" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="F412" t="n">
+        <v>18.6</v>
+      </c>
       <c r="G412" t="n">
-        <v>15959834</v>
-      </c>
-      <c r="H412" s="2" t="n">
-        <v>0</v>
+        <v>16107900</v>
+      </c>
+      <c r="H412" s="3" t="n">
+        <v>0.16</v>
       </c>
       <c r="I412" t="n">
         <v>13.4</v>
       </c>
-      <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr"/>
-      <c r="L412" t="inlineStr"/>
-      <c r="M412" t="inlineStr"/>
+      <c r="J412" t="n">
+        <v>20.69</v>
+      </c>
+      <c r="K412" t="n">
+        <v>23.03</v>
+      </c>
+      <c r="L412" t="n">
+        <v>28.41</v>
+      </c>
+      <c r="M412" t="n">
+        <v>23.14</v>
+      </c>
       <c r="N412" s="2" t="n">
-        <v>43.83</v>
+        <v>43.92</v>
       </c>
       <c r="O412" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -30757,13 +30757,84 @@
       <c r="T412" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U412" s="2" t="n">
-        <v>17.1</v>
-      </c>
+      <c r="U412" s="2" t="inlineStr"/>
       <c r="V412" t="inlineStr"/>
       <c r="W412" s="2" t="n">
         <v>146.6</v>
       </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>KORU</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>19.58</v>
+      </c>
+      <c r="D413" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="E413" t="n">
+        <v>19.21</v>
+      </c>
+      <c r="F413" t="n">
+        <v>19.32</v>
+      </c>
+      <c r="G413" t="n">
+        <v>11950944</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="I413" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="J413" t="n">
+        <v>20.76</v>
+      </c>
+      <c r="K413" t="n">
+        <v>22.45</v>
+      </c>
+      <c r="L413" t="n">
+        <v>28.44</v>
+      </c>
+      <c r="M413" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>46.88</v>
+      </c>
+      <c r="O413" t="n">
+        <v>29</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -30714,7 +30714,7 @@
         <v>18.6</v>
       </c>
       <c r="G412" t="n">
-        <v>16107900</v>
+        <v>16683700</v>
       </c>
       <c r="H412" s="3" t="n">
         <v>0.16</v>
@@ -30781,37 +30781,37 @@
         <v>19.75</v>
       </c>
       <c r="E413" t="n">
-        <v>19.21</v>
+        <v>17.78</v>
       </c>
       <c r="F413" t="n">
-        <v>19.32</v>
+        <v>18.32</v>
       </c>
       <c r="G413" t="n">
-        <v>11950944</v>
-      </c>
-      <c r="H413" s="3" t="n">
-        <v>3.87</v>
+        <v>24205791</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>-1.51</v>
       </c>
       <c r="I413" t="n">
         <v>13.4</v>
       </c>
       <c r="J413" t="n">
-        <v>20.76</v>
+        <v>20.71</v>
       </c>
       <c r="K413" t="n">
-        <v>22.45</v>
+        <v>22.43</v>
       </c>
       <c r="L413" t="n">
-        <v>28.44</v>
+        <v>28.43</v>
       </c>
       <c r="M413" t="n">
-        <v>23.2</v>
+        <v>23.19</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>46.88</v>
+        <v>44.07</v>
       </c>
       <c r="O413" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -30825,13 +30825,13 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>4.96</v>
+        <v>5.01</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>16.8</v>
+        <v>18.1</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>16.2</v>
+        <v>18</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="inlineStr"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -1721,7 +1721,7 @@
         <v>2.11</v>
       </c>
       <c r="K17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="L17" t="n">
         <v>2.59</v>
@@ -2086,7 +2086,7 @@
         <v>2.17</v>
       </c>
       <c r="K22" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="L22" t="n">
         <v>2.53</v>
@@ -8689,7 +8689,7 @@
         <v>13.4</v>
       </c>
       <c r="J112" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="K112" t="n">
         <v>2.67</v>
@@ -13024,7 +13024,7 @@
         <v>13.4</v>
       </c>
       <c r="J171" t="n">
-        <v>4.86</v>
+        <v>4.85</v>
       </c>
       <c r="K171" t="n">
         <v>4.34</v>
@@ -20129,7 +20129,7 @@
         <v>13.4</v>
       </c>
       <c r="J268" t="n">
-        <v>18.15</v>
+        <v>18.14</v>
       </c>
       <c r="K268" t="n">
         <v>12.11</v>
@@ -20202,7 +20202,7 @@
         <v>13.4</v>
       </c>
       <c r="J269" t="n">
-        <v>18.55</v>
+        <v>18.54</v>
       </c>
       <c r="K269" t="n">
         <v>12.38</v>
@@ -26510,7 +26510,7 @@
         <v>13.4</v>
       </c>
       <c r="J355" t="n">
-        <v>46.66</v>
+        <v>46.67</v>
       </c>
       <c r="K355" t="n">
         <v>35.18</v>
@@ -28959,7 +28959,7 @@
         <v>13.4</v>
       </c>
       <c r="J388" t="n">
-        <v>17.8</v>
+        <v>17.79</v>
       </c>
       <c r="K388" t="n">
         <v>32.76</v>
@@ -29401,7 +29401,7 @@
         <v>13.4</v>
       </c>
       <c r="J394" t="n">
-        <v>18</v>
+        <v>17.99</v>
       </c>
       <c r="K394" t="n">
         <v>31.04</v>
@@ -30784,13 +30784,13 @@
         <v>17.78</v>
       </c>
       <c r="F413" t="n">
-        <v>18.32</v>
+        <v>18.28</v>
       </c>
       <c r="G413" t="n">
-        <v>24205791</v>
+        <v>25671951</v>
       </c>
       <c r="H413" s="1" t="n">
-        <v>-1.51</v>
+        <v>-1.72</v>
       </c>
       <c r="I413" t="n">
         <v>13.4</v>
@@ -30808,7 +30808,7 @@
         <v>23.19</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>44.07</v>
+        <v>43.97</v>
       </c>
       <c r="O413" t="n">
         <v>26</v>
@@ -30828,13 +30828,15 @@
         <v>5.01</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>18.1</v>
+        <v>17.7</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>145.9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -30774,41 +30774,25 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="C413" t="n">
-        <v>19.58</v>
-      </c>
-      <c r="D413" t="n">
-        <v>19.75</v>
-      </c>
-      <c r="E413" t="n">
-        <v>17.78</v>
-      </c>
-      <c r="F413" t="n">
-        <v>18.28</v>
-      </c>
+      <c r="C413" t="inlineStr"/>
+      <c r="D413" t="inlineStr"/>
+      <c r="E413" t="inlineStr"/>
+      <c r="F413" t="inlineStr"/>
       <c r="G413" t="n">
         <v>25671951</v>
       </c>
-      <c r="H413" s="1" t="n">
-        <v>-1.72</v>
+      <c r="H413" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I413" t="n">
         <v>13.4</v>
       </c>
-      <c r="J413" t="n">
-        <v>20.71</v>
-      </c>
-      <c r="K413" t="n">
-        <v>22.43</v>
-      </c>
-      <c r="L413" t="n">
-        <v>28.43</v>
-      </c>
-      <c r="M413" t="n">
-        <v>23.19</v>
-      </c>
+      <c r="J413" t="inlineStr"/>
+      <c r="K413" t="inlineStr"/>
+      <c r="L413" t="inlineStr"/>
+      <c r="M413" t="inlineStr"/>
       <c r="N413" s="2" t="n">
-        <v>43.97</v>
+        <v>44.75</v>
       </c>
       <c r="O413" t="n">
         <v>26</v>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -30774,25 +30774,41 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="C413" t="inlineStr"/>
-      <c r="D413" t="inlineStr"/>
-      <c r="E413" t="inlineStr"/>
-      <c r="F413" t="inlineStr"/>
+      <c r="C413" t="n">
+        <v>19.58</v>
+      </c>
+      <c r="D413" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="E413" t="n">
+        <v>17.79</v>
+      </c>
+      <c r="F413" t="n">
+        <v>18.28</v>
+      </c>
       <c r="G413" t="n">
-        <v>25671951</v>
-      </c>
-      <c r="H413" s="2" t="n">
-        <v>0</v>
+        <v>25673500</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>-1.72</v>
       </c>
       <c r="I413" t="n">
         <v>13.4</v>
       </c>
-      <c r="J413" t="inlineStr"/>
-      <c r="K413" t="inlineStr"/>
-      <c r="L413" t="inlineStr"/>
-      <c r="M413" t="inlineStr"/>
+      <c r="J413" t="n">
+        <v>20.71</v>
+      </c>
+      <c r="K413" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="L413" t="n">
+        <v>28.43</v>
+      </c>
+      <c r="M413" t="n">
+        <v>23.19</v>
+      </c>
       <c r="N413" s="2" t="n">
-        <v>44.75</v>
+        <v>43.97</v>
       </c>
       <c r="O413" t="n">
         <v>26</v>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -30811,7 +30811,7 @@
         <v>43.97</v>
       </c>
       <c r="O413" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -30830,13 +30830,84 @@
       <c r="T413" s="2" t="n">
         <v>17.7</v>
       </c>
-      <c r="U413" s="2" t="n">
-        <v>17</v>
-      </c>
+      <c r="U413" s="2" t="inlineStr"/>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="n">
         <v>145.9</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>KORU</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>20.16</v>
+      </c>
+      <c r="D414" t="n">
+        <v>20.73</v>
+      </c>
+      <c r="E414" t="n">
+        <v>20.11</v>
+      </c>
+      <c r="F414" t="n">
+        <v>20.63</v>
+      </c>
+      <c r="G414" t="n">
+        <v>15666306</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>12.86</v>
+      </c>
+      <c r="I414" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="J414" t="n">
+        <v>20.79</v>
+      </c>
+      <c r="K414" t="n">
+        <v>22.19</v>
+      </c>
+      <c r="L414" t="n">
+        <v>28.49</v>
+      </c>
+      <c r="M414" t="n">
+        <v>23.26</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>48.03</v>
+      </c>
+      <c r="O414" t="n">
+        <v>29</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -30787,7 +30787,7 @@
         <v>18.28</v>
       </c>
       <c r="G413" t="n">
-        <v>25673500</v>
+        <v>26890200</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>-1.72</v>
@@ -30857,19 +30857,19 @@
         <v>20.11</v>
       </c>
       <c r="F414" t="n">
-        <v>20.63</v>
+        <v>20.41</v>
       </c>
       <c r="G414" t="n">
-        <v>15666306</v>
+        <v>18014889</v>
       </c>
       <c r="H414" s="3" t="n">
-        <v>12.86</v>
+        <v>11.65</v>
       </c>
       <c r="I414" t="n">
         <v>13.4</v>
       </c>
       <c r="J414" t="n">
-        <v>20.79</v>
+        <v>20.78</v>
       </c>
       <c r="K414" t="n">
         <v>22.19</v>
@@ -30881,7 +30881,7 @@
         <v>23.26</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>48.03</v>
+        <v>47.44</v>
       </c>
       <c r="O414" t="n">
         <v>29</v>
@@ -30901,13 +30901,15 @@
         <v>4.95</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>15.6</v>
+        <v>15.4</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>11.7</v>
+        <v>13.1</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="n">
+        <v>145.7</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -30847,41 +30847,25 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="C414" t="n">
-        <v>20.16</v>
-      </c>
-      <c r="D414" t="n">
-        <v>20.73</v>
-      </c>
-      <c r="E414" t="n">
-        <v>20.11</v>
-      </c>
-      <c r="F414" t="n">
-        <v>20.41</v>
-      </c>
+      <c r="C414" t="inlineStr"/>
+      <c r="D414" t="inlineStr"/>
+      <c r="E414" t="inlineStr"/>
+      <c r="F414" t="inlineStr"/>
       <c r="G414" t="n">
         <v>18014889</v>
       </c>
-      <c r="H414" s="3" t="n">
-        <v>11.65</v>
+      <c r="H414" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I414" t="n">
         <v>13.4</v>
       </c>
-      <c r="J414" t="n">
-        <v>20.78</v>
-      </c>
-      <c r="K414" t="n">
-        <v>22.19</v>
-      </c>
-      <c r="L414" t="n">
-        <v>28.49</v>
-      </c>
-      <c r="M414" t="n">
-        <v>23.26</v>
-      </c>
+      <c r="J414" t="inlineStr"/>
+      <c r="K414" t="inlineStr"/>
+      <c r="L414" t="inlineStr"/>
+      <c r="M414" t="inlineStr"/>
       <c r="N414" s="2" t="n">
-        <v>47.44</v>
+        <v>41.01</v>
       </c>
       <c r="O414" t="n">
         <v>29</v>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -30847,25 +30847,41 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr"/>
-      <c r="D414" t="inlineStr"/>
-      <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
+      <c r="C414" t="n">
+        <v>20.16</v>
+      </c>
+      <c r="D414" t="n">
+        <v>20.73</v>
+      </c>
+      <c r="E414" t="n">
+        <v>20.11</v>
+      </c>
+      <c r="F414" t="n">
+        <v>20.41</v>
+      </c>
       <c r="G414" t="n">
-        <v>18014889</v>
-      </c>
-      <c r="H414" s="2" t="n">
-        <v>0</v>
+        <v>18182800</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>11.65</v>
       </c>
       <c r="I414" t="n">
         <v>13.4</v>
       </c>
-      <c r="J414" t="inlineStr"/>
-      <c r="K414" t="inlineStr"/>
-      <c r="L414" t="inlineStr"/>
-      <c r="M414" t="inlineStr"/>
+      <c r="J414" t="n">
+        <v>20.78</v>
+      </c>
+      <c r="K414" t="n">
+        <v>22.19</v>
+      </c>
+      <c r="L414" t="n">
+        <v>28.49</v>
+      </c>
+      <c r="M414" t="n">
+        <v>23.26</v>
+      </c>
       <c r="N414" s="2" t="n">
-        <v>41.01</v>
+        <v>47.44</v>
       </c>
       <c r="O414" t="n">
         <v>29</v>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -30884,7 +30884,7 @@
         <v>47.44</v>
       </c>
       <c r="O414" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -30903,13 +30903,84 @@
       <c r="T414" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U414" s="2" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="U414" s="2" t="inlineStr"/>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="n">
         <v>145.7</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>KORU</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>19.67</v>
+      </c>
+      <c r="D415" t="n">
+        <v>19.74</v>
+      </c>
+      <c r="E415" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="F415" t="n">
+        <v>19.43</v>
+      </c>
+      <c r="G415" t="n">
+        <v>8903842</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="I415" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="J415" t="n">
+        <v>20.73</v>
+      </c>
+      <c r="K415" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="L415" t="n">
+        <v>28.54</v>
+      </c>
+      <c r="M415" t="n">
+        <v>23.32</v>
+      </c>
+      <c r="N415" s="2" t="n">
+        <v>46.63</v>
+      </c>
+      <c r="O415" t="n">
+        <v>29</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>5</v>
+      </c>
+      <c r="T415" s="2" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="U415" s="2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -649,7 +649,9 @@
       <c r="T2" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U2" s="2" t="inlineStr"/>
+      <c r="U2" s="2" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" s="1" t="n">
         <v>168.6</v>
@@ -722,7 +724,9 @@
       <c r="T3" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U3" s="2" t="inlineStr"/>
+      <c r="U3" s="2" t="n">
+        <v>13.5</v>
+      </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" s="1" t="n">
         <v>163.6</v>
@@ -795,7 +799,9 @@
       <c r="T4" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U4" s="2" t="inlineStr"/>
+      <c r="U4" s="2" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" s="1" t="n">
         <v>157.4</v>
@@ -868,7 +874,9 @@
       <c r="T5" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" s="1" t="n">
         <v>156.7</v>
@@ -945,7 +953,9 @@
       <c r="T6" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="n">
+        <v>16.5</v>
+      </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" s="1" t="n">
         <v>158.5</v>
@@ -1018,7 +1028,9 @@
       <c r="T7" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="n">
+        <v>18.2</v>
+      </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" s="1" t="n">
         <v>155.4</v>
@@ -1091,7 +1103,9 @@
       <c r="T8" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="n">
+        <v>15</v>
+      </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" s="1" t="n">
         <v>159.4</v>
@@ -1164,7 +1178,9 @@
       <c r="T9" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" s="1" t="n">
         <v>162.6</v>
@@ -1237,7 +1253,9 @@
       <c r="T10" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="U10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="n">
+        <v>15.8</v>
+      </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" s="1" t="n">
         <v>163.6</v>
@@ -1314,7 +1332,9 @@
       <c r="T11" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V11" t="inlineStr"/>
       <c r="W11" s="1" t="n">
         <v>166.5</v>
@@ -1387,7 +1407,9 @@
       <c r="T12" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="n">
+        <v>11.3</v>
+      </c>
       <c r="V12" t="inlineStr"/>
       <c r="W12" s="1" t="n">
         <v>166.9</v>
@@ -1460,7 +1482,9 @@
       <c r="T13" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="n">
+        <v>14.1</v>
+      </c>
       <c r="V13" t="inlineStr"/>
       <c r="W13" s="1" t="n">
         <v>168.8</v>
@@ -1533,7 +1557,9 @@
       <c r="T14" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="U14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="n">
+        <v>12.8</v>
+      </c>
       <c r="V14" t="inlineStr"/>
       <c r="W14" s="1" t="n">
         <v>166.1</v>
@@ -1606,7 +1632,9 @@
       <c r="T15" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="n">
+        <v>11</v>
+      </c>
       <c r="V15" t="inlineStr"/>
       <c r="W15" s="1" t="n">
         <v>163.4</v>
@@ -1679,7 +1707,9 @@
       <c r="T16" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V16" t="inlineStr"/>
       <c r="W16" s="1" t="n">
         <v>168</v>
@@ -1752,7 +1782,9 @@
       <c r="T17" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="n">
+        <v>9.300000000000001</v>
+      </c>
       <c r="V17" t="inlineStr"/>
       <c r="W17" s="1" t="n">
         <v>183.1</v>
@@ -1825,7 +1857,9 @@
       <c r="T18" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="n">
+        <v>9.300000000000001</v>
+      </c>
       <c r="V18" t="inlineStr"/>
       <c r="W18" s="1" t="n">
         <v>175.8</v>
@@ -1898,7 +1932,9 @@
       <c r="T19" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="n">
+        <v>11.2</v>
+      </c>
       <c r="V19" t="inlineStr"/>
       <c r="W19" s="1" t="n">
         <v>178.6</v>
@@ -1971,7 +2007,9 @@
       <c r="T20" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="n">
+        <v>18.2</v>
+      </c>
       <c r="V20" t="inlineStr"/>
       <c r="W20" s="1" t="n">
         <v>165</v>
@@ -2044,7 +2082,9 @@
       <c r="T21" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="n">
+        <v>15.1</v>
+      </c>
       <c r="V21" t="inlineStr"/>
       <c r="W21" s="1" t="n">
         <v>156.9</v>
@@ -2117,7 +2157,9 @@
       <c r="T22" s="2" t="n">
         <v>19.4</v>
       </c>
-      <c r="U22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V22" t="inlineStr"/>
       <c r="W22" s="1" t="n">
         <v>157.6</v>
@@ -2190,7 +2232,9 @@
       <c r="T23" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="n">
+        <v>20.5</v>
+      </c>
       <c r="V23" t="inlineStr"/>
       <c r="W23" s="2" t="n">
         <v>153.4</v>
@@ -2267,7 +2311,9 @@
       <c r="T24" s="2" t="n">
         <v>21.1</v>
       </c>
-      <c r="U24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="n">
+        <v>19.5</v>
+      </c>
       <c r="V24" t="inlineStr"/>
       <c r="W24" s="2" t="n">
         <v>149.3</v>
@@ -2344,7 +2390,9 @@
       <c r="T25" s="2" t="n">
         <v>19.6</v>
       </c>
-      <c r="U25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="n">
+        <v>18.7</v>
+      </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" s="1" t="n">
         <v>157.9</v>
@@ -2417,7 +2465,9 @@
       <c r="T26" s="2" t="n">
         <v>22.8</v>
       </c>
-      <c r="U26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="n">
+        <v>21.8</v>
+      </c>
       <c r="V26" t="inlineStr"/>
       <c r="W26" s="2" t="n">
         <v>154.3</v>
@@ -2490,7 +2540,9 @@
       <c r="T27" s="2" t="n">
         <v>23.5</v>
       </c>
-      <c r="U27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="n">
+        <v>24.6</v>
+      </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" s="2" t="n">
         <v>151.4</v>
@@ -2563,7 +2615,9 @@
       <c r="T28" s="2" t="n">
         <v>21.9</v>
       </c>
-      <c r="U28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V28" t="inlineStr"/>
       <c r="W28" s="2" t="n">
         <v>138.9</v>
@@ -2640,7 +2694,9 @@
       <c r="T29" s="2" t="n">
         <v>24.9</v>
       </c>
-      <c r="U29" s="2" t="inlineStr"/>
+      <c r="U29" s="3" t="n">
+        <v>31.1</v>
+      </c>
       <c r="V29" t="inlineStr"/>
       <c r="W29" s="2" t="n">
         <v>137.6</v>
@@ -2713,7 +2769,9 @@
       <c r="T30" s="2" t="n">
         <v>23.4</v>
       </c>
-      <c r="U30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="n">
+        <v>24.7</v>
+      </c>
       <c r="V30" t="inlineStr"/>
       <c r="W30" s="2" t="n">
         <v>139.9</v>
@@ -2790,8 +2848,14 @@
       <c r="T31" s="3" t="n">
         <v>27.9</v>
       </c>
-      <c r="U31" s="2" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
+      <c r="U31" s="3" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W31" s="2" t="n">
         <v>146</v>
       </c>
@@ -2863,8 +2927,14 @@
       <c r="T32" s="3" t="n">
         <v>26.9</v>
       </c>
-      <c r="U32" s="2" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
+      <c r="U32" s="3" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W32" s="2" t="n">
         <v>132.8</v>
       </c>
@@ -2936,7 +3006,9 @@
       <c r="T33" s="2" t="n">
         <v>24.2</v>
       </c>
-      <c r="U33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="n">
+        <v>23.2</v>
+      </c>
       <c r="V33" t="inlineStr"/>
       <c r="W33" s="2" t="n">
         <v>128.7</v>
@@ -3013,7 +3085,9 @@
       <c r="T34" s="2" t="n">
         <v>24.7</v>
       </c>
-      <c r="U34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="n">
+        <v>23.4</v>
+      </c>
       <c r="V34" t="inlineStr"/>
       <c r="W34" s="2" t="n">
         <v>128.9</v>
@@ -3086,7 +3160,9 @@
       <c r="T35" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="U35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="n">
+        <v>21.4</v>
+      </c>
       <c r="V35" t="inlineStr"/>
       <c r="W35" s="2" t="n">
         <v>130.3</v>
@@ -3159,7 +3235,9 @@
       <c r="T36" s="2" t="n">
         <v>20.5</v>
       </c>
-      <c r="U36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="n">
+        <v>16.4</v>
+      </c>
       <c r="V36" t="inlineStr"/>
       <c r="W36" s="2" t="n">
         <v>133.9</v>
@@ -3232,7 +3310,9 @@
       <c r="T37" s="2" t="n">
         <v>21.7</v>
       </c>
-      <c r="U37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V37" t="inlineStr"/>
       <c r="W37" s="2" t="n">
         <v>136.8</v>
@@ -3305,7 +3385,9 @@
       <c r="T38" s="2" t="n">
         <v>19.9</v>
       </c>
-      <c r="U38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="n">
+        <v>18.5</v>
+      </c>
       <c r="V38" t="inlineStr"/>
       <c r="W38" s="2" t="n">
         <v>136.4</v>
@@ -3378,7 +3460,9 @@
       <c r="T39" s="2" t="n">
         <v>19.8</v>
       </c>
-      <c r="U39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="n">
+        <v>18.6</v>
+      </c>
       <c r="V39" t="inlineStr"/>
       <c r="W39" s="2" t="n">
         <v>140.8</v>
@@ -3451,7 +3535,9 @@
       <c r="T40" s="2" t="n">
         <v>19.3</v>
       </c>
-      <c r="U40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V40" t="inlineStr"/>
       <c r="W40" s="2" t="n">
         <v>141.7</v>
@@ -3524,7 +3610,9 @@
       <c r="T41" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="n">
+        <v>13</v>
+      </c>
       <c r="V41" t="inlineStr"/>
       <c r="W41" s="2" t="n">
         <v>144</v>
@@ -3597,7 +3685,9 @@
       <c r="T42" s="2" t="n">
         <v>17.1</v>
       </c>
-      <c r="U42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="n">
+        <v>12.2</v>
+      </c>
       <c r="V42" t="inlineStr"/>
       <c r="W42" s="2" t="n">
         <v>148.7</v>
@@ -3670,7 +3760,9 @@
       <c r="T43" s="2" t="n">
         <v>18.3</v>
       </c>
-      <c r="U43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V43" t="inlineStr"/>
       <c r="W43" s="2" t="n">
         <v>144.8</v>
@@ -3743,7 +3835,9 @@
       <c r="T44" s="2" t="n">
         <v>18.7</v>
       </c>
-      <c r="U44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="n">
+        <v>17.1</v>
+      </c>
       <c r="V44" t="inlineStr"/>
       <c r="W44" s="2" t="n">
         <v>140.9</v>
@@ -3820,7 +3914,9 @@
       <c r="T45" s="2" t="n">
         <v>21.6</v>
       </c>
-      <c r="U45" s="2" t="inlineStr"/>
+      <c r="U45" s="3" t="n">
+        <v>25.4</v>
+      </c>
       <c r="V45" t="inlineStr"/>
       <c r="W45" s="2" t="n">
         <v>139</v>
@@ -3893,7 +3989,9 @@
       <c r="T46" s="2" t="n">
         <v>22.3</v>
       </c>
-      <c r="U46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="n">
+        <v>21.8</v>
+      </c>
       <c r="V46" t="inlineStr"/>
       <c r="W46" s="2" t="n">
         <v>148.6</v>
@@ -3966,7 +4064,9 @@
       <c r="T47" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="U47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="n">
+        <v>20.1</v>
+      </c>
       <c r="V47" t="inlineStr"/>
       <c r="W47" s="2" t="n">
         <v>143</v>
@@ -4039,7 +4139,9 @@
       <c r="T48" s="2" t="n">
         <v>21.5</v>
       </c>
-      <c r="U48" s="2" t="inlineStr"/>
+      <c r="U48" s="3" t="n">
+        <v>26.7</v>
+      </c>
       <c r="V48" t="inlineStr"/>
       <c r="W48" s="2" t="n">
         <v>144.3</v>
@@ -4112,8 +4214,14 @@
       <c r="T49" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="U49" s="2" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
+      <c r="U49" s="3" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="V49" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W49" s="2" t="n">
         <v>139.2</v>
       </c>
@@ -4189,8 +4297,14 @@
       <c r="T50" s="3" t="n">
         <v>45.3</v>
       </c>
-      <c r="U50" s="2" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
+      <c r="U50" s="3" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="V50" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W50" s="2" t="n">
         <v>136.5</v>
       </c>
@@ -4266,8 +4380,14 @@
       <c r="T51" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="U51" s="2" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
+      <c r="U51" s="3" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="V51" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W51" s="2" t="n">
         <v>133.8</v>
       </c>
@@ -4343,8 +4463,14 @@
       <c r="T52" s="3" t="n">
         <v>52.3</v>
       </c>
-      <c r="U52" s="2" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
+      <c r="U52" s="3" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="V52" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W52" s="2" t="n">
         <v>135.7</v>
       </c>
@@ -4416,8 +4542,14 @@
       <c r="T53" s="3" t="n">
         <v>33.6</v>
       </c>
-      <c r="U53" s="2" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
+      <c r="U53" s="3" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="V53" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W53" s="2" t="n">
         <v>142.2</v>
       </c>
@@ -4489,8 +4621,14 @@
       <c r="T54" s="3" t="n">
         <v>40.7</v>
       </c>
-      <c r="U54" s="2" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
+      <c r="U54" s="3" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="V54" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W54" s="2" t="n">
         <v>127.5</v>
       </c>
@@ -4562,8 +4700,14 @@
       <c r="T55" s="3" t="n">
         <v>37.6</v>
       </c>
-      <c r="U55" s="2" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
+      <c r="U55" s="3" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="V55" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W55" s="2" t="n">
         <v>128.6</v>
       </c>
@@ -4635,7 +4779,9 @@
       <c r="T56" s="3" t="n">
         <v>30.9</v>
       </c>
-      <c r="U56" s="2" t="inlineStr"/>
+      <c r="U56" s="3" t="n">
+        <v>28.5</v>
+      </c>
       <c r="V56" t="inlineStr"/>
       <c r="W56" s="2" t="n">
         <v>135.7</v>
@@ -4708,7 +4854,9 @@
       <c r="T57" s="3" t="n">
         <v>30.1</v>
       </c>
-      <c r="U57" s="2" t="inlineStr"/>
+      <c r="U57" s="3" t="n">
+        <v>26</v>
+      </c>
       <c r="V57" t="inlineStr"/>
       <c r="W57" s="2" t="n">
         <v>135.8</v>
@@ -4781,8 +4929,14 @@
       <c r="T58" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="U58" s="2" t="inlineStr"/>
-      <c r="V58" t="inlineStr"/>
+      <c r="U58" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="V58" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W58" s="2" t="n">
         <v>131.3</v>
       </c>
@@ -4854,8 +5008,14 @@
       <c r="T59" s="3" t="n">
         <v>29.6</v>
       </c>
-      <c r="U59" s="2" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
+      <c r="U59" s="3" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="V59" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W59" s="2" t="n">
         <v>130</v>
       </c>
@@ -4927,7 +5087,9 @@
       <c r="T60" s="3" t="n">
         <v>33.8</v>
       </c>
-      <c r="U60" s="2" t="inlineStr"/>
+      <c r="U60" s="3" t="n">
+        <v>30.6</v>
+      </c>
       <c r="V60" t="inlineStr"/>
       <c r="W60" s="3" t="n">
         <v>125.8</v>
@@ -5000,7 +5162,9 @@
       <c r="T61" s="3" t="n">
         <v>30.6</v>
       </c>
-      <c r="U61" s="2" t="inlineStr"/>
+      <c r="U61" s="3" t="n">
+        <v>29.1</v>
+      </c>
       <c r="V61" t="inlineStr"/>
       <c r="W61" s="3" t="n">
         <v>125.9</v>
@@ -5073,8 +5237,14 @@
       <c r="T62" s="3" t="n">
         <v>28.5</v>
       </c>
-      <c r="U62" s="2" t="inlineStr"/>
-      <c r="V62" t="inlineStr"/>
+      <c r="U62" s="3" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="V62" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W62" s="3" t="n">
         <v>126.7</v>
       </c>
@@ -5146,7 +5316,9 @@
       <c r="T63" s="3" t="n">
         <v>26.5</v>
       </c>
-      <c r="U63" s="2" t="inlineStr"/>
+      <c r="U63" s="3" t="n">
+        <v>25.7</v>
+      </c>
       <c r="V63" t="inlineStr"/>
       <c r="W63" s="2" t="n">
         <v>129</v>
@@ -5219,7 +5391,9 @@
       <c r="T64" s="2" t="n">
         <v>24.8</v>
       </c>
-      <c r="U64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="n">
+        <v>23.6</v>
+      </c>
       <c r="V64" t="inlineStr"/>
       <c r="W64" s="2" t="n">
         <v>132.4</v>
@@ -5292,7 +5466,9 @@
       <c r="T65" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="U65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="n">
+        <v>21.4</v>
+      </c>
       <c r="V65" t="inlineStr"/>
       <c r="W65" s="2" t="n">
         <v>131.3</v>
@@ -5365,7 +5541,9 @@
       <c r="T66" s="2" t="n">
         <v>24.2</v>
       </c>
-      <c r="U66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V66" t="inlineStr"/>
       <c r="W66" s="2" t="n">
         <v>134.3</v>
@@ -5438,7 +5616,9 @@
       <c r="T67" s="2" t="n">
         <v>24.7</v>
       </c>
-      <c r="U67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="n">
+        <v>22.9</v>
+      </c>
       <c r="V67" t="inlineStr"/>
       <c r="W67" s="2" t="n">
         <v>132.7</v>
@@ -5511,7 +5691,9 @@
       <c r="T68" s="2" t="n">
         <v>24.6</v>
       </c>
-      <c r="U68" s="2" t="inlineStr"/>
+      <c r="U68" s="3" t="n">
+        <v>27.5</v>
+      </c>
       <c r="V68" t="inlineStr"/>
       <c r="W68" s="2" t="n">
         <v>134.1</v>
@@ -5584,7 +5766,9 @@
       <c r="T69" s="2" t="n">
         <v>22.7</v>
       </c>
-      <c r="U69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="n">
+        <v>20</v>
+      </c>
       <c r="V69" t="inlineStr"/>
       <c r="W69" s="2" t="n">
         <v>134.8</v>
@@ -5657,7 +5841,9 @@
       <c r="T70" s="2" t="n">
         <v>23.6</v>
       </c>
-      <c r="U70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V70" t="inlineStr"/>
       <c r="W70" s="2" t="n">
         <v>134.1</v>
@@ -5730,7 +5916,9 @@
       <c r="T71" s="2" t="n">
         <v>24.8</v>
       </c>
-      <c r="U71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="n">
+        <v>22.2</v>
+      </c>
       <c r="V71" t="inlineStr"/>
       <c r="W71" s="2" t="n">
         <v>133.2</v>
@@ -5803,7 +5991,9 @@
       <c r="T72" s="2" t="n">
         <v>23.5</v>
       </c>
-      <c r="U72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="n">
+        <v>19.8</v>
+      </c>
       <c r="V72" t="inlineStr"/>
       <c r="W72" s="2" t="n">
         <v>132.2</v>
@@ -5876,7 +6066,9 @@
       <c r="T73" s="2" t="n">
         <v>22.5</v>
       </c>
-      <c r="U73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="n">
+        <v>18.1</v>
+      </c>
       <c r="V73" t="inlineStr"/>
       <c r="W73" s="2" t="n">
         <v>131.5</v>
@@ -5949,7 +6141,9 @@
       <c r="T74" s="2" t="n">
         <v>21.9</v>
       </c>
-      <c r="U74" s="2" t="inlineStr"/>
+      <c r="U74" s="3" t="n">
+        <v>26.9</v>
+      </c>
       <c r="V74" t="inlineStr"/>
       <c r="W74" s="2" t="n">
         <v>128.4</v>
@@ -6022,7 +6216,9 @@
       <c r="T75" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="n">
+        <v>18.7</v>
+      </c>
       <c r="V75" t="inlineStr"/>
       <c r="W75" s="2" t="n">
         <v>137.7</v>
@@ -6095,7 +6291,9 @@
       <c r="T76" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="n">
+        <v>15.4</v>
+      </c>
       <c r="V76" t="inlineStr"/>
       <c r="W76" s="2" t="n">
         <v>140.5</v>
@@ -6168,7 +6366,9 @@
       <c r="T77" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="n">
+        <v>15.2</v>
+      </c>
       <c r="V77" t="inlineStr"/>
       <c r="W77" s="2" t="n">
         <v>138.9</v>
@@ -6241,7 +6441,9 @@
       <c r="T78" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="n">
+        <v>15.1</v>
+      </c>
       <c r="V78" t="inlineStr"/>
       <c r="W78" s="2" t="n">
         <v>140.9</v>
@@ -6314,7 +6516,9 @@
       <c r="T79" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="n">
+        <v>13.4</v>
+      </c>
       <c r="V79" t="inlineStr"/>
       <c r="W79" s="2" t="n">
         <v>136</v>
@@ -6387,7 +6591,9 @@
       <c r="T80" s="2" t="n">
         <v>18.1</v>
       </c>
-      <c r="U80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="n">
+        <v>13.5</v>
+      </c>
       <c r="V80" t="inlineStr"/>
       <c r="W80" s="2" t="n">
         <v>135.9</v>
@@ -6460,7 +6666,9 @@
       <c r="T81" s="2" t="n">
         <v>18.1</v>
       </c>
-      <c r="U81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V81" t="inlineStr"/>
       <c r="W81" s="2" t="n">
         <v>137.3</v>
@@ -6533,7 +6741,9 @@
       <c r="T82" s="2" t="n">
         <v>20.9</v>
       </c>
-      <c r="U82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="n">
+        <v>18.1</v>
+      </c>
       <c r="V82" t="inlineStr"/>
       <c r="W82" s="2" t="n">
         <v>137.3</v>
@@ -6606,7 +6816,9 @@
       <c r="T83" s="2" t="n">
         <v>20.3</v>
       </c>
-      <c r="U83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="n">
+        <v>16.5</v>
+      </c>
       <c r="V83" t="inlineStr"/>
       <c r="W83" s="2" t="n">
         <v>139</v>
@@ -6679,7 +6891,9 @@
       <c r="T84" s="2" t="n">
         <v>22.3</v>
       </c>
-      <c r="U84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="n">
+        <v>21.7</v>
+      </c>
       <c r="V84" t="inlineStr"/>
       <c r="W84" s="2" t="n">
         <v>139.3</v>
@@ -6752,7 +6966,9 @@
       <c r="T85" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V85" t="inlineStr"/>
       <c r="W85" s="2" t="n">
         <v>140.9</v>
@@ -6825,7 +7041,9 @@
       <c r="T86" s="2" t="n">
         <v>19.3</v>
       </c>
-      <c r="U86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="n">
+        <v>19.5</v>
+      </c>
       <c r="V86" t="inlineStr"/>
       <c r="W86" s="2" t="n">
         <v>137.6</v>
@@ -6898,7 +7116,9 @@
       <c r="T87" s="2" t="n">
         <v>19.2</v>
       </c>
-      <c r="U87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="n">
+        <v>17.4</v>
+      </c>
       <c r="V87" t="inlineStr"/>
       <c r="W87" s="2" t="n">
         <v>137.3</v>
@@ -6971,7 +7191,9 @@
       <c r="T88" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="n">
+        <v>17</v>
+      </c>
       <c r="V88" t="inlineStr"/>
       <c r="W88" s="2" t="n">
         <v>138.2</v>
@@ -7044,7 +7266,9 @@
       <c r="T89" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="n">
+        <v>13.3</v>
+      </c>
       <c r="V89" t="inlineStr"/>
       <c r="W89" s="2" t="n">
         <v>141</v>
@@ -7117,7 +7341,9 @@
       <c r="T90" s="2" t="n">
         <v>17.7</v>
       </c>
-      <c r="U90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V90" t="inlineStr"/>
       <c r="W90" s="2" t="n">
         <v>141.6</v>
@@ -7190,7 +7416,9 @@
       <c r="T91" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V91" t="inlineStr"/>
       <c r="W91" s="2" t="n">
         <v>137.5</v>
@@ -7263,7 +7491,9 @@
       <c r="T92" s="2" t="n">
         <v>18.5</v>
       </c>
-      <c r="U92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="n">
+        <v>19</v>
+      </c>
       <c r="V92" t="inlineStr"/>
       <c r="W92" s="2" t="n">
         <v>140.1</v>
@@ -7336,7 +7566,9 @@
       <c r="T93" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="n">
+        <v>14.3</v>
+      </c>
       <c r="V93" t="inlineStr"/>
       <c r="W93" s="2" t="n">
         <v>138.9</v>
@@ -7409,7 +7641,9 @@
       <c r="T94" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V94" t="inlineStr"/>
       <c r="W94" s="2" t="n">
         <v>139.2</v>
@@ -7482,7 +7716,9 @@
       <c r="T95" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="U95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="n">
+        <v>15.9</v>
+      </c>
       <c r="V95" t="inlineStr"/>
       <c r="W95" s="2" t="n">
         <v>141.2</v>
@@ -7555,7 +7791,9 @@
       <c r="T96" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="n">
+        <v>13.9</v>
+      </c>
       <c r="V96" t="inlineStr"/>
       <c r="W96" s="2" t="n">
         <v>141.4</v>
@@ -7628,7 +7866,9 @@
       <c r="T97" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V97" t="inlineStr"/>
       <c r="W97" s="2" t="n">
         <v>145.6</v>
@@ -7701,7 +7941,9 @@
       <c r="T98" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="U98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="n">
+        <v>21.7</v>
+      </c>
       <c r="V98" t="inlineStr"/>
       <c r="W98" s="2" t="n">
         <v>149.6</v>
@@ -7774,7 +8016,9 @@
       <c r="T99" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V99" t="inlineStr"/>
       <c r="W99" s="1" t="n">
         <v>156.6</v>
@@ -7847,7 +8091,9 @@
       <c r="T100" s="2" t="n">
         <v>21.6</v>
       </c>
-      <c r="U100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="n">
+        <v>21</v>
+      </c>
       <c r="V100" t="inlineStr"/>
       <c r="W100" s="2" t="n">
         <v>154.4</v>
@@ -7920,7 +8166,9 @@
       <c r="T101" s="2" t="n">
         <v>20.1</v>
       </c>
-      <c r="U101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V101" t="inlineStr"/>
       <c r="W101" s="2" t="n">
         <v>148.4</v>
@@ -7993,7 +8241,9 @@
       <c r="T102" s="2" t="n">
         <v>20.6</v>
       </c>
-      <c r="U102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="n">
+        <v>18.4</v>
+      </c>
       <c r="V102" t="inlineStr"/>
       <c r="W102" s="2" t="n">
         <v>149.2</v>
@@ -8066,7 +8316,9 @@
       <c r="T103" s="2" t="n">
         <v>19.8</v>
       </c>
-      <c r="U103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="n">
+        <v>13.4</v>
+      </c>
       <c r="V103" t="inlineStr"/>
       <c r="W103" s="2" t="n">
         <v>154.8</v>
@@ -8139,7 +8391,9 @@
       <c r="T104" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="n">
+        <v>11.2</v>
+      </c>
       <c r="V104" t="inlineStr"/>
       <c r="W104" s="1" t="n">
         <v>155</v>
@@ -8212,7 +8466,9 @@
       <c r="T105" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="n">
+        <v>10.4</v>
+      </c>
       <c r="V105" t="inlineStr"/>
       <c r="W105" s="2" t="n">
         <v>152.2</v>
@@ -8285,7 +8541,9 @@
       <c r="T106" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V106" t="inlineStr"/>
       <c r="W106" s="2" t="n">
         <v>147.5</v>
@@ -8358,7 +8616,9 @@
       <c r="T107" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="n">
+        <v>12.2</v>
+      </c>
       <c r="V107" t="inlineStr"/>
       <c r="W107" s="2" t="n">
         <v>143.4</v>
@@ -8431,7 +8691,9 @@
       <c r="T108" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U108" s="2" t="inlineStr"/>
+      <c r="U108" s="2" t="n">
+        <v>10.2</v>
+      </c>
       <c r="V108" t="inlineStr"/>
       <c r="W108" s="2" t="n">
         <v>139.6</v>
@@ -8504,7 +8766,9 @@
       <c r="T109" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U109" s="2" t="inlineStr"/>
+      <c r="U109" s="2" t="n">
+        <v>9.699999999999999</v>
+      </c>
       <c r="V109" t="inlineStr"/>
       <c r="W109" s="2" t="n">
         <v>140.1</v>
@@ -8577,7 +8841,9 @@
       <c r="T110" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U110" s="2" t="inlineStr"/>
+      <c r="U110" s="2" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V110" t="inlineStr"/>
       <c r="W110" s="2" t="n">
         <v>139.3</v>
@@ -8650,7 +8916,9 @@
       <c r="T111" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U111" s="2" t="inlineStr"/>
+      <c r="U111" s="2" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V111" t="inlineStr"/>
       <c r="W111" s="2" t="n">
         <v>141.4</v>
@@ -8723,7 +8991,9 @@
       <c r="T112" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U112" s="2" t="inlineStr"/>
+      <c r="U112" s="2" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V112" t="inlineStr"/>
       <c r="W112" s="2" t="n">
         <v>138</v>
@@ -8796,7 +9066,9 @@
       <c r="T113" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U113" s="2" t="inlineStr"/>
+      <c r="U113" s="2" t="n">
+        <v>10.5</v>
+      </c>
       <c r="V113" t="inlineStr"/>
       <c r="W113" s="2" t="n">
         <v>140.8</v>
@@ -8869,7 +9141,9 @@
       <c r="T114" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="U114" s="2" t="inlineStr"/>
+      <c r="U114" s="2" t="n">
+        <v>9.6</v>
+      </c>
       <c r="V114" t="inlineStr"/>
       <c r="W114" s="2" t="n">
         <v>141.8</v>
@@ -8942,7 +9216,9 @@
       <c r="T115" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U115" s="2" t="inlineStr"/>
+      <c r="U115" s="2" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V115" t="inlineStr"/>
       <c r="W115" s="2" t="n">
         <v>143.3</v>
@@ -9015,7 +9291,9 @@
       <c r="T116" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U116" s="2" t="inlineStr"/>
+      <c r="U116" s="2" t="n">
+        <v>12.5</v>
+      </c>
       <c r="V116" t="inlineStr"/>
       <c r="W116" s="2" t="n">
         <v>145</v>
@@ -9088,7 +9366,9 @@
       <c r="T117" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U117" s="2" t="inlineStr"/>
+      <c r="U117" s="2" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V117" t="inlineStr"/>
       <c r="W117" s="2" t="n">
         <v>147</v>
@@ -9161,7 +9441,9 @@
       <c r="T118" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U118" s="2" t="inlineStr"/>
+      <c r="U118" s="2" t="n">
+        <v>12.2</v>
+      </c>
       <c r="V118" t="inlineStr"/>
       <c r="W118" s="2" t="n">
         <v>143.7</v>
@@ -9234,7 +9516,9 @@
       <c r="T119" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U119" s="2" t="inlineStr"/>
+      <c r="U119" s="2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V119" t="inlineStr"/>
       <c r="W119" s="2" t="n">
         <v>146.7</v>
@@ -9307,7 +9591,9 @@
       <c r="T120" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U120" s="2" t="inlineStr"/>
+      <c r="U120" s="2" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V120" t="inlineStr"/>
       <c r="W120" s="2" t="n">
         <v>151.1</v>
@@ -9380,7 +9666,9 @@
       <c r="T121" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U121" s="2" t="inlineStr"/>
+      <c r="U121" s="2" t="n">
+        <v>9.9</v>
+      </c>
       <c r="V121" t="inlineStr"/>
       <c r="W121" s="2" t="n">
         <v>150.4</v>
@@ -9453,7 +9741,9 @@
       <c r="T122" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U122" s="2" t="inlineStr"/>
+      <c r="U122" s="2" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V122" t="inlineStr"/>
       <c r="W122" s="2" t="n">
         <v>154.8</v>
@@ -9526,7 +9816,9 @@
       <c r="T123" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U123" s="2" t="inlineStr"/>
+      <c r="U123" s="2" t="n">
+        <v>8.4</v>
+      </c>
       <c r="V123" t="inlineStr"/>
       <c r="W123" s="2" t="n">
         <v>153.4</v>
@@ -9599,7 +9891,9 @@
       <c r="T124" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U124" s="2" t="inlineStr"/>
+      <c r="U124" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="V124" t="inlineStr"/>
       <c r="W124" s="1" t="n">
         <v>159.3</v>
@@ -9672,7 +9966,9 @@
       <c r="T125" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U125" s="2" t="inlineStr"/>
+      <c r="U125" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="V125" t="inlineStr"/>
       <c r="W125" s="1" t="n">
         <v>159.4</v>
@@ -9745,7 +10041,9 @@
       <c r="T126" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U126" s="2" t="inlineStr"/>
+      <c r="U126" s="2" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V126" t="inlineStr"/>
       <c r="W126" s="2" t="n">
         <v>145.6</v>
@@ -9822,7 +10120,9 @@
       <c r="T127" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="U127" s="2" t="inlineStr"/>
+      <c r="U127" s="2" t="n">
+        <v>7.9</v>
+      </c>
       <c r="V127" t="inlineStr"/>
       <c r="W127" s="2" t="n">
         <v>147.6</v>
@@ -9895,7 +10195,9 @@
       <c r="T128" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U128" s="2" t="inlineStr"/>
+      <c r="U128" s="2" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V128" t="inlineStr"/>
       <c r="W128" s="2" t="n">
         <v>149.1</v>
@@ -9968,7 +10270,9 @@
       <c r="T129" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="U129" s="2" t="inlineStr"/>
+      <c r="U129" s="2" t="n">
+        <v>13.8</v>
+      </c>
       <c r="V129" t="inlineStr"/>
       <c r="W129" s="2" t="n">
         <v>154.1</v>
@@ -10045,7 +10349,9 @@
       <c r="T130" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U130" s="2" t="inlineStr"/>
+      <c r="U130" s="2" t="n">
+        <v>16.8</v>
+      </c>
       <c r="V130" t="inlineStr"/>
       <c r="W130" s="2" t="n">
         <v>152.3</v>
@@ -10118,7 +10424,9 @@
       <c r="T131" s="2" t="n">
         <v>20.4</v>
       </c>
-      <c r="U131" s="2" t="inlineStr"/>
+      <c r="U131" s="2" t="n">
+        <v>20</v>
+      </c>
       <c r="V131" t="inlineStr"/>
       <c r="W131" s="1" t="n">
         <v>155.5</v>
@@ -10191,7 +10499,9 @@
       <c r="T132" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U132" s="2" t="inlineStr"/>
+      <c r="U132" s="2" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V132" t="inlineStr"/>
       <c r="W132" s="1" t="n">
         <v>159.3</v>
@@ -10264,7 +10574,9 @@
       <c r="T133" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U133" s="2" t="inlineStr"/>
+      <c r="U133" s="2" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V133" t="inlineStr"/>
       <c r="W133" s="2" t="n">
         <v>149.9</v>
@@ -10337,7 +10649,9 @@
       <c r="T134" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U134" s="2" t="inlineStr"/>
+      <c r="U134" s="2" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V134" t="inlineStr"/>
       <c r="W134" s="2" t="n">
         <v>149.7</v>
@@ -10410,7 +10724,9 @@
       <c r="T135" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U135" s="2" t="inlineStr"/>
+      <c r="U135" s="2" t="n">
+        <v>12.5</v>
+      </c>
       <c r="V135" t="inlineStr"/>
       <c r="W135" s="2" t="n">
         <v>147</v>
@@ -10483,7 +10799,9 @@
       <c r="T136" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U136" s="2" t="inlineStr"/>
+      <c r="U136" s="2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V136" t="inlineStr"/>
       <c r="W136" s="2" t="n">
         <v>147.5</v>
@@ -10560,7 +10878,9 @@
       <c r="T137" s="2" t="n">
         <v>16.2</v>
       </c>
-      <c r="U137" s="2" t="inlineStr"/>
+      <c r="U137" s="2" t="n">
+        <v>15.9</v>
+      </c>
       <c r="V137" t="inlineStr"/>
       <c r="W137" s="2" t="n">
         <v>148.6</v>
@@ -10633,7 +10953,9 @@
       <c r="T138" s="2" t="n">
         <v>14.7</v>
       </c>
-      <c r="U138" s="2" t="inlineStr"/>
+      <c r="U138" s="2" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V138" t="inlineStr"/>
       <c r="W138" s="2" t="n">
         <v>151.4</v>
@@ -10706,7 +11028,9 @@
       <c r="T139" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="U139" s="2" t="inlineStr"/>
+      <c r="U139" s="2" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V139" t="inlineStr"/>
       <c r="W139" s="2" t="n">
         <v>153.1</v>
@@ -10779,7 +11103,9 @@
       <c r="T140" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U140" s="2" t="inlineStr"/>
+      <c r="U140" s="2" t="n">
+        <v>11.9</v>
+      </c>
       <c r="V140" t="inlineStr"/>
       <c r="W140" s="2" t="n">
         <v>150.6</v>
@@ -10856,7 +11182,9 @@
       <c r="T141" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U141" s="2" t="inlineStr"/>
+      <c r="U141" s="2" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V141" t="inlineStr"/>
       <c r="W141" s="2" t="n">
         <v>153.8</v>
@@ -10929,7 +11257,9 @@
       <c r="T142" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="U142" s="2" t="inlineStr"/>
+      <c r="U142" s="2" t="n">
+        <v>7.8</v>
+      </c>
       <c r="V142" t="inlineStr"/>
       <c r="W142" s="2" t="n">
         <v>153.9</v>
@@ -11002,7 +11332,9 @@
       <c r="T143" s="2" t="n">
         <v>15.6</v>
       </c>
-      <c r="U143" s="2" t="inlineStr"/>
+      <c r="U143" s="2" t="n">
+        <v>10.2</v>
+      </c>
       <c r="V143" t="inlineStr"/>
       <c r="W143" s="2" t="n">
         <v>153.2</v>
@@ -11075,7 +11407,9 @@
       <c r="T144" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U144" s="2" t="inlineStr"/>
+      <c r="U144" s="2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V144" t="inlineStr"/>
       <c r="W144" s="2" t="n">
         <v>144.6</v>
@@ -11152,7 +11486,9 @@
       <c r="T145" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U145" s="2" t="inlineStr"/>
+      <c r="U145" s="2" t="n">
+        <v>18.2</v>
+      </c>
       <c r="V145" t="inlineStr"/>
       <c r="W145" s="2" t="n">
         <v>144.3</v>
@@ -11225,7 +11561,9 @@
       <c r="T146" s="2" t="n">
         <v>14.2</v>
       </c>
-      <c r="U146" s="2" t="inlineStr"/>
+      <c r="U146" s="2" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V146" t="inlineStr"/>
       <c r="W146" s="2" t="n">
         <v>146.4</v>
@@ -11302,7 +11640,9 @@
       <c r="T147" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U147" s="2" t="inlineStr"/>
+      <c r="U147" s="2" t="n">
+        <v>8.1</v>
+      </c>
       <c r="V147" t="inlineStr"/>
       <c r="W147" s="2" t="n">
         <v>150</v>
@@ -11375,7 +11715,9 @@
       <c r="T148" s="2" t="n">
         <v>14.6</v>
       </c>
-      <c r="U148" s="2" t="inlineStr"/>
+      <c r="U148" s="2" t="n">
+        <v>7.8</v>
+      </c>
       <c r="V148" t="inlineStr"/>
       <c r="W148" s="1" t="n">
         <v>156.5</v>
@@ -11448,7 +11790,9 @@
       <c r="T149" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U149" s="2" t="inlineStr"/>
+      <c r="U149" s="2" t="n">
+        <v>15.1</v>
+      </c>
       <c r="V149" t="inlineStr"/>
       <c r="W149" s="2" t="n">
         <v>150.9</v>
@@ -11521,7 +11865,9 @@
       <c r="T150" s="2" t="n">
         <v>14.4</v>
       </c>
-      <c r="U150" s="2" t="inlineStr"/>
+      <c r="U150" s="2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V150" t="inlineStr"/>
       <c r="W150" s="2" t="n">
         <v>152.5</v>
@@ -11598,7 +11944,9 @@
       <c r="T151" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U151" s="2" t="inlineStr"/>
+      <c r="U151" s="2" t="n">
+        <v>11.6</v>
+      </c>
       <c r="V151" t="inlineStr"/>
       <c r="W151" s="2" t="n">
         <v>152.1</v>
@@ -11671,7 +12019,9 @@
       <c r="T152" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U152" s="2" t="inlineStr"/>
+      <c r="U152" s="2" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V152" t="inlineStr"/>
       <c r="W152" s="2" t="n">
         <v>151.5</v>
@@ -11744,7 +12094,9 @@
       <c r="T153" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U153" s="2" t="inlineStr"/>
+      <c r="U153" s="2" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V153" t="inlineStr"/>
       <c r="W153" s="2" t="n">
         <v>150.2</v>
@@ -11817,7 +12169,9 @@
       <c r="T154" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U154" s="2" t="inlineStr"/>
+      <c r="U154" s="2" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V154" t="inlineStr"/>
       <c r="W154" s="2" t="n">
         <v>154</v>
@@ -11890,7 +12244,9 @@
       <c r="T155" s="2" t="n">
         <v>15.2</v>
       </c>
-      <c r="U155" s="2" t="inlineStr"/>
+      <c r="U155" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="V155" t="inlineStr"/>
       <c r="W155" s="2" t="n">
         <v>148.2</v>
@@ -11963,7 +12319,9 @@
       <c r="T156" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U156" s="2" t="inlineStr"/>
+      <c r="U156" s="2" t="n">
+        <v>8.300000000000001</v>
+      </c>
       <c r="V156" t="inlineStr"/>
       <c r="W156" s="2" t="n">
         <v>148.8</v>
@@ -12036,7 +12394,9 @@
       <c r="T157" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="U157" s="2" t="inlineStr"/>
+      <c r="U157" s="2" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V157" t="inlineStr"/>
       <c r="W157" s="2" t="n">
         <v>150.9</v>
@@ -12109,7 +12469,9 @@
       <c r="T158" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U158" s="2" t="inlineStr"/>
+      <c r="U158" s="2" t="n">
+        <v>13.4</v>
+      </c>
       <c r="V158" t="inlineStr"/>
       <c r="W158" s="2" t="n">
         <v>151.9</v>
@@ -12182,7 +12544,9 @@
       <c r="T159" s="2" t="n">
         <v>14.7</v>
       </c>
-      <c r="U159" s="2" t="inlineStr"/>
+      <c r="U159" s="2" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V159" t="inlineStr"/>
       <c r="W159" s="2" t="n">
         <v>147.6</v>
@@ -12255,7 +12619,9 @@
       <c r="T160" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U160" s="2" t="inlineStr"/>
+      <c r="U160" s="2" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V160" t="inlineStr"/>
       <c r="W160" s="2" t="n">
         <v>149.5</v>
@@ -12328,7 +12694,9 @@
       <c r="T161" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U161" s="2" t="inlineStr"/>
+      <c r="U161" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="V161" t="inlineStr"/>
       <c r="W161" s="2" t="n">
         <v>152.1</v>
@@ -12401,7 +12769,9 @@
       <c r="T162" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U162" s="2" t="inlineStr"/>
+      <c r="U162" s="2" t="n">
+        <v>16.2</v>
+      </c>
       <c r="V162" t="inlineStr"/>
       <c r="W162" s="2" t="n">
         <v>148.2</v>
@@ -12474,7 +12844,9 @@
       <c r="T163" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U163" s="2" t="inlineStr"/>
+      <c r="U163" s="2" t="n">
+        <v>14.8</v>
+      </c>
       <c r="V163" t="inlineStr"/>
       <c r="W163" s="2" t="n">
         <v>146.4</v>
@@ -12547,7 +12919,9 @@
       <c r="T164" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U164" s="2" t="inlineStr"/>
+      <c r="U164" s="2" t="n">
+        <v>14.4</v>
+      </c>
       <c r="V164" t="inlineStr"/>
       <c r="W164" s="2" t="n">
         <v>148.2</v>
@@ -12620,7 +12994,9 @@
       <c r="T165" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U165" s="2" t="inlineStr"/>
+      <c r="U165" s="2" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V165" t="inlineStr"/>
       <c r="W165" s="2" t="n">
         <v>147</v>
@@ -12693,7 +13069,9 @@
       <c r="T166" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U166" s="2" t="inlineStr"/>
+      <c r="U166" s="2" t="n">
+        <v>9.1</v>
+      </c>
       <c r="V166" t="inlineStr"/>
       <c r="W166" s="2" t="n">
         <v>145.5</v>
@@ -12766,7 +13144,9 @@
       <c r="T167" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U167" s="2" t="inlineStr"/>
+      <c r="U167" s="2" t="n">
+        <v>9.699999999999999</v>
+      </c>
       <c r="V167" t="inlineStr"/>
       <c r="W167" s="2" t="n">
         <v>146.5</v>
@@ -12839,7 +13219,9 @@
       <c r="T168" s="2" t="n">
         <v>16.2</v>
       </c>
-      <c r="U168" s="2" t="inlineStr"/>
+      <c r="U168" s="2" t="n">
+        <v>9.4</v>
+      </c>
       <c r="V168" t="inlineStr"/>
       <c r="W168" s="2" t="n">
         <v>145.9</v>
@@ -12912,7 +13294,9 @@
       <c r="T169" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U169" s="2" t="inlineStr"/>
+      <c r="U169" s="2" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V169" t="inlineStr"/>
       <c r="W169" s="2" t="n">
         <v>145.9</v>
@@ -12985,7 +13369,9 @@
       <c r="T170" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U170" s="2" t="inlineStr"/>
+      <c r="U170" s="2" t="n">
+        <v>10.3</v>
+      </c>
       <c r="V170" t="inlineStr"/>
       <c r="W170" s="2" t="n">
         <v>141.5</v>
@@ -13058,7 +13444,9 @@
       <c r="T171" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U171" s="2" t="inlineStr"/>
+      <c r="U171" s="2" t="n">
+        <v>10.2</v>
+      </c>
       <c r="V171" t="inlineStr"/>
       <c r="W171" s="2" t="n">
         <v>143</v>
@@ -13131,7 +13519,9 @@
       <c r="T172" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U172" s="2" t="inlineStr"/>
+      <c r="U172" s="2" t="n">
+        <v>12</v>
+      </c>
       <c r="V172" t="inlineStr"/>
       <c r="W172" s="2" t="n">
         <v>143.4</v>
@@ -13204,7 +13594,9 @@
       <c r="T173" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U173" s="2" t="inlineStr"/>
+      <c r="U173" s="2" t="n">
+        <v>10.3</v>
+      </c>
       <c r="V173" t="inlineStr"/>
       <c r="W173" s="2" t="n">
         <v>143.7</v>
@@ -13277,7 +13669,9 @@
       <c r="T174" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U174" s="2" t="inlineStr"/>
+      <c r="U174" s="2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V174" t="inlineStr"/>
       <c r="W174" s="2" t="n">
         <v>145.9</v>
@@ -13350,7 +13744,9 @@
       <c r="T175" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U175" s="2" t="inlineStr"/>
+      <c r="U175" s="2" t="n">
+        <v>11.9</v>
+      </c>
       <c r="V175" t="inlineStr"/>
       <c r="W175" s="2" t="n">
         <v>144.6</v>
@@ -13423,7 +13819,9 @@
       <c r="T176" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U176" s="2" t="inlineStr"/>
+      <c r="U176" s="2" t="n">
+        <v>8.4</v>
+      </c>
       <c r="V176" t="inlineStr"/>
       <c r="W176" s="2" t="n">
         <v>142.5</v>
@@ -13496,7 +13894,9 @@
       <c r="T177" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U177" s="2" t="inlineStr"/>
+      <c r="U177" s="2" t="n">
+        <v>11.3</v>
+      </c>
       <c r="V177" t="inlineStr"/>
       <c r="W177" s="2" t="n">
         <v>145.2</v>
@@ -13569,7 +13969,9 @@
       <c r="T178" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U178" s="2" t="inlineStr"/>
+      <c r="U178" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="V178" t="inlineStr"/>
       <c r="W178" s="2" t="n">
         <v>145.8</v>
@@ -13642,7 +14044,9 @@
       <c r="T179" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U179" s="2" t="inlineStr"/>
+      <c r="U179" s="2" t="n">
+        <v>11.3</v>
+      </c>
       <c r="V179" t="inlineStr"/>
       <c r="W179" s="2" t="n">
         <v>145.3</v>
@@ -13719,7 +14123,9 @@
       <c r="T180" s="2" t="n">
         <v>21.7</v>
       </c>
-      <c r="U180" s="2" t="inlineStr"/>
+      <c r="U180" s="3" t="n">
+        <v>25.7</v>
+      </c>
       <c r="V180" t="inlineStr"/>
       <c r="W180" s="2" t="n">
         <v>138.9</v>
@@ -13792,7 +14198,9 @@
       <c r="T181" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U181" s="2" t="inlineStr"/>
+      <c r="U181" s="2" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V181" t="inlineStr"/>
       <c r="W181" s="2" t="n">
         <v>142.8</v>
@@ -13865,7 +14273,9 @@
       <c r="T182" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="U182" s="2" t="inlineStr"/>
+      <c r="U182" s="2" t="n">
+        <v>17.7</v>
+      </c>
       <c r="V182" t="inlineStr"/>
       <c r="W182" s="2" t="n">
         <v>146.5</v>
@@ -13938,7 +14348,9 @@
       <c r="T183" s="2" t="n">
         <v>20.6</v>
       </c>
-      <c r="U183" s="2" t="inlineStr"/>
+      <c r="U183" s="2" t="n">
+        <v>17.1</v>
+      </c>
       <c r="V183" t="inlineStr"/>
       <c r="W183" s="2" t="n">
         <v>145</v>
@@ -14011,7 +14423,9 @@
       <c r="T184" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="U184" s="2" t="inlineStr"/>
+      <c r="U184" s="2" t="n">
+        <v>23.8</v>
+      </c>
       <c r="V184" t="inlineStr"/>
       <c r="W184" s="2" t="n">
         <v>147.1</v>
@@ -14084,7 +14498,9 @@
       <c r="T185" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="U185" s="2" t="inlineStr"/>
+      <c r="U185" s="2" t="n">
+        <v>17.9</v>
+      </c>
       <c r="V185" t="inlineStr"/>
       <c r="W185" s="2" t="n">
         <v>147.6</v>
@@ -14157,7 +14573,9 @@
       <c r="T186" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U186" s="2" t="inlineStr"/>
+      <c r="U186" s="2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V186" t="inlineStr"/>
       <c r="W186" s="2" t="n">
         <v>151.3</v>
@@ -14230,7 +14648,9 @@
       <c r="T187" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U187" s="2" t="inlineStr"/>
+      <c r="U187" s="2" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V187" t="inlineStr"/>
       <c r="W187" s="2" t="n">
         <v>149.9</v>
@@ -14303,7 +14723,9 @@
       <c r="T188" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U188" s="2" t="inlineStr"/>
+      <c r="U188" s="2" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V188" t="inlineStr"/>
       <c r="W188" s="2" t="n">
         <v>152.9</v>
@@ -14376,7 +14798,9 @@
       <c r="T189" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U189" s="2" t="inlineStr"/>
+      <c r="U189" s="2" t="n">
+        <v>13.8</v>
+      </c>
       <c r="V189" t="inlineStr"/>
       <c r="W189" s="2" t="n">
         <v>154.3</v>
@@ -14449,7 +14873,9 @@
       <c r="T190" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U190" s="2" t="inlineStr"/>
+      <c r="U190" s="2" t="n">
+        <v>14.5</v>
+      </c>
       <c r="V190" t="inlineStr"/>
       <c r="W190" s="2" t="n">
         <v>153.5</v>
@@ -14522,7 +14948,9 @@
       <c r="T191" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U191" s="2" t="inlineStr"/>
+      <c r="U191" s="2" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V191" t="inlineStr"/>
       <c r="W191" s="2" t="n">
         <v>148.5</v>
@@ -14595,7 +15023,9 @@
       <c r="T192" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U192" s="2" t="inlineStr"/>
+      <c r="U192" s="2" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V192" t="inlineStr"/>
       <c r="W192" s="2" t="n">
         <v>140.4</v>
@@ -14668,7 +15098,9 @@
       <c r="T193" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U193" s="2" t="inlineStr"/>
+      <c r="U193" s="2" t="n">
+        <v>15.2</v>
+      </c>
       <c r="V193" t="inlineStr"/>
       <c r="W193" s="2" t="n">
         <v>139.4</v>
@@ -14741,7 +15173,9 @@
       <c r="T194" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U194" s="2" t="inlineStr"/>
+      <c r="U194" s="2" t="n">
+        <v>14.2</v>
+      </c>
       <c r="V194" t="inlineStr"/>
       <c r="W194" s="2" t="n">
         <v>141.1</v>
@@ -14814,7 +15248,9 @@
       <c r="T195" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U195" s="2" t="inlineStr"/>
+      <c r="U195" s="2" t="n">
+        <v>13.8</v>
+      </c>
       <c r="V195" t="inlineStr"/>
       <c r="W195" s="2" t="n">
         <v>142.8</v>
@@ -14887,7 +15323,9 @@
       <c r="T196" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U196" s="2" t="inlineStr"/>
+      <c r="U196" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="V196" t="inlineStr"/>
       <c r="W196" s="2" t="n">
         <v>142</v>
@@ -14960,7 +15398,9 @@
       <c r="T197" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="U197" s="6" t="inlineStr"/>
+      <c r="U197" s="6" t="n">
+        <v>15.2</v>
+      </c>
       <c r="V197" s="4" t="inlineStr"/>
       <c r="W197" s="6" t="n">
         <v>144</v>
@@ -15033,7 +15473,9 @@
       <c r="T198" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U198" s="2" t="inlineStr"/>
+      <c r="U198" s="2" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V198" t="inlineStr"/>
       <c r="W198" s="2" t="n">
         <v>143.6</v>
@@ -15106,7 +15548,9 @@
       <c r="T199" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U199" s="2" t="inlineStr"/>
+      <c r="U199" s="2" t="n">
+        <v>15.9</v>
+      </c>
       <c r="V199" t="inlineStr"/>
       <c r="W199" s="2" t="n">
         <v>143.5</v>
@@ -15183,7 +15627,9 @@
       <c r="T200" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U200" s="2" t="inlineStr"/>
+      <c r="U200" s="2" t="n">
+        <v>16.8</v>
+      </c>
       <c r="V200" t="inlineStr"/>
       <c r="W200" s="2" t="n">
         <v>141.3</v>
@@ -15256,7 +15702,9 @@
       <c r="T201" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U201" s="2" t="inlineStr"/>
+      <c r="U201" s="2" t="n">
+        <v>11.2</v>
+      </c>
       <c r="V201" t="inlineStr"/>
       <c r="W201" s="2" t="n">
         <v>142.9</v>
@@ -15329,7 +15777,9 @@
       <c r="T202" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U202" s="2" t="inlineStr"/>
+      <c r="U202" s="2" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V202" t="inlineStr"/>
       <c r="W202" s="2" t="n">
         <v>143.4</v>
@@ -15402,7 +15852,9 @@
       <c r="T203" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U203" s="2" t="inlineStr"/>
+      <c r="U203" s="2" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V203" t="inlineStr"/>
       <c r="W203" s="2" t="n">
         <v>138.6</v>
@@ -15479,7 +15931,9 @@
       <c r="T204" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="U204" s="2" t="inlineStr"/>
+      <c r="U204" s="2" t="n">
+        <v>17</v>
+      </c>
       <c r="V204" t="inlineStr"/>
       <c r="W204" s="2" t="n">
         <v>142.5</v>
@@ -15552,7 +16006,9 @@
       <c r="T205" s="2" t="n">
         <v>19.8</v>
       </c>
-      <c r="U205" s="2" t="inlineStr"/>
+      <c r="U205" s="2" t="n">
+        <v>18.5</v>
+      </c>
       <c r="V205" t="inlineStr"/>
       <c r="W205" s="2" t="n">
         <v>137.9</v>
@@ -15625,7 +16081,9 @@
       <c r="T206" s="2" t="n">
         <v>22.4</v>
       </c>
-      <c r="U206" s="2" t="inlineStr"/>
+      <c r="U206" s="2" t="n">
+        <v>19.4</v>
+      </c>
       <c r="V206" t="inlineStr"/>
       <c r="W206" s="2" t="n">
         <v>140.9</v>
@@ -15698,7 +16156,9 @@
       <c r="T207" s="2" t="n">
         <v>24.7</v>
       </c>
-      <c r="U207" s="2" t="inlineStr"/>
+      <c r="U207" s="2" t="n">
+        <v>20.9</v>
+      </c>
       <c r="V207" t="inlineStr"/>
       <c r="W207" s="2" t="n">
         <v>143</v>
@@ -15771,7 +16231,9 @@
       <c r="T208" s="2" t="n">
         <v>23.7</v>
       </c>
-      <c r="U208" s="2" t="inlineStr"/>
+      <c r="U208" s="3" t="n">
+        <v>26.9</v>
+      </c>
       <c r="V208" t="inlineStr"/>
       <c r="W208" s="2" t="n">
         <v>143.1</v>
@@ -15844,8 +16306,14 @@
       <c r="T209" s="3" t="n">
         <v>26.4</v>
       </c>
-      <c r="U209" s="2" t="inlineStr"/>
-      <c r="V209" t="inlineStr"/>
+      <c r="U209" s="3" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="V209" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W209" s="2" t="n">
         <v>145</v>
       </c>
@@ -15917,7 +16385,9 @@
       <c r="T210" s="2" t="n">
         <v>23.4</v>
       </c>
-      <c r="U210" s="2" t="inlineStr"/>
+      <c r="U210" s="2" t="n">
+        <v>23.3</v>
+      </c>
       <c r="V210" t="inlineStr"/>
       <c r="W210" s="2" t="n">
         <v>148.3</v>
@@ -15990,7 +16460,9 @@
       <c r="T211" s="2" t="n">
         <v>20.5</v>
       </c>
-      <c r="U211" s="2" t="inlineStr"/>
+      <c r="U211" s="2" t="n">
+        <v>14.3</v>
+      </c>
       <c r="V211" t="inlineStr"/>
       <c r="W211" s="2" t="n">
         <v>148.6</v>
@@ -16063,7 +16535,9 @@
       <c r="T212" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U212" s="2" t="inlineStr"/>
+      <c r="U212" s="2" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V212" t="inlineStr"/>
       <c r="W212" s="2" t="n">
         <v>151.7</v>
@@ -16136,7 +16610,9 @@
       <c r="T213" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U213" s="2" t="inlineStr"/>
+      <c r="U213" s="2" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V213" t="inlineStr"/>
       <c r="W213" s="2" t="n">
         <v>145</v>
@@ -16209,7 +16685,9 @@
       <c r="T214" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U214" s="2" t="inlineStr"/>
+      <c r="U214" s="2" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V214" t="inlineStr"/>
       <c r="W214" s="2" t="n">
         <v>143</v>
@@ -16282,7 +16760,9 @@
       <c r="T215" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U215" s="2" t="inlineStr"/>
+      <c r="U215" s="2" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V215" t="inlineStr"/>
       <c r="W215" s="2" t="n">
         <v>144.9</v>
@@ -16355,7 +16835,9 @@
       <c r="T216" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U216" s="2" t="inlineStr"/>
+      <c r="U216" s="2" t="n">
+        <v>10.5</v>
+      </c>
       <c r="V216" t="inlineStr"/>
       <c r="W216" s="2" t="n">
         <v>144.9</v>
@@ -16428,7 +16910,9 @@
       <c r="T217" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U217" s="2" t="inlineStr"/>
+      <c r="U217" s="2" t="n">
+        <v>9.800000000000001</v>
+      </c>
       <c r="V217" t="inlineStr"/>
       <c r="W217" s="2" t="n">
         <v>149.2</v>
@@ -16505,7 +16989,9 @@
       <c r="T218" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U218" s="2" t="inlineStr"/>
+      <c r="U218" s="2" t="n">
+        <v>10.3</v>
+      </c>
       <c r="V218" t="inlineStr"/>
       <c r="W218" s="2" t="n">
         <v>148.9</v>
@@ -16578,7 +17064,9 @@
       <c r="T219" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U219" s="2" t="inlineStr"/>
+      <c r="U219" s="2" t="n">
+        <v>9.9</v>
+      </c>
       <c r="V219" t="inlineStr"/>
       <c r="W219" s="2" t="n">
         <v>148.8</v>
@@ -16651,7 +17139,9 @@
       <c r="T220" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U220" s="2" t="inlineStr"/>
+      <c r="U220" s="2" t="n">
+        <v>9.4</v>
+      </c>
       <c r="V220" t="inlineStr"/>
       <c r="W220" s="2" t="n">
         <v>150.6</v>
@@ -16724,7 +17214,9 @@
       <c r="T221" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U221" s="2" t="inlineStr"/>
+      <c r="U221" s="2" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V221" t="inlineStr"/>
       <c r="W221" s="2" t="n">
         <v>150.3</v>
@@ -16797,7 +17289,9 @@
       <c r="T222" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U222" s="2" t="inlineStr"/>
+      <c r="U222" s="2" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V222" t="inlineStr"/>
       <c r="W222" s="2" t="n">
         <v>147.6</v>
@@ -16870,7 +17364,9 @@
       <c r="T223" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U223" s="2" t="inlineStr"/>
+      <c r="U223" s="2" t="n">
+        <v>10.7</v>
+      </c>
       <c r="V223" t="inlineStr"/>
       <c r="W223" s="2" t="n">
         <v>148.3</v>
@@ -16943,7 +17439,9 @@
       <c r="T224" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U224" s="2" t="inlineStr"/>
+      <c r="U224" s="2" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V224" t="inlineStr"/>
       <c r="W224" s="2" t="n">
         <v>153.6</v>
@@ -17016,7 +17514,9 @@
       <c r="T225" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U225" s="2" t="inlineStr"/>
+      <c r="U225" s="2" t="n">
+        <v>12.9</v>
+      </c>
       <c r="V225" t="inlineStr"/>
       <c r="W225" s="1" t="n">
         <v>161.9</v>
@@ -17093,7 +17593,9 @@
       <c r="T226" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U226" s="2" t="inlineStr"/>
+      <c r="U226" s="2" t="n">
+        <v>11.9</v>
+      </c>
       <c r="V226" t="inlineStr"/>
       <c r="W226" s="1" t="n">
         <v>157</v>
@@ -17170,7 +17672,9 @@
       <c r="T227" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U227" s="2" t="inlineStr"/>
+      <c r="U227" s="2" t="n">
+        <v>16.9</v>
+      </c>
       <c r="V227" t="inlineStr"/>
       <c r="W227" s="2" t="n">
         <v>153.5</v>
@@ -17243,7 +17747,9 @@
       <c r="T228" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U228" s="2" t="inlineStr"/>
+      <c r="U228" s="2" t="n">
+        <v>15.8</v>
+      </c>
       <c r="V228" t="inlineStr"/>
       <c r="W228" s="1" t="n">
         <v>155.4</v>
@@ -17316,7 +17822,9 @@
       <c r="T229" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U229" s="2" t="inlineStr"/>
+      <c r="U229" s="2" t="n">
+        <v>10.4</v>
+      </c>
       <c r="V229" t="inlineStr"/>
       <c r="W229" s="1" t="n">
         <v>155.9</v>
@@ -17389,7 +17897,9 @@
       <c r="T230" s="2" t="n">
         <v>14.1</v>
       </c>
-      <c r="U230" s="2" t="inlineStr"/>
+      <c r="U230" s="2" t="n">
+        <v>7.7</v>
+      </c>
       <c r="V230" t="inlineStr"/>
       <c r="W230" s="1" t="n">
         <v>159.9</v>
@@ -17462,7 +17972,9 @@
       <c r="T231" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="U231" s="2" t="inlineStr"/>
+      <c r="U231" s="2" t="n">
+        <v>7.6</v>
+      </c>
       <c r="V231" t="inlineStr"/>
       <c r="W231" s="1" t="n">
         <v>160.5</v>
@@ -17535,7 +18047,9 @@
       <c r="T232" s="2" t="n">
         <v>13.5</v>
       </c>
-      <c r="U232" s="2" t="inlineStr"/>
+      <c r="U232" s="2" t="n">
+        <v>7.4</v>
+      </c>
       <c r="V232" t="inlineStr"/>
       <c r="W232" s="1" t="n">
         <v>160.5</v>
@@ -17608,7 +18122,9 @@
       <c r="T233" s="2" t="n">
         <v>13.6</v>
       </c>
-      <c r="U233" s="2" t="inlineStr"/>
+      <c r="U233" s="2" t="n">
+        <v>7.7</v>
+      </c>
       <c r="V233" t="inlineStr"/>
       <c r="W233" s="2" t="n">
         <v>151.4</v>
@@ -17681,7 +18197,9 @@
       <c r="T234" s="2" t="n">
         <v>14.2</v>
       </c>
-      <c r="U234" s="2" t="inlineStr"/>
+      <c r="U234" s="2" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="V234" t="inlineStr"/>
       <c r="W234" s="2" t="n">
         <v>150.5</v>
@@ -17754,7 +18272,9 @@
       <c r="T235" s="2" t="n">
         <v>14.3</v>
       </c>
-      <c r="U235" s="2" t="inlineStr"/>
+      <c r="U235" s="2" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V235" t="inlineStr"/>
       <c r="W235" s="2" t="n">
         <v>148.3</v>
@@ -17827,7 +18347,9 @@
       <c r="T236" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U236" s="2" t="inlineStr"/>
+      <c r="U236" s="2" t="n">
+        <v>10.7</v>
+      </c>
       <c r="V236" t="inlineStr"/>
       <c r="W236" s="2" t="n">
         <v>148.7</v>
@@ -17900,7 +18422,9 @@
       <c r="T237" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="U237" s="2" t="inlineStr"/>
+      <c r="U237" s="2" t="n">
+        <v>9.9</v>
+      </c>
       <c r="V237" t="inlineStr"/>
       <c r="W237" s="2" t="n">
         <v>141.9</v>
@@ -17973,7 +18497,9 @@
       <c r="T238" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U238" s="2" t="inlineStr"/>
+      <c r="U238" s="2" t="n">
+        <v>8.300000000000001</v>
+      </c>
       <c r="V238" t="inlineStr"/>
       <c r="W238" s="2" t="n">
         <v>142.4</v>
@@ -18046,7 +18572,9 @@
       <c r="T239" s="2" t="n">
         <v>14.8</v>
       </c>
-      <c r="U239" s="2" t="inlineStr"/>
+      <c r="U239" s="2" t="n">
+        <v>8</v>
+      </c>
       <c r="V239" t="inlineStr"/>
       <c r="W239" s="2" t="n">
         <v>146.2</v>
@@ -18119,7 +18647,9 @@
       <c r="T240" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U240" s="2" t="inlineStr"/>
+      <c r="U240" s="2" t="n">
+        <v>9.199999999999999</v>
+      </c>
       <c r="V240" t="inlineStr"/>
       <c r="W240" s="2" t="n">
         <v>143.6</v>
@@ -18192,7 +18722,9 @@
       <c r="T241" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U241" s="2" t="inlineStr"/>
+      <c r="U241" s="2" t="n">
+        <v>13.6</v>
+      </c>
       <c r="V241" t="inlineStr"/>
       <c r="W241" s="2" t="n">
         <v>147.1</v>
@@ -18265,7 +18797,9 @@
       <c r="T242" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="U242" s="2" t="inlineStr"/>
+      <c r="U242" s="2" t="n">
+        <v>8.5</v>
+      </c>
       <c r="V242" t="inlineStr"/>
       <c r="W242" s="2" t="n">
         <v>146</v>
@@ -18338,7 +18872,9 @@
       <c r="T243" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U243" s="2" t="inlineStr"/>
+      <c r="U243" s="2" t="n">
+        <v>9.6</v>
+      </c>
       <c r="V243" t="inlineStr"/>
       <c r="W243" s="2" t="n">
         <v>149.8</v>
@@ -18411,7 +18947,9 @@
       <c r="T244" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U244" s="2" t="inlineStr"/>
+      <c r="U244" s="2" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V244" t="inlineStr"/>
       <c r="W244" s="2" t="n">
         <v>151.6</v>
@@ -18484,7 +19022,9 @@
       <c r="T245" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U245" s="2" t="inlineStr"/>
+      <c r="U245" s="2" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V245" t="inlineStr"/>
       <c r="W245" s="2" t="n">
         <v>152.5</v>
@@ -18557,7 +19097,9 @@
       <c r="T246" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U246" s="2" t="inlineStr"/>
+      <c r="U246" s="2" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V246" t="inlineStr"/>
       <c r="W246" s="2" t="n">
         <v>151.6</v>
@@ -18630,7 +19172,9 @@
       <c r="T247" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="U247" s="2" t="inlineStr"/>
+      <c r="U247" s="2" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V247" t="inlineStr"/>
       <c r="W247" s="2" t="n">
         <v>153.6</v>
@@ -18703,7 +19247,9 @@
       <c r="T248" s="2" t="n">
         <v>20.1</v>
       </c>
-      <c r="U248" s="2" t="inlineStr"/>
+      <c r="U248" s="2" t="n">
+        <v>16.8</v>
+      </c>
       <c r="V248" t="inlineStr"/>
       <c r="W248" s="1" t="n">
         <v>155</v>
@@ -18776,7 +19322,9 @@
       <c r="T249" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U249" s="2" t="inlineStr"/>
+      <c r="U249" s="2" t="n">
+        <v>12.2</v>
+      </c>
       <c r="V249" t="inlineStr"/>
       <c r="W249" s="2" t="n">
         <v>144.4</v>
@@ -18849,7 +19397,9 @@
       <c r="T250" s="2" t="n">
         <v>15.6</v>
       </c>
-      <c r="U250" s="2" t="inlineStr"/>
+      <c r="U250" s="2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V250" t="inlineStr"/>
       <c r="W250" s="2" t="n">
         <v>141.3</v>
@@ -18922,7 +19472,9 @@
       <c r="T251" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U251" s="2" t="inlineStr"/>
+      <c r="U251" s="2" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V251" t="inlineStr"/>
       <c r="W251" s="2" t="n">
         <v>144</v>
@@ -18995,7 +19547,9 @@
       <c r="T252" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U252" s="2" t="inlineStr"/>
+      <c r="U252" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="V252" t="inlineStr"/>
       <c r="W252" s="2" t="n">
         <v>148.1</v>
@@ -19068,7 +19622,9 @@
       <c r="T253" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U253" s="2" t="inlineStr"/>
+      <c r="U253" s="2" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V253" t="inlineStr"/>
       <c r="W253" s="2" t="n">
         <v>147.2</v>
@@ -19141,7 +19697,9 @@
       <c r="T254" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U254" s="2" t="inlineStr"/>
+      <c r="U254" s="2" t="n">
+        <v>13.2</v>
+      </c>
       <c r="V254" t="inlineStr"/>
       <c r="W254" s="2" t="n">
         <v>145</v>
@@ -19214,7 +19772,9 @@
       <c r="T255" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U255" s="2" t="inlineStr"/>
+      <c r="U255" s="2" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V255" t="inlineStr"/>
       <c r="W255" s="2" t="n">
         <v>143.7</v>
@@ -19287,7 +19847,9 @@
       <c r="T256" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U256" s="2" t="inlineStr"/>
+      <c r="U256" s="2" t="n">
+        <v>16.4</v>
+      </c>
       <c r="V256" t="inlineStr"/>
       <c r="W256" s="2" t="n">
         <v>143.6</v>
@@ -19360,7 +19922,9 @@
       <c r="T257" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U257" s="2" t="inlineStr"/>
+      <c r="U257" s="2" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V257" t="inlineStr"/>
       <c r="W257" s="2" t="n">
         <v>146.6</v>
@@ -19433,7 +19997,9 @@
       <c r="T258" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U258" s="2" t="inlineStr"/>
+      <c r="U258" s="2" t="n">
+        <v>14.5</v>
+      </c>
       <c r="V258" t="inlineStr"/>
       <c r="W258" s="2" t="n">
         <v>143.9</v>
@@ -19506,7 +20072,9 @@
       <c r="T259" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U259" s="2" t="inlineStr"/>
+      <c r="U259" s="2" t="n">
+        <v>17.5</v>
+      </c>
       <c r="V259" t="inlineStr"/>
       <c r="W259" s="2" t="n">
         <v>143.2</v>
@@ -19579,7 +20147,9 @@
       <c r="T260" s="2" t="n">
         <v>21.8</v>
       </c>
-      <c r="U260" s="2" t="inlineStr"/>
+      <c r="U260" s="2" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V260" t="inlineStr"/>
       <c r="W260" s="2" t="n">
         <v>137.2</v>
@@ -19652,7 +20222,9 @@
       <c r="T261" s="2" t="n">
         <v>20.4</v>
       </c>
-      <c r="U261" s="2" t="inlineStr"/>
+      <c r="U261" s="2" t="n">
+        <v>15</v>
+      </c>
       <c r="V261" t="inlineStr"/>
       <c r="W261" s="2" t="n">
         <v>140.3</v>
@@ -19725,7 +20297,9 @@
       <c r="T262" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U262" s="2" t="inlineStr"/>
+      <c r="U262" s="2" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V262" t="inlineStr"/>
       <c r="W262" s="2" t="n">
         <v>145.2</v>
@@ -19798,7 +20372,9 @@
       <c r="T263" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U263" s="2" t="inlineStr"/>
+      <c r="U263" s="2" t="n">
+        <v>13.6</v>
+      </c>
       <c r="V263" t="inlineStr"/>
       <c r="W263" s="2" t="n">
         <v>145.7</v>
@@ -19871,7 +20447,9 @@
       <c r="T264" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U264" s="2" t="inlineStr"/>
+      <c r="U264" s="2" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V264" t="inlineStr"/>
       <c r="W264" s="2" t="n">
         <v>143.8</v>
@@ -19944,7 +20522,9 @@
       <c r="T265" s="2" t="n">
         <v>20.8</v>
       </c>
-      <c r="U265" s="2" t="inlineStr"/>
+      <c r="U265" s="2" t="n">
+        <v>21.5</v>
+      </c>
       <c r="V265" t="inlineStr"/>
       <c r="W265" s="2" t="n">
         <v>142.5</v>
@@ -20017,7 +20597,9 @@
       <c r="T266" s="2" t="n">
         <v>20.6</v>
       </c>
-      <c r="U266" s="2" t="inlineStr"/>
+      <c r="U266" s="2" t="n">
+        <v>22.4</v>
+      </c>
       <c r="V266" t="inlineStr"/>
       <c r="W266" s="2" t="n">
         <v>139.4</v>
@@ -20090,7 +20672,9 @@
       <c r="T267" s="2" t="n">
         <v>20.3</v>
       </c>
-      <c r="U267" s="2" t="inlineStr"/>
+      <c r="U267" s="2" t="n">
+        <v>16.2</v>
+      </c>
       <c r="V267" t="inlineStr"/>
       <c r="W267" s="2" t="n">
         <v>140.3</v>
@@ -20163,7 +20747,9 @@
       <c r="T268" s="2" t="n">
         <v>19.6</v>
       </c>
-      <c r="U268" s="2" t="inlineStr"/>
+      <c r="U268" s="2" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V268" t="inlineStr"/>
       <c r="W268" s="2" t="n">
         <v>139.2</v>
@@ -20236,7 +20822,9 @@
       <c r="T269" s="2" t="n">
         <v>20.2</v>
       </c>
-      <c r="U269" s="2" t="inlineStr"/>
+      <c r="U269" s="2" t="n">
+        <v>16.6</v>
+      </c>
       <c r="V269" t="inlineStr"/>
       <c r="W269" s="2" t="n">
         <v>141.2</v>
@@ -20309,7 +20897,9 @@
       <c r="T270" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U270" s="2" t="inlineStr"/>
+      <c r="U270" s="2" t="n">
+        <v>17.8</v>
+      </c>
       <c r="V270" t="inlineStr"/>
       <c r="W270" s="2" t="n">
         <v>145.5</v>
@@ -20382,7 +20972,9 @@
       <c r="T271" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="U271" s="2" t="inlineStr"/>
+      <c r="U271" s="2" t="n">
+        <v>15.1</v>
+      </c>
       <c r="V271" t="inlineStr"/>
       <c r="W271" s="2" t="n">
         <v>141.4</v>
@@ -20455,7 +21047,9 @@
       <c r="T272" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U272" s="2" t="inlineStr"/>
+      <c r="U272" s="2" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V272" t="inlineStr"/>
       <c r="W272" s="2" t="n">
         <v>141.9</v>
@@ -20528,7 +21122,9 @@
       <c r="T273" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U273" s="2" t="inlineStr"/>
+      <c r="U273" s="2" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V273" t="inlineStr"/>
       <c r="W273" s="2" t="n">
         <v>146.1</v>
@@ -20601,7 +21197,9 @@
       <c r="T274" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U274" s="2" t="inlineStr"/>
+      <c r="U274" s="2" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V274" t="inlineStr"/>
       <c r="W274" s="2" t="n">
         <v>146.6</v>
@@ -20674,7 +21272,9 @@
       <c r="T275" s="2" t="n">
         <v>19.9</v>
       </c>
-      <c r="U275" s="2" t="inlineStr"/>
+      <c r="U275" s="2" t="n">
+        <v>19</v>
+      </c>
       <c r="V275" t="inlineStr"/>
       <c r="W275" s="2" t="n">
         <v>146.7</v>
@@ -20747,7 +21347,9 @@
       <c r="T276" s="2" t="n">
         <v>21.4</v>
       </c>
-      <c r="U276" s="2" t="inlineStr"/>
+      <c r="U276" s="2" t="n">
+        <v>16.3</v>
+      </c>
       <c r="V276" t="inlineStr"/>
       <c r="W276" s="2" t="n">
         <v>151.8</v>
@@ -20824,7 +21426,9 @@
       <c r="T277" s="6" t="n">
         <v>23.6</v>
       </c>
-      <c r="U277" s="6" t="inlineStr"/>
+      <c r="U277" s="6" t="n">
+        <v>20.3</v>
+      </c>
       <c r="V277" s="4" t="inlineStr"/>
       <c r="W277" s="6" t="n">
         <v>152.8</v>
@@ -20897,7 +21501,9 @@
       <c r="T278" s="2" t="n">
         <v>21.1</v>
       </c>
-      <c r="U278" s="2" t="inlineStr"/>
+      <c r="U278" s="2" t="n">
+        <v>17.8</v>
+      </c>
       <c r="V278" t="inlineStr"/>
       <c r="W278" s="2" t="n">
         <v>152.9</v>
@@ -20970,7 +21576,9 @@
       <c r="T279" s="6" t="n">
         <v>23.8</v>
       </c>
-      <c r="U279" s="6" t="inlineStr"/>
+      <c r="U279" s="6" t="n">
+        <v>21.9</v>
+      </c>
       <c r="V279" s="4" t="inlineStr"/>
       <c r="W279" s="6" t="n">
         <v>153.9</v>
@@ -21043,8 +21651,14 @@
       <c r="T280" s="3" t="n">
         <v>29.5</v>
       </c>
-      <c r="U280" s="2" t="inlineStr"/>
-      <c r="V280" t="inlineStr"/>
+      <c r="U280" s="3" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="V280" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W280" s="2" t="n">
         <v>151.8</v>
       </c>
@@ -21116,7 +21730,9 @@
       <c r="T281" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="U281" s="2" t="inlineStr"/>
+      <c r="U281" s="2" t="n">
+        <v>22.7</v>
+      </c>
       <c r="V281" t="inlineStr"/>
       <c r="W281" s="1" t="n">
         <v>158</v>
@@ -21189,7 +21805,9 @@
       <c r="T282" s="2" t="n">
         <v>24.9</v>
       </c>
-      <c r="U282" s="2" t="inlineStr"/>
+      <c r="U282" s="2" t="n">
+        <v>21.3</v>
+      </c>
       <c r="V282" t="inlineStr"/>
       <c r="W282" s="2" t="n">
         <v>154.5</v>
@@ -21262,7 +21880,9 @@
       <c r="T283" s="2" t="n">
         <v>24.2</v>
       </c>
-      <c r="U283" s="2" t="inlineStr"/>
+      <c r="U283" s="2" t="n">
+        <v>19</v>
+      </c>
       <c r="V283" t="inlineStr"/>
       <c r="W283" s="2" t="n">
         <v>152.4</v>
@@ -21333,7 +21953,9 @@
       <c r="T284" s="7" t="n">
         <v>27.3</v>
       </c>
-      <c r="U284" s="6" t="inlineStr"/>
+      <c r="U284" s="6" t="n">
+        <v>24.2</v>
+      </c>
       <c r="V284" s="4" t="inlineStr"/>
       <c r="W284" s="6" t="n">
         <v>139.9</v>
@@ -21406,8 +22028,14 @@
       <c r="T285" s="3" t="n">
         <v>27.2</v>
       </c>
-      <c r="U285" s="2" t="inlineStr"/>
-      <c r="V285" t="inlineStr"/>
+      <c r="U285" s="3" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="V285" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W285" s="2" t="n">
         <v>137.8</v>
       </c>
@@ -21479,7 +22107,9 @@
       <c r="T286" s="2" t="n">
         <v>23.5</v>
       </c>
-      <c r="U286" s="2" t="inlineStr"/>
+      <c r="U286" s="2" t="n">
+        <v>17.4</v>
+      </c>
       <c r="V286" t="inlineStr"/>
       <c r="W286" s="2" t="n">
         <v>141.5</v>
@@ -21552,7 +22182,9 @@
       <c r="T287" s="2" t="n">
         <v>22.4</v>
       </c>
-      <c r="U287" s="2" t="inlineStr"/>
+      <c r="U287" s="2" t="n">
+        <v>17.5</v>
+      </c>
       <c r="V287" t="inlineStr"/>
       <c r="W287" s="2" t="n">
         <v>145</v>
@@ -21625,7 +22257,9 @@
       <c r="T288" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="U288" s="2" t="inlineStr"/>
+      <c r="U288" s="2" t="n">
+        <v>22.1</v>
+      </c>
       <c r="V288" t="inlineStr"/>
       <c r="W288" s="2" t="n">
         <v>136.5</v>
@@ -21698,7 +22332,9 @@
       <c r="T289" s="2" t="n">
         <v>24.1</v>
       </c>
-      <c r="U289" s="2" t="inlineStr"/>
+      <c r="U289" s="2" t="n">
+        <v>20.7</v>
+      </c>
       <c r="V289" t="inlineStr"/>
       <c r="W289" s="2" t="n">
         <v>138.3</v>
@@ -21775,8 +22411,14 @@
       <c r="T290" s="7" t="n">
         <v>26.8</v>
       </c>
-      <c r="U290" s="6" t="inlineStr"/>
-      <c r="V290" s="4" t="inlineStr"/>
+      <c r="U290" s="7" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="V290" s="7" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W290" s="6" t="n">
         <v>139.1</v>
       </c>
@@ -21848,7 +22490,9 @@
       <c r="T291" s="3" t="n">
         <v>26.1</v>
       </c>
-      <c r="U291" s="2" t="inlineStr"/>
+      <c r="U291" s="2" t="n">
+        <v>23.2</v>
+      </c>
       <c r="V291" t="inlineStr"/>
       <c r="W291" s="2" t="n">
         <v>142</v>
@@ -21925,7 +22569,9 @@
       <c r="T292" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="U292" s="2" t="inlineStr"/>
+      <c r="U292" s="2" t="n">
+        <v>20.7</v>
+      </c>
       <c r="V292" t="inlineStr"/>
       <c r="W292" s="2" t="n">
         <v>142.6</v>
@@ -21998,7 +22644,9 @@
       <c r="T293" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="U293" s="2" t="inlineStr"/>
+      <c r="U293" s="2" t="n">
+        <v>19.1</v>
+      </c>
       <c r="V293" t="inlineStr"/>
       <c r="W293" s="2" t="n">
         <v>140.9</v>
@@ -22071,7 +22719,9 @@
       <c r="T294" s="7" t="n">
         <v>27.4</v>
       </c>
-      <c r="U294" s="6" t="inlineStr"/>
+      <c r="U294" s="6" t="n">
+        <v>23.9</v>
+      </c>
       <c r="V294" s="4" t="inlineStr"/>
       <c r="W294" s="6" t="n">
         <v>144</v>
@@ -22144,8 +22794,14 @@
       <c r="T295" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="U295" s="2" t="inlineStr"/>
-      <c r="V295" t="inlineStr"/>
+      <c r="U295" s="3" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="V295" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W295" s="2" t="n">
         <v>139</v>
       </c>
@@ -22221,7 +22877,9 @@
       <c r="T296" s="3" t="n">
         <v>30.6</v>
       </c>
-      <c r="U296" s="2" t="inlineStr"/>
+      <c r="U296" s="2" t="n">
+        <v>23</v>
+      </c>
       <c r="V296" t="inlineStr"/>
       <c r="W296" s="2" t="n">
         <v>142.2</v>
@@ -22294,7 +22952,9 @@
       <c r="T297" s="3" t="n">
         <v>25.2</v>
       </c>
-      <c r="U297" s="2" t="inlineStr"/>
+      <c r="U297" s="2" t="n">
+        <v>19</v>
+      </c>
       <c r="V297" t="inlineStr"/>
       <c r="W297" s="2" t="n">
         <v>145.4</v>
@@ -22367,7 +23027,9 @@
       <c r="T298" s="2" t="n">
         <v>24.5</v>
       </c>
-      <c r="U298" s="2" t="inlineStr"/>
+      <c r="U298" s="2" t="n">
+        <v>23</v>
+      </c>
       <c r="V298" t="inlineStr"/>
       <c r="W298" s="2" t="n">
         <v>143.8</v>
@@ -22440,7 +23102,9 @@
       <c r="T299" s="2" t="n">
         <v>23.9</v>
       </c>
-      <c r="U299" s="2" t="inlineStr"/>
+      <c r="U299" s="3" t="n">
+        <v>27.6</v>
+      </c>
       <c r="V299" t="inlineStr"/>
       <c r="W299" s="2" t="n">
         <v>146.9</v>
@@ -22513,7 +23177,9 @@
       <c r="T300" s="2" t="n">
         <v>24.2</v>
       </c>
-      <c r="U300" s="2" t="inlineStr"/>
+      <c r="U300" s="2" t="n">
+        <v>18.1</v>
+      </c>
       <c r="V300" t="inlineStr"/>
       <c r="W300" s="2" t="n">
         <v>147.6</v>
@@ -22586,8 +23252,14 @@
       <c r="T301" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="U301" s="2" t="inlineStr"/>
-      <c r="V301" t="inlineStr"/>
+      <c r="U301" s="3" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="V301" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
       <c r="W301" s="2" t="n">
         <v>148.4</v>
       </c>
@@ -22659,7 +23331,9 @@
       <c r="T302" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="U302" s="2" t="inlineStr"/>
+      <c r="U302" s="2" t="n">
+        <v>16.5</v>
+      </c>
       <c r="V302" t="inlineStr"/>
       <c r="W302" s="2" t="n">
         <v>150.4</v>
@@ -22732,7 +23406,9 @@
       <c r="T303" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U303" s="2" t="inlineStr"/>
+      <c r="U303" s="2" t="n">
+        <v>14.1</v>
+      </c>
       <c r="V303" t="inlineStr"/>
       <c r="W303" s="2" t="n">
         <v>143.3</v>
@@ -22805,7 +23481,9 @@
       <c r="T304" s="2" t="n">
         <v>19.2</v>
       </c>
-      <c r="U304" s="2" t="inlineStr"/>
+      <c r="U304" s="2" t="n">
+        <v>19.1</v>
+      </c>
       <c r="V304" t="inlineStr"/>
       <c r="W304" s="2" t="n">
         <v>144.2</v>
@@ -22878,7 +23556,9 @@
       <c r="T305" s="2" t="n">
         <v>19.1</v>
       </c>
-      <c r="U305" s="2" t="inlineStr"/>
+      <c r="U305" s="2" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V305" t="inlineStr"/>
       <c r="W305" s="1" t="n">
         <v>156.9</v>
@@ -22951,7 +23631,9 @@
       <c r="T306" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U306" s="2" t="inlineStr"/>
+      <c r="U306" s="2" t="n">
+        <v>12.5</v>
+      </c>
       <c r="V306" t="inlineStr"/>
       <c r="W306" s="2" t="n">
         <v>149.9</v>
@@ -23024,7 +23706,9 @@
       <c r="T307" s="2" t="n">
         <v>18.2</v>
       </c>
-      <c r="U307" s="2" t="inlineStr"/>
+      <c r="U307" s="2" t="n">
+        <v>12.6</v>
+      </c>
       <c r="V307" t="inlineStr"/>
       <c r="W307" s="2" t="n">
         <v>139.2</v>
@@ -23097,7 +23781,9 @@
       <c r="T308" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U308" s="2" t="inlineStr"/>
+      <c r="U308" s="2" t="n">
+        <v>12</v>
+      </c>
       <c r="V308" t="inlineStr"/>
       <c r="W308" s="2" t="n">
         <v>140.7</v>
@@ -23170,7 +23856,9 @@
       <c r="T309" s="2" t="n">
         <v>17.5</v>
       </c>
-      <c r="U309" s="2" t="inlineStr"/>
+      <c r="U309" s="2" t="n">
+        <v>14.2</v>
+      </c>
       <c r="V309" t="inlineStr"/>
       <c r="W309" s="2" t="n">
         <v>141.8</v>
@@ -23243,7 +23931,9 @@
       <c r="T310" s="2" t="n">
         <v>18.9</v>
       </c>
-      <c r="U310" s="2" t="inlineStr"/>
+      <c r="U310" s="2" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V310" t="inlineStr"/>
       <c r="W310" s="2" t="n">
         <v>141.9</v>
@@ -23316,7 +24006,9 @@
       <c r="T311" s="2" t="n">
         <v>19.5</v>
       </c>
-      <c r="U311" s="2" t="inlineStr"/>
+      <c r="U311" s="2" t="n">
+        <v>16.2</v>
+      </c>
       <c r="V311" t="inlineStr"/>
       <c r="W311" s="2" t="n">
         <v>140.9</v>
@@ -23389,7 +24081,9 @@
       <c r="T312" s="2" t="n">
         <v>18.9</v>
       </c>
-      <c r="U312" s="2" t="inlineStr"/>
+      <c r="U312" s="2" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V312" t="inlineStr"/>
       <c r="W312" s="2" t="n">
         <v>140.8</v>
@@ -23462,7 +24156,9 @@
       <c r="T313" s="2" t="n">
         <v>19.3</v>
       </c>
-      <c r="U313" s="2" t="inlineStr"/>
+      <c r="U313" s="2" t="n">
+        <v>14.8</v>
+      </c>
       <c r="V313" t="inlineStr"/>
       <c r="W313" s="2" t="n">
         <v>139.6</v>
@@ -23535,7 +24231,9 @@
       <c r="T314" s="2" t="n">
         <v>18.7</v>
       </c>
-      <c r="U314" s="2" t="inlineStr"/>
+      <c r="U314" s="2" t="n">
+        <v>16.6</v>
+      </c>
       <c r="V314" t="inlineStr"/>
       <c r="W314" s="2" t="n">
         <v>139.1</v>
@@ -23608,7 +24306,9 @@
       <c r="T315" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="U315" s="2" t="inlineStr"/>
+      <c r="U315" s="2" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V315" t="inlineStr"/>
       <c r="W315" s="2" t="n">
         <v>139.6</v>
@@ -23681,7 +24381,9 @@
       <c r="T316" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U316" s="2" t="inlineStr"/>
+      <c r="U316" s="2" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V316" t="inlineStr"/>
       <c r="W316" s="2" t="n">
         <v>138.2</v>
@@ -23754,7 +24456,9 @@
       <c r="T317" s="2" t="n">
         <v>18.8</v>
       </c>
-      <c r="U317" s="2" t="inlineStr"/>
+      <c r="U317" s="2" t="n">
+        <v>18.1</v>
+      </c>
       <c r="V317" t="inlineStr"/>
       <c r="W317" s="2" t="n">
         <v>141.9</v>
@@ -23827,7 +24531,9 @@
       <c r="T318" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U318" s="2" t="inlineStr"/>
+      <c r="U318" s="2" t="n">
+        <v>11.6</v>
+      </c>
       <c r="V318" t="inlineStr"/>
       <c r="W318" s="2" t="n">
         <v>143.3</v>
@@ -23900,7 +24606,9 @@
       <c r="T319" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="U319" s="2" t="inlineStr"/>
+      <c r="U319" s="2" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V319" t="inlineStr"/>
       <c r="W319" s="2" t="n">
         <v>141.4</v>
@@ -23973,7 +24681,9 @@
       <c r="T320" s="2" t="n">
         <v>18.3</v>
       </c>
-      <c r="U320" s="2" t="inlineStr"/>
+      <c r="U320" s="2" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V320" t="inlineStr"/>
       <c r="W320" s="2" t="n">
         <v>141.7</v>
@@ -24046,7 +24756,9 @@
       <c r="T321" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U321" s="2" t="inlineStr"/>
+      <c r="U321" s="2" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V321" t="inlineStr"/>
       <c r="W321" s="2" t="n">
         <v>138.7</v>
@@ -24119,7 +24831,9 @@
       <c r="T322" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U322" s="2" t="inlineStr"/>
+      <c r="U322" s="2" t="n">
+        <v>11.7</v>
+      </c>
       <c r="V322" t="inlineStr"/>
       <c r="W322" s="2" t="n">
         <v>135.4</v>
@@ -24192,7 +24906,9 @@
       <c r="T323" s="2" t="n">
         <v>17.1</v>
       </c>
-      <c r="U323" s="2" t="inlineStr"/>
+      <c r="U323" s="2" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V323" t="inlineStr"/>
       <c r="W323" s="2" t="n">
         <v>136.1</v>
@@ -24265,7 +24981,9 @@
       <c r="T324" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U324" s="2" t="inlineStr"/>
+      <c r="U324" s="2" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V324" t="inlineStr"/>
       <c r="W324" s="2" t="n">
         <v>138.2</v>
@@ -24338,7 +25056,9 @@
       <c r="T325" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U325" s="2" t="inlineStr"/>
+      <c r="U325" s="2" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V325" t="inlineStr"/>
       <c r="W325" s="2" t="n">
         <v>140.2</v>
@@ -24411,7 +25131,9 @@
       <c r="T326" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="U326" s="6" t="inlineStr"/>
+      <c r="U326" s="6" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V326" s="4" t="inlineStr"/>
       <c r="W326" s="6" t="n">
         <v>139.4</v>
@@ -24484,7 +25206,9 @@
       <c r="T327" s="2" t="n">
         <v>17.9</v>
       </c>
-      <c r="U327" s="2" t="inlineStr"/>
+      <c r="U327" s="2" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V327" t="inlineStr"/>
       <c r="W327" s="2" t="n">
         <v>141.5</v>
@@ -24557,7 +25281,9 @@
       <c r="T328" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U328" s="2" t="inlineStr"/>
+      <c r="U328" s="2" t="n">
+        <v>11.8</v>
+      </c>
       <c r="V328" t="inlineStr"/>
       <c r="W328" s="2" t="n">
         <v>139.3</v>
@@ -24630,7 +25356,9 @@
       <c r="T329" s="6" t="n">
         <v>18.4</v>
       </c>
-      <c r="U329" s="6" t="inlineStr"/>
+      <c r="U329" s="6" t="n">
+        <v>16.8</v>
+      </c>
       <c r="V329" s="4" t="inlineStr"/>
       <c r="W329" s="6" t="n">
         <v>145.8</v>
@@ -24703,7 +25431,9 @@
       <c r="T330" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U330" s="2" t="inlineStr"/>
+      <c r="U330" s="2" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V330" t="inlineStr"/>
       <c r="W330" s="2" t="n">
         <v>138.4</v>
@@ -24780,7 +25510,9 @@
       <c r="T331" s="2" t="n">
         <v>18.1</v>
       </c>
-      <c r="U331" s="2" t="inlineStr"/>
+      <c r="U331" s="2" t="n">
+        <v>13.3</v>
+      </c>
       <c r="V331" t="inlineStr"/>
       <c r="W331" s="2" t="n">
         <v>135.5</v>
@@ -24853,7 +25585,9 @@
       <c r="T332" s="2" t="n">
         <v>17.4</v>
       </c>
-      <c r="U332" s="2" t="inlineStr"/>
+      <c r="U332" s="2" t="n">
+        <v>16.2</v>
+      </c>
       <c r="V332" t="inlineStr"/>
       <c r="W332" s="2" t="n">
         <v>132.3</v>
@@ -24926,7 +25660,9 @@
       <c r="T333" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="U333" s="2" t="inlineStr"/>
+      <c r="U333" s="2" t="n">
+        <v>14</v>
+      </c>
       <c r="V333" t="inlineStr"/>
       <c r="W333" s="2" t="n">
         <v>137</v>
@@ -24999,7 +25735,9 @@
       <c r="T334" s="2" t="n">
         <v>16.7</v>
       </c>
-      <c r="U334" s="2" t="inlineStr"/>
+      <c r="U334" s="2" t="n">
+        <v>17.4</v>
+      </c>
       <c r="V334" t="inlineStr"/>
       <c r="W334" s="2" t="n">
         <v>137.4</v>
@@ -25072,7 +25810,9 @@
       <c r="T335" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="U335" s="2" t="inlineStr"/>
+      <c r="U335" s="2" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V335" t="inlineStr"/>
       <c r="W335" s="2" t="n">
         <v>139</v>
@@ -25145,7 +25885,9 @@
       <c r="T336" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U336" s="2" t="inlineStr"/>
+      <c r="U336" s="2" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V336" t="inlineStr"/>
       <c r="W336" s="2" t="n">
         <v>138.6</v>
@@ -25218,7 +25960,9 @@
       <c r="T337" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U337" s="2" t="inlineStr"/>
+      <c r="U337" s="2" t="n">
+        <v>10.9</v>
+      </c>
       <c r="V337" t="inlineStr"/>
       <c r="W337" s="2" t="n">
         <v>139.5</v>
@@ -25291,7 +26035,9 @@
       <c r="T338" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U338" s="2" t="inlineStr"/>
+      <c r="U338" s="2" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V338" t="inlineStr"/>
       <c r="W338" s="2" t="n">
         <v>144.2</v>
@@ -25364,7 +26110,9 @@
       <c r="T339" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U339" s="2" t="inlineStr"/>
+      <c r="U339" s="2" t="n">
+        <v>9.6</v>
+      </c>
       <c r="V339" t="inlineStr"/>
       <c r="W339" s="2" t="n">
         <v>142.5</v>
@@ -25437,7 +26185,9 @@
       <c r="T340" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U340" s="2" t="inlineStr"/>
+      <c r="U340" s="2" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V340" t="inlineStr"/>
       <c r="W340" s="2" t="n">
         <v>143.2</v>
@@ -25510,7 +26260,9 @@
       <c r="T341" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U341" s="2" t="inlineStr"/>
+      <c r="U341" s="2" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V341" t="inlineStr"/>
       <c r="W341" s="2" t="n">
         <v>136.9</v>
@@ -25583,7 +26335,9 @@
       <c r="T342" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U342" s="2" t="inlineStr"/>
+      <c r="U342" s="2" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V342" t="inlineStr"/>
       <c r="W342" s="2" t="n">
         <v>142.1</v>
@@ -25660,7 +26414,9 @@
       <c r="T343" s="6" t="n">
         <v>21.5</v>
       </c>
-      <c r="U343" s="6" t="inlineStr"/>
+      <c r="U343" s="7" t="n">
+        <v>28.7</v>
+      </c>
       <c r="V343" s="4" t="inlineStr"/>
       <c r="W343" s="6" t="n">
         <v>152.2</v>
@@ -25733,7 +26489,9 @@
       <c r="T344" s="2" t="n">
         <v>18.9</v>
       </c>
-      <c r="U344" s="2" t="inlineStr"/>
+      <c r="U344" s="2" t="n">
+        <v>16</v>
+      </c>
       <c r="V344" t="inlineStr"/>
       <c r="W344" s="2" t="n">
         <v>145</v>
@@ -25806,7 +26564,9 @@
       <c r="T345" s="2" t="n">
         <v>19.9</v>
       </c>
-      <c r="U345" s="2" t="inlineStr"/>
+      <c r="U345" s="2" t="n">
+        <v>20.6</v>
+      </c>
       <c r="V345" t="inlineStr"/>
       <c r="W345" s="2" t="n">
         <v>142</v>
@@ -25879,7 +26639,9 @@
       <c r="T346" s="2" t="n">
         <v>22.2</v>
       </c>
-      <c r="U346" s="2" t="inlineStr"/>
+      <c r="U346" s="2" t="n">
+        <v>23.9</v>
+      </c>
       <c r="V346" t="inlineStr"/>
       <c r="W346" s="2" t="n">
         <v>143.1</v>
@@ -25952,7 +26714,9 @@
       <c r="T347" s="2" t="n">
         <v>19.4</v>
       </c>
-      <c r="U347" s="2" t="inlineStr"/>
+      <c r="U347" s="2" t="n">
+        <v>21.1</v>
+      </c>
       <c r="V347" t="inlineStr"/>
       <c r="W347" s="2" t="n">
         <v>143</v>
@@ -26025,7 +26789,9 @@
       <c r="T348" s="2" t="n">
         <v>17.7</v>
       </c>
-      <c r="U348" s="2" t="inlineStr"/>
+      <c r="U348" s="2" t="n">
+        <v>19.1</v>
+      </c>
       <c r="V348" t="inlineStr"/>
       <c r="W348" s="2" t="n">
         <v>142.6</v>
@@ -26098,7 +26864,9 @@
       <c r="T349" s="2" t="n">
         <v>16.2</v>
       </c>
-      <c r="U349" s="2" t="inlineStr"/>
+      <c r="U349" s="2" t="n">
+        <v>12.9</v>
+      </c>
       <c r="V349" t="inlineStr"/>
       <c r="W349" s="2" t="n">
         <v>144.3</v>
@@ -26171,7 +26939,9 @@
       <c r="T350" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U350" s="2" t="inlineStr"/>
+      <c r="U350" s="2" t="n">
+        <v>16.1</v>
+      </c>
       <c r="V350" t="inlineStr"/>
       <c r="W350" s="2" t="n">
         <v>142.7</v>
@@ -26248,7 +27018,9 @@
       <c r="T351" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U351" s="2" t="inlineStr"/>
+      <c r="U351" s="2" t="n">
+        <v>20.7</v>
+      </c>
       <c r="V351" t="inlineStr"/>
       <c r="W351" s="2" t="n">
         <v>142.6</v>
@@ -26321,7 +27093,9 @@
       <c r="T352" s="2" t="n">
         <v>16.4</v>
       </c>
-      <c r="U352" s="2" t="inlineStr"/>
+      <c r="U352" s="2" t="n">
+        <v>15.7</v>
+      </c>
       <c r="V352" t="inlineStr"/>
       <c r="W352" s="2" t="n">
         <v>146.7</v>
@@ -26394,7 +27168,9 @@
       <c r="T353" s="2" t="n">
         <v>17.3</v>
       </c>
-      <c r="U353" s="2" t="inlineStr"/>
+      <c r="U353" s="2" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V353" t="inlineStr"/>
       <c r="W353" s="2" t="n">
         <v>141.9</v>
@@ -26471,7 +27247,9 @@
       <c r="T354" s="6" t="n">
         <v>19.5</v>
       </c>
-      <c r="U354" s="6" t="inlineStr"/>
+      <c r="U354" s="6" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V354" s="4" t="inlineStr"/>
       <c r="W354" s="6" t="n">
         <v>143.1</v>
@@ -26544,7 +27322,9 @@
       <c r="T355" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U355" s="2" t="inlineStr"/>
+      <c r="U355" s="2" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V355" t="inlineStr"/>
       <c r="W355" s="2" t="n">
         <v>145.3</v>
@@ -26617,7 +27397,9 @@
       <c r="T356" s="2" t="n">
         <v>18.9</v>
       </c>
-      <c r="U356" s="2" t="inlineStr"/>
+      <c r="U356" s="2" t="n">
+        <v>16</v>
+      </c>
       <c r="V356" t="inlineStr"/>
       <c r="W356" s="2" t="n">
         <v>139.9</v>
@@ -26690,7 +27472,9 @@
       <c r="T357" s="2" t="n">
         <v>18.4</v>
       </c>
-      <c r="U357" s="2" t="inlineStr"/>
+      <c r="U357" s="2" t="n">
+        <v>17.6</v>
+      </c>
       <c r="V357" t="inlineStr"/>
       <c r="W357" s="2" t="n">
         <v>139.4</v>
@@ -26763,7 +27547,9 @@
       <c r="T358" s="2" t="n">
         <v>17.6</v>
       </c>
-      <c r="U358" s="2" t="inlineStr"/>
+      <c r="U358" s="2" t="n">
+        <v>13.6</v>
+      </c>
       <c r="V358" t="inlineStr"/>
       <c r="W358" s="2" t="n">
         <v>144.5</v>
@@ -26836,7 +27622,9 @@
       <c r="T359" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U359" s="2" t="inlineStr"/>
+      <c r="U359" s="2" t="n">
+        <v>11.6</v>
+      </c>
       <c r="V359" t="inlineStr"/>
       <c r="W359" s="2" t="n">
         <v>149.6</v>
@@ -26913,7 +27701,9 @@
       <c r="T360" s="6" t="n">
         <v>16.6</v>
       </c>
-      <c r="U360" s="6" t="inlineStr"/>
+      <c r="U360" s="6" t="n">
+        <v>13</v>
+      </c>
       <c r="V360" s="4" t="inlineStr"/>
       <c r="W360" s="6" t="n">
         <v>154.8</v>
@@ -26990,7 +27780,9 @@
       <c r="T361" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U361" s="2" t="inlineStr"/>
+      <c r="U361" s="2" t="n">
+        <v>13.2</v>
+      </c>
       <c r="V361" t="inlineStr"/>
       <c r="W361" s="2" t="n">
         <v>150</v>
@@ -27063,7 +27855,9 @@
       <c r="T362" s="2" t="n">
         <v>15.6</v>
       </c>
-      <c r="U362" s="2" t="inlineStr"/>
+      <c r="U362" s="2" t="n">
+        <v>8.699999999999999</v>
+      </c>
       <c r="V362" t="inlineStr"/>
       <c r="W362" s="2" t="n">
         <v>145.4</v>
@@ -27140,7 +27934,9 @@
       <c r="T363" s="2" t="n">
         <v>16.1</v>
       </c>
-      <c r="U363" s="2" t="inlineStr"/>
+      <c r="U363" s="2" t="n">
+        <v>10.7</v>
+      </c>
       <c r="V363" t="inlineStr"/>
       <c r="W363" s="2" t="n">
         <v>145.7</v>
@@ -27213,7 +28009,9 @@
       <c r="T364" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="U364" s="2" t="inlineStr"/>
+      <c r="U364" s="2" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V364" t="inlineStr"/>
       <c r="W364" s="2" t="n">
         <v>149.8</v>
@@ -27286,7 +28084,9 @@
       <c r="T365" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U365" s="2" t="inlineStr"/>
+      <c r="U365" s="2" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V365" t="inlineStr"/>
       <c r="W365" s="2" t="n">
         <v>144.7</v>
@@ -27363,7 +28163,9 @@
       <c r="T366" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="U366" s="2" t="inlineStr"/>
+      <c r="U366" s="2" t="n">
+        <v>9.9</v>
+      </c>
       <c r="V366" t="inlineStr"/>
       <c r="W366" s="2" t="n">
         <v>144.3</v>
@@ -27436,7 +28238,9 @@
       <c r="T367" s="6" t="n">
         <v>17.2</v>
       </c>
-      <c r="U367" s="6" t="inlineStr"/>
+      <c r="U367" s="6" t="n">
+        <v>14.6</v>
+      </c>
       <c r="V367" s="4" t="inlineStr"/>
       <c r="W367" s="6" t="n">
         <v>145.7</v>
@@ -27509,7 +28313,9 @@
       <c r="T368" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U368" s="2" t="inlineStr"/>
+      <c r="U368" s="2" t="n">
+        <v>10.6</v>
+      </c>
       <c r="V368" t="inlineStr"/>
       <c r="W368" s="2" t="n">
         <v>145.1</v>
@@ -27582,7 +28388,9 @@
       <c r="T369" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U369" s="2" t="inlineStr"/>
+      <c r="U369" s="2" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V369" t="inlineStr"/>
       <c r="W369" s="2" t="n">
         <v>148.5</v>
@@ -27659,7 +28467,9 @@
       <c r="T370" s="6" t="n">
         <v>16.7</v>
       </c>
-      <c r="U370" s="6" t="inlineStr"/>
+      <c r="U370" s="6" t="n">
+        <v>12.7</v>
+      </c>
       <c r="V370" s="4" t="inlineStr"/>
       <c r="W370" s="6" t="n">
         <v>145.7</v>
@@ -27736,7 +28546,9 @@
       <c r="T371" s="2" t="n">
         <v>18.8</v>
       </c>
-      <c r="U371" s="2" t="inlineStr"/>
+      <c r="U371" s="2" t="n">
+        <v>16.7</v>
+      </c>
       <c r="V371" t="inlineStr"/>
       <c r="W371" s="2" t="n">
         <v>147.3</v>
@@ -27813,7 +28625,9 @@
       <c r="T372" s="2" t="n">
         <v>18.6</v>
       </c>
-      <c r="U372" s="2" t="inlineStr"/>
+      <c r="U372" s="2" t="n">
+        <v>13.4</v>
+      </c>
       <c r="V372" t="inlineStr"/>
       <c r="W372" s="2" t="n">
         <v>146.1</v>
@@ -27886,7 +28700,9 @@
       <c r="T373" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="U373" s="2" t="inlineStr"/>
+      <c r="U373" s="2" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V373" t="inlineStr"/>
       <c r="W373" s="2" t="n">
         <v>151.7</v>
@@ -27959,7 +28775,9 @@
       <c r="T374" s="2" t="n">
         <v>16.6</v>
       </c>
-      <c r="U374" s="2" t="inlineStr"/>
+      <c r="U374" s="2" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V374" t="inlineStr"/>
       <c r="W374" s="2" t="n">
         <v>150.2</v>
@@ -28032,7 +28850,9 @@
       <c r="T375" s="2" t="n">
         <v>18.7</v>
       </c>
-      <c r="U375" s="2" t="inlineStr"/>
+      <c r="U375" s="2" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V375" t="inlineStr"/>
       <c r="W375" s="2" t="n">
         <v>145.9</v>
@@ -28109,7 +28929,9 @@
       <c r="T376" s="6" t="n">
         <v>18.6</v>
       </c>
-      <c r="U376" s="6" t="inlineStr"/>
+      <c r="U376" s="6" t="n">
+        <v>15.4</v>
+      </c>
       <c r="V376" s="4" t="inlineStr"/>
       <c r="W376" s="6" t="n">
         <v>147.3</v>
@@ -28182,7 +29004,9 @@
       <c r="T377" s="2" t="n">
         <v>18.7</v>
       </c>
-      <c r="U377" s="2" t="inlineStr"/>
+      <c r="U377" s="2" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V377" t="inlineStr"/>
       <c r="W377" s="2" t="n">
         <v>146.6</v>
@@ -28259,7 +29083,9 @@
       <c r="T378" s="6" t="n">
         <v>18.2</v>
       </c>
-      <c r="U378" s="6" t="inlineStr"/>
+      <c r="U378" s="6" t="n">
+        <v>15.8</v>
+      </c>
       <c r="V378" s="4" t="inlineStr"/>
       <c r="W378" s="6" t="n">
         <v>143</v>
@@ -28336,7 +29162,9 @@
       <c r="T379" s="6" t="n">
         <v>20.7</v>
       </c>
-      <c r="U379" s="6" t="inlineStr"/>
+      <c r="U379" s="6" t="n">
+        <v>19.5</v>
+      </c>
       <c r="V379" s="4" t="inlineStr"/>
       <c r="W379" s="6" t="n">
         <v>139.6</v>
@@ -28409,7 +29237,9 @@
       <c r="T380" s="2" t="n">
         <v>17.1</v>
       </c>
-      <c r="U380" s="2" t="inlineStr"/>
+      <c r="U380" s="2" t="n">
+        <v>14.1</v>
+      </c>
       <c r="V380" t="inlineStr"/>
       <c r="W380" s="2" t="n">
         <v>139.9</v>
@@ -28482,7 +29312,9 @@
       <c r="T381" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U381" s="2" t="inlineStr"/>
+      <c r="U381" s="2" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V381" t="inlineStr"/>
       <c r="W381" s="2" t="n">
         <v>141.2</v>
@@ -28555,7 +29387,9 @@
       <c r="T382" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="U382" s="2" t="inlineStr"/>
+      <c r="U382" s="2" t="n">
+        <v>9.4</v>
+      </c>
       <c r="V382" t="inlineStr"/>
       <c r="W382" s="2" t="n">
         <v>140</v>
@@ -28628,7 +29462,9 @@
       <c r="T383" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U383" s="2" t="inlineStr"/>
+      <c r="U383" s="2" t="n">
+        <v>13.9</v>
+      </c>
       <c r="V383" t="inlineStr"/>
       <c r="W383" s="3" t="n">
         <v>126.4</v>
@@ -28701,7 +29537,9 @@
       <c r="T384" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U384" s="2" t="inlineStr"/>
+      <c r="U384" s="2" t="n">
+        <v>12.1</v>
+      </c>
       <c r="V384" t="inlineStr"/>
       <c r="W384" s="2" t="n">
         <v>133.3</v>
@@ -28774,7 +29612,9 @@
       <c r="T385" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U385" s="2" t="inlineStr"/>
+      <c r="U385" s="2" t="n">
+        <v>12.6</v>
+      </c>
       <c r="V385" t="inlineStr"/>
       <c r="W385" s="2" t="n">
         <v>134.7</v>
@@ -28847,7 +29687,9 @@
       <c r="T386" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U386" s="2" t="inlineStr"/>
+      <c r="U386" s="2" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V386" t="inlineStr"/>
       <c r="W386" s="2" t="n">
         <v>132.6</v>
@@ -28920,7 +29762,9 @@
       <c r="T387" s="2" t="n">
         <v>15.5</v>
       </c>
-      <c r="U387" s="2" t="inlineStr"/>
+      <c r="U387" s="2" t="n">
+        <v>9.300000000000001</v>
+      </c>
       <c r="V387" t="inlineStr"/>
       <c r="W387" s="2" t="n">
         <v>137.1</v>
@@ -28993,7 +29837,9 @@
       <c r="T388" s="2" t="n">
         <v>15.3</v>
       </c>
-      <c r="U388" s="2" t="inlineStr"/>
+      <c r="U388" s="2" t="n">
+        <v>12.5</v>
+      </c>
       <c r="V388" t="inlineStr"/>
       <c r="W388" s="2" t="n">
         <v>135.6</v>
@@ -29066,7 +29912,9 @@
       <c r="T389" s="2" t="n">
         <v>14.6</v>
       </c>
-      <c r="U389" s="2" t="inlineStr"/>
+      <c r="U389" s="2" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V389" t="inlineStr"/>
       <c r="W389" s="2" t="n">
         <v>136.5</v>
@@ -29139,7 +29987,9 @@
       <c r="T390" s="2" t="n">
         <v>14.6</v>
       </c>
-      <c r="U390" s="2" t="inlineStr"/>
+      <c r="U390" s="2" t="n">
+        <v>9.5</v>
+      </c>
       <c r="V390" t="inlineStr"/>
       <c r="W390" s="2" t="n">
         <v>134.4</v>
@@ -29212,7 +30062,9 @@
       <c r="T391" s="2" t="n">
         <v>14.2</v>
       </c>
-      <c r="U391" s="2" t="inlineStr"/>
+      <c r="U391" s="2" t="n">
+        <v>9.199999999999999</v>
+      </c>
       <c r="V391" t="inlineStr"/>
       <c r="W391" s="2" t="n">
         <v>138.4</v>
@@ -29285,7 +30137,9 @@
       <c r="T392" s="2" t="n">
         <v>15.2</v>
       </c>
-      <c r="U392" s="2" t="inlineStr"/>
+      <c r="U392" s="2" t="n">
+        <v>8.300000000000001</v>
+      </c>
       <c r="V392" t="inlineStr"/>
       <c r="W392" s="2" t="n">
         <v>142.9</v>
@@ -29362,7 +30216,9 @@
       <c r="T393" s="6" t="n">
         <v>15.8</v>
       </c>
-      <c r="U393" s="6" t="inlineStr"/>
+      <c r="U393" s="6" t="n">
+        <v>10.1</v>
+      </c>
       <c r="V393" s="4" t="inlineStr"/>
       <c r="W393" s="6" t="n">
         <v>143.6</v>
@@ -29435,7 +30291,9 @@
       <c r="T394" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U394" s="2" t="inlineStr"/>
+      <c r="U394" s="2" t="n">
+        <v>9.800000000000001</v>
+      </c>
       <c r="V394" t="inlineStr"/>
       <c r="W394" s="2" t="n">
         <v>142.9</v>
@@ -29508,7 +30366,9 @@
       <c r="T395" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="U395" s="2" t="inlineStr"/>
+      <c r="U395" s="2" t="n">
+        <v>12.3</v>
+      </c>
       <c r="V395" t="inlineStr"/>
       <c r="W395" s="2" t="n">
         <v>143.2</v>
@@ -29581,7 +30441,9 @@
       <c r="T396" s="2" t="n">
         <v>15.1</v>
       </c>
-      <c r="U396" s="2" t="inlineStr"/>
+      <c r="U396" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="V396" t="inlineStr"/>
       <c r="W396" s="2" t="n">
         <v>143.9</v>
@@ -29654,7 +30516,9 @@
       <c r="T397" s="2" t="n">
         <v>15.9</v>
       </c>
-      <c r="U397" s="2" t="inlineStr"/>
+      <c r="U397" s="2" t="n">
+        <v>8.699999999999999</v>
+      </c>
       <c r="V397" t="inlineStr"/>
       <c r="W397" s="2" t="n">
         <v>145.6</v>
@@ -29727,7 +30591,9 @@
       <c r="T398" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U398" s="2" t="inlineStr"/>
+      <c r="U398" s="2" t="n">
+        <v>8.4</v>
+      </c>
       <c r="V398" t="inlineStr"/>
       <c r="W398" s="2" t="n">
         <v>143.3</v>
@@ -29800,7 +30666,9 @@
       <c r="T399" s="2" t="n">
         <v>15.2</v>
       </c>
-      <c r="U399" s="2" t="inlineStr"/>
+      <c r="U399" s="2" t="n">
+        <v>12.9</v>
+      </c>
       <c r="V399" t="inlineStr"/>
       <c r="W399" s="2" t="n">
         <v>143</v>
@@ -29873,7 +30741,9 @@
       <c r="T400" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="U400" s="2" t="inlineStr"/>
+      <c r="U400" s="2" t="n">
+        <v>11.5</v>
+      </c>
       <c r="V400" t="inlineStr"/>
       <c r="W400" s="2" t="n">
         <v>144.1</v>
@@ -29946,7 +30816,9 @@
       <c r="T401" s="2" t="n">
         <v>14.4</v>
       </c>
-      <c r="U401" s="2" t="inlineStr"/>
+      <c r="U401" s="2" t="n">
+        <v>10.2</v>
+      </c>
       <c r="V401" t="inlineStr"/>
       <c r="W401" s="2" t="n">
         <v>149.8</v>
@@ -30019,7 +30891,9 @@
       <c r="T402" s="2" t="n">
         <v>14.9</v>
       </c>
-      <c r="U402" s="2" t="inlineStr"/>
+      <c r="U402" s="2" t="n">
+        <v>8.9</v>
+      </c>
       <c r="V402" t="inlineStr"/>
       <c r="W402" s="2" t="n">
         <v>148.5</v>
@@ -30096,7 +30970,9 @@
       <c r="T403" s="2" t="n">
         <v>16.3</v>
       </c>
-      <c r="U403" s="2" t="inlineStr"/>
+      <c r="U403" s="2" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V403" t="inlineStr"/>
       <c r="W403" s="2" t="n">
         <v>149.2</v>
@@ -30169,7 +31045,9 @@
       <c r="T404" s="2" t="n">
         <v>15.2</v>
       </c>
-      <c r="U404" s="2" t="inlineStr"/>
+      <c r="U404" s="2" t="n">
+        <v>10.4</v>
+      </c>
       <c r="V404" t="inlineStr"/>
       <c r="W404" s="2" t="n">
         <v>144.1</v>
@@ -30242,7 +31120,9 @@
       <c r="T405" s="2" t="n">
         <v>14.3</v>
       </c>
-      <c r="U405" s="2" t="inlineStr"/>
+      <c r="U405" s="2" t="n">
+        <v>10.8</v>
+      </c>
       <c r="V405" t="inlineStr"/>
       <c r="W405" s="2" t="n">
         <v>150.6</v>
@@ -30315,7 +31195,9 @@
       <c r="T406" s="2" t="n">
         <v>14.5</v>
       </c>
-      <c r="U406" s="2" t="inlineStr"/>
+      <c r="U406" s="2" t="n">
+        <v>12</v>
+      </c>
       <c r="V406" t="inlineStr"/>
       <c r="W406" s="2" t="n">
         <v>151.6</v>
@@ -30388,7 +31270,9 @@
       <c r="T407" s="2" t="n">
         <v>15.7</v>
       </c>
-      <c r="U407" s="2" t="inlineStr"/>
+      <c r="U407" s="2" t="n">
+        <v>10.4</v>
+      </c>
       <c r="V407" t="inlineStr"/>
       <c r="W407" s="2" t="n">
         <v>148.9</v>
@@ -30461,7 +31345,9 @@
       <c r="T408" s="2" t="n">
         <v>16.5</v>
       </c>
-      <c r="U408" s="2" t="inlineStr"/>
+      <c r="U408" s="2" t="n">
+        <v>11.4</v>
+      </c>
       <c r="V408" t="inlineStr"/>
       <c r="W408" s="2" t="n">
         <v>149.2</v>
@@ -30534,7 +31420,9 @@
       <c r="T409" s="2" t="n">
         <v>17.8</v>
       </c>
-      <c r="U409" s="2" t="inlineStr"/>
+      <c r="U409" s="2" t="n">
+        <v>17.5</v>
+      </c>
       <c r="V409" t="inlineStr"/>
       <c r="W409" s="2" t="n">
         <v>147</v>
@@ -30607,7 +31495,9 @@
       <c r="T410" s="2" t="n">
         <v>15.8</v>
       </c>
-      <c r="U410" s="2" t="inlineStr"/>
+      <c r="U410" s="2" t="n">
+        <v>13</v>
+      </c>
       <c r="V410" t="inlineStr"/>
       <c r="W410" s="2" t="n">
         <v>154.5</v>
@@ -30684,7 +31574,9 @@
       <c r="T411" s="6" t="n">
         <v>17.1</v>
       </c>
-      <c r="U411" s="6" t="inlineStr"/>
+      <c r="U411" s="6" t="n">
+        <v>12</v>
+      </c>
       <c r="V411" s="4" t="inlineStr"/>
       <c r="W411" s="6" t="n">
         <v>152.1</v>
@@ -30757,7 +31649,9 @@
       <c r="T412" s="2" t="n">
         <v>17.2</v>
       </c>
-      <c r="U412" s="2" t="inlineStr"/>
+      <c r="U412" s="2" t="n">
+        <v>17.1</v>
+      </c>
       <c r="V412" t="inlineStr"/>
       <c r="W412" s="2" t="n">
         <v>146.6</v>
@@ -30830,7 +31724,9 @@
       <c r="T413" s="2" t="n">
         <v>17.7</v>
       </c>
-      <c r="U413" s="2" t="inlineStr"/>
+      <c r="U413" s="2" t="n">
+        <v>17</v>
+      </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="n">
         <v>145.9</v>
@@ -30903,7 +31799,9 @@
       <c r="T414" s="2" t="n">
         <v>15.4</v>
       </c>
-      <c r="U414" s="2" t="inlineStr"/>
+      <c r="U414" s="2" t="n">
+        <v>13.1</v>
+      </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="n">
         <v>145.7</v>
@@ -30927,22 +31825,22 @@
         <v>19.74</v>
       </c>
       <c r="E415" t="n">
-        <v>19.27</v>
+        <v>18.99</v>
       </c>
       <c r="F415" t="n">
-        <v>19.43</v>
+        <v>19.55</v>
       </c>
       <c r="G415" t="n">
-        <v>8903842</v>
+        <v>18530083</v>
       </c>
       <c r="H415" s="1" t="n">
-        <v>-4.8</v>
+        <v>-4.21</v>
       </c>
       <c r="I415" t="n">
         <v>13.4</v>
       </c>
       <c r="J415" t="n">
-        <v>20.73</v>
+        <v>20.74</v>
       </c>
       <c r="K415" t="n">
         <v>21.89</v>
@@ -30954,7 +31852,7 @@
         <v>23.32</v>
       </c>
       <c r="N415" s="2" t="n">
-        <v>46.63</v>
+        <v>46.91</v>
       </c>
       <c r="O415" t="n">
         <v>29</v>
@@ -30974,10 +31872,10 @@
         <v>5</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>7.5</v>
+        <v>10.1</v>
       </c>
       <c r="V415" t="inlineStr"/>
       <c r="W415" s="2" t="inlineStr"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31756,7 +31756,7 @@
         <v>20.41</v>
       </c>
       <c r="G414" t="n">
-        <v>18182800</v>
+        <v>18545600</v>
       </c>
       <c r="H414" s="3" t="n">
         <v>11.65</v>
@@ -31822,37 +31822,37 @@
         <v>19.67</v>
       </c>
       <c r="D415" t="n">
-        <v>19.74</v>
+        <v>20.06</v>
       </c>
       <c r="E415" t="n">
         <v>18.99</v>
       </c>
       <c r="F415" t="n">
-        <v>19.55</v>
+        <v>20.04</v>
       </c>
       <c r="G415" t="n">
-        <v>18530083</v>
+        <v>22072832</v>
       </c>
       <c r="H415" s="1" t="n">
-        <v>-4.21</v>
+        <v>-1.81</v>
       </c>
       <c r="I415" t="n">
         <v>13.4</v>
       </c>
       <c r="J415" t="n">
-        <v>20.74</v>
+        <v>20.76</v>
       </c>
       <c r="K415" t="n">
-        <v>21.89</v>
+        <v>21.9</v>
       </c>
       <c r="L415" t="n">
         <v>28.54</v>
       </c>
       <c r="M415" t="n">
-        <v>23.32</v>
+        <v>23.33</v>
       </c>
       <c r="N415" s="2" t="n">
-        <v>46.91</v>
+        <v>48.11</v>
       </c>
       <c r="O415" t="n">
         <v>29</v>
@@ -31872,13 +31872,15 @@
         <v>5</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>15.3</v>
+        <v>14.8</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>10.1</v>
+        <v>11.4</v>
       </c>
       <c r="V415" t="inlineStr"/>
-      <c r="W415" s="2" t="inlineStr"/>
+      <c r="W415" s="2" t="n">
+        <v>148.1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8506,7 +8506,7 @@
         <v>3.48</v>
       </c>
       <c r="K106" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="L106" t="n">
         <v>2.33</v>
@@ -31626,7 +31626,7 @@
         <v>48.11</v>
       </c>
       <c r="O412" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31652,6 +31652,79 @@
       <c r="W412" s="2" t="n">
         <v>148.1</v>
       </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>KORU</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>21.79</v>
+      </c>
+      <c r="D413" t="n">
+        <v>22.63</v>
+      </c>
+      <c r="E413" t="n">
+        <v>21.48</v>
+      </c>
+      <c r="F413" t="n">
+        <v>22.49</v>
+      </c>
+      <c r="G413" t="n">
+        <v>13273095</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>12.23</v>
+      </c>
+      <c r="I413" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="J413" t="n">
+        <v>20.87</v>
+      </c>
+      <c r="K413" t="n">
+        <v>21.59</v>
+      </c>
+      <c r="L413" t="n">
+        <v>28.63</v>
+      </c>
+      <c r="M413" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>53.55</v>
+      </c>
+      <c r="O413" t="n">
+        <v>34</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31668,19 +31668,19 @@
         <v>21.79</v>
       </c>
       <c r="D413" t="n">
-        <v>22.63</v>
+        <v>22.76</v>
       </c>
       <c r="E413" t="n">
         <v>21.48</v>
       </c>
       <c r="F413" t="n">
-        <v>22.49</v>
+        <v>22.55</v>
       </c>
       <c r="G413" t="n">
-        <v>13273095</v>
+        <v>17927088</v>
       </c>
       <c r="H413" s="1" t="n">
-        <v>12.23</v>
+        <v>12.52</v>
       </c>
       <c r="I413" t="n">
         <v>13.4</v>
@@ -31698,7 +31698,7 @@
         <v>23.4</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>53.55</v>
+        <v>53.68</v>
       </c>
       <c r="O413" t="n">
         <v>34</v>
@@ -31715,13 +31715,13 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>4.95</v>
+        <v>4.96</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="inlineStr"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31677,7 +31677,7 @@
         <v>22.55</v>
       </c>
       <c r="G413" t="n">
-        <v>17927088</v>
+        <v>18069337</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>12.52</v>
@@ -31724,7 +31724,9 @@
         <v>10</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>142.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31653,6 +31653,79 @@
         <v>142.2</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>KORU</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>21.93</v>
+      </c>
+      <c r="D413" t="n">
+        <v>23.55</v>
+      </c>
+      <c r="E413" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="F413" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="G413" t="n">
+        <v>12429565</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="I413" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="J413" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="K413" t="n">
+        <v>21.36</v>
+      </c>
+      <c r="L413" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="M413" t="n">
+        <v>23.48</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>60.21</v>
+      </c>
+      <c r="O413" t="n">
+        <v>37</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31668,19 +31668,19 @@
         <v>21.93</v>
       </c>
       <c r="D413" t="n">
-        <v>23.55</v>
+        <v>23.61</v>
       </c>
       <c r="E413" t="n">
         <v>21.89</v>
       </c>
       <c r="F413" t="n">
-        <v>23.4</v>
+        <v>23.38</v>
       </c>
       <c r="G413" t="n">
-        <v>12429565</v>
+        <v>18514841</v>
       </c>
       <c r="H413" s="3" t="n">
-        <v>3.77</v>
+        <v>3.68</v>
       </c>
       <c r="I413" t="n">
         <v>13.4</v>
@@ -31698,10 +31698,10 @@
         <v>23.48</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>60.21</v>
+        <v>60.17</v>
       </c>
       <c r="O413" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31718,10 +31718,10 @@
         <v>4.95</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>6.7</v>
+        <v>8.1</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="inlineStr"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -1447,7 +1447,7 @@
         <v>2.11</v>
       </c>
       <c r="K13" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="L13" t="n">
         <v>2.59</v>
@@ -1822,7 +1822,7 @@
         <v>2.17</v>
       </c>
       <c r="K18" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="L18" t="n">
         <v>2.53</v>
@@ -8431,7 +8431,7 @@
         <v>3.48</v>
       </c>
       <c r="K105" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="L105" t="n">
         <v>2.33</v>
@@ -8653,7 +8653,7 @@
         <v>13.4</v>
       </c>
       <c r="J108" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="K108" t="n">
         <v>2.67</v>
@@ -13106,7 +13106,7 @@
         <v>13.4</v>
       </c>
       <c r="J167" t="n">
-        <v>4.85</v>
+        <v>4.86</v>
       </c>
       <c r="K167" t="n">
         <v>4.34</v>
@@ -20409,7 +20409,7 @@
         <v>13.4</v>
       </c>
       <c r="J264" t="n">
-        <v>18.14</v>
+        <v>18.15</v>
       </c>
       <c r="K264" t="n">
         <v>12.11</v>
@@ -20484,7 +20484,7 @@
         <v>13.4</v>
       </c>
       <c r="J265" t="n">
-        <v>18.54</v>
+        <v>18.55</v>
       </c>
       <c r="K265" t="n">
         <v>12.38</v>
@@ -26984,7 +26984,7 @@
         <v>13.4</v>
       </c>
       <c r="J351" t="n">
-        <v>46.67</v>
+        <v>46.66</v>
       </c>
       <c r="K351" t="n">
         <v>35.18</v>
@@ -29499,7 +29499,7 @@
         <v>13.4</v>
       </c>
       <c r="J384" t="n">
-        <v>17.79</v>
+        <v>17.8</v>
       </c>
       <c r="K384" t="n">
         <v>32.76</v>
@@ -29953,7 +29953,7 @@
         <v>13.4</v>
       </c>
       <c r="J390" t="n">
-        <v>17.99</v>
+        <v>18</v>
       </c>
       <c r="K390" t="n">
         <v>31.04</v>
@@ -31602,7 +31602,7 @@
         <v>22.55</v>
       </c>
       <c r="G412" t="n">
-        <v>18202600</v>
+        <v>18698700</v>
       </c>
       <c r="H412" s="3" t="n">
         <v>12.52</v>
@@ -31668,40 +31668,40 @@
         <v>21.93</v>
       </c>
       <c r="D413" t="n">
-        <v>23.61</v>
+        <v>23.93</v>
       </c>
       <c r="E413" t="n">
         <v>21.89</v>
       </c>
       <c r="F413" t="n">
-        <v>23.38</v>
+        <v>23.77</v>
       </c>
       <c r="G413" t="n">
-        <v>18514841</v>
+        <v>21398407</v>
       </c>
       <c r="H413" s="3" t="n">
-        <v>3.68</v>
+        <v>5.41</v>
       </c>
       <c r="I413" t="n">
         <v>13.4</v>
       </c>
       <c r="J413" t="n">
-        <v>21.1</v>
+        <v>21.12</v>
       </c>
       <c r="K413" t="n">
-        <v>21.36</v>
+        <v>21.37</v>
       </c>
       <c r="L413" t="n">
-        <v>28.7</v>
+        <v>28.71</v>
       </c>
       <c r="M413" t="n">
         <v>23.48</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>60.17</v>
+        <v>60.91</v>
       </c>
       <c r="O413" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31715,16 +31715,18 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>4.95</v>
+        <v>4.97</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>8.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>144.8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31619,19 +31619,11 @@
         </is>
       </c>
       <c r="R412" t="inlineStr"/>
-      <c r="S412" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="T412" s="2" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="U412" s="2" t="n">
-        <v>8.800000000000001</v>
-      </c>
+      <c r="S412" t="inlineStr"/>
+      <c r="T412" s="2" t="inlineStr"/>
+      <c r="U412" s="2" t="inlineStr"/>
       <c r="V412" t="inlineStr"/>
-      <c r="W412" s="2" t="n">
-        <v>144.8</v>
-      </c>
+      <c r="W412" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31582,31 +31582,47 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C412" t="n">
+        <v>22.42</v>
+      </c>
+      <c r="D412" t="n">
+        <v>22.52</v>
+      </c>
+      <c r="E412" t="n">
+        <v>21.07</v>
+      </c>
+      <c r="F412" t="n">
+        <v>21.5</v>
+      </c>
       <c r="G412" t="n">
-        <v>21398407</v>
-      </c>
-      <c r="H412" s="2" t="n">
-        <v>0</v>
+        <v>13786779</v>
+      </c>
+      <c r="H412" s="1" t="n">
+        <v>-4.66</v>
       </c>
       <c r="I412" t="n">
         <v>13.4</v>
       </c>
-      <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr"/>
-      <c r="L412" t="inlineStr"/>
-      <c r="M412" t="inlineStr"/>
+      <c r="J412" t="n">
+        <v>21.01</v>
+      </c>
+      <c r="K412" t="n">
+        <v>21.33</v>
+      </c>
+      <c r="L412" t="n">
+        <v>28.69</v>
+      </c>
+      <c r="M412" t="n">
+        <v>23.47</v>
+      </c>
       <c r="N412" s="2" t="n">
-        <v>58.51</v>
+        <v>55.56</v>
       </c>
       <c r="O412" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31619,9 +31635,15 @@
         </is>
       </c>
       <c r="R412" t="inlineStr"/>
-      <c r="S412" t="inlineStr"/>
-      <c r="T412" s="2" t="inlineStr"/>
-      <c r="U412" s="2" t="inlineStr"/>
+      <c r="S412" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="T412" s="2" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="U412" s="2" t="n">
+        <v>8.4</v>
+      </c>
       <c r="V412" t="inlineStr"/>
       <c r="W412" s="2" t="inlineStr"/>
     </row>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1368,7 +1368,7 @@
         <v>2.11</v>
       </c>
       <c r="K12" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="L12" t="n">
         <v>2.59</v>
@@ -1743,7 +1743,7 @@
         <v>2.17</v>
       </c>
       <c r="K17" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="L17" t="n">
         <v>2.53</v>
@@ -8352,7 +8352,7 @@
         <v>3.48</v>
       </c>
       <c r="K104" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="L104" t="n">
         <v>2.33</v>
@@ -8574,7 +8574,7 @@
         <v>13.4</v>
       </c>
       <c r="J107" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="K107" t="n">
         <v>2.67</v>
@@ -13027,7 +13027,7 @@
         <v>13.4</v>
       </c>
       <c r="J166" t="n">
-        <v>4.86</v>
+        <v>4.85</v>
       </c>
       <c r="K166" t="n">
         <v>4.34</v>
@@ -20330,7 +20330,7 @@
         <v>13.4</v>
       </c>
       <c r="J263" t="n">
-        <v>18.15</v>
+        <v>18.14</v>
       </c>
       <c r="K263" t="n">
         <v>12.11</v>
@@ -20405,7 +20405,7 @@
         <v>13.4</v>
       </c>
       <c r="J264" t="n">
-        <v>18.55</v>
+        <v>18.54</v>
       </c>
       <c r="K264" t="n">
         <v>12.38</v>
@@ -26905,7 +26905,7 @@
         <v>13.4</v>
       </c>
       <c r="J350" t="n">
-        <v>46.66</v>
+        <v>46.67</v>
       </c>
       <c r="K350" t="n">
         <v>35.18</v>
@@ -29420,7 +29420,7 @@
         <v>13.4</v>
       </c>
       <c r="J383" t="n">
-        <v>17.8</v>
+        <v>17.79</v>
       </c>
       <c r="K383" t="n">
         <v>32.76</v>
@@ -29874,7 +29874,7 @@
         <v>13.4</v>
       </c>
       <c r="J389" t="n">
-        <v>18</v>
+        <v>17.99</v>
       </c>
       <c r="K389" t="n">
         <v>31.04</v>
@@ -31582,47 +31582,47 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="C412" t="n">
-        <v>22.42</v>
+        <v>21.93</v>
       </c>
       <c r="D412" t="n">
-        <v>22.52</v>
+        <v>23.94</v>
       </c>
       <c r="E412" t="n">
-        <v>21.07</v>
+        <v>21.89</v>
       </c>
       <c r="F412" t="n">
-        <v>21.5</v>
+        <v>23.77</v>
       </c>
       <c r="G412" t="n">
-        <v>13786779</v>
-      </c>
-      <c r="H412" s="1" t="n">
-        <v>-4.66</v>
+        <v>22090700</v>
+      </c>
+      <c r="H412" s="3" t="n">
+        <v>5.41</v>
       </c>
       <c r="I412" t="n">
         <v>13.4</v>
       </c>
       <c r="J412" t="n">
-        <v>21.01</v>
+        <v>21.12</v>
       </c>
       <c r="K412" t="n">
-        <v>21.33</v>
+        <v>21.37</v>
       </c>
       <c r="L412" t="n">
-        <v>28.69</v>
+        <v>28.71</v>
       </c>
       <c r="M412" t="n">
-        <v>23.47</v>
+        <v>23.48</v>
       </c>
       <c r="N412" s="2" t="n">
-        <v>55.56</v>
+        <v>60.91</v>
       </c>
       <c r="O412" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31631,21 +31631,88 @@
       </c>
       <c r="Q412" t="inlineStr">
         <is>
-          <t>2x BUY</t>
+          <t>BUY STOP</t>
         </is>
       </c>
       <c r="R412" t="inlineStr"/>
-      <c r="S412" t="n">
-        <v>5.09</v>
-      </c>
-      <c r="T412" s="2" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="U412" s="2" t="n">
-        <v>8.4</v>
-      </c>
+      <c r="S412" t="inlineStr"/>
+      <c r="T412" s="2" t="inlineStr"/>
+      <c r="U412" s="2" t="inlineStr"/>
       <c r="V412" t="inlineStr"/>
       <c r="W412" s="2" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>KORU</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>22.42</v>
+      </c>
+      <c r="D413" t="n">
+        <v>22.52</v>
+      </c>
+      <c r="E413" t="n">
+        <v>20.98</v>
+      </c>
+      <c r="F413" t="n">
+        <v>21.26</v>
+      </c>
+      <c r="G413" t="n">
+        <v>18102520</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>-10.56</v>
+      </c>
+      <c r="I413" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="J413" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="K413" t="n">
+        <v>21.11</v>
+      </c>
+      <c r="L413" t="n">
+        <v>28.76</v>
+      </c>
+      <c r="M413" t="n">
+        <v>23.55</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>52.46</v>
+      </c>
+      <c r="O413" t="n">
+        <v>35</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31662,13 +31662,13 @@
         <v>20.98</v>
       </c>
       <c r="F413" t="n">
-        <v>21.26</v>
+        <v>21.27</v>
       </c>
       <c r="G413" t="n">
-        <v>18102520</v>
+        <v>18265717</v>
       </c>
       <c r="H413" s="1" t="n">
-        <v>-10.56</v>
+        <v>-10.52</v>
       </c>
       <c r="I413" t="n">
         <v>13.4</v>
@@ -31686,7 +31686,7 @@
         <v>23.55</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>52.46</v>
+        <v>52.48</v>
       </c>
       <c r="O413" t="n">
         <v>35</v>
@@ -31709,10 +31709,12 @@
         <v>15.2</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>146.1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31652,41 +31652,25 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="C413" t="n">
-        <v>22.42</v>
-      </c>
-      <c r="D413" t="n">
-        <v>22.52</v>
-      </c>
-      <c r="E413" t="n">
-        <v>20.98</v>
-      </c>
-      <c r="F413" t="n">
-        <v>21.27</v>
-      </c>
+      <c r="C413" t="inlineStr"/>
+      <c r="D413" t="inlineStr"/>
+      <c r="E413" t="inlineStr"/>
+      <c r="F413" t="inlineStr"/>
       <c r="G413" t="n">
         <v>18265717</v>
       </c>
-      <c r="H413" s="1" t="n">
-        <v>-10.52</v>
+      <c r="H413" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I413" t="n">
         <v>13.4</v>
       </c>
-      <c r="J413" t="n">
-        <v>21.14</v>
-      </c>
-      <c r="K413" t="n">
-        <v>21.11</v>
-      </c>
-      <c r="L413" t="n">
-        <v>28.76</v>
-      </c>
-      <c r="M413" t="n">
-        <v>23.55</v>
-      </c>
+      <c r="J413" t="inlineStr"/>
+      <c r="K413" t="inlineStr"/>
+      <c r="L413" t="inlineStr"/>
+      <c r="M413" t="inlineStr"/>
       <c r="N413" s="2" t="n">
-        <v>52.48</v>
+        <v>59.02</v>
       </c>
       <c r="O413" t="n">
         <v>35</v>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31652,25 +31652,41 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="C413" t="inlineStr"/>
-      <c r="D413" t="inlineStr"/>
-      <c r="E413" t="inlineStr"/>
-      <c r="F413" t="inlineStr"/>
+      <c r="C413" t="n">
+        <v>22.42</v>
+      </c>
+      <c r="D413" t="n">
+        <v>22.53</v>
+      </c>
+      <c r="E413" t="n">
+        <v>20.98</v>
+      </c>
+      <c r="F413" t="n">
+        <v>21.27</v>
+      </c>
       <c r="G413" t="n">
-        <v>18265717</v>
-      </c>
-      <c r="H413" s="2" t="n">
-        <v>0</v>
+        <v>18418400</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>-10.52</v>
       </c>
       <c r="I413" t="n">
         <v>13.4</v>
       </c>
-      <c r="J413" t="inlineStr"/>
-      <c r="K413" t="inlineStr"/>
-      <c r="L413" t="inlineStr"/>
-      <c r="M413" t="inlineStr"/>
+      <c r="J413" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="K413" t="n">
+        <v>21.11</v>
+      </c>
+      <c r="L413" t="n">
+        <v>28.76</v>
+      </c>
+      <c r="M413" t="n">
+        <v>23.55</v>
+      </c>
       <c r="N413" s="2" t="n">
-        <v>59.02</v>
+        <v>52.48</v>
       </c>
       <c r="O413" t="n">
         <v>35</v>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31689,7 +31689,7 @@
         <v>52.48</v>
       </c>
       <c r="O413" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31715,6 +31715,83 @@
       <c r="W413" s="2" t="n">
         <v>146.1</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>KORU</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="D414" t="n">
+        <v>21.12</v>
+      </c>
+      <c r="E414" t="n">
+        <v>19.89</v>
+      </c>
+      <c r="F414" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="G414" t="n">
+        <v>13486537</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>-6.02</v>
+      </c>
+      <c r="I414" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="J414" t="n">
+        <v>21.12</v>
+      </c>
+      <c r="K414" t="n">
+        <v>20.79</v>
+      </c>
+      <c r="L414" t="n">
+        <v>28.81</v>
+      </c>
+      <c r="M414" t="n">
+        <v>23.61</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="O414" t="n">
+        <v>35</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>2nd: MA60, 50% cash, 5d</t>
+        </is>
+      </c>
+      <c r="S414" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31665,7 +31665,7 @@
         <v>21.27</v>
       </c>
       <c r="G413" t="n">
-        <v>18418400</v>
+        <v>18596600</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>-10.52</v>
@@ -31737,19 +31737,19 @@
         <v>19.89</v>
       </c>
       <c r="F414" t="n">
-        <v>19.99</v>
+        <v>20.14</v>
       </c>
       <c r="G414" t="n">
-        <v>13486537</v>
+        <v>17061733</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>-6.02</v>
+        <v>-5.31</v>
       </c>
       <c r="I414" t="n">
         <v>13.4</v>
       </c>
       <c r="J414" t="n">
-        <v>21.12</v>
+        <v>21.13</v>
       </c>
       <c r="K414" t="n">
         <v>20.79</v>
@@ -31761,10 +31761,10 @@
         <v>23.61</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>48.5</v>
+        <v>48.81</v>
       </c>
       <c r="O414" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31782,16 +31782,18 @@
         </is>
       </c>
       <c r="S414" t="n">
-        <v>5.18</v>
+        <v>5.16</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>15.9</v>
+        <v>15.7</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>11.6</v>
+        <v>12.1</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="n">
+        <v>146</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31727,41 +31727,25 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="C414" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="D414" t="n">
-        <v>21.12</v>
-      </c>
-      <c r="E414" t="n">
-        <v>19.89</v>
-      </c>
-      <c r="F414" t="n">
-        <v>20.14</v>
-      </c>
+      <c r="C414" t="inlineStr"/>
+      <c r="D414" t="inlineStr"/>
+      <c r="E414" t="inlineStr"/>
+      <c r="F414" t="inlineStr"/>
       <c r="G414" t="n">
         <v>17061733</v>
       </c>
-      <c r="H414" s="1" t="n">
-        <v>-5.31</v>
+      <c r="H414" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I414" t="n">
         <v>13.4</v>
       </c>
-      <c r="J414" t="n">
-        <v>21.13</v>
-      </c>
-      <c r="K414" t="n">
-        <v>20.79</v>
-      </c>
-      <c r="L414" t="n">
-        <v>28.81</v>
-      </c>
-      <c r="M414" t="n">
-        <v>23.61</v>
-      </c>
+      <c r="J414" t="inlineStr"/>
+      <c r="K414" t="inlineStr"/>
+      <c r="L414" t="inlineStr"/>
+      <c r="M414" t="inlineStr"/>
       <c r="N414" s="2" t="n">
-        <v>48.81</v>
+        <v>51.32</v>
       </c>
       <c r="O414" t="n">
         <v>36</v>
@@ -31776,11 +31760,7 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R414" t="inlineStr">
-        <is>
-          <t>2nd: MA60, 50% cash, 5d</t>
-        </is>
-      </c>
+      <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
         <v>5.16</v>
       </c>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31727,25 +31727,41 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr"/>
-      <c r="D414" t="inlineStr"/>
-      <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
+      <c r="C414" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="D414" t="n">
+        <v>21.13</v>
+      </c>
+      <c r="E414" t="n">
+        <v>19.89</v>
+      </c>
+      <c r="F414" t="n">
+        <v>20.14</v>
+      </c>
       <c r="G414" t="n">
-        <v>17061733</v>
-      </c>
-      <c r="H414" s="2" t="n">
-        <v>0</v>
+        <v>17226100</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>-5.31</v>
       </c>
       <c r="I414" t="n">
         <v>13.4</v>
       </c>
-      <c r="J414" t="inlineStr"/>
-      <c r="K414" t="inlineStr"/>
-      <c r="L414" t="inlineStr"/>
-      <c r="M414" t="inlineStr"/>
+      <c r="J414" t="n">
+        <v>21.13</v>
+      </c>
+      <c r="K414" t="n">
+        <v>20.79</v>
+      </c>
+      <c r="L414" t="n">
+        <v>28.81</v>
+      </c>
+      <c r="M414" t="n">
+        <v>23.61</v>
+      </c>
       <c r="N414" s="2" t="n">
-        <v>51.32</v>
+        <v>48.81</v>
       </c>
       <c r="O414" t="n">
         <v>36</v>
@@ -31760,7 +31776,11 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R414" t="inlineStr"/>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>2nd: MA60, 50% cash, 5d</t>
+        </is>
+      </c>
       <c r="S414" t="n">
         <v>5.16</v>
       </c>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31635,11 +31635,19 @@
         </is>
       </c>
       <c r="R412" t="inlineStr"/>
-      <c r="S412" t="inlineStr"/>
-      <c r="T412" s="2" t="inlineStr"/>
-      <c r="U412" s="2" t="inlineStr"/>
+      <c r="S412" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="T412" s="2" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="U412" s="2" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="V412" t="inlineStr"/>
-      <c r="W412" s="2" t="inlineStr"/>
+      <c r="W412" s="2" t="n">
+        <v>144.8</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31803,6 +31803,79 @@
         <v>146</v>
       </c>
     </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>KORU</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>21.27</v>
+      </c>
+      <c r="D415" t="n">
+        <v>21.73</v>
+      </c>
+      <c r="E415" t="n">
+        <v>20.62</v>
+      </c>
+      <c r="F415" t="n">
+        <v>21.62</v>
+      </c>
+      <c r="G415" t="n">
+        <v>13965979</v>
+      </c>
+      <c r="H415" s="3" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="I415" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="J415" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="K415" t="n">
+        <v>20.65</v>
+      </c>
+      <c r="L415" t="n">
+        <v>28.86</v>
+      </c>
+      <c r="M415" t="n">
+        <v>23.68</v>
+      </c>
+      <c r="N415" s="2" t="n">
+        <v>45.77</v>
+      </c>
+      <c r="O415" t="n">
+        <v>38</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="T415" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="U415" s="2" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31748,7 +31748,7 @@
         <v>20.14</v>
       </c>
       <c r="G414" t="n">
-        <v>17226100</v>
+        <v>17426500</v>
       </c>
       <c r="H414" s="1" t="n">
         <v>-5.31</v>
@@ -31818,19 +31818,19 @@
         <v>21.27</v>
       </c>
       <c r="D415" t="n">
-        <v>21.73</v>
+        <v>21.77</v>
       </c>
       <c r="E415" t="n">
         <v>20.62</v>
       </c>
       <c r="F415" t="n">
-        <v>21.62</v>
+        <v>21.59</v>
       </c>
       <c r="G415" t="n">
-        <v>13965979</v>
+        <v>15683798</v>
       </c>
       <c r="H415" s="3" t="n">
-        <v>7.35</v>
+        <v>7.2</v>
       </c>
       <c r="I415" t="n">
         <v>13.4</v>
@@ -31848,10 +31848,10 @@
         <v>23.68</v>
       </c>
       <c r="N415" s="2" t="n">
-        <v>45.77</v>
+        <v>45.69</v>
       </c>
       <c r="O415" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31865,16 +31865,18 @@
       </c>
       <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
-        <v>5.2</v>
+        <v>5.18</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>11.2</v>
+        <v>12.5</v>
       </c>
       <c r="V415" t="inlineStr"/>
-      <c r="W415" s="2" t="inlineStr"/>
+      <c r="W415" s="2" t="n">
+        <v>144.9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31739,25 +31739,41 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr"/>
-      <c r="D414" t="inlineStr"/>
-      <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
+      <c r="C414" t="n">
+        <v>21.27</v>
+      </c>
+      <c r="D414" t="n">
+        <v>21.77</v>
+      </c>
+      <c r="E414" t="n">
+        <v>20.62</v>
+      </c>
+      <c r="F414" t="n">
+        <v>21.59</v>
+      </c>
       <c r="G414" t="n">
-        <v>15683798</v>
-      </c>
-      <c r="H414" s="2" t="n">
-        <v>0</v>
+        <v>15853000</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>7.2</v>
       </c>
       <c r="I414" t="n">
         <v>13.4</v>
       </c>
-      <c r="J414" t="inlineStr"/>
-      <c r="K414" t="inlineStr"/>
-      <c r="L414" t="inlineStr"/>
-      <c r="M414" t="inlineStr"/>
+      <c r="J414" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="K414" t="n">
+        <v>20.65</v>
+      </c>
+      <c r="L414" t="n">
+        <v>28.86</v>
+      </c>
+      <c r="M414" t="n">
+        <v>23.68</v>
+      </c>
       <c r="N414" s="2" t="n">
-        <v>41.83</v>
+        <v>45.69</v>
       </c>
       <c r="O414" t="n">
         <v>37</v>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8349,7 +8349,7 @@
         <v>13.4</v>
       </c>
       <c r="J104" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="K104" t="n">
         <v>2.67</v>
@@ -20105,7 +20105,7 @@
         <v>13.4</v>
       </c>
       <c r="J260" t="n">
-        <v>18.14</v>
+        <v>18.15</v>
       </c>
       <c r="K260" t="n">
         <v>12.11</v>
@@ -20180,7 +20180,7 @@
         <v>13.4</v>
       </c>
       <c r="J261" t="n">
-        <v>18.54</v>
+        <v>18.55</v>
       </c>
       <c r="K261" t="n">
         <v>12.38</v>
@@ -26680,7 +26680,7 @@
         <v>13.4</v>
       </c>
       <c r="J347" t="n">
-        <v>46.67</v>
+        <v>46.66</v>
       </c>
       <c r="K347" t="n">
         <v>35.18</v>
@@ -29195,7 +29195,7 @@
         <v>13.4</v>
       </c>
       <c r="J380" t="n">
-        <v>17.79</v>
+        <v>17.8</v>
       </c>
       <c r="K380" t="n">
         <v>32.76</v>
@@ -29649,7 +29649,7 @@
         <v>13.4</v>
       </c>
       <c r="J386" t="n">
-        <v>17.99</v>
+        <v>18</v>
       </c>
       <c r="K386" t="n">
         <v>31.04</v>
@@ -31652,6 +31652,83 @@
       <c r="W412" s="2" t="n">
         <v>144.9</v>
       </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>KORU</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>20.71</v>
+      </c>
+      <c r="D413" t="n">
+        <v>20.89</v>
+      </c>
+      <c r="E413" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="F413" t="n">
+        <v>19.72</v>
+      </c>
+      <c r="G413" t="n">
+        <v>9190359</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>-8.66</v>
+      </c>
+      <c r="I413" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="J413" t="n">
+        <v>21.08</v>
+      </c>
+      <c r="K413" t="n">
+        <v>20.53</v>
+      </c>
+      <c r="L413" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="M413" t="n">
+        <v>23.74</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>41.17</v>
+      </c>
+      <c r="O413" t="n">
+        <v>34</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>2nd: MA60, 50% cash, 5d</t>
+        </is>
+      </c>
+      <c r="S413" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -8349,7 +8349,7 @@
         <v>13.4</v>
       </c>
       <c r="J104" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="K104" t="n">
         <v>2.67</v>
@@ -20105,7 +20105,7 @@
         <v>13.4</v>
       </c>
       <c r="J260" t="n">
-        <v>18.15</v>
+        <v>18.14</v>
       </c>
       <c r="K260" t="n">
         <v>12.11</v>
@@ -20180,7 +20180,7 @@
         <v>13.4</v>
       </c>
       <c r="J261" t="n">
-        <v>18.55</v>
+        <v>18.54</v>
       </c>
       <c r="K261" t="n">
         <v>12.38</v>
@@ -26680,7 +26680,7 @@
         <v>13.4</v>
       </c>
       <c r="J347" t="n">
-        <v>46.66</v>
+        <v>46.67</v>
       </c>
       <c r="K347" t="n">
         <v>35.18</v>
@@ -29195,7 +29195,7 @@
         <v>13.4</v>
       </c>
       <c r="J380" t="n">
-        <v>17.8</v>
+        <v>17.79</v>
       </c>
       <c r="K380" t="n">
         <v>32.76</v>
@@ -29649,7 +29649,7 @@
         <v>13.4</v>
       </c>
       <c r="J386" t="n">
-        <v>18</v>
+        <v>17.99</v>
       </c>
       <c r="K386" t="n">
         <v>31.04</v>
@@ -31674,22 +31674,22 @@
         <v>19.27</v>
       </c>
       <c r="F413" t="n">
-        <v>19.72</v>
+        <v>20.4</v>
       </c>
       <c r="G413" t="n">
-        <v>9190359</v>
+        <v>14722682</v>
       </c>
       <c r="H413" s="3" t="n">
-        <v>-8.66</v>
+        <v>-5.51</v>
       </c>
       <c r="I413" t="n">
         <v>13.4</v>
       </c>
       <c r="J413" t="n">
-        <v>21.08</v>
+        <v>21.12</v>
       </c>
       <c r="K413" t="n">
-        <v>20.53</v>
+        <v>20.54</v>
       </c>
       <c r="L413" t="n">
         <v>28.9</v>
@@ -31698,7 +31698,7 @@
         <v>23.74</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>41.17</v>
+        <v>42.4</v>
       </c>
       <c r="O413" t="n">
         <v>34</v>
@@ -31719,16 +31719,18 @@
         </is>
       </c>
       <c r="S413" t="n">
-        <v>5.26</v>
+        <v>5.24</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>16.5</v>
+        <v>16.1</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>9.5</v>
+        <v>11.3</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>146.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31657,6 +31657,79 @@
         <v>146.2</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>KORU</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>21.31</v>
+      </c>
+      <c r="D413" t="n">
+        <v>21.54</v>
+      </c>
+      <c r="E413" t="n">
+        <v>20.76</v>
+      </c>
+      <c r="F413" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="G413" t="n">
+        <v>7658915</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="I413" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="J413" t="n">
+        <v>21.11</v>
+      </c>
+      <c r="K413" t="n">
+        <v>20.37</v>
+      </c>
+      <c r="L413" t="n">
+        <v>28.91</v>
+      </c>
+      <c r="M413" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>42.76</v>
+      </c>
+      <c r="O413" t="n">
+        <v>33</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -8052,7 +8052,7 @@
         <v>3.48</v>
       </c>
       <c r="K100" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="L100" t="n">
         <v>2.33</v>
@@ -31602,7 +31602,7 @@
         <v>20.4</v>
       </c>
       <c r="G412" t="n">
-        <v>14814400</v>
+        <v>14975000</v>
       </c>
       <c r="H412" s="1" t="n">
         <v>-5.51</v>
@@ -31672,40 +31672,40 @@
         <v>21.31</v>
       </c>
       <c r="D413" t="n">
-        <v>21.54</v>
+        <v>21.55</v>
       </c>
       <c r="E413" t="n">
         <v>20.76</v>
       </c>
       <c r="F413" t="n">
-        <v>20.9</v>
+        <v>21.47</v>
       </c>
       <c r="G413" t="n">
-        <v>7658915</v>
+        <v>11428440</v>
       </c>
       <c r="H413" s="3" t="n">
-        <v>2.45</v>
+        <v>5.25</v>
       </c>
       <c r="I413" t="n">
         <v>13.4</v>
       </c>
       <c r="J413" t="n">
-        <v>21.11</v>
+        <v>21.14</v>
       </c>
       <c r="K413" t="n">
-        <v>20.37</v>
+        <v>20.38</v>
       </c>
       <c r="L413" t="n">
         <v>28.91</v>
       </c>
       <c r="M413" t="n">
-        <v>23.8</v>
+        <v>23.81</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>42.76</v>
+        <v>44.15</v>
       </c>
       <c r="O413" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31719,13 +31719,13 @@
       </c>
       <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>5.27</v>
+        <v>5.26</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>10</v>
+        <v>11.7</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="inlineStr"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31589,25 +31589,41 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
+      <c r="C412" t="n">
+        <v>21.31</v>
+      </c>
+      <c r="D412" t="n">
+        <v>21.55</v>
+      </c>
+      <c r="E412" t="n">
+        <v>20.76</v>
+      </c>
+      <c r="F412" t="n">
+        <v>21.47</v>
+      </c>
       <c r="G412" t="n">
-        <v>11509028</v>
-      </c>
-      <c r="H412" s="2" t="n">
-        <v>0</v>
+        <v>11609000</v>
+      </c>
+      <c r="H412" s="1" t="n">
+        <v>5.25</v>
       </c>
       <c r="I412" t="n">
         <v>13.4</v>
       </c>
-      <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr"/>
-      <c r="L412" t="inlineStr"/>
-      <c r="M412" t="inlineStr"/>
+      <c r="J412" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="K412" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="L412" t="n">
+        <v>28.91</v>
+      </c>
+      <c r="M412" t="n">
+        <v>23.81</v>
+      </c>
       <c r="N412" s="2" t="n">
-        <v>41.47</v>
+        <v>44.15</v>
       </c>
       <c r="O412" t="n">
         <v>32</v>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31626,7 +31626,7 @@
         <v>44.15</v>
       </c>
       <c r="O412" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31653,6 +31653,83 @@
         <v>144.6</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>KORU</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>20.85</v>
+      </c>
+      <c r="D413" t="n">
+        <v>21</v>
+      </c>
+      <c r="E413" t="n">
+        <v>19.67</v>
+      </c>
+      <c r="F413" t="n">
+        <v>19.69</v>
+      </c>
+      <c r="G413" t="n">
+        <v>15289367</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>-8.289999999999999</v>
+      </c>
+      <c r="I413" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="J413" t="n">
+        <v>21.17</v>
+      </c>
+      <c r="K413" t="n">
+        <v>20.25</v>
+      </c>
+      <c r="L413" t="n">
+        <v>28.91</v>
+      </c>
+      <c r="M413" t="n">
+        <v>23.87</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>46.65</v>
+      </c>
+      <c r="O413" t="n">
+        <v>33</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>2nd: MA60, 50% cash, 5d</t>
+        </is>
+      </c>
+      <c r="S413" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -7973,7 +7973,7 @@
         <v>3.48</v>
       </c>
       <c r="K99" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="L99" t="n">
         <v>2.33</v>
@@ -8195,7 +8195,7 @@
         <v>13.4</v>
       </c>
       <c r="J102" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="K102" t="n">
         <v>2.67</v>
@@ -19951,7 +19951,7 @@
         <v>13.4</v>
       </c>
       <c r="J258" t="n">
-        <v>18.14</v>
+        <v>18.15</v>
       </c>
       <c r="K258" t="n">
         <v>12.11</v>
@@ -20026,7 +20026,7 @@
         <v>13.4</v>
       </c>
       <c r="J259" t="n">
-        <v>18.54</v>
+        <v>18.55</v>
       </c>
       <c r="K259" t="n">
         <v>12.38</v>
@@ -26526,7 +26526,7 @@
         <v>13.4</v>
       </c>
       <c r="J345" t="n">
-        <v>46.67</v>
+        <v>46.66</v>
       </c>
       <c r="K345" t="n">
         <v>35.18</v>
@@ -29041,7 +29041,7 @@
         <v>13.4</v>
       </c>
       <c r="J378" t="n">
-        <v>17.79</v>
+        <v>17.8</v>
       </c>
       <c r="K378" t="n">
         <v>32.76</v>
@@ -29495,7 +29495,7 @@
         <v>13.4</v>
       </c>
       <c r="J384" t="n">
-        <v>17.99</v>
+        <v>18</v>
       </c>
       <c r="K384" t="n">
         <v>31.04</v>
@@ -31602,7 +31602,7 @@
         <v>21.47</v>
       </c>
       <c r="G412" t="n">
-        <v>11609000</v>
+        <v>11925300</v>
       </c>
       <c r="H412" s="1" t="n">
         <v>5.25</v>
@@ -31674,22 +31674,22 @@
         <v>19.67</v>
       </c>
       <c r="F413" t="n">
-        <v>19.69</v>
+        <v>20.02</v>
       </c>
       <c r="G413" t="n">
-        <v>15289367</v>
+        <v>18376849</v>
       </c>
       <c r="H413" s="3" t="n">
-        <v>-8.289999999999999</v>
+        <v>-6.75</v>
       </c>
       <c r="I413" t="n">
         <v>13.4</v>
       </c>
       <c r="J413" t="n">
-        <v>21.17</v>
+        <v>21.18</v>
       </c>
       <c r="K413" t="n">
-        <v>20.25</v>
+        <v>20.26</v>
       </c>
       <c r="L413" t="n">
         <v>28.91</v>
@@ -31698,10 +31698,10 @@
         <v>23.87</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>46.65</v>
+        <v>47.36</v>
       </c>
       <c r="O413" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31719,16 +31719,18 @@
         </is>
       </c>
       <c r="S413" t="n">
-        <v>5.3</v>
+        <v>5.29</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>15.9</v>
+        <v>16.3</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>11.4</v>
+        <v>12.2</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>141.9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31671,13 +31671,13 @@
         <v>21</v>
       </c>
       <c r="E413" t="n">
-        <v>19.67</v>
+        <v>19.68</v>
       </c>
       <c r="F413" t="n">
         <v>20.02</v>
       </c>
       <c r="G413" t="n">
-        <v>18376849</v>
+        <v>18835900</v>
       </c>
       <c r="H413" s="3" t="n">
         <v>-6.75</v>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31701,7 +31701,7 @@
         <v>47.36</v>
       </c>
       <c r="O413" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31732,6 +31732,79 @@
         <v>141.9</v>
       </c>
     </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>KORU</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>20.42</v>
+      </c>
+      <c r="D414" t="n">
+        <v>20.73</v>
+      </c>
+      <c r="E414" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="F414" t="n">
+        <v>20.02</v>
+      </c>
+      <c r="G414" t="n">
+        <v>13549046</v>
+      </c>
+      <c r="H414" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I414" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="J414" t="n">
+        <v>21.18</v>
+      </c>
+      <c r="K414" t="n">
+        <v>20.13</v>
+      </c>
+      <c r="L414" t="n">
+        <v>28.92</v>
+      </c>
+      <c r="M414" t="n">
+        <v>23.93</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>42.33</v>
+      </c>
+      <c r="O414" t="n">
+        <v>27</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31677,7 +31677,7 @@
         <v>20.02</v>
       </c>
       <c r="G413" t="n">
-        <v>18835900</v>
+        <v>19281200</v>
       </c>
       <c r="H413" s="3" t="n">
         <v>-6.75</v>
@@ -31747,40 +31747,40 @@
         <v>20.42</v>
       </c>
       <c r="D414" t="n">
-        <v>20.73</v>
+        <v>21.25</v>
       </c>
       <c r="E414" t="n">
         <v>19.7</v>
       </c>
       <c r="F414" t="n">
-        <v>20.02</v>
+        <v>21.09</v>
       </c>
       <c r="G414" t="n">
-        <v>13549046</v>
-      </c>
-      <c r="H414" s="2" t="n">
-        <v>0</v>
+        <v>21013682</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>5.34</v>
       </c>
       <c r="I414" t="n">
         <v>13.4</v>
       </c>
       <c r="J414" t="n">
-        <v>21.18</v>
+        <v>21.23</v>
       </c>
       <c r="K414" t="n">
-        <v>20.13</v>
+        <v>20.15</v>
       </c>
       <c r="L414" t="n">
         <v>28.92</v>
       </c>
       <c r="M414" t="n">
-        <v>23.93</v>
+        <v>23.94</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>42.33</v>
+        <v>45.27</v>
       </c>
       <c r="O414" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31794,16 +31794,18 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.26</v>
+        <v>5.24</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>17.3</v>
+        <v>16.4</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="n">
+        <v>142.8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31743,41 +31743,25 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C414" t="n">
-        <v>20.42</v>
-      </c>
-      <c r="D414" t="n">
-        <v>21.25</v>
-      </c>
-      <c r="E414" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="F414" t="n">
-        <v>21.09</v>
-      </c>
+      <c r="C414" t="inlineStr"/>
+      <c r="D414" t="inlineStr"/>
+      <c r="E414" t="inlineStr"/>
+      <c r="F414" t="inlineStr"/>
       <c r="G414" t="n">
         <v>21013682</v>
       </c>
-      <c r="H414" s="1" t="n">
-        <v>5.34</v>
+      <c r="H414" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I414" t="n">
         <v>13.4</v>
       </c>
-      <c r="J414" t="n">
-        <v>21.23</v>
-      </c>
-      <c r="K414" t="n">
-        <v>20.15</v>
-      </c>
-      <c r="L414" t="n">
-        <v>28.92</v>
-      </c>
-      <c r="M414" t="n">
-        <v>23.94</v>
-      </c>
+      <c r="J414" t="inlineStr"/>
+      <c r="K414" t="inlineStr"/>
+      <c r="L414" t="inlineStr"/>
+      <c r="M414" t="inlineStr"/>
       <c r="N414" s="2" t="n">
-        <v>45.27</v>
+        <v>42.33</v>
       </c>
       <c r="O414" t="n">
         <v>28</v>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31743,28 +31743,44 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr"/>
-      <c r="D414" t="inlineStr"/>
-      <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
+      <c r="C414" t="n">
+        <v>20.42</v>
+      </c>
+      <c r="D414" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="E414" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="F414" t="n">
+        <v>21.09</v>
+      </c>
       <c r="G414" t="n">
-        <v>21013682</v>
-      </c>
-      <c r="H414" s="2" t="n">
-        <v>0</v>
+        <v>21173800</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>5.34</v>
       </c>
       <c r="I414" t="n">
         <v>13.4</v>
       </c>
-      <c r="J414" t="inlineStr"/>
-      <c r="K414" t="inlineStr"/>
-      <c r="L414" t="inlineStr"/>
-      <c r="M414" t="inlineStr"/>
+      <c r="J414" t="n">
+        <v>21.23</v>
+      </c>
+      <c r="K414" t="n">
+        <v>20.15</v>
+      </c>
+      <c r="L414" t="n">
+        <v>28.92</v>
+      </c>
+      <c r="M414" t="n">
+        <v>23.94</v>
+      </c>
       <c r="N414" s="2" t="n">
-        <v>42.33</v>
+        <v>45.27</v>
       </c>
       <c r="O414" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31780,7 +31780,7 @@
         <v>45.27</v>
       </c>
       <c r="O414" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31806,6 +31806,79 @@
       <c r="W414" s="2" t="n">
         <v>142.8</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>KORU</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>22.74</v>
+      </c>
+      <c r="D415" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="E415" t="n">
+        <v>22.29</v>
+      </c>
+      <c r="F415" t="n">
+        <v>22.54</v>
+      </c>
+      <c r="G415" t="n">
+        <v>13971555</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="I415" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="J415" t="n">
+        <v>21.32</v>
+      </c>
+      <c r="K415" t="n">
+        <v>20.05</v>
+      </c>
+      <c r="L415" t="n">
+        <v>28.94</v>
+      </c>
+      <c r="M415" t="n">
+        <v>24.01</v>
+      </c>
+      <c r="N415" s="2" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="O415" t="n">
+        <v>31</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="T415" s="2" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="U415" s="2" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31756,7 +31756,7 @@
         <v>21.09</v>
       </c>
       <c r="G414" t="n">
-        <v>21173800</v>
+        <v>21472900</v>
       </c>
       <c r="H414" s="1" t="n">
         <v>5.34</v>
@@ -31825,22 +31825,22 @@
         <v>23.3</v>
       </c>
       <c r="E415" t="n">
-        <v>22.29</v>
+        <v>22.27</v>
       </c>
       <c r="F415" t="n">
-        <v>22.54</v>
+        <v>22.95</v>
       </c>
       <c r="G415" t="n">
-        <v>13971555</v>
+        <v>19798121</v>
       </c>
       <c r="H415" s="1" t="n">
-        <v>6.88</v>
+        <v>8.82</v>
       </c>
       <c r="I415" t="n">
         <v>13.4</v>
       </c>
       <c r="J415" t="n">
-        <v>21.32</v>
+        <v>21.34</v>
       </c>
       <c r="K415" t="n">
         <v>20.05</v>
@@ -31852,7 +31852,7 @@
         <v>24.01</v>
       </c>
       <c r="N415" s="2" t="n">
-        <v>61.1</v>
+        <v>61.97</v>
       </c>
       <c r="O415" t="n">
         <v>31</v>
@@ -31869,13 +31869,13 @@
       </c>
       <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
-        <v>5.25</v>
+        <v>5.28</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>15.8</v>
+        <v>15.3</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>10.4</v>
+        <v>11</v>
       </c>
       <c r="V415" t="inlineStr"/>
       <c r="W415" s="2" t="inlineStr"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31743,25 +31743,41 @@
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr"/>
-      <c r="D414" t="inlineStr"/>
-      <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
+      <c r="C414" t="n">
+        <v>22.74</v>
+      </c>
+      <c r="D414" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="E414" t="n">
+        <v>22.28</v>
+      </c>
+      <c r="F414" t="n">
+        <v>22.95</v>
+      </c>
       <c r="G414" t="n">
-        <v>21457081</v>
-      </c>
-      <c r="H414" s="1" t="n">
-        <v>0</v>
+        <v>21566800</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>8.82</v>
       </c>
       <c r="I414" t="n">
         <v>13.4</v>
       </c>
-      <c r="J414" t="inlineStr"/>
-      <c r="K414" t="inlineStr"/>
-      <c r="L414" t="inlineStr"/>
-      <c r="M414" t="inlineStr"/>
+      <c r="J414" t="n">
+        <v>21.34</v>
+      </c>
+      <c r="K414" t="n">
+        <v>20.05</v>
+      </c>
+      <c r="L414" t="n">
+        <v>28.94</v>
+      </c>
+      <c r="M414" t="n">
+        <v>24.01</v>
+      </c>
       <c r="N414" s="1" t="n">
-        <v>57.66</v>
+        <v>61.97</v>
       </c>
       <c r="O414" t="n">
         <v>31</v>
@@ -31773,7 +31789,7 @@
       </c>
       <c r="Q414" t="inlineStr">
         <is>
-          <t>2x BUY</t>
+          <t>BUY STOP</t>
         </is>
       </c>
       <c r="R414" t="inlineStr"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31630,7 +31630,7 @@
         <v>61.97</v>
       </c>
       <c r="O412" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -764,7 +764,7 @@
         <v>2.11</v>
       </c>
       <c r="K4" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="L4" t="n">
         <v>2.59</v>
@@ -1139,7 +1139,7 @@
         <v>2.17</v>
       </c>
       <c r="K9" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="L9" t="n">
         <v>2.53</v>
@@ -7748,7 +7748,7 @@
         <v>3.48</v>
       </c>
       <c r="K96" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="L96" t="n">
         <v>2.33</v>
@@ -12423,7 +12423,7 @@
         <v>13.4</v>
       </c>
       <c r="J158" t="n">
-        <v>4.85</v>
+        <v>4.86</v>
       </c>
       <c r="K158" t="n">
         <v>4.34</v>
@@ -31630,7 +31630,7 @@
         <v>61.97</v>
       </c>
       <c r="O412" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31656,6 +31656,79 @@
       <c r="W412" s="2" t="n">
         <v>144.9</v>
       </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>KORU</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="D413" t="n">
+        <v>23.17</v>
+      </c>
+      <c r="E413" t="n">
+        <v>22.44</v>
+      </c>
+      <c r="F413" t="n">
+        <v>23.04</v>
+      </c>
+      <c r="G413" t="n">
+        <v>6543136</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="I413" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="J413" t="n">
+        <v>21.32</v>
+      </c>
+      <c r="K413" t="n">
+        <v>19.97</v>
+      </c>
+      <c r="L413" t="n">
+        <v>28.94</v>
+      </c>
+      <c r="M413" t="n">
+        <v>24.09</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>62.09</v>
+      </c>
+      <c r="O413" t="n">
+        <v>44</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>BUY STOP</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31531,7 +31531,7 @@
         <v>22.95</v>
       </c>
       <c r="G411" t="n">
-        <v>21566800</v>
+        <v>21736300</v>
       </c>
       <c r="H411" s="1" t="n">
         <v>8.82</v>
@@ -31593,25 +31593,41 @@
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
+      <c r="C412" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="D412" t="n">
+        <v>23.17</v>
+      </c>
+      <c r="E412" t="n">
+        <v>22.44</v>
+      </c>
+      <c r="F412" t="n">
+        <v>22.78</v>
+      </c>
       <c r="G412" t="n">
-        <v>7691783</v>
-      </c>
-      <c r="H412" s="2" t="n">
-        <v>0</v>
+        <v>7823900</v>
+      </c>
+      <c r="H412" s="3" t="n">
+        <v>-0.74</v>
       </c>
       <c r="I412" t="n">
         <v>13.4</v>
       </c>
-      <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr"/>
-      <c r="L412" t="inlineStr"/>
-      <c r="M412" t="inlineStr"/>
+      <c r="J412" t="n">
+        <v>21.31</v>
+      </c>
+      <c r="K412" t="n">
+        <v>19.97</v>
+      </c>
+      <c r="L412" t="n">
+        <v>28.94</v>
+      </c>
+      <c r="M412" t="n">
+        <v>24.09</v>
+      </c>
       <c r="N412" s="2" t="n">
-        <v>61.9</v>
+        <v>61.33</v>
       </c>
       <c r="O412" t="n">
         <v>43</v>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31630,7 +31630,7 @@
         <v>61.33</v>
       </c>
       <c r="O412" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31656,6 +31656,79 @@
       <c r="W412" s="2" t="n">
         <v>143</v>
       </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>KORU</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>22.33</v>
+      </c>
+      <c r="D413" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="E413" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="F413" t="n">
+        <v>21.98</v>
+      </c>
+      <c r="G413" t="n">
+        <v>7088053</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>-3.51</v>
+      </c>
+      <c r="I413" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="J413" t="n">
+        <v>21.22</v>
+      </c>
+      <c r="K413" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="L413" t="n">
+        <v>28.94</v>
+      </c>
+      <c r="M413" t="n">
+        <v>24.17</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>59.78</v>
+      </c>
+      <c r="O413" t="n">
+        <v>48</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -7895,7 +7895,7 @@
         <v>13.4</v>
       </c>
       <c r="J98" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="K98" t="n">
         <v>2.67</v>
@@ -19651,7 +19651,7 @@
         <v>13.4</v>
       </c>
       <c r="J254" t="n">
-        <v>18.15</v>
+        <v>18.14</v>
       </c>
       <c r="K254" t="n">
         <v>12.11</v>
@@ -19726,7 +19726,7 @@
         <v>13.4</v>
       </c>
       <c r="J255" t="n">
-        <v>18.55</v>
+        <v>18.54</v>
       </c>
       <c r="K255" t="n">
         <v>12.38</v>
@@ -26226,7 +26226,7 @@
         <v>13.4</v>
       </c>
       <c r="J341" t="n">
-        <v>46.66</v>
+        <v>46.67</v>
       </c>
       <c r="K341" t="n">
         <v>35.18</v>
@@ -28741,7 +28741,7 @@
         <v>13.4</v>
       </c>
       <c r="J374" t="n">
-        <v>17.8</v>
+        <v>17.79</v>
       </c>
       <c r="K374" t="n">
         <v>32.76</v>
@@ -29195,7 +29195,7 @@
         <v>13.4</v>
       </c>
       <c r="J380" t="n">
-        <v>18</v>
+        <v>17.99</v>
       </c>
       <c r="K380" t="n">
         <v>31.04</v>
@@ -31606,7 +31606,7 @@
         <v>22.78</v>
       </c>
       <c r="G412" t="n">
-        <v>7823900</v>
+        <v>8118600</v>
       </c>
       <c r="H412" s="3" t="n">
         <v>-0.74</v>
@@ -31675,34 +31675,34 @@
         <v>22.4</v>
       </c>
       <c r="E413" t="n">
-        <v>21.7</v>
+        <v>21.01</v>
       </c>
       <c r="F413" t="n">
-        <v>21.98</v>
+        <v>21.01</v>
       </c>
       <c r="G413" t="n">
-        <v>7088053</v>
+        <v>11782234</v>
       </c>
       <c r="H413" s="3" t="n">
-        <v>-3.51</v>
+        <v>-7.77</v>
       </c>
       <c r="I413" t="n">
         <v>13.4</v>
       </c>
       <c r="J413" t="n">
-        <v>21.22</v>
+        <v>21.17</v>
       </c>
       <c r="K413" t="n">
-        <v>19.99</v>
+        <v>19.97</v>
       </c>
       <c r="L413" t="n">
-        <v>28.94</v>
+        <v>28.93</v>
       </c>
       <c r="M413" t="n">
-        <v>24.17</v>
+        <v>24.16</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>59.78</v>
+        <v>56.86</v>
       </c>
       <c r="O413" t="n">
         <v>48</v>
@@ -31717,15 +31717,19 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R413" t="inlineStr"/>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>1st: MA20, 10% cash</t>
+        </is>
+      </c>
       <c r="S413" t="n">
-        <v>5.28</v>
+        <v>5.27</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>15.4</v>
+        <v>15.1</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="inlineStr"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31593,25 +31593,41 @@
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr"/>
-      <c r="D412" t="inlineStr"/>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
+      <c r="C412" t="n">
+        <v>22.34</v>
+      </c>
+      <c r="D412" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="E412" t="n">
+        <v>21.01</v>
+      </c>
+      <c r="F412" t="n">
+        <v>21.01</v>
+      </c>
       <c r="G412" t="n">
-        <v>12242801</v>
-      </c>
-      <c r="H412" s="2" t="n">
-        <v>0</v>
+        <v>12207900</v>
+      </c>
+      <c r="H412" s="3" t="n">
+        <v>-7.77</v>
       </c>
       <c r="I412" t="n">
         <v>13.4</v>
       </c>
-      <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr"/>
-      <c r="L412" t="inlineStr"/>
-      <c r="M412" t="inlineStr"/>
+      <c r="J412" t="n">
+        <v>21.17</v>
+      </c>
+      <c r="K412" t="n">
+        <v>19.97</v>
+      </c>
+      <c r="L412" t="n">
+        <v>28.93</v>
+      </c>
+      <c r="M412" t="n">
+        <v>24.16</v>
+      </c>
       <c r="N412" s="2" t="n">
-        <v>62.42</v>
+        <v>56.86</v>
       </c>
       <c r="O412" t="n">
         <v>47</v>
@@ -31623,10 +31639,14 @@
       </c>
       <c r="Q412" t="inlineStr">
         <is>
-          <t>BUY STOP</t>
-        </is>
-      </c>
-      <c r="R412" t="inlineStr"/>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R412" t="inlineStr">
+        <is>
+          <t>1st: MA20, 10% cash</t>
+        </is>
+      </c>
       <c r="S412" t="n">
         <v>5.27</v>
       </c>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W412"/>
+  <dimension ref="A1:W413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31661,6 +31661,83 @@
         <v>141.2</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>KORU</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="D413" t="n">
+        <v>19.74</v>
+      </c>
+      <c r="E413" t="n">
+        <v>19.02</v>
+      </c>
+      <c r="F413" t="n">
+        <v>19.73</v>
+      </c>
+      <c r="G413" t="n">
+        <v>12621436</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>-6.09</v>
+      </c>
+      <c r="I413" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="J413" t="n">
+        <v>20.95</v>
+      </c>
+      <c r="K413" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="L413" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="M413" t="n">
+        <v>24.22</v>
+      </c>
+      <c r="N413" s="2" t="n">
+        <v>48.21</v>
+      </c>
+      <c r="O413" t="n">
+        <v>42</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>2nd: MA60, 50% cash, 5d</t>
+        </is>
+      </c>
+      <c r="S413" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="T413" s="2" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="U413" s="2" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -7820,7 +7820,7 @@
         <v>13.4</v>
       </c>
       <c r="J97" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="K97" t="n">
         <v>2.67</v>
@@ -19576,7 +19576,7 @@
         <v>13.4</v>
       </c>
       <c r="J253" t="n">
-        <v>18.14</v>
+        <v>18.15</v>
       </c>
       <c r="K253" t="n">
         <v>12.11</v>
@@ -19651,7 +19651,7 @@
         <v>13.4</v>
       </c>
       <c r="J254" t="n">
-        <v>18.54</v>
+        <v>18.55</v>
       </c>
       <c r="K254" t="n">
         <v>12.38</v>
@@ -26151,7 +26151,7 @@
         <v>13.4</v>
       </c>
       <c r="J340" t="n">
-        <v>46.67</v>
+        <v>46.66</v>
       </c>
       <c r="K340" t="n">
         <v>35.18</v>
@@ -28666,7 +28666,7 @@
         <v>13.4</v>
       </c>
       <c r="J373" t="n">
-        <v>17.79</v>
+        <v>17.8</v>
       </c>
       <c r="K373" t="n">
         <v>32.76</v>
@@ -29120,7 +29120,7 @@
         <v>13.4</v>
       </c>
       <c r="J379" t="n">
-        <v>17.99</v>
+        <v>18</v>
       </c>
       <c r="K379" t="n">
         <v>31.04</v>
@@ -31606,7 +31606,7 @@
         <v>21.01</v>
       </c>
       <c r="G412" t="n">
-        <v>12207900</v>
+        <v>12499500</v>
       </c>
       <c r="H412" s="3" t="n">
         <v>-7.77</v>
@@ -31676,25 +31676,25 @@
         <v>19.6</v>
       </c>
       <c r="D413" t="n">
-        <v>19.74</v>
+        <v>20.4</v>
       </c>
       <c r="E413" t="n">
         <v>19.02</v>
       </c>
       <c r="F413" t="n">
-        <v>19.73</v>
+        <v>20.1</v>
       </c>
       <c r="G413" t="n">
-        <v>12621436</v>
+        <v>21836974</v>
       </c>
       <c r="H413" s="3" t="n">
-        <v>-6.09</v>
+        <v>-4.33</v>
       </c>
       <c r="I413" t="n">
         <v>13.4</v>
       </c>
       <c r="J413" t="n">
-        <v>20.95</v>
+        <v>20.96</v>
       </c>
       <c r="K413" t="n">
         <v>19.9</v>
@@ -31703,13 +31703,13 @@
         <v>28.9</v>
       </c>
       <c r="M413" t="n">
-        <v>24.22</v>
+        <v>24.23</v>
       </c>
       <c r="N413" s="2" t="n">
-        <v>48.21</v>
+        <v>49.17</v>
       </c>
       <c r="O413" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31721,19 +31721,15 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R413" t="inlineStr">
-        <is>
-          <t>2nd: MA60, 50% cash, 5d</t>
-        </is>
-      </c>
+      <c r="R413" t="inlineStr"/>
       <c r="S413" t="n">
-        <v>5.32</v>
+        <v>5.28</v>
       </c>
       <c r="T413" s="2" t="n">
-        <v>15.8</v>
+        <v>15.1</v>
       </c>
       <c r="U413" s="2" t="n">
-        <v>7.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="inlineStr"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31672,41 +31672,25 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="C413" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="D413" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="E413" t="n">
-        <v>19.02</v>
-      </c>
-      <c r="F413" t="n">
-        <v>20.1</v>
-      </c>
+      <c r="C413" t="inlineStr"/>
+      <c r="D413" t="inlineStr"/>
+      <c r="E413" t="inlineStr"/>
+      <c r="F413" t="inlineStr"/>
       <c r="G413" t="n">
-        <v>21836974</v>
-      </c>
-      <c r="H413" s="3" t="n">
-        <v>-4.33</v>
+        <v>21954619</v>
+      </c>
+      <c r="H413" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I413" t="n">
         <v>13.4</v>
       </c>
-      <c r="J413" t="n">
-        <v>20.96</v>
-      </c>
-      <c r="K413" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="L413" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="M413" t="n">
-        <v>24.23</v>
-      </c>
+      <c r="J413" t="inlineStr"/>
+      <c r="K413" t="inlineStr"/>
+      <c r="L413" t="inlineStr"/>
+      <c r="M413" t="inlineStr"/>
       <c r="N413" s="2" t="n">
-        <v>49.17</v>
+        <v>51.69</v>
       </c>
       <c r="O413" t="n">
         <v>45</v>
@@ -31732,7 +31716,9 @@
         <v>9.300000000000001</v>
       </c>
       <c r="V413" t="inlineStr"/>
-      <c r="W413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="n">
+        <v>141.8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31672,25 +31672,41 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="C413" t="inlineStr"/>
-      <c r="D413" t="inlineStr"/>
-      <c r="E413" t="inlineStr"/>
-      <c r="F413" t="inlineStr"/>
+      <c r="C413" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="D413" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="E413" t="n">
+        <v>19.03</v>
+      </c>
+      <c r="F413" t="n">
+        <v>20.05</v>
+      </c>
       <c r="G413" t="n">
-        <v>21954619</v>
-      </c>
-      <c r="H413" s="2" t="n">
-        <v>0</v>
+        <v>22189000</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>-4.57</v>
       </c>
       <c r="I413" t="n">
         <v>13.4</v>
       </c>
-      <c r="J413" t="inlineStr"/>
-      <c r="K413" t="inlineStr"/>
-      <c r="L413" t="inlineStr"/>
-      <c r="M413" t="inlineStr"/>
+      <c r="J413" t="n">
+        <v>20.96</v>
+      </c>
+      <c r="K413" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="L413" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="M413" t="n">
+        <v>24.23</v>
+      </c>
       <c r="N413" s="2" t="n">
-        <v>51.69</v>
+        <v>49.04</v>
       </c>
       <c r="O413" t="n">
         <v>45</v>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31709,7 +31709,7 @@
         <v>49.04</v>
       </c>
       <c r="O413" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31735,6 +31735,83 @@
       <c r="W413" s="2" t="n">
         <v>141.8</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>KORU</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="D414" t="n">
+        <v>18.82</v>
+      </c>
+      <c r="E414" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="F414" t="n">
+        <v>18.27</v>
+      </c>
+      <c r="G414" t="n">
+        <v>18805346</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>-8.880000000000001</v>
+      </c>
+      <c r="I414" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="J414" t="n">
+        <v>20.82</v>
+      </c>
+      <c r="K414" t="n">
+        <v>19.84</v>
+      </c>
+      <c r="L414" t="n">
+        <v>28.84</v>
+      </c>
+      <c r="M414" t="n">
+        <v>24.28</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="O414" t="n">
+        <v>41</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>2nd: MA60, 50% cash, 5d</t>
+        </is>
+      </c>
+      <c r="S414" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31685,7 +31685,7 @@
         <v>20.05</v>
       </c>
       <c r="G413" t="n">
-        <v>22189000</v>
+        <v>23053000</v>
       </c>
       <c r="H413" s="3" t="n">
         <v>-4.57</v>
@@ -31754,37 +31754,37 @@
         <v>18.82</v>
       </c>
       <c r="E414" t="n">
-        <v>18.15</v>
+        <v>16.95</v>
       </c>
       <c r="F414" t="n">
-        <v>18.27</v>
+        <v>17.65</v>
       </c>
       <c r="G414" t="n">
-        <v>18805346</v>
+        <v>37679009</v>
       </c>
       <c r="H414" s="3" t="n">
-        <v>-8.880000000000001</v>
+        <v>-11.97</v>
       </c>
       <c r="I414" t="n">
         <v>13.4</v>
       </c>
       <c r="J414" t="n">
-        <v>20.82</v>
+        <v>20.79</v>
       </c>
       <c r="K414" t="n">
-        <v>19.84</v>
+        <v>19.83</v>
       </c>
       <c r="L414" t="n">
-        <v>28.84</v>
+        <v>28.83</v>
       </c>
       <c r="M414" t="n">
         <v>24.28</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>45.6</v>
+        <v>44.24</v>
       </c>
       <c r="O414" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31802,13 +31802,13 @@
         </is>
       </c>
       <c r="S414" t="n">
-        <v>5.3</v>
+        <v>5.23</v>
       </c>
       <c r="T414" s="2" t="n">
         <v>15.4</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>7.6</v>
+        <v>10.2</v>
       </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="inlineStr"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31754,13 +31754,13 @@
         <v>18.82</v>
       </c>
       <c r="E414" t="n">
-        <v>16.95</v>
+        <v>16.96</v>
       </c>
       <c r="F414" t="n">
         <v>17.65</v>
       </c>
       <c r="G414" t="n">
-        <v>37679009</v>
+        <v>37891400</v>
       </c>
       <c r="H414" s="3" t="n">
         <v>-11.97</v>
@@ -31811,7 +31811,9 @@
         <v>10.2</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="n">
+        <v>149.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31784,7 +31784,7 @@
         <v>44.24</v>
       </c>
       <c r="O414" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31814,6 +31814,79 @@
       <c r="W414" s="2" t="n">
         <v>149.2</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>KORU</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="D415" t="n">
+        <v>18.22</v>
+      </c>
+      <c r="E415" t="n">
+        <v>17.66</v>
+      </c>
+      <c r="F415" t="n">
+        <v>17.84</v>
+      </c>
+      <c r="G415" t="n">
+        <v>7547909</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="I415" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="J415" t="n">
+        <v>20.52</v>
+      </c>
+      <c r="K415" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="L415" t="n">
+        <v>28.78</v>
+      </c>
+      <c r="M415" t="n">
+        <v>24.33</v>
+      </c>
+      <c r="N415" s="2" t="n">
+        <v>37.22</v>
+      </c>
+      <c r="O415" t="n">
+        <v>44</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="T415" s="2" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="U415" s="2" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31760,7 +31760,7 @@
         <v>17.65</v>
       </c>
       <c r="G414" t="n">
-        <v>37891400</v>
+        <v>38427600</v>
       </c>
       <c r="H414" s="3" t="n">
         <v>-11.97</v>
@@ -31833,16 +31833,16 @@
         <v>18.22</v>
       </c>
       <c r="E415" t="n">
-        <v>17.66</v>
+        <v>17.65</v>
       </c>
       <c r="F415" t="n">
-        <v>17.84</v>
+        <v>17.85</v>
       </c>
       <c r="G415" t="n">
-        <v>7547909</v>
+        <v>10724629</v>
       </c>
       <c r="H415" s="1" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="I415" t="n">
         <v>13.4</v>
@@ -31860,10 +31860,10 @@
         <v>24.33</v>
       </c>
       <c r="N415" s="2" t="n">
-        <v>37.22</v>
+        <v>37.26</v>
       </c>
       <c r="O415" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31877,13 +31877,13 @@
       </c>
       <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
-        <v>5.26</v>
+        <v>5.24</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>7.3</v>
+        <v>9.1</v>
       </c>
       <c r="V415" t="inlineStr"/>
       <c r="W415" s="2" t="inlineStr"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31826,41 +31826,25 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="C415" t="n">
-        <v>18.15</v>
-      </c>
-      <c r="D415" t="n">
-        <v>18.22</v>
-      </c>
-      <c r="E415" t="n">
-        <v>17.65</v>
-      </c>
-      <c r="F415" t="n">
-        <v>17.85</v>
-      </c>
+      <c r="C415" t="inlineStr"/>
+      <c r="D415" t="inlineStr"/>
+      <c r="E415" t="inlineStr"/>
+      <c r="F415" t="inlineStr"/>
       <c r="G415" t="n">
-        <v>10724629</v>
-      </c>
-      <c r="H415" s="1" t="n">
-        <v>1.13</v>
+        <v>10808321</v>
+      </c>
+      <c r="H415" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I415" t="n">
         <v>13.4</v>
       </c>
-      <c r="J415" t="n">
-        <v>20.52</v>
-      </c>
-      <c r="K415" t="n">
-        <v>19.82</v>
-      </c>
-      <c r="L415" t="n">
-        <v>28.78</v>
-      </c>
-      <c r="M415" t="n">
-        <v>24.33</v>
-      </c>
+      <c r="J415" t="inlineStr"/>
+      <c r="K415" t="inlineStr"/>
+      <c r="L415" t="inlineStr"/>
+      <c r="M415" t="inlineStr"/>
       <c r="N415" s="2" t="n">
-        <v>37.26</v>
+        <v>36.57</v>
       </c>
       <c r="O415" t="n">
         <v>45</v>
@@ -31886,7 +31870,9 @@
         <v>9.1</v>
       </c>
       <c r="V415" t="inlineStr"/>
-      <c r="W415" s="2" t="inlineStr"/>
+      <c r="W415" s="2" t="n">
+        <v>154.3</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31826,25 +31826,41 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
-      <c r="D415" t="inlineStr"/>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
+      <c r="C415" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="D415" t="n">
+        <v>18.22</v>
+      </c>
+      <c r="E415" t="n">
+        <v>17.65</v>
+      </c>
+      <c r="F415" t="n">
+        <v>17.85</v>
+      </c>
       <c r="G415" t="n">
-        <v>10808321</v>
-      </c>
-      <c r="H415" s="2" t="n">
-        <v>0</v>
+        <v>10883500</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>1.13</v>
       </c>
       <c r="I415" t="n">
         <v>13.4</v>
       </c>
-      <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr"/>
-      <c r="L415" t="inlineStr"/>
-      <c r="M415" t="inlineStr"/>
+      <c r="J415" t="n">
+        <v>20.52</v>
+      </c>
+      <c r="K415" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="L415" t="n">
+        <v>28.78</v>
+      </c>
+      <c r="M415" t="n">
+        <v>24.33</v>
+      </c>
       <c r="N415" s="2" t="n">
-        <v>36.57</v>
+        <v>37.26</v>
       </c>
       <c r="O415" t="n">
         <v>45</v>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -608,7 +608,7 @@
         <v>1.22</v>
       </c>
       <c r="I2" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J2" t="n">
         <v>2.14</v>
@@ -683,7 +683,7 @@
         <v>-4.84</v>
       </c>
       <c r="I3" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J3" t="n">
         <v>2.15</v>
@@ -758,7 +758,7 @@
         <v>-0.42</v>
       </c>
       <c r="I4" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J4" t="n">
         <v>2.15</v>
@@ -833,7 +833,7 @@
         <v>0.43</v>
       </c>
       <c r="I5" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J5" t="n">
         <v>2.17</v>
@@ -908,7 +908,7 @@
         <v>1.69</v>
       </c>
       <c r="I6" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J6" t="n">
         <v>2.19</v>
@@ -983,7 +983,7 @@
         <v>-10</v>
       </c>
       <c r="I7" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J7" t="n">
         <v>2.19</v>
@@ -1062,7 +1062,7 @@
         <v>-6.94</v>
       </c>
       <c r="I8" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J8" t="n">
         <v>2.19</v>
@@ -1141,7 +1141,7 @@
         <v>-1.49</v>
       </c>
       <c r="I9" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J9" t="n">
         <v>2.19</v>
@@ -1216,7 +1216,7 @@
         <v>1.01</v>
       </c>
       <c r="I10" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J10" t="n">
         <v>2.19</v>
@@ -1291,7 +1291,7 @@
         <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J11" t="n">
         <v>2.2</v>
@@ -1366,7 +1366,7 @@
         <v>-5.56</v>
       </c>
       <c r="I12" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J12" t="n">
         <v>2.2</v>
@@ -1445,7 +1445,7 @@
         <v>3.43</v>
       </c>
       <c r="I13" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J13" t="n">
         <v>2.2</v>
@@ -1520,7 +1520,7 @@
         <v>-8.529999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J14" t="n">
         <v>2.2</v>
@@ -1603,7 +1603,7 @@
         <v>3.11</v>
       </c>
       <c r="I15" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J15" t="n">
         <v>2.19</v>
@@ -1682,7 +1682,7 @@
         <v>7.04</v>
       </c>
       <c r="I16" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J16" t="n">
         <v>2.19</v>
@@ -1757,7 +1757,7 @@
         <v>-3.76</v>
       </c>
       <c r="I17" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J17" t="n">
         <v>2.19</v>
@@ -1836,7 +1836,7 @@
         <v>4.88</v>
       </c>
       <c r="I18" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J18" t="n">
         <v>2.19</v>
@@ -1911,7 +1911,7 @@
         <v>8.84</v>
       </c>
       <c r="I19" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J19" t="n">
         <v>2.19</v>
@@ -1986,7 +1986,7 @@
         <v>-4.7</v>
       </c>
       <c r="I20" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J20" t="n">
         <v>2.18</v>
@@ -2061,7 +2061,7 @@
         <v>1.35</v>
       </c>
       <c r="I21" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J21" t="n">
         <v>2.17</v>
@@ -2136,7 +2136,7 @@
         <v>-2.65</v>
       </c>
       <c r="I22" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J22" t="n">
         <v>2.16</v>
@@ -2211,7 +2211,7 @@
         <v>0.91</v>
       </c>
       <c r="I23" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J23" t="n">
         <v>2.15</v>
@@ -2286,7 +2286,7 @@
         <v>2.25</v>
       </c>
       <c r="I24" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J24" t="n">
         <v>2.15</v>
@@ -2361,7 +2361,7 @@
         <v>-1.32</v>
       </c>
       <c r="I25" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J25" t="n">
         <v>2.14</v>
@@ -2436,7 +2436,7 @@
         <v>-1.34</v>
       </c>
       <c r="I26" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J26" t="n">
         <v>2.13</v>
@@ -2511,7 +2511,7 @@
         <v>-1.81</v>
       </c>
       <c r="I27" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J27" t="n">
         <v>2.13</v>
@@ -2586,7 +2586,7 @@
         <v>-9.220000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J28" t="n">
         <v>2.13</v>
@@ -2665,7 +2665,7 @@
         <v>-4.06</v>
       </c>
       <c r="I29" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J29" t="n">
         <v>2.13</v>
@@ -2740,7 +2740,7 @@
         <v>4.76</v>
       </c>
       <c r="I30" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J30" t="n">
         <v>2.13</v>
@@ -2815,7 +2815,7 @@
         <v>-1.01</v>
       </c>
       <c r="I31" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J31" t="n">
         <v>2.12</v>
@@ -2890,7 +2890,7 @@
         <v>-8.67</v>
       </c>
       <c r="I32" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J32" t="n">
         <v>2.1</v>
@@ -2969,7 +2969,7 @@
         <v>-10.61</v>
       </c>
       <c r="I33" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J33" t="n">
         <v>2.08</v>
@@ -3052,7 +3052,7 @@
         <v>-3.12</v>
       </c>
       <c r="I34" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J34" t="n">
         <v>2.06</v>
@@ -3135,7 +3135,7 @@
         <v>-10.32</v>
       </c>
       <c r="I35" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J35" t="n">
         <v>2.03</v>
@@ -3218,7 +3218,7 @@
         <v>24.46</v>
       </c>
       <c r="I36" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J36" t="n">
         <v>2.01</v>
@@ -3297,7 +3297,7 @@
         <v>-6.94</v>
       </c>
       <c r="I37" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J37" t="n">
         <v>1.99</v>
@@ -3376,7 +3376,7 @@
         <v>14.29</v>
       </c>
       <c r="I38" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J38" t="n">
         <v>1.97</v>
@@ -3455,7 +3455,7 @@
         <v>-0.54</v>
       </c>
       <c r="I39" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J39" t="n">
         <v>1.95</v>
@@ -3530,7 +3530,7 @@
         <v>0.55</v>
       </c>
       <c r="I40" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J40" t="n">
         <v>1.93</v>
@@ -3605,7 +3605,7 @@
         <v>-2.17</v>
       </c>
       <c r="I41" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J41" t="n">
         <v>1.9</v>
@@ -3684,7 +3684,7 @@
         <v>1.67</v>
       </c>
       <c r="I42" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J42" t="n">
         <v>1.89</v>
@@ -3763,7 +3763,7 @@
         <v>0.55</v>
       </c>
       <c r="I43" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J43" t="n">
         <v>1.87</v>
@@ -3838,7 +3838,7 @@
         <v>2.17</v>
       </c>
       <c r="I44" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J44" t="n">
         <v>1.85</v>
@@ -3913,7 +3913,7 @@
         <v>3.72</v>
       </c>
       <c r="I45" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J45" t="n">
         <v>1.83</v>
@@ -3992,7 +3992,7 @@
         <v>2.05</v>
       </c>
       <c r="I46" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J46" t="n">
         <v>1.82</v>
@@ -4067,7 +4067,7 @@
         <v>-0.5</v>
       </c>
       <c r="I47" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J47" t="n">
         <v>1.81</v>
@@ -4142,7 +4142,7 @@
         <v>-1.01</v>
       </c>
       <c r="I48" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J48" t="n">
         <v>1.81</v>
@@ -4217,7 +4217,7 @@
         <v>2.55</v>
       </c>
       <c r="I49" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J49" t="n">
         <v>1.82</v>
@@ -4292,7 +4292,7 @@
         <v>0.5</v>
       </c>
       <c r="I50" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J50" t="n">
         <v>1.82</v>
@@ -4367,7 +4367,7 @@
         <v>-2.97</v>
       </c>
       <c r="I51" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J51" t="n">
         <v>1.82</v>
@@ -4442,7 +4442,7 @@
         <v>10.71</v>
       </c>
       <c r="I52" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J52" t="n">
         <v>1.84</v>
@@ -4517,7 +4517,7 @@
         <v>4.15</v>
       </c>
       <c r="I53" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J53" t="n">
         <v>1.87</v>
@@ -4592,7 +4592,7 @@
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J54" t="n">
         <v>1.91</v>
@@ -4667,7 +4667,7 @@
         <v>-3.54</v>
       </c>
       <c r="I55" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J55" t="n">
         <v>1.95</v>
@@ -4742,7 +4742,7 @@
         <v>-3.21</v>
       </c>
       <c r="I56" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J56" t="n">
         <v>1.97</v>
@@ -4817,7 +4817,7 @@
         <v>2.84</v>
       </c>
       <c r="I57" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J57" t="n">
         <v>1.99</v>
@@ -4892,7 +4892,7 @@
         <v>1.38</v>
       </c>
       <c r="I58" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J58" t="n">
         <v>2.01</v>
@@ -4967,7 +4967,7 @@
         <v>0.45</v>
       </c>
       <c r="I59" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J59" t="n">
         <v>2.03</v>
@@ -5042,7 +5042,7 @@
         <v>2.71</v>
       </c>
       <c r="I60" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J60" t="n">
         <v>2.05</v>
@@ -5117,7 +5117,7 @@
         <v>0.88</v>
       </c>
       <c r="I61" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J61" t="n">
         <v>2.08</v>
@@ -5192,7 +5192,7 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J62" t="n">
         <v>2.1</v>
@@ -5267,7 +5267,7 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J63" t="n">
         <v>2.12</v>
@@ -5342,7 +5342,7 @@
         <v>-2.18</v>
       </c>
       <c r="I64" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J64" t="n">
         <v>2.14</v>
@@ -5417,7 +5417,7 @@
         <v>3.57</v>
       </c>
       <c r="I65" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J65" t="n">
         <v>2.16</v>
@@ -5492,7 +5492,7 @@
         <v>-3.88</v>
       </c>
       <c r="I66" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J66" t="n">
         <v>2.17</v>
@@ -5567,7 +5567,7 @@
         <v>3.14</v>
       </c>
       <c r="I67" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J67" t="n">
         <v>2.19</v>
@@ -5642,7 +5642,7 @@
         <v>4.78</v>
       </c>
       <c r="I68" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J68" t="n">
         <v>2.21</v>
@@ -5717,7 +5717,7 @@
         <v>3.73</v>
       </c>
       <c r="I69" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J69" t="n">
         <v>2.23</v>
@@ -5792,7 +5792,7 @@
         <v>5.2</v>
       </c>
       <c r="I70" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J70" t="n">
         <v>2.26</v>
@@ -5867,7 +5867,7 @@
         <v>-5.7</v>
       </c>
       <c r="I71" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J71" t="n">
         <v>2.29</v>
@@ -5942,7 +5942,7 @@
         <v>5.65</v>
       </c>
       <c r="I72" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J72" t="n">
         <v>2.31</v>
@@ -6017,7 +6017,7 @@
         <v>1.15</v>
       </c>
       <c r="I73" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J73" t="n">
         <v>2.33</v>
@@ -6092,7 +6092,7 @@
         <v>9.43</v>
       </c>
       <c r="I74" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J74" t="n">
         <v>2.36</v>
@@ -6167,7 +6167,7 @@
         <v>6.55</v>
       </c>
       <c r="I75" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J75" t="n">
         <v>2.41</v>
@@ -6242,7 +6242,7 @@
         <v>0.65</v>
       </c>
       <c r="I76" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J76" t="n">
         <v>2.46</v>
@@ -6317,7 +6317,7 @@
         <v>4.5</v>
       </c>
       <c r="I77" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J77" t="n">
         <v>2.51</v>
@@ -6392,7 +6392,7 @@
         <v>-1.54</v>
       </c>
       <c r="I78" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J78" t="n">
         <v>2.56</v>
@@ -6467,7 +6467,7 @@
         <v>3.75</v>
       </c>
       <c r="I79" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J79" t="n">
         <v>2.62</v>
@@ -6542,7 +6542,7 @@
         <v>3.31</v>
       </c>
       <c r="I80" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J80" t="n">
         <v>2.68</v>
@@ -6617,7 +6617,7 @@
         <v>-5.83</v>
       </c>
       <c r="I81" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J81" t="n">
         <v>2.72</v>
@@ -6692,7 +6692,7 @@
         <v>8.050000000000001</v>
       </c>
       <c r="I82" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J82" t="n">
         <v>2.78</v>
@@ -6767,7 +6767,7 @@
         <v>-6.88</v>
       </c>
       <c r="I83" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J83" t="n">
         <v>2.83</v>
@@ -6842,7 +6842,7 @@
         <v>5.23</v>
       </c>
       <c r="I84" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J84" t="n">
         <v>2.89</v>
@@ -6917,7 +6917,7 @@
         <v>2.92</v>
       </c>
       <c r="I85" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J85" t="n">
         <v>2.95</v>
@@ -6992,7 +6992,7 @@
         <v>3.69</v>
       </c>
       <c r="I86" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J86" t="n">
         <v>3.02</v>
@@ -7067,7 +7067,7 @@
         <v>14.25</v>
       </c>
       <c r="I87" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J87" t="n">
         <v>3.12</v>
@@ -7142,7 +7142,7 @@
         <v>-1.2</v>
       </c>
       <c r="I88" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J88" t="n">
         <v>3.2</v>
@@ -7217,7 +7217,7 @@
         <v>-1.94</v>
       </c>
       <c r="I89" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J89" t="n">
         <v>3.28</v>
@@ -7292,7 +7292,7 @@
         <v>-4.95</v>
       </c>
       <c r="I90" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J90" t="n">
         <v>3.34</v>
@@ -7367,7 +7367,7 @@
         <v>4.17</v>
       </c>
       <c r="I91" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J91" t="n">
         <v>3.42</v>
@@ -7442,7 +7442,7 @@
         <v>-0.5</v>
       </c>
       <c r="I92" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J92" t="n">
         <v>3.48</v>
@@ -7517,7 +7517,7 @@
         <v>1.26</v>
       </c>
       <c r="I93" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J93" t="n">
         <v>3.55</v>
@@ -7592,7 +7592,7 @@
         <v>2.73</v>
       </c>
       <c r="I94" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J94" t="n">
         <v>3.61</v>
@@ -7667,7 +7667,7 @@
         <v>-10.39</v>
       </c>
       <c r="I95" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J95" t="n">
         <v>3.65</v>
@@ -7742,7 +7742,7 @@
         <v>8.09</v>
       </c>
       <c r="I96" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J96" t="n">
         <v>3.69</v>
@@ -7817,7 +7817,7 @@
         <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J97" t="n">
         <v>3.73</v>
@@ -7892,7 +7892,7 @@
         <v>4.49</v>
       </c>
       <c r="I98" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J98" t="n">
         <v>3.78</v>
@@ -7967,7 +7967,7 @@
         <v>-2.39</v>
       </c>
       <c r="I99" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J99" t="n">
         <v>3.82</v>
@@ -8042,7 +8042,7 @@
         <v>2.44</v>
       </c>
       <c r="I100" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J100" t="n">
         <v>3.85</v>
@@ -8117,7 +8117,7 @@
         <v>-0.48</v>
       </c>
       <c r="I101" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J101" t="n">
         <v>3.9</v>
@@ -8192,7 +8192,7 @@
         <v>0</v>
       </c>
       <c r="I102" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J102" t="n">
         <v>3.94</v>
@@ -8267,7 +8267,7 @@
         <v>-0.24</v>
       </c>
       <c r="I103" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J103" t="n">
         <v>3.98</v>
@@ -8342,7 +8342,7 @@
         <v>-2.64</v>
       </c>
       <c r="I104" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J104" t="n">
         <v>4.01</v>
@@ -8417,7 +8417,7 @@
         <v>5.93</v>
       </c>
       <c r="I105" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J105" t="n">
         <v>4.05</v>
@@ -8492,7 +8492,7 @@
         <v>-3.73</v>
       </c>
       <c r="I106" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J106" t="n">
         <v>4.07</v>
@@ -8567,7 +8567,7 @@
         <v>3.63</v>
       </c>
       <c r="I107" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J107" t="n">
         <v>4.08</v>
@@ -8642,7 +8642,7 @@
         <v>-2.1</v>
       </c>
       <c r="I108" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J108" t="n">
         <v>4.08</v>
@@ -8717,7 +8717,7 @@
         <v>-0.48</v>
       </c>
       <c r="I109" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J109" t="n">
         <v>4.09</v>
@@ -8792,7 +8792,7 @@
         <v>-2.16</v>
       </c>
       <c r="I110" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J110" t="n">
         <v>4.1</v>
@@ -8871,7 +8871,7 @@
         <v>3.19</v>
       </c>
       <c r="I111" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J111" t="n">
         <v>4.11</v>
@@ -8946,7 +8946,7 @@
         <v>0.95</v>
       </c>
       <c r="I112" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J112" t="n">
         <v>4.13</v>
@@ -9021,7 +9021,7 @@
         <v>-3.76</v>
       </c>
       <c r="I113" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J113" t="n">
         <v>4.13</v>
@@ -9100,7 +9100,7 @@
         <v>-9.050000000000001</v>
       </c>
       <c r="I114" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J114" t="n">
         <v>4.11</v>
@@ -9175,7 +9175,7 @@
         <v>7.26</v>
       </c>
       <c r="I115" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J115" t="n">
         <v>4.12</v>
@@ -9250,7 +9250,7 @@
         <v>2.26</v>
       </c>
       <c r="I116" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J116" t="n">
         <v>4.13</v>
@@ -9325,7 +9325,7 @@
         <v>0.98</v>
       </c>
       <c r="I117" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J117" t="n">
         <v>4.13</v>
@@ -9400,7 +9400,7 @@
         <v>0.97</v>
       </c>
       <c r="I118" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J118" t="n">
         <v>4.13</v>
@@ -9475,7 +9475,7 @@
         <v>0.24</v>
       </c>
       <c r="I119" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J119" t="n">
         <v>4.13</v>
@@ -9550,7 +9550,7 @@
         <v>-1.92</v>
       </c>
       <c r="I120" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J120" t="n">
         <v>4.13</v>
@@ -9629,7 +9629,7 @@
         <v>4.16</v>
       </c>
       <c r="I121" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J121" t="n">
         <v>4.13</v>
@@ -9704,7 +9704,7 @@
         <v>2.58</v>
       </c>
       <c r="I122" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J122" t="n">
         <v>4.14</v>
@@ -9779,7 +9779,7 @@
         <v>-4.12</v>
       </c>
       <c r="I123" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J123" t="n">
         <v>4.14</v>
@@ -9854,7 +9854,7 @@
         <v>-1.19</v>
       </c>
       <c r="I124" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J124" t="n">
         <v>4.15</v>
@@ -9933,7 +9933,7 @@
         <v>-2.42</v>
       </c>
       <c r="I125" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J125" t="n">
         <v>4.14</v>
@@ -10008,7 +10008,7 @@
         <v>-5.45</v>
       </c>
       <c r="I126" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J126" t="n">
         <v>4.12</v>
@@ -10083,7 +10083,7 @@
         <v>-0.52</v>
       </c>
       <c r="I127" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J127" t="n">
         <v>4.1</v>
@@ -10158,7 +10158,7 @@
         <v>-0.79</v>
       </c>
       <c r="I128" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J128" t="n">
         <v>4.08</v>
@@ -10237,7 +10237,7 @@
         <v>9.81</v>
       </c>
       <c r="I129" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J129" t="n">
         <v>4.07</v>
@@ -10312,7 +10312,7 @@
         <v>-3.38</v>
       </c>
       <c r="I130" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J130" t="n">
         <v>4.07</v>
@@ -10391,7 +10391,7 @@
         <v>-1.5</v>
       </c>
       <c r="I131" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J131" t="n">
         <v>4.06</v>
@@ -10466,7 +10466,7 @@
         <v>0.51</v>
       </c>
       <c r="I132" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J132" t="n">
         <v>4.04</v>
@@ -10541,7 +10541,7 @@
         <v>4.55</v>
       </c>
       <c r="I133" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J133" t="n">
         <v>4.04</v>
@@ -10616,7 +10616,7 @@
         <v>-5.56</v>
       </c>
       <c r="I134" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J134" t="n">
         <v>4.05</v>
@@ -10695,7 +10695,7 @@
         <v>-1.53</v>
       </c>
       <c r="I135" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J135" t="n">
         <v>4.05</v>
@@ -10770,7 +10770,7 @@
         <v>3.9</v>
       </c>
       <c r="I136" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J136" t="n">
         <v>4.04</v>
@@ -10845,7 +10845,7 @@
         <v>0.75</v>
       </c>
       <c r="I137" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J137" t="n">
         <v>4.04</v>
@@ -10920,7 +10920,7 @@
         <v>2.23</v>
       </c>
       <c r="I138" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J138" t="n">
         <v>4.04</v>
@@ -10995,7 +10995,7 @@
         <v>1.94</v>
       </c>
       <c r="I139" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J139" t="n">
         <v>4.04</v>
@@ -11070,7 +11070,7 @@
         <v>3.1</v>
       </c>
       <c r="I140" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J140" t="n">
         <v>4.05</v>
@@ -11145,7 +11145,7 @@
         <v>6.93</v>
       </c>
       <c r="I141" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J141" t="n">
         <v>4.07</v>
@@ -11220,7 +11220,7 @@
         <v>4.75</v>
       </c>
       <c r="I142" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J142" t="n">
         <v>4.09</v>
@@ -11295,7 +11295,7 @@
         <v>3.09</v>
       </c>
       <c r="I143" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J143" t="n">
         <v>4.13</v>
@@ -11370,7 +11370,7 @@
         <v>2</v>
       </c>
       <c r="I144" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J144" t="n">
         <v>4.18</v>
@@ -11445,7 +11445,7 @@
         <v>5.69</v>
       </c>
       <c r="I145" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J145" t="n">
         <v>4.25</v>
@@ -11520,7 +11520,7 @@
         <v>-3.34</v>
       </c>
       <c r="I146" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J146" t="n">
         <v>4.32</v>
@@ -11595,7 +11595,7 @@
         <v>3.65</v>
       </c>
       <c r="I147" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J147" t="n">
         <v>4.4</v>
@@ -11670,7 +11670,7 @@
         <v>-2.96</v>
       </c>
       <c r="I148" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J148" t="n">
         <v>4.47</v>
@@ -11745,7 +11745,7 @@
         <v>5.92</v>
       </c>
       <c r="I149" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J149" t="n">
         <v>4.54</v>
@@ -11820,7 +11820,7 @@
         <v>-0.54</v>
       </c>
       <c r="I150" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J150" t="n">
         <v>4.62</v>
@@ -11895,7 +11895,7 @@
         <v>-5.25</v>
       </c>
       <c r="I151" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J151" t="n">
         <v>4.68</v>
@@ -11970,7 +11970,7 @@
         <v>-0.57</v>
       </c>
       <c r="I152" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J152" t="n">
         <v>4.74</v>
@@ -12045,7 +12045,7 @@
         <v>-3.85</v>
       </c>
       <c r="I153" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J153" t="n">
         <v>4.79</v>
@@ -12120,7 +12120,7 @@
         <v>5</v>
       </c>
       <c r="I154" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J154" t="n">
         <v>4.85</v>
@@ -12195,7 +12195,7 @@
         <v>-0.38</v>
       </c>
       <c r="I155" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J155" t="n">
         <v>4.92</v>
@@ -12270,7 +12270,7 @@
         <v>6.5</v>
       </c>
       <c r="I156" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J156" t="n">
         <v>5</v>
@@ -12345,7 +12345,7 @@
         <v>6.1</v>
       </c>
       <c r="I157" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J157" t="n">
         <v>5.1</v>
@@ -12420,7 +12420,7 @@
         <v>1.18</v>
       </c>
       <c r="I158" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J158" t="n">
         <v>5.19</v>
@@ -12495,7 +12495,7 @@
         <v>3.18</v>
       </c>
       <c r="I159" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J159" t="n">
         <v>5.29</v>
@@ -12570,7 +12570,7 @@
         <v>-4.86</v>
       </c>
       <c r="I160" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J160" t="n">
         <v>5.36</v>
@@ -12645,7 +12645,7 @@
         <v>2.73</v>
       </c>
       <c r="I161" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J161" t="n">
         <v>5.44</v>
@@ -12720,7 +12720,7 @@
         <v>-2.65</v>
       </c>
       <c r="I162" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J162" t="n">
         <v>5.49</v>
@@ -12795,7 +12795,7 @@
         <v>-9.710000000000001</v>
       </c>
       <c r="I163" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J163" t="n">
         <v>5.5</v>
@@ -12874,7 +12874,7 @@
         <v>10.38</v>
       </c>
       <c r="I164" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J164" t="n">
         <v>5.54</v>
@@ -12949,7 +12949,7 @@
         <v>-3.25</v>
       </c>
       <c r="I165" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J165" t="n">
         <v>5.55</v>
@@ -13024,7 +13024,7 @@
         <v>8.83</v>
       </c>
       <c r="I166" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J166" t="n">
         <v>5.6</v>
@@ -13099,7 +13099,7 @@
         <v>9.58</v>
       </c>
       <c r="I167" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J167" t="n">
         <v>5.67</v>
@@ -13174,7 +13174,7 @@
         <v>2.07</v>
       </c>
       <c r="I168" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J168" t="n">
         <v>5.75</v>
@@ -13249,7 +13249,7 @@
         <v>6.68</v>
       </c>
       <c r="I169" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J169" t="n">
         <v>5.84</v>
@@ -13324,7 +13324,7 @@
         <v>-6.12</v>
       </c>
       <c r="I170" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J170" t="n">
         <v>5.91</v>
@@ -13399,7 +13399,7 @@
         <v>2.75</v>
       </c>
       <c r="I171" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J171" t="n">
         <v>6</v>
@@ -13474,7 +13474,7 @@
         <v>1.97</v>
       </c>
       <c r="I172" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J172" t="n">
         <v>6.1</v>
@@ -13549,7 +13549,7 @@
         <v>6.64</v>
       </c>
       <c r="I173" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J173" t="n">
         <v>6.24</v>
@@ -13624,7 +13624,7 @@
         <v>7.39</v>
       </c>
       <c r="I174" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J174" t="n">
         <v>6.39</v>
@@ -13699,7 +13699,7 @@
         <v>0.36</v>
       </c>
       <c r="I175" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J175" t="n">
         <v>6.54</v>
@@ -13774,7 +13774,7 @@
         <v>7.82</v>
       </c>
       <c r="I176" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J176" t="n">
         <v>6.71</v>
@@ -13849,7 +13849,7 @@
         <v>-5.02</v>
       </c>
       <c r="I177" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J177" t="n">
         <v>6.84</v>
@@ -13924,7 +13924,7 @@
         <v>5.17</v>
       </c>
       <c r="I178" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J178" t="n">
         <v>6.99</v>
@@ -13999,7 +13999,7 @@
         <v>11.62</v>
       </c>
       <c r="I179" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J179" t="n">
         <v>7.18</v>
@@ -14074,7 +14074,7 @@
         <v>-14.81</v>
       </c>
       <c r="I180" s="4" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J180" s="4" t="n">
         <v>7.32</v>
@@ -14149,7 +14149,7 @@
         <v>2.47</v>
       </c>
       <c r="I181" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J181" t="n">
         <v>7.45</v>
@@ -14224,7 +14224,7 @@
         <v>-9.52</v>
       </c>
       <c r="I182" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J182" t="n">
         <v>7.55</v>
@@ -14299,7 +14299,7 @@
         <v>-5.7</v>
       </c>
       <c r="I183" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J183" t="n">
         <v>7.66</v>
@@ -14378,7 +14378,7 @@
         <v>12.5</v>
       </c>
       <c r="I184" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J184" t="n">
         <v>7.78</v>
@@ -14453,7 +14453,7 @@
         <v>-1.19</v>
       </c>
       <c r="I185" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J185" t="n">
         <v>7.91</v>
@@ -14528,7 +14528,7 @@
         <v>2.06</v>
       </c>
       <c r="I186" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J186" t="n">
         <v>8.029999999999999</v>
@@ -14603,7 +14603,7 @@
         <v>-5.92</v>
       </c>
       <c r="I187" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J187" t="n">
         <v>8.09</v>
@@ -14682,7 +14682,7 @@
         <v>0.38</v>
       </c>
       <c r="I188" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J188" t="n">
         <v>8.140000000000001</v>
@@ -14757,7 +14757,7 @@
         <v>-3.76</v>
       </c>
       <c r="I189" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J189" t="n">
         <v>8.16</v>
@@ -14832,7 +14832,7 @@
         <v>-4.69</v>
       </c>
       <c r="I190" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J190" t="n">
         <v>8.18</v>
@@ -14907,7 +14907,7 @@
         <v>-3.28</v>
       </c>
       <c r="I191" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J191" t="n">
         <v>8.18</v>
@@ -14982,7 +14982,7 @@
         <v>-6.79</v>
       </c>
       <c r="I192" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J192" t="n">
         <v>8.140000000000001</v>
@@ -15061,7 +15061,7 @@
         <v>2.28</v>
       </c>
       <c r="I193" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J193" t="n">
         <v>8.1</v>
@@ -15136,7 +15136,7 @@
         <v>3.71</v>
       </c>
       <c r="I194" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J194" t="n">
         <v>8.029999999999999</v>
@@ -15211,7 +15211,7 @@
         <v>-2</v>
       </c>
       <c r="I195" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J195" t="n">
         <v>7.96</v>
@@ -15286,7 +15286,7 @@
         <v>5.99</v>
       </c>
       <c r="I196" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J196" t="n">
         <v>7.87</v>
@@ -15361,7 +15361,7 @@
         <v>-2.2</v>
       </c>
       <c r="I197" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J197" t="n">
         <v>7.8</v>
@@ -15436,7 +15436,7 @@
         <v>-0.99</v>
       </c>
       <c r="I198" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J198" t="n">
         <v>7.71</v>
@@ -15511,7 +15511,7 @@
         <v>4.69</v>
       </c>
       <c r="I199" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J199" t="n">
         <v>7.58</v>
@@ -15586,7 +15586,7 @@
         <v>2.99</v>
       </c>
       <c r="I200" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J200" t="n">
         <v>7.53</v>
@@ -15661,7 +15661,7 @@
         <v>-3.56</v>
       </c>
       <c r="I201" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J201" t="n">
         <v>7.46</v>
@@ -15740,7 +15740,7 @@
         <v>7.66</v>
       </c>
       <c r="I202" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J202" t="n">
         <v>7.46</v>
@@ -15815,7 +15815,7 @@
         <v>2.41</v>
       </c>
       <c r="I203" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J203" t="n">
         <v>7.49</v>
@@ -15890,7 +15890,7 @@
         <v>1.49</v>
       </c>
       <c r="I204" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J204" t="n">
         <v>7.48</v>
@@ -15965,7 +15965,7 @@
         <v>3.67</v>
       </c>
       <c r="I205" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J205" t="n">
         <v>7.49</v>
@@ -16040,7 +16040,7 @@
         <v>-5.31</v>
       </c>
       <c r="I206" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J206" t="n">
         <v>7.47</v>
@@ -16115,7 +16115,7 @@
         <v>-7.35</v>
       </c>
       <c r="I207" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J207" t="n">
         <v>7.44</v>
@@ -16190,7 +16190,7 @@
         <v>0</v>
       </c>
       <c r="I208" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J208" t="n">
         <v>7.42</v>
@@ -16265,7 +16265,7 @@
         <v>-4.03</v>
       </c>
       <c r="I209" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J209" t="n">
         <v>7.39</v>
@@ -16344,7 +16344,7 @@
         <v>-2.94</v>
       </c>
       <c r="I210" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J210" t="n">
         <v>7.37</v>
@@ -16423,7 +16423,7 @@
         <v>4.91</v>
       </c>
       <c r="I211" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J211" t="n">
         <v>7.38</v>
@@ -16498,7 +16498,7 @@
         <v>4.13</v>
       </c>
       <c r="I212" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J212" t="n">
         <v>7.43</v>
@@ -16573,7 +16573,7 @@
         <v>1.45</v>
       </c>
       <c r="I213" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J213" t="n">
         <v>7.48</v>
@@ -16648,7 +16648,7 @@
         <v>3.26</v>
       </c>
       <c r="I214" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J214" t="n">
         <v>7.53</v>
@@ -16723,7 +16723,7 @@
         <v>5.8</v>
       </c>
       <c r="I215" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J215" t="n">
         <v>7.6</v>
@@ -16798,7 +16798,7 @@
         <v>3.93</v>
       </c>
       <c r="I216" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J216" t="n">
         <v>7.68</v>
@@ -16873,7 +16873,7 @@
         <v>9.06</v>
       </c>
       <c r="I217" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J217" t="n">
         <v>7.8</v>
@@ -16948,7 +16948,7 @@
         <v>-0.53</v>
       </c>
       <c r="I218" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J218" t="n">
         <v>7.92</v>
@@ -17023,7 +17023,7 @@
         <v>-4.02</v>
       </c>
       <c r="I219" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J219" t="n">
         <v>8</v>
@@ -17098,7 +17098,7 @@
         <v>14.76</v>
       </c>
       <c r="I220" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J220" t="n">
         <v>8.15</v>
@@ -17173,7 +17173,7 @@
         <v>7.87</v>
       </c>
       <c r="I221" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J221" t="n">
         <v>8.34</v>
@@ -17248,7 +17248,7 @@
         <v>8.19</v>
       </c>
       <c r="I222" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J222" t="n">
         <v>8.56</v>
@@ -17323,7 +17323,7 @@
         <v>-1.73</v>
       </c>
       <c r="I223" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J223" t="n">
         <v>8.75</v>
@@ -17398,7 +17398,7 @@
         <v>-1.17</v>
       </c>
       <c r="I224" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J224" t="n">
         <v>8.93</v>
@@ -17473,7 +17473,7 @@
         <v>6.01</v>
       </c>
       <c r="I225" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J225" t="n">
         <v>9.130000000000001</v>
@@ -17548,7 +17548,7 @@
         <v>0.48</v>
       </c>
       <c r="I226" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J226" t="n">
         <v>9.359999999999999</v>
@@ -17623,7 +17623,7 @@
         <v>-4.05</v>
       </c>
       <c r="I227" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J227" t="n">
         <v>9.59</v>
@@ -17698,7 +17698,7 @@
         <v>5.72</v>
       </c>
       <c r="I228" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J228" t="n">
         <v>9.859999999999999</v>
@@ -17773,7 +17773,7 @@
         <v>4</v>
       </c>
       <c r="I229" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J229" t="n">
         <v>10.17</v>
@@ -17848,7 +17848,7 @@
         <v>3.17</v>
       </c>
       <c r="I230" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J230" t="n">
         <v>10.5</v>
@@ -17923,7 +17923,7 @@
         <v>-3.51</v>
       </c>
       <c r="I231" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J231" t="n">
         <v>10.8</v>
@@ -17998,7 +17998,7 @@
         <v>12.57</v>
       </c>
       <c r="I232" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J232" t="n">
         <v>11.17</v>
@@ -18073,7 +18073,7 @@
         <v>1.01</v>
       </c>
       <c r="I233" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J233" t="n">
         <v>11.53</v>
@@ -18148,7 +18148,7 @@
         <v>4.99</v>
       </c>
       <c r="I234" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J234" t="n">
         <v>11.92</v>
@@ -18223,7 +18223,7 @@
         <v>-1.46</v>
       </c>
       <c r="I235" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J235" t="n">
         <v>12.28</v>
@@ -18298,7 +18298,7 @@
         <v>13.38</v>
       </c>
       <c r="I236" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J236" t="n">
         <v>12.73</v>
@@ -18373,7 +18373,7 @@
         <v>7.21</v>
       </c>
       <c r="I237" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J237" t="n">
         <v>13.2</v>
@@ -18448,7 +18448,7 @@
         <v>-2.7</v>
       </c>
       <c r="I238" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J238" t="n">
         <v>13.64</v>
@@ -18523,7 +18523,7 @@
         <v>-5.39</v>
       </c>
       <c r="I239" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J239" t="n">
         <v>14.06</v>
@@ -18598,7 +18598,7 @@
         <v>-3.16</v>
       </c>
       <c r="I240" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J240" t="n">
         <v>14.38</v>
@@ -18673,7 +18673,7 @@
         <v>7.78</v>
       </c>
       <c r="I241" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J241" t="n">
         <v>14.72</v>
@@ -18748,7 +18748,7 @@
         <v>-9.199999999999999</v>
       </c>
       <c r="I242" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J242" t="n">
         <v>14.94</v>
@@ -18823,7 +18823,7 @@
         <v>-0.61</v>
       </c>
       <c r="I243" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J243" t="n">
         <v>15.16</v>
@@ -18898,7 +18898,7 @@
         <v>10.87</v>
       </c>
       <c r="I244" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J244" t="n">
         <v>15.48</v>
@@ -18973,7 +18973,7 @@
         <v>3.36</v>
       </c>
       <c r="I245" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J245" t="n">
         <v>15.79</v>
@@ -19048,7 +19048,7 @@
         <v>-3.57</v>
       </c>
       <c r="I246" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J246" t="n">
         <v>16.07</v>
@@ -19123,7 +19123,7 @@
         <v>14.14</v>
       </c>
       <c r="I247" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J247" t="n">
         <v>16.5</v>
@@ -19198,7 +19198,7 @@
         <v>1.06</v>
       </c>
       <c r="I248" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J248" t="n">
         <v>16.9</v>
@@ -19273,7 +19273,7 @@
         <v>7.14</v>
       </c>
       <c r="I249" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J249" t="n">
         <v>17.36</v>
@@ -19348,7 +19348,7 @@
         <v>-6.79</v>
       </c>
       <c r="I250" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J250" t="n">
         <v>17.72</v>
@@ -19423,7 +19423,7 @@
         <v>4.46</v>
       </c>
       <c r="I251" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J251" t="n">
         <v>18.15</v>
@@ -19498,7 +19498,7 @@
         <v>5</v>
       </c>
       <c r="I252" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J252" t="n">
         <v>18.55</v>
@@ -19573,7 +19573,7 @@
         <v>14.65</v>
       </c>
       <c r="I253" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J253" t="n">
         <v>19.1</v>
@@ -19648,7 +19648,7 @@
         <v>-5.03</v>
       </c>
       <c r="I254" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J254" t="n">
         <v>19.56</v>
@@ -19723,7 +19723,7 @@
         <v>10.96</v>
       </c>
       <c r="I255" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J255" t="n">
         <v>20.17</v>
@@ -19798,7 +19798,7 @@
         <v>9.08</v>
       </c>
       <c r="I256" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J256" t="n">
         <v>20.79</v>
@@ -19873,7 +19873,7 @@
         <v>2.79</v>
       </c>
       <c r="I257" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J257" t="n">
         <v>21.4</v>
@@ -19948,7 +19948,7 @@
         <v>1.65</v>
       </c>
       <c r="I258" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J258" t="n">
         <v>22.05</v>
@@ -20023,7 +20023,7 @@
         <v>-7.15</v>
       </c>
       <c r="I259" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J259" t="n">
         <v>22.64</v>
@@ -20098,7 +20098,7 @@
         <v>-31.09</v>
       </c>
       <c r="I260" s="4" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J260" s="4" t="n">
         <v>22.81</v>
@@ -20177,7 +20177,7 @@
         <v>4.37</v>
       </c>
       <c r="I261" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J261" t="n">
         <v>22.95</v>
@@ -20252,7 +20252,7 @@
         <v>-18.45</v>
       </c>
       <c r="I262" s="4" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J262" s="4" t="n">
         <v>22.99</v>
@@ -20327,7 +20327,7 @@
         <v>1.52</v>
       </c>
       <c r="I263" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J263" t="n">
         <v>23.04</v>
@@ -20406,7 +20406,7 @@
         <v>15.68</v>
       </c>
       <c r="I264" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J264" t="n">
         <v>23.14</v>
@@ -20481,7 +20481,7 @@
         <v>-7.25</v>
       </c>
       <c r="I265" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J265" t="n">
         <v>23.13</v>
@@ -20556,7 +20556,7 @@
         <v>5.46</v>
       </c>
       <c r="I266" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J266" t="n">
         <v>23.21</v>
@@ -20631,7 +20631,7 @@
         <v>-20.25</v>
       </c>
       <c r="I267" s="4" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J267" s="4" t="n">
         <v>22.97</v>
@@ -20704,7 +20704,7 @@
         <v>0.64</v>
       </c>
       <c r="I268" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J268" t="n">
         <v>22.71</v>
@@ -20783,7 +20783,7 @@
         <v>21</v>
       </c>
       <c r="I269" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J269" t="n">
         <v>22.55</v>
@@ -20858,7 +20858,7 @@
         <v>3.4</v>
       </c>
       <c r="I270" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J270" t="n">
         <v>22.5</v>
@@ -20933,7 +20933,7 @@
         <v>-5.01</v>
       </c>
       <c r="I271" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J271" t="n">
         <v>22.35</v>
@@ -21008,7 +21008,7 @@
         <v>5.8</v>
       </c>
       <c r="I272" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J272" t="n">
         <v>22.2</v>
@@ -21083,7 +21083,7 @@
         <v>-19.32</v>
       </c>
       <c r="I273" s="4" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J273" s="4" t="n">
         <v>21.69</v>
@@ -21166,7 +21166,7 @@
         <v>17.71</v>
       </c>
       <c r="I274" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J274" t="n">
         <v>21.39</v>
@@ -21241,7 +21241,7 @@
         <v>-11.12</v>
       </c>
       <c r="I275" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J275" t="n">
         <v>20.85</v>
@@ -21320,7 +21320,7 @@
         <v>-2.38</v>
       </c>
       <c r="I276" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J276" t="n">
         <v>20.16</v>
@@ -21395,7 +21395,7 @@
         <v>-17.58</v>
       </c>
       <c r="I277" s="4" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J277" s="4" t="n">
         <v>19.28</v>
@@ -21470,7 +21470,7 @@
         <v>1.48</v>
       </c>
       <c r="I278" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J278" t="n">
         <v>18.39</v>
@@ -21549,7 +21549,7 @@
         <v>-11.24</v>
       </c>
       <c r="I279" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J279" t="n">
         <v>17.54</v>
@@ -21628,7 +21628,7 @@
         <v>16.86</v>
       </c>
       <c r="I280" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J280" t="n">
         <v>17.24</v>
@@ -21703,7 +21703,7 @@
         <v>7.67</v>
       </c>
       <c r="I281" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J281" t="n">
         <v>16.96</v>
@@ -21778,7 +21778,7 @@
         <v>-7.78</v>
       </c>
       <c r="I282" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J282" t="n">
         <v>16.8</v>
@@ -21853,7 +21853,7 @@
         <v>7.02</v>
       </c>
       <c r="I283" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J283" t="n">
         <v>16.69</v>
@@ -21928,7 +21928,7 @@
         <v>2.98</v>
       </c>
       <c r="I284" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J284" t="n">
         <v>16.46</v>
@@ -22007,7 +22007,7 @@
         <v>30.23</v>
       </c>
       <c r="I285" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J285" t="n">
         <v>16.54</v>
@@ -22082,7 +22082,7 @@
         <v>-1.38</v>
       </c>
       <c r="I286" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J286" t="n">
         <v>16.55</v>
@@ -22157,7 +22157,7 @@
         <v>-1.35</v>
       </c>
       <c r="I287" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J287" t="n">
         <v>16.75</v>
@@ -22232,7 +22232,7 @@
         <v>5.08</v>
       </c>
       <c r="I288" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J288" t="n">
         <v>17</v>
@@ -22307,7 +22307,7 @@
         <v>11.98</v>
       </c>
       <c r="I289" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J289" t="n">
         <v>17.2</v>
@@ -22382,7 +22382,7 @@
         <v>-3.84</v>
       </c>
       <c r="I290" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J290" t="n">
         <v>17.32</v>
@@ -22457,7 +22457,7 @@
         <v>5.2</v>
       </c>
       <c r="I291" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J291" t="n">
         <v>17.56</v>
@@ -22532,7 +22532,7 @@
         <v>9.98</v>
       </c>
       <c r="I292" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J292" t="n">
         <v>17.85</v>
@@ -22607,7 +22607,7 @@
         <v>-4.23</v>
       </c>
       <c r="I293" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J293" t="n">
         <v>18.28</v>
@@ -22682,7 +22682,7 @@
         <v>-6.52</v>
       </c>
       <c r="I294" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J294" t="n">
         <v>18.5</v>
@@ -22757,7 +22757,7 @@
         <v>17.54</v>
       </c>
       <c r="I295" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J295" t="n">
         <v>19.01</v>
@@ -22832,7 +22832,7 @@
         <v>-9.65</v>
       </c>
       <c r="I296" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J296" t="n">
         <v>19.42</v>
@@ -22907,7 +22907,7 @@
         <v>7.34</v>
       </c>
       <c r="I297" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J297" t="n">
         <v>20.06</v>
@@ -22982,7 +22982,7 @@
         <v>4.67</v>
       </c>
       <c r="I298" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J298" t="n">
         <v>20.75</v>
@@ -23057,7 +23057,7 @@
         <v>-4.57</v>
       </c>
       <c r="I299" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J299" t="n">
         <v>21.46</v>
@@ -23132,7 +23132,7 @@
         <v>-0.8</v>
       </c>
       <c r="I300" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J300" t="n">
         <v>22.05</v>
@@ -23207,7 +23207,7 @@
         <v>12.69</v>
       </c>
       <c r="I301" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J301" t="n">
         <v>22.76</v>
@@ -23282,7 +23282,7 @@
         <v>2.52</v>
       </c>
       <c r="I302" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J302" t="n">
         <v>23.56</v>
@@ -23357,7 +23357,7 @@
         <v>3.19</v>
       </c>
       <c r="I303" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J303" t="n">
         <v>24.36</v>
@@ -23432,7 +23432,7 @@
         <v>17.69</v>
       </c>
       <c r="I304" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J304" t="n">
         <v>25.41</v>
@@ -23507,7 +23507,7 @@
         <v>14.65</v>
       </c>
       <c r="I305" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J305" t="n">
         <v>26.5</v>
@@ -23582,7 +23582,7 @@
         <v>-8.41</v>
       </c>
       <c r="I306" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J306" t="n">
         <v>27.42</v>
@@ -23657,7 +23657,7 @@
         <v>22.62</v>
       </c>
       <c r="I307" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J307" t="n">
         <v>28.79</v>
@@ -23732,7 +23732,7 @@
         <v>4.33</v>
       </c>
       <c r="I308" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J308" t="n">
         <v>30.21</v>
@@ -23807,7 +23807,7 @@
         <v>-22.56</v>
       </c>
       <c r="I309" s="4" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J309" s="4" t="n">
         <v>30.96</v>
@@ -23882,7 +23882,7 @@
         <v>17.42</v>
       </c>
       <c r="I310" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J310" t="n">
         <v>32.08</v>
@@ -23957,7 +23957,7 @@
         <v>2.91</v>
       </c>
       <c r="I311" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J311" t="n">
         <v>33.2</v>
@@ -24032,7 +24032,7 @@
         <v>-18.31</v>
       </c>
       <c r="I312" s="4" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J312" s="4" t="n">
         <v>33.79</v>
@@ -24107,7 +24107,7 @@
         <v>-5</v>
       </c>
       <c r="I313" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J313" t="n">
         <v>34.34</v>
@@ -24182,7 +24182,7 @@
         <v>-3.36</v>
       </c>
       <c r="I314" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J314" t="n">
         <v>34.91</v>
@@ -24261,7 +24261,7 @@
         <v>10.26</v>
       </c>
       <c r="I315" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J315" t="n">
         <v>35.46</v>
@@ -24336,7 +24336,7 @@
         <v>10.31</v>
       </c>
       <c r="I316" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J316" t="n">
         <v>36.33</v>
@@ -24411,7 +24411,7 @@
         <v>-6.98</v>
       </c>
       <c r="I317" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J317" t="n">
         <v>36.96</v>
@@ -24486,7 +24486,7 @@
         <v>30.06</v>
       </c>
       <c r="I318" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J318" t="n">
         <v>38.12</v>
@@ -24561,7 +24561,7 @@
         <v>-3.57</v>
       </c>
       <c r="I319" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J319" t="n">
         <v>39.25</v>
@@ -24636,7 +24636,7 @@
         <v>12.4</v>
       </c>
       <c r="I320" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J320" t="n">
         <v>40.7</v>
@@ -24711,7 +24711,7 @@
         <v>-0.93</v>
       </c>
       <c r="I321" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J321" t="n">
         <v>41.96</v>
@@ -24786,7 +24786,7 @@
         <v>16.04</v>
       </c>
       <c r="I322" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J322" t="n">
         <v>43.61</v>
@@ -24861,7 +24861,7 @@
         <v>-3.16</v>
       </c>
       <c r="I323" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J323" t="n">
         <v>45.12</v>
@@ -24936,7 +24936,7 @@
         <v>-2.29</v>
       </c>
       <c r="I324" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J324" t="n">
         <v>46.28</v>
@@ -25011,7 +25011,7 @@
         <v>-12.28</v>
       </c>
       <c r="I325" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J325" t="n">
         <v>46.81</v>
@@ -25086,7 +25086,7 @@
         <v>-41.89</v>
       </c>
       <c r="I326" s="4" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J326" s="4" t="n">
         <v>46.41</v>
@@ -25165,7 +25165,7 @@
         <v>16.3</v>
       </c>
       <c r="I327" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J327" t="n">
         <v>45.83</v>
@@ -25240,7 +25240,7 @@
         <v>-2.45</v>
       </c>
       <c r="I328" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J328" t="n">
         <v>45.1</v>
@@ -25315,7 +25315,7 @@
         <v>-9.050000000000001</v>
       </c>
       <c r="I329" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J329" t="n">
         <v>44.77</v>
@@ -25390,7 +25390,7 @@
         <v>33.78</v>
       </c>
       <c r="I330" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J330" t="n">
         <v>44.64</v>
@@ -25465,7 +25465,7 @@
         <v>-2.04</v>
       </c>
       <c r="I331" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J331" t="n">
         <v>44.41</v>
@@ -25540,7 +25540,7 @@
         <v>21.14</v>
       </c>
       <c r="I332" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J332" t="n">
         <v>45.03</v>
@@ -25615,7 +25615,7 @@
         <v>-8.029999999999999</v>
       </c>
       <c r="I333" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J333" t="n">
         <v>45.54</v>
@@ -25690,7 +25690,7 @@
         <v>-0.5</v>
       </c>
       <c r="I334" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J334" t="n">
         <v>46.1</v>
@@ -25769,7 +25769,7 @@
         <v>19.29</v>
       </c>
       <c r="I335" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J335" t="n">
         <v>46.93</v>
@@ -25844,7 +25844,7 @@
         <v>-0.2</v>
       </c>
       <c r="I336" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J336" t="n">
         <v>47.55</v>
@@ -25919,7 +25919,7 @@
         <v>-35.7</v>
       </c>
       <c r="I337" s="4" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J337" s="4" t="n">
         <v>47.35</v>
@@ -25998,7 +25998,7 @@
         <v>5.89</v>
       </c>
       <c r="I338" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J338" t="n">
         <v>46.66</v>
@@ -26073,7 +26073,7 @@
         <v>11.85</v>
       </c>
       <c r="I339" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J339" t="n">
         <v>46.29</v>
@@ -26148,7 +26148,7 @@
         <v>-10.9</v>
       </c>
       <c r="I340" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J340" t="n">
         <v>45.39</v>
@@ -26223,7 +26223,7 @@
         <v>-0.03</v>
       </c>
       <c r="I341" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J341" t="n">
         <v>44.51</v>
@@ -26298,7 +26298,7 @@
         <v>5.82</v>
       </c>
       <c r="I342" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J342" t="n">
         <v>43.3</v>
@@ -26373,7 +26373,7 @@
         <v>-23.21</v>
       </c>
       <c r="I343" s="4" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J343" s="4" t="n">
         <v>41.74</v>
@@ -26452,7 +26452,7 @@
         <v>-9.77</v>
       </c>
       <c r="I344" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J344" t="n">
         <v>40.1</v>
@@ -26531,7 +26531,7 @@
         <v>15.37</v>
       </c>
       <c r="I345" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J345" t="n">
         <v>39.04</v>
@@ -26606,7 +26606,7 @@
         <v>-12.78</v>
       </c>
       <c r="I346" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J346" t="n">
         <v>38.87</v>
@@ -26685,7 +26685,7 @@
         <v>1.58</v>
       </c>
       <c r="I347" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J347" t="n">
         <v>38.48</v>
@@ -26760,7 +26760,7 @@
         <v>3</v>
       </c>
       <c r="I348" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J348" t="n">
         <v>38.18</v>
@@ -26835,7 +26835,7 @@
         <v>-2.28</v>
       </c>
       <c r="I349" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J349" t="n">
         <v>38</v>
@@ -26914,7 +26914,7 @@
         <v>-24.74</v>
       </c>
       <c r="I350" s="4" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J350" s="4" t="n">
         <v>36.94</v>
@@ -26989,7 +26989,7 @@
         <v>14.84</v>
       </c>
       <c r="I351" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J351" t="n">
         <v>36.08</v>
@@ -27064,7 +27064,7 @@
         <v>-9.140000000000001</v>
       </c>
       <c r="I352" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J352" t="n">
         <v>34.68</v>
@@ -27139,7 +27139,7 @@
         <v>-14.72</v>
       </c>
       <c r="I353" s="4" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J353" s="4" t="n">
         <v>33.31</v>
@@ -27218,7 +27218,7 @@
         <v>-2.09</v>
       </c>
       <c r="I354" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J354" t="n">
         <v>31.94</v>
@@ -27297,7 +27297,7 @@
         <v>0.82</v>
       </c>
       <c r="I355" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J355" t="n">
         <v>30.13</v>
@@ -27376,7 +27376,7 @@
         <v>18.03</v>
       </c>
       <c r="I356" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J356" t="n">
         <v>28.5</v>
@@ -27451,7 +27451,7 @@
         <v>-4.46</v>
       </c>
       <c r="I357" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J357" t="n">
         <v>27.79</v>
@@ -27526,7 +27526,7 @@
         <v>6.02</v>
       </c>
       <c r="I358" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J358" t="n">
         <v>27.03</v>
@@ -27601,7 +27601,7 @@
         <v>-18.9</v>
       </c>
       <c r="I359" s="4" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J359" s="4" t="n">
         <v>25.85</v>
@@ -27680,7 +27680,7 @@
         <v>-3.59</v>
       </c>
       <c r="I360" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J360" t="n">
         <v>24.87</v>
@@ -27755,7 +27755,7 @@
         <v>-17.78</v>
       </c>
       <c r="I361" s="4" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J361" s="4" t="n">
         <v>23.73</v>
@@ -27834,7 +27834,7 @@
         <v>-14.63</v>
       </c>
       <c r="I362" s="4" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J362" s="4" t="n">
         <v>22.38</v>
@@ -27913,7 +27913,7 @@
         <v>34.77</v>
       </c>
       <c r="I363" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J363" t="n">
         <v>21.69</v>
@@ -27988,7 +27988,7 @@
         <v>-7.92</v>
       </c>
       <c r="I364" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J364" t="n">
         <v>21.09</v>
@@ -28063,7 +28063,7 @@
         <v>5.87</v>
       </c>
       <c r="I365" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J365" t="n">
         <v>20.32</v>
@@ -28138,7 +28138,7 @@
         <v>20.48</v>
       </c>
       <c r="I366" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J366" t="n">
         <v>19.91</v>
@@ -28213,7 +28213,7 @@
         <v>-3.56</v>
       </c>
       <c r="I367" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J367" t="n">
         <v>19.45</v>
@@ -28288,7 +28288,7 @@
         <v>-8.84</v>
       </c>
       <c r="I368" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J368" t="n">
         <v>18.87</v>
@@ -28363,7 +28363,7 @@
         <v>3.27</v>
       </c>
       <c r="I369" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J369" t="n">
         <v>18.34</v>
@@ -28438,7 +28438,7 @@
         <v>-5.47</v>
       </c>
       <c r="I370" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J370" t="n">
         <v>18.12</v>
@@ -28513,7 +28513,7 @@
         <v>7.5</v>
       </c>
       <c r="I371" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J371" t="n">
         <v>17.8</v>
@@ -28588,7 +28588,7 @@
         <v>15.19</v>
       </c>
       <c r="I372" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J372" t="n">
         <v>17.72</v>
@@ -28663,7 +28663,7 @@
         <v>4.68</v>
       </c>
       <c r="I373" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J373" t="n">
         <v>17.85</v>
@@ -28738,7 +28738,7 @@
         <v>1.55</v>
       </c>
       <c r="I374" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J374" t="n">
         <v>18.02</v>
@@ -28813,7 +28813,7 @@
         <v>8.98</v>
       </c>
       <c r="I375" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J375" t="n">
         <v>18.27</v>
@@ -28888,7 +28888,7 @@
         <v>-24.21</v>
       </c>
       <c r="I376" s="4" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J376" s="4" t="n">
         <v>18.08</v>
@@ -28967,7 +28967,7 @@
         <v>7.12</v>
       </c>
       <c r="I377" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J377" t="n">
         <v>18</v>
@@ -29042,7 +29042,7 @@
         <v>6.38</v>
       </c>
       <c r="I378" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J378" t="n">
         <v>17.91</v>
@@ -29117,7 +29117,7 @@
         <v>0.15</v>
       </c>
       <c r="I379" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J379" t="n">
         <v>18.04</v>
@@ -29192,7 +29192,7 @@
         <v>-7.86</v>
       </c>
       <c r="I380" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J380" t="n">
         <v>18.11</v>
@@ -29267,7 +29267,7 @@
         <v>11.03</v>
       </c>
       <c r="I381" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J381" t="n">
         <v>18.45</v>
@@ -29342,7 +29342,7 @@
         <v>-1.63</v>
       </c>
       <c r="I382" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J382" t="n">
         <v>18.87</v>
@@ -29417,7 +29417,7 @@
         <v>4.49</v>
       </c>
       <c r="I383" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J383" t="n">
         <v>19.12</v>
@@ -29492,7 +29492,7 @@
         <v>-2.99</v>
       </c>
       <c r="I384" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J384" t="n">
         <v>19.41</v>
@@ -29567,7 +29567,7 @@
         <v>0.91</v>
       </c>
       <c r="I385" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J385" t="n">
         <v>19.67</v>
@@ -29642,7 +29642,7 @@
         <v>-8.49</v>
       </c>
       <c r="I386" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J386" t="n">
         <v>19.67</v>
@@ -29721,7 +29721,7 @@
         <v>5.06</v>
       </c>
       <c r="I387" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J387" t="n">
         <v>19.76</v>
@@ -29796,7 +29796,7 @@
         <v>2.68</v>
       </c>
       <c r="I388" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J388" t="n">
         <v>19.95</v>
@@ -29871,7 +29871,7 @@
         <v>13.44</v>
       </c>
       <c r="I389" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J389" t="n">
         <v>20.26</v>
@@ -29946,7 +29946,7 @@
         <v>1.58</v>
       </c>
       <c r="I390" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J390" t="n">
         <v>20.63</v>
@@ -30021,7 +30021,7 @@
         <v>1.51</v>
       </c>
       <c r="I391" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J391" t="n">
         <v>20.96</v>
@@ -30096,7 +30096,7 @@
         <v>-12.52</v>
       </c>
       <c r="I392" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J392" t="n">
         <v>21</v>
@@ -30171,7 +30171,7 @@
         <v>8.970000000000001</v>
       </c>
       <c r="I393" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J393" t="n">
         <v>21.09</v>
@@ -30246,7 +30246,7 @@
         <v>-19.51</v>
       </c>
       <c r="I394" s="4" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J394" s="4" t="n">
         <v>20.94</v>
@@ -30325,7 +30325,7 @@
         <v>0.16</v>
       </c>
       <c r="I395" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J395" t="n">
         <v>20.69</v>
@@ -30400,7 +30400,7 @@
         <v>-1.72</v>
       </c>
       <c r="I396" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J396" t="n">
         <v>20.71</v>
@@ -30475,7 +30475,7 @@
         <v>11.65</v>
       </c>
       <c r="I397" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J397" t="n">
         <v>20.78</v>
@@ -30550,7 +30550,7 @@
         <v>-1.81</v>
       </c>
       <c r="I398" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J398" t="n">
         <v>20.76</v>
@@ -30625,7 +30625,7 @@
         <v>12.52</v>
       </c>
       <c r="I399" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J399" t="n">
         <v>20.87</v>
@@ -30700,7 +30700,7 @@
         <v>5.41</v>
       </c>
       <c r="I400" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J400" t="n">
         <v>21.12</v>
@@ -30775,7 +30775,7 @@
         <v>-10.52</v>
       </c>
       <c r="I401" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J401" t="n">
         <v>21.14</v>
@@ -30850,7 +30850,7 @@
         <v>-5.31</v>
       </c>
       <c r="I402" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J402" t="n">
         <v>21.13</v>
@@ -30929,7 +30929,7 @@
         <v>7.2</v>
       </c>
       <c r="I403" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J403" t="n">
         <v>21.14</v>
@@ -31004,7 +31004,7 @@
         <v>-5.51</v>
       </c>
       <c r="I404" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J404" t="n">
         <v>21.12</v>
@@ -31083,7 +31083,7 @@
         <v>5.25</v>
       </c>
       <c r="I405" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J405" t="n">
         <v>21.14</v>
@@ -31158,7 +31158,7 @@
         <v>-6.75</v>
       </c>
       <c r="I406" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J406" t="n">
         <v>21.18</v>
@@ -31237,7 +31237,7 @@
         <v>5.34</v>
       </c>
       <c r="I407" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J407" t="n">
         <v>21.23</v>
@@ -31312,7 +31312,7 @@
         <v>8.82</v>
       </c>
       <c r="I408" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J408" t="n">
         <v>21.34</v>
@@ -31387,7 +31387,7 @@
         <v>-0.74</v>
       </c>
       <c r="I409" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J409" t="n">
         <v>21.31</v>
@@ -31462,7 +31462,7 @@
         <v>-7.77</v>
       </c>
       <c r="I410" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J410" t="n">
         <v>21.17</v>
@@ -31541,7 +31541,7 @@
         <v>-4.57</v>
       </c>
       <c r="I411" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J411" t="n">
         <v>20.96</v>
@@ -31616,7 +31616,7 @@
         <v>-11.97</v>
       </c>
       <c r="I412" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J412" t="n">
         <v>20.79</v>
@@ -31695,7 +31695,7 @@
         <v>1.13</v>
       </c>
       <c r="I413" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J413" t="n">
         <v>20.52</v>
@@ -31713,11 +31713,11 @@
         <v>37.26</v>
       </c>
       <c r="O413" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="Q413" t="inlineStr">
@@ -31738,6 +31738,85 @@
       <c r="V413" t="inlineStr"/>
       <c r="W413" s="2" t="n">
         <v>154.3</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>KORU</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>16.56</v>
+      </c>
+      <c r="D414" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="E414" t="n">
+        <v>15.61</v>
+      </c>
+      <c r="F414" t="n">
+        <v>15.74</v>
+      </c>
+      <c r="G414" t="n">
+        <v>32203828</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>-11.82</v>
+      </c>
+      <c r="I414" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J414" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="K414" t="n">
+        <v>19.78</v>
+      </c>
+      <c r="L414" t="n">
+        <v>28.71</v>
+      </c>
+      <c r="M414" t="n">
+        <v>24.37</v>
+      </c>
+      <c r="N414" s="1" t="n">
+        <v>29.23</v>
+      </c>
+      <c r="O414" t="n">
+        <v>46</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S414" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="3" t="n">
+        <v>155.1</v>
       </c>
     </row>
   </sheetData>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31744,6 +31744,79 @@
         <v>155.1</v>
       </c>
     </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>KORU</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="D414" t="n">
+        <v>14.61</v>
+      </c>
+      <c r="E414" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="F414" t="n">
+        <v>14.38</v>
+      </c>
+      <c r="G414" t="n">
+        <v>32950638</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>-8.640000000000001</v>
+      </c>
+      <c r="I414" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J414" t="n">
+        <v>20.17</v>
+      </c>
+      <c r="K414" t="n">
+        <v>19.71</v>
+      </c>
+      <c r="L414" t="n">
+        <v>28.61</v>
+      </c>
+      <c r="M414" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>31.06</v>
+      </c>
+      <c r="O414" t="n">
+        <v>44</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -12048,7 +12048,7 @@
         <v>13.5</v>
       </c>
       <c r="J153" t="n">
-        <v>4.85</v>
+        <v>4.86</v>
       </c>
       <c r="K153" t="n">
         <v>4.34</v>
@@ -31689,7 +31689,7 @@
         <v>15.74</v>
       </c>
       <c r="G413" t="n">
-        <v>32490700</v>
+        <v>33485300</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>-11.82</v>
@@ -31759,28 +31759,28 @@
         <v>13.78</v>
       </c>
       <c r="D414" t="n">
-        <v>14.61</v>
+        <v>14.76</v>
       </c>
       <c r="E414" t="n">
         <v>13.75</v>
       </c>
       <c r="F414" t="n">
-        <v>14.38</v>
+        <v>14.72</v>
       </c>
       <c r="G414" t="n">
-        <v>32950638</v>
+        <v>38436243</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>-8.640000000000001</v>
+        <v>-6.48</v>
       </c>
       <c r="I414" t="n">
         <v>13.5</v>
       </c>
       <c r="J414" t="n">
-        <v>20.17</v>
+        <v>20.19</v>
       </c>
       <c r="K414" t="n">
-        <v>19.71</v>
+        <v>19.72</v>
       </c>
       <c r="L414" t="n">
         <v>28.61</v>
@@ -31789,10 +31789,10 @@
         <v>24.4</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>31.06</v>
+        <v>31.65</v>
       </c>
       <c r="O414" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31808,12 +31808,8 @@
       <c r="S414" t="n">
         <v>5.22</v>
       </c>
-      <c r="T414" s="2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="U414" s="2" t="n">
-        <v>9.699999999999999</v>
-      </c>
+      <c r="T414" s="2" t="inlineStr"/>
+      <c r="U414" s="2" t="inlineStr"/>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="inlineStr"/>
     </row>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31721,7 +31721,7 @@
       </c>
       <c r="P413" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="Q413" t="inlineStr">

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31717,11 +31717,11 @@
         <v>31.65</v>
       </c>
       <c r="O413" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>fear</t>
         </is>
       </c>
       <c r="Q413" t="inlineStr">
@@ -31743,6 +31743,79 @@
       <c r="W413" s="2" t="n">
         <v>154.7</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>KORU</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>13.45</v>
+      </c>
+      <c r="D414" t="n">
+        <v>13.89</v>
+      </c>
+      <c r="E414" t="n">
+        <v>13.42</v>
+      </c>
+      <c r="F414" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="G414" t="n">
+        <v>19088458</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>-7.88</v>
+      </c>
+      <c r="I414" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J414" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="K414" t="n">
+        <v>19.58</v>
+      </c>
+      <c r="L414" t="n">
+        <v>28.52</v>
+      </c>
+      <c r="M414" t="n">
+        <v>24.42</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="O414" t="n">
+        <v>37</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31762,25 +31762,25 @@
         <v>13.89</v>
       </c>
       <c r="E414" t="n">
-        <v>13.42</v>
+        <v>12.93</v>
       </c>
       <c r="F414" t="n">
-        <v>13.56</v>
+        <v>13.06</v>
       </c>
       <c r="G414" t="n">
-        <v>19088458</v>
+        <v>31468578</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>-7.88</v>
+        <v>-11.28</v>
       </c>
       <c r="I414" t="n">
         <v>13.5</v>
       </c>
       <c r="J414" t="n">
-        <v>19.95</v>
+        <v>19.93</v>
       </c>
       <c r="K414" t="n">
-        <v>19.58</v>
+        <v>19.57</v>
       </c>
       <c r="L414" t="n">
         <v>28.52</v>
@@ -31789,10 +31789,10 @@
         <v>24.42</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>31.6</v>
+        <v>30.74</v>
       </c>
       <c r="O414" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31806,13 +31806,13 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>15.7</v>
+        <v>17.2</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>8.1</v>
+        <v>14</v>
       </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="inlineStr"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -7520,7 +7520,7 @@
         <v>13.5</v>
       </c>
       <c r="J93" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="K93" t="n">
         <v>2.67</v>
@@ -11973,7 +11973,7 @@
         <v>13.5</v>
       </c>
       <c r="J152" t="n">
-        <v>4.86</v>
+        <v>4.85</v>
       </c>
       <c r="K152" t="n">
         <v>4.34</v>
@@ -19276,7 +19276,7 @@
         <v>13.5</v>
       </c>
       <c r="J249" t="n">
-        <v>18.15</v>
+        <v>18.14</v>
       </c>
       <c r="K249" t="n">
         <v>12.11</v>
@@ -19351,7 +19351,7 @@
         <v>13.5</v>
       </c>
       <c r="J250" t="n">
-        <v>18.55</v>
+        <v>18.54</v>
       </c>
       <c r="K250" t="n">
         <v>12.38</v>
@@ -25851,7 +25851,7 @@
         <v>13.5</v>
       </c>
       <c r="J336" t="n">
-        <v>46.66</v>
+        <v>46.67</v>
       </c>
       <c r="K336" t="n">
         <v>35.18</v>
@@ -28366,7 +28366,7 @@
         <v>13.5</v>
       </c>
       <c r="J369" t="n">
-        <v>17.8</v>
+        <v>17.79</v>
       </c>
       <c r="K369" t="n">
         <v>32.76</v>
@@ -28820,7 +28820,7 @@
         <v>13.5</v>
       </c>
       <c r="J375" t="n">
-        <v>18</v>
+        <v>17.99</v>
       </c>
       <c r="K375" t="n">
         <v>31.04</v>
@@ -31693,7 +31693,7 @@
         <v>14.72</v>
       </c>
       <c r="G413" t="n">
-        <v>38205400</v>
+        <v>39795000</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>-6.48</v>
@@ -31762,37 +31762,37 @@
         <v>13.89</v>
       </c>
       <c r="E414" t="n">
+        <v>12.88</v>
+      </c>
+      <c r="F414" t="n">
         <v>12.93</v>
       </c>
-      <c r="F414" t="n">
-        <v>13.06</v>
-      </c>
       <c r="G414" t="n">
-        <v>31468578</v>
+        <v>36016444</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>-11.28</v>
+        <v>-12.16</v>
       </c>
       <c r="I414" t="n">
         <v>13.5</v>
       </c>
       <c r="J414" t="n">
-        <v>19.93</v>
+        <v>19.92</v>
       </c>
       <c r="K414" t="n">
         <v>19.57</v>
       </c>
       <c r="L414" t="n">
-        <v>28.52</v>
+        <v>28.51</v>
       </c>
       <c r="M414" t="n">
         <v>24.42</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>30.74</v>
+        <v>30.52</v>
       </c>
       <c r="O414" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31809,13 +31809,15 @@
         <v>5.19</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>17.2</v>
+        <v>16.9</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="1" t="n">
+        <v>157.3</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31768,7 +31768,7 @@
         <v>12.93</v>
       </c>
       <c r="G414" t="n">
-        <v>36016444</v>
+        <v>35997800</v>
       </c>
       <c r="H414" s="1" t="n">
         <v>-12.16</v>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31792,7 +31792,7 @@
         <v>30.52</v>
       </c>
       <c r="O414" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31792,7 +31792,7 @@
         <v>30.52</v>
       </c>
       <c r="O414" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31818,6 +31818,83 @@
       <c r="W414" s="1" t="n">
         <v>157.3</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="4" t="inlineStr">
+        <is>
+          <t>KORU</t>
+        </is>
+      </c>
+      <c r="B415" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C415" s="4" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="D415" s="4" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="E415" s="4" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="F415" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G415" s="4" t="n">
+        <v>39940571</v>
+      </c>
+      <c r="H415" s="5" t="n">
+        <v>-14.93</v>
+      </c>
+      <c r="I415" s="4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J415" s="4" t="n">
+        <v>19.45</v>
+      </c>
+      <c r="K415" s="4" t="n">
+        <v>19.41</v>
+      </c>
+      <c r="L415" s="4" t="n">
+        <v>28.39</v>
+      </c>
+      <c r="M415" s="4" t="n">
+        <v>24.43</v>
+      </c>
+      <c r="N415" s="7" t="n">
+        <v>22.12</v>
+      </c>
+      <c r="O415" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="P415" s="4" t="inlineStr">
+        <is>
+          <t>extreme fear</t>
+        </is>
+      </c>
+      <c r="Q415" s="4" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" s="4" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S415" s="4" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="T415" s="6" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="U415" s="6" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="V415" s="4" t="inlineStr"/>
+      <c r="W415" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31820,81 +31820,81 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="4" t="inlineStr">
-        <is>
-          <t>KORU</t>
-        </is>
-      </c>
-      <c r="B415" s="4" t="inlineStr">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>KORU</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="C415" s="4" t="n">
+      <c r="C415" t="n">
         <v>10.59</v>
       </c>
-      <c r="D415" s="4" t="n">
-        <v>11.14</v>
-      </c>
-      <c r="E415" s="4" t="n">
+      <c r="D415" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="E415" t="n">
         <v>10.45</v>
       </c>
-      <c r="F415" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="G415" s="4" t="n">
-        <v>39940571</v>
-      </c>
-      <c r="H415" s="5" t="n">
-        <v>-14.93</v>
-      </c>
-      <c r="I415" s="4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="J415" s="4" t="n">
-        <v>19.45</v>
-      </c>
-      <c r="K415" s="4" t="n">
-        <v>19.41</v>
-      </c>
-      <c r="L415" s="4" t="n">
+      <c r="F415" t="n">
+        <v>11.68</v>
+      </c>
+      <c r="G415" t="n">
+        <v>66778432</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>-9.67</v>
+      </c>
+      <c r="I415" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J415" t="n">
+        <v>19.48</v>
+      </c>
+      <c r="K415" t="n">
+        <v>19.42</v>
+      </c>
+      <c r="L415" t="n">
         <v>28.39</v>
       </c>
-      <c r="M415" s="4" t="n">
+      <c r="M415" t="n">
         <v>24.43</v>
       </c>
-      <c r="N415" s="7" t="n">
-        <v>22.12</v>
-      </c>
-      <c r="O415" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="P415" s="4" t="inlineStr">
-        <is>
-          <t>extreme fear</t>
-        </is>
-      </c>
-      <c r="Q415" s="4" t="inlineStr">
+      <c r="N415" s="3" t="n">
+        <v>22.94</v>
+      </c>
+      <c r="O415" t="n">
+        <v>30</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
         <is>
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R415" s="4" t="inlineStr">
+      <c r="R415" t="inlineStr">
         <is>
           <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
         </is>
       </c>
-      <c r="S415" s="4" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="T415" s="6" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="U415" s="6" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="V415" s="4" t="inlineStr"/>
-      <c r="W415" s="6" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="T415" s="2" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="U415" s="2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31768,7 +31768,7 @@
         <v>12.93</v>
       </c>
       <c r="G414" t="n">
-        <v>35997800</v>
+        <v>39902200</v>
       </c>
       <c r="H414" s="1" t="n">
         <v>-12.16</v>
@@ -31834,40 +31834,40 @@
         <v>10.59</v>
       </c>
       <c r="D415" t="n">
-        <v>11.91</v>
+        <v>12.06</v>
       </c>
       <c r="E415" t="n">
         <v>10.45</v>
       </c>
       <c r="F415" t="n">
-        <v>11.68</v>
+        <v>12.01</v>
       </c>
       <c r="G415" t="n">
-        <v>66778432</v>
+        <v>73820918</v>
       </c>
       <c r="H415" s="1" t="n">
-        <v>-9.67</v>
+        <v>-7.12</v>
       </c>
       <c r="I415" t="n">
         <v>13.5</v>
       </c>
       <c r="J415" t="n">
-        <v>19.48</v>
+        <v>19.5</v>
       </c>
       <c r="K415" t="n">
         <v>19.42</v>
       </c>
       <c r="L415" t="n">
-        <v>28.39</v>
+        <v>28.4</v>
       </c>
       <c r="M415" t="n">
         <v>24.43</v>
       </c>
       <c r="N415" s="3" t="n">
-        <v>22.94</v>
+        <v>23.36</v>
       </c>
       <c r="O415" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31885,16 +31885,18 @@
         </is>
       </c>
       <c r="S415" t="n">
-        <v>5.08</v>
+        <v>5.09</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="V415" t="inlineStr"/>
-      <c r="W415" s="2" t="inlineStr"/>
+      <c r="W415" s="1" t="n">
+        <v>160.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31830,41 +31830,25 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="C415" t="n">
-        <v>10.59</v>
-      </c>
-      <c r="D415" t="n">
-        <v>12.06</v>
-      </c>
-      <c r="E415" t="n">
-        <v>10.45</v>
-      </c>
-      <c r="F415" t="n">
-        <v>12.01</v>
-      </c>
+      <c r="C415" t="inlineStr"/>
+      <c r="D415" t="inlineStr"/>
+      <c r="E415" t="inlineStr"/>
+      <c r="F415" t="inlineStr"/>
       <c r="G415" t="n">
         <v>73820918</v>
       </c>
-      <c r="H415" s="1" t="n">
-        <v>-7.12</v>
+      <c r="H415" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I415" t="n">
         <v>13.5</v>
       </c>
-      <c r="J415" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="K415" t="n">
-        <v>19.42</v>
-      </c>
-      <c r="L415" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="M415" t="n">
-        <v>24.43</v>
-      </c>
+      <c r="J415" t="inlineStr"/>
+      <c r="K415" t="inlineStr"/>
+      <c r="L415" t="inlineStr"/>
+      <c r="M415" t="inlineStr"/>
       <c r="N415" s="3" t="n">
-        <v>23.36</v>
+        <v>24.62</v>
       </c>
       <c r="O415" t="n">
         <v>32</v>
@@ -31879,11 +31863,7 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R415" t="inlineStr">
-        <is>
-          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
-        </is>
-      </c>
+      <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
         <v>5.09</v>
       </c>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31830,28 +31830,44 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
-      <c r="D415" t="inlineStr"/>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
+      <c r="C415" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="D415" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="E415" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="F415" t="n">
+        <v>12.01</v>
+      </c>
       <c r="G415" t="n">
-        <v>73820918</v>
-      </c>
-      <c r="H415" s="2" t="n">
-        <v>0</v>
+        <v>75820900</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>-7.12</v>
       </c>
       <c r="I415" t="n">
         <v>13.5</v>
       </c>
-      <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr"/>
-      <c r="L415" t="inlineStr"/>
-      <c r="M415" t="inlineStr"/>
+      <c r="J415" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="K415" t="n">
+        <v>19.42</v>
+      </c>
+      <c r="L415" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="M415" t="n">
+        <v>24.43</v>
+      </c>
       <c r="N415" s="3" t="n">
-        <v>24.62</v>
+        <v>23.36</v>
       </c>
       <c r="O415" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31863,7 +31879,11 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R415" t="inlineStr"/>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
       <c r="S415" t="n">
         <v>5.09</v>
       </c>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31867,7 +31867,7 @@
         <v>23.36</v>
       </c>
       <c r="O415" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W415"/>
+  <dimension ref="A1:W416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31867,7 +31867,7 @@
         <v>23.36</v>
       </c>
       <c r="O415" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31897,6 +31897,83 @@
       <c r="W415" s="1" t="n">
         <v>160.4</v>
       </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>KORU</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>11.69</v>
+      </c>
+      <c r="D416" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="E416" t="n">
+        <v>11.17</v>
+      </c>
+      <c r="F416" t="n">
+        <v>11.23</v>
+      </c>
+      <c r="G416" t="n">
+        <v>22796162</v>
+      </c>
+      <c r="H416" s="1" t="n">
+        <v>-6.49</v>
+      </c>
+      <c r="I416" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J416" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="K416" t="n">
+        <v>19.24</v>
+      </c>
+      <c r="L416" t="n">
+        <v>28.26</v>
+      </c>
+      <c r="M416" t="n">
+        <v>24.44</v>
+      </c>
+      <c r="N416" s="3" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="O416" t="n">
+        <v>30</v>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R416" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S416" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="T416" s="2" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="U416" s="2" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="V416" t="inlineStr"/>
+      <c r="W416" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31916,22 +31916,22 @@
         <v>11.72</v>
       </c>
       <c r="E416" t="n">
-        <v>11.17</v>
+        <v>10.59</v>
       </c>
       <c r="F416" t="n">
-        <v>11.23</v>
+        <v>10.84</v>
       </c>
       <c r="G416" t="n">
-        <v>22796162</v>
+        <v>39806043</v>
       </c>
       <c r="H416" s="1" t="n">
-        <v>-6.49</v>
+        <v>-9.74</v>
       </c>
       <c r="I416" t="n">
         <v>13.5</v>
       </c>
       <c r="J416" t="n">
-        <v>19.06</v>
+        <v>19.04</v>
       </c>
       <c r="K416" t="n">
         <v>19.24</v>
@@ -31943,14 +31943,14 @@
         <v>24.44</v>
       </c>
       <c r="N416" s="3" t="n">
-        <v>23.9</v>
+        <v>23.39</v>
       </c>
       <c r="O416" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="P416" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>extreme fear</t>
         </is>
       </c>
       <c r="Q416" t="inlineStr">
@@ -31964,13 +31964,13 @@
         </is>
       </c>
       <c r="S416" t="n">
-        <v>5.09</v>
+        <v>5.1</v>
       </c>
       <c r="T416" s="2" t="n">
-        <v>15.9</v>
+        <v>21.3</v>
       </c>
       <c r="U416" s="2" t="n">
-        <v>8.1</v>
+        <v>22</v>
       </c>
       <c r="V416" t="inlineStr"/>
       <c r="W416" s="2" t="inlineStr"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31843,7 +31843,7 @@
         <v>12.01</v>
       </c>
       <c r="G415" t="n">
-        <v>75820900</v>
+        <v>77442000</v>
       </c>
       <c r="H415" s="1" t="n">
         <v>-7.12</v>
@@ -31916,34 +31916,34 @@
         <v>11.72</v>
       </c>
       <c r="E416" t="n">
-        <v>10.59</v>
+        <v>10.52</v>
       </c>
       <c r="F416" t="n">
-        <v>10.84</v>
+        <v>10.64</v>
       </c>
       <c r="G416" t="n">
-        <v>39806043</v>
+        <v>44648927</v>
       </c>
       <c r="H416" s="1" t="n">
-        <v>-9.74</v>
+        <v>-11.41</v>
       </c>
       <c r="I416" t="n">
         <v>13.5</v>
       </c>
       <c r="J416" t="n">
-        <v>19.04</v>
+        <v>19.03</v>
       </c>
       <c r="K416" t="n">
         <v>19.24</v>
       </c>
       <c r="L416" t="n">
-        <v>28.26</v>
+        <v>28.25</v>
       </c>
       <c r="M416" t="n">
         <v>24.44</v>
       </c>
       <c r="N416" s="3" t="n">
-        <v>23.39</v>
+        <v>23.13</v>
       </c>
       <c r="O416" t="n">
         <v>18</v>
@@ -31967,13 +31967,15 @@
         <v>5.1</v>
       </c>
       <c r="T416" s="2" t="n">
-        <v>21.3</v>
+        <v>20</v>
       </c>
       <c r="U416" s="2" t="n">
-        <v>22</v>
+        <v>23.3</v>
       </c>
       <c r="V416" t="inlineStr"/>
-      <c r="W416" s="2" t="inlineStr"/>
+      <c r="W416" s="1" t="n">
+        <v>168.6</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31834,25 +31834,41 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
-      <c r="D415" t="inlineStr"/>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
+      <c r="C415" t="n">
+        <v>11.69</v>
+      </c>
+      <c r="D415" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="E415" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="F415" t="n">
+        <v>10.64</v>
+      </c>
       <c r="G415" t="n">
-        <v>44648927</v>
-      </c>
-      <c r="H415" s="3" t="n">
-        <v>0</v>
+        <v>45555500</v>
+      </c>
+      <c r="H415" s="2" t="n">
+        <v>-11.41</v>
       </c>
       <c r="I415" t="n">
         <v>13.5</v>
       </c>
-      <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr"/>
-      <c r="L415" t="inlineStr"/>
-      <c r="M415" t="inlineStr"/>
+      <c r="J415" t="n">
+        <v>19.03</v>
+      </c>
+      <c r="K415" t="n">
+        <v>19.24</v>
+      </c>
+      <c r="L415" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="M415" t="n">
+        <v>24.44</v>
+      </c>
       <c r="N415" s="1" t="n">
-        <v>25.01</v>
+        <v>23.13</v>
       </c>
       <c r="O415" t="n">
         <v>18</v>
@@ -31867,7 +31883,11 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R415" t="inlineStr"/>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
       <c r="S415" t="n">
         <v>5.1</v>
       </c>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31721,7 +31721,7 @@
         <v>23.13</v>
       </c>
       <c r="O413" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7295,7 +7295,7 @@
         <v>13.5</v>
       </c>
       <c r="J90" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="K90" t="n">
         <v>2.67</v>
@@ -19051,7 +19051,7 @@
         <v>13.5</v>
       </c>
       <c r="J246" t="n">
-        <v>18.14</v>
+        <v>18.15</v>
       </c>
       <c r="K246" t="n">
         <v>12.11</v>
@@ -19126,7 +19126,7 @@
         <v>13.5</v>
       </c>
       <c r="J247" t="n">
-        <v>18.54</v>
+        <v>18.55</v>
       </c>
       <c r="K247" t="n">
         <v>12.38</v>
@@ -25626,7 +25626,7 @@
         <v>13.5</v>
       </c>
       <c r="J333" t="n">
-        <v>46.67</v>
+        <v>46.66</v>
       </c>
       <c r="K333" t="n">
         <v>35.18</v>
@@ -28141,7 +28141,7 @@
         <v>13.5</v>
       </c>
       <c r="J366" t="n">
-        <v>17.79</v>
+        <v>17.8</v>
       </c>
       <c r="K366" t="n">
         <v>32.76</v>
@@ -28595,7 +28595,7 @@
         <v>13.5</v>
       </c>
       <c r="J372" t="n">
-        <v>17.99</v>
+        <v>18</v>
       </c>
       <c r="K372" t="n">
         <v>31.04</v>
@@ -31633,7 +31633,7 @@
         <v>19.42</v>
       </c>
       <c r="L412" t="n">
-        <v>28.4</v>
+        <v>28.39</v>
       </c>
       <c r="M412" t="n">
         <v>24.43</v>
@@ -31721,7 +31721,7 @@
         <v>23.13</v>
       </c>
       <c r="O413" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31751,6 +31751,83 @@
       <c r="W413" s="1" t="n">
         <v>168.6</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>KORU</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>12.48</v>
+      </c>
+      <c r="D414" t="n">
+        <v>12.51</v>
+      </c>
+      <c r="E414" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="F414" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="G414" t="n">
+        <v>34524732</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>12.59</v>
+      </c>
+      <c r="I414" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J414" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="K414" t="n">
+        <v>19.14</v>
+      </c>
+      <c r="L414" t="n">
+        <v>28.13</v>
+      </c>
+      <c r="M414" t="n">
+        <v>24.45</v>
+      </c>
+      <c r="N414" s="3" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="O414" t="n">
+        <v>24</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>extreme fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S414" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -7073,7 +7073,7 @@
         <v>3.48</v>
       </c>
       <c r="K87" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="L87" t="n">
         <v>2.33</v>
@@ -7295,7 +7295,7 @@
         <v>13.5</v>
       </c>
       <c r="J90" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="K90" t="n">
         <v>2.67</v>
@@ -19051,7 +19051,7 @@
         <v>13.5</v>
       </c>
       <c r="J246" t="n">
-        <v>18.15</v>
+        <v>18.14</v>
       </c>
       <c r="K246" t="n">
         <v>12.11</v>
@@ -19126,7 +19126,7 @@
         <v>13.5</v>
       </c>
       <c r="J247" t="n">
-        <v>18.55</v>
+        <v>18.54</v>
       </c>
       <c r="K247" t="n">
         <v>12.38</v>
@@ -25626,7 +25626,7 @@
         <v>13.5</v>
       </c>
       <c r="J333" t="n">
-        <v>46.66</v>
+        <v>46.67</v>
       </c>
       <c r="K333" t="n">
         <v>35.18</v>
@@ -28141,7 +28141,7 @@
         <v>13.5</v>
       </c>
       <c r="J366" t="n">
-        <v>17.8</v>
+        <v>17.79</v>
       </c>
       <c r="K366" t="n">
         <v>32.76</v>
@@ -28595,7 +28595,7 @@
         <v>13.5</v>
       </c>
       <c r="J372" t="n">
-        <v>18</v>
+        <v>17.99</v>
       </c>
       <c r="K372" t="n">
         <v>31.04</v>
@@ -31773,13 +31773,13 @@
         <v>11.88</v>
       </c>
       <c r="F414" t="n">
-        <v>11.98</v>
+        <v>11.92</v>
       </c>
       <c r="G414" t="n">
-        <v>34524732</v>
+        <v>37830397</v>
       </c>
       <c r="H414" s="3" t="n">
-        <v>12.59</v>
+        <v>12.03</v>
       </c>
       <c r="I414" t="n">
         <v>13.5</v>
@@ -31797,10 +31797,10 @@
         <v>24.45</v>
       </c>
       <c r="N414" s="3" t="n">
-        <v>24.25</v>
+        <v>24.01</v>
       </c>
       <c r="O414" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31818,16 +31818,18 @@
         </is>
       </c>
       <c r="S414" t="n">
-        <v>5.13</v>
+        <v>5.14</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>11.4</v>
+        <v>11.9</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="1" t="n">
+        <v>161.9</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31721,7 +31721,7 @@
         <v>24.01</v>
       </c>
       <c r="O413" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31751,6 +31751,83 @@
       <c r="W413" s="1" t="n">
         <v>161.9</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>KORU</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="D414" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="E414" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="F414" t="n">
+        <v>11.64</v>
+      </c>
+      <c r="G414" t="n">
+        <v>30108277</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>-2.35</v>
+      </c>
+      <c r="I414" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J414" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="K414" t="n">
+        <v>19.04</v>
+      </c>
+      <c r="L414" t="n">
+        <v>28.01</v>
+      </c>
+      <c r="M414" t="n">
+        <v>24.46</v>
+      </c>
+      <c r="N414" s="3" t="n">
+        <v>25.64</v>
+      </c>
+      <c r="O414" t="n">
+        <v>28</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S414" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31773,19 +31773,19 @@
         <v>10.78</v>
       </c>
       <c r="F414" t="n">
-        <v>11.64</v>
+        <v>11.46</v>
       </c>
       <c r="G414" t="n">
-        <v>30108277</v>
+        <v>40820406</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>-2.35</v>
+        <v>-3.86</v>
       </c>
       <c r="I414" t="n">
         <v>13.5</v>
       </c>
       <c r="J414" t="n">
-        <v>17.89</v>
+        <v>17.88</v>
       </c>
       <c r="K414" t="n">
         <v>19.04</v>
@@ -31797,10 +31797,10 @@
         <v>24.46</v>
       </c>
       <c r="N414" s="3" t="n">
-        <v>25.64</v>
+        <v>25.37</v>
       </c>
       <c r="O414" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31818,13 +31818,13 @@
         </is>
       </c>
       <c r="S414" t="n">
-        <v>5.08</v>
+        <v>5.12</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>9.9</v>
+        <v>11.1</v>
       </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="inlineStr"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -7216,7 +7216,7 @@
         <v>13.5</v>
       </c>
       <c r="J89" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="K89" t="n">
         <v>2.67</v>
@@ -11669,7 +11669,7 @@
         <v>13.5</v>
       </c>
       <c r="J148" t="n">
-        <v>4.85</v>
+        <v>4.86</v>
       </c>
       <c r="K148" t="n">
         <v>4.34</v>
@@ -18972,7 +18972,7 @@
         <v>13.5</v>
       </c>
       <c r="J245" t="n">
-        <v>18.14</v>
+        <v>18.15</v>
       </c>
       <c r="K245" t="n">
         <v>12.11</v>
@@ -19047,7 +19047,7 @@
         <v>13.5</v>
       </c>
       <c r="J246" t="n">
-        <v>18.54</v>
+        <v>18.55</v>
       </c>
       <c r="K246" t="n">
         <v>12.38</v>
@@ -25547,7 +25547,7 @@
         <v>13.5</v>
       </c>
       <c r="J332" t="n">
-        <v>46.67</v>
+        <v>46.66</v>
       </c>
       <c r="K332" t="n">
         <v>35.18</v>
@@ -28062,7 +28062,7 @@
         <v>13.5</v>
       </c>
       <c r="J365" t="n">
-        <v>17.79</v>
+        <v>17.8</v>
       </c>
       <c r="K365" t="n">
         <v>32.76</v>
@@ -28516,7 +28516,7 @@
         <v>13.5</v>
       </c>
       <c r="J371" t="n">
-        <v>17.99</v>
+        <v>18</v>
       </c>
       <c r="K371" t="n">
         <v>31.04</v>
@@ -31554,7 +31554,7 @@
         <v>19.42</v>
       </c>
       <c r="L411" t="n">
-        <v>28.39</v>
+        <v>28.4</v>
       </c>
       <c r="M411" t="n">
         <v>24.43</v>
@@ -31697,7 +31697,7 @@
         <v>11.92</v>
       </c>
       <c r="G413" t="n">
-        <v>38147400</v>
+        <v>39043100</v>
       </c>
       <c r="H413" s="3" t="n">
         <v>12.03</v>
@@ -31773,13 +31773,13 @@
         <v>10.78</v>
       </c>
       <c r="F414" t="n">
-        <v>11.46</v>
+        <v>11.34</v>
       </c>
       <c r="G414" t="n">
-        <v>40820406</v>
+        <v>44699825</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>-3.86</v>
+        <v>-4.87</v>
       </c>
       <c r="I414" t="n">
         <v>13.5</v>
@@ -31797,7 +31797,7 @@
         <v>24.46</v>
       </c>
       <c r="N414" s="3" t="n">
-        <v>25.37</v>
+        <v>25.2</v>
       </c>
       <c r="O414" t="n">
         <v>27</v>
@@ -31821,13 +31821,15 @@
         <v>5.12</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>17.5</v>
+        <v>17.3</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="1" t="n">
+        <v>160.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31721,7 +31721,7 @@
         <v>25.2</v>
       </c>
       <c r="O413" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31721,7 +31721,7 @@
         <v>25.2</v>
       </c>
       <c r="O413" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31751,6 +31751,81 @@
       <c r="W413" s="1" t="n">
         <v>160.4</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>KORU</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="D414" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="E414" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="F414" t="n">
+        <v>12.11</v>
+      </c>
+      <c r="G414" t="n">
+        <v>11319789</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="I414" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J414" t="n">
+        <v>17.42</v>
+      </c>
+      <c r="K414" t="n">
+        <v>19</v>
+      </c>
+      <c r="L414" t="n">
+        <v>27.87</v>
+      </c>
+      <c r="M414" t="n">
+        <v>24.46</v>
+      </c>
+      <c r="N414" s="3" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="O414" t="n">
+        <v>29</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S414" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="U414" s="2" t="inlineStr"/>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31721,7 +31721,7 @@
         <v>25.2</v>
       </c>
       <c r="O413" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31764,28 +31764,28 @@
         </is>
       </c>
       <c r="C414" t="n">
-        <v>10.9</v>
+        <v>12.3</v>
       </c>
       <c r="D414" t="n">
         <v>12.37</v>
       </c>
       <c r="E414" t="n">
-        <v>12.1</v>
+        <v>11.27</v>
       </c>
       <c r="F414" t="n">
-        <v>12.11</v>
+        <v>11.94</v>
       </c>
       <c r="G414" t="n">
-        <v>11319789</v>
+        <v>32845841</v>
       </c>
       <c r="H414" s="3" t="n">
-        <v>6.79</v>
+        <v>5.29</v>
       </c>
       <c r="I414" t="n">
         <v>13.5</v>
       </c>
       <c r="J414" t="n">
-        <v>17.42</v>
+        <v>17.41</v>
       </c>
       <c r="K414" t="n">
         <v>19</v>
@@ -31797,10 +31797,10 @@
         <v>24.46</v>
       </c>
       <c r="N414" s="3" t="n">
-        <v>23.9</v>
+        <v>23.14</v>
       </c>
       <c r="O414" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31818,12 +31818,14 @@
         </is>
       </c>
       <c r="S414" t="n">
-        <v>5.1</v>
+        <v>5.11</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="U414" s="2" t="inlineStr"/>
+        <v>16.6</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="inlineStr"/>
     </row>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -6915,7 +6915,7 @@
         <v>3.48</v>
       </c>
       <c r="K85" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="L85" t="n">
         <v>2.33</v>
@@ -11590,7 +11590,7 @@
         <v>13.5</v>
       </c>
       <c r="J147" t="n">
-        <v>4.86</v>
+        <v>4.85</v>
       </c>
       <c r="K147" t="n">
         <v>4.34</v>
@@ -31697,7 +31697,7 @@
         <v>11.34</v>
       </c>
       <c r="G413" t="n">
-        <v>46691600</v>
+        <v>48621700</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>-4.87</v>
@@ -31776,7 +31776,7 @@
         <v>11.94</v>
       </c>
       <c r="G414" t="n">
-        <v>32845841</v>
+        <v>39802990</v>
       </c>
       <c r="H414" s="3" t="n">
         <v>5.29</v>
@@ -31800,7 +31800,7 @@
         <v>23.14</v>
       </c>
       <c r="O414" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31818,16 +31818,18 @@
         </is>
       </c>
       <c r="S414" t="n">
-        <v>5.11</v>
+        <v>5.15</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>10</v>
+        <v>11.4</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="n">
+        <v>150.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31763,41 +31763,25 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="C414" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="D414" t="n">
-        <v>12.37</v>
-      </c>
-      <c r="E414" t="n">
-        <v>11.27</v>
-      </c>
-      <c r="F414" t="n">
-        <v>11.94</v>
-      </c>
+      <c r="C414" t="inlineStr"/>
+      <c r="D414" t="inlineStr"/>
+      <c r="E414" t="inlineStr"/>
+      <c r="F414" t="inlineStr"/>
       <c r="G414" t="n">
         <v>39802990</v>
       </c>
-      <c r="H414" s="3" t="n">
-        <v>5.29</v>
+      <c r="H414" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="I414" t="n">
         <v>13.5</v>
       </c>
-      <c r="J414" t="n">
-        <v>17.41</v>
-      </c>
-      <c r="K414" t="n">
-        <v>19</v>
-      </c>
-      <c r="L414" t="n">
-        <v>27.87</v>
-      </c>
-      <c r="M414" t="n">
-        <v>24.46</v>
-      </c>
+      <c r="J414" t="inlineStr"/>
+      <c r="K414" t="inlineStr"/>
+      <c r="L414" t="inlineStr"/>
+      <c r="M414" t="inlineStr"/>
       <c r="N414" s="3" t="n">
-        <v>23.14</v>
+        <v>20.33</v>
       </c>
       <c r="O414" t="n">
         <v>31</v>
@@ -31812,11 +31796,7 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R414" t="inlineStr">
-        <is>
-          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
-        </is>
-      </c>
+      <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
         <v>5.15</v>
       </c>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31763,28 +31763,44 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr"/>
-      <c r="D414" t="inlineStr"/>
-      <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
+      <c r="C414" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="D414" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="E414" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="F414" t="n">
+        <v>11.94</v>
+      </c>
       <c r="G414" t="n">
-        <v>39802990</v>
-      </c>
-      <c r="H414" s="2" t="n">
-        <v>0</v>
+        <v>40638400</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>5.29</v>
       </c>
       <c r="I414" t="n">
         <v>13.5</v>
       </c>
-      <c r="J414" t="inlineStr"/>
-      <c r="K414" t="inlineStr"/>
-      <c r="L414" t="inlineStr"/>
-      <c r="M414" t="inlineStr"/>
+      <c r="J414" t="n">
+        <v>17.41</v>
+      </c>
+      <c r="K414" t="n">
+        <v>19</v>
+      </c>
+      <c r="L414" t="n">
+        <v>27.87</v>
+      </c>
+      <c r="M414" t="n">
+        <v>24.46</v>
+      </c>
       <c r="N414" s="3" t="n">
-        <v>20.33</v>
+        <v>23.14</v>
       </c>
       <c r="O414" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31796,7 +31812,11 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R414" t="inlineStr"/>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
       <c r="S414" t="n">
         <v>5.15</v>
       </c>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31800,7 +31800,7 @@
         <v>23.14</v>
       </c>
       <c r="O414" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31830,6 +31830,81 @@
       <c r="W414" s="2" t="n">
         <v>150.4</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>KORU</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="D415" t="n">
+        <v>11.08</v>
+      </c>
+      <c r="E415" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="F415" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="G415" t="n">
+        <v>15055614</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>-8.039999999999999</v>
+      </c>
+      <c r="I415" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J415" t="n">
+        <v>16.95</v>
+      </c>
+      <c r="K415" t="n">
+        <v>18.98</v>
+      </c>
+      <c r="L415" t="n">
+        <v>27.71</v>
+      </c>
+      <c r="M415" t="n">
+        <v>24.45</v>
+      </c>
+      <c r="N415" s="3" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="O415" t="n">
+        <v>28</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S415" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="T415" s="2" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="U415" s="2" t="inlineStr"/>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -608,7 +608,7 @@
         <v>-1.49</v>
       </c>
       <c r="I2" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J2" t="n">
         <v>2.19</v>
@@ -683,7 +683,7 @@
         <v>1.01</v>
       </c>
       <c r="I3" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J3" t="n">
         <v>2.19</v>
@@ -758,7 +758,7 @@
         <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J4" t="n">
         <v>2.2</v>
@@ -833,7 +833,7 @@
         <v>-5.56</v>
       </c>
       <c r="I5" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J5" t="n">
         <v>2.2</v>
@@ -912,7 +912,7 @@
         <v>3.43</v>
       </c>
       <c r="I6" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J6" t="n">
         <v>2.2</v>
@@ -987,7 +987,7 @@
         <v>-8.529999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J7" t="n">
         <v>2.2</v>
@@ -1070,7 +1070,7 @@
         <v>3.11</v>
       </c>
       <c r="I8" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J8" t="n">
         <v>2.19</v>
@@ -1149,7 +1149,7 @@
         <v>7.04</v>
       </c>
       <c r="I9" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J9" t="n">
         <v>2.19</v>
@@ -1224,7 +1224,7 @@
         <v>-3.76</v>
       </c>
       <c r="I10" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J10" t="n">
         <v>2.19</v>
@@ -1303,7 +1303,7 @@
         <v>4.88</v>
       </c>
       <c r="I11" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J11" t="n">
         <v>2.19</v>
@@ -1378,7 +1378,7 @@
         <v>8.84</v>
       </c>
       <c r="I12" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J12" t="n">
         <v>2.19</v>
@@ -1453,7 +1453,7 @@
         <v>-4.7</v>
       </c>
       <c r="I13" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J13" t="n">
         <v>2.18</v>
@@ -1528,7 +1528,7 @@
         <v>1.35</v>
       </c>
       <c r="I14" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J14" t="n">
         <v>2.17</v>
@@ -1603,7 +1603,7 @@
         <v>-2.65</v>
       </c>
       <c r="I15" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J15" t="n">
         <v>2.16</v>
@@ -1678,7 +1678,7 @@
         <v>0.91</v>
       </c>
       <c r="I16" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J16" t="n">
         <v>2.15</v>
@@ -1753,7 +1753,7 @@
         <v>2.25</v>
       </c>
       <c r="I17" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J17" t="n">
         <v>2.15</v>
@@ -1828,7 +1828,7 @@
         <v>-1.32</v>
       </c>
       <c r="I18" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J18" t="n">
         <v>2.14</v>
@@ -1903,7 +1903,7 @@
         <v>-1.34</v>
       </c>
       <c r="I19" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J19" t="n">
         <v>2.13</v>
@@ -1978,7 +1978,7 @@
         <v>-1.81</v>
       </c>
       <c r="I20" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J20" t="n">
         <v>2.13</v>
@@ -2053,7 +2053,7 @@
         <v>-9.220000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J21" t="n">
         <v>2.13</v>
@@ -2132,7 +2132,7 @@
         <v>-4.06</v>
       </c>
       <c r="I22" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J22" t="n">
         <v>2.13</v>
@@ -2207,7 +2207,7 @@
         <v>4.76</v>
       </c>
       <c r="I23" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J23" t="n">
         <v>2.13</v>
@@ -2282,7 +2282,7 @@
         <v>-1.01</v>
       </c>
       <c r="I24" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J24" t="n">
         <v>2.12</v>
@@ -2357,7 +2357,7 @@
         <v>-8.67</v>
       </c>
       <c r="I25" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J25" t="n">
         <v>2.1</v>
@@ -2436,7 +2436,7 @@
         <v>-10.61</v>
       </c>
       <c r="I26" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J26" t="n">
         <v>2.08</v>
@@ -2519,7 +2519,7 @@
         <v>-3.12</v>
       </c>
       <c r="I27" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J27" t="n">
         <v>2.06</v>
@@ -2602,7 +2602,7 @@
         <v>-10.32</v>
       </c>
       <c r="I28" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J28" t="n">
         <v>2.03</v>
@@ -2685,7 +2685,7 @@
         <v>24.46</v>
       </c>
       <c r="I29" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J29" t="n">
         <v>2.01</v>
@@ -2764,7 +2764,7 @@
         <v>-6.94</v>
       </c>
       <c r="I30" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J30" t="n">
         <v>1.99</v>
@@ -2843,7 +2843,7 @@
         <v>14.29</v>
       </c>
       <c r="I31" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J31" t="n">
         <v>1.97</v>
@@ -2922,7 +2922,7 @@
         <v>-0.54</v>
       </c>
       <c r="I32" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J32" t="n">
         <v>1.95</v>
@@ -2997,7 +2997,7 @@
         <v>0.55</v>
       </c>
       <c r="I33" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J33" t="n">
         <v>1.93</v>
@@ -3072,7 +3072,7 @@
         <v>-2.17</v>
       </c>
       <c r="I34" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J34" t="n">
         <v>1.9</v>
@@ -3151,7 +3151,7 @@
         <v>1.67</v>
       </c>
       <c r="I35" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J35" t="n">
         <v>1.89</v>
@@ -3230,7 +3230,7 @@
         <v>0.55</v>
       </c>
       <c r="I36" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J36" t="n">
         <v>1.87</v>
@@ -3305,7 +3305,7 @@
         <v>2.17</v>
       </c>
       <c r="I37" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J37" t="n">
         <v>1.85</v>
@@ -3380,7 +3380,7 @@
         <v>3.72</v>
       </c>
       <c r="I38" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J38" t="n">
         <v>1.83</v>
@@ -3459,7 +3459,7 @@
         <v>2.05</v>
       </c>
       <c r="I39" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J39" t="n">
         <v>1.82</v>
@@ -3534,7 +3534,7 @@
         <v>-0.5</v>
       </c>
       <c r="I40" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J40" t="n">
         <v>1.81</v>
@@ -3609,7 +3609,7 @@
         <v>-1.01</v>
       </c>
       <c r="I41" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J41" t="n">
         <v>1.81</v>
@@ -3684,7 +3684,7 @@
         <v>2.55</v>
       </c>
       <c r="I42" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J42" t="n">
         <v>1.82</v>
@@ -3759,7 +3759,7 @@
         <v>0.5</v>
       </c>
       <c r="I43" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J43" t="n">
         <v>1.82</v>
@@ -3834,7 +3834,7 @@
         <v>-2.97</v>
       </c>
       <c r="I44" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J44" t="n">
         <v>1.82</v>
@@ -3909,7 +3909,7 @@
         <v>10.71</v>
       </c>
       <c r="I45" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J45" t="n">
         <v>1.84</v>
@@ -3984,7 +3984,7 @@
         <v>4.15</v>
       </c>
       <c r="I46" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J46" t="n">
         <v>1.87</v>
@@ -4059,7 +4059,7 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J47" t="n">
         <v>1.91</v>
@@ -4134,7 +4134,7 @@
         <v>-3.54</v>
       </c>
       <c r="I48" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J48" t="n">
         <v>1.95</v>
@@ -4209,7 +4209,7 @@
         <v>-3.21</v>
       </c>
       <c r="I49" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J49" t="n">
         <v>1.97</v>
@@ -4284,7 +4284,7 @@
         <v>2.84</v>
       </c>
       <c r="I50" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J50" t="n">
         <v>1.99</v>
@@ -4359,7 +4359,7 @@
         <v>1.38</v>
       </c>
       <c r="I51" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J51" t="n">
         <v>2.01</v>
@@ -4434,7 +4434,7 @@
         <v>0.45</v>
       </c>
       <c r="I52" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J52" t="n">
         <v>2.03</v>
@@ -4509,7 +4509,7 @@
         <v>2.71</v>
       </c>
       <c r="I53" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J53" t="n">
         <v>2.05</v>
@@ -4584,7 +4584,7 @@
         <v>0.88</v>
       </c>
       <c r="I54" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J54" t="n">
         <v>2.08</v>
@@ -4659,7 +4659,7 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J55" t="n">
         <v>2.1</v>
@@ -4734,7 +4734,7 @@
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J56" t="n">
         <v>2.12</v>
@@ -4809,7 +4809,7 @@
         <v>-2.18</v>
       </c>
       <c r="I57" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J57" t="n">
         <v>2.14</v>
@@ -4884,7 +4884,7 @@
         <v>3.57</v>
       </c>
       <c r="I58" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J58" t="n">
         <v>2.16</v>
@@ -4959,7 +4959,7 @@
         <v>-3.88</v>
       </c>
       <c r="I59" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J59" t="n">
         <v>2.17</v>
@@ -5034,7 +5034,7 @@
         <v>3.14</v>
       </c>
       <c r="I60" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J60" t="n">
         <v>2.19</v>
@@ -5109,7 +5109,7 @@
         <v>4.78</v>
       </c>
       <c r="I61" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J61" t="n">
         <v>2.21</v>
@@ -5184,7 +5184,7 @@
         <v>3.73</v>
       </c>
       <c r="I62" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J62" t="n">
         <v>2.23</v>
@@ -5259,7 +5259,7 @@
         <v>5.2</v>
       </c>
       <c r="I63" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J63" t="n">
         <v>2.26</v>
@@ -5334,7 +5334,7 @@
         <v>-5.7</v>
       </c>
       <c r="I64" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J64" t="n">
         <v>2.29</v>
@@ -5409,7 +5409,7 @@
         <v>5.65</v>
       </c>
       <c r="I65" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J65" t="n">
         <v>2.31</v>
@@ -5484,7 +5484,7 @@
         <v>1.15</v>
       </c>
       <c r="I66" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J66" t="n">
         <v>2.33</v>
@@ -5559,7 +5559,7 @@
         <v>9.43</v>
       </c>
       <c r="I67" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J67" t="n">
         <v>2.36</v>
@@ -5634,7 +5634,7 @@
         <v>6.55</v>
       </c>
       <c r="I68" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J68" t="n">
         <v>2.41</v>
@@ -5709,7 +5709,7 @@
         <v>0.65</v>
       </c>
       <c r="I69" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J69" t="n">
         <v>2.46</v>
@@ -5784,7 +5784,7 @@
         <v>4.5</v>
       </c>
       <c r="I70" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J70" t="n">
         <v>2.51</v>
@@ -5859,7 +5859,7 @@
         <v>-1.54</v>
       </c>
       <c r="I71" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J71" t="n">
         <v>2.56</v>
@@ -5934,7 +5934,7 @@
         <v>3.75</v>
       </c>
       <c r="I72" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J72" t="n">
         <v>2.62</v>
@@ -6009,7 +6009,7 @@
         <v>3.31</v>
       </c>
       <c r="I73" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J73" t="n">
         <v>2.68</v>
@@ -6084,7 +6084,7 @@
         <v>-5.83</v>
       </c>
       <c r="I74" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J74" t="n">
         <v>2.72</v>
@@ -6159,7 +6159,7 @@
         <v>8.050000000000001</v>
       </c>
       <c r="I75" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J75" t="n">
         <v>2.78</v>
@@ -6234,7 +6234,7 @@
         <v>-6.88</v>
       </c>
       <c r="I76" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J76" t="n">
         <v>2.83</v>
@@ -6309,7 +6309,7 @@
         <v>5.23</v>
       </c>
       <c r="I77" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J77" t="n">
         <v>2.89</v>
@@ -6384,7 +6384,7 @@
         <v>2.92</v>
       </c>
       <c r="I78" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J78" t="n">
         <v>2.95</v>
@@ -6459,7 +6459,7 @@
         <v>3.69</v>
       </c>
       <c r="I79" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J79" t="n">
         <v>3.02</v>
@@ -6534,7 +6534,7 @@
         <v>14.25</v>
       </c>
       <c r="I80" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J80" t="n">
         <v>3.12</v>
@@ -6609,7 +6609,7 @@
         <v>-1.2</v>
       </c>
       <c r="I81" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J81" t="n">
         <v>3.2</v>
@@ -6684,7 +6684,7 @@
         <v>-1.94</v>
       </c>
       <c r="I82" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J82" t="n">
         <v>3.28</v>
@@ -6759,7 +6759,7 @@
         <v>-4.95</v>
       </c>
       <c r="I83" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J83" t="n">
         <v>3.34</v>
@@ -6834,7 +6834,7 @@
         <v>4.17</v>
       </c>
       <c r="I84" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J84" t="n">
         <v>3.42</v>
@@ -6909,7 +6909,7 @@
         <v>-0.5</v>
       </c>
       <c r="I85" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J85" t="n">
         <v>3.48</v>
@@ -6984,7 +6984,7 @@
         <v>1.26</v>
       </c>
       <c r="I86" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J86" t="n">
         <v>3.55</v>
@@ -7059,7 +7059,7 @@
         <v>2.73</v>
       </c>
       <c r="I87" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J87" t="n">
         <v>3.61</v>
@@ -7134,7 +7134,7 @@
         <v>-10.39</v>
       </c>
       <c r="I88" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J88" t="n">
         <v>3.65</v>
@@ -7209,7 +7209,7 @@
         <v>8.09</v>
       </c>
       <c r="I89" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J89" t="n">
         <v>3.69</v>
@@ -7284,7 +7284,7 @@
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J90" t="n">
         <v>3.73</v>
@@ -7359,7 +7359,7 @@
         <v>4.49</v>
       </c>
       <c r="I91" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J91" t="n">
         <v>3.78</v>
@@ -7434,7 +7434,7 @@
         <v>-2.39</v>
       </c>
       <c r="I92" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J92" t="n">
         <v>3.82</v>
@@ -7509,7 +7509,7 @@
         <v>2.44</v>
       </c>
       <c r="I93" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J93" t="n">
         <v>3.85</v>
@@ -7584,7 +7584,7 @@
         <v>-0.48</v>
       </c>
       <c r="I94" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J94" t="n">
         <v>3.9</v>
@@ -7659,7 +7659,7 @@
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J95" t="n">
         <v>3.94</v>
@@ -7734,7 +7734,7 @@
         <v>-0.24</v>
       </c>
       <c r="I96" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J96" t="n">
         <v>3.98</v>
@@ -7809,7 +7809,7 @@
         <v>-2.64</v>
       </c>
       <c r="I97" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J97" t="n">
         <v>4.01</v>
@@ -7884,7 +7884,7 @@
         <v>5.93</v>
       </c>
       <c r="I98" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J98" t="n">
         <v>4.05</v>
@@ -7959,7 +7959,7 @@
         <v>-3.73</v>
       </c>
       <c r="I99" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J99" t="n">
         <v>4.07</v>
@@ -8034,7 +8034,7 @@
         <v>3.63</v>
       </c>
       <c r="I100" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J100" t="n">
         <v>4.08</v>
@@ -8109,7 +8109,7 @@
         <v>-2.1</v>
       </c>
       <c r="I101" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J101" t="n">
         <v>4.08</v>
@@ -8184,7 +8184,7 @@
         <v>-0.48</v>
       </c>
       <c r="I102" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J102" t="n">
         <v>4.09</v>
@@ -8259,7 +8259,7 @@
         <v>-2.16</v>
       </c>
       <c r="I103" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J103" t="n">
         <v>4.1</v>
@@ -8338,7 +8338,7 @@
         <v>3.19</v>
       </c>
       <c r="I104" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J104" t="n">
         <v>4.11</v>
@@ -8413,7 +8413,7 @@
         <v>0.95</v>
       </c>
       <c r="I105" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J105" t="n">
         <v>4.13</v>
@@ -8488,7 +8488,7 @@
         <v>-3.76</v>
       </c>
       <c r="I106" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J106" t="n">
         <v>4.13</v>
@@ -8567,7 +8567,7 @@
         <v>-9.050000000000001</v>
       </c>
       <c r="I107" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J107" t="n">
         <v>4.11</v>
@@ -8642,7 +8642,7 @@
         <v>7.26</v>
       </c>
       <c r="I108" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J108" t="n">
         <v>4.12</v>
@@ -8717,7 +8717,7 @@
         <v>2.26</v>
       </c>
       <c r="I109" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J109" t="n">
         <v>4.13</v>
@@ -8792,7 +8792,7 @@
         <v>0.98</v>
       </c>
       <c r="I110" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J110" t="n">
         <v>4.13</v>
@@ -8867,7 +8867,7 @@
         <v>0.97</v>
       </c>
       <c r="I111" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J111" t="n">
         <v>4.13</v>
@@ -8942,7 +8942,7 @@
         <v>0.24</v>
       </c>
       <c r="I112" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J112" t="n">
         <v>4.13</v>
@@ -9017,7 +9017,7 @@
         <v>-1.92</v>
       </c>
       <c r="I113" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J113" t="n">
         <v>4.13</v>
@@ -9096,7 +9096,7 @@
         <v>4.16</v>
       </c>
       <c r="I114" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J114" t="n">
         <v>4.13</v>
@@ -9171,7 +9171,7 @@
         <v>2.58</v>
       </c>
       <c r="I115" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J115" t="n">
         <v>4.14</v>
@@ -9246,7 +9246,7 @@
         <v>-4.12</v>
       </c>
       <c r="I116" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J116" t="n">
         <v>4.14</v>
@@ -9321,7 +9321,7 @@
         <v>-1.19</v>
       </c>
       <c r="I117" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J117" t="n">
         <v>4.15</v>
@@ -9400,7 +9400,7 @@
         <v>-2.42</v>
       </c>
       <c r="I118" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J118" t="n">
         <v>4.14</v>
@@ -9475,7 +9475,7 @@
         <v>-5.45</v>
       </c>
       <c r="I119" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J119" t="n">
         <v>4.12</v>
@@ -9550,7 +9550,7 @@
         <v>-0.52</v>
       </c>
       <c r="I120" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J120" t="n">
         <v>4.1</v>
@@ -9625,7 +9625,7 @@
         <v>-0.79</v>
       </c>
       <c r="I121" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J121" t="n">
         <v>4.08</v>
@@ -9704,7 +9704,7 @@
         <v>9.81</v>
       </c>
       <c r="I122" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J122" t="n">
         <v>4.07</v>
@@ -9779,7 +9779,7 @@
         <v>-3.38</v>
       </c>
       <c r="I123" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J123" t="n">
         <v>4.07</v>
@@ -9858,7 +9858,7 @@
         <v>-1.5</v>
       </c>
       <c r="I124" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J124" t="n">
         <v>4.06</v>
@@ -9933,7 +9933,7 @@
         <v>0.51</v>
       </c>
       <c r="I125" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J125" t="n">
         <v>4.04</v>
@@ -10008,7 +10008,7 @@
         <v>4.55</v>
       </c>
       <c r="I126" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J126" t="n">
         <v>4.04</v>
@@ -10083,7 +10083,7 @@
         <v>-5.56</v>
       </c>
       <c r="I127" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J127" t="n">
         <v>4.05</v>
@@ -10162,7 +10162,7 @@
         <v>-1.53</v>
       </c>
       <c r="I128" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J128" t="n">
         <v>4.05</v>
@@ -10237,7 +10237,7 @@
         <v>3.9</v>
       </c>
       <c r="I129" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J129" t="n">
         <v>4.04</v>
@@ -10312,7 +10312,7 @@
         <v>0.75</v>
       </c>
       <c r="I130" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J130" t="n">
         <v>4.04</v>
@@ -10387,7 +10387,7 @@
         <v>2.23</v>
       </c>
       <c r="I131" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J131" t="n">
         <v>4.04</v>
@@ -10462,7 +10462,7 @@
         <v>1.94</v>
       </c>
       <c r="I132" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J132" t="n">
         <v>4.04</v>
@@ -10537,7 +10537,7 @@
         <v>3.1</v>
       </c>
       <c r="I133" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J133" t="n">
         <v>4.05</v>
@@ -10612,7 +10612,7 @@
         <v>6.93</v>
       </c>
       <c r="I134" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J134" t="n">
         <v>4.07</v>
@@ -10687,7 +10687,7 @@
         <v>4.75</v>
       </c>
       <c r="I135" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J135" t="n">
         <v>4.09</v>
@@ -10762,7 +10762,7 @@
         <v>3.09</v>
       </c>
       <c r="I136" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J136" t="n">
         <v>4.13</v>
@@ -10837,7 +10837,7 @@
         <v>2</v>
       </c>
       <c r="I137" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J137" t="n">
         <v>4.18</v>
@@ -10912,7 +10912,7 @@
         <v>5.69</v>
       </c>
       <c r="I138" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J138" t="n">
         <v>4.25</v>
@@ -10987,7 +10987,7 @@
         <v>-3.34</v>
       </c>
       <c r="I139" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J139" t="n">
         <v>4.32</v>
@@ -11062,7 +11062,7 @@
         <v>3.65</v>
       </c>
       <c r="I140" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J140" t="n">
         <v>4.4</v>
@@ -11137,7 +11137,7 @@
         <v>-2.96</v>
       </c>
       <c r="I141" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J141" t="n">
         <v>4.47</v>
@@ -11212,7 +11212,7 @@
         <v>5.92</v>
       </c>
       <c r="I142" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J142" t="n">
         <v>4.54</v>
@@ -11287,7 +11287,7 @@
         <v>-0.54</v>
       </c>
       <c r="I143" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J143" t="n">
         <v>4.62</v>
@@ -11362,7 +11362,7 @@
         <v>-5.25</v>
       </c>
       <c r="I144" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J144" t="n">
         <v>4.68</v>
@@ -11437,7 +11437,7 @@
         <v>-0.57</v>
       </c>
       <c r="I145" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J145" t="n">
         <v>4.74</v>
@@ -11512,7 +11512,7 @@
         <v>-3.85</v>
       </c>
       <c r="I146" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J146" t="n">
         <v>4.79</v>
@@ -11587,7 +11587,7 @@
         <v>5</v>
       </c>
       <c r="I147" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J147" t="n">
         <v>4.85</v>
@@ -11662,7 +11662,7 @@
         <v>-0.38</v>
       </c>
       <c r="I148" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J148" t="n">
         <v>4.92</v>
@@ -11737,7 +11737,7 @@
         <v>6.5</v>
       </c>
       <c r="I149" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J149" t="n">
         <v>5</v>
@@ -11812,7 +11812,7 @@
         <v>6.1</v>
       </c>
       <c r="I150" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J150" t="n">
         <v>5.1</v>
@@ -11887,7 +11887,7 @@
         <v>1.18</v>
       </c>
       <c r="I151" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J151" t="n">
         <v>5.19</v>
@@ -11962,7 +11962,7 @@
         <v>3.18</v>
       </c>
       <c r="I152" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J152" t="n">
         <v>5.29</v>
@@ -12037,7 +12037,7 @@
         <v>-4.86</v>
       </c>
       <c r="I153" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J153" t="n">
         <v>5.36</v>
@@ -12112,7 +12112,7 @@
         <v>2.73</v>
       </c>
       <c r="I154" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J154" t="n">
         <v>5.44</v>
@@ -12187,7 +12187,7 @@
         <v>-2.65</v>
       </c>
       <c r="I155" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J155" t="n">
         <v>5.49</v>
@@ -12262,7 +12262,7 @@
         <v>-9.710000000000001</v>
       </c>
       <c r="I156" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J156" t="n">
         <v>5.5</v>
@@ -12341,7 +12341,7 @@
         <v>10.38</v>
       </c>
       <c r="I157" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J157" t="n">
         <v>5.54</v>
@@ -12416,7 +12416,7 @@
         <v>-3.25</v>
       </c>
       <c r="I158" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J158" t="n">
         <v>5.55</v>
@@ -12491,7 +12491,7 @@
         <v>8.83</v>
       </c>
       <c r="I159" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J159" t="n">
         <v>5.6</v>
@@ -12566,7 +12566,7 @@
         <v>9.58</v>
       </c>
       <c r="I160" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J160" t="n">
         <v>5.67</v>
@@ -12641,7 +12641,7 @@
         <v>2.07</v>
       </c>
       <c r="I161" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J161" t="n">
         <v>5.75</v>
@@ -12716,7 +12716,7 @@
         <v>6.68</v>
       </c>
       <c r="I162" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J162" t="n">
         <v>5.84</v>
@@ -12791,7 +12791,7 @@
         <v>-6.12</v>
       </c>
       <c r="I163" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J163" t="n">
         <v>5.91</v>
@@ -12866,7 +12866,7 @@
         <v>2.75</v>
       </c>
       <c r="I164" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J164" t="n">
         <v>6</v>
@@ -12941,7 +12941,7 @@
         <v>1.97</v>
       </c>
       <c r="I165" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J165" t="n">
         <v>6.1</v>
@@ -13016,7 +13016,7 @@
         <v>6.64</v>
       </c>
       <c r="I166" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J166" t="n">
         <v>6.24</v>
@@ -13091,7 +13091,7 @@
         <v>7.39</v>
       </c>
       <c r="I167" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J167" t="n">
         <v>6.39</v>
@@ -13166,7 +13166,7 @@
         <v>0.36</v>
       </c>
       <c r="I168" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J168" t="n">
         <v>6.54</v>
@@ -13241,7 +13241,7 @@
         <v>7.82</v>
       </c>
       <c r="I169" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J169" t="n">
         <v>6.71</v>
@@ -13316,7 +13316,7 @@
         <v>-5.02</v>
       </c>
       <c r="I170" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J170" t="n">
         <v>6.84</v>
@@ -13391,7 +13391,7 @@
         <v>5.17</v>
       </c>
       <c r="I171" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J171" t="n">
         <v>6.99</v>
@@ -13466,7 +13466,7 @@
         <v>11.62</v>
       </c>
       <c r="I172" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J172" t="n">
         <v>7.18</v>
@@ -13541,7 +13541,7 @@
         <v>-14.81</v>
       </c>
       <c r="I173" s="4" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J173" s="4" t="n">
         <v>7.32</v>
@@ -13616,7 +13616,7 @@
         <v>2.47</v>
       </c>
       <c r="I174" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J174" t="n">
         <v>7.45</v>
@@ -13691,7 +13691,7 @@
         <v>-9.52</v>
       </c>
       <c r="I175" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J175" t="n">
         <v>7.55</v>
@@ -13766,7 +13766,7 @@
         <v>-5.7</v>
       </c>
       <c r="I176" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J176" t="n">
         <v>7.66</v>
@@ -13845,7 +13845,7 @@
         <v>12.5</v>
       </c>
       <c r="I177" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J177" t="n">
         <v>7.78</v>
@@ -13920,7 +13920,7 @@
         <v>-1.19</v>
       </c>
       <c r="I178" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J178" t="n">
         <v>7.91</v>
@@ -13995,7 +13995,7 @@
         <v>2.06</v>
       </c>
       <c r="I179" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J179" t="n">
         <v>8.029999999999999</v>
@@ -14070,7 +14070,7 @@
         <v>-5.92</v>
       </c>
       <c r="I180" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J180" t="n">
         <v>8.09</v>
@@ -14149,7 +14149,7 @@
         <v>0.38</v>
       </c>
       <c r="I181" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J181" t="n">
         <v>8.140000000000001</v>
@@ -14224,7 +14224,7 @@
         <v>-3.76</v>
       </c>
       <c r="I182" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J182" t="n">
         <v>8.16</v>
@@ -14299,7 +14299,7 @@
         <v>-4.69</v>
       </c>
       <c r="I183" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J183" t="n">
         <v>8.18</v>
@@ -14374,7 +14374,7 @@
         <v>-3.28</v>
       </c>
       <c r="I184" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J184" t="n">
         <v>8.18</v>
@@ -14449,7 +14449,7 @@
         <v>-6.79</v>
       </c>
       <c r="I185" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J185" t="n">
         <v>8.140000000000001</v>
@@ -14528,7 +14528,7 @@
         <v>2.28</v>
       </c>
       <c r="I186" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J186" t="n">
         <v>8.1</v>
@@ -14603,7 +14603,7 @@
         <v>3.71</v>
       </c>
       <c r="I187" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J187" t="n">
         <v>8.029999999999999</v>
@@ -14678,7 +14678,7 @@
         <v>-2</v>
       </c>
       <c r="I188" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J188" t="n">
         <v>7.96</v>
@@ -14753,7 +14753,7 @@
         <v>5.99</v>
       </c>
       <c r="I189" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J189" t="n">
         <v>7.87</v>
@@ -14828,7 +14828,7 @@
         <v>-2.2</v>
       </c>
       <c r="I190" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J190" t="n">
         <v>7.8</v>
@@ -14903,7 +14903,7 @@
         <v>-0.99</v>
       </c>
       <c r="I191" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J191" t="n">
         <v>7.71</v>
@@ -14978,7 +14978,7 @@
         <v>4.69</v>
       </c>
       <c r="I192" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J192" t="n">
         <v>7.58</v>
@@ -15053,7 +15053,7 @@
         <v>2.99</v>
       </c>
       <c r="I193" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J193" t="n">
         <v>7.53</v>
@@ -15128,7 +15128,7 @@
         <v>-3.56</v>
       </c>
       <c r="I194" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J194" t="n">
         <v>7.46</v>
@@ -15207,7 +15207,7 @@
         <v>7.66</v>
       </c>
       <c r="I195" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J195" t="n">
         <v>7.46</v>
@@ -15282,7 +15282,7 @@
         <v>2.41</v>
       </c>
       <c r="I196" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J196" t="n">
         <v>7.49</v>
@@ -15357,7 +15357,7 @@
         <v>1.49</v>
       </c>
       <c r="I197" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J197" t="n">
         <v>7.48</v>
@@ -15432,7 +15432,7 @@
         <v>3.67</v>
       </c>
       <c r="I198" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J198" t="n">
         <v>7.49</v>
@@ -15507,7 +15507,7 @@
         <v>-5.31</v>
       </c>
       <c r="I199" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J199" t="n">
         <v>7.47</v>
@@ -15582,7 +15582,7 @@
         <v>-7.35</v>
       </c>
       <c r="I200" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J200" t="n">
         <v>7.44</v>
@@ -15657,7 +15657,7 @@
         <v>0</v>
       </c>
       <c r="I201" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J201" t="n">
         <v>7.42</v>
@@ -15732,7 +15732,7 @@
         <v>-4.03</v>
       </c>
       <c r="I202" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J202" t="n">
         <v>7.39</v>
@@ -15811,7 +15811,7 @@
         <v>-2.94</v>
       </c>
       <c r="I203" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J203" t="n">
         <v>7.37</v>
@@ -15890,7 +15890,7 @@
         <v>4.91</v>
       </c>
       <c r="I204" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J204" t="n">
         <v>7.38</v>
@@ -15965,7 +15965,7 @@
         <v>4.13</v>
       </c>
       <c r="I205" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J205" t="n">
         <v>7.43</v>
@@ -16040,7 +16040,7 @@
         <v>1.45</v>
       </c>
       <c r="I206" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J206" t="n">
         <v>7.48</v>
@@ -16115,7 +16115,7 @@
         <v>3.26</v>
       </c>
       <c r="I207" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J207" t="n">
         <v>7.53</v>
@@ -16190,7 +16190,7 @@
         <v>5.8</v>
       </c>
       <c r="I208" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J208" t="n">
         <v>7.6</v>
@@ -16265,7 +16265,7 @@
         <v>3.93</v>
       </c>
       <c r="I209" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J209" t="n">
         <v>7.68</v>
@@ -16340,7 +16340,7 @@
         <v>9.06</v>
       </c>
       <c r="I210" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J210" t="n">
         <v>7.8</v>
@@ -16415,7 +16415,7 @@
         <v>-0.53</v>
       </c>
       <c r="I211" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J211" t="n">
         <v>7.92</v>
@@ -16490,7 +16490,7 @@
         <v>-4.02</v>
       </c>
       <c r="I212" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J212" t="n">
         <v>8</v>
@@ -16565,7 +16565,7 @@
         <v>14.76</v>
       </c>
       <c r="I213" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J213" t="n">
         <v>8.15</v>
@@ -16640,7 +16640,7 @@
         <v>7.87</v>
       </c>
       <c r="I214" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J214" t="n">
         <v>8.34</v>
@@ -16715,7 +16715,7 @@
         <v>8.19</v>
       </c>
       <c r="I215" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J215" t="n">
         <v>8.56</v>
@@ -16790,7 +16790,7 @@
         <v>-1.73</v>
       </c>
       <c r="I216" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J216" t="n">
         <v>8.75</v>
@@ -16865,7 +16865,7 @@
         <v>-1.17</v>
       </c>
       <c r="I217" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J217" t="n">
         <v>8.93</v>
@@ -16940,7 +16940,7 @@
         <v>6.01</v>
       </c>
       <c r="I218" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J218" t="n">
         <v>9.130000000000001</v>
@@ -17015,7 +17015,7 @@
         <v>0.48</v>
       </c>
       <c r="I219" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J219" t="n">
         <v>9.359999999999999</v>
@@ -17090,7 +17090,7 @@
         <v>-4.05</v>
       </c>
       <c r="I220" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J220" t="n">
         <v>9.59</v>
@@ -17165,7 +17165,7 @@
         <v>5.72</v>
       </c>
       <c r="I221" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J221" t="n">
         <v>9.859999999999999</v>
@@ -17240,7 +17240,7 @@
         <v>4</v>
       </c>
       <c r="I222" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J222" t="n">
         <v>10.17</v>
@@ -17315,7 +17315,7 @@
         <v>3.17</v>
       </c>
       <c r="I223" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J223" t="n">
         <v>10.5</v>
@@ -17390,7 +17390,7 @@
         <v>-3.51</v>
       </c>
       <c r="I224" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J224" t="n">
         <v>10.8</v>
@@ -17465,7 +17465,7 @@
         <v>12.57</v>
       </c>
       <c r="I225" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J225" t="n">
         <v>11.17</v>
@@ -17540,7 +17540,7 @@
         <v>1.01</v>
       </c>
       <c r="I226" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J226" t="n">
         <v>11.53</v>
@@ -17615,7 +17615,7 @@
         <v>4.99</v>
       </c>
       <c r="I227" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J227" t="n">
         <v>11.92</v>
@@ -17690,7 +17690,7 @@
         <v>-1.46</v>
       </c>
       <c r="I228" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J228" t="n">
         <v>12.28</v>
@@ -17765,7 +17765,7 @@
         <v>13.38</v>
       </c>
       <c r="I229" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J229" t="n">
         <v>12.73</v>
@@ -17840,7 +17840,7 @@
         <v>7.21</v>
       </c>
       <c r="I230" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J230" t="n">
         <v>13.2</v>
@@ -17915,7 +17915,7 @@
         <v>-2.7</v>
       </c>
       <c r="I231" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J231" t="n">
         <v>13.64</v>
@@ -17990,7 +17990,7 @@
         <v>-5.39</v>
       </c>
       <c r="I232" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J232" t="n">
         <v>14.06</v>
@@ -18065,7 +18065,7 @@
         <v>-3.16</v>
       </c>
       <c r="I233" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J233" t="n">
         <v>14.38</v>
@@ -18140,7 +18140,7 @@
         <v>7.78</v>
       </c>
       <c r="I234" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J234" t="n">
         <v>14.72</v>
@@ -18215,7 +18215,7 @@
         <v>-9.199999999999999</v>
       </c>
       <c r="I235" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J235" t="n">
         <v>14.94</v>
@@ -18290,7 +18290,7 @@
         <v>-0.61</v>
       </c>
       <c r="I236" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J236" t="n">
         <v>15.16</v>
@@ -18365,7 +18365,7 @@
         <v>10.87</v>
       </c>
       <c r="I237" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J237" t="n">
         <v>15.48</v>
@@ -18440,7 +18440,7 @@
         <v>3.36</v>
       </c>
       <c r="I238" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J238" t="n">
         <v>15.79</v>
@@ -18515,7 +18515,7 @@
         <v>-3.57</v>
       </c>
       <c r="I239" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J239" t="n">
         <v>16.07</v>
@@ -18590,7 +18590,7 @@
         <v>14.14</v>
       </c>
       <c r="I240" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J240" t="n">
         <v>16.5</v>
@@ -18665,7 +18665,7 @@
         <v>1.06</v>
       </c>
       <c r="I241" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J241" t="n">
         <v>16.9</v>
@@ -18740,7 +18740,7 @@
         <v>7.14</v>
       </c>
       <c r="I242" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J242" t="n">
         <v>17.36</v>
@@ -18815,7 +18815,7 @@
         <v>-6.79</v>
       </c>
       <c r="I243" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J243" t="n">
         <v>17.72</v>
@@ -18890,7 +18890,7 @@
         <v>4.46</v>
       </c>
       <c r="I244" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J244" t="n">
         <v>18.15</v>
@@ -18965,7 +18965,7 @@
         <v>5</v>
       </c>
       <c r="I245" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J245" t="n">
         <v>18.55</v>
@@ -19040,7 +19040,7 @@
         <v>14.65</v>
       </c>
       <c r="I246" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J246" t="n">
         <v>19.1</v>
@@ -19115,7 +19115,7 @@
         <v>-5.03</v>
       </c>
       <c r="I247" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J247" t="n">
         <v>19.56</v>
@@ -19190,7 +19190,7 @@
         <v>10.96</v>
       </c>
       <c r="I248" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J248" t="n">
         <v>20.17</v>
@@ -19265,7 +19265,7 @@
         <v>9.08</v>
       </c>
       <c r="I249" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J249" t="n">
         <v>20.79</v>
@@ -19340,7 +19340,7 @@
         <v>2.79</v>
       </c>
       <c r="I250" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J250" t="n">
         <v>21.4</v>
@@ -19415,7 +19415,7 @@
         <v>1.65</v>
       </c>
       <c r="I251" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J251" t="n">
         <v>22.05</v>
@@ -19490,7 +19490,7 @@
         <v>-7.15</v>
       </c>
       <c r="I252" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J252" t="n">
         <v>22.64</v>
@@ -19565,7 +19565,7 @@
         <v>-31.09</v>
       </c>
       <c r="I253" s="4" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J253" s="4" t="n">
         <v>22.81</v>
@@ -19644,7 +19644,7 @@
         <v>4.37</v>
       </c>
       <c r="I254" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J254" t="n">
         <v>22.95</v>
@@ -19719,7 +19719,7 @@
         <v>-18.45</v>
       </c>
       <c r="I255" s="4" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J255" s="4" t="n">
         <v>22.99</v>
@@ -19794,7 +19794,7 @@
         <v>1.52</v>
       </c>
       <c r="I256" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J256" t="n">
         <v>23.04</v>
@@ -19873,7 +19873,7 @@
         <v>15.68</v>
       </c>
       <c r="I257" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J257" t="n">
         <v>23.14</v>
@@ -19948,7 +19948,7 @@
         <v>-7.25</v>
       </c>
       <c r="I258" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J258" t="n">
         <v>23.13</v>
@@ -20023,7 +20023,7 @@
         <v>5.46</v>
       </c>
       <c r="I259" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J259" t="n">
         <v>23.21</v>
@@ -20098,7 +20098,7 @@
         <v>-20.25</v>
       </c>
       <c r="I260" s="4" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J260" s="4" t="n">
         <v>22.97</v>
@@ -20171,7 +20171,7 @@
         <v>0.64</v>
       </c>
       <c r="I261" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J261" t="n">
         <v>22.71</v>
@@ -20250,7 +20250,7 @@
         <v>21</v>
       </c>
       <c r="I262" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J262" t="n">
         <v>22.55</v>
@@ -20325,7 +20325,7 @@
         <v>3.4</v>
       </c>
       <c r="I263" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J263" t="n">
         <v>22.5</v>
@@ -20400,7 +20400,7 @@
         <v>-5.01</v>
       </c>
       <c r="I264" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J264" t="n">
         <v>22.35</v>
@@ -20475,7 +20475,7 @@
         <v>5.8</v>
       </c>
       <c r="I265" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J265" t="n">
         <v>22.2</v>
@@ -20550,7 +20550,7 @@
         <v>-19.32</v>
       </c>
       <c r="I266" s="4" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J266" s="4" t="n">
         <v>21.69</v>
@@ -20633,7 +20633,7 @@
         <v>17.71</v>
       </c>
       <c r="I267" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J267" t="n">
         <v>21.39</v>
@@ -20708,7 +20708,7 @@
         <v>-11.12</v>
       </c>
       <c r="I268" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J268" t="n">
         <v>20.85</v>
@@ -20787,7 +20787,7 @@
         <v>-2.38</v>
       </c>
       <c r="I269" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J269" t="n">
         <v>20.16</v>
@@ -20862,7 +20862,7 @@
         <v>-17.58</v>
       </c>
       <c r="I270" s="4" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J270" s="4" t="n">
         <v>19.28</v>
@@ -20937,7 +20937,7 @@
         <v>1.48</v>
       </c>
       <c r="I271" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J271" t="n">
         <v>18.39</v>
@@ -21016,7 +21016,7 @@
         <v>-11.24</v>
       </c>
       <c r="I272" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J272" t="n">
         <v>17.54</v>
@@ -21095,7 +21095,7 @@
         <v>16.86</v>
       </c>
       <c r="I273" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J273" t="n">
         <v>17.24</v>
@@ -21170,7 +21170,7 @@
         <v>7.67</v>
       </c>
       <c r="I274" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J274" t="n">
         <v>16.96</v>
@@ -21245,7 +21245,7 @@
         <v>-7.78</v>
       </c>
       <c r="I275" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J275" t="n">
         <v>16.8</v>
@@ -21320,7 +21320,7 @@
         <v>7.02</v>
       </c>
       <c r="I276" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J276" t="n">
         <v>16.69</v>
@@ -21395,7 +21395,7 @@
         <v>2.98</v>
       </c>
       <c r="I277" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J277" t="n">
         <v>16.46</v>
@@ -21474,7 +21474,7 @@
         <v>30.23</v>
       </c>
       <c r="I278" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J278" t="n">
         <v>16.54</v>
@@ -21549,7 +21549,7 @@
         <v>-1.38</v>
       </c>
       <c r="I279" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J279" t="n">
         <v>16.55</v>
@@ -21624,7 +21624,7 @@
         <v>-1.35</v>
       </c>
       <c r="I280" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J280" t="n">
         <v>16.75</v>
@@ -21699,7 +21699,7 @@
         <v>5.08</v>
       </c>
       <c r="I281" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J281" t="n">
         <v>17</v>
@@ -21774,7 +21774,7 @@
         <v>11.98</v>
       </c>
       <c r="I282" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J282" t="n">
         <v>17.2</v>
@@ -21849,7 +21849,7 @@
         <v>-3.84</v>
       </c>
       <c r="I283" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J283" t="n">
         <v>17.32</v>
@@ -21924,7 +21924,7 @@
         <v>5.2</v>
       </c>
       <c r="I284" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J284" t="n">
         <v>17.56</v>
@@ -21999,7 +21999,7 @@
         <v>9.98</v>
       </c>
       <c r="I285" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J285" t="n">
         <v>17.85</v>
@@ -22074,7 +22074,7 @@
         <v>-4.23</v>
       </c>
       <c r="I286" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J286" t="n">
         <v>18.28</v>
@@ -22149,7 +22149,7 @@
         <v>-6.52</v>
       </c>
       <c r="I287" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J287" t="n">
         <v>18.5</v>
@@ -22224,7 +22224,7 @@
         <v>17.54</v>
       </c>
       <c r="I288" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J288" t="n">
         <v>19.01</v>
@@ -22299,7 +22299,7 @@
         <v>-9.65</v>
       </c>
       <c r="I289" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J289" t="n">
         <v>19.42</v>
@@ -22374,7 +22374,7 @@
         <v>7.34</v>
       </c>
       <c r="I290" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J290" t="n">
         <v>20.06</v>
@@ -22449,7 +22449,7 @@
         <v>4.67</v>
       </c>
       <c r="I291" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J291" t="n">
         <v>20.75</v>
@@ -22524,7 +22524,7 @@
         <v>-4.57</v>
       </c>
       <c r="I292" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J292" t="n">
         <v>21.46</v>
@@ -22599,7 +22599,7 @@
         <v>-0.8</v>
       </c>
       <c r="I293" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J293" t="n">
         <v>22.05</v>
@@ -22674,7 +22674,7 @@
         <v>12.69</v>
       </c>
       <c r="I294" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J294" t="n">
         <v>22.76</v>
@@ -22749,7 +22749,7 @@
         <v>2.52</v>
       </c>
       <c r="I295" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J295" t="n">
         <v>23.56</v>
@@ -22824,7 +22824,7 @@
         <v>3.19</v>
       </c>
       <c r="I296" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J296" t="n">
         <v>24.36</v>
@@ -22899,7 +22899,7 @@
         <v>17.69</v>
       </c>
       <c r="I297" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J297" t="n">
         <v>25.41</v>
@@ -22974,7 +22974,7 @@
         <v>14.65</v>
       </c>
       <c r="I298" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J298" t="n">
         <v>26.5</v>
@@ -23049,7 +23049,7 @@
         <v>-8.41</v>
       </c>
       <c r="I299" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J299" t="n">
         <v>27.42</v>
@@ -23124,7 +23124,7 @@
         <v>22.62</v>
       </c>
       <c r="I300" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J300" t="n">
         <v>28.79</v>
@@ -23199,7 +23199,7 @@
         <v>4.33</v>
       </c>
       <c r="I301" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J301" t="n">
         <v>30.21</v>
@@ -23274,7 +23274,7 @@
         <v>-22.56</v>
       </c>
       <c r="I302" s="4" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J302" s="4" t="n">
         <v>30.96</v>
@@ -23349,7 +23349,7 @@
         <v>17.42</v>
       </c>
       <c r="I303" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J303" t="n">
         <v>32.08</v>
@@ -23424,7 +23424,7 @@
         <v>2.91</v>
       </c>
       <c r="I304" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J304" t="n">
         <v>33.2</v>
@@ -23499,7 +23499,7 @@
         <v>-18.31</v>
       </c>
       <c r="I305" s="4" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J305" s="4" t="n">
         <v>33.79</v>
@@ -23574,7 +23574,7 @@
         <v>-5</v>
       </c>
       <c r="I306" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J306" t="n">
         <v>34.34</v>
@@ -23649,7 +23649,7 @@
         <v>-3.36</v>
       </c>
       <c r="I307" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J307" t="n">
         <v>34.91</v>
@@ -23728,7 +23728,7 @@
         <v>10.26</v>
       </c>
       <c r="I308" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J308" t="n">
         <v>35.46</v>
@@ -23803,7 +23803,7 @@
         <v>10.31</v>
       </c>
       <c r="I309" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J309" t="n">
         <v>36.33</v>
@@ -23878,7 +23878,7 @@
         <v>-6.98</v>
       </c>
       <c r="I310" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J310" t="n">
         <v>36.96</v>
@@ -23953,7 +23953,7 @@
         <v>30.06</v>
       </c>
       <c r="I311" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J311" t="n">
         <v>38.12</v>
@@ -24028,7 +24028,7 @@
         <v>-3.57</v>
       </c>
       <c r="I312" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J312" t="n">
         <v>39.25</v>
@@ -24103,7 +24103,7 @@
         <v>12.4</v>
       </c>
       <c r="I313" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J313" t="n">
         <v>40.7</v>
@@ -24178,7 +24178,7 @@
         <v>-0.93</v>
       </c>
       <c r="I314" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J314" t="n">
         <v>41.96</v>
@@ -24253,7 +24253,7 @@
         <v>16.04</v>
       </c>
       <c r="I315" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J315" t="n">
         <v>43.61</v>
@@ -24328,7 +24328,7 @@
         <v>-3.16</v>
       </c>
       <c r="I316" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J316" t="n">
         <v>45.12</v>
@@ -24403,7 +24403,7 @@
         <v>-2.29</v>
       </c>
       <c r="I317" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J317" t="n">
         <v>46.28</v>
@@ -24478,7 +24478,7 @@
         <v>-12.28</v>
       </c>
       <c r="I318" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J318" t="n">
         <v>46.81</v>
@@ -24553,7 +24553,7 @@
         <v>-41.89</v>
       </c>
       <c r="I319" s="4" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J319" s="4" t="n">
         <v>46.41</v>
@@ -24632,7 +24632,7 @@
         <v>16.3</v>
       </c>
       <c r="I320" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J320" t="n">
         <v>45.83</v>
@@ -24707,7 +24707,7 @@
         <v>-2.45</v>
       </c>
       <c r="I321" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J321" t="n">
         <v>45.1</v>
@@ -24782,7 +24782,7 @@
         <v>-9.050000000000001</v>
       </c>
       <c r="I322" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J322" t="n">
         <v>44.77</v>
@@ -24857,7 +24857,7 @@
         <v>33.78</v>
       </c>
       <c r="I323" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J323" t="n">
         <v>44.64</v>
@@ -24932,7 +24932,7 @@
         <v>-2.04</v>
       </c>
       <c r="I324" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J324" t="n">
         <v>44.41</v>
@@ -25007,7 +25007,7 @@
         <v>21.14</v>
       </c>
       <c r="I325" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J325" t="n">
         <v>45.03</v>
@@ -25082,7 +25082,7 @@
         <v>-8.029999999999999</v>
       </c>
       <c r="I326" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J326" t="n">
         <v>45.54</v>
@@ -25157,7 +25157,7 @@
         <v>-0.5</v>
       </c>
       <c r="I327" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J327" t="n">
         <v>46.1</v>
@@ -25236,7 +25236,7 @@
         <v>19.29</v>
       </c>
       <c r="I328" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J328" t="n">
         <v>46.93</v>
@@ -25311,7 +25311,7 @@
         <v>-0.2</v>
       </c>
       <c r="I329" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J329" t="n">
         <v>47.55</v>
@@ -25386,7 +25386,7 @@
         <v>-35.7</v>
       </c>
       <c r="I330" s="4" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J330" s="4" t="n">
         <v>47.35</v>
@@ -25465,7 +25465,7 @@
         <v>5.89</v>
       </c>
       <c r="I331" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J331" t="n">
         <v>46.66</v>
@@ -25540,7 +25540,7 @@
         <v>11.85</v>
       </c>
       <c r="I332" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J332" t="n">
         <v>46.29</v>
@@ -25615,7 +25615,7 @@
         <v>-10.9</v>
       </c>
       <c r="I333" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J333" t="n">
         <v>45.39</v>
@@ -25690,7 +25690,7 @@
         <v>-0.03</v>
       </c>
       <c r="I334" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J334" t="n">
         <v>44.51</v>
@@ -25765,7 +25765,7 @@
         <v>5.82</v>
       </c>
       <c r="I335" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J335" t="n">
         <v>43.3</v>
@@ -25840,7 +25840,7 @@
         <v>-23.21</v>
       </c>
       <c r="I336" s="4" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J336" s="4" t="n">
         <v>41.74</v>
@@ -25919,7 +25919,7 @@
         <v>-9.77</v>
       </c>
       <c r="I337" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J337" t="n">
         <v>40.1</v>
@@ -25998,7 +25998,7 @@
         <v>15.37</v>
       </c>
       <c r="I338" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J338" t="n">
         <v>39.04</v>
@@ -26073,7 +26073,7 @@
         <v>-12.78</v>
       </c>
       <c r="I339" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J339" t="n">
         <v>38.87</v>
@@ -26152,7 +26152,7 @@
         <v>1.58</v>
       </c>
       <c r="I340" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J340" t="n">
         <v>38.48</v>
@@ -26227,7 +26227,7 @@
         <v>3</v>
       </c>
       <c r="I341" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J341" t="n">
         <v>38.18</v>
@@ -26302,7 +26302,7 @@
         <v>-2.28</v>
       </c>
       <c r="I342" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J342" t="n">
         <v>38</v>
@@ -26381,7 +26381,7 @@
         <v>-24.74</v>
       </c>
       <c r="I343" s="4" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J343" s="4" t="n">
         <v>36.94</v>
@@ -26456,7 +26456,7 @@
         <v>14.84</v>
       </c>
       <c r="I344" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J344" t="n">
         <v>36.08</v>
@@ -26531,7 +26531,7 @@
         <v>-9.140000000000001</v>
       </c>
       <c r="I345" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J345" t="n">
         <v>34.68</v>
@@ -26606,7 +26606,7 @@
         <v>-14.72</v>
       </c>
       <c r="I346" s="4" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J346" s="4" t="n">
         <v>33.31</v>
@@ -26685,7 +26685,7 @@
         <v>-2.09</v>
       </c>
       <c r="I347" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J347" t="n">
         <v>31.94</v>
@@ -26764,7 +26764,7 @@
         <v>0.82</v>
       </c>
       <c r="I348" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J348" t="n">
         <v>30.13</v>
@@ -26843,7 +26843,7 @@
         <v>18.03</v>
       </c>
       <c r="I349" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J349" t="n">
         <v>28.5</v>
@@ -26918,7 +26918,7 @@
         <v>-4.46</v>
       </c>
       <c r="I350" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J350" t="n">
         <v>27.79</v>
@@ -26993,7 +26993,7 @@
         <v>6.02</v>
       </c>
       <c r="I351" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J351" t="n">
         <v>27.03</v>
@@ -27068,7 +27068,7 @@
         <v>-18.9</v>
       </c>
       <c r="I352" s="4" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J352" s="4" t="n">
         <v>25.85</v>
@@ -27147,7 +27147,7 @@
         <v>-3.59</v>
       </c>
       <c r="I353" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J353" t="n">
         <v>24.87</v>
@@ -27222,7 +27222,7 @@
         <v>-17.78</v>
       </c>
       <c r="I354" s="4" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J354" s="4" t="n">
         <v>23.73</v>
@@ -27301,7 +27301,7 @@
         <v>-14.63</v>
       </c>
       <c r="I355" s="4" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J355" s="4" t="n">
         <v>22.38</v>
@@ -27380,7 +27380,7 @@
         <v>34.77</v>
       </c>
       <c r="I356" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J356" t="n">
         <v>21.69</v>
@@ -27455,7 +27455,7 @@
         <v>-7.92</v>
       </c>
       <c r="I357" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J357" t="n">
         <v>21.09</v>
@@ -27530,7 +27530,7 @@
         <v>5.87</v>
       </c>
       <c r="I358" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J358" t="n">
         <v>20.32</v>
@@ -27605,7 +27605,7 @@
         <v>20.48</v>
       </c>
       <c r="I359" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J359" t="n">
         <v>19.91</v>
@@ -27680,7 +27680,7 @@
         <v>-3.56</v>
       </c>
       <c r="I360" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J360" t="n">
         <v>19.45</v>
@@ -27755,7 +27755,7 @@
         <v>-8.84</v>
       </c>
       <c r="I361" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J361" t="n">
         <v>18.87</v>
@@ -27830,7 +27830,7 @@
         <v>3.27</v>
       </c>
       <c r="I362" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J362" t="n">
         <v>18.34</v>
@@ -27905,7 +27905,7 @@
         <v>-5.47</v>
       </c>
       <c r="I363" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J363" t="n">
         <v>18.12</v>
@@ -27980,7 +27980,7 @@
         <v>7.5</v>
       </c>
       <c r="I364" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J364" t="n">
         <v>17.8</v>
@@ -28055,7 +28055,7 @@
         <v>15.19</v>
       </c>
       <c r="I365" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J365" t="n">
         <v>17.72</v>
@@ -28130,7 +28130,7 @@
         <v>4.68</v>
       </c>
       <c r="I366" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J366" t="n">
         <v>17.85</v>
@@ -28205,7 +28205,7 @@
         <v>1.55</v>
       </c>
       <c r="I367" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J367" t="n">
         <v>18.02</v>
@@ -28280,7 +28280,7 @@
         <v>8.98</v>
       </c>
       <c r="I368" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J368" t="n">
         <v>18.27</v>
@@ -28355,7 +28355,7 @@
         <v>-24.21</v>
       </c>
       <c r="I369" s="4" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J369" s="4" t="n">
         <v>18.08</v>
@@ -28434,7 +28434,7 @@
         <v>7.12</v>
       </c>
       <c r="I370" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J370" t="n">
         <v>18</v>
@@ -28509,7 +28509,7 @@
         <v>6.38</v>
       </c>
       <c r="I371" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J371" t="n">
         <v>17.91</v>
@@ -28584,7 +28584,7 @@
         <v>0.15</v>
       </c>
       <c r="I372" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J372" t="n">
         <v>18.04</v>
@@ -28659,7 +28659,7 @@
         <v>-7.86</v>
       </c>
       <c r="I373" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J373" t="n">
         <v>18.11</v>
@@ -28734,7 +28734,7 @@
         <v>11.03</v>
       </c>
       <c r="I374" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J374" t="n">
         <v>18.45</v>
@@ -28809,7 +28809,7 @@
         <v>-1.63</v>
       </c>
       <c r="I375" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J375" t="n">
         <v>18.87</v>
@@ -28884,7 +28884,7 @@
         <v>4.49</v>
       </c>
       <c r="I376" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J376" t="n">
         <v>19.12</v>
@@ -28959,7 +28959,7 @@
         <v>-2.99</v>
       </c>
       <c r="I377" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J377" t="n">
         <v>19.41</v>
@@ -29034,7 +29034,7 @@
         <v>0.91</v>
       </c>
       <c r="I378" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J378" t="n">
         <v>19.67</v>
@@ -29109,7 +29109,7 @@
         <v>-8.49</v>
       </c>
       <c r="I379" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J379" t="n">
         <v>19.67</v>
@@ -29188,7 +29188,7 @@
         <v>5.06</v>
       </c>
       <c r="I380" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J380" t="n">
         <v>19.76</v>
@@ -29263,7 +29263,7 @@
         <v>2.68</v>
       </c>
       <c r="I381" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J381" t="n">
         <v>19.95</v>
@@ -29338,7 +29338,7 @@
         <v>13.44</v>
       </c>
       <c r="I382" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J382" t="n">
         <v>20.26</v>
@@ -29413,7 +29413,7 @@
         <v>1.58</v>
       </c>
       <c r="I383" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J383" t="n">
         <v>20.63</v>
@@ -29488,7 +29488,7 @@
         <v>1.51</v>
       </c>
       <c r="I384" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J384" t="n">
         <v>20.96</v>
@@ -29563,7 +29563,7 @@
         <v>-12.52</v>
       </c>
       <c r="I385" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J385" t="n">
         <v>21</v>
@@ -29638,7 +29638,7 @@
         <v>8.970000000000001</v>
       </c>
       <c r="I386" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J386" t="n">
         <v>21.09</v>
@@ -29713,7 +29713,7 @@
         <v>-19.51</v>
       </c>
       <c r="I387" s="4" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J387" s="4" t="n">
         <v>20.94</v>
@@ -29792,7 +29792,7 @@
         <v>0.16</v>
       </c>
       <c r="I388" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J388" t="n">
         <v>20.69</v>
@@ -29867,7 +29867,7 @@
         <v>-1.72</v>
       </c>
       <c r="I389" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J389" t="n">
         <v>20.71</v>
@@ -29942,7 +29942,7 @@
         <v>11.65</v>
       </c>
       <c r="I390" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J390" t="n">
         <v>20.78</v>
@@ -30017,7 +30017,7 @@
         <v>-1.81</v>
       </c>
       <c r="I391" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J391" t="n">
         <v>20.76</v>
@@ -30092,7 +30092,7 @@
         <v>12.52</v>
       </c>
       <c r="I392" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J392" t="n">
         <v>20.87</v>
@@ -30167,7 +30167,7 @@
         <v>5.41</v>
       </c>
       <c r="I393" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J393" t="n">
         <v>21.12</v>
@@ -30242,7 +30242,7 @@
         <v>-10.52</v>
       </c>
       <c r="I394" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J394" t="n">
         <v>21.14</v>
@@ -30317,7 +30317,7 @@
         <v>-5.31</v>
       </c>
       <c r="I395" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J395" t="n">
         <v>21.13</v>
@@ -30396,7 +30396,7 @@
         <v>7.2</v>
       </c>
       <c r="I396" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J396" t="n">
         <v>21.14</v>
@@ -30471,7 +30471,7 @@
         <v>-5.51</v>
       </c>
       <c r="I397" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J397" t="n">
         <v>21.12</v>
@@ -30550,7 +30550,7 @@
         <v>5.25</v>
       </c>
       <c r="I398" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J398" t="n">
         <v>21.14</v>
@@ -30625,7 +30625,7 @@
         <v>-6.75</v>
       </c>
       <c r="I399" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J399" t="n">
         <v>21.18</v>
@@ -30704,7 +30704,7 @@
         <v>5.34</v>
       </c>
       <c r="I400" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J400" t="n">
         <v>21.23</v>
@@ -30779,7 +30779,7 @@
         <v>8.82</v>
       </c>
       <c r="I401" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J401" t="n">
         <v>21.34</v>
@@ -30854,7 +30854,7 @@
         <v>-0.74</v>
       </c>
       <c r="I402" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J402" t="n">
         <v>21.31</v>
@@ -30929,7 +30929,7 @@
         <v>-7.77</v>
       </c>
       <c r="I403" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J403" t="n">
         <v>21.17</v>
@@ -31008,7 +31008,7 @@
         <v>-4.57</v>
       </c>
       <c r="I404" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J404" t="n">
         <v>20.96</v>
@@ -31083,7 +31083,7 @@
         <v>-11.97</v>
       </c>
       <c r="I405" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J405" t="n">
         <v>20.79</v>
@@ -31162,7 +31162,7 @@
         <v>1.13</v>
       </c>
       <c r="I406" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J406" t="n">
         <v>20.52</v>
@@ -31237,7 +31237,7 @@
         <v>-11.82</v>
       </c>
       <c r="I407" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J407" t="n">
         <v>20.38</v>
@@ -31316,7 +31316,7 @@
         <v>-6.48</v>
       </c>
       <c r="I408" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J408" t="n">
         <v>20.19</v>
@@ -31391,7 +31391,7 @@
         <v>-12.16</v>
       </c>
       <c r="I409" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J409" t="n">
         <v>19.92</v>
@@ -31466,7 +31466,7 @@
         <v>-7.12</v>
       </c>
       <c r="I410" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J410" t="n">
         <v>19.5</v>
@@ -31545,7 +31545,7 @@
         <v>-11.41</v>
       </c>
       <c r="I411" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J411" t="n">
         <v>19.03</v>
@@ -31624,7 +31624,7 @@
         <v>12.03</v>
       </c>
       <c r="I412" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J412" t="n">
         <v>18.5</v>
@@ -31703,7 +31703,7 @@
         <v>-4.87</v>
       </c>
       <c r="I413" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J413" t="n">
         <v>17.88</v>
@@ -31782,7 +31782,7 @@
         <v>5.29</v>
       </c>
       <c r="I414" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J414" t="n">
         <v>17.41</v>
@@ -31800,7 +31800,7 @@
         <v>23.14</v>
       </c>
       <c r="O414" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31843,47 +31843,47 @@
         </is>
       </c>
       <c r="C415" t="n">
-        <v>12.3</v>
+        <v>10.83</v>
       </c>
       <c r="D415" t="n">
-        <v>11.08</v>
+        <v>11.16</v>
       </c>
       <c r="E415" t="n">
-        <v>10.8</v>
+        <v>10.08</v>
       </c>
       <c r="F415" t="n">
-        <v>10.98</v>
+        <v>10.33</v>
       </c>
       <c r="G415" t="n">
-        <v>15055614</v>
+        <v>37779265</v>
       </c>
       <c r="H415" s="1" t="n">
-        <v>-8.039999999999999</v>
+        <v>-13.48</v>
       </c>
       <c r="I415" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J415" t="n">
-        <v>16.95</v>
+        <v>16.92</v>
       </c>
       <c r="K415" t="n">
-        <v>18.98</v>
+        <v>18.97</v>
       </c>
       <c r="L415" t="n">
-        <v>27.71</v>
+        <v>27.7</v>
       </c>
       <c r="M415" t="n">
         <v>24.45</v>
       </c>
       <c r="N415" s="3" t="n">
-        <v>12.9</v>
+        <v>12.4</v>
       </c>
       <c r="O415" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>extreme fear</t>
         </is>
       </c>
       <c r="Q415" t="inlineStr">
@@ -31897,12 +31897,14 @@
         </is>
       </c>
       <c r="S415" t="n">
-        <v>5.04</v>
+        <v>4.95</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="U415" s="2" t="inlineStr"/>
+        <v>19.5</v>
+      </c>
+      <c r="U415" s="2" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V415" t="inlineStr"/>
       <c r="W415" s="2" t="inlineStr"/>
     </row>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31776,7 +31776,7 @@
         <v>11.94</v>
       </c>
       <c r="G414" t="n">
-        <v>40638400</v>
+        <v>42050500</v>
       </c>
       <c r="H414" s="3" t="n">
         <v>5.29</v>
@@ -31832,81 +31832,83 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>KORU</t>
-        </is>
-      </c>
-      <c r="B415" t="inlineStr">
+      <c r="A415" s="4" t="inlineStr">
+        <is>
+          <t>KORU</t>
+        </is>
+      </c>
+      <c r="B415" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="C415" t="n">
+      <c r="C415" s="4" t="n">
         <v>10.83</v>
       </c>
-      <c r="D415" t="n">
+      <c r="D415" s="4" t="n">
         <v>11.16</v>
       </c>
-      <c r="E415" t="n">
-        <v>10.08</v>
-      </c>
-      <c r="F415" t="n">
-        <v>10.33</v>
-      </c>
-      <c r="G415" t="n">
-        <v>37779265</v>
-      </c>
-      <c r="H415" s="1" t="n">
-        <v>-13.48</v>
-      </c>
-      <c r="I415" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="J415" t="n">
-        <v>16.92</v>
-      </c>
-      <c r="K415" t="n">
+      <c r="E415" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F415" s="4" t="n">
+        <v>10.19</v>
+      </c>
+      <c r="G415" s="4" t="n">
+        <v>47196536</v>
+      </c>
+      <c r="H415" s="5" t="n">
+        <v>-14.66</v>
+      </c>
+      <c r="I415" s="4" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="J415" s="4" t="n">
+        <v>16.91</v>
+      </c>
+      <c r="K415" s="4" t="n">
         <v>18.97</v>
       </c>
-      <c r="L415" t="n">
+      <c r="L415" s="4" t="n">
         <v>27.7</v>
       </c>
-      <c r="M415" t="n">
+      <c r="M415" s="4" t="n">
         <v>24.45</v>
       </c>
-      <c r="N415" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="O415" t="n">
+      <c r="N415" s="7" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="O415" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="P415" s="4" t="inlineStr">
+        <is>
+          <t>extreme fear</t>
+        </is>
+      </c>
+      <c r="Q415" s="4" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" s="4" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S415" s="4" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T415" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="P415" t="inlineStr">
-        <is>
-          <t>extreme fear</t>
-        </is>
-      </c>
-      <c r="Q415" t="inlineStr">
-        <is>
-          <t>2x BUY</t>
-        </is>
-      </c>
-      <c r="R415" t="inlineStr">
-        <is>
-          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
-        </is>
-      </c>
-      <c r="S415" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="T415" s="2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="U415" s="2" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="V415" t="inlineStr"/>
-      <c r="W415" s="2" t="inlineStr"/>
+      <c r="U415" s="6" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="V415" s="4" t="inlineStr"/>
+      <c r="W415" s="6" t="n">
+        <v>152.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -608,7 +608,7 @@
         <v>-1.49</v>
       </c>
       <c r="I2" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J2" t="n">
         <v>2.19</v>
@@ -683,7 +683,7 @@
         <v>1.01</v>
       </c>
       <c r="I3" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J3" t="n">
         <v>2.19</v>
@@ -758,7 +758,7 @@
         <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J4" t="n">
         <v>2.2</v>
@@ -833,7 +833,7 @@
         <v>-5.56</v>
       </c>
       <c r="I5" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J5" t="n">
         <v>2.2</v>
@@ -912,7 +912,7 @@
         <v>3.43</v>
       </c>
       <c r="I6" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J6" t="n">
         <v>2.2</v>
@@ -987,7 +987,7 @@
         <v>-8.529999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J7" t="n">
         <v>2.2</v>
@@ -1070,7 +1070,7 @@
         <v>3.11</v>
       </c>
       <c r="I8" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J8" t="n">
         <v>2.19</v>
@@ -1149,7 +1149,7 @@
         <v>7.04</v>
       </c>
       <c r="I9" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J9" t="n">
         <v>2.19</v>
@@ -1224,7 +1224,7 @@
         <v>-3.76</v>
       </c>
       <c r="I10" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J10" t="n">
         <v>2.19</v>
@@ -1303,7 +1303,7 @@
         <v>4.88</v>
       </c>
       <c r="I11" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J11" t="n">
         <v>2.19</v>
@@ -1378,7 +1378,7 @@
         <v>8.84</v>
       </c>
       <c r="I12" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J12" t="n">
         <v>2.19</v>
@@ -1453,7 +1453,7 @@
         <v>-4.7</v>
       </c>
       <c r="I13" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J13" t="n">
         <v>2.18</v>
@@ -1528,7 +1528,7 @@
         <v>1.35</v>
       </c>
       <c r="I14" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J14" t="n">
         <v>2.17</v>
@@ -1603,7 +1603,7 @@
         <v>-2.65</v>
       </c>
       <c r="I15" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J15" t="n">
         <v>2.16</v>
@@ -1678,7 +1678,7 @@
         <v>0.91</v>
       </c>
       <c r="I16" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J16" t="n">
         <v>2.15</v>
@@ -1753,7 +1753,7 @@
         <v>2.25</v>
       </c>
       <c r="I17" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J17" t="n">
         <v>2.15</v>
@@ -1828,7 +1828,7 @@
         <v>-1.32</v>
       </c>
       <c r="I18" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J18" t="n">
         <v>2.14</v>
@@ -1903,7 +1903,7 @@
         <v>-1.34</v>
       </c>
       <c r="I19" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J19" t="n">
         <v>2.13</v>
@@ -1978,7 +1978,7 @@
         <v>-1.81</v>
       </c>
       <c r="I20" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J20" t="n">
         <v>2.13</v>
@@ -2053,7 +2053,7 @@
         <v>-9.220000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J21" t="n">
         <v>2.13</v>
@@ -2132,7 +2132,7 @@
         <v>-4.06</v>
       </c>
       <c r="I22" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J22" t="n">
         <v>2.13</v>
@@ -2207,7 +2207,7 @@
         <v>4.76</v>
       </c>
       <c r="I23" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J23" t="n">
         <v>2.13</v>
@@ -2282,7 +2282,7 @@
         <v>-1.01</v>
       </c>
       <c r="I24" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J24" t="n">
         <v>2.12</v>
@@ -2357,7 +2357,7 @@
         <v>-8.67</v>
       </c>
       <c r="I25" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J25" t="n">
         <v>2.1</v>
@@ -2436,7 +2436,7 @@
         <v>-10.61</v>
       </c>
       <c r="I26" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J26" t="n">
         <v>2.08</v>
@@ -2519,7 +2519,7 @@
         <v>-3.12</v>
       </c>
       <c r="I27" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J27" t="n">
         <v>2.06</v>
@@ -2602,7 +2602,7 @@
         <v>-10.32</v>
       </c>
       <c r="I28" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J28" t="n">
         <v>2.03</v>
@@ -2685,7 +2685,7 @@
         <v>24.46</v>
       </c>
       <c r="I29" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J29" t="n">
         <v>2.01</v>
@@ -2764,7 +2764,7 @@
         <v>-6.94</v>
       </c>
       <c r="I30" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J30" t="n">
         <v>1.99</v>
@@ -2843,7 +2843,7 @@
         <v>14.29</v>
       </c>
       <c r="I31" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J31" t="n">
         <v>1.97</v>
@@ -2922,7 +2922,7 @@
         <v>-0.54</v>
       </c>
       <c r="I32" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J32" t="n">
         <v>1.95</v>
@@ -2997,7 +2997,7 @@
         <v>0.55</v>
       </c>
       <c r="I33" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J33" t="n">
         <v>1.93</v>
@@ -3072,7 +3072,7 @@
         <v>-2.17</v>
       </c>
       <c r="I34" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J34" t="n">
         <v>1.9</v>
@@ -3151,7 +3151,7 @@
         <v>1.67</v>
       </c>
       <c r="I35" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J35" t="n">
         <v>1.89</v>
@@ -3230,7 +3230,7 @@
         <v>0.55</v>
       </c>
       <c r="I36" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J36" t="n">
         <v>1.87</v>
@@ -3305,7 +3305,7 @@
         <v>2.17</v>
       </c>
       <c r="I37" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J37" t="n">
         <v>1.85</v>
@@ -3380,7 +3380,7 @@
         <v>3.72</v>
       </c>
       <c r="I38" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J38" t="n">
         <v>1.83</v>
@@ -3459,7 +3459,7 @@
         <v>2.05</v>
       </c>
       <c r="I39" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J39" t="n">
         <v>1.82</v>
@@ -3534,7 +3534,7 @@
         <v>-0.5</v>
       </c>
       <c r="I40" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J40" t="n">
         <v>1.81</v>
@@ -3609,7 +3609,7 @@
         <v>-1.01</v>
       </c>
       <c r="I41" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J41" t="n">
         <v>1.81</v>
@@ -3684,7 +3684,7 @@
         <v>2.55</v>
       </c>
       <c r="I42" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J42" t="n">
         <v>1.82</v>
@@ -3759,7 +3759,7 @@
         <v>0.5</v>
       </c>
       <c r="I43" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J43" t="n">
         <v>1.82</v>
@@ -3834,7 +3834,7 @@
         <v>-2.97</v>
       </c>
       <c r="I44" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J44" t="n">
         <v>1.82</v>
@@ -3909,7 +3909,7 @@
         <v>10.71</v>
       </c>
       <c r="I45" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J45" t="n">
         <v>1.84</v>
@@ -3984,7 +3984,7 @@
         <v>4.15</v>
       </c>
       <c r="I46" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J46" t="n">
         <v>1.87</v>
@@ -4059,7 +4059,7 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J47" t="n">
         <v>1.91</v>
@@ -4134,7 +4134,7 @@
         <v>-3.54</v>
       </c>
       <c r="I48" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J48" t="n">
         <v>1.95</v>
@@ -4209,7 +4209,7 @@
         <v>-3.21</v>
       </c>
       <c r="I49" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J49" t="n">
         <v>1.97</v>
@@ -4284,7 +4284,7 @@
         <v>2.84</v>
       </c>
       <c r="I50" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J50" t="n">
         <v>1.99</v>
@@ -4359,7 +4359,7 @@
         <v>1.38</v>
       </c>
       <c r="I51" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J51" t="n">
         <v>2.01</v>
@@ -4434,7 +4434,7 @@
         <v>0.45</v>
       </c>
       <c r="I52" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J52" t="n">
         <v>2.03</v>
@@ -4509,7 +4509,7 @@
         <v>2.71</v>
       </c>
       <c r="I53" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J53" t="n">
         <v>2.05</v>
@@ -4584,7 +4584,7 @@
         <v>0.88</v>
       </c>
       <c r="I54" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J54" t="n">
         <v>2.08</v>
@@ -4659,7 +4659,7 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J55" t="n">
         <v>2.1</v>
@@ -4734,7 +4734,7 @@
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J56" t="n">
         <v>2.12</v>
@@ -4809,7 +4809,7 @@
         <v>-2.18</v>
       </c>
       <c r="I57" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J57" t="n">
         <v>2.14</v>
@@ -4884,7 +4884,7 @@
         <v>3.57</v>
       </c>
       <c r="I58" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J58" t="n">
         <v>2.16</v>
@@ -4959,7 +4959,7 @@
         <v>-3.88</v>
       </c>
       <c r="I59" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J59" t="n">
         <v>2.17</v>
@@ -5034,7 +5034,7 @@
         <v>3.14</v>
       </c>
       <c r="I60" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J60" t="n">
         <v>2.19</v>
@@ -5109,7 +5109,7 @@
         <v>4.78</v>
       </c>
       <c r="I61" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J61" t="n">
         <v>2.21</v>
@@ -5184,7 +5184,7 @@
         <v>3.73</v>
       </c>
       <c r="I62" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J62" t="n">
         <v>2.23</v>
@@ -5259,7 +5259,7 @@
         <v>5.2</v>
       </c>
       <c r="I63" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J63" t="n">
         <v>2.26</v>
@@ -5334,7 +5334,7 @@
         <v>-5.7</v>
       </c>
       <c r="I64" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J64" t="n">
         <v>2.29</v>
@@ -5409,7 +5409,7 @@
         <v>5.65</v>
       </c>
       <c r="I65" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J65" t="n">
         <v>2.31</v>
@@ -5484,7 +5484,7 @@
         <v>1.15</v>
       </c>
       <c r="I66" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J66" t="n">
         <v>2.33</v>
@@ -5559,7 +5559,7 @@
         <v>9.43</v>
       </c>
       <c r="I67" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J67" t="n">
         <v>2.36</v>
@@ -5634,7 +5634,7 @@
         <v>6.55</v>
       </c>
       <c r="I68" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J68" t="n">
         <v>2.41</v>
@@ -5709,7 +5709,7 @@
         <v>0.65</v>
       </c>
       <c r="I69" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J69" t="n">
         <v>2.46</v>
@@ -5784,7 +5784,7 @@
         <v>4.5</v>
       </c>
       <c r="I70" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J70" t="n">
         <v>2.51</v>
@@ -5859,7 +5859,7 @@
         <v>-1.54</v>
       </c>
       <c r="I71" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J71" t="n">
         <v>2.56</v>
@@ -5934,7 +5934,7 @@
         <v>3.75</v>
       </c>
       <c r="I72" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J72" t="n">
         <v>2.62</v>
@@ -6009,7 +6009,7 @@
         <v>3.31</v>
       </c>
       <c r="I73" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J73" t="n">
         <v>2.68</v>
@@ -6084,7 +6084,7 @@
         <v>-5.83</v>
       </c>
       <c r="I74" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J74" t="n">
         <v>2.72</v>
@@ -6159,7 +6159,7 @@
         <v>8.050000000000001</v>
       </c>
       <c r="I75" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J75" t="n">
         <v>2.78</v>
@@ -6234,7 +6234,7 @@
         <v>-6.88</v>
       </c>
       <c r="I76" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J76" t="n">
         <v>2.83</v>
@@ -6309,7 +6309,7 @@
         <v>5.23</v>
       </c>
       <c r="I77" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J77" t="n">
         <v>2.89</v>
@@ -6384,7 +6384,7 @@
         <v>2.92</v>
       </c>
       <c r="I78" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J78" t="n">
         <v>2.95</v>
@@ -6459,7 +6459,7 @@
         <v>3.69</v>
       </c>
       <c r="I79" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J79" t="n">
         <v>3.02</v>
@@ -6534,7 +6534,7 @@
         <v>14.25</v>
       </c>
       <c r="I80" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J80" t="n">
         <v>3.12</v>
@@ -6609,7 +6609,7 @@
         <v>-1.2</v>
       </c>
       <c r="I81" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J81" t="n">
         <v>3.2</v>
@@ -6684,7 +6684,7 @@
         <v>-1.94</v>
       </c>
       <c r="I82" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J82" t="n">
         <v>3.28</v>
@@ -6759,7 +6759,7 @@
         <v>-4.95</v>
       </c>
       <c r="I83" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J83" t="n">
         <v>3.34</v>
@@ -6834,7 +6834,7 @@
         <v>4.17</v>
       </c>
       <c r="I84" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J84" t="n">
         <v>3.42</v>
@@ -6909,7 +6909,7 @@
         <v>-0.5</v>
       </c>
       <c r="I85" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J85" t="n">
         <v>3.48</v>
@@ -6984,7 +6984,7 @@
         <v>1.26</v>
       </c>
       <c r="I86" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J86" t="n">
         <v>3.55</v>
@@ -7059,7 +7059,7 @@
         <v>2.73</v>
       </c>
       <c r="I87" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J87" t="n">
         <v>3.61</v>
@@ -7134,7 +7134,7 @@
         <v>-10.39</v>
       </c>
       <c r="I88" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J88" t="n">
         <v>3.65</v>
@@ -7209,7 +7209,7 @@
         <v>8.09</v>
       </c>
       <c r="I89" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J89" t="n">
         <v>3.69</v>
@@ -7284,7 +7284,7 @@
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J90" t="n">
         <v>3.73</v>
@@ -7359,7 +7359,7 @@
         <v>4.49</v>
       </c>
       <c r="I91" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J91" t="n">
         <v>3.78</v>
@@ -7434,7 +7434,7 @@
         <v>-2.39</v>
       </c>
       <c r="I92" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J92" t="n">
         <v>3.82</v>
@@ -7509,7 +7509,7 @@
         <v>2.44</v>
       </c>
       <c r="I93" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J93" t="n">
         <v>3.85</v>
@@ -7584,7 +7584,7 @@
         <v>-0.48</v>
       </c>
       <c r="I94" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J94" t="n">
         <v>3.9</v>
@@ -7659,7 +7659,7 @@
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J95" t="n">
         <v>3.94</v>
@@ -7734,7 +7734,7 @@
         <v>-0.24</v>
       </c>
       <c r="I96" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J96" t="n">
         <v>3.98</v>
@@ -7809,7 +7809,7 @@
         <v>-2.64</v>
       </c>
       <c r="I97" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J97" t="n">
         <v>4.01</v>
@@ -7884,7 +7884,7 @@
         <v>5.93</v>
       </c>
       <c r="I98" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J98" t="n">
         <v>4.05</v>
@@ -7959,7 +7959,7 @@
         <v>-3.73</v>
       </c>
       <c r="I99" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J99" t="n">
         <v>4.07</v>
@@ -8034,7 +8034,7 @@
         <v>3.63</v>
       </c>
       <c r="I100" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J100" t="n">
         <v>4.08</v>
@@ -8109,7 +8109,7 @@
         <v>-2.1</v>
       </c>
       <c r="I101" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J101" t="n">
         <v>4.08</v>
@@ -8184,7 +8184,7 @@
         <v>-0.48</v>
       </c>
       <c r="I102" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J102" t="n">
         <v>4.09</v>
@@ -8259,7 +8259,7 @@
         <v>-2.16</v>
       </c>
       <c r="I103" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J103" t="n">
         <v>4.1</v>
@@ -8338,7 +8338,7 @@
         <v>3.19</v>
       </c>
       <c r="I104" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J104" t="n">
         <v>4.11</v>
@@ -8413,7 +8413,7 @@
         <v>0.95</v>
       </c>
       <c r="I105" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J105" t="n">
         <v>4.13</v>
@@ -8488,7 +8488,7 @@
         <v>-3.76</v>
       </c>
       <c r="I106" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J106" t="n">
         <v>4.13</v>
@@ -8567,7 +8567,7 @@
         <v>-9.050000000000001</v>
       </c>
       <c r="I107" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J107" t="n">
         <v>4.11</v>
@@ -8642,7 +8642,7 @@
         <v>7.26</v>
       </c>
       <c r="I108" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J108" t="n">
         <v>4.12</v>
@@ -8717,7 +8717,7 @@
         <v>2.26</v>
       </c>
       <c r="I109" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J109" t="n">
         <v>4.13</v>
@@ -8792,7 +8792,7 @@
         <v>0.98</v>
       </c>
       <c r="I110" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J110" t="n">
         <v>4.13</v>
@@ -8867,7 +8867,7 @@
         <v>0.97</v>
       </c>
       <c r="I111" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J111" t="n">
         <v>4.13</v>
@@ -8942,7 +8942,7 @@
         <v>0.24</v>
       </c>
       <c r="I112" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J112" t="n">
         <v>4.13</v>
@@ -9017,7 +9017,7 @@
         <v>-1.92</v>
       </c>
       <c r="I113" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J113" t="n">
         <v>4.13</v>
@@ -9096,7 +9096,7 @@
         <v>4.16</v>
       </c>
       <c r="I114" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J114" t="n">
         <v>4.13</v>
@@ -9171,7 +9171,7 @@
         <v>2.58</v>
       </c>
       <c r="I115" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J115" t="n">
         <v>4.14</v>
@@ -9246,7 +9246,7 @@
         <v>-4.12</v>
       </c>
       <c r="I116" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J116" t="n">
         <v>4.14</v>
@@ -9321,7 +9321,7 @@
         <v>-1.19</v>
       </c>
       <c r="I117" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J117" t="n">
         <v>4.15</v>
@@ -9400,7 +9400,7 @@
         <v>-2.42</v>
       </c>
       <c r="I118" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J118" t="n">
         <v>4.14</v>
@@ -9475,7 +9475,7 @@
         <v>-5.45</v>
       </c>
       <c r="I119" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J119" t="n">
         <v>4.12</v>
@@ -9550,7 +9550,7 @@
         <v>-0.52</v>
       </c>
       <c r="I120" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J120" t="n">
         <v>4.1</v>
@@ -9625,7 +9625,7 @@
         <v>-0.79</v>
       </c>
       <c r="I121" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J121" t="n">
         <v>4.08</v>
@@ -9704,7 +9704,7 @@
         <v>9.81</v>
       </c>
       <c r="I122" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J122" t="n">
         <v>4.07</v>
@@ -9779,7 +9779,7 @@
         <v>-3.38</v>
       </c>
       <c r="I123" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J123" t="n">
         <v>4.07</v>
@@ -9858,7 +9858,7 @@
         <v>-1.5</v>
       </c>
       <c r="I124" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J124" t="n">
         <v>4.06</v>
@@ -9933,7 +9933,7 @@
         <v>0.51</v>
       </c>
       <c r="I125" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J125" t="n">
         <v>4.04</v>
@@ -10008,7 +10008,7 @@
         <v>4.55</v>
       </c>
       <c r="I126" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J126" t="n">
         <v>4.04</v>
@@ -10083,7 +10083,7 @@
         <v>-5.56</v>
       </c>
       <c r="I127" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J127" t="n">
         <v>4.05</v>
@@ -10162,7 +10162,7 @@
         <v>-1.53</v>
       </c>
       <c r="I128" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J128" t="n">
         <v>4.05</v>
@@ -10237,7 +10237,7 @@
         <v>3.9</v>
       </c>
       <c r="I129" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J129" t="n">
         <v>4.04</v>
@@ -10312,7 +10312,7 @@
         <v>0.75</v>
       </c>
       <c r="I130" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J130" t="n">
         <v>4.04</v>
@@ -10387,7 +10387,7 @@
         <v>2.23</v>
       </c>
       <c r="I131" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J131" t="n">
         <v>4.04</v>
@@ -10462,7 +10462,7 @@
         <v>1.94</v>
       </c>
       <c r="I132" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J132" t="n">
         <v>4.04</v>
@@ -10537,7 +10537,7 @@
         <v>3.1</v>
       </c>
       <c r="I133" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J133" t="n">
         <v>4.05</v>
@@ -10612,7 +10612,7 @@
         <v>6.93</v>
       </c>
       <c r="I134" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J134" t="n">
         <v>4.07</v>
@@ -10687,7 +10687,7 @@
         <v>4.75</v>
       </c>
       <c r="I135" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J135" t="n">
         <v>4.09</v>
@@ -10762,7 +10762,7 @@
         <v>3.09</v>
       </c>
       <c r="I136" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J136" t="n">
         <v>4.13</v>
@@ -10837,7 +10837,7 @@
         <v>2</v>
       </c>
       <c r="I137" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J137" t="n">
         <v>4.18</v>
@@ -10912,7 +10912,7 @@
         <v>5.69</v>
       </c>
       <c r="I138" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J138" t="n">
         <v>4.25</v>
@@ -10987,7 +10987,7 @@
         <v>-3.34</v>
       </c>
       <c r="I139" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J139" t="n">
         <v>4.32</v>
@@ -11062,7 +11062,7 @@
         <v>3.65</v>
       </c>
       <c r="I140" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J140" t="n">
         <v>4.4</v>
@@ -11137,7 +11137,7 @@
         <v>-2.96</v>
       </c>
       <c r="I141" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J141" t="n">
         <v>4.47</v>
@@ -11212,7 +11212,7 @@
         <v>5.92</v>
       </c>
       <c r="I142" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J142" t="n">
         <v>4.54</v>
@@ -11287,7 +11287,7 @@
         <v>-0.54</v>
       </c>
       <c r="I143" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J143" t="n">
         <v>4.62</v>
@@ -11362,7 +11362,7 @@
         <v>-5.25</v>
       </c>
       <c r="I144" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J144" t="n">
         <v>4.68</v>
@@ -11437,7 +11437,7 @@
         <v>-0.57</v>
       </c>
       <c r="I145" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J145" t="n">
         <v>4.74</v>
@@ -11512,7 +11512,7 @@
         <v>-3.85</v>
       </c>
       <c r="I146" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J146" t="n">
         <v>4.79</v>
@@ -11587,7 +11587,7 @@
         <v>5</v>
       </c>
       <c r="I147" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J147" t="n">
         <v>4.85</v>
@@ -11662,7 +11662,7 @@
         <v>-0.38</v>
       </c>
       <c r="I148" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J148" t="n">
         <v>4.92</v>
@@ -11737,7 +11737,7 @@
         <v>6.5</v>
       </c>
       <c r="I149" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J149" t="n">
         <v>5</v>
@@ -11812,7 +11812,7 @@
         <v>6.1</v>
       </c>
       <c r="I150" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J150" t="n">
         <v>5.1</v>
@@ -11887,7 +11887,7 @@
         <v>1.18</v>
       </c>
       <c r="I151" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J151" t="n">
         <v>5.19</v>
@@ -11962,7 +11962,7 @@
         <v>3.18</v>
       </c>
       <c r="I152" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J152" t="n">
         <v>5.29</v>
@@ -12037,7 +12037,7 @@
         <v>-4.86</v>
       </c>
       <c r="I153" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J153" t="n">
         <v>5.36</v>
@@ -12112,7 +12112,7 @@
         <v>2.73</v>
       </c>
       <c r="I154" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J154" t="n">
         <v>5.44</v>
@@ -12187,7 +12187,7 @@
         <v>-2.65</v>
       </c>
       <c r="I155" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J155" t="n">
         <v>5.49</v>
@@ -12262,7 +12262,7 @@
         <v>-9.710000000000001</v>
       </c>
       <c r="I156" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J156" t="n">
         <v>5.5</v>
@@ -12341,7 +12341,7 @@
         <v>10.38</v>
       </c>
       <c r="I157" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J157" t="n">
         <v>5.54</v>
@@ -12416,7 +12416,7 @@
         <v>-3.25</v>
       </c>
       <c r="I158" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J158" t="n">
         <v>5.55</v>
@@ -12491,7 +12491,7 @@
         <v>8.83</v>
       </c>
       <c r="I159" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J159" t="n">
         <v>5.6</v>
@@ -12566,7 +12566,7 @@
         <v>9.58</v>
       </c>
       <c r="I160" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J160" t="n">
         <v>5.67</v>
@@ -12641,7 +12641,7 @@
         <v>2.07</v>
       </c>
       <c r="I161" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J161" t="n">
         <v>5.75</v>
@@ -12716,7 +12716,7 @@
         <v>6.68</v>
       </c>
       <c r="I162" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J162" t="n">
         <v>5.84</v>
@@ -12791,7 +12791,7 @@
         <v>-6.12</v>
       </c>
       <c r="I163" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J163" t="n">
         <v>5.91</v>
@@ -12866,7 +12866,7 @@
         <v>2.75</v>
       </c>
       <c r="I164" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J164" t="n">
         <v>6</v>
@@ -12941,7 +12941,7 @@
         <v>1.97</v>
       </c>
       <c r="I165" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J165" t="n">
         <v>6.1</v>
@@ -13016,7 +13016,7 @@
         <v>6.64</v>
       </c>
       <c r="I166" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J166" t="n">
         <v>6.24</v>
@@ -13091,7 +13091,7 @@
         <v>7.39</v>
       </c>
       <c r="I167" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J167" t="n">
         <v>6.39</v>
@@ -13166,7 +13166,7 @@
         <v>0.36</v>
       </c>
       <c r="I168" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J168" t="n">
         <v>6.54</v>
@@ -13241,7 +13241,7 @@
         <v>7.82</v>
       </c>
       <c r="I169" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J169" t="n">
         <v>6.71</v>
@@ -13316,7 +13316,7 @@
         <v>-5.02</v>
       </c>
       <c r="I170" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J170" t="n">
         <v>6.84</v>
@@ -13391,7 +13391,7 @@
         <v>5.17</v>
       </c>
       <c r="I171" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J171" t="n">
         <v>6.99</v>
@@ -13466,7 +13466,7 @@
         <v>11.62</v>
       </c>
       <c r="I172" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J172" t="n">
         <v>7.18</v>
@@ -13541,7 +13541,7 @@
         <v>-14.81</v>
       </c>
       <c r="I173" s="4" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J173" s="4" t="n">
         <v>7.32</v>
@@ -13616,7 +13616,7 @@
         <v>2.47</v>
       </c>
       <c r="I174" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J174" t="n">
         <v>7.45</v>
@@ -13691,7 +13691,7 @@
         <v>-9.52</v>
       </c>
       <c r="I175" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J175" t="n">
         <v>7.55</v>
@@ -13766,7 +13766,7 @@
         <v>-5.7</v>
       </c>
       <c r="I176" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J176" t="n">
         <v>7.66</v>
@@ -13845,7 +13845,7 @@
         <v>12.5</v>
       </c>
       <c r="I177" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J177" t="n">
         <v>7.78</v>
@@ -13920,7 +13920,7 @@
         <v>-1.19</v>
       </c>
       <c r="I178" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J178" t="n">
         <v>7.91</v>
@@ -13995,7 +13995,7 @@
         <v>2.06</v>
       </c>
       <c r="I179" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J179" t="n">
         <v>8.029999999999999</v>
@@ -14070,7 +14070,7 @@
         <v>-5.92</v>
       </c>
       <c r="I180" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J180" t="n">
         <v>8.09</v>
@@ -14149,7 +14149,7 @@
         <v>0.38</v>
       </c>
       <c r="I181" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J181" t="n">
         <v>8.140000000000001</v>
@@ -14224,7 +14224,7 @@
         <v>-3.76</v>
       </c>
       <c r="I182" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J182" t="n">
         <v>8.16</v>
@@ -14299,7 +14299,7 @@
         <v>-4.69</v>
       </c>
       <c r="I183" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J183" t="n">
         <v>8.18</v>
@@ -14374,7 +14374,7 @@
         <v>-3.28</v>
       </c>
       <c r="I184" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J184" t="n">
         <v>8.18</v>
@@ -14449,7 +14449,7 @@
         <v>-6.79</v>
       </c>
       <c r="I185" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J185" t="n">
         <v>8.140000000000001</v>
@@ -14528,7 +14528,7 @@
         <v>2.28</v>
       </c>
       <c r="I186" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J186" t="n">
         <v>8.1</v>
@@ -14603,7 +14603,7 @@
         <v>3.71</v>
       </c>
       <c r="I187" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J187" t="n">
         <v>8.029999999999999</v>
@@ -14678,7 +14678,7 @@
         <v>-2</v>
       </c>
       <c r="I188" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J188" t="n">
         <v>7.96</v>
@@ -14753,7 +14753,7 @@
         <v>5.99</v>
       </c>
       <c r="I189" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J189" t="n">
         <v>7.87</v>
@@ -14828,7 +14828,7 @@
         <v>-2.2</v>
       </c>
       <c r="I190" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J190" t="n">
         <v>7.8</v>
@@ -14903,7 +14903,7 @@
         <v>-0.99</v>
       </c>
       <c r="I191" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J191" t="n">
         <v>7.71</v>
@@ -14978,7 +14978,7 @@
         <v>4.69</v>
       </c>
       <c r="I192" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J192" t="n">
         <v>7.58</v>
@@ -15053,7 +15053,7 @@
         <v>2.99</v>
       </c>
       <c r="I193" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J193" t="n">
         <v>7.53</v>
@@ -15128,7 +15128,7 @@
         <v>-3.56</v>
       </c>
       <c r="I194" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J194" t="n">
         <v>7.46</v>
@@ -15207,7 +15207,7 @@
         <v>7.66</v>
       </c>
       <c r="I195" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J195" t="n">
         <v>7.46</v>
@@ -15282,7 +15282,7 @@
         <v>2.41</v>
       </c>
       <c r="I196" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J196" t="n">
         <v>7.49</v>
@@ -15357,7 +15357,7 @@
         <v>1.49</v>
       </c>
       <c r="I197" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J197" t="n">
         <v>7.48</v>
@@ -15432,7 +15432,7 @@
         <v>3.67</v>
       </c>
       <c r="I198" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J198" t="n">
         <v>7.49</v>
@@ -15507,7 +15507,7 @@
         <v>-5.31</v>
       </c>
       <c r="I199" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J199" t="n">
         <v>7.47</v>
@@ -15582,7 +15582,7 @@
         <v>-7.35</v>
       </c>
       <c r="I200" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J200" t="n">
         <v>7.44</v>
@@ -15657,7 +15657,7 @@
         <v>0</v>
       </c>
       <c r="I201" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J201" t="n">
         <v>7.42</v>
@@ -15732,7 +15732,7 @@
         <v>-4.03</v>
       </c>
       <c r="I202" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J202" t="n">
         <v>7.39</v>
@@ -15811,7 +15811,7 @@
         <v>-2.94</v>
       </c>
       <c r="I203" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J203" t="n">
         <v>7.37</v>
@@ -15890,7 +15890,7 @@
         <v>4.91</v>
       </c>
       <c r="I204" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J204" t="n">
         <v>7.38</v>
@@ -15965,7 +15965,7 @@
         <v>4.13</v>
       </c>
       <c r="I205" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J205" t="n">
         <v>7.43</v>
@@ -16040,7 +16040,7 @@
         <v>1.45</v>
       </c>
       <c r="I206" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J206" t="n">
         <v>7.48</v>
@@ -16115,7 +16115,7 @@
         <v>3.26</v>
       </c>
       <c r="I207" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J207" t="n">
         <v>7.53</v>
@@ -16190,7 +16190,7 @@
         <v>5.8</v>
       </c>
       <c r="I208" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J208" t="n">
         <v>7.6</v>
@@ -16265,7 +16265,7 @@
         <v>3.93</v>
       </c>
       <c r="I209" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J209" t="n">
         <v>7.68</v>
@@ -16340,7 +16340,7 @@
         <v>9.06</v>
       </c>
       <c r="I210" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J210" t="n">
         <v>7.8</v>
@@ -16415,7 +16415,7 @@
         <v>-0.53</v>
       </c>
       <c r="I211" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J211" t="n">
         <v>7.92</v>
@@ -16490,7 +16490,7 @@
         <v>-4.02</v>
       </c>
       <c r="I212" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J212" t="n">
         <v>8</v>
@@ -16565,7 +16565,7 @@
         <v>14.76</v>
       </c>
       <c r="I213" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J213" t="n">
         <v>8.15</v>
@@ -16640,7 +16640,7 @@
         <v>7.87</v>
       </c>
       <c r="I214" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J214" t="n">
         <v>8.34</v>
@@ -16715,7 +16715,7 @@
         <v>8.19</v>
       </c>
       <c r="I215" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J215" t="n">
         <v>8.56</v>
@@ -16790,7 +16790,7 @@
         <v>-1.73</v>
       </c>
       <c r="I216" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J216" t="n">
         <v>8.75</v>
@@ -16865,7 +16865,7 @@
         <v>-1.17</v>
       </c>
       <c r="I217" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J217" t="n">
         <v>8.93</v>
@@ -16940,7 +16940,7 @@
         <v>6.01</v>
       </c>
       <c r="I218" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J218" t="n">
         <v>9.130000000000001</v>
@@ -17015,7 +17015,7 @@
         <v>0.48</v>
       </c>
       <c r="I219" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J219" t="n">
         <v>9.359999999999999</v>
@@ -17090,7 +17090,7 @@
         <v>-4.05</v>
       </c>
       <c r="I220" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J220" t="n">
         <v>9.59</v>
@@ -17165,7 +17165,7 @@
         <v>5.72</v>
       </c>
       <c r="I221" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J221" t="n">
         <v>9.859999999999999</v>
@@ -17240,7 +17240,7 @@
         <v>4</v>
       </c>
       <c r="I222" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J222" t="n">
         <v>10.17</v>
@@ -17315,7 +17315,7 @@
         <v>3.17</v>
       </c>
       <c r="I223" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J223" t="n">
         <v>10.5</v>
@@ -17390,7 +17390,7 @@
         <v>-3.51</v>
       </c>
       <c r="I224" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J224" t="n">
         <v>10.8</v>
@@ -17465,7 +17465,7 @@
         <v>12.57</v>
       </c>
       <c r="I225" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J225" t="n">
         <v>11.17</v>
@@ -17540,7 +17540,7 @@
         <v>1.01</v>
       </c>
       <c r="I226" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J226" t="n">
         <v>11.53</v>
@@ -17615,7 +17615,7 @@
         <v>4.99</v>
       </c>
       <c r="I227" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J227" t="n">
         <v>11.92</v>
@@ -17690,7 +17690,7 @@
         <v>-1.46</v>
       </c>
       <c r="I228" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J228" t="n">
         <v>12.28</v>
@@ -17765,7 +17765,7 @@
         <v>13.38</v>
       </c>
       <c r="I229" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J229" t="n">
         <v>12.73</v>
@@ -17840,7 +17840,7 @@
         <v>7.21</v>
       </c>
       <c r="I230" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J230" t="n">
         <v>13.2</v>
@@ -17915,7 +17915,7 @@
         <v>-2.7</v>
       </c>
       <c r="I231" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J231" t="n">
         <v>13.64</v>
@@ -17990,7 +17990,7 @@
         <v>-5.39</v>
       </c>
       <c r="I232" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J232" t="n">
         <v>14.06</v>
@@ -18065,7 +18065,7 @@
         <v>-3.16</v>
       </c>
       <c r="I233" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J233" t="n">
         <v>14.38</v>
@@ -18140,7 +18140,7 @@
         <v>7.78</v>
       </c>
       <c r="I234" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J234" t="n">
         <v>14.72</v>
@@ -18215,7 +18215,7 @@
         <v>-9.199999999999999</v>
       </c>
       <c r="I235" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J235" t="n">
         <v>14.94</v>
@@ -18290,7 +18290,7 @@
         <v>-0.61</v>
       </c>
       <c r="I236" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J236" t="n">
         <v>15.16</v>
@@ -18365,7 +18365,7 @@
         <v>10.87</v>
       </c>
       <c r="I237" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J237" t="n">
         <v>15.48</v>
@@ -18440,7 +18440,7 @@
         <v>3.36</v>
       </c>
       <c r="I238" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J238" t="n">
         <v>15.79</v>
@@ -18515,7 +18515,7 @@
         <v>-3.57</v>
       </c>
       <c r="I239" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J239" t="n">
         <v>16.07</v>
@@ -18590,7 +18590,7 @@
         <v>14.14</v>
       </c>
       <c r="I240" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J240" t="n">
         <v>16.5</v>
@@ -18665,7 +18665,7 @@
         <v>1.06</v>
       </c>
       <c r="I241" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J241" t="n">
         <v>16.9</v>
@@ -18740,7 +18740,7 @@
         <v>7.14</v>
       </c>
       <c r="I242" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J242" t="n">
         <v>17.36</v>
@@ -18815,7 +18815,7 @@
         <v>-6.79</v>
       </c>
       <c r="I243" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J243" t="n">
         <v>17.72</v>
@@ -18890,7 +18890,7 @@
         <v>4.46</v>
       </c>
       <c r="I244" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J244" t="n">
         <v>18.15</v>
@@ -18965,7 +18965,7 @@
         <v>5</v>
       </c>
       <c r="I245" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J245" t="n">
         <v>18.55</v>
@@ -19040,7 +19040,7 @@
         <v>14.65</v>
       </c>
       <c r="I246" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J246" t="n">
         <v>19.1</v>
@@ -19115,7 +19115,7 @@
         <v>-5.03</v>
       </c>
       <c r="I247" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J247" t="n">
         <v>19.56</v>
@@ -19190,7 +19190,7 @@
         <v>10.96</v>
       </c>
       <c r="I248" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J248" t="n">
         <v>20.17</v>
@@ -19265,7 +19265,7 @@
         <v>9.08</v>
       </c>
       <c r="I249" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J249" t="n">
         <v>20.79</v>
@@ -19340,7 +19340,7 @@
         <v>2.79</v>
       </c>
       <c r="I250" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J250" t="n">
         <v>21.4</v>
@@ -19415,7 +19415,7 @@
         <v>1.65</v>
       </c>
       <c r="I251" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J251" t="n">
         <v>22.05</v>
@@ -19490,7 +19490,7 @@
         <v>-7.15</v>
       </c>
       <c r="I252" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J252" t="n">
         <v>22.64</v>
@@ -19565,7 +19565,7 @@
         <v>-31.09</v>
       </c>
       <c r="I253" s="4" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J253" s="4" t="n">
         <v>22.81</v>
@@ -19644,7 +19644,7 @@
         <v>4.37</v>
       </c>
       <c r="I254" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J254" t="n">
         <v>22.95</v>
@@ -19719,7 +19719,7 @@
         <v>-18.45</v>
       </c>
       <c r="I255" s="4" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J255" s="4" t="n">
         <v>22.99</v>
@@ -19794,7 +19794,7 @@
         <v>1.52</v>
       </c>
       <c r="I256" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J256" t="n">
         <v>23.04</v>
@@ -19873,7 +19873,7 @@
         <v>15.68</v>
       </c>
       <c r="I257" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J257" t="n">
         <v>23.14</v>
@@ -19948,7 +19948,7 @@
         <v>-7.25</v>
       </c>
       <c r="I258" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J258" t="n">
         <v>23.13</v>
@@ -20023,7 +20023,7 @@
         <v>5.46</v>
       </c>
       <c r="I259" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J259" t="n">
         <v>23.21</v>
@@ -20098,7 +20098,7 @@
         <v>-20.25</v>
       </c>
       <c r="I260" s="4" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J260" s="4" t="n">
         <v>22.97</v>
@@ -20171,7 +20171,7 @@
         <v>0.64</v>
       </c>
       <c r="I261" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J261" t="n">
         <v>22.71</v>
@@ -20250,7 +20250,7 @@
         <v>21</v>
       </c>
       <c r="I262" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J262" t="n">
         <v>22.55</v>
@@ -20325,7 +20325,7 @@
         <v>3.4</v>
       </c>
       <c r="I263" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J263" t="n">
         <v>22.5</v>
@@ -20400,7 +20400,7 @@
         <v>-5.01</v>
       </c>
       <c r="I264" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J264" t="n">
         <v>22.35</v>
@@ -20475,7 +20475,7 @@
         <v>5.8</v>
       </c>
       <c r="I265" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J265" t="n">
         <v>22.2</v>
@@ -20550,7 +20550,7 @@
         <v>-19.32</v>
       </c>
       <c r="I266" s="4" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J266" s="4" t="n">
         <v>21.69</v>
@@ -20633,7 +20633,7 @@
         <v>17.71</v>
       </c>
       <c r="I267" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J267" t="n">
         <v>21.39</v>
@@ -20708,7 +20708,7 @@
         <v>-11.12</v>
       </c>
       <c r="I268" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J268" t="n">
         <v>20.85</v>
@@ -20787,7 +20787,7 @@
         <v>-2.38</v>
       </c>
       <c r="I269" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J269" t="n">
         <v>20.16</v>
@@ -20862,7 +20862,7 @@
         <v>-17.58</v>
       </c>
       <c r="I270" s="4" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J270" s="4" t="n">
         <v>19.28</v>
@@ -20937,7 +20937,7 @@
         <v>1.48</v>
       </c>
       <c r="I271" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J271" t="n">
         <v>18.39</v>
@@ -21016,7 +21016,7 @@
         <v>-11.24</v>
       </c>
       <c r="I272" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J272" t="n">
         <v>17.54</v>
@@ -21095,7 +21095,7 @@
         <v>16.86</v>
       </c>
       <c r="I273" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J273" t="n">
         <v>17.24</v>
@@ -21170,7 +21170,7 @@
         <v>7.67</v>
       </c>
       <c r="I274" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J274" t="n">
         <v>16.96</v>
@@ -21245,7 +21245,7 @@
         <v>-7.78</v>
       </c>
       <c r="I275" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J275" t="n">
         <v>16.8</v>
@@ -21320,7 +21320,7 @@
         <v>7.02</v>
       </c>
       <c r="I276" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J276" t="n">
         <v>16.69</v>
@@ -21395,7 +21395,7 @@
         <v>2.98</v>
       </c>
       <c r="I277" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J277" t="n">
         <v>16.46</v>
@@ -21474,7 +21474,7 @@
         <v>30.23</v>
       </c>
       <c r="I278" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J278" t="n">
         <v>16.54</v>
@@ -21549,7 +21549,7 @@
         <v>-1.38</v>
       </c>
       <c r="I279" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J279" t="n">
         <v>16.55</v>
@@ -21624,7 +21624,7 @@
         <v>-1.35</v>
       </c>
       <c r="I280" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J280" t="n">
         <v>16.75</v>
@@ -21699,7 +21699,7 @@
         <v>5.08</v>
       </c>
       <c r="I281" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J281" t="n">
         <v>17</v>
@@ -21774,7 +21774,7 @@
         <v>11.98</v>
       </c>
       <c r="I282" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J282" t="n">
         <v>17.2</v>
@@ -21849,7 +21849,7 @@
         <v>-3.84</v>
       </c>
       <c r="I283" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J283" t="n">
         <v>17.32</v>
@@ -21924,7 +21924,7 @@
         <v>5.2</v>
       </c>
       <c r="I284" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J284" t="n">
         <v>17.56</v>
@@ -21999,7 +21999,7 @@
         <v>9.98</v>
       </c>
       <c r="I285" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J285" t="n">
         <v>17.85</v>
@@ -22074,7 +22074,7 @@
         <v>-4.23</v>
       </c>
       <c r="I286" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J286" t="n">
         <v>18.28</v>
@@ -22149,7 +22149,7 @@
         <v>-6.52</v>
       </c>
       <c r="I287" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J287" t="n">
         <v>18.5</v>
@@ -22224,7 +22224,7 @@
         <v>17.54</v>
       </c>
       <c r="I288" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J288" t="n">
         <v>19.01</v>
@@ -22299,7 +22299,7 @@
         <v>-9.65</v>
       </c>
       <c r="I289" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J289" t="n">
         <v>19.42</v>
@@ -22374,7 +22374,7 @@
         <v>7.34</v>
       </c>
       <c r="I290" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J290" t="n">
         <v>20.06</v>
@@ -22449,7 +22449,7 @@
         <v>4.67</v>
       </c>
       <c r="I291" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J291" t="n">
         <v>20.75</v>
@@ -22524,7 +22524,7 @@
         <v>-4.57</v>
       </c>
       <c r="I292" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J292" t="n">
         <v>21.46</v>
@@ -22599,7 +22599,7 @@
         <v>-0.8</v>
       </c>
       <c r="I293" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J293" t="n">
         <v>22.05</v>
@@ -22674,7 +22674,7 @@
         <v>12.69</v>
       </c>
       <c r="I294" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J294" t="n">
         <v>22.76</v>
@@ -22749,7 +22749,7 @@
         <v>2.52</v>
       </c>
       <c r="I295" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J295" t="n">
         <v>23.56</v>
@@ -22824,7 +22824,7 @@
         <v>3.19</v>
       </c>
       <c r="I296" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J296" t="n">
         <v>24.36</v>
@@ -22899,7 +22899,7 @@
         <v>17.69</v>
       </c>
       <c r="I297" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J297" t="n">
         <v>25.41</v>
@@ -22974,7 +22974,7 @@
         <v>14.65</v>
       </c>
       <c r="I298" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J298" t="n">
         <v>26.5</v>
@@ -23049,7 +23049,7 @@
         <v>-8.41</v>
       </c>
       <c r="I299" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J299" t="n">
         <v>27.42</v>
@@ -23124,7 +23124,7 @@
         <v>22.62</v>
       </c>
       <c r="I300" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J300" t="n">
         <v>28.79</v>
@@ -23199,7 +23199,7 @@
         <v>4.33</v>
       </c>
       <c r="I301" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J301" t="n">
         <v>30.21</v>
@@ -23274,7 +23274,7 @@
         <v>-22.56</v>
       </c>
       <c r="I302" s="4" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J302" s="4" t="n">
         <v>30.96</v>
@@ -23349,7 +23349,7 @@
         <v>17.42</v>
       </c>
       <c r="I303" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J303" t="n">
         <v>32.08</v>
@@ -23424,7 +23424,7 @@
         <v>2.91</v>
       </c>
       <c r="I304" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J304" t="n">
         <v>33.2</v>
@@ -23499,7 +23499,7 @@
         <v>-18.31</v>
       </c>
       <c r="I305" s="4" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J305" s="4" t="n">
         <v>33.79</v>
@@ -23574,7 +23574,7 @@
         <v>-5</v>
       </c>
       <c r="I306" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J306" t="n">
         <v>34.34</v>
@@ -23649,7 +23649,7 @@
         <v>-3.36</v>
       </c>
       <c r="I307" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J307" t="n">
         <v>34.91</v>
@@ -23728,7 +23728,7 @@
         <v>10.26</v>
       </c>
       <c r="I308" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J308" t="n">
         <v>35.46</v>
@@ -23803,7 +23803,7 @@
         <v>10.31</v>
       </c>
       <c r="I309" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J309" t="n">
         <v>36.33</v>
@@ -23878,7 +23878,7 @@
         <v>-6.98</v>
       </c>
       <c r="I310" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J310" t="n">
         <v>36.96</v>
@@ -23953,7 +23953,7 @@
         <v>30.06</v>
       </c>
       <c r="I311" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J311" t="n">
         <v>38.12</v>
@@ -24028,7 +24028,7 @@
         <v>-3.57</v>
       </c>
       <c r="I312" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J312" t="n">
         <v>39.25</v>
@@ -24103,7 +24103,7 @@
         <v>12.4</v>
       </c>
       <c r="I313" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J313" t="n">
         <v>40.7</v>
@@ -24178,7 +24178,7 @@
         <v>-0.93</v>
       </c>
       <c r="I314" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J314" t="n">
         <v>41.96</v>
@@ -24253,7 +24253,7 @@
         <v>16.04</v>
       </c>
       <c r="I315" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J315" t="n">
         <v>43.61</v>
@@ -24328,7 +24328,7 @@
         <v>-3.16</v>
       </c>
       <c r="I316" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J316" t="n">
         <v>45.12</v>
@@ -24403,7 +24403,7 @@
         <v>-2.29</v>
       </c>
       <c r="I317" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J317" t="n">
         <v>46.28</v>
@@ -24478,7 +24478,7 @@
         <v>-12.28</v>
       </c>
       <c r="I318" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J318" t="n">
         <v>46.81</v>
@@ -24553,7 +24553,7 @@
         <v>-41.89</v>
       </c>
       <c r="I319" s="4" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J319" s="4" t="n">
         <v>46.41</v>
@@ -24632,7 +24632,7 @@
         <v>16.3</v>
       </c>
       <c r="I320" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J320" t="n">
         <v>45.83</v>
@@ -24707,7 +24707,7 @@
         <v>-2.45</v>
       </c>
       <c r="I321" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J321" t="n">
         <v>45.1</v>
@@ -24782,7 +24782,7 @@
         <v>-9.050000000000001</v>
       </c>
       <c r="I322" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J322" t="n">
         <v>44.77</v>
@@ -24857,7 +24857,7 @@
         <v>33.78</v>
       </c>
       <c r="I323" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J323" t="n">
         <v>44.64</v>
@@ -24932,7 +24932,7 @@
         <v>-2.04</v>
       </c>
       <c r="I324" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J324" t="n">
         <v>44.41</v>
@@ -25007,7 +25007,7 @@
         <v>21.14</v>
       </c>
       <c r="I325" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J325" t="n">
         <v>45.03</v>
@@ -25082,7 +25082,7 @@
         <v>-8.029999999999999</v>
       </c>
       <c r="I326" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J326" t="n">
         <v>45.54</v>
@@ -25157,7 +25157,7 @@
         <v>-0.5</v>
       </c>
       <c r="I327" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J327" t="n">
         <v>46.1</v>
@@ -25236,7 +25236,7 @@
         <v>19.29</v>
       </c>
       <c r="I328" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J328" t="n">
         <v>46.93</v>
@@ -25311,7 +25311,7 @@
         <v>-0.2</v>
       </c>
       <c r="I329" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J329" t="n">
         <v>47.55</v>
@@ -25386,7 +25386,7 @@
         <v>-35.7</v>
       </c>
       <c r="I330" s="4" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J330" s="4" t="n">
         <v>47.35</v>
@@ -25465,7 +25465,7 @@
         <v>5.89</v>
       </c>
       <c r="I331" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J331" t="n">
         <v>46.66</v>
@@ -25540,7 +25540,7 @@
         <v>11.85</v>
       </c>
       <c r="I332" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J332" t="n">
         <v>46.29</v>
@@ -25615,7 +25615,7 @@
         <v>-10.9</v>
       </c>
       <c r="I333" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J333" t="n">
         <v>45.39</v>
@@ -25690,7 +25690,7 @@
         <v>-0.03</v>
       </c>
       <c r="I334" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J334" t="n">
         <v>44.51</v>
@@ -25765,7 +25765,7 @@
         <v>5.82</v>
       </c>
       <c r="I335" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J335" t="n">
         <v>43.3</v>
@@ -25840,7 +25840,7 @@
         <v>-23.21</v>
       </c>
       <c r="I336" s="4" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J336" s="4" t="n">
         <v>41.74</v>
@@ -25919,7 +25919,7 @@
         <v>-9.77</v>
       </c>
       <c r="I337" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J337" t="n">
         <v>40.1</v>
@@ -25998,7 +25998,7 @@
         <v>15.37</v>
       </c>
       <c r="I338" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J338" t="n">
         <v>39.04</v>
@@ -26073,7 +26073,7 @@
         <v>-12.78</v>
       </c>
       <c r="I339" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J339" t="n">
         <v>38.87</v>
@@ -26152,7 +26152,7 @@
         <v>1.58</v>
       </c>
       <c r="I340" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J340" t="n">
         <v>38.48</v>
@@ -26227,7 +26227,7 @@
         <v>3</v>
       </c>
       <c r="I341" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J341" t="n">
         <v>38.18</v>
@@ -26302,7 +26302,7 @@
         <v>-2.28</v>
       </c>
       <c r="I342" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J342" t="n">
         <v>38</v>
@@ -26381,7 +26381,7 @@
         <v>-24.74</v>
       </c>
       <c r="I343" s="4" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J343" s="4" t="n">
         <v>36.94</v>
@@ -26456,7 +26456,7 @@
         <v>14.84</v>
       </c>
       <c r="I344" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J344" t="n">
         <v>36.08</v>
@@ -26531,7 +26531,7 @@
         <v>-9.140000000000001</v>
       </c>
       <c r="I345" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J345" t="n">
         <v>34.68</v>
@@ -26606,7 +26606,7 @@
         <v>-14.72</v>
       </c>
       <c r="I346" s="4" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J346" s="4" t="n">
         <v>33.31</v>
@@ -26685,7 +26685,7 @@
         <v>-2.09</v>
       </c>
       <c r="I347" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J347" t="n">
         <v>31.94</v>
@@ -26764,7 +26764,7 @@
         <v>0.82</v>
       </c>
       <c r="I348" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J348" t="n">
         <v>30.13</v>
@@ -26843,7 +26843,7 @@
         <v>18.03</v>
       </c>
       <c r="I349" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J349" t="n">
         <v>28.5</v>
@@ -26918,7 +26918,7 @@
         <v>-4.46</v>
       </c>
       <c r="I350" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J350" t="n">
         <v>27.79</v>
@@ -26993,7 +26993,7 @@
         <v>6.02</v>
       </c>
       <c r="I351" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J351" t="n">
         <v>27.03</v>
@@ -27068,7 +27068,7 @@
         <v>-18.9</v>
       </c>
       <c r="I352" s="4" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J352" s="4" t="n">
         <v>25.85</v>
@@ -27147,7 +27147,7 @@
         <v>-3.59</v>
       </c>
       <c r="I353" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J353" t="n">
         <v>24.87</v>
@@ -27222,7 +27222,7 @@
         <v>-17.78</v>
       </c>
       <c r="I354" s="4" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J354" s="4" t="n">
         <v>23.73</v>
@@ -27301,7 +27301,7 @@
         <v>-14.63</v>
       </c>
       <c r="I355" s="4" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J355" s="4" t="n">
         <v>22.38</v>
@@ -27380,7 +27380,7 @@
         <v>34.77</v>
       </c>
       <c r="I356" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J356" t="n">
         <v>21.69</v>
@@ -27455,7 +27455,7 @@
         <v>-7.92</v>
       </c>
       <c r="I357" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J357" t="n">
         <v>21.09</v>
@@ -27530,7 +27530,7 @@
         <v>5.87</v>
       </c>
       <c r="I358" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J358" t="n">
         <v>20.32</v>
@@ -27605,7 +27605,7 @@
         <v>20.48</v>
       </c>
       <c r="I359" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J359" t="n">
         <v>19.91</v>
@@ -27680,7 +27680,7 @@
         <v>-3.56</v>
       </c>
       <c r="I360" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J360" t="n">
         <v>19.45</v>
@@ -27755,7 +27755,7 @@
         <v>-8.84</v>
       </c>
       <c r="I361" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J361" t="n">
         <v>18.87</v>
@@ -27830,7 +27830,7 @@
         <v>3.27</v>
       </c>
       <c r="I362" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J362" t="n">
         <v>18.34</v>
@@ -27905,7 +27905,7 @@
         <v>-5.47</v>
       </c>
       <c r="I363" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J363" t="n">
         <v>18.12</v>
@@ -27980,7 +27980,7 @@
         <v>7.5</v>
       </c>
       <c r="I364" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J364" t="n">
         <v>17.8</v>
@@ -28055,7 +28055,7 @@
         <v>15.19</v>
       </c>
       <c r="I365" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J365" t="n">
         <v>17.72</v>
@@ -28130,7 +28130,7 @@
         <v>4.68</v>
       </c>
       <c r="I366" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J366" t="n">
         <v>17.85</v>
@@ -28205,7 +28205,7 @@
         <v>1.55</v>
       </c>
       <c r="I367" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J367" t="n">
         <v>18.02</v>
@@ -28280,7 +28280,7 @@
         <v>8.98</v>
       </c>
       <c r="I368" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J368" t="n">
         <v>18.27</v>
@@ -28355,7 +28355,7 @@
         <v>-24.21</v>
       </c>
       <c r="I369" s="4" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J369" s="4" t="n">
         <v>18.08</v>
@@ -28434,7 +28434,7 @@
         <v>7.12</v>
       </c>
       <c r="I370" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J370" t="n">
         <v>18</v>
@@ -28509,7 +28509,7 @@
         <v>6.38</v>
       </c>
       <c r="I371" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J371" t="n">
         <v>17.91</v>
@@ -28584,7 +28584,7 @@
         <v>0.15</v>
       </c>
       <c r="I372" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J372" t="n">
         <v>18.04</v>
@@ -28659,7 +28659,7 @@
         <v>-7.86</v>
       </c>
       <c r="I373" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J373" t="n">
         <v>18.11</v>
@@ -28734,7 +28734,7 @@
         <v>11.03</v>
       </c>
       <c r="I374" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J374" t="n">
         <v>18.45</v>
@@ -28809,7 +28809,7 @@
         <v>-1.63</v>
       </c>
       <c r="I375" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J375" t="n">
         <v>18.87</v>
@@ -28884,7 +28884,7 @@
         <v>4.49</v>
       </c>
       <c r="I376" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J376" t="n">
         <v>19.12</v>
@@ -28959,7 +28959,7 @@
         <v>-2.99</v>
       </c>
       <c r="I377" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J377" t="n">
         <v>19.41</v>
@@ -29034,7 +29034,7 @@
         <v>0.91</v>
       </c>
       <c r="I378" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J378" t="n">
         <v>19.67</v>
@@ -29109,7 +29109,7 @@
         <v>-8.49</v>
       </c>
       <c r="I379" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J379" t="n">
         <v>19.67</v>
@@ -29188,7 +29188,7 @@
         <v>5.06</v>
       </c>
       <c r="I380" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J380" t="n">
         <v>19.76</v>
@@ -29263,7 +29263,7 @@
         <v>2.68</v>
       </c>
       <c r="I381" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J381" t="n">
         <v>19.95</v>
@@ -29338,7 +29338,7 @@
         <v>13.44</v>
       </c>
       <c r="I382" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J382" t="n">
         <v>20.26</v>
@@ -29413,7 +29413,7 @@
         <v>1.58</v>
       </c>
       <c r="I383" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J383" t="n">
         <v>20.63</v>
@@ -29488,7 +29488,7 @@
         <v>1.51</v>
       </c>
       <c r="I384" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J384" t="n">
         <v>20.96</v>
@@ -29563,7 +29563,7 @@
         <v>-12.52</v>
       </c>
       <c r="I385" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J385" t="n">
         <v>21</v>
@@ -29638,7 +29638,7 @@
         <v>8.970000000000001</v>
       </c>
       <c r="I386" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J386" t="n">
         <v>21.09</v>
@@ -29713,7 +29713,7 @@
         <v>-19.51</v>
       </c>
       <c r="I387" s="4" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J387" s="4" t="n">
         <v>20.94</v>
@@ -29792,7 +29792,7 @@
         <v>0.16</v>
       </c>
       <c r="I388" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J388" t="n">
         <v>20.69</v>
@@ -29867,7 +29867,7 @@
         <v>-1.72</v>
       </c>
       <c r="I389" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J389" t="n">
         <v>20.71</v>
@@ -29942,7 +29942,7 @@
         <v>11.65</v>
       </c>
       <c r="I390" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J390" t="n">
         <v>20.78</v>
@@ -30017,7 +30017,7 @@
         <v>-1.81</v>
       </c>
       <c r="I391" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J391" t="n">
         <v>20.76</v>
@@ -30092,7 +30092,7 @@
         <v>12.52</v>
       </c>
       <c r="I392" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J392" t="n">
         <v>20.87</v>
@@ -30167,7 +30167,7 @@
         <v>5.41</v>
       </c>
       <c r="I393" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J393" t="n">
         <v>21.12</v>
@@ -30242,7 +30242,7 @@
         <v>-10.52</v>
       </c>
       <c r="I394" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J394" t="n">
         <v>21.14</v>
@@ -30317,7 +30317,7 @@
         <v>-5.31</v>
       </c>
       <c r="I395" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J395" t="n">
         <v>21.13</v>
@@ -30396,7 +30396,7 @@
         <v>7.2</v>
       </c>
       <c r="I396" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J396" t="n">
         <v>21.14</v>
@@ -30471,7 +30471,7 @@
         <v>-5.51</v>
       </c>
       <c r="I397" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J397" t="n">
         <v>21.12</v>
@@ -30550,7 +30550,7 @@
         <v>5.25</v>
       </c>
       <c r="I398" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J398" t="n">
         <v>21.14</v>
@@ -30625,7 +30625,7 @@
         <v>-6.75</v>
       </c>
       <c r="I399" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J399" t="n">
         <v>21.18</v>
@@ -30704,7 +30704,7 @@
         <v>5.34</v>
       </c>
       <c r="I400" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J400" t="n">
         <v>21.23</v>
@@ -30779,7 +30779,7 @@
         <v>8.82</v>
       </c>
       <c r="I401" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J401" t="n">
         <v>21.34</v>
@@ -30854,7 +30854,7 @@
         <v>-0.74</v>
       </c>
       <c r="I402" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J402" t="n">
         <v>21.31</v>
@@ -30929,7 +30929,7 @@
         <v>-7.77</v>
       </c>
       <c r="I403" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J403" t="n">
         <v>21.17</v>
@@ -31008,7 +31008,7 @@
         <v>-4.57</v>
       </c>
       <c r="I404" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J404" t="n">
         <v>20.96</v>
@@ -31083,7 +31083,7 @@
         <v>-11.97</v>
       </c>
       <c r="I405" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J405" t="n">
         <v>20.79</v>
@@ -31162,7 +31162,7 @@
         <v>1.13</v>
       </c>
       <c r="I406" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J406" t="n">
         <v>20.52</v>
@@ -31237,7 +31237,7 @@
         <v>-11.82</v>
       </c>
       <c r="I407" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J407" t="n">
         <v>20.38</v>
@@ -31316,7 +31316,7 @@
         <v>-6.48</v>
       </c>
       <c r="I408" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J408" t="n">
         <v>20.19</v>
@@ -31391,7 +31391,7 @@
         <v>-12.16</v>
       </c>
       <c r="I409" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J409" t="n">
         <v>19.92</v>
@@ -31466,7 +31466,7 @@
         <v>-7.12</v>
       </c>
       <c r="I410" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J410" t="n">
         <v>19.5</v>
@@ -31545,7 +31545,7 @@
         <v>-11.41</v>
       </c>
       <c r="I411" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J411" t="n">
         <v>19.03</v>
@@ -31624,7 +31624,7 @@
         <v>12.03</v>
       </c>
       <c r="I412" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J412" t="n">
         <v>18.5</v>
@@ -31703,7 +31703,7 @@
         <v>-4.87</v>
       </c>
       <c r="I413" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J413" t="n">
         <v>17.88</v>
@@ -31782,7 +31782,7 @@
         <v>5.29</v>
       </c>
       <c r="I414" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J414" t="n">
         <v>17.41</v>
@@ -31832,81 +31832,61 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="4" t="inlineStr">
-        <is>
-          <t>KORU</t>
-        </is>
-      </c>
-      <c r="B415" s="4" t="inlineStr">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>KORU</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="C415" s="4" t="n">
-        <v>10.83</v>
-      </c>
-      <c r="D415" s="4" t="n">
-        <v>11.16</v>
-      </c>
-      <c r="E415" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="F415" s="4" t="n">
-        <v>10.19</v>
-      </c>
-      <c r="G415" s="4" t="n">
-        <v>47196536</v>
-      </c>
-      <c r="H415" s="5" t="n">
-        <v>-14.66</v>
-      </c>
-      <c r="I415" s="4" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="J415" s="4" t="n">
-        <v>16.91</v>
-      </c>
-      <c r="K415" s="4" t="n">
-        <v>18.97</v>
-      </c>
-      <c r="L415" s="4" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="M415" s="4" t="n">
-        <v>24.45</v>
-      </c>
-      <c r="N415" s="7" t="n">
-        <v>12.29</v>
-      </c>
-      <c r="O415" s="4" t="n">
+      <c r="C415" t="inlineStr"/>
+      <c r="D415" t="inlineStr"/>
+      <c r="E415" t="inlineStr"/>
+      <c r="F415" t="inlineStr"/>
+      <c r="G415" t="n">
+        <v>47405013</v>
+      </c>
+      <c r="H415" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I415" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J415" t="inlineStr"/>
+      <c r="K415" t="inlineStr"/>
+      <c r="L415" t="inlineStr"/>
+      <c r="M415" t="inlineStr"/>
+      <c r="N415" s="3" t="n">
+        <v>13.71</v>
+      </c>
+      <c r="O415" t="n">
         <v>20</v>
       </c>
-      <c r="P415" s="4" t="inlineStr">
+      <c r="P415" t="inlineStr">
         <is>
           <t>extreme fear</t>
         </is>
       </c>
-      <c r="Q415" s="4" t="inlineStr">
+      <c r="Q415" t="inlineStr">
         <is>
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R415" s="4" t="inlineStr">
-        <is>
-          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
-        </is>
-      </c>
-      <c r="S415" s="4" t="n">
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
         <v>4.95</v>
       </c>
-      <c r="T415" s="6" t="n">
+      <c r="T415" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="U415" s="6" t="n">
+      <c r="U415" s="2" t="n">
         <v>15.2</v>
       </c>
-      <c r="V415" s="4" t="inlineStr"/>
-      <c r="W415" s="6" t="n">
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="2" t="n">
         <v>152.4</v>
       </c>
     </row>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -608,7 +608,7 @@
         <v>-1.49</v>
       </c>
       <c r="I2" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J2" t="n">
         <v>2.19</v>
@@ -683,7 +683,7 @@
         <v>1.01</v>
       </c>
       <c r="I3" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J3" t="n">
         <v>2.19</v>
@@ -758,7 +758,7 @@
         <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J4" t="n">
         <v>2.2</v>
@@ -833,7 +833,7 @@
         <v>-5.56</v>
       </c>
       <c r="I5" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J5" t="n">
         <v>2.2</v>
@@ -912,7 +912,7 @@
         <v>3.43</v>
       </c>
       <c r="I6" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J6" t="n">
         <v>2.2</v>
@@ -987,7 +987,7 @@
         <v>-8.529999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J7" t="n">
         <v>2.2</v>
@@ -1070,7 +1070,7 @@
         <v>3.11</v>
       </c>
       <c r="I8" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J8" t="n">
         <v>2.19</v>
@@ -1149,7 +1149,7 @@
         <v>7.04</v>
       </c>
       <c r="I9" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J9" t="n">
         <v>2.19</v>
@@ -1224,7 +1224,7 @@
         <v>-3.76</v>
       </c>
       <c r="I10" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J10" t="n">
         <v>2.19</v>
@@ -1303,7 +1303,7 @@
         <v>4.88</v>
       </c>
       <c r="I11" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J11" t="n">
         <v>2.19</v>
@@ -1378,7 +1378,7 @@
         <v>8.84</v>
       </c>
       <c r="I12" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J12" t="n">
         <v>2.19</v>
@@ -1453,7 +1453,7 @@
         <v>-4.7</v>
       </c>
       <c r="I13" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J13" t="n">
         <v>2.18</v>
@@ -1528,7 +1528,7 @@
         <v>1.35</v>
       </c>
       <c r="I14" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J14" t="n">
         <v>2.17</v>
@@ -1603,7 +1603,7 @@
         <v>-2.65</v>
       </c>
       <c r="I15" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J15" t="n">
         <v>2.16</v>
@@ -1678,7 +1678,7 @@
         <v>0.91</v>
       </c>
       <c r="I16" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J16" t="n">
         <v>2.15</v>
@@ -1753,7 +1753,7 @@
         <v>2.25</v>
       </c>
       <c r="I17" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J17" t="n">
         <v>2.15</v>
@@ -1828,7 +1828,7 @@
         <v>-1.32</v>
       </c>
       <c r="I18" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J18" t="n">
         <v>2.14</v>
@@ -1903,7 +1903,7 @@
         <v>-1.34</v>
       </c>
       <c r="I19" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J19" t="n">
         <v>2.13</v>
@@ -1978,7 +1978,7 @@
         <v>-1.81</v>
       </c>
       <c r="I20" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J20" t="n">
         <v>2.13</v>
@@ -2053,7 +2053,7 @@
         <v>-9.220000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J21" t="n">
         <v>2.13</v>
@@ -2132,7 +2132,7 @@
         <v>-4.06</v>
       </c>
       <c r="I22" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J22" t="n">
         <v>2.13</v>
@@ -2207,7 +2207,7 @@
         <v>4.76</v>
       </c>
       <c r="I23" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J23" t="n">
         <v>2.13</v>
@@ -2282,7 +2282,7 @@
         <v>-1.01</v>
       </c>
       <c r="I24" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J24" t="n">
         <v>2.12</v>
@@ -2357,7 +2357,7 @@
         <v>-8.67</v>
       </c>
       <c r="I25" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J25" t="n">
         <v>2.1</v>
@@ -2436,7 +2436,7 @@
         <v>-10.61</v>
       </c>
       <c r="I26" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J26" t="n">
         <v>2.08</v>
@@ -2519,7 +2519,7 @@
         <v>-3.12</v>
       </c>
       <c r="I27" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J27" t="n">
         <v>2.06</v>
@@ -2602,7 +2602,7 @@
         <v>-10.32</v>
       </c>
       <c r="I28" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J28" t="n">
         <v>2.03</v>
@@ -2685,7 +2685,7 @@
         <v>24.46</v>
       </c>
       <c r="I29" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J29" t="n">
         <v>2.01</v>
@@ -2764,7 +2764,7 @@
         <v>-6.94</v>
       </c>
       <c r="I30" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J30" t="n">
         <v>1.99</v>
@@ -2843,7 +2843,7 @@
         <v>14.29</v>
       </c>
       <c r="I31" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J31" t="n">
         <v>1.97</v>
@@ -2922,7 +2922,7 @@
         <v>-0.54</v>
       </c>
       <c r="I32" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J32" t="n">
         <v>1.95</v>
@@ -2997,7 +2997,7 @@
         <v>0.55</v>
       </c>
       <c r="I33" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J33" t="n">
         <v>1.93</v>
@@ -3072,7 +3072,7 @@
         <v>-2.17</v>
       </c>
       <c r="I34" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J34" t="n">
         <v>1.9</v>
@@ -3151,7 +3151,7 @@
         <v>1.67</v>
       </c>
       <c r="I35" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J35" t="n">
         <v>1.89</v>
@@ -3230,7 +3230,7 @@
         <v>0.55</v>
       </c>
       <c r="I36" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J36" t="n">
         <v>1.87</v>
@@ -3305,7 +3305,7 @@
         <v>2.17</v>
       </c>
       <c r="I37" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J37" t="n">
         <v>1.85</v>
@@ -3380,7 +3380,7 @@
         <v>3.72</v>
       </c>
       <c r="I38" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J38" t="n">
         <v>1.83</v>
@@ -3459,7 +3459,7 @@
         <v>2.05</v>
       </c>
       <c r="I39" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J39" t="n">
         <v>1.82</v>
@@ -3534,7 +3534,7 @@
         <v>-0.5</v>
       </c>
       <c r="I40" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J40" t="n">
         <v>1.81</v>
@@ -3609,7 +3609,7 @@
         <v>-1.01</v>
       </c>
       <c r="I41" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J41" t="n">
         <v>1.81</v>
@@ -3684,7 +3684,7 @@
         <v>2.55</v>
       </c>
       <c r="I42" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J42" t="n">
         <v>1.82</v>
@@ -3759,7 +3759,7 @@
         <v>0.5</v>
       </c>
       <c r="I43" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J43" t="n">
         <v>1.82</v>
@@ -3834,7 +3834,7 @@
         <v>-2.97</v>
       </c>
       <c r="I44" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J44" t="n">
         <v>1.82</v>
@@ -3909,7 +3909,7 @@
         <v>10.71</v>
       </c>
       <c r="I45" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J45" t="n">
         <v>1.84</v>
@@ -3984,7 +3984,7 @@
         <v>4.15</v>
       </c>
       <c r="I46" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J46" t="n">
         <v>1.87</v>
@@ -4059,7 +4059,7 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J47" t="n">
         <v>1.91</v>
@@ -4134,7 +4134,7 @@
         <v>-3.54</v>
       </c>
       <c r="I48" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J48" t="n">
         <v>1.95</v>
@@ -4209,7 +4209,7 @@
         <v>-3.21</v>
       </c>
       <c r="I49" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J49" t="n">
         <v>1.97</v>
@@ -4284,7 +4284,7 @@
         <v>2.84</v>
       </c>
       <c r="I50" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J50" t="n">
         <v>1.99</v>
@@ -4359,7 +4359,7 @@
         <v>1.38</v>
       </c>
       <c r="I51" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J51" t="n">
         <v>2.01</v>
@@ -4434,7 +4434,7 @@
         <v>0.45</v>
       </c>
       <c r="I52" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J52" t="n">
         <v>2.03</v>
@@ -4509,7 +4509,7 @@
         <v>2.71</v>
       </c>
       <c r="I53" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J53" t="n">
         <v>2.05</v>
@@ -4584,7 +4584,7 @@
         <v>0.88</v>
       </c>
       <c r="I54" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J54" t="n">
         <v>2.08</v>
@@ -4659,7 +4659,7 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J55" t="n">
         <v>2.1</v>
@@ -4734,7 +4734,7 @@
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J56" t="n">
         <v>2.12</v>
@@ -4809,7 +4809,7 @@
         <v>-2.18</v>
       </c>
       <c r="I57" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J57" t="n">
         <v>2.14</v>
@@ -4884,7 +4884,7 @@
         <v>3.57</v>
       </c>
       <c r="I58" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J58" t="n">
         <v>2.16</v>
@@ -4959,7 +4959,7 @@
         <v>-3.88</v>
       </c>
       <c r="I59" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J59" t="n">
         <v>2.17</v>
@@ -5034,7 +5034,7 @@
         <v>3.14</v>
       </c>
       <c r="I60" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J60" t="n">
         <v>2.19</v>
@@ -5109,7 +5109,7 @@
         <v>4.78</v>
       </c>
       <c r="I61" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J61" t="n">
         <v>2.21</v>
@@ -5184,7 +5184,7 @@
         <v>3.73</v>
       </c>
       <c r="I62" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J62" t="n">
         <v>2.23</v>
@@ -5259,7 +5259,7 @@
         <v>5.2</v>
       </c>
       <c r="I63" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J63" t="n">
         <v>2.26</v>
@@ -5334,7 +5334,7 @@
         <v>-5.7</v>
       </c>
       <c r="I64" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J64" t="n">
         <v>2.29</v>
@@ -5409,7 +5409,7 @@
         <v>5.65</v>
       </c>
       <c r="I65" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J65" t="n">
         <v>2.31</v>
@@ -5484,7 +5484,7 @@
         <v>1.15</v>
       </c>
       <c r="I66" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J66" t="n">
         <v>2.33</v>
@@ -5559,7 +5559,7 @@
         <v>9.43</v>
       </c>
       <c r="I67" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J67" t="n">
         <v>2.36</v>
@@ -5634,7 +5634,7 @@
         <v>6.55</v>
       </c>
       <c r="I68" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J68" t="n">
         <v>2.41</v>
@@ -5709,7 +5709,7 @@
         <v>0.65</v>
       </c>
       <c r="I69" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J69" t="n">
         <v>2.46</v>
@@ -5784,7 +5784,7 @@
         <v>4.5</v>
       </c>
       <c r="I70" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J70" t="n">
         <v>2.51</v>
@@ -5859,7 +5859,7 @@
         <v>-1.54</v>
       </c>
       <c r="I71" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J71" t="n">
         <v>2.56</v>
@@ -5934,7 +5934,7 @@
         <v>3.75</v>
       </c>
       <c r="I72" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J72" t="n">
         <v>2.62</v>
@@ -6009,7 +6009,7 @@
         <v>3.31</v>
       </c>
       <c r="I73" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J73" t="n">
         <v>2.68</v>
@@ -6084,7 +6084,7 @@
         <v>-5.83</v>
       </c>
       <c r="I74" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J74" t="n">
         <v>2.72</v>
@@ -6159,7 +6159,7 @@
         <v>8.050000000000001</v>
       </c>
       <c r="I75" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J75" t="n">
         <v>2.78</v>
@@ -6234,7 +6234,7 @@
         <v>-6.88</v>
       </c>
       <c r="I76" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J76" t="n">
         <v>2.83</v>
@@ -6309,7 +6309,7 @@
         <v>5.23</v>
       </c>
       <c r="I77" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J77" t="n">
         <v>2.89</v>
@@ -6384,7 +6384,7 @@
         <v>2.92</v>
       </c>
       <c r="I78" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J78" t="n">
         <v>2.95</v>
@@ -6459,7 +6459,7 @@
         <v>3.69</v>
       </c>
       <c r="I79" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J79" t="n">
         <v>3.02</v>
@@ -6534,7 +6534,7 @@
         <v>14.25</v>
       </c>
       <c r="I80" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J80" t="n">
         <v>3.12</v>
@@ -6609,7 +6609,7 @@
         <v>-1.2</v>
       </c>
       <c r="I81" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J81" t="n">
         <v>3.2</v>
@@ -6684,7 +6684,7 @@
         <v>-1.94</v>
       </c>
       <c r="I82" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J82" t="n">
         <v>3.28</v>
@@ -6759,7 +6759,7 @@
         <v>-4.95</v>
       </c>
       <c r="I83" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J83" t="n">
         <v>3.34</v>
@@ -6834,7 +6834,7 @@
         <v>4.17</v>
       </c>
       <c r="I84" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J84" t="n">
         <v>3.42</v>
@@ -6909,7 +6909,7 @@
         <v>-0.5</v>
       </c>
       <c r="I85" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J85" t="n">
         <v>3.48</v>
@@ -6984,7 +6984,7 @@
         <v>1.26</v>
       </c>
       <c r="I86" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J86" t="n">
         <v>3.55</v>
@@ -7059,7 +7059,7 @@
         <v>2.73</v>
       </c>
       <c r="I87" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J87" t="n">
         <v>3.61</v>
@@ -7134,7 +7134,7 @@
         <v>-10.39</v>
       </c>
       <c r="I88" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J88" t="n">
         <v>3.65</v>
@@ -7209,7 +7209,7 @@
         <v>8.09</v>
       </c>
       <c r="I89" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J89" t="n">
         <v>3.69</v>
@@ -7284,7 +7284,7 @@
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J90" t="n">
         <v>3.73</v>
@@ -7359,7 +7359,7 @@
         <v>4.49</v>
       </c>
       <c r="I91" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J91" t="n">
         <v>3.78</v>
@@ -7434,7 +7434,7 @@
         <v>-2.39</v>
       </c>
       <c r="I92" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J92" t="n">
         <v>3.82</v>
@@ -7509,7 +7509,7 @@
         <v>2.44</v>
       </c>
       <c r="I93" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J93" t="n">
         <v>3.85</v>
@@ -7584,7 +7584,7 @@
         <v>-0.48</v>
       </c>
       <c r="I94" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J94" t="n">
         <v>3.9</v>
@@ -7659,7 +7659,7 @@
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J95" t="n">
         <v>3.94</v>
@@ -7734,7 +7734,7 @@
         <v>-0.24</v>
       </c>
       <c r="I96" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J96" t="n">
         <v>3.98</v>
@@ -7809,7 +7809,7 @@
         <v>-2.64</v>
       </c>
       <c r="I97" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J97" t="n">
         <v>4.01</v>
@@ -7884,7 +7884,7 @@
         <v>5.93</v>
       </c>
       <c r="I98" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J98" t="n">
         <v>4.05</v>
@@ -7959,7 +7959,7 @@
         <v>-3.73</v>
       </c>
       <c r="I99" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J99" t="n">
         <v>4.07</v>
@@ -8034,7 +8034,7 @@
         <v>3.63</v>
       </c>
       <c r="I100" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J100" t="n">
         <v>4.08</v>
@@ -8109,7 +8109,7 @@
         <v>-2.1</v>
       </c>
       <c r="I101" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J101" t="n">
         <v>4.08</v>
@@ -8184,7 +8184,7 @@
         <v>-0.48</v>
       </c>
       <c r="I102" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J102" t="n">
         <v>4.09</v>
@@ -8259,7 +8259,7 @@
         <v>-2.16</v>
       </c>
       <c r="I103" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J103" t="n">
         <v>4.1</v>
@@ -8338,7 +8338,7 @@
         <v>3.19</v>
       </c>
       <c r="I104" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J104" t="n">
         <v>4.11</v>
@@ -8413,7 +8413,7 @@
         <v>0.95</v>
       </c>
       <c r="I105" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J105" t="n">
         <v>4.13</v>
@@ -8488,7 +8488,7 @@
         <v>-3.76</v>
       </c>
       <c r="I106" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J106" t="n">
         <v>4.13</v>
@@ -8567,7 +8567,7 @@
         <v>-9.050000000000001</v>
       </c>
       <c r="I107" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J107" t="n">
         <v>4.11</v>
@@ -8642,7 +8642,7 @@
         <v>7.26</v>
       </c>
       <c r="I108" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J108" t="n">
         <v>4.12</v>
@@ -8717,7 +8717,7 @@
         <v>2.26</v>
       </c>
       <c r="I109" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J109" t="n">
         <v>4.13</v>
@@ -8792,7 +8792,7 @@
         <v>0.98</v>
       </c>
       <c r="I110" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J110" t="n">
         <v>4.13</v>
@@ -8867,7 +8867,7 @@
         <v>0.97</v>
       </c>
       <c r="I111" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J111" t="n">
         <v>4.13</v>
@@ -8942,7 +8942,7 @@
         <v>0.24</v>
       </c>
       <c r="I112" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J112" t="n">
         <v>4.13</v>
@@ -9017,7 +9017,7 @@
         <v>-1.92</v>
       </c>
       <c r="I113" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J113" t="n">
         <v>4.13</v>
@@ -9096,7 +9096,7 @@
         <v>4.16</v>
       </c>
       <c r="I114" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J114" t="n">
         <v>4.13</v>
@@ -9171,7 +9171,7 @@
         <v>2.58</v>
       </c>
       <c r="I115" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J115" t="n">
         <v>4.14</v>
@@ -9246,7 +9246,7 @@
         <v>-4.12</v>
       </c>
       <c r="I116" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J116" t="n">
         <v>4.14</v>
@@ -9321,7 +9321,7 @@
         <v>-1.19</v>
       </c>
       <c r="I117" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J117" t="n">
         <v>4.15</v>
@@ -9400,7 +9400,7 @@
         <v>-2.42</v>
       </c>
       <c r="I118" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J118" t="n">
         <v>4.14</v>
@@ -9475,7 +9475,7 @@
         <v>-5.45</v>
       </c>
       <c r="I119" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J119" t="n">
         <v>4.12</v>
@@ -9550,7 +9550,7 @@
         <v>-0.52</v>
       </c>
       <c r="I120" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J120" t="n">
         <v>4.1</v>
@@ -9625,7 +9625,7 @@
         <v>-0.79</v>
       </c>
       <c r="I121" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J121" t="n">
         <v>4.08</v>
@@ -9704,7 +9704,7 @@
         <v>9.81</v>
       </c>
       <c r="I122" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J122" t="n">
         <v>4.07</v>
@@ -9779,7 +9779,7 @@
         <v>-3.38</v>
       </c>
       <c r="I123" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J123" t="n">
         <v>4.07</v>
@@ -9858,7 +9858,7 @@
         <v>-1.5</v>
       </c>
       <c r="I124" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J124" t="n">
         <v>4.06</v>
@@ -9933,7 +9933,7 @@
         <v>0.51</v>
       </c>
       <c r="I125" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J125" t="n">
         <v>4.04</v>
@@ -10008,7 +10008,7 @@
         <v>4.55</v>
       </c>
       <c r="I126" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J126" t="n">
         <v>4.04</v>
@@ -10083,7 +10083,7 @@
         <v>-5.56</v>
       </c>
       <c r="I127" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J127" t="n">
         <v>4.05</v>
@@ -10162,7 +10162,7 @@
         <v>-1.53</v>
       </c>
       <c r="I128" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J128" t="n">
         <v>4.05</v>
@@ -10237,7 +10237,7 @@
         <v>3.9</v>
       </c>
       <c r="I129" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J129" t="n">
         <v>4.04</v>
@@ -10312,7 +10312,7 @@
         <v>0.75</v>
       </c>
       <c r="I130" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J130" t="n">
         <v>4.04</v>
@@ -10387,7 +10387,7 @@
         <v>2.23</v>
       </c>
       <c r="I131" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J131" t="n">
         <v>4.04</v>
@@ -10462,7 +10462,7 @@
         <v>1.94</v>
       </c>
       <c r="I132" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J132" t="n">
         <v>4.04</v>
@@ -10537,7 +10537,7 @@
         <v>3.1</v>
       </c>
       <c r="I133" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J133" t="n">
         <v>4.05</v>
@@ -10612,7 +10612,7 @@
         <v>6.93</v>
       </c>
       <c r="I134" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J134" t="n">
         <v>4.07</v>
@@ -10687,7 +10687,7 @@
         <v>4.75</v>
       </c>
       <c r="I135" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J135" t="n">
         <v>4.09</v>
@@ -10762,7 +10762,7 @@
         <v>3.09</v>
       </c>
       <c r="I136" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J136" t="n">
         <v>4.13</v>
@@ -10837,7 +10837,7 @@
         <v>2</v>
       </c>
       <c r="I137" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J137" t="n">
         <v>4.18</v>
@@ -10912,7 +10912,7 @@
         <v>5.69</v>
       </c>
       <c r="I138" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J138" t="n">
         <v>4.25</v>
@@ -10987,7 +10987,7 @@
         <v>-3.34</v>
       </c>
       <c r="I139" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J139" t="n">
         <v>4.32</v>
@@ -11062,7 +11062,7 @@
         <v>3.65</v>
       </c>
       <c r="I140" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J140" t="n">
         <v>4.4</v>
@@ -11137,7 +11137,7 @@
         <v>-2.96</v>
       </c>
       <c r="I141" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J141" t="n">
         <v>4.47</v>
@@ -11212,7 +11212,7 @@
         <v>5.92</v>
       </c>
       <c r="I142" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J142" t="n">
         <v>4.54</v>
@@ -11287,7 +11287,7 @@
         <v>-0.54</v>
       </c>
       <c r="I143" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J143" t="n">
         <v>4.62</v>
@@ -11362,7 +11362,7 @@
         <v>-5.25</v>
       </c>
       <c r="I144" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J144" t="n">
         <v>4.68</v>
@@ -11437,7 +11437,7 @@
         <v>-0.57</v>
       </c>
       <c r="I145" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J145" t="n">
         <v>4.74</v>
@@ -11512,7 +11512,7 @@
         <v>-3.85</v>
       </c>
       <c r="I146" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J146" t="n">
         <v>4.79</v>
@@ -11587,7 +11587,7 @@
         <v>5</v>
       </c>
       <c r="I147" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J147" t="n">
         <v>4.85</v>
@@ -11662,7 +11662,7 @@
         <v>-0.38</v>
       </c>
       <c r="I148" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J148" t="n">
         <v>4.92</v>
@@ -11737,7 +11737,7 @@
         <v>6.5</v>
       </c>
       <c r="I149" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J149" t="n">
         <v>5</v>
@@ -11812,7 +11812,7 @@
         <v>6.1</v>
       </c>
       <c r="I150" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J150" t="n">
         <v>5.1</v>
@@ -11887,7 +11887,7 @@
         <v>1.18</v>
       </c>
       <c r="I151" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J151" t="n">
         <v>5.19</v>
@@ -11962,7 +11962,7 @@
         <v>3.18</v>
       </c>
       <c r="I152" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J152" t="n">
         <v>5.29</v>
@@ -12037,7 +12037,7 @@
         <v>-4.86</v>
       </c>
       <c r="I153" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J153" t="n">
         <v>5.36</v>
@@ -12112,7 +12112,7 @@
         <v>2.73</v>
       </c>
       <c r="I154" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J154" t="n">
         <v>5.44</v>
@@ -12187,7 +12187,7 @@
         <v>-2.65</v>
       </c>
       <c r="I155" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J155" t="n">
         <v>5.49</v>
@@ -12262,7 +12262,7 @@
         <v>-9.710000000000001</v>
       </c>
       <c r="I156" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J156" t="n">
         <v>5.5</v>
@@ -12341,7 +12341,7 @@
         <v>10.38</v>
       </c>
       <c r="I157" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J157" t="n">
         <v>5.54</v>
@@ -12416,7 +12416,7 @@
         <v>-3.25</v>
       </c>
       <c r="I158" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J158" t="n">
         <v>5.55</v>
@@ -12491,7 +12491,7 @@
         <v>8.83</v>
       </c>
       <c r="I159" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J159" t="n">
         <v>5.6</v>
@@ -12566,7 +12566,7 @@
         <v>9.58</v>
       </c>
       <c r="I160" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J160" t="n">
         <v>5.67</v>
@@ -12641,7 +12641,7 @@
         <v>2.07</v>
       </c>
       <c r="I161" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J161" t="n">
         <v>5.75</v>
@@ -12716,7 +12716,7 @@
         <v>6.68</v>
       </c>
       <c r="I162" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J162" t="n">
         <v>5.84</v>
@@ -12791,7 +12791,7 @@
         <v>-6.12</v>
       </c>
       <c r="I163" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J163" t="n">
         <v>5.91</v>
@@ -12866,7 +12866,7 @@
         <v>2.75</v>
       </c>
       <c r="I164" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J164" t="n">
         <v>6</v>
@@ -12941,7 +12941,7 @@
         <v>1.97</v>
       </c>
       <c r="I165" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J165" t="n">
         <v>6.1</v>
@@ -13016,7 +13016,7 @@
         <v>6.64</v>
       </c>
       <c r="I166" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J166" t="n">
         <v>6.24</v>
@@ -13091,7 +13091,7 @@
         <v>7.39</v>
       </c>
       <c r="I167" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J167" t="n">
         <v>6.39</v>
@@ -13166,7 +13166,7 @@
         <v>0.36</v>
       </c>
       <c r="I168" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J168" t="n">
         <v>6.54</v>
@@ -13241,7 +13241,7 @@
         <v>7.82</v>
       </c>
       <c r="I169" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J169" t="n">
         <v>6.71</v>
@@ -13316,7 +13316,7 @@
         <v>-5.02</v>
       </c>
       <c r="I170" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J170" t="n">
         <v>6.84</v>
@@ -13391,7 +13391,7 @@
         <v>5.17</v>
       </c>
       <c r="I171" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J171" t="n">
         <v>6.99</v>
@@ -13466,7 +13466,7 @@
         <v>11.62</v>
       </c>
       <c r="I172" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J172" t="n">
         <v>7.18</v>
@@ -13541,7 +13541,7 @@
         <v>-14.81</v>
       </c>
       <c r="I173" s="4" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J173" s="4" t="n">
         <v>7.32</v>
@@ -13616,7 +13616,7 @@
         <v>2.47</v>
       </c>
       <c r="I174" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J174" t="n">
         <v>7.45</v>
@@ -13691,7 +13691,7 @@
         <v>-9.52</v>
       </c>
       <c r="I175" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J175" t="n">
         <v>7.55</v>
@@ -13766,7 +13766,7 @@
         <v>-5.7</v>
       </c>
       <c r="I176" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J176" t="n">
         <v>7.66</v>
@@ -13845,7 +13845,7 @@
         <v>12.5</v>
       </c>
       <c r="I177" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J177" t="n">
         <v>7.78</v>
@@ -13920,7 +13920,7 @@
         <v>-1.19</v>
       </c>
       <c r="I178" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J178" t="n">
         <v>7.91</v>
@@ -13995,7 +13995,7 @@
         <v>2.06</v>
       </c>
       <c r="I179" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J179" t="n">
         <v>8.029999999999999</v>
@@ -14070,7 +14070,7 @@
         <v>-5.92</v>
       </c>
       <c r="I180" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J180" t="n">
         <v>8.09</v>
@@ -14149,7 +14149,7 @@
         <v>0.38</v>
       </c>
       <c r="I181" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J181" t="n">
         <v>8.140000000000001</v>
@@ -14224,7 +14224,7 @@
         <v>-3.76</v>
       </c>
       <c r="I182" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J182" t="n">
         <v>8.16</v>
@@ -14299,7 +14299,7 @@
         <v>-4.69</v>
       </c>
       <c r="I183" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J183" t="n">
         <v>8.18</v>
@@ -14374,7 +14374,7 @@
         <v>-3.28</v>
       </c>
       <c r="I184" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J184" t="n">
         <v>8.18</v>
@@ -14449,7 +14449,7 @@
         <v>-6.79</v>
       </c>
       <c r="I185" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J185" t="n">
         <v>8.140000000000001</v>
@@ -14528,7 +14528,7 @@
         <v>2.28</v>
       </c>
       <c r="I186" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J186" t="n">
         <v>8.1</v>
@@ -14603,7 +14603,7 @@
         <v>3.71</v>
       </c>
       <c r="I187" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J187" t="n">
         <v>8.029999999999999</v>
@@ -14678,7 +14678,7 @@
         <v>-2</v>
       </c>
       <c r="I188" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J188" t="n">
         <v>7.96</v>
@@ -14753,7 +14753,7 @@
         <v>5.99</v>
       </c>
       <c r="I189" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J189" t="n">
         <v>7.87</v>
@@ -14828,7 +14828,7 @@
         <v>-2.2</v>
       </c>
       <c r="I190" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J190" t="n">
         <v>7.8</v>
@@ -14903,7 +14903,7 @@
         <v>-0.99</v>
       </c>
       <c r="I191" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J191" t="n">
         <v>7.71</v>
@@ -14978,7 +14978,7 @@
         <v>4.69</v>
       </c>
       <c r="I192" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J192" t="n">
         <v>7.58</v>
@@ -15053,7 +15053,7 @@
         <v>2.99</v>
       </c>
       <c r="I193" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J193" t="n">
         <v>7.53</v>
@@ -15128,7 +15128,7 @@
         <v>-3.56</v>
       </c>
       <c r="I194" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J194" t="n">
         <v>7.46</v>
@@ -15207,7 +15207,7 @@
         <v>7.66</v>
       </c>
       <c r="I195" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J195" t="n">
         <v>7.46</v>
@@ -15282,7 +15282,7 @@
         <v>2.41</v>
       </c>
       <c r="I196" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J196" t="n">
         <v>7.49</v>
@@ -15357,7 +15357,7 @@
         <v>1.49</v>
       </c>
       <c r="I197" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J197" t="n">
         <v>7.48</v>
@@ -15432,7 +15432,7 @@
         <v>3.67</v>
       </c>
       <c r="I198" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J198" t="n">
         <v>7.49</v>
@@ -15507,7 +15507,7 @@
         <v>-5.31</v>
       </c>
       <c r="I199" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J199" t="n">
         <v>7.47</v>
@@ -15582,7 +15582,7 @@
         <v>-7.35</v>
       </c>
       <c r="I200" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J200" t="n">
         <v>7.44</v>
@@ -15657,7 +15657,7 @@
         <v>0</v>
       </c>
       <c r="I201" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J201" t="n">
         <v>7.42</v>
@@ -15732,7 +15732,7 @@
         <v>-4.03</v>
       </c>
       <c r="I202" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J202" t="n">
         <v>7.39</v>
@@ -15811,7 +15811,7 @@
         <v>-2.94</v>
       </c>
       <c r="I203" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J203" t="n">
         <v>7.37</v>
@@ -15890,7 +15890,7 @@
         <v>4.91</v>
       </c>
       <c r="I204" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J204" t="n">
         <v>7.38</v>
@@ -15965,7 +15965,7 @@
         <v>4.13</v>
       </c>
       <c r="I205" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J205" t="n">
         <v>7.43</v>
@@ -16040,7 +16040,7 @@
         <v>1.45</v>
       </c>
       <c r="I206" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J206" t="n">
         <v>7.48</v>
@@ -16115,7 +16115,7 @@
         <v>3.26</v>
       </c>
       <c r="I207" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J207" t="n">
         <v>7.53</v>
@@ -16190,7 +16190,7 @@
         <v>5.8</v>
       </c>
       <c r="I208" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J208" t="n">
         <v>7.6</v>
@@ -16265,7 +16265,7 @@
         <v>3.93</v>
       </c>
       <c r="I209" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J209" t="n">
         <v>7.68</v>
@@ -16340,7 +16340,7 @@
         <v>9.06</v>
       </c>
       <c r="I210" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J210" t="n">
         <v>7.8</v>
@@ -16415,7 +16415,7 @@
         <v>-0.53</v>
       </c>
       <c r="I211" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J211" t="n">
         <v>7.92</v>
@@ -16490,7 +16490,7 @@
         <v>-4.02</v>
       </c>
       <c r="I212" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J212" t="n">
         <v>8</v>
@@ -16565,7 +16565,7 @@
         <v>14.76</v>
       </c>
       <c r="I213" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J213" t="n">
         <v>8.15</v>
@@ -16640,7 +16640,7 @@
         <v>7.87</v>
       </c>
       <c r="I214" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J214" t="n">
         <v>8.34</v>
@@ -16715,7 +16715,7 @@
         <v>8.19</v>
       </c>
       <c r="I215" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J215" t="n">
         <v>8.56</v>
@@ -16790,7 +16790,7 @@
         <v>-1.73</v>
       </c>
       <c r="I216" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J216" t="n">
         <v>8.75</v>
@@ -16865,7 +16865,7 @@
         <v>-1.17</v>
       </c>
       <c r="I217" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J217" t="n">
         <v>8.93</v>
@@ -16940,7 +16940,7 @@
         <v>6.01</v>
       </c>
       <c r="I218" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J218" t="n">
         <v>9.130000000000001</v>
@@ -17015,7 +17015,7 @@
         <v>0.48</v>
       </c>
       <c r="I219" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J219" t="n">
         <v>9.359999999999999</v>
@@ -17090,7 +17090,7 @@
         <v>-4.05</v>
       </c>
       <c r="I220" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J220" t="n">
         <v>9.59</v>
@@ -17165,7 +17165,7 @@
         <v>5.72</v>
       </c>
       <c r="I221" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J221" t="n">
         <v>9.859999999999999</v>
@@ -17240,7 +17240,7 @@
         <v>4</v>
       </c>
       <c r="I222" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J222" t="n">
         <v>10.17</v>
@@ -17315,7 +17315,7 @@
         <v>3.17</v>
       </c>
       <c r="I223" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J223" t="n">
         <v>10.5</v>
@@ -17390,7 +17390,7 @@
         <v>-3.51</v>
       </c>
       <c r="I224" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J224" t="n">
         <v>10.8</v>
@@ -17465,7 +17465,7 @@
         <v>12.57</v>
       </c>
       <c r="I225" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J225" t="n">
         <v>11.17</v>
@@ -17540,7 +17540,7 @@
         <v>1.01</v>
       </c>
       <c r="I226" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J226" t="n">
         <v>11.53</v>
@@ -17615,7 +17615,7 @@
         <v>4.99</v>
       </c>
       <c r="I227" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J227" t="n">
         <v>11.92</v>
@@ -17690,7 +17690,7 @@
         <v>-1.46</v>
       </c>
       <c r="I228" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J228" t="n">
         <v>12.28</v>
@@ -17765,7 +17765,7 @@
         <v>13.38</v>
       </c>
       <c r="I229" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J229" t="n">
         <v>12.73</v>
@@ -17840,7 +17840,7 @@
         <v>7.21</v>
       </c>
       <c r="I230" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J230" t="n">
         <v>13.2</v>
@@ -17915,7 +17915,7 @@
         <v>-2.7</v>
       </c>
       <c r="I231" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J231" t="n">
         <v>13.64</v>
@@ -17990,7 +17990,7 @@
         <v>-5.39</v>
       </c>
       <c r="I232" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J232" t="n">
         <v>14.06</v>
@@ -18065,7 +18065,7 @@
         <v>-3.16</v>
       </c>
       <c r="I233" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J233" t="n">
         <v>14.38</v>
@@ -18140,7 +18140,7 @@
         <v>7.78</v>
       </c>
       <c r="I234" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J234" t="n">
         <v>14.72</v>
@@ -18215,7 +18215,7 @@
         <v>-9.199999999999999</v>
       </c>
       <c r="I235" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J235" t="n">
         <v>14.94</v>
@@ -18290,7 +18290,7 @@
         <v>-0.61</v>
       </c>
       <c r="I236" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J236" t="n">
         <v>15.16</v>
@@ -18365,7 +18365,7 @@
         <v>10.87</v>
       </c>
       <c r="I237" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J237" t="n">
         <v>15.48</v>
@@ -18440,7 +18440,7 @@
         <v>3.36</v>
       </c>
       <c r="I238" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J238" t="n">
         <v>15.79</v>
@@ -18515,7 +18515,7 @@
         <v>-3.57</v>
       </c>
       <c r="I239" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J239" t="n">
         <v>16.07</v>
@@ -18590,7 +18590,7 @@
         <v>14.14</v>
       </c>
       <c r="I240" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J240" t="n">
         <v>16.5</v>
@@ -18665,7 +18665,7 @@
         <v>1.06</v>
       </c>
       <c r="I241" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J241" t="n">
         <v>16.9</v>
@@ -18740,7 +18740,7 @@
         <v>7.14</v>
       </c>
       <c r="I242" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J242" t="n">
         <v>17.36</v>
@@ -18815,7 +18815,7 @@
         <v>-6.79</v>
       </c>
       <c r="I243" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J243" t="n">
         <v>17.72</v>
@@ -18890,7 +18890,7 @@
         <v>4.46</v>
       </c>
       <c r="I244" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J244" t="n">
         <v>18.15</v>
@@ -18965,7 +18965,7 @@
         <v>5</v>
       </c>
       <c r="I245" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J245" t="n">
         <v>18.55</v>
@@ -19040,7 +19040,7 @@
         <v>14.65</v>
       </c>
       <c r="I246" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J246" t="n">
         <v>19.1</v>
@@ -19115,7 +19115,7 @@
         <v>-5.03</v>
       </c>
       <c r="I247" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J247" t="n">
         <v>19.56</v>
@@ -19190,7 +19190,7 @@
         <v>10.96</v>
       </c>
       <c r="I248" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J248" t="n">
         <v>20.17</v>
@@ -19265,7 +19265,7 @@
         <v>9.08</v>
       </c>
       <c r="I249" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J249" t="n">
         <v>20.79</v>
@@ -19340,7 +19340,7 @@
         <v>2.79</v>
       </c>
       <c r="I250" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J250" t="n">
         <v>21.4</v>
@@ -19415,7 +19415,7 @@
         <v>1.65</v>
       </c>
       <c r="I251" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J251" t="n">
         <v>22.05</v>
@@ -19490,7 +19490,7 @@
         <v>-7.15</v>
       </c>
       <c r="I252" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J252" t="n">
         <v>22.64</v>
@@ -19565,7 +19565,7 @@
         <v>-31.09</v>
       </c>
       <c r="I253" s="4" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J253" s="4" t="n">
         <v>22.81</v>
@@ -19644,7 +19644,7 @@
         <v>4.37</v>
       </c>
       <c r="I254" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J254" t="n">
         <v>22.95</v>
@@ -19719,7 +19719,7 @@
         <v>-18.45</v>
       </c>
       <c r="I255" s="4" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J255" s="4" t="n">
         <v>22.99</v>
@@ -19794,7 +19794,7 @@
         <v>1.52</v>
       </c>
       <c r="I256" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J256" t="n">
         <v>23.04</v>
@@ -19873,7 +19873,7 @@
         <v>15.68</v>
       </c>
       <c r="I257" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J257" t="n">
         <v>23.14</v>
@@ -19948,7 +19948,7 @@
         <v>-7.25</v>
       </c>
       <c r="I258" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J258" t="n">
         <v>23.13</v>
@@ -20023,7 +20023,7 @@
         <v>5.46</v>
       </c>
       <c r="I259" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J259" t="n">
         <v>23.21</v>
@@ -20098,7 +20098,7 @@
         <v>-20.25</v>
       </c>
       <c r="I260" s="4" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J260" s="4" t="n">
         <v>22.97</v>
@@ -20171,7 +20171,7 @@
         <v>0.64</v>
       </c>
       <c r="I261" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J261" t="n">
         <v>22.71</v>
@@ -20250,7 +20250,7 @@
         <v>21</v>
       </c>
       <c r="I262" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J262" t="n">
         <v>22.55</v>
@@ -20325,7 +20325,7 @@
         <v>3.4</v>
       </c>
       <c r="I263" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J263" t="n">
         <v>22.5</v>
@@ -20400,7 +20400,7 @@
         <v>-5.01</v>
       </c>
       <c r="I264" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J264" t="n">
         <v>22.35</v>
@@ -20475,7 +20475,7 @@
         <v>5.8</v>
       </c>
       <c r="I265" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J265" t="n">
         <v>22.2</v>
@@ -20550,7 +20550,7 @@
         <v>-19.32</v>
       </c>
       <c r="I266" s="4" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J266" s="4" t="n">
         <v>21.69</v>
@@ -20633,7 +20633,7 @@
         <v>17.71</v>
       </c>
       <c r="I267" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J267" t="n">
         <v>21.39</v>
@@ -20708,7 +20708,7 @@
         <v>-11.12</v>
       </c>
       <c r="I268" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J268" t="n">
         <v>20.85</v>
@@ -20787,7 +20787,7 @@
         <v>-2.38</v>
       </c>
       <c r="I269" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J269" t="n">
         <v>20.16</v>
@@ -20862,7 +20862,7 @@
         <v>-17.58</v>
       </c>
       <c r="I270" s="4" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J270" s="4" t="n">
         <v>19.28</v>
@@ -20937,7 +20937,7 @@
         <v>1.48</v>
       </c>
       <c r="I271" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J271" t="n">
         <v>18.39</v>
@@ -21016,7 +21016,7 @@
         <v>-11.24</v>
       </c>
       <c r="I272" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J272" t="n">
         <v>17.54</v>
@@ -21095,7 +21095,7 @@
         <v>16.86</v>
       </c>
       <c r="I273" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J273" t="n">
         <v>17.24</v>
@@ -21170,7 +21170,7 @@
         <v>7.67</v>
       </c>
       <c r="I274" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J274" t="n">
         <v>16.96</v>
@@ -21245,7 +21245,7 @@
         <v>-7.78</v>
       </c>
       <c r="I275" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J275" t="n">
         <v>16.8</v>
@@ -21320,7 +21320,7 @@
         <v>7.02</v>
       </c>
       <c r="I276" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J276" t="n">
         <v>16.69</v>
@@ -21395,7 +21395,7 @@
         <v>2.98</v>
       </c>
       <c r="I277" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J277" t="n">
         <v>16.46</v>
@@ -21474,7 +21474,7 @@
         <v>30.23</v>
       </c>
       <c r="I278" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J278" t="n">
         <v>16.54</v>
@@ -21549,7 +21549,7 @@
         <v>-1.38</v>
       </c>
       <c r="I279" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J279" t="n">
         <v>16.55</v>
@@ -21624,7 +21624,7 @@
         <v>-1.35</v>
       </c>
       <c r="I280" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J280" t="n">
         <v>16.75</v>
@@ -21699,7 +21699,7 @@
         <v>5.08</v>
       </c>
       <c r="I281" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J281" t="n">
         <v>17</v>
@@ -21774,7 +21774,7 @@
         <v>11.98</v>
       </c>
       <c r="I282" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J282" t="n">
         <v>17.2</v>
@@ -21849,7 +21849,7 @@
         <v>-3.84</v>
       </c>
       <c r="I283" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J283" t="n">
         <v>17.32</v>
@@ -21924,7 +21924,7 @@
         <v>5.2</v>
       </c>
       <c r="I284" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J284" t="n">
         <v>17.56</v>
@@ -21999,7 +21999,7 @@
         <v>9.98</v>
       </c>
       <c r="I285" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J285" t="n">
         <v>17.85</v>
@@ -22074,7 +22074,7 @@
         <v>-4.23</v>
       </c>
       <c r="I286" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J286" t="n">
         <v>18.28</v>
@@ -22149,7 +22149,7 @@
         <v>-6.52</v>
       </c>
       <c r="I287" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J287" t="n">
         <v>18.5</v>
@@ -22224,7 +22224,7 @@
         <v>17.54</v>
       </c>
       <c r="I288" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J288" t="n">
         <v>19.01</v>
@@ -22299,7 +22299,7 @@
         <v>-9.65</v>
       </c>
       <c r="I289" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J289" t="n">
         <v>19.42</v>
@@ -22374,7 +22374,7 @@
         <v>7.34</v>
       </c>
       <c r="I290" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J290" t="n">
         <v>20.06</v>
@@ -22449,7 +22449,7 @@
         <v>4.67</v>
       </c>
       <c r="I291" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J291" t="n">
         <v>20.75</v>
@@ -22524,7 +22524,7 @@
         <v>-4.57</v>
       </c>
       <c r="I292" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J292" t="n">
         <v>21.46</v>
@@ -22599,7 +22599,7 @@
         <v>-0.8</v>
       </c>
       <c r="I293" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J293" t="n">
         <v>22.05</v>
@@ -22674,7 +22674,7 @@
         <v>12.69</v>
       </c>
       <c r="I294" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J294" t="n">
         <v>22.76</v>
@@ -22749,7 +22749,7 @@
         <v>2.52</v>
       </c>
       <c r="I295" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J295" t="n">
         <v>23.56</v>
@@ -22824,7 +22824,7 @@
         <v>3.19</v>
       </c>
       <c r="I296" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J296" t="n">
         <v>24.36</v>
@@ -22899,7 +22899,7 @@
         <v>17.69</v>
       </c>
       <c r="I297" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J297" t="n">
         <v>25.41</v>
@@ -22974,7 +22974,7 @@
         <v>14.65</v>
       </c>
       <c r="I298" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J298" t="n">
         <v>26.5</v>
@@ -23049,7 +23049,7 @@
         <v>-8.41</v>
       </c>
       <c r="I299" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J299" t="n">
         <v>27.42</v>
@@ -23124,7 +23124,7 @@
         <v>22.62</v>
       </c>
       <c r="I300" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J300" t="n">
         <v>28.79</v>
@@ -23199,7 +23199,7 @@
         <v>4.33</v>
       </c>
       <c r="I301" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J301" t="n">
         <v>30.21</v>
@@ -23274,7 +23274,7 @@
         <v>-22.56</v>
       </c>
       <c r="I302" s="4" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J302" s="4" t="n">
         <v>30.96</v>
@@ -23349,7 +23349,7 @@
         <v>17.42</v>
       </c>
       <c r="I303" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J303" t="n">
         <v>32.08</v>
@@ -23424,7 +23424,7 @@
         <v>2.91</v>
       </c>
       <c r="I304" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J304" t="n">
         <v>33.2</v>
@@ -23499,7 +23499,7 @@
         <v>-18.31</v>
       </c>
       <c r="I305" s="4" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J305" s="4" t="n">
         <v>33.79</v>
@@ -23574,7 +23574,7 @@
         <v>-5</v>
       </c>
       <c r="I306" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J306" t="n">
         <v>34.34</v>
@@ -23649,7 +23649,7 @@
         <v>-3.36</v>
       </c>
       <c r="I307" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J307" t="n">
         <v>34.91</v>
@@ -23728,7 +23728,7 @@
         <v>10.26</v>
       </c>
       <c r="I308" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J308" t="n">
         <v>35.46</v>
@@ -23803,7 +23803,7 @@
         <v>10.31</v>
       </c>
       <c r="I309" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J309" t="n">
         <v>36.33</v>
@@ -23878,7 +23878,7 @@
         <v>-6.98</v>
       </c>
       <c r="I310" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J310" t="n">
         <v>36.96</v>
@@ -23953,7 +23953,7 @@
         <v>30.06</v>
       </c>
       <c r="I311" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J311" t="n">
         <v>38.12</v>
@@ -24028,7 +24028,7 @@
         <v>-3.57</v>
       </c>
       <c r="I312" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J312" t="n">
         <v>39.25</v>
@@ -24103,7 +24103,7 @@
         <v>12.4</v>
       </c>
       <c r="I313" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J313" t="n">
         <v>40.7</v>
@@ -24178,7 +24178,7 @@
         <v>-0.93</v>
       </c>
       <c r="I314" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J314" t="n">
         <v>41.96</v>
@@ -24253,7 +24253,7 @@
         <v>16.04</v>
       </c>
       <c r="I315" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J315" t="n">
         <v>43.61</v>
@@ -24328,7 +24328,7 @@
         <v>-3.16</v>
       </c>
       <c r="I316" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J316" t="n">
         <v>45.12</v>
@@ -24403,7 +24403,7 @@
         <v>-2.29</v>
       </c>
       <c r="I317" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J317" t="n">
         <v>46.28</v>
@@ -24478,7 +24478,7 @@
         <v>-12.28</v>
       </c>
       <c r="I318" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J318" t="n">
         <v>46.81</v>
@@ -24553,7 +24553,7 @@
         <v>-41.89</v>
       </c>
       <c r="I319" s="4" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J319" s="4" t="n">
         <v>46.41</v>
@@ -24632,7 +24632,7 @@
         <v>16.3</v>
       </c>
       <c r="I320" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J320" t="n">
         <v>45.83</v>
@@ -24707,7 +24707,7 @@
         <v>-2.45</v>
       </c>
       <c r="I321" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J321" t="n">
         <v>45.1</v>
@@ -24782,7 +24782,7 @@
         <v>-9.050000000000001</v>
       </c>
       <c r="I322" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J322" t="n">
         <v>44.77</v>
@@ -24857,7 +24857,7 @@
         <v>33.78</v>
       </c>
       <c r="I323" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J323" t="n">
         <v>44.64</v>
@@ -24932,7 +24932,7 @@
         <v>-2.04</v>
       </c>
       <c r="I324" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J324" t="n">
         <v>44.41</v>
@@ -25007,7 +25007,7 @@
         <v>21.14</v>
       </c>
       <c r="I325" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J325" t="n">
         <v>45.03</v>
@@ -25082,7 +25082,7 @@
         <v>-8.029999999999999</v>
       </c>
       <c r="I326" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J326" t="n">
         <v>45.54</v>
@@ -25157,7 +25157,7 @@
         <v>-0.5</v>
       </c>
       <c r="I327" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J327" t="n">
         <v>46.1</v>
@@ -25236,7 +25236,7 @@
         <v>19.29</v>
       </c>
       <c r="I328" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J328" t="n">
         <v>46.93</v>
@@ -25311,7 +25311,7 @@
         <v>-0.2</v>
       </c>
       <c r="I329" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J329" t="n">
         <v>47.55</v>
@@ -25386,7 +25386,7 @@
         <v>-35.7</v>
       </c>
       <c r="I330" s="4" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J330" s="4" t="n">
         <v>47.35</v>
@@ -25465,7 +25465,7 @@
         <v>5.89</v>
       </c>
       <c r="I331" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J331" t="n">
         <v>46.66</v>
@@ -25540,7 +25540,7 @@
         <v>11.85</v>
       </c>
       <c r="I332" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J332" t="n">
         <v>46.29</v>
@@ -25615,7 +25615,7 @@
         <v>-10.9</v>
       </c>
       <c r="I333" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J333" t="n">
         <v>45.39</v>
@@ -25690,7 +25690,7 @@
         <v>-0.03</v>
       </c>
       <c r="I334" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J334" t="n">
         <v>44.51</v>
@@ -25765,7 +25765,7 @@
         <v>5.82</v>
       </c>
       <c r="I335" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J335" t="n">
         <v>43.3</v>
@@ -25840,7 +25840,7 @@
         <v>-23.21</v>
       </c>
       <c r="I336" s="4" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J336" s="4" t="n">
         <v>41.74</v>
@@ -25919,7 +25919,7 @@
         <v>-9.77</v>
       </c>
       <c r="I337" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J337" t="n">
         <v>40.1</v>
@@ -25998,7 +25998,7 @@
         <v>15.37</v>
       </c>
       <c r="I338" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J338" t="n">
         <v>39.04</v>
@@ -26073,7 +26073,7 @@
         <v>-12.78</v>
       </c>
       <c r="I339" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J339" t="n">
         <v>38.87</v>
@@ -26152,7 +26152,7 @@
         <v>1.58</v>
       </c>
       <c r="I340" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J340" t="n">
         <v>38.48</v>
@@ -26227,7 +26227,7 @@
         <v>3</v>
       </c>
       <c r="I341" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J341" t="n">
         <v>38.18</v>
@@ -26302,7 +26302,7 @@
         <v>-2.28</v>
       </c>
       <c r="I342" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J342" t="n">
         <v>38</v>
@@ -26381,7 +26381,7 @@
         <v>-24.74</v>
       </c>
       <c r="I343" s="4" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J343" s="4" t="n">
         <v>36.94</v>
@@ -26456,7 +26456,7 @@
         <v>14.84</v>
       </c>
       <c r="I344" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J344" t="n">
         <v>36.08</v>
@@ -26531,7 +26531,7 @@
         <v>-9.140000000000001</v>
       </c>
       <c r="I345" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J345" t="n">
         <v>34.68</v>
@@ -26606,7 +26606,7 @@
         <v>-14.72</v>
       </c>
       <c r="I346" s="4" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J346" s="4" t="n">
         <v>33.31</v>
@@ -26685,7 +26685,7 @@
         <v>-2.09</v>
       </c>
       <c r="I347" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J347" t="n">
         <v>31.94</v>
@@ -26764,7 +26764,7 @@
         <v>0.82</v>
       </c>
       <c r="I348" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J348" t="n">
         <v>30.13</v>
@@ -26843,7 +26843,7 @@
         <v>18.03</v>
       </c>
       <c r="I349" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J349" t="n">
         <v>28.5</v>
@@ -26918,7 +26918,7 @@
         <v>-4.46</v>
       </c>
       <c r="I350" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J350" t="n">
         <v>27.79</v>
@@ -26993,7 +26993,7 @@
         <v>6.02</v>
       </c>
       <c r="I351" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J351" t="n">
         <v>27.03</v>
@@ -27068,7 +27068,7 @@
         <v>-18.9</v>
       </c>
       <c r="I352" s="4" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J352" s="4" t="n">
         <v>25.85</v>
@@ -27147,7 +27147,7 @@
         <v>-3.59</v>
       </c>
       <c r="I353" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J353" t="n">
         <v>24.87</v>
@@ -27222,7 +27222,7 @@
         <v>-17.78</v>
       </c>
       <c r="I354" s="4" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J354" s="4" t="n">
         <v>23.73</v>
@@ -27301,7 +27301,7 @@
         <v>-14.63</v>
       </c>
       <c r="I355" s="4" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J355" s="4" t="n">
         <v>22.38</v>
@@ -27380,7 +27380,7 @@
         <v>34.77</v>
       </c>
       <c r="I356" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J356" t="n">
         <v>21.69</v>
@@ -27455,7 +27455,7 @@
         <v>-7.92</v>
       </c>
       <c r="I357" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J357" t="n">
         <v>21.09</v>
@@ -27530,7 +27530,7 @@
         <v>5.87</v>
       </c>
       <c r="I358" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J358" t="n">
         <v>20.32</v>
@@ -27605,7 +27605,7 @@
         <v>20.48</v>
       </c>
       <c r="I359" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J359" t="n">
         <v>19.91</v>
@@ -27680,7 +27680,7 @@
         <v>-3.56</v>
       </c>
       <c r="I360" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J360" t="n">
         <v>19.45</v>
@@ -27755,7 +27755,7 @@
         <v>-8.84</v>
       </c>
       <c r="I361" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J361" t="n">
         <v>18.87</v>
@@ -27830,7 +27830,7 @@
         <v>3.27</v>
       </c>
       <c r="I362" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J362" t="n">
         <v>18.34</v>
@@ -27905,7 +27905,7 @@
         <v>-5.47</v>
       </c>
       <c r="I363" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J363" t="n">
         <v>18.12</v>
@@ -27980,7 +27980,7 @@
         <v>7.5</v>
       </c>
       <c r="I364" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J364" t="n">
         <v>17.8</v>
@@ -28055,7 +28055,7 @@
         <v>15.19</v>
       </c>
       <c r="I365" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J365" t="n">
         <v>17.72</v>
@@ -28130,7 +28130,7 @@
         <v>4.68</v>
       </c>
       <c r="I366" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J366" t="n">
         <v>17.85</v>
@@ -28205,7 +28205,7 @@
         <v>1.55</v>
       </c>
       <c r="I367" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J367" t="n">
         <v>18.02</v>
@@ -28280,7 +28280,7 @@
         <v>8.98</v>
       </c>
       <c r="I368" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J368" t="n">
         <v>18.27</v>
@@ -28355,7 +28355,7 @@
         <v>-24.21</v>
       </c>
       <c r="I369" s="4" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J369" s="4" t="n">
         <v>18.08</v>
@@ -28434,7 +28434,7 @@
         <v>7.12</v>
       </c>
       <c r="I370" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J370" t="n">
         <v>18</v>
@@ -28509,7 +28509,7 @@
         <v>6.38</v>
       </c>
       <c r="I371" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J371" t="n">
         <v>17.91</v>
@@ -28584,7 +28584,7 @@
         <v>0.15</v>
       </c>
       <c r="I372" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J372" t="n">
         <v>18.04</v>
@@ -28659,7 +28659,7 @@
         <v>-7.86</v>
       </c>
       <c r="I373" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J373" t="n">
         <v>18.11</v>
@@ -28734,7 +28734,7 @@
         <v>11.03</v>
       </c>
       <c r="I374" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J374" t="n">
         <v>18.45</v>
@@ -28809,7 +28809,7 @@
         <v>-1.63</v>
       </c>
       <c r="I375" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J375" t="n">
         <v>18.87</v>
@@ -28884,7 +28884,7 @@
         <v>4.49</v>
       </c>
       <c r="I376" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J376" t="n">
         <v>19.12</v>
@@ -28959,7 +28959,7 @@
         <v>-2.99</v>
       </c>
       <c r="I377" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J377" t="n">
         <v>19.41</v>
@@ -29034,7 +29034,7 @@
         <v>0.91</v>
       </c>
       <c r="I378" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J378" t="n">
         <v>19.67</v>
@@ -29109,7 +29109,7 @@
         <v>-8.49</v>
       </c>
       <c r="I379" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J379" t="n">
         <v>19.67</v>
@@ -29188,7 +29188,7 @@
         <v>5.06</v>
       </c>
       <c r="I380" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J380" t="n">
         <v>19.76</v>
@@ -29263,7 +29263,7 @@
         <v>2.68</v>
       </c>
       <c r="I381" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J381" t="n">
         <v>19.95</v>
@@ -29338,7 +29338,7 @@
         <v>13.44</v>
       </c>
       <c r="I382" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J382" t="n">
         <v>20.26</v>
@@ -29413,7 +29413,7 @@
         <v>1.58</v>
       </c>
       <c r="I383" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J383" t="n">
         <v>20.63</v>
@@ -29488,7 +29488,7 @@
         <v>1.51</v>
       </c>
       <c r="I384" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J384" t="n">
         <v>20.96</v>
@@ -29563,7 +29563,7 @@
         <v>-12.52</v>
       </c>
       <c r="I385" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J385" t="n">
         <v>21</v>
@@ -29638,7 +29638,7 @@
         <v>8.970000000000001</v>
       </c>
       <c r="I386" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J386" t="n">
         <v>21.09</v>
@@ -29713,7 +29713,7 @@
         <v>-19.51</v>
       </c>
       <c r="I387" s="4" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J387" s="4" t="n">
         <v>20.94</v>
@@ -29792,7 +29792,7 @@
         <v>0.16</v>
       </c>
       <c r="I388" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J388" t="n">
         <v>20.69</v>
@@ -29867,7 +29867,7 @@
         <v>-1.72</v>
       </c>
       <c r="I389" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J389" t="n">
         <v>20.71</v>
@@ -29942,7 +29942,7 @@
         <v>11.65</v>
       </c>
       <c r="I390" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J390" t="n">
         <v>20.78</v>
@@ -30017,7 +30017,7 @@
         <v>-1.81</v>
       </c>
       <c r="I391" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J391" t="n">
         <v>20.76</v>
@@ -30092,7 +30092,7 @@
         <v>12.52</v>
       </c>
       <c r="I392" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J392" t="n">
         <v>20.87</v>
@@ -30167,7 +30167,7 @@
         <v>5.41</v>
       </c>
       <c r="I393" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J393" t="n">
         <v>21.12</v>
@@ -30242,7 +30242,7 @@
         <v>-10.52</v>
       </c>
       <c r="I394" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J394" t="n">
         <v>21.14</v>
@@ -30317,7 +30317,7 @@
         <v>-5.31</v>
       </c>
       <c r="I395" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J395" t="n">
         <v>21.13</v>
@@ -30396,7 +30396,7 @@
         <v>7.2</v>
       </c>
       <c r="I396" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J396" t="n">
         <v>21.14</v>
@@ -30471,7 +30471,7 @@
         <v>-5.51</v>
       </c>
       <c r="I397" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J397" t="n">
         <v>21.12</v>
@@ -30550,7 +30550,7 @@
         <v>5.25</v>
       </c>
       <c r="I398" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J398" t="n">
         <v>21.14</v>
@@ -30625,7 +30625,7 @@
         <v>-6.75</v>
       </c>
       <c r="I399" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J399" t="n">
         <v>21.18</v>
@@ -30704,7 +30704,7 @@
         <v>5.34</v>
       </c>
       <c r="I400" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J400" t="n">
         <v>21.23</v>
@@ -30779,7 +30779,7 @@
         <v>8.82</v>
       </c>
       <c r="I401" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J401" t="n">
         <v>21.34</v>
@@ -30854,7 +30854,7 @@
         <v>-0.74</v>
       </c>
       <c r="I402" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J402" t="n">
         <v>21.31</v>
@@ -30929,7 +30929,7 @@
         <v>-7.77</v>
       </c>
       <c r="I403" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J403" t="n">
         <v>21.17</v>
@@ -31008,7 +31008,7 @@
         <v>-4.57</v>
       </c>
       <c r="I404" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J404" t="n">
         <v>20.96</v>
@@ -31083,7 +31083,7 @@
         <v>-11.97</v>
       </c>
       <c r="I405" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J405" t="n">
         <v>20.79</v>
@@ -31162,7 +31162,7 @@
         <v>1.13</v>
       </c>
       <c r="I406" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J406" t="n">
         <v>20.52</v>
@@ -31237,7 +31237,7 @@
         <v>-11.82</v>
       </c>
       <c r="I407" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J407" t="n">
         <v>20.38</v>
@@ -31316,7 +31316,7 @@
         <v>-6.48</v>
       </c>
       <c r="I408" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J408" t="n">
         <v>20.19</v>
@@ -31391,7 +31391,7 @@
         <v>-12.16</v>
       </c>
       <c r="I409" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J409" t="n">
         <v>19.92</v>
@@ -31466,7 +31466,7 @@
         <v>-7.12</v>
       </c>
       <c r="I410" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J410" t="n">
         <v>19.5</v>
@@ -31545,7 +31545,7 @@
         <v>-11.41</v>
       </c>
       <c r="I411" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J411" t="n">
         <v>19.03</v>
@@ -31624,7 +31624,7 @@
         <v>12.03</v>
       </c>
       <c r="I412" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J412" t="n">
         <v>18.5</v>
@@ -31703,7 +31703,7 @@
         <v>-4.87</v>
       </c>
       <c r="I413" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J413" t="n">
         <v>17.88</v>
@@ -31782,7 +31782,7 @@
         <v>5.29</v>
       </c>
       <c r="I414" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="J414" t="n">
         <v>17.41</v>
@@ -31832,61 +31832,81 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>KORU</t>
-        </is>
-      </c>
-      <c r="B415" t="inlineStr">
+      <c r="A415" s="4" t="inlineStr">
+        <is>
+          <t>KORU</t>
+        </is>
+      </c>
+      <c r="B415" s="4" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
-      <c r="D415" t="inlineStr"/>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
-      <c r="G415" t="n">
-        <v>47405013</v>
-      </c>
-      <c r="H415" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I415" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr"/>
-      <c r="L415" t="inlineStr"/>
-      <c r="M415" t="inlineStr"/>
-      <c r="N415" s="3" t="n">
-        <v>13.71</v>
-      </c>
-      <c r="O415" t="n">
+      <c r="C415" s="4" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="D415" s="4" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="E415" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F415" s="4" t="n">
+        <v>10.19</v>
+      </c>
+      <c r="G415" s="4" t="n">
+        <v>47417200</v>
+      </c>
+      <c r="H415" s="5" t="n">
+        <v>-14.66</v>
+      </c>
+      <c r="I415" s="4" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="J415" s="4" t="n">
+        <v>16.91</v>
+      </c>
+      <c r="K415" s="4" t="n">
+        <v>18.97</v>
+      </c>
+      <c r="L415" s="4" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="M415" s="4" t="n">
+        <v>24.45</v>
+      </c>
+      <c r="N415" s="7" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="O415" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="P415" t="inlineStr">
+      <c r="P415" s="4" t="inlineStr">
         <is>
           <t>extreme fear</t>
         </is>
       </c>
-      <c r="Q415" t="inlineStr">
+      <c r="Q415" s="4" t="inlineStr">
         <is>
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R415" t="inlineStr"/>
-      <c r="S415" t="n">
+      <c r="R415" s="4" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S415" s="4" t="n">
         <v>4.95</v>
       </c>
-      <c r="T415" s="2" t="n">
+      <c r="T415" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="U415" s="2" t="n">
+      <c r="U415" s="6" t="n">
         <v>15.2</v>
       </c>
-      <c r="V415" t="inlineStr"/>
-      <c r="W415" s="2" t="n">
+      <c r="V415" s="4" t="inlineStr"/>
+      <c r="W415" s="6" t="n">
         <v>152.4</v>
       </c>
     </row>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31879,7 +31879,7 @@
         <v>12.29</v>
       </c>
       <c r="O415" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W415"/>
+  <dimension ref="A1:W416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31879,7 +31879,7 @@
         <v>12.29</v>
       </c>
       <c r="O415" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P415" s="4" t="inlineStr">
         <is>
@@ -31909,6 +31909,83 @@
       <c r="W415" s="6" t="n">
         <v>152.4</v>
       </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>KORU</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="D416" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="E416" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="F416" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="G416" t="n">
+        <v>23114025</v>
+      </c>
+      <c r="H416" s="3" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="I416" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="J416" t="n">
+        <v>16.37</v>
+      </c>
+      <c r="K416" t="n">
+        <v>18.88</v>
+      </c>
+      <c r="L416" t="n">
+        <v>27.53</v>
+      </c>
+      <c r="M416" t="n">
+        <v>24.44</v>
+      </c>
+      <c r="N416" s="3" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="O416" t="n">
+        <v>20</v>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>extreme fear</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R416" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S416" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="T416" s="2" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="U416" s="2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="V416" t="inlineStr"/>
+      <c r="W416" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31855,7 +31855,7 @@
         <v>10.19</v>
       </c>
       <c r="G415" s="4" t="n">
-        <v>47417200</v>
+        <v>49195200</v>
       </c>
       <c r="H415" s="5" t="n">
         <v>-14.66</v>
@@ -31931,19 +31931,19 @@
         <v>10.29</v>
       </c>
       <c r="F416" t="n">
-        <v>10.64</v>
+        <v>10.58</v>
       </c>
       <c r="G416" t="n">
-        <v>23114025</v>
+        <v>26121412</v>
       </c>
       <c r="H416" s="3" t="n">
-        <v>4.42</v>
+        <v>3.83</v>
       </c>
       <c r="I416" t="n">
         <v>13.6</v>
       </c>
       <c r="J416" t="n">
-        <v>16.37</v>
+        <v>16.36</v>
       </c>
       <c r="K416" t="n">
         <v>18.88</v>
@@ -31955,10 +31955,10 @@
         <v>24.44</v>
       </c>
       <c r="N416" s="3" t="n">
-        <v>14.71</v>
+        <v>14.41</v>
       </c>
       <c r="O416" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P416" t="inlineStr">
         <is>
@@ -31976,16 +31976,18 @@
         </is>
       </c>
       <c r="S416" t="n">
-        <v>4.98</v>
+        <v>4.99</v>
       </c>
       <c r="T416" s="2" t="n">
-        <v>20.1</v>
+        <v>19.5</v>
       </c>
       <c r="U416" s="2" t="n">
-        <v>15.5</v>
+        <v>16.8</v>
       </c>
       <c r="V416" t="inlineStr"/>
-      <c r="W416" s="2" t="inlineStr"/>
+      <c r="W416" s="2" t="n">
+        <v>151.8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31846,25 +31846,41 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
-      <c r="D415" t="inlineStr"/>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
+      <c r="C415" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="D415" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="E415" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="F415" t="n">
+        <v>10.58</v>
+      </c>
       <c r="G415" t="n">
-        <v>26121412</v>
-      </c>
-      <c r="H415" s="2" t="n">
-        <v>0</v>
+        <v>26249500</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>3.83</v>
       </c>
       <c r="I415" t="n">
         <v>13.6</v>
       </c>
-      <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr"/>
-      <c r="L415" t="inlineStr"/>
-      <c r="M415" t="inlineStr"/>
+      <c r="J415" t="n">
+        <v>16.36</v>
+      </c>
+      <c r="K415" t="n">
+        <v>18.88</v>
+      </c>
+      <c r="L415" t="n">
+        <v>27.53</v>
+      </c>
+      <c r="M415" t="n">
+        <v>24.44</v>
+      </c>
       <c r="N415" s="1" t="n">
-        <v>12.42</v>
+        <v>14.41</v>
       </c>
       <c r="O415" t="n">
         <v>21</v>
@@ -31879,7 +31895,11 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R415" t="inlineStr"/>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
       <c r="S415" t="n">
         <v>4.99</v>
       </c>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6690,7 +6690,7 @@
         <v>3.48</v>
       </c>
       <c r="K82" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="L82" t="n">
         <v>2.33</v>
@@ -6912,7 +6912,7 @@
         <v>13.6</v>
       </c>
       <c r="J85" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="K85" t="n">
         <v>2.67</v>
@@ -18668,7 +18668,7 @@
         <v>13.6</v>
       </c>
       <c r="J241" t="n">
-        <v>18.15</v>
+        <v>18.14</v>
       </c>
       <c r="K241" t="n">
         <v>12.11</v>
@@ -18743,7 +18743,7 @@
         <v>13.6</v>
       </c>
       <c r="J242" t="n">
-        <v>18.55</v>
+        <v>18.54</v>
       </c>
       <c r="K242" t="n">
         <v>12.38</v>
@@ -25243,7 +25243,7 @@
         <v>13.6</v>
       </c>
       <c r="J328" t="n">
-        <v>46.66</v>
+        <v>46.67</v>
       </c>
       <c r="K328" t="n">
         <v>35.18</v>
@@ -27758,7 +27758,7 @@
         <v>13.6</v>
       </c>
       <c r="J361" t="n">
-        <v>17.8</v>
+        <v>17.79</v>
       </c>
       <c r="K361" t="n">
         <v>32.76</v>
@@ -28212,7 +28212,7 @@
         <v>13.6</v>
       </c>
       <c r="J367" t="n">
-        <v>18</v>
+        <v>17.99</v>
       </c>
       <c r="K367" t="n">
         <v>31.04</v>
@@ -31733,7 +31733,7 @@
         <v>14.41</v>
       </c>
       <c r="O413" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31763,6 +31763,83 @@
       <c r="W413" s="2" t="n">
         <v>151.8</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>KORU</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="D414" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E414" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="F414" t="n">
+        <v>10.93</v>
+      </c>
+      <c r="G414" t="n">
+        <v>23434167</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="I414" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="J414" t="n">
+        <v>15.89</v>
+      </c>
+      <c r="K414" t="n">
+        <v>18.81</v>
+      </c>
+      <c r="L414" t="n">
+        <v>27.32</v>
+      </c>
+      <c r="M414" t="n">
+        <v>24.44</v>
+      </c>
+      <c r="N414" s="3" t="n">
+        <v>17.94</v>
+      </c>
+      <c r="O414" t="n">
+        <v>27</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S414" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31779,19 +31779,19 @@
         <v>10.55</v>
       </c>
       <c r="D414" t="n">
-        <v>11.1</v>
+        <v>11.19</v>
       </c>
       <c r="E414" t="n">
         <v>10.35</v>
       </c>
       <c r="F414" t="n">
-        <v>10.93</v>
+        <v>10.89</v>
       </c>
       <c r="G414" t="n">
-        <v>23434167</v>
+        <v>30575952</v>
       </c>
       <c r="H414" s="3" t="n">
-        <v>3.31</v>
+        <v>2.93</v>
       </c>
       <c r="I414" t="n">
         <v>13.6</v>
@@ -31803,13 +31803,13 @@
         <v>18.81</v>
       </c>
       <c r="L414" t="n">
-        <v>27.32</v>
+        <v>27.31</v>
       </c>
       <c r="M414" t="n">
         <v>24.44</v>
       </c>
       <c r="N414" s="3" t="n">
-        <v>17.94</v>
+        <v>17.73</v>
       </c>
       <c r="O414" t="n">
         <v>27</v>
@@ -31830,16 +31830,18 @@
         </is>
       </c>
       <c r="S414" t="n">
-        <v>4.97</v>
+        <v>4.99</v>
       </c>
       <c r="T414" s="2" t="n">
         <v>18.4</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>9.1</v>
+        <v>10.5</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="n">
+        <v>151</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31630,7 +31630,7 @@
         <v>10.58</v>
       </c>
       <c r="G412" t="n">
-        <v>26249500</v>
+        <v>26648700</v>
       </c>
       <c r="H412" s="1" t="n">
         <v>3.83</v>
@@ -31696,28 +31696,44 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="C413" t="inlineStr"/>
-      <c r="D413" t="inlineStr"/>
-      <c r="E413" t="inlineStr"/>
-      <c r="F413" t="inlineStr"/>
+      <c r="C413" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="D413" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="E413" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="F413" t="n">
+        <v>10.89</v>
+      </c>
       <c r="G413" t="n">
-        <v>30575952</v>
-      </c>
-      <c r="H413" s="2" t="n">
-        <v>0</v>
+        <v>30940500</v>
+      </c>
+      <c r="H413" s="1" t="n">
+        <v>2.93</v>
       </c>
       <c r="I413" t="n">
         <v>13.6</v>
       </c>
-      <c r="J413" t="inlineStr"/>
-      <c r="K413" t="inlineStr"/>
-      <c r="L413" t="inlineStr"/>
-      <c r="M413" t="inlineStr"/>
+      <c r="J413" t="n">
+        <v>15.89</v>
+      </c>
+      <c r="K413" t="n">
+        <v>18.81</v>
+      </c>
+      <c r="L413" t="n">
+        <v>27.31</v>
+      </c>
+      <c r="M413" t="n">
+        <v>24.44</v>
+      </c>
       <c r="N413" s="1" t="n">
-        <v>16.07</v>
+        <v>17.73</v>
       </c>
       <c r="O413" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31729,7 +31745,11 @@
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R413" t="inlineStr"/>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
       <c r="S413" t="n">
         <v>4.99</v>
       </c>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31733,7 +31733,7 @@
         <v>17.73</v>
       </c>
       <c r="O413" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31763,6 +31763,83 @@
       <c r="W413" s="2" t="n">
         <v>151</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>KORU</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>11.52</v>
+      </c>
+      <c r="D414" t="n">
+        <v>11.64</v>
+      </c>
+      <c r="E414" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="F414" t="n">
+        <v>11.37</v>
+      </c>
+      <c r="G414" t="n">
+        <v>17800910</v>
+      </c>
+      <c r="H414" s="1" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="I414" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="J414" t="n">
+        <v>15.38</v>
+      </c>
+      <c r="K414" t="n">
+        <v>18.73</v>
+      </c>
+      <c r="L414" t="n">
+        <v>27.06</v>
+      </c>
+      <c r="M414" t="n">
+        <v>24.43</v>
+      </c>
+      <c r="N414" s="1" t="n">
+        <v>21.45</v>
+      </c>
+      <c r="O414" t="n">
+        <v>32</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>4th: MA200, RSI≤30, 100% cash, 40d</t>
+        </is>
+      </c>
+      <c r="S414" t="n">
+        <v>5</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31709,7 +31709,7 @@
         <v>10.89</v>
       </c>
       <c r="G413" t="n">
-        <v>30940500</v>
+        <v>32291300</v>
       </c>
       <c r="H413" s="1" t="n">
         <v>2.93</v>
@@ -31779,28 +31779,28 @@
         <v>11.52</v>
       </c>
       <c r="D414" t="n">
-        <v>11.64</v>
+        <v>12.03</v>
       </c>
       <c r="E414" t="n">
         <v>11.29</v>
       </c>
       <c r="F414" t="n">
-        <v>11.37</v>
+        <v>11.84</v>
       </c>
       <c r="G414" t="n">
-        <v>17800910</v>
+        <v>34389058</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>4.41</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="I414" t="n">
         <v>13.6</v>
       </c>
       <c r="J414" t="n">
-        <v>15.38</v>
+        <v>15.41</v>
       </c>
       <c r="K414" t="n">
-        <v>18.73</v>
+        <v>18.74</v>
       </c>
       <c r="L414" t="n">
         <v>27.06</v>
@@ -31809,10 +31809,10 @@
         <v>24.43</v>
       </c>
       <c r="N414" s="1" t="n">
-        <v>21.45</v>
+        <v>23.8</v>
       </c>
       <c r="O414" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31830,13 +31830,13 @@
         </is>
       </c>
       <c r="S414" t="n">
-        <v>5</v>
+        <v>4.99</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>8.699999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="V414" t="inlineStr"/>
       <c r="W414" s="2" t="inlineStr"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -29427,7 +29427,7 @@
         <v>49.53</v>
       </c>
       <c r="O383" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P383" s="4" t="inlineStr">
         <is>
@@ -29506,7 +29506,7 @@
         <v>43.92</v>
       </c>
       <c r="O384" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P384" t="inlineStr">
         <is>
@@ -29656,7 +29656,7 @@
         <v>47.44</v>
       </c>
       <c r="O386" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P386" t="inlineStr">
         <is>
@@ -29731,7 +29731,7 @@
         <v>48.11</v>
       </c>
       <c r="O387" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="P387" t="inlineStr">
         <is>
@@ -29956,7 +29956,7 @@
         <v>52.48</v>
       </c>
       <c r="O390" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P390" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>48.81</v>
       </c>
       <c r="O391" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P391" t="inlineStr">
         <is>
@@ -30185,7 +30185,7 @@
         <v>42.4</v>
       </c>
       <c r="O393" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P393" t="inlineStr">
         <is>
@@ -30264,7 +30264,7 @@
         <v>44.15</v>
       </c>
       <c r="O394" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="P394" t="inlineStr">
         <is>
@@ -30493,7 +30493,7 @@
         <v>61.97</v>
       </c>
       <c r="O397" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="P397" t="inlineStr">
         <is>
@@ -30568,7 +30568,7 @@
         <v>61.33</v>
       </c>
       <c r="O398" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P398" t="inlineStr">
         <is>
@@ -30722,7 +30722,7 @@
         <v>49.04</v>
       </c>
       <c r="O400" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P400" t="inlineStr">
         <is>
@@ -30797,7 +30797,7 @@
         <v>44.24</v>
       </c>
       <c r="O401" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P401" t="inlineStr">
         <is>
@@ -30876,11 +30876,11 @@
         <v>37.26</v>
       </c>
       <c r="O402" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="P402" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>fear</t>
         </is>
       </c>
       <c r="Q402" t="inlineStr">
@@ -30951,7 +30951,7 @@
         <v>29.23</v>
       </c>
       <c r="O403" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P403" t="inlineStr">
         <is>
@@ -31030,11 +31030,11 @@
         <v>31.65</v>
       </c>
       <c r="O404" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="P404" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="Q404" t="inlineStr">
@@ -31105,7 +31105,7 @@
         <v>30.52</v>
       </c>
       <c r="O405" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P405" t="inlineStr">
         <is>
@@ -31180,7 +31180,7 @@
         <v>23.36</v>
       </c>
       <c r="O406" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P406" t="inlineStr">
         <is>
@@ -31259,7 +31259,7 @@
         <v>23.13</v>
       </c>
       <c r="O407" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="P407" t="inlineStr">
         <is>
@@ -31338,7 +31338,7 @@
         <v>24.01</v>
       </c>
       <c r="O408" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P408" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>25.2</v>
       </c>
       <c r="O409" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P409" t="inlineStr">
         <is>
@@ -31496,7 +31496,7 @@
         <v>23.14</v>
       </c>
       <c r="O410" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="P410" t="inlineStr">
         <is>
@@ -31575,7 +31575,7 @@
         <v>12.29</v>
       </c>
       <c r="O411" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P411" s="4" t="inlineStr">
         <is>
@@ -31654,7 +31654,7 @@
         <v>14.41</v>
       </c>
       <c r="O412" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -31733,7 +31733,7 @@
         <v>17.73</v>
       </c>
       <c r="O413" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31785,13 +31785,13 @@
         <v>11.29</v>
       </c>
       <c r="F414" t="n">
-        <v>11.84</v>
+        <v>11.86</v>
       </c>
       <c r="G414" t="n">
-        <v>34389058</v>
+        <v>39563733</v>
       </c>
       <c r="H414" s="1" t="n">
-        <v>8.720000000000001</v>
+        <v>8.91</v>
       </c>
       <c r="I414" t="n">
         <v>13.6</v>
@@ -31809,10 +31809,10 @@
         <v>24.43</v>
       </c>
       <c r="N414" s="1" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="O414" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31839,7 +31839,9 @@
         <v>12.5</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="n">
+        <v>149.2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W413"/>
+  <dimension ref="A1:W414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31737,7 +31737,7 @@
         <v>23.9</v>
       </c>
       <c r="O413" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P413" t="inlineStr">
         <is>
@@ -31767,6 +31767,79 @@
       <c r="W413" s="2" t="n">
         <v>149.2</v>
       </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>KORU</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>13.21</v>
+      </c>
+      <c r="D414" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="E414" t="n">
+        <v>13.06</v>
+      </c>
+      <c r="F414" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="G414" t="n">
+        <v>29213426</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="I414" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="J414" t="n">
+        <v>15.08</v>
+      </c>
+      <c r="K414" t="n">
+        <v>18.65</v>
+      </c>
+      <c r="L414" t="n">
+        <v>26.86</v>
+      </c>
+      <c r="M414" t="n">
+        <v>24.44</v>
+      </c>
+      <c r="N414" s="2" t="n">
+        <v>36.36</v>
+      </c>
+      <c r="O414" t="n">
+        <v>35</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="T414" s="2" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="U414" s="2" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -6536,7 +6536,7 @@
         <v>3.48</v>
       </c>
       <c r="K80" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="L80" t="n">
         <v>2.33</v>
@@ -6758,7 +6758,7 @@
         <v>13.6</v>
       </c>
       <c r="J83" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="K83" t="n">
         <v>2.67</v>
@@ -18514,7 +18514,7 @@
         <v>13.6</v>
       </c>
       <c r="J239" t="n">
-        <v>18.14</v>
+        <v>18.15</v>
       </c>
       <c r="K239" t="n">
         <v>12.11</v>
@@ -18589,7 +18589,7 @@
         <v>13.6</v>
       </c>
       <c r="J240" t="n">
-        <v>18.54</v>
+        <v>18.55</v>
       </c>
       <c r="K240" t="n">
         <v>12.38</v>
@@ -25089,7 +25089,7 @@
         <v>13.6</v>
       </c>
       <c r="J326" t="n">
-        <v>46.67</v>
+        <v>46.66</v>
       </c>
       <c r="K326" t="n">
         <v>35.18</v>
@@ -27604,7 +27604,7 @@
         <v>13.6</v>
       </c>
       <c r="J359" t="n">
-        <v>17.79</v>
+        <v>17.8</v>
       </c>
       <c r="K359" t="n">
         <v>32.76</v>
@@ -28058,7 +28058,7 @@
         <v>13.6</v>
       </c>
       <c r="J365" t="n">
-        <v>17.99</v>
+        <v>18</v>
       </c>
       <c r="K365" t="n">
         <v>31.04</v>
@@ -31096,7 +31096,7 @@
         <v>19.42</v>
       </c>
       <c r="L405" t="n">
-        <v>28.4</v>
+        <v>28.39</v>
       </c>
       <c r="M405" t="n">
         <v>24.43</v>
@@ -31713,7 +31713,7 @@
         <v>11.86</v>
       </c>
       <c r="G413" t="n">
-        <v>39953900</v>
+        <v>42454900</v>
       </c>
       <c r="H413" s="3" t="n">
         <v>8.91</v>
@@ -31783,25 +31783,25 @@
         <v>13.21</v>
       </c>
       <c r="D414" t="n">
-        <v>13.64</v>
+        <v>13.89</v>
       </c>
       <c r="E414" t="n">
         <v>13.06</v>
       </c>
       <c r="F414" t="n">
-        <v>13.56</v>
+        <v>13.78</v>
       </c>
       <c r="G414" t="n">
-        <v>29213426</v>
+        <v>46148537</v>
       </c>
       <c r="H414" s="3" t="n">
-        <v>14.33</v>
+        <v>16.19</v>
       </c>
       <c r="I414" t="n">
         <v>13.6</v>
       </c>
       <c r="J414" t="n">
-        <v>15.08</v>
+        <v>15.1</v>
       </c>
       <c r="K414" t="n">
         <v>18.65</v>
@@ -31813,10 +31813,10 @@
         <v>24.44</v>
       </c>
       <c r="N414" s="2" t="n">
-        <v>36.36</v>
+        <v>37.28</v>
       </c>
       <c r="O414" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31830,16 +31830,18 @@
       </c>
       <c r="R414" t="inlineStr"/>
       <c r="S414" t="n">
-        <v>5.02</v>
+        <v>5.05</v>
       </c>
       <c r="T414" s="2" t="n">
-        <v>17.3</v>
+        <v>16.9</v>
       </c>
       <c r="U414" s="2" t="n">
-        <v>14.4</v>
+        <v>13.1</v>
       </c>
       <c r="V414" t="inlineStr"/>
-      <c r="W414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="n">
+        <v>148.7</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31792,7 +31792,7 @@
         <v>13.78</v>
       </c>
       <c r="G414" t="n">
-        <v>46148537</v>
+        <v>45833200</v>
       </c>
       <c r="H414" s="3" t="n">
         <v>16.19</v>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W414"/>
+  <dimension ref="A1:W415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -31816,7 +31816,7 @@
         <v>37.28</v>
       </c>
       <c r="O414" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="P414" t="inlineStr">
         <is>
@@ -31842,6 +31842,79 @@
       <c r="W414" s="2" t="n">
         <v>148.7</v>
       </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>KORU</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="D415" t="n">
+        <v>12.94</v>
+      </c>
+      <c r="E415" t="n">
+        <v>12.21</v>
+      </c>
+      <c r="F415" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="G415" t="n">
+        <v>24505998</v>
+      </c>
+      <c r="H415" s="1" t="n">
+        <v>-8.56</v>
+      </c>
+      <c r="I415" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="J415" t="n">
+        <v>14.67</v>
+      </c>
+      <c r="K415" t="n">
+        <v>18.55</v>
+      </c>
+      <c r="L415" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="M415" t="n">
+        <v>24.44</v>
+      </c>
+      <c r="N415" s="2" t="n">
+        <v>33.79</v>
+      </c>
+      <c r="O415" t="n">
+        <v>35</v>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="n">
+        <v>5</v>
+      </c>
+      <c r="T415" s="2" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="U415" s="2" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31792,7 +31792,7 @@
         <v>13.78</v>
       </c>
       <c r="G414" t="n">
-        <v>45833200</v>
+        <v>47800100</v>
       </c>
       <c r="H414" s="3" t="n">
         <v>16.19</v>
@@ -31864,22 +31864,22 @@
         <v>12.21</v>
       </c>
       <c r="F415" t="n">
-        <v>12.6</v>
+        <v>12.73</v>
       </c>
       <c r="G415" t="n">
-        <v>24505998</v>
+        <v>34191951</v>
       </c>
       <c r="H415" s="1" t="n">
-        <v>-8.56</v>
+        <v>-7.62</v>
       </c>
       <c r="I415" t="n">
         <v>13.6</v>
       </c>
       <c r="J415" t="n">
-        <v>14.67</v>
+        <v>14.68</v>
       </c>
       <c r="K415" t="n">
-        <v>18.55</v>
+        <v>18.56</v>
       </c>
       <c r="L415" t="n">
         <v>26.57</v>
@@ -31888,7 +31888,7 @@
         <v>24.44</v>
       </c>
       <c r="N415" s="2" t="n">
-        <v>33.79</v>
+        <v>34.06</v>
       </c>
       <c r="O415" t="n">
         <v>35</v>
@@ -31905,16 +31905,18 @@
       </c>
       <c r="R415" t="inlineStr"/>
       <c r="S415" t="n">
-        <v>5</v>
+        <v>4.99</v>
       </c>
       <c r="T415" s="2" t="n">
-        <v>16.3</v>
+        <v>17.2</v>
       </c>
       <c r="U415" s="2" t="n">
-        <v>10.2</v>
+        <v>13.6</v>
       </c>
       <c r="V415" t="inlineStr"/>
-      <c r="W415" s="2" t="inlineStr"/>
+      <c r="W415" s="2" t="n">
+        <v>151</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31867,7 +31867,7 @@
         <v>12.73</v>
       </c>
       <c r="G415" t="n">
-        <v>34191951</v>
+        <v>37256500</v>
       </c>
       <c r="H415" s="1" t="n">
         <v>-7.62</v>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31891,7 +31891,7 @@
         <v>34.06</v>
       </c>
       <c r="O415" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W415"/>
+  <dimension ref="A1:W416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -608,7 +608,7 @@
         <v>-8.529999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J2" t="n">
         <v>2.2</v>
@@ -691,7 +691,7 @@
         <v>3.11</v>
       </c>
       <c r="I3" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J3" t="n">
         <v>2.19</v>
@@ -770,7 +770,7 @@
         <v>7.04</v>
       </c>
       <c r="I4" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J4" t="n">
         <v>2.19</v>
@@ -845,7 +845,7 @@
         <v>-3.76</v>
       </c>
       <c r="I5" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J5" t="n">
         <v>2.19</v>
@@ -924,7 +924,7 @@
         <v>4.88</v>
       </c>
       <c r="I6" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J6" t="n">
         <v>2.19</v>
@@ -999,7 +999,7 @@
         <v>8.84</v>
       </c>
       <c r="I7" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J7" t="n">
         <v>2.19</v>
@@ -1074,7 +1074,7 @@
         <v>-4.7</v>
       </c>
       <c r="I8" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J8" t="n">
         <v>2.18</v>
@@ -1149,7 +1149,7 @@
         <v>1.35</v>
       </c>
       <c r="I9" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J9" t="n">
         <v>2.17</v>
@@ -1224,7 +1224,7 @@
         <v>-2.65</v>
       </c>
       <c r="I10" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J10" t="n">
         <v>2.16</v>
@@ -1299,7 +1299,7 @@
         <v>0.91</v>
       </c>
       <c r="I11" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J11" t="n">
         <v>2.15</v>
@@ -1374,7 +1374,7 @@
         <v>2.25</v>
       </c>
       <c r="I12" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J12" t="n">
         <v>2.15</v>
@@ -1449,7 +1449,7 @@
         <v>-1.32</v>
       </c>
       <c r="I13" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J13" t="n">
         <v>2.14</v>
@@ -1524,7 +1524,7 @@
         <v>-1.34</v>
       </c>
       <c r="I14" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J14" t="n">
         <v>2.13</v>
@@ -1599,7 +1599,7 @@
         <v>-1.81</v>
       </c>
       <c r="I15" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J15" t="n">
         <v>2.13</v>
@@ -1674,7 +1674,7 @@
         <v>-9.220000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J16" t="n">
         <v>2.13</v>
@@ -1753,7 +1753,7 @@
         <v>-4.06</v>
       </c>
       <c r="I17" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J17" t="n">
         <v>2.13</v>
@@ -1828,7 +1828,7 @@
         <v>4.76</v>
       </c>
       <c r="I18" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J18" t="n">
         <v>2.13</v>
@@ -1903,7 +1903,7 @@
         <v>-1.01</v>
       </c>
       <c r="I19" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J19" t="n">
         <v>2.12</v>
@@ -1978,7 +1978,7 @@
         <v>-8.67</v>
       </c>
       <c r="I20" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J20" t="n">
         <v>2.1</v>
@@ -2057,7 +2057,7 @@
         <v>-10.61</v>
       </c>
       <c r="I21" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J21" t="n">
         <v>2.08</v>
@@ -2140,7 +2140,7 @@
         <v>-3.12</v>
       </c>
       <c r="I22" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J22" t="n">
         <v>2.06</v>
@@ -2223,7 +2223,7 @@
         <v>-10.32</v>
       </c>
       <c r="I23" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J23" t="n">
         <v>2.03</v>
@@ -2306,7 +2306,7 @@
         <v>24.46</v>
       </c>
       <c r="I24" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J24" t="n">
         <v>2.01</v>
@@ -2385,7 +2385,7 @@
         <v>-6.94</v>
       </c>
       <c r="I25" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J25" t="n">
         <v>1.99</v>
@@ -2464,7 +2464,7 @@
         <v>14.29</v>
       </c>
       <c r="I26" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J26" t="n">
         <v>1.97</v>
@@ -2543,7 +2543,7 @@
         <v>-0.54</v>
       </c>
       <c r="I27" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J27" t="n">
         <v>1.95</v>
@@ -2618,7 +2618,7 @@
         <v>0.55</v>
       </c>
       <c r="I28" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J28" t="n">
         <v>1.93</v>
@@ -2693,7 +2693,7 @@
         <v>-2.17</v>
       </c>
       <c r="I29" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J29" t="n">
         <v>1.9</v>
@@ -2772,7 +2772,7 @@
         <v>1.67</v>
       </c>
       <c r="I30" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J30" t="n">
         <v>1.89</v>
@@ -2851,7 +2851,7 @@
         <v>0.55</v>
       </c>
       <c r="I31" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J31" t="n">
         <v>1.87</v>
@@ -2926,7 +2926,7 @@
         <v>2.17</v>
       </c>
       <c r="I32" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J32" t="n">
         <v>1.85</v>
@@ -3001,7 +3001,7 @@
         <v>3.72</v>
       </c>
       <c r="I33" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J33" t="n">
         <v>1.83</v>
@@ -3080,7 +3080,7 @@
         <v>2.05</v>
       </c>
       <c r="I34" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J34" t="n">
         <v>1.82</v>
@@ -3155,7 +3155,7 @@
         <v>-0.5</v>
       </c>
       <c r="I35" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J35" t="n">
         <v>1.81</v>
@@ -3230,7 +3230,7 @@
         <v>-1.01</v>
       </c>
       <c r="I36" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J36" t="n">
         <v>1.81</v>
@@ -3305,7 +3305,7 @@
         <v>2.55</v>
       </c>
       <c r="I37" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J37" t="n">
         <v>1.82</v>
@@ -3380,7 +3380,7 @@
         <v>0.5</v>
       </c>
       <c r="I38" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J38" t="n">
         <v>1.82</v>
@@ -3455,7 +3455,7 @@
         <v>-2.97</v>
       </c>
       <c r="I39" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J39" t="n">
         <v>1.82</v>
@@ -3530,7 +3530,7 @@
         <v>10.71</v>
       </c>
       <c r="I40" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J40" t="n">
         <v>1.84</v>
@@ -3605,7 +3605,7 @@
         <v>4.15</v>
       </c>
       <c r="I41" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J41" t="n">
         <v>1.87</v>
@@ -3680,7 +3680,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J42" t="n">
         <v>1.91</v>
@@ -3755,7 +3755,7 @@
         <v>-3.54</v>
       </c>
       <c r="I43" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J43" t="n">
         <v>1.95</v>
@@ -3830,7 +3830,7 @@
         <v>-3.21</v>
       </c>
       <c r="I44" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J44" t="n">
         <v>1.97</v>
@@ -3905,7 +3905,7 @@
         <v>2.84</v>
       </c>
       <c r="I45" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J45" t="n">
         <v>1.99</v>
@@ -3980,7 +3980,7 @@
         <v>1.38</v>
       </c>
       <c r="I46" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J46" t="n">
         <v>2.01</v>
@@ -4055,7 +4055,7 @@
         <v>0.45</v>
       </c>
       <c r="I47" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J47" t="n">
         <v>2.03</v>
@@ -4130,7 +4130,7 @@
         <v>2.71</v>
       </c>
       <c r="I48" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J48" t="n">
         <v>2.05</v>
@@ -4205,7 +4205,7 @@
         <v>0.88</v>
       </c>
       <c r="I49" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J49" t="n">
         <v>2.08</v>
@@ -4280,7 +4280,7 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J50" t="n">
         <v>2.1</v>
@@ -4355,7 +4355,7 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J51" t="n">
         <v>2.12</v>
@@ -4430,7 +4430,7 @@
         <v>-2.18</v>
       </c>
       <c r="I52" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J52" t="n">
         <v>2.14</v>
@@ -4505,7 +4505,7 @@
         <v>3.57</v>
       </c>
       <c r="I53" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J53" t="n">
         <v>2.16</v>
@@ -4580,7 +4580,7 @@
         <v>-3.88</v>
       </c>
       <c r="I54" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J54" t="n">
         <v>2.17</v>
@@ -4655,7 +4655,7 @@
         <v>3.14</v>
       </c>
       <c r="I55" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J55" t="n">
         <v>2.19</v>
@@ -4730,7 +4730,7 @@
         <v>4.78</v>
       </c>
       <c r="I56" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J56" t="n">
         <v>2.21</v>
@@ -4805,7 +4805,7 @@
         <v>3.73</v>
       </c>
       <c r="I57" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J57" t="n">
         <v>2.23</v>
@@ -4880,7 +4880,7 @@
         <v>5.2</v>
       </c>
       <c r="I58" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J58" t="n">
         <v>2.26</v>
@@ -4955,7 +4955,7 @@
         <v>-5.7</v>
       </c>
       <c r="I59" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J59" t="n">
         <v>2.29</v>
@@ -5030,7 +5030,7 @@
         <v>5.65</v>
       </c>
       <c r="I60" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J60" t="n">
         <v>2.31</v>
@@ -5105,7 +5105,7 @@
         <v>1.15</v>
       </c>
       <c r="I61" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J61" t="n">
         <v>2.33</v>
@@ -5180,7 +5180,7 @@
         <v>9.43</v>
       </c>
       <c r="I62" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J62" t="n">
         <v>2.36</v>
@@ -5255,7 +5255,7 @@
         <v>6.55</v>
       </c>
       <c r="I63" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J63" t="n">
         <v>2.41</v>
@@ -5330,7 +5330,7 @@
         <v>0.65</v>
       </c>
       <c r="I64" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J64" t="n">
         <v>2.46</v>
@@ -5405,7 +5405,7 @@
         <v>4.5</v>
       </c>
       <c r="I65" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J65" t="n">
         <v>2.51</v>
@@ -5480,7 +5480,7 @@
         <v>-1.54</v>
       </c>
       <c r="I66" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J66" t="n">
         <v>2.56</v>
@@ -5555,7 +5555,7 @@
         <v>3.75</v>
       </c>
       <c r="I67" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J67" t="n">
         <v>2.62</v>
@@ -5630,7 +5630,7 @@
         <v>3.31</v>
       </c>
       <c r="I68" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J68" t="n">
         <v>2.68</v>
@@ -5705,7 +5705,7 @@
         <v>-5.83</v>
       </c>
       <c r="I69" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J69" t="n">
         <v>2.72</v>
@@ -5780,7 +5780,7 @@
         <v>8.050000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J70" t="n">
         <v>2.78</v>
@@ -5855,7 +5855,7 @@
         <v>-6.88</v>
       </c>
       <c r="I71" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J71" t="n">
         <v>2.83</v>
@@ -5930,7 +5930,7 @@
         <v>5.23</v>
       </c>
       <c r="I72" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J72" t="n">
         <v>2.89</v>
@@ -6005,7 +6005,7 @@
         <v>2.92</v>
       </c>
       <c r="I73" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J73" t="n">
         <v>2.95</v>
@@ -6080,7 +6080,7 @@
         <v>3.69</v>
       </c>
       <c r="I74" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J74" t="n">
         <v>3.02</v>
@@ -6155,7 +6155,7 @@
         <v>14.25</v>
       </c>
       <c r="I75" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J75" t="n">
         <v>3.12</v>
@@ -6230,7 +6230,7 @@
         <v>-1.2</v>
       </c>
       <c r="I76" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J76" t="n">
         <v>3.2</v>
@@ -6305,7 +6305,7 @@
         <v>-1.94</v>
       </c>
       <c r="I77" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J77" t="n">
         <v>3.28</v>
@@ -6380,7 +6380,7 @@
         <v>-4.95</v>
       </c>
       <c r="I78" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J78" t="n">
         <v>3.34</v>
@@ -6455,7 +6455,7 @@
         <v>4.17</v>
       </c>
       <c r="I79" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J79" t="n">
         <v>3.42</v>
@@ -6530,7 +6530,7 @@
         <v>-0.5</v>
       </c>
       <c r="I80" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J80" t="n">
         <v>3.48</v>
@@ -6605,7 +6605,7 @@
         <v>1.26</v>
       </c>
       <c r="I81" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J81" t="n">
         <v>3.55</v>
@@ -6680,7 +6680,7 @@
         <v>2.73</v>
       </c>
       <c r="I82" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J82" t="n">
         <v>3.61</v>
@@ -6755,7 +6755,7 @@
         <v>-10.39</v>
       </c>
       <c r="I83" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J83" t="n">
         <v>3.65</v>
@@ -6830,7 +6830,7 @@
         <v>8.09</v>
       </c>
       <c r="I84" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J84" t="n">
         <v>3.69</v>
@@ -6905,7 +6905,7 @@
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J85" t="n">
         <v>3.73</v>
@@ -6980,7 +6980,7 @@
         <v>4.49</v>
       </c>
       <c r="I86" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J86" t="n">
         <v>3.78</v>
@@ -7055,7 +7055,7 @@
         <v>-2.39</v>
       </c>
       <c r="I87" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J87" t="n">
         <v>3.82</v>
@@ -7130,7 +7130,7 @@
         <v>2.44</v>
       </c>
       <c r="I88" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J88" t="n">
         <v>3.85</v>
@@ -7205,7 +7205,7 @@
         <v>-0.48</v>
       </c>
       <c r="I89" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J89" t="n">
         <v>3.9</v>
@@ -7280,7 +7280,7 @@
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J90" t="n">
         <v>3.94</v>
@@ -7355,7 +7355,7 @@
         <v>-0.24</v>
       </c>
       <c r="I91" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J91" t="n">
         <v>3.98</v>
@@ -7430,7 +7430,7 @@
         <v>-2.64</v>
       </c>
       <c r="I92" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J92" t="n">
         <v>4.01</v>
@@ -7505,7 +7505,7 @@
         <v>5.93</v>
       </c>
       <c r="I93" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J93" t="n">
         <v>4.05</v>
@@ -7580,7 +7580,7 @@
         <v>-3.73</v>
       </c>
       <c r="I94" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J94" t="n">
         <v>4.07</v>
@@ -7655,7 +7655,7 @@
         <v>3.63</v>
       </c>
       <c r="I95" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J95" t="n">
         <v>4.08</v>
@@ -7730,7 +7730,7 @@
         <v>-2.1</v>
       </c>
       <c r="I96" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J96" t="n">
         <v>4.08</v>
@@ -7805,7 +7805,7 @@
         <v>-0.48</v>
       </c>
       <c r="I97" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J97" t="n">
         <v>4.09</v>
@@ -7880,7 +7880,7 @@
         <v>-2.16</v>
       </c>
       <c r="I98" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J98" t="n">
         <v>4.1</v>
@@ -7959,7 +7959,7 @@
         <v>3.19</v>
       </c>
       <c r="I99" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J99" t="n">
         <v>4.11</v>
@@ -8034,7 +8034,7 @@
         <v>0.95</v>
       </c>
       <c r="I100" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J100" t="n">
         <v>4.13</v>
@@ -8109,7 +8109,7 @@
         <v>-3.76</v>
       </c>
       <c r="I101" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J101" t="n">
         <v>4.13</v>
@@ -8188,7 +8188,7 @@
         <v>-9.050000000000001</v>
       </c>
       <c r="I102" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J102" t="n">
         <v>4.11</v>
@@ -8263,7 +8263,7 @@
         <v>7.26</v>
       </c>
       <c r="I103" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J103" t="n">
         <v>4.12</v>
@@ -8338,7 +8338,7 @@
         <v>2.26</v>
       </c>
       <c r="I104" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J104" t="n">
         <v>4.13</v>
@@ -8413,7 +8413,7 @@
         <v>0.98</v>
       </c>
       <c r="I105" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J105" t="n">
         <v>4.13</v>
@@ -8488,7 +8488,7 @@
         <v>0.97</v>
       </c>
       <c r="I106" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J106" t="n">
         <v>4.13</v>
@@ -8563,7 +8563,7 @@
         <v>0.24</v>
       </c>
       <c r="I107" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J107" t="n">
         <v>4.13</v>
@@ -8638,7 +8638,7 @@
         <v>-1.92</v>
       </c>
       <c r="I108" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J108" t="n">
         <v>4.13</v>
@@ -8717,7 +8717,7 @@
         <v>4.16</v>
       </c>
       <c r="I109" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J109" t="n">
         <v>4.13</v>
@@ -8792,7 +8792,7 @@
         <v>2.58</v>
       </c>
       <c r="I110" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J110" t="n">
         <v>4.14</v>
@@ -8867,7 +8867,7 @@
         <v>-4.12</v>
       </c>
       <c r="I111" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J111" t="n">
         <v>4.14</v>
@@ -8942,7 +8942,7 @@
         <v>-1.19</v>
       </c>
       <c r="I112" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J112" t="n">
         <v>4.15</v>
@@ -9021,7 +9021,7 @@
         <v>-2.42</v>
       </c>
       <c r="I113" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J113" t="n">
         <v>4.14</v>
@@ -9096,7 +9096,7 @@
         <v>-5.45</v>
       </c>
       <c r="I114" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J114" t="n">
         <v>4.12</v>
@@ -9171,7 +9171,7 @@
         <v>-0.52</v>
       </c>
       <c r="I115" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J115" t="n">
         <v>4.1</v>
@@ -9246,7 +9246,7 @@
         <v>-0.79</v>
       </c>
       <c r="I116" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J116" t="n">
         <v>4.08</v>
@@ -9325,7 +9325,7 @@
         <v>9.81</v>
       </c>
       <c r="I117" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J117" t="n">
         <v>4.07</v>
@@ -9400,7 +9400,7 @@
         <v>-3.38</v>
       </c>
       <c r="I118" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J118" t="n">
         <v>4.07</v>
@@ -9479,7 +9479,7 @@
         <v>-1.5</v>
       </c>
       <c r="I119" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J119" t="n">
         <v>4.06</v>
@@ -9554,7 +9554,7 @@
         <v>0.51</v>
       </c>
       <c r="I120" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J120" t="n">
         <v>4.04</v>
@@ -9629,7 +9629,7 @@
         <v>4.55</v>
       </c>
       <c r="I121" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J121" t="n">
         <v>4.04</v>
@@ -9704,7 +9704,7 @@
         <v>-5.56</v>
       </c>
       <c r="I122" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J122" t="n">
         <v>4.05</v>
@@ -9783,7 +9783,7 @@
         <v>-1.53</v>
       </c>
       <c r="I123" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J123" t="n">
         <v>4.05</v>
@@ -9858,7 +9858,7 @@
         <v>3.9</v>
       </c>
       <c r="I124" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J124" t="n">
         <v>4.04</v>
@@ -9933,7 +9933,7 @@
         <v>0.75</v>
       </c>
       <c r="I125" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J125" t="n">
         <v>4.04</v>
@@ -10008,7 +10008,7 @@
         <v>2.23</v>
       </c>
       <c r="I126" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J126" t="n">
         <v>4.04</v>
@@ -10083,7 +10083,7 @@
         <v>1.94</v>
       </c>
       <c r="I127" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J127" t="n">
         <v>4.04</v>
@@ -10158,7 +10158,7 @@
         <v>3.1</v>
       </c>
       <c r="I128" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J128" t="n">
         <v>4.05</v>
@@ -10233,7 +10233,7 @@
         <v>6.93</v>
       </c>
       <c r="I129" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J129" t="n">
         <v>4.07</v>
@@ -10308,7 +10308,7 @@
         <v>4.75</v>
       </c>
       <c r="I130" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J130" t="n">
         <v>4.09</v>
@@ -10383,7 +10383,7 @@
         <v>3.09</v>
       </c>
       <c r="I131" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J131" t="n">
         <v>4.13</v>
@@ -10458,7 +10458,7 @@
         <v>2</v>
       </c>
       <c r="I132" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J132" t="n">
         <v>4.18</v>
@@ -10533,7 +10533,7 @@
         <v>5.69</v>
       </c>
       <c r="I133" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J133" t="n">
         <v>4.25</v>
@@ -10608,7 +10608,7 @@
         <v>-3.34</v>
       </c>
       <c r="I134" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J134" t="n">
         <v>4.32</v>
@@ -10683,7 +10683,7 @@
         <v>3.65</v>
       </c>
       <c r="I135" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J135" t="n">
         <v>4.4</v>
@@ -10758,7 +10758,7 @@
         <v>-2.96</v>
       </c>
       <c r="I136" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J136" t="n">
         <v>4.47</v>
@@ -10833,7 +10833,7 @@
         <v>5.92</v>
       </c>
       <c r="I137" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J137" t="n">
         <v>4.54</v>
@@ -10908,7 +10908,7 @@
         <v>-0.54</v>
       </c>
       <c r="I138" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J138" t="n">
         <v>4.62</v>
@@ -10983,7 +10983,7 @@
         <v>-5.25</v>
       </c>
       <c r="I139" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J139" t="n">
         <v>4.68</v>
@@ -11058,7 +11058,7 @@
         <v>-0.57</v>
       </c>
       <c r="I140" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J140" t="n">
         <v>4.74</v>
@@ -11133,7 +11133,7 @@
         <v>-3.85</v>
       </c>
       <c r="I141" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J141" t="n">
         <v>4.79</v>
@@ -11208,7 +11208,7 @@
         <v>5</v>
       </c>
       <c r="I142" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J142" t="n">
         <v>4.85</v>
@@ -11283,7 +11283,7 @@
         <v>-0.38</v>
       </c>
       <c r="I143" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J143" t="n">
         <v>4.92</v>
@@ -11358,7 +11358,7 @@
         <v>6.5</v>
       </c>
       <c r="I144" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J144" t="n">
         <v>5</v>
@@ -11433,7 +11433,7 @@
         <v>6.1</v>
       </c>
       <c r="I145" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J145" t="n">
         <v>5.1</v>
@@ -11508,7 +11508,7 @@
         <v>1.18</v>
       </c>
       <c r="I146" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J146" t="n">
         <v>5.19</v>
@@ -11583,7 +11583,7 @@
         <v>3.18</v>
       </c>
       <c r="I147" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J147" t="n">
         <v>5.29</v>
@@ -11658,7 +11658,7 @@
         <v>-4.86</v>
       </c>
       <c r="I148" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J148" t="n">
         <v>5.36</v>
@@ -11733,7 +11733,7 @@
         <v>2.73</v>
       </c>
       <c r="I149" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J149" t="n">
         <v>5.44</v>
@@ -11808,7 +11808,7 @@
         <v>-2.65</v>
       </c>
       <c r="I150" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J150" t="n">
         <v>5.49</v>
@@ -11883,7 +11883,7 @@
         <v>-9.710000000000001</v>
       </c>
       <c r="I151" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J151" t="n">
         <v>5.5</v>
@@ -11962,7 +11962,7 @@
         <v>10.38</v>
       </c>
       <c r="I152" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J152" t="n">
         <v>5.54</v>
@@ -12037,7 +12037,7 @@
         <v>-3.25</v>
       </c>
       <c r="I153" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J153" t="n">
         <v>5.55</v>
@@ -12112,7 +12112,7 @@
         <v>8.83</v>
       </c>
       <c r="I154" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J154" t="n">
         <v>5.6</v>
@@ -12187,7 +12187,7 @@
         <v>9.58</v>
       </c>
       <c r="I155" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J155" t="n">
         <v>5.67</v>
@@ -12262,7 +12262,7 @@
         <v>2.07</v>
       </c>
       <c r="I156" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J156" t="n">
         <v>5.75</v>
@@ -12337,7 +12337,7 @@
         <v>6.68</v>
       </c>
       <c r="I157" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J157" t="n">
         <v>5.84</v>
@@ -12412,7 +12412,7 @@
         <v>-6.12</v>
       </c>
       <c r="I158" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J158" t="n">
         <v>5.91</v>
@@ -12487,7 +12487,7 @@
         <v>2.75</v>
       </c>
       <c r="I159" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J159" t="n">
         <v>6</v>
@@ -12562,7 +12562,7 @@
         <v>1.97</v>
       </c>
       <c r="I160" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J160" t="n">
         <v>6.1</v>
@@ -12637,7 +12637,7 @@
         <v>6.64</v>
       </c>
       <c r="I161" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J161" t="n">
         <v>6.24</v>
@@ -12712,7 +12712,7 @@
         <v>7.39</v>
       </c>
       <c r="I162" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J162" t="n">
         <v>6.39</v>
@@ -12787,7 +12787,7 @@
         <v>0.36</v>
       </c>
       <c r="I163" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J163" t="n">
         <v>6.54</v>
@@ -12862,7 +12862,7 @@
         <v>7.82</v>
       </c>
       <c r="I164" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J164" t="n">
         <v>6.71</v>
@@ -12937,7 +12937,7 @@
         <v>-5.02</v>
       </c>
       <c r="I165" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J165" t="n">
         <v>6.84</v>
@@ -13012,7 +13012,7 @@
         <v>5.17</v>
       </c>
       <c r="I166" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J166" t="n">
         <v>6.99</v>
@@ -13087,7 +13087,7 @@
         <v>11.62</v>
       </c>
       <c r="I167" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J167" t="n">
         <v>7.18</v>
@@ -13162,7 +13162,7 @@
         <v>-14.81</v>
       </c>
       <c r="I168" s="4" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J168" s="4" t="n">
         <v>7.32</v>
@@ -13237,7 +13237,7 @@
         <v>2.47</v>
       </c>
       <c r="I169" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J169" t="n">
         <v>7.45</v>
@@ -13312,7 +13312,7 @@
         <v>-9.52</v>
       </c>
       <c r="I170" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J170" t="n">
         <v>7.55</v>
@@ -13387,7 +13387,7 @@
         <v>-5.7</v>
       </c>
       <c r="I171" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J171" t="n">
         <v>7.66</v>
@@ -13466,7 +13466,7 @@
         <v>12.5</v>
       </c>
       <c r="I172" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J172" t="n">
         <v>7.78</v>
@@ -13541,7 +13541,7 @@
         <v>-1.19</v>
       </c>
       <c r="I173" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J173" t="n">
         <v>7.91</v>
@@ -13616,7 +13616,7 @@
         <v>2.06</v>
       </c>
       <c r="I174" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J174" t="n">
         <v>8.029999999999999</v>
@@ -13691,7 +13691,7 @@
         <v>-5.92</v>
       </c>
       <c r="I175" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J175" t="n">
         <v>8.09</v>
@@ -13770,7 +13770,7 @@
         <v>0.38</v>
       </c>
       <c r="I176" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J176" t="n">
         <v>8.140000000000001</v>
@@ -13845,7 +13845,7 @@
         <v>-3.76</v>
       </c>
       <c r="I177" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J177" t="n">
         <v>8.16</v>
@@ -13920,7 +13920,7 @@
         <v>-4.69</v>
       </c>
       <c r="I178" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J178" t="n">
         <v>8.18</v>
@@ -13995,7 +13995,7 @@
         <v>-3.28</v>
       </c>
       <c r="I179" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J179" t="n">
         <v>8.18</v>
@@ -14070,7 +14070,7 @@
         <v>-6.79</v>
       </c>
       <c r="I180" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J180" t="n">
         <v>8.140000000000001</v>
@@ -14149,7 +14149,7 @@
         <v>2.28</v>
       </c>
       <c r="I181" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J181" t="n">
         <v>8.1</v>
@@ -14224,7 +14224,7 @@
         <v>3.71</v>
       </c>
       <c r="I182" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J182" t="n">
         <v>8.029999999999999</v>
@@ -14299,7 +14299,7 @@
         <v>-2</v>
       </c>
       <c r="I183" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J183" t="n">
         <v>7.96</v>
@@ -14374,7 +14374,7 @@
         <v>5.99</v>
       </c>
       <c r="I184" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J184" t="n">
         <v>7.87</v>
@@ -14449,7 +14449,7 @@
         <v>-2.2</v>
       </c>
       <c r="I185" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J185" t="n">
         <v>7.8</v>
@@ -14524,7 +14524,7 @@
         <v>-0.99</v>
       </c>
       <c r="I186" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J186" t="n">
         <v>7.71</v>
@@ -14599,7 +14599,7 @@
         <v>4.69</v>
       </c>
       <c r="I187" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J187" t="n">
         <v>7.58</v>
@@ -14674,7 +14674,7 @@
         <v>2.99</v>
       </c>
       <c r="I188" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J188" t="n">
         <v>7.53</v>
@@ -14749,7 +14749,7 @@
         <v>-3.56</v>
       </c>
       <c r="I189" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J189" t="n">
         <v>7.46</v>
@@ -14828,7 +14828,7 @@
         <v>7.66</v>
       </c>
       <c r="I190" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J190" t="n">
         <v>7.46</v>
@@ -14903,7 +14903,7 @@
         <v>2.41</v>
       </c>
       <c r="I191" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J191" t="n">
         <v>7.49</v>
@@ -14978,7 +14978,7 @@
         <v>1.49</v>
       </c>
       <c r="I192" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J192" t="n">
         <v>7.48</v>
@@ -15053,7 +15053,7 @@
         <v>3.67</v>
       </c>
       <c r="I193" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J193" t="n">
         <v>7.49</v>
@@ -15128,7 +15128,7 @@
         <v>-5.31</v>
       </c>
       <c r="I194" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J194" t="n">
         <v>7.47</v>
@@ -15203,7 +15203,7 @@
         <v>-7.35</v>
       </c>
       <c r="I195" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J195" t="n">
         <v>7.44</v>
@@ -15278,7 +15278,7 @@
         <v>0</v>
       </c>
       <c r="I196" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J196" t="n">
         <v>7.42</v>
@@ -15353,7 +15353,7 @@
         <v>-4.03</v>
       </c>
       <c r="I197" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J197" t="n">
         <v>7.39</v>
@@ -15432,7 +15432,7 @@
         <v>-2.94</v>
       </c>
       <c r="I198" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J198" t="n">
         <v>7.37</v>
@@ -15511,7 +15511,7 @@
         <v>4.91</v>
       </c>
       <c r="I199" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J199" t="n">
         <v>7.38</v>
@@ -15586,7 +15586,7 @@
         <v>4.13</v>
       </c>
       <c r="I200" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J200" t="n">
         <v>7.43</v>
@@ -15661,7 +15661,7 @@
         <v>1.45</v>
       </c>
       <c r="I201" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J201" t="n">
         <v>7.48</v>
@@ -15736,7 +15736,7 @@
         <v>3.26</v>
       </c>
       <c r="I202" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J202" t="n">
         <v>7.53</v>
@@ -15811,7 +15811,7 @@
         <v>5.8</v>
       </c>
       <c r="I203" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J203" t="n">
         <v>7.6</v>
@@ -15886,7 +15886,7 @@
         <v>3.93</v>
       </c>
       <c r="I204" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J204" t="n">
         <v>7.68</v>
@@ -15961,7 +15961,7 @@
         <v>9.06</v>
       </c>
       <c r="I205" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J205" t="n">
         <v>7.8</v>
@@ -16036,7 +16036,7 @@
         <v>-0.53</v>
       </c>
       <c r="I206" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J206" t="n">
         <v>7.92</v>
@@ -16111,7 +16111,7 @@
         <v>-4.02</v>
       </c>
       <c r="I207" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J207" t="n">
         <v>8</v>
@@ -16186,7 +16186,7 @@
         <v>14.76</v>
       </c>
       <c r="I208" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J208" t="n">
         <v>8.15</v>
@@ -16261,7 +16261,7 @@
         <v>7.87</v>
       </c>
       <c r="I209" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J209" t="n">
         <v>8.34</v>
@@ -16336,7 +16336,7 @@
         <v>8.19</v>
       </c>
       <c r="I210" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J210" t="n">
         <v>8.56</v>
@@ -16411,7 +16411,7 @@
         <v>-1.73</v>
       </c>
       <c r="I211" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J211" t="n">
         <v>8.75</v>
@@ -16486,7 +16486,7 @@
         <v>-1.17</v>
       </c>
       <c r="I212" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J212" t="n">
         <v>8.93</v>
@@ -16561,7 +16561,7 @@
         <v>6.01</v>
       </c>
       <c r="I213" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J213" t="n">
         <v>9.130000000000001</v>
@@ -16636,7 +16636,7 @@
         <v>0.48</v>
       </c>
       <c r="I214" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J214" t="n">
         <v>9.359999999999999</v>
@@ -16711,7 +16711,7 @@
         <v>-4.05</v>
       </c>
       <c r="I215" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J215" t="n">
         <v>9.59</v>
@@ -16786,7 +16786,7 @@
         <v>5.72</v>
       </c>
       <c r="I216" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J216" t="n">
         <v>9.859999999999999</v>
@@ -16861,7 +16861,7 @@
         <v>4</v>
       </c>
       <c r="I217" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J217" t="n">
         <v>10.17</v>
@@ -16936,7 +16936,7 @@
         <v>3.17</v>
       </c>
       <c r="I218" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J218" t="n">
         <v>10.5</v>
@@ -17011,7 +17011,7 @@
         <v>-3.51</v>
       </c>
       <c r="I219" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J219" t="n">
         <v>10.8</v>
@@ -17086,7 +17086,7 @@
         <v>12.57</v>
       </c>
       <c r="I220" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J220" t="n">
         <v>11.17</v>
@@ -17161,7 +17161,7 @@
         <v>1.01</v>
       </c>
       <c r="I221" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J221" t="n">
         <v>11.53</v>
@@ -17236,7 +17236,7 @@
         <v>4.99</v>
       </c>
       <c r="I222" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J222" t="n">
         <v>11.92</v>
@@ -17311,7 +17311,7 @@
         <v>-1.46</v>
       </c>
       <c r="I223" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J223" t="n">
         <v>12.28</v>
@@ -17386,7 +17386,7 @@
         <v>13.38</v>
       </c>
       <c r="I224" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J224" t="n">
         <v>12.73</v>
@@ -17461,7 +17461,7 @@
         <v>7.21</v>
       </c>
       <c r="I225" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J225" t="n">
         <v>13.2</v>
@@ -17536,7 +17536,7 @@
         <v>-2.7</v>
       </c>
       <c r="I226" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J226" t="n">
         <v>13.64</v>
@@ -17611,7 +17611,7 @@
         <v>-5.39</v>
       </c>
       <c r="I227" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J227" t="n">
         <v>14.06</v>
@@ -17686,7 +17686,7 @@
         <v>-3.16</v>
       </c>
       <c r="I228" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J228" t="n">
         <v>14.38</v>
@@ -17761,7 +17761,7 @@
         <v>7.78</v>
       </c>
       <c r="I229" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J229" t="n">
         <v>14.72</v>
@@ -17836,7 +17836,7 @@
         <v>-9.199999999999999</v>
       </c>
       <c r="I230" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J230" t="n">
         <v>14.94</v>
@@ -17911,7 +17911,7 @@
         <v>-0.61</v>
       </c>
       <c r="I231" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J231" t="n">
         <v>15.16</v>
@@ -17986,7 +17986,7 @@
         <v>10.87</v>
       </c>
       <c r="I232" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J232" t="n">
         <v>15.48</v>
@@ -18061,7 +18061,7 @@
         <v>3.36</v>
       </c>
       <c r="I233" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J233" t="n">
         <v>15.79</v>
@@ -18136,7 +18136,7 @@
         <v>-3.57</v>
       </c>
       <c r="I234" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J234" t="n">
         <v>16.07</v>
@@ -18211,7 +18211,7 @@
         <v>14.14</v>
       </c>
       <c r="I235" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J235" t="n">
         <v>16.5</v>
@@ -18286,7 +18286,7 @@
         <v>1.06</v>
       </c>
       <c r="I236" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J236" t="n">
         <v>16.9</v>
@@ -18361,7 +18361,7 @@
         <v>7.14</v>
       </c>
       <c r="I237" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J237" t="n">
         <v>17.36</v>
@@ -18436,7 +18436,7 @@
         <v>-6.79</v>
       </c>
       <c r="I238" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J238" t="n">
         <v>17.72</v>
@@ -18511,7 +18511,7 @@
         <v>4.46</v>
       </c>
       <c r="I239" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J239" t="n">
         <v>18.15</v>
@@ -18586,7 +18586,7 @@
         <v>5</v>
       </c>
       <c r="I240" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J240" t="n">
         <v>18.55</v>
@@ -18661,7 +18661,7 @@
         <v>14.65</v>
       </c>
       <c r="I241" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J241" t="n">
         <v>19.1</v>
@@ -18736,7 +18736,7 @@
         <v>-5.03</v>
       </c>
       <c r="I242" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J242" t="n">
         <v>19.56</v>
@@ -18811,7 +18811,7 @@
         <v>10.96</v>
       </c>
       <c r="I243" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J243" t="n">
         <v>20.17</v>
@@ -18886,7 +18886,7 @@
         <v>9.08</v>
       </c>
       <c r="I244" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J244" t="n">
         <v>20.79</v>
@@ -18961,7 +18961,7 @@
         <v>2.79</v>
       </c>
       <c r="I245" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J245" t="n">
         <v>21.4</v>
@@ -19036,7 +19036,7 @@
         <v>1.65</v>
       </c>
       <c r="I246" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J246" t="n">
         <v>22.05</v>
@@ -19111,7 +19111,7 @@
         <v>-7.15</v>
       </c>
       <c r="I247" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J247" t="n">
         <v>22.64</v>
@@ -19186,7 +19186,7 @@
         <v>-31.09</v>
       </c>
       <c r="I248" s="4" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J248" s="4" t="n">
         <v>22.81</v>
@@ -19265,7 +19265,7 @@
         <v>4.37</v>
       </c>
       <c r="I249" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J249" t="n">
         <v>22.95</v>
@@ -19340,7 +19340,7 @@
         <v>-18.45</v>
       </c>
       <c r="I250" s="4" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J250" s="4" t="n">
         <v>22.99</v>
@@ -19415,7 +19415,7 @@
         <v>1.52</v>
       </c>
       <c r="I251" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J251" t="n">
         <v>23.04</v>
@@ -19494,7 +19494,7 @@
         <v>15.68</v>
       </c>
       <c r="I252" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J252" t="n">
         <v>23.14</v>
@@ -19569,7 +19569,7 @@
         <v>-7.25</v>
       </c>
       <c r="I253" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J253" t="n">
         <v>23.13</v>
@@ -19644,7 +19644,7 @@
         <v>5.46</v>
       </c>
       <c r="I254" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J254" t="n">
         <v>23.21</v>
@@ -19719,7 +19719,7 @@
         <v>-20.25</v>
       </c>
       <c r="I255" s="4" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J255" s="4" t="n">
         <v>22.97</v>
@@ -19792,7 +19792,7 @@
         <v>0.64</v>
       </c>
       <c r="I256" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J256" t="n">
         <v>22.71</v>
@@ -19871,7 +19871,7 @@
         <v>21</v>
       </c>
       <c r="I257" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J257" t="n">
         <v>22.55</v>
@@ -19946,7 +19946,7 @@
         <v>3.4</v>
       </c>
       <c r="I258" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J258" t="n">
         <v>22.5</v>
@@ -20021,7 +20021,7 @@
         <v>-5.01</v>
       </c>
       <c r="I259" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J259" t="n">
         <v>22.35</v>
@@ -20096,7 +20096,7 @@
         <v>5.8</v>
       </c>
       <c r="I260" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J260" t="n">
         <v>22.2</v>
@@ -20171,7 +20171,7 @@
         <v>-19.32</v>
       </c>
       <c r="I261" s="4" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J261" s="4" t="n">
         <v>21.69</v>
@@ -20254,7 +20254,7 @@
         <v>17.71</v>
       </c>
       <c r="I262" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J262" t="n">
         <v>21.39</v>
@@ -20329,7 +20329,7 @@
         <v>-11.12</v>
       </c>
       <c r="I263" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J263" t="n">
         <v>20.85</v>
@@ -20408,7 +20408,7 @@
         <v>-2.38</v>
       </c>
       <c r="I264" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J264" t="n">
         <v>20.16</v>
@@ -20483,7 +20483,7 @@
         <v>-17.58</v>
       </c>
       <c r="I265" s="4" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J265" s="4" t="n">
         <v>19.28</v>
@@ -20558,7 +20558,7 @@
         <v>1.48</v>
       </c>
       <c r="I266" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J266" t="n">
         <v>18.39</v>
@@ -20637,7 +20637,7 @@
         <v>-11.24</v>
       </c>
       <c r="I267" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J267" t="n">
         <v>17.54</v>
@@ -20716,7 +20716,7 @@
         <v>16.86</v>
       </c>
       <c r="I268" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J268" t="n">
         <v>17.24</v>
@@ -20791,7 +20791,7 @@
         <v>7.67</v>
       </c>
       <c r="I269" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J269" t="n">
         <v>16.96</v>
@@ -20866,7 +20866,7 @@
         <v>-7.78</v>
       </c>
       <c r="I270" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J270" t="n">
         <v>16.8</v>
@@ -20941,7 +20941,7 @@
         <v>7.02</v>
       </c>
       <c r="I271" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J271" t="n">
         <v>16.69</v>
@@ -21016,7 +21016,7 @@
         <v>2.98</v>
       </c>
       <c r="I272" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J272" t="n">
         <v>16.46</v>
@@ -21095,7 +21095,7 @@
         <v>30.23</v>
       </c>
       <c r="I273" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J273" t="n">
         <v>16.54</v>
@@ -21170,7 +21170,7 @@
         <v>-1.38</v>
       </c>
       <c r="I274" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J274" t="n">
         <v>16.55</v>
@@ -21245,7 +21245,7 @@
         <v>-1.35</v>
       </c>
       <c r="I275" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J275" t="n">
         <v>16.75</v>
@@ -21320,7 +21320,7 @@
         <v>5.08</v>
       </c>
       <c r="I276" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J276" t="n">
         <v>17</v>
@@ -21395,7 +21395,7 @@
         <v>11.98</v>
       </c>
       <c r="I277" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J277" t="n">
         <v>17.2</v>
@@ -21470,7 +21470,7 @@
         <v>-3.84</v>
       </c>
       <c r="I278" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J278" t="n">
         <v>17.32</v>
@@ -21545,7 +21545,7 @@
         <v>5.2</v>
       </c>
       <c r="I279" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J279" t="n">
         <v>17.56</v>
@@ -21620,7 +21620,7 @@
         <v>9.98</v>
       </c>
       <c r="I280" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J280" t="n">
         <v>17.85</v>
@@ -21695,7 +21695,7 @@
         <v>-4.23</v>
       </c>
       <c r="I281" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J281" t="n">
         <v>18.28</v>
@@ -21770,7 +21770,7 @@
         <v>-6.52</v>
       </c>
       <c r="I282" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J282" t="n">
         <v>18.5</v>
@@ -21845,7 +21845,7 @@
         <v>17.54</v>
       </c>
       <c r="I283" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J283" t="n">
         <v>19.01</v>
@@ -21920,7 +21920,7 @@
         <v>-9.65</v>
       </c>
       <c r="I284" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J284" t="n">
         <v>19.42</v>
@@ -21995,7 +21995,7 @@
         <v>7.34</v>
       </c>
       <c r="I285" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J285" t="n">
         <v>20.06</v>
@@ -22070,7 +22070,7 @@
         <v>4.67</v>
       </c>
       <c r="I286" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J286" t="n">
         <v>20.75</v>
@@ -22145,7 +22145,7 @@
         <v>-4.57</v>
       </c>
       <c r="I287" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J287" t="n">
         <v>21.46</v>
@@ -22220,7 +22220,7 @@
         <v>-0.8</v>
       </c>
       <c r="I288" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J288" t="n">
         <v>22.05</v>
@@ -22295,7 +22295,7 @@
         <v>12.69</v>
       </c>
       <c r="I289" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J289" t="n">
         <v>22.76</v>
@@ -22370,7 +22370,7 @@
         <v>2.52</v>
       </c>
       <c r="I290" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J290" t="n">
         <v>23.56</v>
@@ -22445,7 +22445,7 @@
         <v>3.19</v>
       </c>
       <c r="I291" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J291" t="n">
         <v>24.36</v>
@@ -22520,7 +22520,7 @@
         <v>17.69</v>
       </c>
       <c r="I292" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J292" t="n">
         <v>25.41</v>
@@ -22595,7 +22595,7 @@
         <v>14.65</v>
       </c>
       <c r="I293" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J293" t="n">
         <v>26.5</v>
@@ -22670,7 +22670,7 @@
         <v>-8.41</v>
       </c>
       <c r="I294" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J294" t="n">
         <v>27.42</v>
@@ -22745,7 +22745,7 @@
         <v>22.62</v>
       </c>
       <c r="I295" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J295" t="n">
         <v>28.79</v>
@@ -22820,7 +22820,7 @@
         <v>4.33</v>
       </c>
       <c r="I296" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J296" t="n">
         <v>30.21</v>
@@ -22895,7 +22895,7 @@
         <v>-22.56</v>
       </c>
       <c r="I297" s="4" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J297" s="4" t="n">
         <v>30.96</v>
@@ -22970,7 +22970,7 @@
         <v>17.42</v>
       </c>
       <c r="I298" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J298" t="n">
         <v>32.08</v>
@@ -23045,7 +23045,7 @@
         <v>2.91</v>
       </c>
       <c r="I299" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J299" t="n">
         <v>33.2</v>
@@ -23120,7 +23120,7 @@
         <v>-18.31</v>
       </c>
       <c r="I300" s="4" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J300" s="4" t="n">
         <v>33.79</v>
@@ -23195,7 +23195,7 @@
         <v>-5</v>
       </c>
       <c r="I301" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J301" t="n">
         <v>34.34</v>
@@ -23270,7 +23270,7 @@
         <v>-3.36</v>
       </c>
       <c r="I302" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J302" t="n">
         <v>34.91</v>
@@ -23349,7 +23349,7 @@
         <v>10.26</v>
       </c>
       <c r="I303" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J303" t="n">
         <v>35.46</v>
@@ -23424,7 +23424,7 @@
         <v>10.31</v>
       </c>
       <c r="I304" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J304" t="n">
         <v>36.33</v>
@@ -23499,7 +23499,7 @@
         <v>-6.98</v>
       </c>
       <c r="I305" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J305" t="n">
         <v>36.96</v>
@@ -23574,7 +23574,7 @@
         <v>30.06</v>
       </c>
       <c r="I306" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J306" t="n">
         <v>38.12</v>
@@ -23649,7 +23649,7 @@
         <v>-3.57</v>
       </c>
       <c r="I307" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J307" t="n">
         <v>39.25</v>
@@ -23724,7 +23724,7 @@
         <v>12.4</v>
       </c>
       <c r="I308" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J308" t="n">
         <v>40.7</v>
@@ -23799,7 +23799,7 @@
         <v>-0.93</v>
       </c>
       <c r="I309" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J309" t="n">
         <v>41.96</v>
@@ -23874,7 +23874,7 @@
         <v>16.04</v>
       </c>
       <c r="I310" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J310" t="n">
         <v>43.61</v>
@@ -23949,7 +23949,7 @@
         <v>-3.16</v>
       </c>
       <c r="I311" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J311" t="n">
         <v>45.12</v>
@@ -24024,7 +24024,7 @@
         <v>-2.29</v>
       </c>
       <c r="I312" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J312" t="n">
         <v>46.28</v>
@@ -24099,7 +24099,7 @@
         <v>-12.28</v>
       </c>
       <c r="I313" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J313" t="n">
         <v>46.81</v>
@@ -24174,7 +24174,7 @@
         <v>-41.89</v>
       </c>
       <c r="I314" s="4" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J314" s="4" t="n">
         <v>46.41</v>
@@ -24253,7 +24253,7 @@
         <v>16.3</v>
       </c>
       <c r="I315" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J315" t="n">
         <v>45.83</v>
@@ -24328,7 +24328,7 @@
         <v>-2.45</v>
       </c>
       <c r="I316" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J316" t="n">
         <v>45.1</v>
@@ -24403,7 +24403,7 @@
         <v>-9.050000000000001</v>
       </c>
       <c r="I317" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J317" t="n">
         <v>44.77</v>
@@ -24478,7 +24478,7 @@
         <v>33.78</v>
       </c>
       <c r="I318" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J318" t="n">
         <v>44.64</v>
@@ -24553,7 +24553,7 @@
         <v>-2.04</v>
       </c>
       <c r="I319" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J319" t="n">
         <v>44.41</v>
@@ -24628,7 +24628,7 @@
         <v>21.14</v>
       </c>
       <c r="I320" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J320" t="n">
         <v>45.03</v>
@@ -24703,7 +24703,7 @@
         <v>-8.029999999999999</v>
       </c>
       <c r="I321" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J321" t="n">
         <v>45.54</v>
@@ -24778,7 +24778,7 @@
         <v>-0.5</v>
       </c>
       <c r="I322" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J322" t="n">
         <v>46.1</v>
@@ -24857,7 +24857,7 @@
         <v>19.29</v>
       </c>
       <c r="I323" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J323" t="n">
         <v>46.93</v>
@@ -24932,7 +24932,7 @@
         <v>-0.2</v>
       </c>
       <c r="I324" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J324" t="n">
         <v>47.55</v>
@@ -25007,7 +25007,7 @@
         <v>-35.7</v>
       </c>
       <c r="I325" s="4" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J325" s="4" t="n">
         <v>47.35</v>
@@ -25086,7 +25086,7 @@
         <v>5.89</v>
       </c>
       <c r="I326" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J326" t="n">
         <v>46.66</v>
@@ -25161,7 +25161,7 @@
         <v>11.85</v>
       </c>
       <c r="I327" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J327" t="n">
         <v>46.29</v>
@@ -25236,7 +25236,7 @@
         <v>-10.9</v>
       </c>
       <c r="I328" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J328" t="n">
         <v>45.39</v>
@@ -25311,7 +25311,7 @@
         <v>-0.03</v>
       </c>
       <c r="I329" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J329" t="n">
         <v>44.51</v>
@@ -25386,7 +25386,7 @@
         <v>5.82</v>
       </c>
       <c r="I330" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J330" t="n">
         <v>43.3</v>
@@ -25461,7 +25461,7 @@
         <v>-23.21</v>
       </c>
       <c r="I331" s="4" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J331" s="4" t="n">
         <v>41.74</v>
@@ -25540,7 +25540,7 @@
         <v>-9.77</v>
       </c>
       <c r="I332" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J332" t="n">
         <v>40.1</v>
@@ -25619,7 +25619,7 @@
         <v>15.37</v>
       </c>
       <c r="I333" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J333" t="n">
         <v>39.04</v>
@@ -25694,7 +25694,7 @@
         <v>-12.78</v>
       </c>
       <c r="I334" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J334" t="n">
         <v>38.87</v>
@@ -25773,7 +25773,7 @@
         <v>1.58</v>
       </c>
       <c r="I335" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J335" t="n">
         <v>38.48</v>
@@ -25848,7 +25848,7 @@
         <v>3</v>
       </c>
       <c r="I336" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J336" t="n">
         <v>38.18</v>
@@ -25923,7 +25923,7 @@
         <v>-2.28</v>
       </c>
       <c r="I337" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J337" t="n">
         <v>38</v>
@@ -26002,7 +26002,7 @@
         <v>-24.74</v>
       </c>
       <c r="I338" s="4" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J338" s="4" t="n">
         <v>36.94</v>
@@ -26077,7 +26077,7 @@
         <v>14.84</v>
       </c>
       <c r="I339" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J339" t="n">
         <v>36.08</v>
@@ -26152,7 +26152,7 @@
         <v>-9.140000000000001</v>
       </c>
       <c r="I340" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J340" t="n">
         <v>34.68</v>
@@ -26227,7 +26227,7 @@
         <v>-14.72</v>
       </c>
       <c r="I341" s="4" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J341" s="4" t="n">
         <v>33.31</v>
@@ -26306,7 +26306,7 @@
         <v>-2.09</v>
       </c>
       <c r="I342" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J342" t="n">
         <v>31.94</v>
@@ -26385,7 +26385,7 @@
         <v>0.82</v>
       </c>
       <c r="I343" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J343" t="n">
         <v>30.13</v>
@@ -26464,7 +26464,7 @@
         <v>18.03</v>
       </c>
       <c r="I344" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J344" t="n">
         <v>28.5</v>
@@ -26539,7 +26539,7 @@
         <v>-4.46</v>
       </c>
       <c r="I345" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J345" t="n">
         <v>27.79</v>
@@ -26614,7 +26614,7 @@
         <v>6.02</v>
       </c>
       <c r="I346" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J346" t="n">
         <v>27.03</v>
@@ -26689,7 +26689,7 @@
         <v>-18.9</v>
       </c>
       <c r="I347" s="4" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J347" s="4" t="n">
         <v>25.85</v>
@@ -26768,7 +26768,7 @@
         <v>-3.59</v>
       </c>
       <c r="I348" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J348" t="n">
         <v>24.87</v>
@@ -26843,7 +26843,7 @@
         <v>-17.78</v>
       </c>
       <c r="I349" s="4" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J349" s="4" t="n">
         <v>23.73</v>
@@ -26922,7 +26922,7 @@
         <v>-14.63</v>
       </c>
       <c r="I350" s="4" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J350" s="4" t="n">
         <v>22.38</v>
@@ -27001,7 +27001,7 @@
         <v>34.77</v>
       </c>
       <c r="I351" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J351" t="n">
         <v>21.69</v>
@@ -27076,7 +27076,7 @@
         <v>-7.92</v>
       </c>
       <c r="I352" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J352" t="n">
         <v>21.09</v>
@@ -27151,7 +27151,7 @@
         <v>5.87</v>
       </c>
       <c r="I353" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J353" t="n">
         <v>20.32</v>
@@ -27226,7 +27226,7 @@
         <v>20.48</v>
       </c>
       <c r="I354" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J354" t="n">
         <v>19.91</v>
@@ -27301,7 +27301,7 @@
         <v>-3.56</v>
       </c>
       <c r="I355" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J355" t="n">
         <v>19.45</v>
@@ -27376,7 +27376,7 @@
         <v>-8.84</v>
       </c>
       <c r="I356" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J356" t="n">
         <v>18.87</v>
@@ -27451,7 +27451,7 @@
         <v>3.27</v>
       </c>
       <c r="I357" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J357" t="n">
         <v>18.34</v>
@@ -27526,7 +27526,7 @@
         <v>-5.47</v>
       </c>
       <c r="I358" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J358" t="n">
         <v>18.12</v>
@@ -27601,7 +27601,7 @@
         <v>7.5</v>
       </c>
       <c r="I359" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J359" t="n">
         <v>17.8</v>
@@ -27676,7 +27676,7 @@
         <v>15.19</v>
       </c>
       <c r="I360" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J360" t="n">
         <v>17.72</v>
@@ -27751,7 +27751,7 @@
         <v>4.68</v>
       </c>
       <c r="I361" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J361" t="n">
         <v>17.85</v>
@@ -27826,7 +27826,7 @@
         <v>1.55</v>
       </c>
       <c r="I362" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J362" t="n">
         <v>18.02</v>
@@ -27901,7 +27901,7 @@
         <v>8.98</v>
       </c>
       <c r="I363" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J363" t="n">
         <v>18.27</v>
@@ -27976,7 +27976,7 @@
         <v>-24.21</v>
       </c>
       <c r="I364" s="4" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J364" s="4" t="n">
         <v>18.08</v>
@@ -28055,7 +28055,7 @@
         <v>7.12</v>
       </c>
       <c r="I365" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J365" t="n">
         <v>18</v>
@@ -28130,7 +28130,7 @@
         <v>6.38</v>
       </c>
       <c r="I366" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J366" t="n">
         <v>17.91</v>
@@ -28205,7 +28205,7 @@
         <v>0.15</v>
       </c>
       <c r="I367" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J367" t="n">
         <v>18.04</v>
@@ -28280,7 +28280,7 @@
         <v>-7.86</v>
       </c>
       <c r="I368" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J368" t="n">
         <v>18.11</v>
@@ -28355,7 +28355,7 @@
         <v>11.03</v>
       </c>
       <c r="I369" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J369" t="n">
         <v>18.45</v>
@@ -28430,7 +28430,7 @@
         <v>-1.63</v>
       </c>
       <c r="I370" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J370" t="n">
         <v>18.87</v>
@@ -28505,7 +28505,7 @@
         <v>4.49</v>
       </c>
       <c r="I371" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J371" t="n">
         <v>19.12</v>
@@ -28580,7 +28580,7 @@
         <v>-2.99</v>
       </c>
       <c r="I372" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J372" t="n">
         <v>19.41</v>
@@ -28655,7 +28655,7 @@
         <v>0.91</v>
       </c>
       <c r="I373" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J373" t="n">
         <v>19.67</v>
@@ -28730,7 +28730,7 @@
         <v>-8.49</v>
       </c>
       <c r="I374" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J374" t="n">
         <v>19.67</v>
@@ -28809,7 +28809,7 @@
         <v>5.06</v>
       </c>
       <c r="I375" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J375" t="n">
         <v>19.76</v>
@@ -28884,7 +28884,7 @@
         <v>2.68</v>
       </c>
       <c r="I376" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J376" t="n">
         <v>19.95</v>
@@ -28959,7 +28959,7 @@
         <v>13.44</v>
       </c>
       <c r="I377" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J377" t="n">
         <v>20.26</v>
@@ -29034,7 +29034,7 @@
         <v>1.58</v>
       </c>
       <c r="I378" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J378" t="n">
         <v>20.63</v>
@@ -29109,7 +29109,7 @@
         <v>1.51</v>
       </c>
       <c r="I379" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J379" t="n">
         <v>20.96</v>
@@ -29184,7 +29184,7 @@
         <v>-12.52</v>
       </c>
       <c r="I380" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J380" t="n">
         <v>21</v>
@@ -29259,7 +29259,7 @@
         <v>8.970000000000001</v>
       </c>
       <c r="I381" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J381" t="n">
         <v>21.09</v>
@@ -29334,7 +29334,7 @@
         <v>-19.51</v>
       </c>
       <c r="I382" s="4" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J382" s="4" t="n">
         <v>20.94</v>
@@ -29413,7 +29413,7 @@
         <v>0.16</v>
       </c>
       <c r="I383" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J383" t="n">
         <v>20.69</v>
@@ -29488,7 +29488,7 @@
         <v>-1.72</v>
       </c>
       <c r="I384" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J384" t="n">
         <v>20.71</v>
@@ -29563,7 +29563,7 @@
         <v>11.65</v>
       </c>
       <c r="I385" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J385" t="n">
         <v>20.78</v>
@@ -29638,7 +29638,7 @@
         <v>-1.81</v>
       </c>
       <c r="I386" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J386" t="n">
         <v>20.76</v>
@@ -29713,7 +29713,7 @@
         <v>12.52</v>
       </c>
       <c r="I387" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J387" t="n">
         <v>20.87</v>
@@ -29788,7 +29788,7 @@
         <v>5.41</v>
       </c>
       <c r="I388" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J388" t="n">
         <v>21.12</v>
@@ -29863,7 +29863,7 @@
         <v>-10.52</v>
       </c>
       <c r="I389" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J389" t="n">
         <v>21.14</v>
@@ -29938,7 +29938,7 @@
         <v>-5.31</v>
       </c>
       <c r="I390" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J390" t="n">
         <v>21.13</v>
@@ -30017,7 +30017,7 @@
         <v>7.2</v>
       </c>
       <c r="I391" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J391" t="n">
         <v>21.14</v>
@@ -30092,7 +30092,7 @@
         <v>-5.51</v>
       </c>
       <c r="I392" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J392" t="n">
         <v>21.12</v>
@@ -30171,7 +30171,7 @@
         <v>5.25</v>
       </c>
       <c r="I393" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J393" t="n">
         <v>21.14</v>
@@ -30246,7 +30246,7 @@
         <v>-6.75</v>
       </c>
       <c r="I394" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J394" t="n">
         <v>21.18</v>
@@ -30325,7 +30325,7 @@
         <v>5.34</v>
       </c>
       <c r="I395" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J395" t="n">
         <v>21.23</v>
@@ -30400,7 +30400,7 @@
         <v>8.82</v>
       </c>
       <c r="I396" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J396" t="n">
         <v>21.34</v>
@@ -30475,7 +30475,7 @@
         <v>-0.74</v>
       </c>
       <c r="I397" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J397" t="n">
         <v>21.31</v>
@@ -30550,7 +30550,7 @@
         <v>-7.77</v>
       </c>
       <c r="I398" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J398" t="n">
         <v>21.17</v>
@@ -30629,7 +30629,7 @@
         <v>-4.57</v>
       </c>
       <c r="I399" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J399" t="n">
         <v>20.96</v>
@@ -30704,7 +30704,7 @@
         <v>-11.97</v>
       </c>
       <c r="I400" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J400" t="n">
         <v>20.79</v>
@@ -30783,7 +30783,7 @@
         <v>1.13</v>
       </c>
       <c r="I401" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J401" t="n">
         <v>20.52</v>
@@ -30858,7 +30858,7 @@
         <v>-11.82</v>
       </c>
       <c r="I402" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J402" t="n">
         <v>20.38</v>
@@ -30937,7 +30937,7 @@
         <v>-6.48</v>
       </c>
       <c r="I403" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J403" t="n">
         <v>20.19</v>
@@ -31012,7 +31012,7 @@
         <v>-12.16</v>
       </c>
       <c r="I404" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J404" t="n">
         <v>19.92</v>
@@ -31087,7 +31087,7 @@
         <v>-7.12</v>
       </c>
       <c r="I405" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J405" t="n">
         <v>19.5</v>
@@ -31166,7 +31166,7 @@
         <v>-11.41</v>
       </c>
       <c r="I406" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J406" t="n">
         <v>19.03</v>
@@ -31245,7 +31245,7 @@
         <v>12.03</v>
       </c>
       <c r="I407" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J407" t="n">
         <v>18.5</v>
@@ -31324,7 +31324,7 @@
         <v>-4.87</v>
       </c>
       <c r="I408" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J408" t="n">
         <v>17.88</v>
@@ -31403,7 +31403,7 @@
         <v>5.29</v>
       </c>
       <c r="I409" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J409" t="n">
         <v>17.41</v>
@@ -31482,7 +31482,7 @@
         <v>-14.66</v>
       </c>
       <c r="I410" s="4" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J410" s="4" t="n">
         <v>16.91</v>
@@ -31561,7 +31561,7 @@
         <v>3.83</v>
       </c>
       <c r="I411" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J411" t="n">
         <v>16.36</v>
@@ -31640,7 +31640,7 @@
         <v>2.93</v>
       </c>
       <c r="I412" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J412" t="n">
         <v>15.89</v>
@@ -31719,7 +31719,7 @@
         <v>8.91</v>
       </c>
       <c r="I413" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J413" t="n">
         <v>15.41</v>
@@ -31798,7 +31798,7 @@
         <v>16.19</v>
       </c>
       <c r="I414" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J414" t="n">
         <v>15.1</v>
@@ -31873,7 +31873,7 @@
         <v>-7.62</v>
       </c>
       <c r="I415" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J415" t="n">
         <v>14.68</v>
@@ -31891,7 +31891,7 @@
         <v>34.06</v>
       </c>
       <c r="O415" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="P415" t="inlineStr">
         <is>
@@ -31917,6 +31917,79 @@
       <c r="W415" s="2" t="n">
         <v>151</v>
       </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="4" t="inlineStr">
+        <is>
+          <t>KORU</t>
+        </is>
+      </c>
+      <c r="B416" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C416" s="4" t="n">
+        <v>10.84</v>
+      </c>
+      <c r="D416" s="4" t="n">
+        <v>11.13</v>
+      </c>
+      <c r="E416" s="4" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="F416" s="4" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="G416" s="4" t="n">
+        <v>27583807</v>
+      </c>
+      <c r="H416" s="5" t="n">
+        <v>-16.81</v>
+      </c>
+      <c r="I416" s="4" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="J416" s="4" t="n">
+        <v>14.06</v>
+      </c>
+      <c r="K416" s="4" t="n">
+        <v>18.45</v>
+      </c>
+      <c r="L416" s="4" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="M416" s="4" t="n">
+        <v>24.43</v>
+      </c>
+      <c r="N416" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="O416" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="P416" s="4" t="inlineStr">
+        <is>
+          <t>fear</t>
+        </is>
+      </c>
+      <c r="Q416" s="4" t="inlineStr">
+        <is>
+          <t>2x BUY</t>
+        </is>
+      </c>
+      <c r="R416" s="4" t="inlineStr"/>
+      <c r="S416" s="4" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="T416" s="6" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="U416" s="6" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="V416" s="4" t="inlineStr"/>
+      <c r="W416" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -31867,7 +31867,7 @@
         <v>12.73</v>
       </c>
       <c r="G415" t="n">
-        <v>37256500</v>
+        <v>39318300</v>
       </c>
       <c r="H415" s="1" t="n">
         <v>-7.62</v>
@@ -31936,16 +31936,16 @@
         <v>11.13</v>
       </c>
       <c r="E416" s="4" t="n">
-        <v>10.57</v>
+        <v>10.11</v>
       </c>
       <c r="F416" s="4" t="n">
-        <v>10.59</v>
+        <v>10.63</v>
       </c>
       <c r="G416" s="4" t="n">
-        <v>27583807</v>
+        <v>43866047</v>
       </c>
       <c r="H416" s="5" t="n">
-        <v>-16.81</v>
+        <v>-16.5</v>
       </c>
       <c r="I416" s="4" t="n">
         <v>13.7</v>
@@ -31963,10 +31963,10 @@
         <v>24.43</v>
       </c>
       <c r="N416" s="6" t="n">
-        <v>34</v>
+        <v>34.08</v>
       </c>
       <c r="O416" s="4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P416" s="4" t="inlineStr">
         <is>
@@ -31980,13 +31980,13 @@
       </c>
       <c r="R416" s="4" t="inlineStr"/>
       <c r="S416" s="4" t="n">
-        <v>4.95</v>
+        <v>4.93</v>
       </c>
       <c r="T416" s="6" t="n">
         <v>19.4</v>
       </c>
       <c r="U416" s="6" t="n">
-        <v>12.7</v>
+        <v>19.3</v>
       </c>
       <c r="V416" s="4" t="inlineStr"/>
       <c r="W416" s="6" t="inlineStr"/>

--- a/US_stock/KORU_table.xlsx
+++ b/US_stock/KORU_table.xlsx
@@ -608,7 +608,7 @@
         <v>3.11</v>
       </c>
       <c r="I2" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J2" t="n">
         <v>2.19</v>
@@ -687,7 +687,7 @@
         <v>7.04</v>
       </c>
       <c r="I3" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J3" t="n">
         <v>2.19</v>
@@ -762,7 +762,7 @@
         <v>-3.76</v>
       </c>
       <c r="I4" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J4" t="n">
         <v>2.19</v>
@@ -841,7 +841,7 @@
         <v>4.88</v>
       </c>
       <c r="I5" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J5" t="n">
         <v>2.19</v>
@@ -916,7 +916,7 @@
         <v>8.84</v>
       </c>
       <c r="I6" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J6" t="n">
         <v>2.19</v>
@@ -991,7 +991,7 @@
         <v>-4.7</v>
       </c>
       <c r="I7" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J7" t="n">
         <v>2.18</v>
@@ -1066,7 +1066,7 @@
         <v>1.35</v>
       </c>
       <c r="I8" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J8" t="n">
         <v>2.17</v>
@@ -1141,7 +1141,7 @@
         <v>-2.65</v>
       </c>
       <c r="I9" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J9" t="n">
         <v>2.16</v>
@@ -1216,7 +1216,7 @@
         <v>0.91</v>
       </c>
       <c r="I10" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J10" t="n">
         <v>2.15</v>
@@ -1291,7 +1291,7 @@
         <v>2.25</v>
       </c>
       <c r="I11" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J11" t="n">
         <v>2.15</v>
@@ -1366,7 +1366,7 @@
         <v>-1.32</v>
       </c>
       <c r="I12" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J12" t="n">
         <v>2.14</v>
@@ -1441,7 +1441,7 @@
         <v>-1.34</v>
       </c>
       <c r="I13" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J13" t="n">
         <v>2.13</v>
@@ -1516,7 +1516,7 @@
         <v>-1.81</v>
       </c>
       <c r="I14" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J14" t="n">
         <v>2.13</v>
@@ -1591,7 +1591,7 @@
         <v>-9.220000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J15" t="n">
         <v>2.13</v>
@@ -1670,7 +1670,7 @@
         <v>-4.06</v>
       </c>
       <c r="I16" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J16" t="n">
         <v>2.13</v>
@@ -1745,7 +1745,7 @@
         <v>4.76</v>
       </c>
       <c r="I17" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J17" t="n">
         <v>2.13</v>
@@ -1820,7 +1820,7 @@
         <v>-1.01</v>
       </c>
       <c r="I18" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J18" t="n">
         <v>2.12</v>
@@ -1895,7 +1895,7 @@
         <v>-8.67</v>
       </c>
       <c r="I19" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J19" t="n">
         <v>2.1</v>
@@ -1974,7 +1974,7 @@
         <v>-10.61</v>
       </c>
       <c r="I20" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J20" t="n">
         <v>2.08</v>
@@ -2057,7 +2057,7 @@
         <v>-3.12</v>
       </c>
       <c r="I21" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J21" t="n">
         <v>2.06</v>
@@ -2140,7 +2140,7 @@
         <v>-10.32</v>
       </c>
       <c r="I22" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J22" t="n">
         <v>2.03</v>
@@ -2223,7 +2223,7 @@
         <v>24.46</v>
       </c>
       <c r="I23" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J23" t="n">
         <v>2.01</v>
@@ -2302,7 +2302,7 @@
         <v>-6.94</v>
       </c>
       <c r="I24" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J24" t="n">
         <v>1.99</v>
@@ -2381,7 +2381,7 @@
         <v>14.29</v>
       </c>
       <c r="I25" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J25" t="n">
         <v>1.97</v>
@@ -2460,7 +2460,7 @@
         <v>-0.54</v>
       </c>
       <c r="I26" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J26" t="n">
         <v>1.95</v>
@@ -2535,7 +2535,7 @@
         <v>0.55</v>
       </c>
       <c r="I27" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J27" t="n">
         <v>1.93</v>
@@ -2610,7 +2610,7 @@
         <v>-2.17</v>
       </c>
       <c r="I28" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J28" t="n">
         <v>1.9</v>
@@ -2689,7 +2689,7 @@
         <v>1.67</v>
       </c>
       <c r="I29" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J29" t="n">
         <v>1.89</v>
@@ -2768,7 +2768,7 @@
         <v>0.55</v>
       </c>
       <c r="I30" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J30" t="n">
         <v>1.87</v>
@@ -2843,7 +2843,7 @@
         <v>2.17</v>
       </c>
       <c r="I31" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J31" t="n">
         <v>1.85</v>
@@ -2918,7 +2918,7 @@
         <v>3.72</v>
       </c>
       <c r="I32" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J32" t="n">
         <v>1.83</v>
@@ -2997,7 +2997,7 @@
         <v>2.05</v>
       </c>
       <c r="I33" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J33" t="n">
         <v>1.82</v>
@@ -3072,7 +3072,7 @@
         <v>-0.5</v>
       </c>
       <c r="I34" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J34" t="n">
         <v>1.81</v>
@@ -3147,7 +3147,7 @@
         <v>-1.01</v>
       </c>
       <c r="I35" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J35" t="n">
         <v>1.81</v>
@@ -3222,7 +3222,7 @@
         <v>2.55</v>
       </c>
       <c r="I36" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J36" t="n">
         <v>1.82</v>
@@ -3297,7 +3297,7 @@
         <v>0.5</v>
       </c>
       <c r="I37" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J37" t="n">
         <v>1.82</v>
@@ -3372,7 +3372,7 @@
         <v>-2.97</v>
       </c>
       <c r="I38" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J38" t="n">
         <v>1.82</v>
@@ -3447,7 +3447,7 @@
         <v>10.71</v>
       </c>
       <c r="I39" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J39" t="n">
         <v>1.84</v>
@@ -3522,7 +3522,7 @@
         <v>4.15</v>
       </c>
       <c r="I40" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J40" t="n">
         <v>1.87</v>
@@ -3597,7 +3597,7 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J41" t="n">
         <v>1.91</v>
@@ -3672,7 +3672,7 @@
         <v>-3.54</v>
       </c>
       <c r="I42" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J42" t="n">
         <v>1.95</v>
@@ -3747,7 +3747,7 @@
         <v>-3.21</v>
       </c>
       <c r="I43" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J43" t="n">
         <v>1.97</v>
@@ -3822,7 +3822,7 @@
         <v>2.84</v>
       </c>
       <c r="I44" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J44" t="n">
         <v>1.99</v>
@@ -3897,7 +3897,7 @@
         <v>1.38</v>
       </c>
       <c r="I45" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J45" t="n">
         <v>2.01</v>
@@ -3972,7 +3972,7 @@
         <v>0.45</v>
       </c>
       <c r="I46" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J46" t="n">
         <v>2.03</v>
@@ -4047,7 +4047,7 @@
         <v>2.71</v>
       </c>
       <c r="I47" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J47" t="n">
         <v>2.05</v>
@@ -4122,7 +4122,7 @@
         <v>0.88</v>
       </c>
       <c r="I48" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J48" t="n">
         <v>2.08</v>
@@ -4197,7 +4197,7 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J49" t="n">
         <v>2.1</v>
@@ -4272,7 +4272,7 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J50" t="n">
         <v>2.12</v>
@@ -4347,7 +4347,7 @@
         <v>-2.18</v>
       </c>
       <c r="I51" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J51" t="n">
         <v>2.14</v>
@@ -4422,7 +4422,7 @@
         <v>3.57</v>
       </c>
       <c r="I52" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J52" t="n">
         <v>2.16</v>
@@ -4497,7 +4497,7 @@
         <v>-3.88</v>
       </c>
       <c r="I53" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J53" t="n">
         <v>2.17</v>
@@ -4572,7 +4572,7 @@
         <v>3.14</v>
       </c>
       <c r="I54" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J54" t="n">
         <v>2.19</v>
@@ -4647,7 +4647,7 @@
         <v>4.78</v>
       </c>
       <c r="I55" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J55" t="n">
         <v>2.21</v>
@@ -4722,7 +4722,7 @@
         <v>3.73</v>
       </c>
       <c r="I56" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J56" t="n">
         <v>2.23</v>
@@ -4797,7 +4797,7 @@
         <v>5.2</v>
       </c>
       <c r="I57" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J57" t="n">
         <v>2.26</v>
@@ -4872,7 +4872,7 @@
         <v>-5.7</v>
       </c>
       <c r="I58" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J58" t="n">
         <v>2.29</v>
@@ -4947,7 +4947,7 @@
         <v>5.65</v>
       </c>
       <c r="I59" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J59" t="n">
         <v>2.31</v>
@@ -5022,7 +5022,7 @@
         <v>1.15</v>
       </c>
       <c r="I60" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J60" t="n">
         <v>2.33</v>
@@ -5097,7 +5097,7 @@
         <v>9.43</v>
       </c>
       <c r="I61" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J61" t="n">
         <v>2.36</v>
@@ -5172,7 +5172,7 @@
         <v>6.55</v>
       </c>
       <c r="I62" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J62" t="n">
         <v>2.41</v>
@@ -5247,7 +5247,7 @@
         <v>0.65</v>
       </c>
       <c r="I63" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J63" t="n">
         <v>2.46</v>
@@ -5322,7 +5322,7 @@
         <v>4.5</v>
       </c>
       <c r="I64" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J64" t="n">
         <v>2.51</v>
@@ -5397,7 +5397,7 @@
         <v>-1.54</v>
       </c>
       <c r="I65" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J65" t="n">
         <v>2.56</v>
@@ -5472,7 +5472,7 @@
         <v>3.75</v>
       </c>
       <c r="I66" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J66" t="n">
         <v>2.62</v>
@@ -5547,7 +5547,7 @@
         <v>3.31</v>
       </c>
       <c r="I67" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J67" t="n">
         <v>2.68</v>
@@ -5622,7 +5622,7 @@
         <v>-5.83</v>
       </c>
       <c r="I68" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J68" t="n">
         <v>2.72</v>
@@ -5697,7 +5697,7 @@
         <v>8.050000000000001</v>
       </c>
       <c r="I69" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J69" t="n">
         <v>2.78</v>
@@ -5772,7 +5772,7 @@
         <v>-6.88</v>
       </c>
       <c r="I70" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J70" t="n">
         <v>2.83</v>
@@ -5847,7 +5847,7 @@
         <v>5.23</v>
       </c>
       <c r="I71" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J71" t="n">
         <v>2.89</v>
@@ -5922,7 +5922,7 @@
         <v>2.92</v>
       </c>
       <c r="I72" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J72" t="n">
         <v>2.95</v>
@@ -5997,7 +5997,7 @@
         <v>3.69</v>
       </c>
       <c r="I73" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J73" t="n">
         <v>3.02</v>
@@ -6072,7 +6072,7 @@
         <v>14.25</v>
       </c>
       <c r="I74" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J74" t="n">
         <v>3.12</v>
@@ -6147,7 +6147,7 @@
         <v>-1.2</v>
       </c>
       <c r="I75" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J75" t="n">
         <v>3.2</v>
@@ -6222,7 +6222,7 @@
         <v>-1.94</v>
       </c>
       <c r="I76" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J76" t="n">
         <v>3.28</v>
@@ -6297,7 +6297,7 @@
         <v>-4.95</v>
       </c>
       <c r="I77" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J77" t="n">
         <v>3.34</v>
@@ -6372,7 +6372,7 @@
         <v>4.17</v>
       </c>
       <c r="I78" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J78" t="n">
         <v>3.42</v>
@@ -6447,7 +6447,7 @@
         <v>-0.5</v>
       </c>
       <c r="I79" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J79" t="n">
         <v>3.48</v>
@@ -6522,7 +6522,7 @@
         <v>1.26</v>
       </c>
       <c r="I80" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J80" t="n">
         <v>3.55</v>
@@ -6597,7 +6597,7 @@
         <v>2.73</v>
       </c>
       <c r="I81" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J81" t="n">
         <v>3.61</v>
@@ -6672,7 +6672,7 @@
         <v>-10.39</v>
       </c>
       <c r="I82" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J82" t="n">
         <v>3.65</v>
@@ -6747,7 +6747,7 @@
         <v>8.09</v>
       </c>
       <c r="I83" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J83" t="n">
         <v>3.69</v>
@@ -6822,7 +6822,7 @@
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J84" t="n">
         <v>3.73</v>
@@ -6897,7 +6897,7 @@
         <v>4.49</v>
       </c>
       <c r="I85" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J85" t="n">
         <v>3.78</v>
@@ -6972,7 +6972,7 @@
         <v>-2.39</v>
       </c>
       <c r="I86" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J86" t="n">
         <v>3.82</v>
@@ -7047,7 +7047,7 @@
         <v>2.44</v>
       </c>
       <c r="I87" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J87" t="n">
         <v>3.85</v>
@@ -7122,7 +7122,7 @@
         <v>-0.48</v>
       </c>
       <c r="I88" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J88" t="n">
         <v>3.9</v>
@@ -7197,7 +7197,7 @@
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J89" t="n">
         <v>3.94</v>
@@ -7272,7 +7272,7 @@
         <v>-0.24</v>
       </c>
       <c r="I90" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J90" t="n">
         <v>3.98</v>
@@ -7347,7 +7347,7 @@
         <v>-2.64</v>
       </c>
       <c r="I91" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J91" t="n">
         <v>4.01</v>
@@ -7422,7 +7422,7 @@
         <v>5.93</v>
       </c>
       <c r="I92" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J92" t="n">
         <v>4.05</v>
@@ -7497,7 +7497,7 @@
         <v>-3.73</v>
       </c>
       <c r="I93" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J93" t="n">
         <v>4.07</v>
@@ -7572,7 +7572,7 @@
         <v>3.63</v>
       </c>
       <c r="I94" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J94" t="n">
         <v>4.08</v>
@@ -7647,7 +7647,7 @@
         <v>-2.1</v>
       </c>
       <c r="I95" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J95" t="n">
         <v>4.08</v>
@@ -7722,7 +7722,7 @@
         <v>-0.48</v>
       </c>
       <c r="I96" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J96" t="n">
         <v>4.09</v>
@@ -7797,7 +7797,7 @@
         <v>-2.16</v>
       </c>
       <c r="I97" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J97" t="n">
         <v>4.1</v>
@@ -7876,7 +7876,7 @@
         <v>3.19</v>
       </c>
       <c r="I98" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J98" t="n">
         <v>4.11</v>
@@ -7951,7 +7951,7 @@
         <v>0.95</v>
       </c>
       <c r="I99" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J99" t="n">
         <v>4.13</v>
@@ -8026,7 +8026,7 @@
         <v>-3.76</v>
       </c>
       <c r="I100" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J100" t="n">
         <v>4.13</v>
@@ -8105,7 +8105,7 @@
         <v>-9.050000000000001</v>
       </c>
       <c r="I101" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J101" t="n">
         <v>4.11</v>
@@ -8180,7 +8180,7 @@
         <v>7.26</v>
       </c>
       <c r="I102" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J102" t="n">
         <v>4.12</v>
@@ -8255,7 +8255,7 @@
         <v>2.26</v>
       </c>
       <c r="I103" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J103" t="n">
         <v>4.13</v>
@@ -8330,7 +8330,7 @@
         <v>0.98</v>
       </c>
       <c r="I104" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J104" t="n">
         <v>4.13</v>
@@ -8405,7 +8405,7 @@
         <v>0.97</v>
       </c>
       <c r="I105" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J105" t="n">
         <v>4.13</v>
@@ -8480,7 +8480,7 @@
         <v>0.24</v>
       </c>
       <c r="I106" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J106" t="n">
         <v>4.13</v>
@@ -8555,7 +8555,7 @@
         <v>-1.92</v>
       </c>
       <c r="I107" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J107" t="n">
         <v>4.13</v>
@@ -8634,7 +8634,7 @@
         <v>4.16</v>
       </c>
       <c r="I108" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J108" t="n">
         <v>4.13</v>
@@ -8709,7 +8709,7 @@
         <v>2.58</v>
       </c>
       <c r="I109" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J109" t="n">
         <v>4.14</v>
@@ -8784,7 +8784,7 @@
         <v>-4.12</v>
       </c>
       <c r="I110" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J110" t="n">
         <v>4.14</v>
@@ -8859,7 +8859,7 @@
         <v>-1.19</v>
       </c>
       <c r="I111" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J111" t="n">
         <v>4.15</v>
@@ -8938,7 +8938,7 @@
         <v>-2.42</v>
       </c>
       <c r="I112" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J112" t="n">
         <v>4.14</v>
@@ -9013,7 +9013,7 @@
         <v>-5.45</v>
       </c>
       <c r="I113" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J113" t="n">
         <v>4.12</v>
@@ -9088,7 +9088,7 @@
         <v>-0.52</v>
       </c>
       <c r="I114" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J114" t="n">
         <v>4.1</v>
@@ -9163,7 +9163,7 @@
         <v>-0.79</v>
       </c>
       <c r="I115" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J115" t="n">
         <v>4.08</v>
@@ -9242,7 +9242,7 @@
         <v>9.81</v>
       </c>
       <c r="I116" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J116" t="n">
         <v>4.07</v>
@@ -9317,7 +9317,7 @@
         <v>-3.38</v>
       </c>
       <c r="I117" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J117" t="n">
         <v>4.07</v>
@@ -9396,7 +9396,7 @@
         <v>-1.5</v>
       </c>
       <c r="I118" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J118" t="n">
         <v>4.06</v>
@@ -9471,7 +9471,7 @@
         <v>0.51</v>
       </c>
       <c r="I119" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J119" t="n">
         <v>4.04</v>
@@ -9546,7 +9546,7 @@
         <v>4.55</v>
       </c>
       <c r="I120" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J120" t="n">
         <v>4.04</v>
@@ -9621,7 +9621,7 @@
         <v>-5.56</v>
       </c>
       <c r="I121" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J121" t="n">
         <v>4.05</v>
@@ -9700,7 +9700,7 @@
         <v>-1.53</v>
       </c>
       <c r="I122" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J122" t="n">
         <v>4.05</v>
@@ -9775,7 +9775,7 @@
         <v>3.9</v>
       </c>
       <c r="I123" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J123" t="n">
         <v>4.04</v>
@@ -9850,7 +9850,7 @@
         <v>0.75</v>
       </c>
       <c r="I124" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J124" t="n">
         <v>4.04</v>
@@ -9925,7 +9925,7 @@
         <v>2.23</v>
       </c>
       <c r="I125" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J125" t="n">
         <v>4.04</v>
@@ -10000,7 +10000,7 @@
         <v>1.94</v>
       </c>
       <c r="I126" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J126" t="n">
         <v>4.04</v>
@@ -10075,7 +10075,7 @@
         <v>3.1</v>
       </c>
       <c r="I127" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J127" t="n">
         <v>4.05</v>
@@ -10150,7 +10150,7 @@
         <v>6.93</v>
       </c>
       <c r="I128" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J128" t="n">
         <v>4.07</v>
@@ -10225,7 +10225,7 @@
         <v>4.75</v>
       </c>
       <c r="I129" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J129" t="n">
         <v>4.09</v>
@@ -10300,7 +10300,7 @@
         <v>3.09</v>
       </c>
       <c r="I130" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J130" t="n">
         <v>4.13</v>
@@ -10375,7 +10375,7 @@
         <v>2</v>
       </c>
       <c r="I131" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J131" t="n">
         <v>4.18</v>
@@ -10450,7 +10450,7 @@
         <v>5.69</v>
       </c>
       <c r="I132" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J132" t="n">
         <v>4.25</v>
@@ -10525,7 +10525,7 @@
         <v>-3.34</v>
       </c>
       <c r="I133" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J133" t="n">
         <v>4.32</v>
@@ -10600,7 +10600,7 @@
         <v>3.65</v>
       </c>
       <c r="I134" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J134" t="n">
         <v>4.4</v>
@@ -10675,7 +10675,7 @@
         <v>-2.96</v>
       </c>
       <c r="I135" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J135" t="n">
         <v>4.47</v>
@@ -10750,7 +10750,7 @@
         <v>5.92</v>
       </c>
       <c r="I136" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J136" t="n">
         <v>4.54</v>
@@ -10825,7 +10825,7 @@
         <v>-0.54</v>
       </c>
       <c r="I137" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J137" t="n">
         <v>4.62</v>
@@ -10900,7 +10900,7 @@
         <v>-5.25</v>
       </c>
       <c r="I138" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J138" t="n">
         <v>4.68</v>
@@ -10975,7 +10975,7 @@
         <v>-0.57</v>
       </c>
       <c r="I139" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J139" t="n">
         <v>4.74</v>
@@ -11050,7 +11050,7 @@
         <v>-3.85</v>
       </c>
       <c r="I140" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J140" t="n">
         <v>4.79</v>
@@ -11125,7 +11125,7 @@
         <v>5</v>
       </c>
       <c r="I141" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J141" t="n">
         <v>4.85</v>
@@ -11200,7 +11200,7 @@
         <v>-0.38</v>
       </c>
       <c r="I142" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J142" t="n">
         <v>4.92</v>
@@ -11275,7 +11275,7 @@
         <v>6.5</v>
       </c>
       <c r="I143" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J143" t="n">
         <v>5</v>
@@ -11350,7 +11350,7 @@
         <v>6.1</v>
       </c>
       <c r="I144" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J144" t="n">
         <v>5.1</v>
@@ -11425,7 +11425,7 @@
         <v>1.18</v>
       </c>
       <c r="I145" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J145" t="n">
         <v>5.19</v>
@@ -11500,7 +11500,7 @@
         <v>3.18</v>
       </c>
       <c r="I146" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J146" t="n">
         <v>5.29</v>
@@ -11575,7 +11575,7 @@
         <v>-4.86</v>
       </c>
       <c r="I147" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J147" t="n">
         <v>5.36</v>
@@ -11650,7 +11650,7 @@
         <v>2.73</v>
       </c>
       <c r="I148" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J148" t="n">
         <v>5.44</v>
@@ -11725,7 +11725,7 @@
         <v>-2.65</v>
       </c>
       <c r="I149" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J149" t="n">
         <v>5.49</v>
@@ -11800,7 +11800,7 @@
         <v>-9.710000000000001</v>
       </c>
       <c r="I150" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J150" t="n">
         <v>5.5</v>
@@ -11879,7 +11879,7 @@
         <v>10.38</v>
       </c>
       <c r="I151" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J151" t="n">
         <v>5.54</v>
@@ -11954,7 +11954,7 @@
         <v>-3.25</v>
       </c>
       <c r="I152" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J152" t="n">
         <v>5.55</v>
@@ -12029,7 +12029,7 @@
         <v>8.83</v>
       </c>
       <c r="I153" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J153" t="n">
         <v>5.6</v>
@@ -12104,7 +12104,7 @@
         <v>9.58</v>
       </c>
       <c r="I154" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J154" t="n">
         <v>5.67</v>
@@ -12179,7 +12179,7 @@
         <v>2.07</v>
       </c>
       <c r="I155" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J155" t="n">
         <v>5.75</v>
@@ -12254,7 +12254,7 @@
         <v>6.68</v>
       </c>
       <c r="I156" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J156" t="n">
         <v>5.84</v>
@@ -12329,7 +12329,7 @@
         <v>-6.12</v>
       </c>
       <c r="I157" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J157" t="n">
         <v>5.91</v>
@@ -12404,7 +12404,7 @@
         <v>2.75</v>
       </c>
       <c r="I158" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J158" t="n">
         <v>6</v>
@@ -12479,7 +12479,7 @@
         <v>1.97</v>
       </c>
       <c r="I159" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J159" t="n">
         <v>6.1</v>
@@ -12554,7 +12554,7 @@
         <v>6.64</v>
       </c>
       <c r="I160" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J160" t="n">
         <v>6.24</v>
@@ -12629,7 +12629,7 @@
         <v>7.39</v>
       </c>
       <c r="I161" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J161" t="n">
         <v>6.39</v>
@@ -12704,7 +12704,7 @@
         <v>0.36</v>
       </c>
       <c r="I162" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J162" t="n">
         <v>6.54</v>
@@ -12779,7 +12779,7 @@
         <v>7.82</v>
       </c>
       <c r="I163" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J163" t="n">
         <v>6.71</v>
@@ -12854,7 +12854,7 @@
         <v>-5.02</v>
       </c>
       <c r="I164" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J164" t="n">
         <v>6.84</v>
@@ -12929,7 +12929,7 @@
         <v>5.17</v>
       </c>
       <c r="I165" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J165" t="n">
         <v>6.99</v>
@@ -13004,7 +13004,7 @@
         <v>11.62</v>
       </c>
       <c r="I166" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J166" t="n">
         <v>7.18</v>
@@ -13079,7 +13079,7 @@
         <v>-14.81</v>
       </c>
       <c r="I167" s="4" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J167" s="4" t="n">
         <v>7.32</v>
@@ -13154,7 +13154,7 @@
         <v>2.47</v>
       </c>
       <c r="I168" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J168" t="n">
         <v>7.45</v>
@@ -13229,7 +13229,7 @@
         <v>-9.52</v>
       </c>
       <c r="I169" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J169" t="n">
         <v>7.55</v>
@@ -13304,7 +13304,7 @@
         <v>-5.7</v>
       </c>
       <c r="I170" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J170" t="n">
         <v>7.66</v>
@@ -13383,7 +13383,7 @@
         <v>12.5</v>
       </c>
       <c r="I171" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J171" t="n">
         <v>7.78</v>
@@ -13458,7 +13458,7 @@
         <v>-1.19</v>
       </c>
       <c r="I172" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J172" t="n">
         <v>7.91</v>
@@ -13533,7 +13533,7 @@
         <v>2.06</v>
       </c>
       <c r="I173" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J173" t="n">
         <v>8.029999999999999</v>
@@ -13608,7 +13608,7 @@
         <v>-5.92</v>
       </c>
       <c r="I174" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J174" t="n">
         <v>8.09</v>
@@ -13687,7 +13687,7 @@
         <v>0.38</v>
       </c>
       <c r="I175" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J175" t="n">
         <v>8.140000000000001</v>
@@ -13762,7 +13762,7 @@
         <v>-3.76</v>
       </c>
       <c r="I176" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J176" t="n">
         <v>8.16</v>
@@ -13837,7 +13837,7 @@
         <v>-4.69</v>
       </c>
       <c r="I177" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J177" t="n">
         <v>8.18</v>
@@ -13912,7 +13912,7 @@
         <v>-3.28</v>
       </c>
       <c r="I178" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J178" t="n">
         <v>8.18</v>
@@ -13987,7 +13987,7 @@
         <v>-6.79</v>
       </c>
       <c r="I179" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J179" t="n">
         <v>8.140000000000001</v>
@@ -14066,7 +14066,7 @@
         <v>2.28</v>
       </c>
       <c r="I180" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J180" t="n">
         <v>8.1</v>
@@ -14141,7 +14141,7 @@
         <v>3.71</v>
       </c>
       <c r="I181" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J181" t="n">
         <v>8.029999999999999</v>
@@ -14216,7 +14216,7 @@
         <v>-2</v>
       </c>
       <c r="I182" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J182" t="n">
         <v>7.96</v>
@@ -14291,7 +14291,7 @@
         <v>5.99</v>
       </c>
       <c r="I183" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J183" t="n">
         <v>7.87</v>
@@ -14366,7 +14366,7 @@
         <v>-2.2</v>
       </c>
       <c r="I184" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J184" t="n">
         <v>7.8</v>
@@ -14441,7 +14441,7 @@
         <v>-0.99</v>
       </c>
       <c r="I185" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J185" t="n">
         <v>7.71</v>
@@ -14516,7 +14516,7 @@
         <v>4.69</v>
       </c>
       <c r="I186" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J186" t="n">
         <v>7.58</v>
@@ -14591,7 +14591,7 @@
         <v>2.99</v>
       </c>
       <c r="I187" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J187" t="n">
         <v>7.53</v>
@@ -14666,7 +14666,7 @@
         <v>-3.56</v>
       </c>
       <c r="I188" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J188" t="n">
         <v>7.46</v>
@@ -14745,7 +14745,7 @@
         <v>7.66</v>
       </c>
       <c r="I189" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J189" t="n">
         <v>7.46</v>
@@ -14820,7 +14820,7 @@
         <v>2.41</v>
       </c>
       <c r="I190" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J190" t="n">
         <v>7.49</v>
@@ -14895,7 +14895,7 @@
         <v>1.49</v>
       </c>
       <c r="I191" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J191" t="n">
         <v>7.48</v>
@@ -14970,7 +14970,7 @@
         <v>3.67</v>
       </c>
       <c r="I192" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J192" t="n">
         <v>7.49</v>
@@ -15045,7 +15045,7 @@
         <v>-5.31</v>
       </c>
       <c r="I193" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J193" t="n">
         <v>7.47</v>
@@ -15120,7 +15120,7 @@
         <v>-7.35</v>
       </c>
       <c r="I194" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J194" t="n">
         <v>7.44</v>
@@ -15195,7 +15195,7 @@
         <v>0</v>
       </c>
       <c r="I195" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J195" t="n">
         <v>7.42</v>
@@ -15270,7 +15270,7 @@
         <v>-4.03</v>
       </c>
       <c r="I196" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J196" t="n">
         <v>7.39</v>
@@ -15349,7 +15349,7 @@
         <v>-2.94</v>
       </c>
       <c r="I197" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J197" t="n">
         <v>7.37</v>
@@ -15428,7 +15428,7 @@
         <v>4.91</v>
       </c>
       <c r="I198" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J198" t="n">
         <v>7.38</v>
@@ -15503,7 +15503,7 @@
         <v>4.13</v>
       </c>
       <c r="I199" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J199" t="n">
         <v>7.43</v>
@@ -15578,7 +15578,7 @@
         <v>1.45</v>
       </c>
       <c r="I200" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J200" t="n">
         <v>7.48</v>
@@ -15653,7 +15653,7 @@
         <v>3.26</v>
       </c>
       <c r="I201" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J201" t="n">
         <v>7.53</v>
@@ -15728,7 +15728,7 @@
         <v>5.8</v>
       </c>
       <c r="I202" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J202" t="n">
         <v>7.6</v>
@@ -15803,7 +15803,7 @@
         <v>3.93</v>
       </c>
       <c r="I203" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J203" t="n">
         <v>7.68</v>
@@ -15878,7 +15878,7 @@
         <v>9.06</v>
       </c>
       <c r="I204" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J204" t="n">
         <v>7.8</v>
@@ -15953,7 +15953,7 @@
         <v>-0.53</v>
       </c>
       <c r="I205" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J205" t="n">
         <v>7.92</v>
@@ -16028,7 +16028,7 @@
         <v>-4.02</v>
       </c>
       <c r="I206" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J206" t="n">
         <v>8</v>
@@ -16103,7 +16103,7 @@
         <v>14.76</v>
       </c>
       <c r="I207" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J207" t="n">
         <v>8.15</v>
@@ -16178,7 +16178,7 @@
         <v>7.87</v>
       </c>
       <c r="I208" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J208" t="n">
         <v>8.34</v>
@@ -16253,7 +16253,7 @@
         <v>8.19</v>
       </c>
       <c r="I209" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J209" t="n">
         <v>8.56</v>
@@ -16328,7 +16328,7 @@
         <v>-1.73</v>
       </c>
       <c r="I210" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J210" t="n">
         <v>8.75</v>
@@ -16403,7 +16403,7 @@
         <v>-1.17</v>
       </c>
       <c r="I211" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J211" t="n">
         <v>8.93</v>
@@ -16478,7 +16478,7 @@
         <v>6.01</v>
       </c>
       <c r="I212" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J212" t="n">
         <v>9.130000000000001</v>
@@ -16553,7 +16553,7 @@
         <v>0.48</v>
       </c>
       <c r="I213" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J213" t="n">
         <v>9.359999999999999</v>
@@ -16628,7 +16628,7 @@
         <v>-4.05</v>
       </c>
       <c r="I214" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J214" t="n">
         <v>9.59</v>
@@ -16703,7 +16703,7 @@
         <v>5.72</v>
       </c>
       <c r="I215" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J215" t="n">
         <v>9.859999999999999</v>
@@ -16778,7 +16778,7 @@
         <v>4</v>
       </c>
       <c r="I216" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J216" t="n">
         <v>10.17</v>
@@ -16853,7 +16853,7 @@
         <v>3.17</v>
       </c>
       <c r="I217" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J217" t="n">
         <v>10.5</v>
@@ -16928,7 +16928,7 @@
         <v>-3.51</v>
       </c>
       <c r="I218" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J218" t="n">
         <v>10.8</v>
@@ -17003,7 +17003,7 @@
         <v>12.57</v>
       </c>
       <c r="I219" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J219" t="n">
         <v>11.17</v>
@@ -17078,7 +17078,7 @@
         <v>1.01</v>
       </c>
       <c r="I220" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J220" t="n">
         <v>11.53</v>
@@ -17153,7 +17153,7 @@
         <v>4.99</v>
       </c>
       <c r="I221" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J221" t="n">
         <v>11.92</v>
@@ -17228,7 +17228,7 @@
         <v>-1.46</v>
       </c>
       <c r="I222" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J222" t="n">
         <v>12.28</v>
@@ -17303,7 +17303,7 @@
         <v>13.38</v>
       </c>
       <c r="I223" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J223" t="n">
         <v>12.73</v>
@@ -17378,7 +17378,7 @@
         <v>7.21</v>
       </c>
       <c r="I224" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J224" t="n">
         <v>13.2</v>
@@ -17453,7 +17453,7 @@
         <v>-2.7</v>
       </c>
       <c r="I225" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J225" t="n">
         <v>13.64</v>
@@ -17528,7 +17528,7 @@
         <v>-5.39</v>
       </c>
       <c r="I226" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J226" t="n">
         <v>14.06</v>
@@ -17603,7 +17603,7 @@
         <v>-3.16</v>
       </c>
       <c r="I227" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J227" t="n">
         <v>14.38</v>
@@ -17678,7 +17678,7 @@
         <v>7.78</v>
       </c>
       <c r="I228" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J228" t="n">
         <v>14.72</v>
@@ -17753,7 +17753,7 @@
         <v>-9.199999999999999</v>
       </c>
       <c r="I229" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J229" t="n">
         <v>14.94</v>
@@ -17828,7 +17828,7 @@
         <v>-0.61</v>
       </c>
       <c r="I230" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J230" t="n">
         <v>15.16</v>
@@ -17903,7 +17903,7 @@
         <v>10.87</v>
       </c>
       <c r="I231" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J231" t="n">
         <v>15.48</v>
@@ -17978,7 +17978,7 @@
         <v>3.36</v>
       </c>
       <c r="I232" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J232" t="n">
         <v>15.79</v>
@@ -18053,7 +18053,7 @@
         <v>-3.57</v>
       </c>
       <c r="I233" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J233" t="n">
         <v>16.07</v>
@@ -18128,7 +18128,7 @@
         <v>14.14</v>
       </c>
       <c r="I234" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J234" t="n">
         <v>16.5</v>
@@ -18203,7 +18203,7 @@
         <v>1.06</v>
       </c>
       <c r="I235" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J235" t="n">
         <v>16.9</v>
@@ -18278,7 +18278,7 @@
         <v>7.14</v>
       </c>
       <c r="I236" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J236" t="n">
         <v>17.36</v>
@@ -18353,7 +18353,7 @@
         <v>-6.79</v>
       </c>
       <c r="I237" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J237" t="n">
         <v>17.72</v>
@@ -18428,7 +18428,7 @@
         <v>4.46</v>
       </c>
       <c r="I238" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J238" t="n">
         <v>18.15</v>
@@ -18503,7 +18503,7 @@
         <v>5</v>
       </c>
       <c r="I239" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J239" t="n">
         <v>18.55</v>
@@ -18578,7 +18578,7 @@
         <v>14.65</v>
       </c>
       <c r="I240" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J240" t="n">
         <v>19.1</v>
@@ -18653,7 +18653,7 @@
         <v>-5.03</v>
       </c>
       <c r="I241" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J241" t="n">
         <v>19.56</v>
@@ -18728,7 +18728,7 @@
         <v>10.96</v>
       </c>
       <c r="I242" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J242" t="n">
         <v>20.17</v>
@@ -18803,7 +18803,7 @@
         <v>9.08</v>
       </c>
       <c r="I243" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J243" t="n">
         <v>20.79</v>
@@ -18878,7 +18878,7 @@
         <v>2.79</v>
       </c>
       <c r="I244" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J244" t="n">
         <v>21.4</v>
@@ -18953,7 +18953,7 @@
         <v>1.65</v>
       </c>
       <c r="I245" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J245" t="n">
         <v>22.05</v>
@@ -19028,7 +19028,7 @@
         <v>-7.15</v>
       </c>
       <c r="I246" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J246" t="n">
         <v>22.64</v>
@@ -19103,7 +19103,7 @@
         <v>-31.09</v>
       </c>
       <c r="I247" s="4" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J247" s="4" t="n">
         <v>22.81</v>
@@ -19182,7 +19182,7 @@
         <v>4.37</v>
       </c>
       <c r="I248" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J248" t="n">
         <v>22.95</v>
@@ -19257,7 +19257,7 @@
         <v>-18.45</v>
       </c>
       <c r="I249" s="4" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J249" s="4" t="n">
         <v>22.99</v>
@@ -19332,7 +19332,7 @@
         <v>1.52</v>
       </c>
       <c r="I250" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J250" t="n">
         <v>23.04</v>
@@ -19411,7 +19411,7 @@
         <v>15.68</v>
       </c>
       <c r="I251" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J251" t="n">
         <v>23.14</v>
@@ -19486,7 +19486,7 @@
         <v>-7.25</v>
       </c>
       <c r="I252" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J252" t="n">
         <v>23.13</v>
@@ -19561,7 +19561,7 @@
         <v>5.46</v>
       </c>
       <c r="I253" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J253" t="n">
         <v>23.21</v>
@@ -19636,7 +19636,7 @@
         <v>-20.25</v>
       </c>
       <c r="I254" s="4" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J254" s="4" t="n">
         <v>22.97</v>
@@ -19709,7 +19709,7 @@
         <v>0.64</v>
       </c>
       <c r="I255" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J255" t="n">
         <v>22.71</v>
@@ -19788,7 +19788,7 @@
         <v>21</v>
       </c>
       <c r="I256" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J256" t="n">
         <v>22.55</v>
@@ -19863,7 +19863,7 @@
         <v>3.4</v>
       </c>
       <c r="I257" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J257" t="n">
         <v>22.5</v>
@@ -19938,7 +19938,7 @@
         <v>-5.01</v>
       </c>
       <c r="I258" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J258" t="n">
         <v>22.35</v>
@@ -20013,7 +20013,7 @@
         <v>5.8</v>
       </c>
       <c r="I259" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J259" t="n">
         <v>22.2</v>
@@ -20088,7 +20088,7 @@
         <v>-19.32</v>
       </c>
       <c r="I260" s="4" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J260" s="4" t="n">
         <v>21.69</v>
@@ -20171,7 +20171,7 @@
         <v>17.71</v>
       </c>
       <c r="I261" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J261" t="n">
         <v>21.39</v>
@@ -20246,7 +20246,7 @@
         <v>-11.12</v>
       </c>
       <c r="I262" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J262" t="n">
         <v>20.85</v>
@@ -20325,7 +20325,7 @@
         <v>-2.38</v>
       </c>
       <c r="I263" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J263" t="n">
         <v>20.16</v>
@@ -20400,7 +20400,7 @@
         <v>-17.58</v>
       </c>
       <c r="I264" s="4" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J264" s="4" t="n">
         <v>19.28</v>
@@ -20475,7 +20475,7 @@
         <v>1.48</v>
       </c>
       <c r="I265" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J265" t="n">
         <v>18.39</v>
@@ -20554,7 +20554,7 @@
         <v>-11.24</v>
       </c>
       <c r="I266" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J266" t="n">
         <v>17.54</v>
@@ -20633,7 +20633,7 @@
         <v>16.86</v>
       </c>
       <c r="I267" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J267" t="n">
         <v>17.24</v>
@@ -20708,7 +20708,7 @@
         <v>7.67</v>
       </c>
       <c r="I268" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J268" t="n">
         <v>16.96</v>
@@ -20783,7 +20783,7 @@
         <v>-7.78</v>
       </c>
       <c r="I269" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J269" t="n">
         <v>16.8</v>
@@ -20858,7 +20858,7 @@
         <v>7.02</v>
       </c>
       <c r="I270" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J270" t="n">
         <v>16.69</v>
@@ -20933,7 +20933,7 @@
         <v>2.98</v>
       </c>
       <c r="I271" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J271" t="n">
         <v>16.46</v>
@@ -21012,7 +21012,7 @@
         <v>30.23</v>
       </c>
       <c r="I272" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J272" t="n">
         <v>16.54</v>
@@ -21087,7 +21087,7 @@
         <v>-1.38</v>
       </c>
       <c r="I273" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J273" t="n">
         <v>16.55</v>
@@ -21162,7 +21162,7 @@
         <v>-1.35</v>
       </c>
       <c r="I274" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J274" t="n">
         <v>16.75</v>
@@ -21237,7 +21237,7 @@
         <v>5.08</v>
       </c>
       <c r="I275" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J275" t="n">
         <v>17</v>
@@ -21312,7 +21312,7 @@
         <v>11.98</v>
       </c>
       <c r="I276" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J276" t="n">
         <v>17.2</v>
@@ -21387,7 +21387,7 @@
         <v>-3.84</v>
       </c>
       <c r="I277" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J277" t="n">
         <v>17.32</v>
@@ -21462,7 +21462,7 @@
         <v>5.2</v>
       </c>
       <c r="I278" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J278" t="n">
         <v>17.56</v>
@@ -21537,7 +21537,7 @@
         <v>9.98</v>
       </c>
       <c r="I279" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J279" t="n">
         <v>17.85</v>
@@ -21612,7 +21612,7 @@
         <v>-4.23</v>
       </c>
       <c r="I280" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J280" t="n">
         <v>18.28</v>
@@ -21687,7 +21687,7 @@
         <v>-6.52</v>
       </c>
       <c r="I281" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J281" t="n">
         <v>18.5</v>
@@ -21762,7 +21762,7 @@
         <v>17.54</v>
       </c>
       <c r="I282" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J282" t="n">
         <v>19.01</v>
@@ -21837,7 +21837,7 @@
         <v>-9.65</v>
       </c>
       <c r="I283" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J283" t="n">
         <v>19.42</v>
@@ -21912,7 +21912,7 @@
         <v>7.34</v>
       </c>
       <c r="I284" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J284" t="n">
         <v>20.06</v>
@@ -21987,7 +21987,7 @@
         <v>4.67</v>
       </c>
       <c r="I285" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J285" t="n">
         <v>20.75</v>
@@ -22062,7 +22062,7 @@
         <v>-4.57</v>
       </c>
       <c r="I286" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J286" t="n">
         <v>21.46</v>
@@ -22137,7 +22137,7 @@
         <v>-0.8</v>
       </c>
       <c r="I287" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J287" t="n">
         <v>22.05</v>
@@ -22212,7 +22212,7 @@
         <v>12.69</v>
       </c>
       <c r="I288" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J288" t="n">
         <v>22.76</v>
@@ -22287,7 +22287,7 @@
         <v>2.52</v>
       </c>
       <c r="I289" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J289" t="n">
         <v>23.56</v>
@@ -22362,7 +22362,7 @@
         <v>3.19</v>
       </c>
       <c r="I290" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J290" t="n">
         <v>24.36</v>
@@ -22437,7 +22437,7 @@
         <v>17.69</v>
       </c>
       <c r="I291" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J291" t="n">
         <v>25.41</v>
@@ -22512,7 +22512,7 @@
         <v>14.65</v>
       </c>
       <c r="I292" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J292" t="n">
         <v>26.5</v>
@@ -22587,7 +22587,7 @@
         <v>-8.41</v>
       </c>
       <c r="I293" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J293" t="n">
         <v>27.42</v>
@@ -22662,7 +22662,7 @@
         <v>22.62</v>
       </c>
       <c r="I294" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J294" t="n">
         <v>28.79</v>
@@ -22737,7 +22737,7 @@
         <v>4.33</v>
       </c>
       <c r="I295" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J295" t="n">
         <v>30.21</v>
@@ -22812,7 +22812,7 @@
         <v>-22.56</v>
       </c>
       <c r="I296" s="4" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J296" s="4" t="n">
         <v>30.96</v>
@@ -22887,7 +22887,7 @@
         <v>17.42</v>
       </c>
       <c r="I297" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J297" t="n">
         <v>32.08</v>
@@ -22962,7 +22962,7 @@
         <v>2.91</v>
       </c>
       <c r="I298" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J298" t="n">
         <v>33.2</v>
@@ -23037,7 +23037,7 @@
         <v>-18.31</v>
       </c>
       <c r="I299" s="4" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J299" s="4" t="n">
         <v>33.79</v>
@@ -23112,7 +23112,7 @@
         <v>-5</v>
       </c>
       <c r="I300" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J300" t="n">
         <v>34.34</v>
@@ -23187,7 +23187,7 @@
         <v>-3.36</v>
       </c>
       <c r="I301" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J301" t="n">
         <v>34.91</v>
@@ -23266,7 +23266,7 @@
         <v>10.26</v>
       </c>
       <c r="I302" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J302" t="n">
         <v>35.46</v>
@@ -23341,7 +23341,7 @@
         <v>10.31</v>
       </c>
       <c r="I303" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J303" t="n">
         <v>36.33</v>
@@ -23416,7 +23416,7 @@
         <v>-6.98</v>
       </c>
       <c r="I304" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J304" t="n">
         <v>36.96</v>
@@ -23491,7 +23491,7 @@
         <v>30.06</v>
       </c>
       <c r="I305" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J305" t="n">
         <v>38.12</v>
@@ -23566,7 +23566,7 @@
         <v>-3.57</v>
       </c>
       <c r="I306" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J306" t="n">
         <v>39.25</v>
@@ -23641,7 +23641,7 @@
         <v>12.4</v>
       </c>
       <c r="I307" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J307" t="n">
         <v>40.7</v>
@@ -23716,7 +23716,7 @@
         <v>-0.93</v>
       </c>
       <c r="I308" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J308" t="n">
         <v>41.96</v>
@@ -23791,7 +23791,7 @@
         <v>16.04</v>
       </c>
       <c r="I309" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J309" t="n">
         <v>43.61</v>
@@ -23866,7 +23866,7 @@
         <v>-3.16</v>
       </c>
       <c r="I310" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J310" t="n">
         <v>45.12</v>
@@ -23941,7 +23941,7 @@
         <v>-2.29</v>
       </c>
       <c r="I311" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J311" t="n">
         <v>46.28</v>
@@ -24016,7 +24016,7 @@
         <v>-12.28</v>
       </c>
       <c r="I312" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J312" t="n">
         <v>46.81</v>
@@ -24091,7 +24091,7 @@
         <v>-41.89</v>
       </c>
       <c r="I313" s="4" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J313" s="4" t="n">
         <v>46.41</v>
@@ -24170,7 +24170,7 @@
         <v>16.3</v>
       </c>
       <c r="I314" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J314" t="n">
         <v>45.83</v>
@@ -24245,7 +24245,7 @@
         <v>-2.45</v>
       </c>
       <c r="I315" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J315" t="n">
         <v>45.1</v>
@@ -24320,7 +24320,7 @@
         <v>-9.050000000000001</v>
       </c>
       <c r="I316" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J316" t="n">
         <v>44.77</v>
@@ -24395,7 +24395,7 @@
         <v>33.78</v>
       </c>
       <c r="I317" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J317" t="n">
         <v>44.64</v>
@@ -24470,7 +24470,7 @@
         <v>-2.04</v>
       </c>
       <c r="I318" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J318" t="n">
         <v>44.41</v>
@@ -24545,7 +24545,7 @@
         <v>21.14</v>
       </c>
       <c r="I319" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J319" t="n">
         <v>45.03</v>
@@ -24620,7 +24620,7 @@
         <v>-8.029999999999999</v>
       </c>
       <c r="I320" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J320" t="n">
         <v>45.54</v>
@@ -24695,7 +24695,7 @@
         <v>-0.5</v>
       </c>
       <c r="I321" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J321" t="n">
         <v>46.1</v>
@@ -24774,7 +24774,7 @@
         <v>19.29</v>
       </c>
       <c r="I322" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J322" t="n">
         <v>46.93</v>
@@ -24849,7 +24849,7 @@
         <v>-0.2</v>
       </c>
       <c r="I323" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J323" t="n">
         <v>47.55</v>
@@ -24924,7 +24924,7 @@
         <v>-35.7</v>
       </c>
       <c r="I324" s="4" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J324" s="4" t="n">
         <v>47.35</v>
@@ -25003,7 +25003,7 @@
         <v>5.89</v>
       </c>
       <c r="I325" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J325" t="n">
         <v>46.66</v>
@@ -25078,7 +25078,7 @@
         <v>11.85</v>
       </c>
       <c r="I326" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J326" t="n">
         <v>46.29</v>
@@ -25153,7 +25153,7 @@
         <v>-10.9</v>
       </c>
       <c r="I327" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J327" t="n">
         <v>45.39</v>
@@ -25228,7 +25228,7 @@
         <v>-0.03</v>
       </c>
       <c r="I328" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J328" t="n">
         <v>44.51</v>
@@ -25303,7 +25303,7 @@
         <v>5.82</v>
       </c>
       <c r="I329" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J329" t="n">
         <v>43.3</v>
@@ -25378,7 +25378,7 @@
         <v>-23.21</v>
       </c>
       <c r="I330" s="4" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J330" s="4" t="n">
         <v>41.74</v>
@@ -25457,7 +25457,7 @@
         <v>-9.77</v>
       </c>
       <c r="I331" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J331" t="n">
         <v>40.1</v>
@@ -25536,7 +25536,7 @@
         <v>15.37</v>
       </c>
       <c r="I332" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J332" t="n">
         <v>39.04</v>
@@ -25611,7 +25611,7 @@
         <v>-12.78</v>
       </c>
       <c r="I333" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J333" t="n">
         <v>38.87</v>
@@ -25690,7 +25690,7 @@
         <v>1.58</v>
       </c>
       <c r="I334" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J334" t="n">
         <v>38.48</v>
@@ -25765,7 +25765,7 @@
         <v>3</v>
       </c>
       <c r="I335" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J335" t="n">
         <v>38.18</v>
@@ -25840,7 +25840,7 @@
         <v>-2.28</v>
       </c>
       <c r="I336" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J336" t="n">
         <v>38</v>
@@ -25919,7 +25919,7 @@
         <v>-24.74</v>
       </c>
       <c r="I337" s="4" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J337" s="4" t="n">
         <v>36.94</v>
@@ -25994,7 +25994,7 @@
         <v>14.84</v>
       </c>
       <c r="I338" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J338" t="n">
         <v>36.08</v>
@@ -26069,7 +26069,7 @@
         <v>-9.140000000000001</v>
       </c>
       <c r="I339" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J339" t="n">
         <v>34.68</v>
@@ -26144,7 +26144,7 @@
         <v>-14.72</v>
       </c>
       <c r="I340" s="4" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J340" s="4" t="n">
         <v>33.31</v>
@@ -26223,7 +26223,7 @@
         <v>-2.09</v>
       </c>
       <c r="I341" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J341" t="n">
         <v>31.94</v>
@@ -26302,7 +26302,7 @@
         <v>0.82</v>
       </c>
       <c r="I342" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J342" t="n">
         <v>30.13</v>
@@ -26381,7 +26381,7 @@
         <v>18.03</v>
       </c>
       <c r="I343" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J343" t="n">
         <v>28.5</v>
@@ -26456,7 +26456,7 @@
         <v>-4.46</v>
       </c>
       <c r="I344" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J344" t="n">
         <v>27.79</v>
@@ -26531,7 +26531,7 @@
         <v>6.02</v>
       </c>
       <c r="I345" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J345" t="n">
         <v>27.03</v>
@@ -26606,7 +26606,7 @@
         <v>-18.9</v>
       </c>
       <c r="I346" s="4" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J346" s="4" t="n">
         <v>25.85</v>
@@ -26685,7 +26685,7 @@
         <v>-3.59</v>
       </c>
       <c r="I347" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J347" t="n">
         <v>24.87</v>
@@ -26760,7 +26760,7 @@
         <v>-17.78</v>
       </c>
       <c r="I348" s="4" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J348" s="4" t="n">
         <v>23.73</v>
@@ -26839,7 +26839,7 @@
         <v>-14.63</v>
       </c>
       <c r="I349" s="4" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J349" s="4" t="n">
         <v>22.38</v>
@@ -26918,7 +26918,7 @@
         <v>34.77</v>
       </c>
       <c r="I350" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J350" t="n">
         <v>21.69</v>
@@ -26993,7 +26993,7 @@
         <v>-7.92</v>
       </c>
       <c r="I351" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J351" t="n">
         <v>21.09</v>
@@ -27068,7 +27068,7 @@
         <v>5.87</v>
       </c>
       <c r="I352" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J352" t="n">
         <v>20.32</v>
@@ -27143,7 +27143,7 @@
         <v>20.48</v>
       </c>
       <c r="I353" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J353" t="n">
         <v>19.91</v>
@@ -27218,7 +27218,7 @@
         <v>-3.56</v>
       </c>
       <c r="I354" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J354" t="n">
         <v>19.45</v>
@@ -27293,7 +27293,7 @@
         <v>-8.84</v>
       </c>
       <c r="I355" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J355" t="n">
         <v>18.87</v>
@@ -27368,7 +27368,7 @@
         <v>3.27</v>
       </c>
       <c r="I356" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J356" t="n">
         <v>18.34</v>
@@ -27443,7 +27443,7 @@
         <v>-5.47</v>
       </c>
       <c r="I357" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J357" t="n">
         <v>18.12</v>
@@ -27518,7 +27518,7 @@
         <v>7.5</v>
       </c>
       <c r="I358" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J358" t="n">
         <v>17.8</v>
@@ -27593,7 +27593,7 @@
         <v>15.19</v>
       </c>
       <c r="I359" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J359" t="n">
         <v>17.72</v>
@@ -27668,7 +27668,7 @@
         <v>4.68</v>
       </c>
       <c r="I360" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J360" t="n">
         <v>17.85</v>
@@ -27743,7 +27743,7 @@
         <v>1.55</v>
       </c>
       <c r="I361" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J361" t="n">
         <v>18.02</v>
@@ -27818,7 +27818,7 @@
         <v>8.98</v>
       </c>
       <c r="I362" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J362" t="n">
         <v>18.27</v>
@@ -27893,7 +27893,7 @@
         <v>-24.21</v>
       </c>
       <c r="I363" s="4" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J363" s="4" t="n">
         <v>18.08</v>
@@ -27972,7 +27972,7 @@
         <v>7.12</v>
       </c>
       <c r="I364" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J364" t="n">
         <v>18</v>
@@ -28047,7 +28047,7 @@
         <v>6.38</v>
       </c>
       <c r="I365" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J365" t="n">
         <v>17.91</v>
@@ -28122,7 +28122,7 @@
         <v>0.15</v>
       </c>
       <c r="I366" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J366" t="n">
         <v>18.04</v>
@@ -28197,7 +28197,7 @@
         <v>-7.86</v>
       </c>
       <c r="I367" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J367" t="n">
         <v>18.11</v>
@@ -28272,7 +28272,7 @@
         <v>11.03</v>
       </c>
       <c r="I368" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J368" t="n">
         <v>18.45</v>
@@ -28347,7 +28347,7 @@
         <v>-1.63</v>
       </c>
       <c r="I369" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J369" t="n">
         <v>18.87</v>
@@ -28422,7 +28422,7 @@
         <v>4.49</v>
       </c>
       <c r="I370" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J370" t="n">
         <v>19.12</v>
@@ -28497,7 +28497,7 @@
         <v>-2.99</v>
       </c>
       <c r="I371" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J371" t="n">
         <v>19.41</v>
@@ -28572,7 +28572,7 @@
         <v>0.91</v>
       </c>
       <c r="I372" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J372" t="n">
         <v>19.67</v>
@@ -28647,7 +28647,7 @@
         <v>-8.49</v>
       </c>
       <c r="I373" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J373" t="n">
         <v>19.67</v>
@@ -28726,7 +28726,7 @@
         <v>5.06</v>
       </c>
       <c r="I374" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J374" t="n">
         <v>19.76</v>
@@ -28801,7 +28801,7 @@
         <v>2.68</v>
       </c>
       <c r="I375" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J375" t="n">
         <v>19.95</v>
@@ -28876,7 +28876,7 @@
         <v>13.44</v>
       </c>
       <c r="I376" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J376" t="n">
         <v>20.26</v>
@@ -28951,7 +28951,7 @@
         <v>1.58</v>
       </c>
       <c r="I377" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J377" t="n">
         <v>20.63</v>
@@ -29026,7 +29026,7 @@
         <v>1.51</v>
       </c>
       <c r="I378" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J378" t="n">
         <v>20.96</v>
@@ -29101,7 +29101,7 @@
         <v>-12.52</v>
       </c>
       <c r="I379" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J379" t="n">
         <v>21</v>
@@ -29176,7 +29176,7 @@
         <v>8.970000000000001</v>
       </c>
       <c r="I380" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J380" t="n">
         <v>21.09</v>
@@ -29251,7 +29251,7 @@
         <v>-19.51</v>
       </c>
       <c r="I381" s="4" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J381" s="4" t="n">
         <v>20.94</v>
@@ -29330,7 +29330,7 @@
         <v>0.16</v>
       </c>
       <c r="I382" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J382" t="n">
         <v>20.69</v>
@@ -29405,7 +29405,7 @@
         <v>-1.72</v>
       </c>
       <c r="I383" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J383" t="n">
         <v>20.71</v>
@@ -29480,7 +29480,7 @@
         <v>11.65</v>
       </c>
       <c r="I384" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J384" t="n">
         <v>20.78</v>
@@ -29555,7 +29555,7 @@
         <v>-1.81</v>
       </c>
       <c r="I385" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J385" t="n">
         <v>20.76</v>
@@ -29630,7 +29630,7 @@
         <v>12.52</v>
       </c>
       <c r="I386" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J386" t="n">
         <v>20.87</v>
@@ -29705,7 +29705,7 @@
         <v>5.41</v>
       </c>
       <c r="I387" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J387" t="n">
         <v>21.12</v>
@@ -29780,7 +29780,7 @@
         <v>-10.52</v>
       </c>
       <c r="I388" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J388" t="n">
         <v>21.14</v>
@@ -29855,7 +29855,7 @@
         <v>-5.31</v>
       </c>
       <c r="I389" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J389" t="n">
         <v>21.13</v>
@@ -29934,7 +29934,7 @@
         <v>7.2</v>
       </c>
       <c r="I390" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J390" t="n">
         <v>21.14</v>
@@ -30009,7 +30009,7 @@
         <v>-5.51</v>
       </c>
       <c r="I391" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J391" t="n">
         <v>21.12</v>
@@ -30088,7 +30088,7 @@
         <v>5.25</v>
       </c>
       <c r="I392" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J392" t="n">
         <v>21.14</v>
@@ -30163,7 +30163,7 @@
         <v>-6.75</v>
       </c>
       <c r="I393" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J393" t="n">
         <v>21.18</v>
@@ -30242,7 +30242,7 @@
         <v>5.34</v>
       </c>
       <c r="I394" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J394" t="n">
         <v>21.23</v>
@@ -30317,7 +30317,7 @@
         <v>8.82</v>
       </c>
       <c r="I395" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J395" t="n">
         <v>21.34</v>
@@ -30392,7 +30392,7 @@
         <v>-0.74</v>
       </c>
       <c r="I396" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J396" t="n">
         <v>21.31</v>
@@ -30467,7 +30467,7 @@
         <v>-7.77</v>
       </c>
       <c r="I397" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J397" t="n">
         <v>21.17</v>
@@ -30546,7 +30546,7 @@
         <v>-4.57</v>
       </c>
       <c r="I398" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J398" t="n">
         <v>20.96</v>
@@ -30621,7 +30621,7 @@
         <v>-11.97</v>
       </c>
       <c r="I399" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J399" t="n">
         <v>20.79</v>
@@ -30700,7 +30700,7 @@
         <v>1.13</v>
       </c>
       <c r="I400" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J400" t="n">
         <v>20.52</v>
@@ -30775,7 +30775,7 @@
         <v>-11.82</v>
       </c>
       <c r="I401" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J401" t="n">
         <v>20.38</v>
@@ -30854,7 +30854,7 @@
         <v>-6.48</v>
       </c>
       <c r="I402" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J402" t="n">
         <v>20.19</v>
@@ -30929,7 +30929,7 @@
         <v>-12.16</v>
       </c>
       <c r="I403" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J403" t="n">
         <v>19.92</v>
@@ -31004,7 +31004,7 @@
         <v>-7.12</v>
       </c>
       <c r="I404" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J404" t="n">
         <v>19.5</v>
@@ -31083,7 +31083,7 @@
         <v>-11.41</v>
       </c>
       <c r="I405" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J405" t="n">
         <v>19.03</v>
@@ -31162,7 +31162,7 @@
         <v>12.03</v>
       </c>
       <c r="I406" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J406" t="n">
         <v>18.5</v>
@@ -31241,7 +31241,7 @@
         <v>-4.87</v>
       </c>
       <c r="I407" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J407" t="n">
         <v>17.88</v>
@@ -31320,7 +31320,7 @@
         <v>5.29</v>
       </c>
       <c r="I408" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J408" t="n">
         <v>17.41</v>
@@ -31399,7 +31399,7 @@
         <v>-14.66</v>
       </c>
       <c r="I409" s="4" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J409" s="4" t="n">
         <v>16.91</v>
@@ -31478,7 +31478,7 @@
         <v>3.83</v>
       </c>
       <c r="I410" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J410" t="n">
         <v>16.36</v>
@@ -31557,7 +31557,7 @@
         <v>2.93</v>
       </c>
       <c r="I411" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J411" t="n">
         <v>15.89</v>
@@ -31636,7 +31636,7 @@
         <v>8.91</v>
       </c>
       <c r="I412" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J412" t="n">
         <v>15.41</v>
@@ -31715,7 +31715,7 @@
         <v>16.19</v>
       </c>
       <c r="I413" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J413" t="n">
         <v>15.1</v>
@@ -31790,7 +31790,7 @@
         <v>-7.62</v>
       </c>
       <c r="I414" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J414" t="n">
         <v>14.68</v>
@@ -31836,61 +31836,77 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>KORU</t>
-        </is>
-      </c>
-      <c r="B415" t="inlineStr">
+      <c r="A415" s="4" t="inlineStr">
+        <is>
+          <t>KORU</t>
+        </is>
+      </c>
+      <c r="B415" s="4" t="inlineStr">
         <is>
           <t>2026-10-30</t>
         </is>
       </c>
-      <c r="C415" t="inlineStr"/>
-      <c r="D415" t="inlineStr"/>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
-      <c r="G415" t="n">
-        <v>44283381</v>
-      </c>
-      <c r="H415" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I415" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr"/>
-      <c r="L415" t="inlineStr"/>
-      <c r="M415" t="inlineStr"/>
-      <c r="N415" s="2" t="n">
-        <v>39.21</v>
-      </c>
-      <c r="O415" t="n">
+      <c r="C415" s="4" t="n">
+        <v>10.84</v>
+      </c>
+      <c r="D415" s="4" t="n">
+        <v>11.13</v>
+      </c>
+      <c r="E415" s="4" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="F415" s="4" t="n">
+        <v>10.63</v>
+      </c>
+      <c r="G415" s="4" t="n">
+        <v>44494100</v>
+      </c>
+      <c r="H415" s="5" t="n">
+        <v>-16.5</v>
+      </c>
+      <c r="I415" s="4" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="J415" s="4" t="n">
+        <v>14.06</v>
+      </c>
+      <c r="K415" s="4" t="n">
+        <v>18.45</v>
+      </c>
+      <c r="L415" s="4" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="M415" s="4" t="n">
+        <v>24.43</v>
+      </c>
+      <c r="N415" s="6" t="n">
+        <v>34.08</v>
+      </c>
+      <c r="O415" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="P415" t="inlineStr">
+      <c r="P415" s="4" t="inlineStr">
         <is>
           <t>fear</t>
         </is>
       </c>
-      <c r="Q415" t="inlineStr">
+      <c r="Q415" s="4" t="inlineStr">
         <is>
           <t>2x BUY</t>
         </is>
       </c>
-      <c r="R415" t="inlineStr"/>
-      <c r="S415" t="n">
+      <c r="R415" s="4" t="inlineStr"/>
+      <c r="S415" s="4" t="n">
         <v>4.93</v>
       </c>
-      <c r="T415" s="2" t="n">
+      <c r="T415" s="6" t="n">
         <v>19.4</v>
       </c>
-      <c r="U415" s="2" t="n">
+      <c r="U415" s="6" t="n">
         <v>19.3</v>
       </c>
-      <c r="V415" t="inlineStr"/>
-      <c r="W415" s="2" t="n">
+      <c r="V415" s="4" t="inlineStr"/>
+      <c r="W415" s="6" t="n">
         <v>149.8</v>
       </c>
     </row>
